--- a/data/summary2026.xlsx
+++ b/data/summary2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="276">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -727,6 +727,9 @@
   </si>
   <si>
     <t xml:space="preserve">Jacob Liberta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jorge Minyety</t>
   </si>
   <si>
     <t xml:space="preserve">Owen Macneil</t>
@@ -912,8 +915,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K118" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K118"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K119" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K119"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -3631,31 +3634,31 @@
         <v>84</v>
       </c>
       <c r="C70" t="n">
-        <v>84.6</v>
+        <v>86</v>
       </c>
       <c r="D70" t="n">
-        <v>19</v>
+        <v>21.1</v>
       </c>
       <c r="E70" t="n">
-        <v>65.6</v>
+        <v>64.9</v>
       </c>
       <c r="F70" t="n">
-        <v>19</v>
+        <v>21.1</v>
       </c>
       <c r="G70" t="n">
-        <v>37.8</v>
+        <v>38.8</v>
       </c>
       <c r="H70" t="n">
-        <v>11.1</v>
+        <v>11.9</v>
       </c>
       <c r="I70" t="n">
         <v>33.3</v>
       </c>
       <c r="J70" t="n">
-        <v>50</v>
+        <v>51.9</v>
       </c>
       <c r="K70" t="n">
-        <v>53.8</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="71">
@@ -3701,31 +3704,31 @@
         <v>84</v>
       </c>
       <c r="C72" t="n">
-        <v>77.1</v>
+        <v>78.8</v>
       </c>
       <c r="D72" t="n">
-        <v>31.8</v>
+        <v>31.2</v>
       </c>
       <c r="E72" t="n">
-        <v>45.3</v>
+        <v>47.6</v>
       </c>
       <c r="F72" t="n">
-        <v>31.8</v>
+        <v>31.2</v>
       </c>
       <c r="G72" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="H72" t="n">
-        <v>10.8</v>
+        <v>10.1</v>
       </c>
       <c r="I72" t="n">
-        <v>43.2</v>
+        <v>42.5</v>
       </c>
       <c r="J72" t="n">
-        <v>21.6</v>
+        <v>25</v>
       </c>
       <c r="K72" t="n">
-        <v>61.5</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="73">
@@ -3736,31 +3739,31 @@
         <v>84</v>
       </c>
       <c r="C73" t="n">
-        <v>70</v>
+        <v>70.4</v>
       </c>
       <c r="D73" t="n">
-        <v>35.8</v>
+        <v>33.7</v>
       </c>
       <c r="E73" t="n">
-        <v>34.2</v>
+        <v>36.7</v>
       </c>
       <c r="F73" t="n">
-        <v>35.8</v>
+        <v>33.7</v>
       </c>
       <c r="G73" t="n">
-        <v>28.6</v>
+        <v>29.5</v>
       </c>
       <c r="H73" t="n">
-        <v>6.1</v>
+        <v>8.5</v>
       </c>
       <c r="I73" t="n">
-        <v>52.3</v>
+        <v>51.1</v>
       </c>
       <c r="J73" t="n">
-        <v>20.5</v>
+        <v>21.3</v>
       </c>
       <c r="K73" t="n">
-        <v>47.6</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="74">
@@ -3771,31 +3774,31 @@
         <v>84</v>
       </c>
       <c r="C74" t="n">
-        <v>74.5</v>
+        <v>76.8</v>
       </c>
       <c r="D74" t="n">
-        <v>41</v>
+        <v>42.5</v>
       </c>
       <c r="E74" t="n">
-        <v>33.5</v>
+        <v>34.3</v>
       </c>
       <c r="F74" t="n">
-        <v>41</v>
+        <v>42.5</v>
       </c>
       <c r="G74" t="n">
-        <v>24.6</v>
+        <v>24.3</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>36.8</v>
+        <v>36.1</v>
       </c>
       <c r="J74" t="n">
-        <v>24.6</v>
+        <v>27.9</v>
       </c>
       <c r="K74" t="n">
-        <v>71.7</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="75">
@@ -3806,31 +3809,31 @@
         <v>84</v>
       </c>
       <c r="C75" t="n">
-        <v>70.5</v>
+        <v>71.4</v>
       </c>
       <c r="D75" t="n">
-        <v>18.1</v>
+        <v>20</v>
       </c>
       <c r="E75" t="n">
-        <v>52.4</v>
+        <v>51.4</v>
       </c>
       <c r="F75" t="n">
-        <v>18.1</v>
+        <v>20</v>
       </c>
       <c r="G75" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="H75" t="n">
-        <v>14.5</v>
+        <v>13.6</v>
       </c>
       <c r="I75" t="n">
-        <v>32.6</v>
+        <v>31.9</v>
       </c>
       <c r="J75" t="n">
-        <v>39.5</v>
+        <v>38.3</v>
       </c>
       <c r="K75" t="n">
-        <v>31.7</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="76">
@@ -3841,31 +3844,31 @@
         <v>84</v>
       </c>
       <c r="C76" t="n">
-        <v>73.2</v>
+        <v>73.8</v>
       </c>
       <c r="D76" t="n">
-        <v>31</v>
+        <v>32.7</v>
       </c>
       <c r="E76" t="n">
-        <v>42.2</v>
+        <v>41.1</v>
       </c>
       <c r="F76" t="n">
-        <v>31</v>
+        <v>32.7</v>
       </c>
       <c r="G76" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H76" t="n">
-        <v>9.3</v>
+        <v>8.7</v>
       </c>
       <c r="I76" t="n">
-        <v>51.9</v>
+        <v>51.7</v>
       </c>
       <c r="J76" t="n">
-        <v>22.2</v>
+        <v>20.7</v>
       </c>
       <c r="K76" t="n">
-        <v>28</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="77">
@@ -3911,31 +3914,31 @@
         <v>84</v>
       </c>
       <c r="C78" t="n">
-        <v>66.7</v>
+        <v>69</v>
       </c>
       <c r="D78" t="n">
-        <v>32.7</v>
+        <v>30.6</v>
       </c>
       <c r="E78" t="n">
-        <v>34</v>
+        <v>38.4</v>
       </c>
       <c r="F78" t="n">
-        <v>32.7</v>
+        <v>30.6</v>
       </c>
       <c r="G78" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="H78" t="n">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="I78" t="n">
-        <v>62.2</v>
+        <v>59.2</v>
       </c>
       <c r="J78" t="n">
-        <v>13.3</v>
+        <v>16.3</v>
       </c>
       <c r="K78" t="n">
-        <v>44.4</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="79">
@@ -3946,31 +3949,31 @@
         <v>84</v>
       </c>
       <c r="C79" t="n">
-        <v>72.7</v>
+        <v>72</v>
       </c>
       <c r="D79" t="n">
-        <v>48.5</v>
+        <v>46.5</v>
       </c>
       <c r="E79" t="n">
-        <v>24.2</v>
+        <v>25.5</v>
       </c>
       <c r="F79" t="n">
-        <v>48.5</v>
+        <v>46.5</v>
       </c>
       <c r="G79" t="n">
-        <v>22.6</v>
+        <v>23.7</v>
       </c>
       <c r="H79" t="n">
-        <v>12.5</v>
+        <v>10.8</v>
       </c>
       <c r="I79" t="n">
-        <v>47.6</v>
+        <v>48</v>
       </c>
       <c r="J79" t="n">
-        <v>28.6</v>
+        <v>32</v>
       </c>
       <c r="K79" t="n">
-        <v>57.1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="80">
@@ -3981,25 +3984,31 @@
         <v>84</v>
       </c>
       <c r="C80" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="D80"/>
-      <c r="E80"/>
-      <c r="F80"/>
+        <v>75</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>75</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
       <c r="G80" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="H80" t="n">
         <v>25</v>
       </c>
-      <c r="H80" t="n">
-        <v>28.6</v>
-      </c>
       <c r="I80" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K80" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="81">
@@ -4010,31 +4019,31 @@
         <v>84</v>
       </c>
       <c r="C81" t="n">
-        <v>63.1</v>
+        <v>61.4</v>
       </c>
       <c r="D81" t="n">
-        <v>20.2</v>
+        <v>19.3</v>
       </c>
       <c r="E81" t="n">
-        <v>42.9</v>
+        <v>42.1</v>
       </c>
       <c r="F81" t="n">
-        <v>20.2</v>
+        <v>19.3</v>
       </c>
       <c r="G81" t="n">
         <v>19.4</v>
       </c>
       <c r="H81" t="n">
-        <v>10.3</v>
+        <v>12.2</v>
       </c>
       <c r="I81" t="n">
-        <v>63</v>
+        <v>62.5</v>
       </c>
       <c r="J81" t="n">
-        <v>15.2</v>
+        <v>16.7</v>
       </c>
       <c r="K81" t="n">
-        <v>46.7</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="82">
@@ -4045,31 +4054,31 @@
         <v>84</v>
       </c>
       <c r="C82" t="n">
-        <v>40.9</v>
+        <v>41.3</v>
       </c>
       <c r="D82" t="n">
-        <v>11.5</v>
+        <v>23.7</v>
       </c>
       <c r="E82" t="n">
-        <v>29.4</v>
+        <v>17.6</v>
       </c>
       <c r="F82" t="n">
-        <v>11.5</v>
+        <v>23.7</v>
       </c>
       <c r="G82" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="H82" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I82" t="n">
+        <v>75</v>
+      </c>
+      <c r="J82" t="n">
+        <v>25</v>
+      </c>
+      <c r="K82" t="n">
         <v>26.3</v>
-      </c>
-      <c r="H82" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I82" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="J82" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="K82" t="n">
-        <v>22.2</v>
       </c>
     </row>
     <row r="83">
@@ -4179,31 +4188,31 @@
         <v>98</v>
       </c>
       <c r="C86" t="n">
-        <v>83.3</v>
+        <v>85.2</v>
       </c>
       <c r="D86" t="n">
-        <v>27</v>
+        <v>33.3</v>
       </c>
       <c r="E86" t="n">
-        <v>56.3</v>
+        <v>51.9</v>
       </c>
       <c r="F86" t="n">
-        <v>27</v>
+        <v>33.3</v>
       </c>
       <c r="G86" t="n">
-        <v>42.6</v>
+        <v>44.9</v>
       </c>
       <c r="H86" t="n">
-        <v>17.6</v>
+        <v>15.8</v>
       </c>
       <c r="I86" t="n">
+        <v>50</v>
+      </c>
+      <c r="J86" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="K86" t="n">
         <v>47.1</v>
-      </c>
-      <c r="J86" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="K86" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="87">
@@ -4214,31 +4223,31 @@
         <v>98</v>
       </c>
       <c r="C87" t="n">
-        <v>71</v>
+        <v>75.7</v>
       </c>
       <c r="D87" t="n">
-        <v>29.4</v>
+        <v>33.3</v>
       </c>
       <c r="E87" t="n">
-        <v>41.6</v>
+        <v>42.4</v>
       </c>
       <c r="F87" t="n">
-        <v>29.4</v>
+        <v>33.3</v>
       </c>
       <c r="G87" t="n">
-        <v>19.5</v>
+        <v>19.1</v>
       </c>
       <c r="H87" t="n">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="I87" t="n">
-        <v>42.1</v>
+        <v>41.5</v>
       </c>
       <c r="J87" t="n">
-        <v>21.1</v>
+        <v>22</v>
       </c>
       <c r="K87" t="n">
-        <v>34.2</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="88">
@@ -4249,31 +4258,31 @@
         <v>98</v>
       </c>
       <c r="C88" t="n">
-        <v>67.2</v>
+        <v>68.3</v>
       </c>
       <c r="D88" t="n">
-        <v>6.9</v>
+        <v>13.1</v>
       </c>
       <c r="E88" t="n">
-        <v>60.3</v>
+        <v>55.2</v>
       </c>
       <c r="F88" t="n">
-        <v>6.9</v>
+        <v>13.1</v>
       </c>
       <c r="G88" t="n">
-        <v>30.4</v>
+        <v>28.3</v>
       </c>
       <c r="H88" t="n">
-        <v>25.7</v>
+        <v>24.1</v>
       </c>
       <c r="I88" t="n">
-        <v>22.2</v>
+        <v>24.4</v>
       </c>
       <c r="J88" t="n">
-        <v>36.1</v>
+        <v>34.1</v>
       </c>
       <c r="K88" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="89">
@@ -4284,31 +4293,31 @@
         <v>98</v>
       </c>
       <c r="C89" t="n">
-        <v>68</v>
+        <v>68.5</v>
       </c>
       <c r="D89" t="n">
-        <v>25</v>
+        <v>28.4</v>
       </c>
       <c r="E89" t="n">
-        <v>43</v>
+        <v>40.1</v>
       </c>
       <c r="F89" t="n">
-        <v>25</v>
+        <v>28.4</v>
       </c>
       <c r="G89" t="n">
-        <v>26.5</v>
+        <v>25.4</v>
       </c>
       <c r="H89" t="n">
-        <v>10.8</v>
+        <v>10.1</v>
       </c>
       <c r="I89" t="n">
-        <v>40.5</v>
+        <v>38.6</v>
       </c>
       <c r="J89" t="n">
-        <v>33.3</v>
+        <v>34.1</v>
       </c>
       <c r="K89" t="n">
-        <v>54.8</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="90">
@@ -4319,31 +4328,31 @@
         <v>98</v>
       </c>
       <c r="C90" t="n">
-        <v>81.2</v>
+        <v>84.2</v>
       </c>
       <c r="D90" t="n">
-        <v>25.7</v>
+        <v>28.6</v>
       </c>
       <c r="E90" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="F90" t="n">
-        <v>25.7</v>
+        <v>28.6</v>
       </c>
       <c r="G90" t="n">
-        <v>37.4</v>
+        <v>36.1</v>
       </c>
       <c r="H90" t="n">
-        <v>9.3</v>
+        <v>8.5</v>
       </c>
       <c r="I90" t="n">
-        <v>34.6</v>
+        <v>33.3</v>
       </c>
       <c r="J90" t="n">
-        <v>42.3</v>
+        <v>36.7</v>
       </c>
       <c r="K90" t="n">
-        <v>57.7</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="91">
@@ -4424,28 +4433,28 @@
         <v>98</v>
       </c>
       <c r="C93" t="n">
-        <v>77.1</v>
+        <v>77.6</v>
       </c>
       <c r="D93" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E93" t="n">
-        <v>51.1</v>
+        <v>48.6</v>
       </c>
       <c r="F93" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G93" t="n">
-        <v>38.2</v>
+        <v>37.9</v>
       </c>
       <c r="H93" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="I93" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="J93" t="n">
-        <v>30</v>
+        <v>31.2</v>
       </c>
       <c r="K93" t="n">
         <v>50</v>
@@ -4459,31 +4468,31 @@
         <v>98</v>
       </c>
       <c r="C94" t="n">
-        <v>63.6</v>
+        <v>64.3</v>
       </c>
       <c r="D94" t="n">
-        <v>15.1</v>
+        <v>19.4</v>
       </c>
       <c r="E94" t="n">
-        <v>48.5</v>
+        <v>44.9</v>
       </c>
       <c r="F94" t="n">
-        <v>15.1</v>
+        <v>19.4</v>
       </c>
       <c r="G94" t="n">
-        <v>16.5</v>
+        <v>17.3</v>
       </c>
       <c r="H94" t="n">
-        <v>8.7</v>
+        <v>8.1</v>
       </c>
       <c r="I94" t="n">
-        <v>35.3</v>
+        <v>36.4</v>
       </c>
       <c r="J94" t="n">
-        <v>25.5</v>
+        <v>23.6</v>
       </c>
       <c r="K94" t="n">
-        <v>43.1</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="95">
@@ -4494,31 +4503,31 @@
         <v>98</v>
       </c>
       <c r="C95" t="n">
-        <v>61</v>
+        <v>61.9</v>
       </c>
       <c r="D95" t="n">
-        <v>14.9</v>
+        <v>18.2</v>
       </c>
       <c r="E95" t="n">
-        <v>46.1</v>
+        <v>43.7</v>
       </c>
       <c r="F95" t="n">
-        <v>14.9</v>
+        <v>18.2</v>
       </c>
       <c r="G95" t="n">
-        <v>18.4</v>
+        <v>18.8</v>
       </c>
       <c r="H95" t="n">
-        <v>12.1</v>
+        <v>11.3</v>
       </c>
       <c r="I95" t="n">
-        <v>35.7</v>
+        <v>33.3</v>
       </c>
       <c r="J95" t="n">
-        <v>31</v>
+        <v>28.9</v>
       </c>
       <c r="K95" t="n">
-        <v>47.6</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="96">
@@ -4529,31 +4538,31 @@
         <v>98</v>
       </c>
       <c r="C96" t="n">
-        <v>60</v>
+        <v>61.7</v>
       </c>
       <c r="D96" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="E96" t="n">
-        <v>45</v>
+        <v>43.2</v>
       </c>
       <c r="F96" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="G96" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="H96" t="n">
-        <v>11.5</v>
+        <v>10.8</v>
       </c>
       <c r="I96" t="n">
-        <v>56.8</v>
+        <v>57.5</v>
       </c>
       <c r="J96" t="n">
-        <v>24.3</v>
+        <v>25</v>
       </c>
       <c r="K96" t="n">
-        <v>54.1</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="97">
@@ -4564,31 +4573,31 @@
         <v>113</v>
       </c>
       <c r="C97" t="n">
-        <v>83.3</v>
+        <v>66.7</v>
       </c>
       <c r="D97" t="n">
-        <v>68.4</v>
+        <v>57.7</v>
       </c>
       <c r="E97" t="n">
-        <v>14.9</v>
+        <v>9</v>
       </c>
       <c r="F97" t="n">
-        <v>68.4</v>
+        <v>57.7</v>
       </c>
       <c r="G97" t="n">
-        <v>26.3</v>
+        <v>27.3</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>42.9</v>
+        <v>44.4</v>
       </c>
       <c r="J97" t="n">
-        <v>42.9</v>
+        <v>44.4</v>
       </c>
       <c r="K97" t="n">
-        <v>42.9</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="98">
@@ -4634,31 +4643,31 @@
         <v>113</v>
       </c>
       <c r="C99" t="n">
-        <v>65.4</v>
+        <v>65.5</v>
       </c>
       <c r="D99" t="n">
-        <v>16.1</v>
+        <v>17.9</v>
       </c>
       <c r="E99" t="n">
-        <v>49.3</v>
+        <v>47.6</v>
       </c>
       <c r="F99" t="n">
-        <v>16.1</v>
+        <v>17.9</v>
       </c>
       <c r="G99" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="H99" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="I99" t="n">
-        <v>29.4</v>
+        <v>35</v>
       </c>
       <c r="J99" t="n">
-        <v>29.4</v>
+        <v>30</v>
       </c>
       <c r="K99" t="n">
-        <v>53.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="100">
@@ -4672,28 +4681,28 @@
         <v>63.3</v>
       </c>
       <c r="D100" t="n">
-        <v>28.4</v>
+        <v>29.4</v>
       </c>
       <c r="E100" t="n">
-        <v>34.9</v>
+        <v>33.9</v>
       </c>
       <c r="F100" t="n">
-        <v>28.4</v>
+        <v>29.4</v>
       </c>
       <c r="G100" t="n">
-        <v>31.2</v>
+        <v>30.9</v>
       </c>
       <c r="H100" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="I100" t="n">
-        <v>36.4</v>
+        <v>35.3</v>
       </c>
       <c r="J100" t="n">
-        <v>24.2</v>
+        <v>23.5</v>
       </c>
       <c r="K100" t="n">
-        <v>36.4</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="101">
@@ -4704,31 +4713,31 @@
         <v>113</v>
       </c>
       <c r="C101" t="n">
-        <v>77.3</v>
+        <v>77.6</v>
       </c>
       <c r="D101" t="n">
-        <v>34.1</v>
+        <v>35.6</v>
       </c>
       <c r="E101" t="n">
-        <v>43.2</v>
+        <v>42</v>
       </c>
       <c r="F101" t="n">
-        <v>34.1</v>
+        <v>35.6</v>
       </c>
       <c r="G101" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="H101" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I101" t="n">
-        <v>40</v>
+        <v>38.5</v>
       </c>
       <c r="J101" t="n">
-        <v>24</v>
+        <v>26.9</v>
       </c>
       <c r="K101" t="n">
-        <v>24.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="102">
@@ -4742,28 +4751,28 @@
         <v>56.9</v>
       </c>
       <c r="D102" t="n">
-        <v>27.5</v>
+        <v>28.1</v>
       </c>
       <c r="E102" t="n">
-        <v>29.4</v>
+        <v>28.8</v>
       </c>
       <c r="F102" t="n">
-        <v>27.5</v>
+        <v>28.1</v>
       </c>
       <c r="G102" t="n">
-        <v>14.9</v>
+        <v>15.8</v>
       </c>
       <c r="H102" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="I102" t="n">
-        <v>62.5</v>
+        <v>61</v>
       </c>
       <c r="J102" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="K102" t="n">
-        <v>50</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="103">
@@ -4801,31 +4810,31 @@
         <v>113</v>
       </c>
       <c r="C104" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
       <c r="D104" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="E104" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="F104" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="G104" t="n">
-        <v>7.2</v>
+        <v>7.9</v>
       </c>
       <c r="H104" t="n">
-        <v>12.2</v>
+        <v>11.7</v>
       </c>
       <c r="I104" t="n">
-        <v>59.3</v>
+        <v>58.2</v>
       </c>
       <c r="J104" t="n">
-        <v>16.7</v>
+        <v>16.4</v>
       </c>
       <c r="K104" t="n">
-        <v>20.8</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="105">
@@ -4871,31 +4880,31 @@
         <v>113</v>
       </c>
       <c r="C106" t="n">
-        <v>72.6</v>
+        <v>73.2</v>
       </c>
       <c r="D106" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="E106" t="n">
-        <v>45.2</v>
+        <v>45.9</v>
       </c>
       <c r="F106" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="G106" t="n">
-        <v>20.3</v>
+        <v>19.9</v>
       </c>
       <c r="H106" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="I106" t="n">
-        <v>39.1</v>
+        <v>40.3</v>
       </c>
       <c r="J106" t="n">
-        <v>31.9</v>
+        <v>30.6</v>
       </c>
       <c r="K106" t="n">
-        <v>42</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="107">
@@ -4944,28 +4953,28 @@
         <v>59.5</v>
       </c>
       <c r="D108" t="n">
-        <v>20</v>
+        <v>20.9</v>
       </c>
       <c r="E108" t="n">
-        <v>39.5</v>
+        <v>38.6</v>
       </c>
       <c r="F108" t="n">
-        <v>20</v>
+        <v>20.9</v>
       </c>
       <c r="G108" t="n">
-        <v>19</v>
+        <v>18.6</v>
       </c>
       <c r="H108" t="n">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="I108" t="n">
+        <v>50</v>
+      </c>
+      <c r="J108" t="n">
+        <v>25</v>
+      </c>
+      <c r="K108" t="n">
         <v>52.6</v>
-      </c>
-      <c r="J108" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="K108" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="109">
@@ -4976,31 +4985,31 @@
         <v>113</v>
       </c>
       <c r="C109" t="n">
-        <v>69.1</v>
+        <v>69</v>
       </c>
       <c r="D109" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="E109" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="F109" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="G109" t="n">
-        <v>37</v>
+        <v>35.9</v>
       </c>
       <c r="H109" t="n">
-        <v>8.2</v>
+        <v>7.9</v>
       </c>
       <c r="I109" t="n">
-        <v>48.8</v>
+        <v>50</v>
       </c>
       <c r="J109" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K109" t="n">
-        <v>40.9</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="110">
@@ -5011,31 +5020,31 @@
         <v>113</v>
       </c>
       <c r="C110" t="n">
-        <v>72.7</v>
+        <v>74.4</v>
       </c>
       <c r="D110" t="n">
-        <v>21.4</v>
+        <v>22.9</v>
       </c>
       <c r="E110" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
       <c r="F110" t="n">
-        <v>21.4</v>
+        <v>22.9</v>
       </c>
       <c r="G110" t="n">
-        <v>29.4</v>
+        <v>29.7</v>
       </c>
       <c r="H110" t="n">
-        <v>10.1</v>
+        <v>10.7</v>
       </c>
       <c r="I110" t="n">
-        <v>44.9</v>
+        <v>43.1</v>
       </c>
       <c r="J110" t="n">
-        <v>24.5</v>
+        <v>27.5</v>
       </c>
       <c r="K110" t="n">
-        <v>52.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="111">
@@ -5046,31 +5055,31 @@
         <v>113</v>
       </c>
       <c r="C111" t="n">
-        <v>71.9</v>
+        <v>72.9</v>
       </c>
       <c r="D111" t="n">
-        <v>27.8</v>
+        <v>28.9</v>
       </c>
       <c r="E111" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="F111" t="n">
-        <v>27.8</v>
+        <v>28.9</v>
       </c>
       <c r="G111" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="H111" t="n">
-        <v>9.3</v>
+        <v>8.9</v>
       </c>
       <c r="I111" t="n">
-        <v>42.3</v>
+        <v>40</v>
       </c>
       <c r="J111" t="n">
-        <v>36.5</v>
+        <v>40</v>
       </c>
       <c r="K111" t="n">
-        <v>55.8</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="112">
@@ -5108,31 +5117,31 @@
         <v>113</v>
       </c>
       <c r="C113" t="n">
-        <v>63</v>
+        <v>65.5</v>
       </c>
       <c r="D113" t="n">
-        <v>25</v>
+        <v>25.9</v>
       </c>
       <c r="E113" t="n">
-        <v>38</v>
+        <v>39.6</v>
       </c>
       <c r="F113" t="n">
-        <v>25</v>
+        <v>25.9</v>
       </c>
       <c r="G113" t="n">
-        <v>16.1</v>
+        <v>17.1</v>
       </c>
       <c r="H113" t="n">
-        <v>15.8</v>
+        <v>14.3</v>
       </c>
       <c r="I113" t="n">
-        <v>53.8</v>
+        <v>50</v>
       </c>
       <c r="J113" t="n">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="K113" t="n">
-        <v>38.5</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="114">
@@ -5802,31 +5811,31 @@
         <v>151</v>
       </c>
       <c r="C133" t="n">
-        <v>69.1</v>
+        <v>71.3</v>
       </c>
       <c r="D133" t="n">
-        <v>17.1</v>
+        <v>20</v>
       </c>
       <c r="E133" t="n">
-        <v>52</v>
+        <v>51.3</v>
       </c>
       <c r="F133" t="n">
-        <v>17.1</v>
+        <v>20</v>
       </c>
       <c r="G133" t="n">
-        <v>32.3</v>
+        <v>32.7</v>
       </c>
       <c r="H133" t="n">
-        <v>10.5</v>
+        <v>9.7</v>
       </c>
       <c r="I133" t="n">
         <v>50</v>
       </c>
       <c r="J133" t="n">
-        <v>18.4</v>
+        <v>20</v>
       </c>
       <c r="K133" t="n">
-        <v>40.6</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="134">
@@ -5837,31 +5846,31 @@
         <v>151</v>
       </c>
       <c r="C134" t="n">
-        <v>69.8</v>
+        <v>70.5</v>
       </c>
       <c r="D134" t="n">
-        <v>25.8</v>
+        <v>25.3</v>
       </c>
       <c r="E134" t="n">
-        <v>44</v>
+        <v>45.2</v>
       </c>
       <c r="F134" t="n">
-        <v>25.8</v>
+        <v>25.3</v>
       </c>
       <c r="G134" t="n">
-        <v>17.6</v>
+        <v>17.1</v>
       </c>
       <c r="H134" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="I134" t="n">
-        <v>57.1</v>
+        <v>55.6</v>
       </c>
       <c r="J134" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="K134" t="n">
-        <v>36.8</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="135">
@@ -5942,31 +5951,31 @@
         <v>151</v>
       </c>
       <c r="C137" t="n">
-        <v>64.4</v>
+        <v>63.9</v>
       </c>
       <c r="D137" t="n">
-        <v>15.2</v>
+        <v>17.6</v>
       </c>
       <c r="E137" t="n">
-        <v>49.2</v>
+        <v>46.3</v>
       </c>
       <c r="F137" t="n">
-        <v>15.2</v>
+        <v>17.6</v>
       </c>
       <c r="G137" t="n">
-        <v>9.2</v>
+        <v>10.8</v>
       </c>
       <c r="H137" t="n">
-        <v>16</v>
+        <v>16.3</v>
       </c>
       <c r="I137" t="n">
-        <v>63.2</v>
+        <v>62.9</v>
       </c>
       <c r="J137" t="n">
-        <v>19.1</v>
+        <v>18.6</v>
       </c>
       <c r="K137" t="n">
-        <v>39.1</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="138">
@@ -5977,31 +5986,31 @@
         <v>151</v>
       </c>
       <c r="C138" t="n">
-        <v>82.4</v>
+        <v>81.8</v>
       </c>
       <c r="D138" t="n">
-        <v>16.8</v>
+        <v>20.9</v>
       </c>
       <c r="E138" t="n">
-        <v>65.6</v>
+        <v>60.9</v>
       </c>
       <c r="F138" t="n">
-        <v>16.8</v>
+        <v>20.9</v>
       </c>
       <c r="G138" t="n">
-        <v>21.7</v>
+        <v>21.2</v>
       </c>
       <c r="H138" t="n">
-        <v>11.2</v>
+        <v>10.7</v>
       </c>
       <c r="I138" t="n">
-        <v>34.4</v>
+        <v>33.3</v>
       </c>
       <c r="J138" t="n">
-        <v>36.1</v>
+        <v>36.5</v>
       </c>
       <c r="K138" t="n">
-        <v>35.7</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="139">
@@ -6012,31 +6021,31 @@
         <v>151</v>
       </c>
       <c r="C139" t="n">
-        <v>52.3</v>
+        <v>51.8</v>
       </c>
       <c r="D139" t="n">
-        <v>20.2</v>
+        <v>21.2</v>
       </c>
       <c r="E139" t="n">
-        <v>32.1</v>
+        <v>30.6</v>
       </c>
       <c r="F139" t="n">
-        <v>20.2</v>
+        <v>21.2</v>
       </c>
       <c r="G139" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="H139" t="n">
-        <v>14.7</v>
+        <v>13.9</v>
       </c>
       <c r="I139" t="n">
-        <v>47.5</v>
+        <v>48.8</v>
       </c>
       <c r="J139" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="K139" t="n">
-        <v>27.8</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="140">
@@ -6047,31 +6056,31 @@
         <v>151</v>
       </c>
       <c r="C140" t="n">
-        <v>56</v>
+        <v>55.3</v>
       </c>
       <c r="D140" t="n">
-        <v>20.6</v>
+        <v>21.5</v>
       </c>
       <c r="E140" t="n">
-        <v>35.4</v>
+        <v>33.8</v>
       </c>
       <c r="F140" t="n">
-        <v>20.6</v>
+        <v>21.5</v>
       </c>
       <c r="G140" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="H140" t="n">
-        <v>12.1</v>
+        <v>12.9</v>
       </c>
       <c r="I140" t="n">
-        <v>42.9</v>
+        <v>42.2</v>
       </c>
       <c r="J140" t="n">
-        <v>28.6</v>
+        <v>28.9</v>
       </c>
       <c r="K140" t="n">
-        <v>58.3</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="141">
@@ -6082,31 +6091,31 @@
         <v>151</v>
       </c>
       <c r="C141" t="n">
-        <v>58.2</v>
+        <v>58.9</v>
       </c>
       <c r="D141" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="E141" t="n">
-        <v>36.2</v>
+        <v>36.4</v>
       </c>
       <c r="F141" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="G141" t="n">
         <v>9</v>
       </c>
       <c r="H141" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="I141" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J141" t="n">
-        <v>16</v>
+        <v>15.6</v>
       </c>
       <c r="K141" t="n">
-        <v>29.6</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="142">
@@ -6120,28 +6129,28 @@
         <v>72.4</v>
       </c>
       <c r="D142" t="n">
-        <v>12.6</v>
+        <v>14.8</v>
       </c>
       <c r="E142" t="n">
-        <v>59.8</v>
+        <v>57.6</v>
       </c>
       <c r="F142" t="n">
-        <v>12.6</v>
+        <v>14.8</v>
       </c>
       <c r="G142" t="n">
-        <v>31.3</v>
+        <v>29.7</v>
       </c>
       <c r="H142" t="n">
-        <v>14.4</v>
+        <v>13.8</v>
       </c>
       <c r="I142" t="n">
-        <v>28.8</v>
+        <v>30.4</v>
       </c>
       <c r="J142" t="n">
-        <v>34.6</v>
+        <v>33.9</v>
       </c>
       <c r="K142" t="n">
-        <v>56.8</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="143">
@@ -6187,31 +6196,31 @@
         <v>151</v>
       </c>
       <c r="C144" t="n">
-        <v>75.6</v>
+        <v>75.2</v>
       </c>
       <c r="D144" t="n">
         <v>21.8</v>
       </c>
       <c r="E144" t="n">
-        <v>53.8</v>
+        <v>53.4</v>
       </c>
       <c r="F144" t="n">
         <v>21.8</v>
       </c>
       <c r="G144" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="H144" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="I144" t="n">
-        <v>32.8</v>
+        <v>32.3</v>
       </c>
       <c r="J144" t="n">
-        <v>31.1</v>
+        <v>30.6</v>
       </c>
       <c r="K144" t="n">
-        <v>49.1</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="145">
@@ -6278,31 +6287,31 @@
         <v>165</v>
       </c>
       <c r="C147" t="n">
-        <v>67.1</v>
+        <v>67.3</v>
       </c>
       <c r="D147" t="n">
-        <v>24.2</v>
+        <v>24.5</v>
       </c>
       <c r="E147" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="F147" t="n">
-        <v>24.2</v>
+        <v>24.5</v>
       </c>
       <c r="G147" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="H147" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="I147" t="n">
-        <v>48.8</v>
+        <v>48.6</v>
       </c>
       <c r="J147" t="n">
-        <v>23.2</v>
+        <v>23.5</v>
       </c>
       <c r="K147" t="n">
-        <v>39.3</v>
+        <v>39.4</v>
       </c>
     </row>
   </sheetData>
@@ -8323,13 +8332,13 @@
         <v>84</v>
       </c>
       <c r="C58" t="n">
-        <v>66.7</v>
+        <v>68.2</v>
       </c>
       <c r="D58" t="n">
-        <v>66.7</v>
+        <v>67.2</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="F58" t="n">
         <v>50</v>
@@ -8338,16 +8347,16 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>38.5</v>
+        <v>37.5</v>
       </c>
       <c r="I58" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="J58" t="n">
-        <v>4.2</v>
+        <v>6.7</v>
       </c>
       <c r="K58" t="n">
-        <v>5.6</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="59">
@@ -8638,31 +8647,31 @@
         <v>84</v>
       </c>
       <c r="C67" t="n">
-        <v>61.4</v>
+        <v>63.1</v>
       </c>
       <c r="D67" t="n">
-        <v>61.6</v>
+        <v>62.4</v>
       </c>
       <c r="E67" t="n">
-        <v>30.1</v>
+        <v>31.7</v>
       </c>
       <c r="F67" t="n">
-        <v>47.8</v>
+        <v>52.7</v>
       </c>
       <c r="G67" t="n">
-        <v>10.8</v>
+        <v>8.9</v>
       </c>
       <c r="H67" t="n">
-        <v>41.7</v>
+        <v>38.2</v>
       </c>
       <c r="I67" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="J67" t="n">
-        <v>29.6</v>
+        <v>28</v>
       </c>
       <c r="K67" t="n">
-        <v>15.7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="68">
@@ -8708,31 +8717,31 @@
         <v>98</v>
       </c>
       <c r="C69" t="n">
-        <v>43.2</v>
+        <v>40</v>
       </c>
       <c r="D69" t="n">
-        <v>48.1</v>
+        <v>47.8</v>
       </c>
       <c r="E69" t="n">
-        <v>11.5</v>
+        <v>13.2</v>
       </c>
       <c r="F69" t="n">
-        <v>55</v>
+        <v>52.4</v>
       </c>
       <c r="G69" t="n">
-        <v>22.7</v>
+        <v>22</v>
       </c>
       <c r="H69" t="n">
-        <v>45</v>
+        <v>43.5</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>39</v>
+        <v>34.8</v>
       </c>
       <c r="K69" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -8881,31 +8890,31 @@
         <v>98</v>
       </c>
       <c r="C74" t="n">
-        <v>55</v>
+        <v>57.4</v>
       </c>
       <c r="D74" t="n">
-        <v>56</v>
+        <v>57.6</v>
       </c>
       <c r="E74" t="n">
-        <v>18.8</v>
+        <v>21.9</v>
       </c>
       <c r="F74" t="n">
-        <v>21.7</v>
+        <v>22.2</v>
       </c>
       <c r="G74" t="n">
-        <v>9.8</v>
+        <v>8.2</v>
       </c>
       <c r="H74" t="n">
-        <v>43.3</v>
+        <v>42.9</v>
       </c>
       <c r="I74" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
-        <v>22.1</v>
+        <v>21.8</v>
       </c>
       <c r="K74" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
@@ -8984,31 +8993,31 @@
         <v>98</v>
       </c>
       <c r="C77" t="n">
-        <v>68.3</v>
+        <v>68.2</v>
       </c>
       <c r="D77" t="n">
-        <v>66.4</v>
+        <v>66.2</v>
       </c>
       <c r="E77" t="n">
-        <v>20.7</v>
+        <v>26.1</v>
       </c>
       <c r="F77" t="n">
-        <v>30</v>
+        <v>33.3</v>
       </c>
       <c r="G77" t="n">
-        <v>8.5</v>
+        <v>8.2</v>
       </c>
       <c r="H77" t="n">
-        <v>45.8</v>
+        <v>45</v>
       </c>
       <c r="I77" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J77" t="n">
-        <v>25.7</v>
+        <v>25</v>
       </c>
       <c r="K77" t="n">
-        <v>6.1</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="78">
@@ -9019,31 +9028,31 @@
         <v>98</v>
       </c>
       <c r="C78" t="n">
-        <v>52.2</v>
+        <v>63.6</v>
       </c>
       <c r="D78" t="n">
-        <v>55.6</v>
+        <v>63.1</v>
       </c>
       <c r="E78" t="n">
-        <v>24.5</v>
+        <v>35.4</v>
       </c>
       <c r="F78" t="n">
-        <v>40.4</v>
+        <v>38.5</v>
       </c>
       <c r="G78" t="n">
-        <v>10.5</v>
+        <v>9.1</v>
       </c>
       <c r="H78" t="n">
-        <v>26.4</v>
+        <v>54.5</v>
       </c>
       <c r="I78" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>25.3</v>
+        <v>23.5</v>
       </c>
       <c r="K78" t="n">
-        <v>7.9</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="79">
@@ -9054,31 +9063,31 @@
         <v>98</v>
       </c>
       <c r="C79" t="n">
-        <v>50.8</v>
+        <v>52.2</v>
       </c>
       <c r="D79" t="n">
-        <v>58.6</v>
+        <v>55.6</v>
       </c>
       <c r="E79" t="n">
-        <v>23.2</v>
+        <v>24.5</v>
       </c>
       <c r="F79" t="n">
-        <v>36.4</v>
+        <v>40.4</v>
       </c>
       <c r="G79" t="n">
-        <v>11.9</v>
+        <v>10.5</v>
       </c>
       <c r="H79" t="n">
-        <v>60</v>
+        <v>26.4</v>
       </c>
       <c r="I79" t="n">
-        <v>1.7</v>
+        <v>6.1</v>
       </c>
       <c r="J79" t="n">
-        <v>21.8</v>
+        <v>25.3</v>
       </c>
       <c r="K79" t="n">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="80">
@@ -9086,34 +9095,34 @@
         <v>240</v>
       </c>
       <c r="B80" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C80" t="n">
-        <v>66.7</v>
+        <v>50.8</v>
       </c>
       <c r="D80" t="n">
-        <v>65.9</v>
+        <v>58.6</v>
       </c>
       <c r="E80" t="n">
-        <v>33.3</v>
+        <v>23.2</v>
       </c>
       <c r="F80" t="n">
-        <v>25</v>
+        <v>36.4</v>
       </c>
       <c r="G80" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="H80" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="J80" t="n">
-        <v>18.9</v>
+        <v>21.8</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="81">
@@ -9124,28 +9133,28 @@
         <v>113</v>
       </c>
       <c r="C81" t="n">
-        <v>56.7</v>
+        <v>66.7</v>
       </c>
       <c r="D81" t="n">
-        <v>55.3</v>
+        <v>65.9</v>
       </c>
       <c r="E81" t="n">
-        <v>23.5</v>
+        <v>33.3</v>
       </c>
       <c r="F81" t="n">
-        <v>41.7</v>
+        <v>25</v>
       </c>
       <c r="G81" t="n">
-        <v>16.7</v>
+        <v>12</v>
       </c>
       <c r="H81" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="I81" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>36.2</v>
+        <v>18.9</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -9159,31 +9168,31 @@
         <v>113</v>
       </c>
       <c r="C82" t="n">
-        <v>59.8</v>
+        <v>54.5</v>
       </c>
       <c r="D82" t="n">
-        <v>65.7</v>
+        <v>56.9</v>
       </c>
       <c r="E82" t="n">
-        <v>24.5</v>
+        <v>26.9</v>
       </c>
       <c r="F82" t="n">
-        <v>43.2</v>
+        <v>40</v>
       </c>
       <c r="G82" t="n">
-        <v>5.3</v>
+        <v>15.2</v>
       </c>
       <c r="H82" t="n">
-        <v>48.8</v>
+        <v>31.8</v>
       </c>
       <c r="I82" t="n">
-        <v>2.7</v>
+        <v>9.1</v>
       </c>
       <c r="J82" t="n">
-        <v>19.8</v>
+        <v>33.9</v>
       </c>
       <c r="K82" t="n">
-        <v>8.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -9194,31 +9203,31 @@
         <v>113</v>
       </c>
       <c r="C83" t="n">
-        <v>65.1</v>
+        <v>59.8</v>
       </c>
       <c r="D83" t="n">
-        <v>66.7</v>
+        <v>65.7</v>
       </c>
       <c r="E83" t="n">
-        <v>38</v>
+        <v>24.5</v>
       </c>
       <c r="F83" t="n">
-        <v>66.7</v>
+        <v>43.2</v>
       </c>
       <c r="G83" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="H83" t="n">
-        <v>60.9</v>
+        <v>48.8</v>
       </c>
       <c r="I83" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J83" t="n">
-        <v>32.9</v>
+        <v>19.8</v>
       </c>
       <c r="K83" t="n">
-        <v>30.2</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="84">
@@ -9229,31 +9238,31 @@
         <v>113</v>
       </c>
       <c r="C84" t="n">
-        <v>70</v>
+        <v>61.2</v>
       </c>
       <c r="D84" t="n">
-        <v>67.4</v>
+        <v>64.6</v>
       </c>
       <c r="E84" t="n">
-        <v>36.8</v>
+        <v>35.2</v>
       </c>
       <c r="F84" t="n">
         <v>66.7</v>
       </c>
       <c r="G84" t="n">
-        <v>7.5</v>
+        <v>10.2</v>
       </c>
       <c r="H84" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I84" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
-        <v>34.3</v>
+        <v>36.8</v>
       </c>
       <c r="K84" t="n">
-        <v>27.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="85">
@@ -9264,31 +9273,31 @@
         <v>113</v>
       </c>
       <c r="C85" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D85" t="n">
-        <v>65.8</v>
+        <v>67.4</v>
       </c>
       <c r="E85" t="n">
-        <v>21.9</v>
+        <v>36.8</v>
       </c>
       <c r="F85" t="n">
-        <v>28.6</v>
+        <v>66.7</v>
       </c>
       <c r="G85" t="n">
-        <v>4.9</v>
+        <v>7.5</v>
       </c>
       <c r="H85" t="n">
-        <v>63.6</v>
+        <v>50</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J85" t="n">
-        <v>18.2</v>
+        <v>34.3</v>
       </c>
       <c r="K85" t="n">
-        <v>9.7</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="86">
@@ -9299,31 +9308,31 @@
         <v>113</v>
       </c>
       <c r="C86" t="n">
-        <v>74.1</v>
+        <v>57.8</v>
       </c>
       <c r="D86" t="n">
-        <v>68.3</v>
+        <v>64.2</v>
       </c>
       <c r="E86" t="n">
-        <v>41.4</v>
+        <v>24.4</v>
       </c>
       <c r="F86" t="n">
-        <v>56.2</v>
+        <v>25</v>
       </c>
       <c r="G86" t="n">
-        <v>14.8</v>
+        <v>6.5</v>
       </c>
       <c r="H86" t="n">
-        <v>64.3</v>
+        <v>67.6</v>
       </c>
       <c r="I86" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>37.7</v>
+        <v>17.9</v>
       </c>
       <c r="K86" t="n">
-        <v>18.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="87">
@@ -9334,31 +9343,31 @@
         <v>113</v>
       </c>
       <c r="C87" t="n">
-        <v>68.9</v>
+        <v>71.9</v>
       </c>
       <c r="D87" t="n">
-        <v>65.3</v>
+        <v>67.5</v>
       </c>
       <c r="E87" t="n">
-        <v>25.3</v>
+        <v>42.5</v>
       </c>
       <c r="F87" t="n">
-        <v>37.7</v>
+        <v>58.8</v>
       </c>
       <c r="G87" t="n">
-        <v>9.7</v>
+        <v>12.5</v>
       </c>
       <c r="H87" t="n">
-        <v>47.1</v>
+        <v>50</v>
       </c>
       <c r="I87" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="J87" t="n">
-        <v>21.5</v>
+        <v>38.1</v>
       </c>
       <c r="K87" t="n">
-        <v>6.4</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="88">
@@ -9369,31 +9378,31 @@
         <v>113</v>
       </c>
       <c r="C88" t="n">
-        <v>70.3</v>
+        <v>66.2</v>
       </c>
       <c r="D88" t="n">
-        <v>71.3</v>
+        <v>64.6</v>
       </c>
       <c r="E88" t="n">
-        <v>31.7</v>
+        <v>27.1</v>
       </c>
       <c r="F88" t="n">
-        <v>51.6</v>
+        <v>36.7</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="H88" t="n">
-        <v>40.7</v>
+        <v>43.6</v>
       </c>
       <c r="I88" t="n">
         <v>2.8</v>
       </c>
       <c r="J88" t="n">
-        <v>20.3</v>
+        <v>22</v>
       </c>
       <c r="K88" t="n">
-        <v>22.1</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="89">
@@ -9404,31 +9413,31 @@
         <v>113</v>
       </c>
       <c r="C89" t="n">
-        <v>61.8</v>
+        <v>70.3</v>
       </c>
       <c r="D89" t="n">
-        <v>60.7</v>
+        <v>71.3</v>
       </c>
       <c r="E89" t="n">
-        <v>17.5</v>
+        <v>31.7</v>
       </c>
       <c r="F89" t="n">
-        <v>60.5</v>
+        <v>51.6</v>
       </c>
       <c r="G89" t="n">
-        <v>16.4</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>36.4</v>
+        <v>40.7</v>
       </c>
       <c r="I89" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="J89" t="n">
-        <v>32.7</v>
+        <v>20.3</v>
       </c>
       <c r="K89" t="n">
-        <v>25.4</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="90">
@@ -9436,104 +9445,104 @@
         <v>250</v>
       </c>
       <c r="B90" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>50</v>
+        <v>63.8</v>
       </c>
       <c r="D90" t="n">
-        <v>52.6</v>
+        <v>61.6</v>
       </c>
       <c r="E90" t="n">
-        <v>10.3</v>
+        <v>17.9</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G90" t="n">
-        <v>17.9</v>
+        <v>15.5</v>
       </c>
       <c r="H90" t="n">
         <v>40</v>
       </c>
       <c r="I90" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J90" t="n">
-        <v>16.2</v>
+        <v>32</v>
       </c>
       <c r="K90" t="n">
-        <v>-17.9</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>130</v>
+        <v>251</v>
       </c>
       <c r="B91" t="s">
         <v>131</v>
       </c>
       <c r="C91" t="n">
-        <v>50.9</v>
+        <v>50</v>
       </c>
       <c r="D91" t="n">
-        <v>59.1</v>
+        <v>52.6</v>
       </c>
       <c r="E91" t="n">
-        <v>15.9</v>
+        <v>10.3</v>
       </c>
       <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="H91" t="n">
         <v>40</v>
       </c>
-      <c r="G91" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="H91" t="n">
-        <v>42.5</v>
-      </c>
       <c r="I91" t="n">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="J91" t="n">
-        <v>23.8</v>
+        <v>16.2</v>
       </c>
       <c r="K91" t="n">
-        <v>1.8</v>
+        <v>-17.9</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>251</v>
+        <v>130</v>
       </c>
       <c r="B92" t="s">
         <v>131</v>
       </c>
       <c r="C92" t="n">
-        <v>52</v>
+        <v>50.9</v>
       </c>
       <c r="D92" t="n">
-        <v>65.3</v>
+        <v>59.1</v>
       </c>
       <c r="E92" t="n">
-        <v>25</v>
+        <v>15.9</v>
       </c>
       <c r="F92" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="G92" t="n">
-        <v>7.7</v>
+        <v>12.7</v>
       </c>
       <c r="H92" t="n">
-        <v>38.9</v>
+        <v>42.5</v>
       </c>
       <c r="I92" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J92" t="n">
-        <v>20</v>
+        <v>23.8</v>
       </c>
       <c r="K92" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="93">
@@ -9544,31 +9553,31 @@
         <v>131</v>
       </c>
       <c r="C93" t="n">
-        <v>69.6</v>
+        <v>52</v>
       </c>
       <c r="D93" t="n">
-        <v>67.9</v>
+        <v>65.3</v>
       </c>
       <c r="E93" t="n">
+        <v>25</v>
+      </c>
+      <c r="F93" t="n">
+        <v>25</v>
+      </c>
+      <c r="G93" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H93" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="I93" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J93" t="n">
         <v>20</v>
       </c>
-      <c r="F93" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="G93" t="n">
-        <v>8.7</v>
-      </c>
-      <c r="H93" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="I93" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" t="n">
-        <v>20.5</v>
-      </c>
       <c r="K93" t="n">
-        <v>8.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="94">
@@ -9579,31 +9588,31 @@
         <v>131</v>
       </c>
       <c r="C94" t="n">
-        <v>66.1</v>
+        <v>69.6</v>
       </c>
       <c r="D94" t="n">
-        <v>60.9</v>
+        <v>67.9</v>
       </c>
       <c r="E94" t="n">
-        <v>25.4</v>
+        <v>20</v>
       </c>
       <c r="F94" t="n">
-        <v>11.5</v>
+        <v>44.4</v>
       </c>
       <c r="G94" t="n">
-        <v>14.3</v>
+        <v>8.7</v>
       </c>
       <c r="H94" t="n">
-        <v>47.7</v>
+        <v>35.3</v>
       </c>
       <c r="I94" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="K94" t="n">
-        <v>-8.9</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="95">
@@ -9614,101 +9623,101 @@
         <v>131</v>
       </c>
       <c r="C95" t="n">
-        <v>53.6</v>
+        <v>66.1</v>
       </c>
       <c r="D95" t="n">
-        <v>64.1</v>
+        <v>60.9</v>
       </c>
       <c r="E95" t="n">
-        <v>8.3</v>
+        <v>25.4</v>
       </c>
       <c r="F95" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G95" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H95" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="I95" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J95" t="n">
         <v>20</v>
       </c>
-      <c r="G95" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H95" t="n">
-        <v>50</v>
-      </c>
-      <c r="I95" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J95" t="n">
-        <v>13.6</v>
-      </c>
       <c r="K95" t="n">
-        <v>3.5</v>
+        <v>-8.9</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>141</v>
+        <v>255</v>
       </c>
       <c r="B96" t="s">
         <v>131</v>
       </c>
       <c r="C96" t="n">
-        <v>51.2</v>
+        <v>53.6</v>
       </c>
       <c r="D96" t="n">
-        <v>56.6</v>
+        <v>64.1</v>
       </c>
       <c r="E96" t="n">
-        <v>24.5</v>
+        <v>8.3</v>
       </c>
       <c r="F96" t="n">
-        <v>34.8</v>
+        <v>20</v>
       </c>
       <c r="G96" t="n">
-        <v>20.9</v>
+        <v>3.6</v>
       </c>
       <c r="H96" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I96" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="J96" t="n">
-        <v>28.6</v>
+        <v>13.6</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>255</v>
+        <v>141</v>
       </c>
       <c r="B97" t="s">
         <v>131</v>
       </c>
       <c r="C97" t="n">
-        <v>62.5</v>
+        <v>51.2</v>
       </c>
       <c r="D97" t="n">
-        <v>58.3</v>
+        <v>56.6</v>
       </c>
       <c r="E97" t="n">
-        <v>26.9</v>
+        <v>24.5</v>
       </c>
       <c r="F97" t="n">
-        <v>14.3</v>
+        <v>34.8</v>
       </c>
       <c r="G97" t="n">
-        <v>18.8</v>
+        <v>20.9</v>
       </c>
       <c r="H97" t="n">
-        <v>41.7</v>
+        <v>40</v>
       </c>
       <c r="I97" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="J97" t="n">
-        <v>17.9</v>
+        <v>28.6</v>
       </c>
       <c r="K97" t="n">
-        <v>-12.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -9719,31 +9728,31 @@
         <v>131</v>
       </c>
       <c r="C98" t="n">
-        <v>52.6</v>
+        <v>62.5</v>
       </c>
       <c r="D98" t="n">
-        <v>56.2</v>
+        <v>58.3</v>
       </c>
       <c r="E98" t="n">
-        <v>30</v>
+        <v>26.9</v>
       </c>
       <c r="F98" t="n">
-        <v>10</v>
+        <v>14.3</v>
       </c>
       <c r="G98" t="n">
-        <v>15.8</v>
+        <v>18.8</v>
       </c>
       <c r="H98" t="n">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="I98" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="J98" t="n">
-        <v>15.2</v>
+        <v>17.9</v>
       </c>
       <c r="K98" t="n">
-        <v>-10.5</v>
+        <v>-12.6</v>
       </c>
     </row>
     <row r="99">
@@ -9754,31 +9763,31 @@
         <v>131</v>
       </c>
       <c r="C99" t="n">
-        <v>59.2</v>
+        <v>52.6</v>
       </c>
       <c r="D99" t="n">
-        <v>61.6</v>
+        <v>56.2</v>
       </c>
       <c r="E99" t="n">
-        <v>28.6</v>
+        <v>30</v>
       </c>
       <c r="F99" t="n">
-        <v>61.1</v>
+        <v>10</v>
       </c>
       <c r="G99" t="n">
-        <v>12.7</v>
+        <v>15.8</v>
       </c>
       <c r="H99" t="n">
-        <v>36.1</v>
+        <v>50</v>
       </c>
       <c r="I99" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="J99" t="n">
-        <v>32.8</v>
+        <v>15.2</v>
       </c>
       <c r="K99" t="n">
-        <v>18.3</v>
+        <v>-10.5</v>
       </c>
     </row>
     <row r="100">
@@ -9789,31 +9798,31 @@
         <v>131</v>
       </c>
       <c r="C100" t="n">
-        <v>55.6</v>
+        <v>59.2</v>
       </c>
       <c r="D100" t="n">
-        <v>61.3</v>
+        <v>61.6</v>
       </c>
       <c r="E100" t="n">
-        <v>26.9</v>
+        <v>28.6</v>
       </c>
       <c r="F100" t="n">
-        <v>36.4</v>
+        <v>61.1</v>
       </c>
       <c r="G100" t="n">
-        <v>16.7</v>
+        <v>12.7</v>
       </c>
       <c r="H100" t="n">
-        <v>40</v>
+        <v>36.1</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="J100" t="n">
-        <v>27.8</v>
+        <v>32.8</v>
       </c>
       <c r="K100" t="n">
-        <v>5.5</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="101">
@@ -9824,31 +9833,31 @@
         <v>131</v>
       </c>
       <c r="C101" t="n">
-        <v>44</v>
+        <v>55.6</v>
       </c>
       <c r="D101" t="n">
-        <v>56.3</v>
+        <v>61.3</v>
       </c>
       <c r="E101" t="n">
-        <v>23.1</v>
+        <v>26.9</v>
       </c>
       <c r="F101" t="n">
-        <v>38.5</v>
+        <v>36.4</v>
       </c>
       <c r="G101" t="n">
-        <v>8</v>
+        <v>16.7</v>
       </c>
       <c r="H101" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I101" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>26.5</v>
+        <v>27.8</v>
       </c>
       <c r="K101" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="102">
@@ -9859,31 +9868,31 @@
         <v>131</v>
       </c>
       <c r="C102" t="n">
-        <v>38.9</v>
+        <v>44</v>
       </c>
       <c r="D102" t="n">
-        <v>52</v>
+        <v>56.3</v>
       </c>
       <c r="E102" t="n">
-        <v>16.3</v>
+        <v>23.1</v>
       </c>
       <c r="F102" t="n">
-        <v>33.3</v>
+        <v>38.5</v>
       </c>
       <c r="G102" t="n">
-        <v>27.8</v>
+        <v>8</v>
       </c>
       <c r="H102" t="n">
-        <v>22.2</v>
+        <v>50</v>
       </c>
       <c r="I102" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="J102" t="n">
-        <v>31</v>
+        <v>26.5</v>
       </c>
       <c r="K102" t="n">
-        <v>-11.1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="103">
@@ -9894,31 +9903,31 @@
         <v>131</v>
       </c>
       <c r="C103" t="n">
-        <v>60.9</v>
+        <v>38.9</v>
       </c>
       <c r="D103" t="n">
-        <v>61.6</v>
+        <v>52</v>
       </c>
       <c r="E103" t="n">
-        <v>23.9</v>
+        <v>16.3</v>
       </c>
       <c r="F103" t="n">
-        <v>32.6</v>
+        <v>33.3</v>
       </c>
       <c r="G103" t="n">
-        <v>8</v>
+        <v>27.8</v>
       </c>
       <c r="H103" t="n">
-        <v>58.9</v>
+        <v>22.2</v>
       </c>
       <c r="I103" t="n">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="J103" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K103" t="n">
-        <v>9.2</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="104">
@@ -9929,31 +9938,31 @@
         <v>131</v>
       </c>
       <c r="C104" t="n">
-        <v>57.8</v>
+        <v>60.9</v>
       </c>
       <c r="D104" t="n">
-        <v>60.9</v>
+        <v>61.6</v>
       </c>
       <c r="E104" t="n">
-        <v>20.1</v>
+        <v>23.9</v>
       </c>
       <c r="F104" t="n">
-        <v>40.5</v>
+        <v>32.6</v>
       </c>
       <c r="G104" t="n">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="H104" t="n">
-        <v>40.9</v>
+        <v>58.9</v>
       </c>
       <c r="I104" t="n">
-        <v>7.8</v>
+        <v>1.1</v>
       </c>
       <c r="J104" t="n">
-        <v>15.3</v>
+        <v>24</v>
       </c>
       <c r="K104" t="n">
-        <v>8.6</v>
+        <v>9.2</v>
       </c>
     </row>
     <row r="105">
@@ -9961,34 +9970,34 @@
         <v>263</v>
       </c>
       <c r="B105" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C105" t="n">
-        <v>64.2</v>
+        <v>57.8</v>
       </c>
       <c r="D105" t="n">
-        <v>68.7</v>
+        <v>60.9</v>
       </c>
       <c r="E105" t="n">
-        <v>25</v>
+        <v>20.1</v>
       </c>
       <c r="F105" t="n">
-        <v>46.3</v>
+        <v>40.5</v>
       </c>
       <c r="G105" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="H105" t="n">
-        <v>49.5</v>
+        <v>40.9</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J105" t="n">
-        <v>22.2</v>
+        <v>15.3</v>
       </c>
       <c r="K105" t="n">
-        <v>16</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="106">
@@ -9999,31 +10008,31 @@
         <v>151</v>
       </c>
       <c r="C106" t="n">
-        <v>53.8</v>
+        <v>64.2</v>
       </c>
       <c r="D106" t="n">
-        <v>64</v>
+        <v>68.7</v>
       </c>
       <c r="E106" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F106" t="n">
-        <v>32</v>
+        <v>46.3</v>
       </c>
       <c r="G106" t="n">
-        <v>9.2</v>
+        <v>2.2</v>
       </c>
       <c r="H106" t="n">
-        <v>31.4</v>
+        <v>49.5</v>
       </c>
       <c r="I106" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>21.4</v>
+        <v>22.2</v>
       </c>
       <c r="K106" t="n">
-        <v>3.1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="107">
@@ -10034,101 +10043,101 @@
         <v>151</v>
       </c>
       <c r="C107" t="n">
-        <v>59</v>
+        <v>55.7</v>
       </c>
       <c r="D107" t="n">
-        <v>67.1</v>
+        <v>64.6</v>
       </c>
       <c r="E107" t="n">
-        <v>39.6</v>
+        <v>15.2</v>
       </c>
       <c r="F107" t="n">
-        <v>72</v>
+        <v>33.3</v>
       </c>
       <c r="G107" t="n">
-        <v>5.3</v>
+        <v>8.6</v>
       </c>
       <c r="H107" t="n">
-        <v>50</v>
+        <v>30.9</v>
       </c>
       <c r="I107" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="J107" t="n">
-        <v>41.3</v>
+        <v>21.3</v>
       </c>
       <c r="K107" t="n">
-        <v>44.7</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>198</v>
+        <v>266</v>
       </c>
       <c r="B108" t="s">
         <v>151</v>
       </c>
       <c r="C108" t="n">
-        <v>63.3</v>
+        <v>59</v>
       </c>
       <c r="D108" t="n">
-        <v>60.7</v>
+        <v>67.1</v>
       </c>
       <c r="E108" t="n">
-        <v>13.6</v>
+        <v>39.6</v>
       </c>
       <c r="F108" t="n">
-        <v>41.7</v>
+        <v>72</v>
       </c>
       <c r="G108" t="n">
-        <v>10.3</v>
+        <v>5.3</v>
       </c>
       <c r="H108" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="I108" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J108" t="n">
-        <v>29.2</v>
+        <v>41.3</v>
       </c>
       <c r="K108" t="n">
-        <v>6.9</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>266</v>
+        <v>198</v>
       </c>
       <c r="B109" t="s">
         <v>151</v>
       </c>
       <c r="C109" t="n">
-        <v>66.7</v>
+        <v>63.3</v>
       </c>
       <c r="D109" t="n">
-        <v>60.5</v>
+        <v>60.7</v>
       </c>
       <c r="E109" t="n">
-        <v>25</v>
+        <v>13.6</v>
       </c>
       <c r="F109" t="n">
-        <v>42.1</v>
+        <v>41.7</v>
       </c>
       <c r="G109" t="n">
-        <v>6.7</v>
+        <v>10.3</v>
       </c>
       <c r="H109" t="n">
-        <v>57.9</v>
+        <v>35</v>
       </c>
       <c r="I109" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J109" t="n">
-        <v>49.2</v>
+        <v>29.2</v>
       </c>
       <c r="K109" t="n">
-        <v>20</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="110">
@@ -10139,29 +10148,31 @@
         <v>151</v>
       </c>
       <c r="C110" t="n">
-        <v>84.6</v>
+        <v>63.6</v>
       </c>
       <c r="D110" t="n">
-        <v>74.4</v>
-      </c>
-      <c r="E110"/>
+        <v>62.2</v>
+      </c>
+      <c r="E110" t="n">
+        <v>34.7</v>
+      </c>
       <c r="F110" t="n">
-        <v>47.1</v>
+        <v>44.4</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="H110" t="n">
-        <v>45.2</v>
+        <v>53.8</v>
       </c>
       <c r="I110" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J110" t="n">
-        <v>28.4</v>
+        <v>43.2</v>
       </c>
       <c r="K110" t="n">
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="111">
@@ -10172,31 +10183,29 @@
         <v>151</v>
       </c>
       <c r="C111" t="n">
-        <v>50</v>
+        <v>84.6</v>
       </c>
       <c r="D111" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="E111" t="n">
-        <v>0</v>
-      </c>
+        <v>74.4</v>
+      </c>
+      <c r="E111"/>
       <c r="F111" t="n">
-        <v>25</v>
+        <v>47.1</v>
       </c>
       <c r="G111" t="n">
-        <v>30.8</v>
+        <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>37.5</v>
+        <v>45.2</v>
       </c>
       <c r="I111" t="n">
-        <v>7.7</v>
+        <v>2.4</v>
       </c>
       <c r="J111" t="n">
-        <v>31.2</v>
+        <v>28.4</v>
       </c>
       <c r="K111" t="n">
-        <v>-23.1</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="112">
@@ -10207,31 +10216,31 @@
         <v>151</v>
       </c>
       <c r="C112" t="n">
-        <v>60.7</v>
+        <v>50</v>
       </c>
       <c r="D112" t="n">
-        <v>62.4</v>
+        <v>45.1</v>
       </c>
       <c r="E112" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G112" t="n">
-        <v>17.9</v>
+        <v>30.8</v>
       </c>
       <c r="H112" t="n">
-        <v>56.2</v>
+        <v>37.5</v>
       </c>
       <c r="I112" t="n">
-        <v>3.6</v>
+        <v>7.7</v>
       </c>
       <c r="J112" t="n">
-        <v>28.9</v>
+        <v>31.2</v>
       </c>
       <c r="K112" t="n">
-        <v>3.5</v>
+        <v>-23.1</v>
       </c>
     </row>
     <row r="113">
@@ -10242,31 +10251,31 @@
         <v>151</v>
       </c>
       <c r="C113" t="n">
-        <v>65.8</v>
+        <v>60.7</v>
       </c>
       <c r="D113" t="n">
-        <v>67.5</v>
+        <v>62.4</v>
       </c>
       <c r="E113" t="n">
-        <v>36.4</v>
+        <v>23.1</v>
       </c>
       <c r="F113" t="n">
-        <v>38.1</v>
+        <v>30</v>
       </c>
       <c r="G113" t="n">
-        <v>7.9</v>
+        <v>17.9</v>
       </c>
       <c r="H113" t="n">
-        <v>53.8</v>
+        <v>56.2</v>
       </c>
       <c r="I113" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="J113" t="n">
-        <v>26.8</v>
+        <v>28.9</v>
       </c>
       <c r="K113" t="n">
-        <v>13.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="114">
@@ -10277,31 +10286,31 @@
         <v>151</v>
       </c>
       <c r="C114" t="n">
-        <v>52.3</v>
+        <v>65.8</v>
       </c>
       <c r="D114" t="n">
-        <v>60.1</v>
+        <v>67.5</v>
       </c>
       <c r="E114" t="n">
-        <v>20.8</v>
+        <v>36.4</v>
       </c>
       <c r="F114" t="n">
-        <v>46.7</v>
+        <v>38.1</v>
       </c>
       <c r="G114" t="n">
-        <v>10.5</v>
+        <v>7.9</v>
       </c>
       <c r="H114" t="n">
-        <v>52.7</v>
+        <v>53.8</v>
       </c>
       <c r="I114" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J114" t="n">
-        <v>24.5</v>
+        <v>26.8</v>
       </c>
       <c r="K114" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="115">
@@ -10312,31 +10321,31 @@
         <v>151</v>
       </c>
       <c r="C115" t="n">
-        <v>66.7</v>
+        <v>52.3</v>
       </c>
       <c r="D115" t="n">
-        <v>56.7</v>
+        <v>60.1</v>
       </c>
       <c r="E115" t="n">
-        <v>14.3</v>
+        <v>20.8</v>
       </c>
       <c r="F115" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="G115" t="n">
-        <v>22.2</v>
+        <v>10.5</v>
       </c>
       <c r="H115" t="n">
-        <v>20</v>
+        <v>52.7</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="J115" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="116">
@@ -10347,31 +10356,31 @@
         <v>151</v>
       </c>
       <c r="C116" t="n">
-        <v>67.1</v>
+        <v>66.7</v>
       </c>
       <c r="D116" t="n">
-        <v>68.1</v>
+        <v>56.7</v>
       </c>
       <c r="E116" t="n">
-        <v>23.7</v>
+        <v>14.3</v>
       </c>
       <c r="F116" t="n">
         <v>50</v>
       </c>
       <c r="G116" t="n">
-        <v>6.5</v>
+        <v>22.2</v>
       </c>
       <c r="H116" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I116" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>26.2</v>
+        <v>25</v>
       </c>
       <c r="K116" t="n">
-        <v>16.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -10382,64 +10391,99 @@
         <v>151</v>
       </c>
       <c r="C117" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D117" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="E117" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F117" t="n">
+        <v>50</v>
+      </c>
+      <c r="G117" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H117" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J117" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="K117" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>275</v>
+      </c>
+      <c r="B118" t="s">
+        <v>151</v>
+      </c>
+      <c r="C118" t="n">
         <v>61.7</v>
       </c>
-      <c r="D117" t="n">
+      <c r="D118" t="n">
         <v>63.5</v>
       </c>
-      <c r="E117" t="n">
+      <c r="E118" t="n">
         <v>24.5</v>
       </c>
-      <c r="F117" t="n">
+      <c r="F118" t="n">
         <v>48</v>
       </c>
-      <c r="G117" t="n">
+      <c r="G118" t="n">
         <v>6.7</v>
       </c>
-      <c r="H117" t="n">
+      <c r="H118" t="n">
         <v>46.5</v>
       </c>
-      <c r="I117" t="n">
+      <c r="I118" t="n">
         <v>5</v>
       </c>
-      <c r="J117" t="n">
+      <c r="J118" t="n">
         <v>20.4</v>
       </c>
-      <c r="K117" t="n">
+      <c r="K118" t="n">
         <v>13.3</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118"/>
-      <c r="B118" t="s">
+    <row r="119">
+      <c r="A119"/>
+      <c r="B119" t="s">
         <v>165</v>
       </c>
-      <c r="C118" t="n">
+      <c r="C119" t="n">
         <v>57.6</v>
       </c>
-      <c r="D118" t="n">
+      <c r="D119" t="n">
         <v>61.2</v>
       </c>
-      <c r="E118" t="n">
-        <v>23</v>
-      </c>
-      <c r="F118" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="G118" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="H118" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="I118" t="n">
+      <c r="E119" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F119" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="G119" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H119" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="I119" t="n">
         <v>3.2</v>
       </c>
-      <c r="J118" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="K118" t="n">
-        <v>8.7</v>
+      <c r="J119" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="K119" t="n">
+        <v>8.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/summary2026.xlsx
+++ b/data/summary2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="284">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -312,9 +312,15 @@
     <t xml:space="preserve">Kitchener Panthers</t>
   </si>
   <si>
+    <t xml:space="preserve">Cameron Bauer</t>
+  </si>
+  <si>
     <t xml:space="preserve">Charlie Towers</t>
   </si>
   <si>
+    <t xml:space="preserve">Ernesto Punales</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jamie Cabral</t>
   </si>
   <si>
@@ -360,6 +366,9 @@
     <t xml:space="preserve">Christian Inoa</t>
   </si>
   <si>
+    <t xml:space="preserve">Cleveland Brownlee</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cristian Inoa</t>
   </si>
   <si>
@@ -393,6 +402,9 @@
     <t xml:space="preserve">Starling Joseph</t>
   </si>
   <si>
+    <t xml:space="preserve">Trent Leniham</t>
+  </si>
+  <si>
     <t xml:space="preserve">Trent Lenihan</t>
   </si>
   <si>
@@ -405,12 +417,15 @@
     <t xml:space="preserve">Xavier Whittle</t>
   </si>
   <si>
+    <t xml:space="preserve">Ben Sitarenios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toronto Maple Leafs</t>
+  </si>
+  <si>
     <t xml:space="preserve">Benjamin Sitarenios</t>
   </si>
   <si>
-    <t xml:space="preserve">Toronto Maple Leafs</t>
-  </si>
-  <si>
     <t xml:space="preserve">Benjamin Sterritt</t>
   </si>
   <si>
@@ -429,6 +444,9 @@
     <t xml:space="preserve">Dennis Dei Baning</t>
   </si>
   <si>
+    <t xml:space="preserve">Dennis Dei Banning</t>
+  </si>
+  <si>
     <t xml:space="preserve">JJ Dutton</t>
   </si>
   <si>
@@ -444,9 +462,15 @@
     <t xml:space="preserve">Marcus Knecht</t>
   </si>
   <si>
+    <t xml:space="preserve">Martin Knecht</t>
+  </si>
+  <si>
     <t xml:space="preserve">Matt Brandt</t>
   </si>
   <si>
+    <t xml:space="preserve">Matt Fabian</t>
+  </si>
+  <si>
     <t xml:space="preserve">Matthew Fabian</t>
   </si>
   <si>
@@ -720,9 +744,6 @@
     <t xml:space="preserve">Elian Serrata</t>
   </si>
   <si>
-    <t xml:space="preserve">Ernesto Punales</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gavin McLean</t>
   </si>
   <si>
@@ -775,6 +796,9 @@
   </si>
   <si>
     <t xml:space="preserve">Camden Dimidjian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Boisvert</t>
   </si>
   <si>
     <t xml:space="preserve">Frankie Gulko</t>
@@ -895,8 +919,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K147" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K147"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K155" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K155"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -915,8 +939,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K119" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K119"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K120" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K120"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -2383,28 +2407,28 @@
         <v>71.9</v>
       </c>
       <c r="D34" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="E34" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="F34" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="G34" t="n">
-        <v>35.4</v>
+        <v>36.1</v>
       </c>
       <c r="H34" t="n">
-        <v>8.3</v>
+        <v>10.3</v>
       </c>
       <c r="I34" t="n">
-        <v>62.5</v>
+        <v>65.4</v>
       </c>
       <c r="J34" t="n">
-        <v>20.8</v>
+        <v>19.2</v>
       </c>
       <c r="K34" t="n">
-        <v>45.8</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,31 +2439,31 @@
         <v>46</v>
       </c>
       <c r="C35" t="n">
-        <v>71.6</v>
+        <v>73</v>
       </c>
       <c r="D35" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="E35" t="n">
-        <v>48.3</v>
+        <v>49.8</v>
       </c>
       <c r="F35" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="G35" t="n">
-        <v>18.1</v>
+        <v>17.1</v>
       </c>
       <c r="H35" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="I35" t="n">
-        <v>42.1</v>
+        <v>39.7</v>
       </c>
       <c r="J35" t="n">
-        <v>36.8</v>
+        <v>36.5</v>
       </c>
       <c r="K35" t="n">
-        <v>49.1</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="36">
@@ -2479,31 +2503,31 @@
         <v>46</v>
       </c>
       <c r="C37" t="n">
-        <v>68.2</v>
+        <v>68.4</v>
       </c>
       <c r="D37" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="E37" t="n">
-        <v>48.7</v>
+        <v>49</v>
       </c>
       <c r="F37" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="G37" t="n">
-        <v>13.8</v>
+        <v>12.9</v>
       </c>
       <c r="H37" t="n">
-        <v>9.7</v>
+        <v>10.4</v>
       </c>
       <c r="I37" t="n">
-        <v>59.6</v>
+        <v>57.1</v>
       </c>
       <c r="J37" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="K37" t="n">
-        <v>28.8</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="38">
@@ -2514,31 +2538,31 @@
         <v>46</v>
       </c>
       <c r="C38" t="n">
-        <v>76.3</v>
+        <v>77</v>
       </c>
       <c r="D38" t="n">
-        <v>30</v>
+        <v>32.7</v>
       </c>
       <c r="E38" t="n">
-        <v>46.3</v>
+        <v>44.3</v>
       </c>
       <c r="F38" t="n">
-        <v>30</v>
+        <v>32.7</v>
       </c>
       <c r="G38" t="n">
-        <v>25</v>
+        <v>25.8</v>
       </c>
       <c r="H38" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="I38" t="n">
-        <v>45.3</v>
+        <v>46.4</v>
       </c>
       <c r="J38" t="n">
-        <v>35.8</v>
+        <v>33.9</v>
       </c>
       <c r="K38" t="n">
-        <v>37.3</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="39">
@@ -2549,16 +2573,16 @@
         <v>46</v>
       </c>
       <c r="C39" t="n">
-        <v>50</v>
+        <v>71.4</v>
       </c>
       <c r="D39" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="F39" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -2567,13 +2591,13 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="J39" t="n">
-        <v>60</v>
+        <v>55.6</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="40">
@@ -2584,31 +2608,31 @@
         <v>46</v>
       </c>
       <c r="C40" t="n">
-        <v>59.8</v>
+        <v>60.5</v>
       </c>
       <c r="D40" t="n">
-        <v>26</v>
+        <v>28.7</v>
       </c>
       <c r="E40" t="n">
-        <v>33.8</v>
+        <v>31.8</v>
       </c>
       <c r="F40" t="n">
-        <v>26</v>
+        <v>28.7</v>
       </c>
       <c r="G40" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="H40" t="n">
-        <v>12.5</v>
+        <v>11.6</v>
       </c>
       <c r="I40" t="n">
-        <v>48.8</v>
+        <v>53.2</v>
       </c>
       <c r="J40" t="n">
-        <v>14</v>
+        <v>12.8</v>
       </c>
       <c r="K40" t="n">
-        <v>18.6</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="41">
@@ -2654,31 +2678,31 @@
         <v>46</v>
       </c>
       <c r="C42" t="n">
-        <v>69.4</v>
+        <v>72.7</v>
       </c>
       <c r="D42" t="n">
-        <v>37.7</v>
+        <v>44.8</v>
       </c>
       <c r="E42" t="n">
-        <v>31.7</v>
+        <v>27.9</v>
       </c>
       <c r="F42" t="n">
-        <v>37.7</v>
+        <v>44.8</v>
       </c>
       <c r="G42" t="n">
-        <v>42.1</v>
+        <v>39.7</v>
       </c>
       <c r="H42" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I42" t="n">
         <v>50</v>
       </c>
       <c r="J42" t="n">
-        <v>35.7</v>
+        <v>27.8</v>
       </c>
       <c r="K42" t="n">
-        <v>57.1</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="43">
@@ -2724,31 +2748,31 @@
         <v>46</v>
       </c>
       <c r="C44" t="n">
-        <v>68</v>
+        <v>68.6</v>
       </c>
       <c r="D44" t="n">
-        <v>14.6</v>
+        <v>16.3</v>
       </c>
       <c r="E44" t="n">
-        <v>53.4</v>
+        <v>52.3</v>
       </c>
       <c r="F44" t="n">
-        <v>14.6</v>
+        <v>16.3</v>
       </c>
       <c r="G44" t="n">
-        <v>30.1</v>
+        <v>29.6</v>
       </c>
       <c r="H44" t="n">
-        <v>11.3</v>
+        <v>12.5</v>
       </c>
       <c r="I44" t="n">
-        <v>28.9</v>
+        <v>28.2</v>
       </c>
       <c r="J44" t="n">
-        <v>47.4</v>
+        <v>46.2</v>
       </c>
       <c r="K44" t="n">
-        <v>26.3</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="45">
@@ -2829,31 +2853,31 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>69.8</v>
+        <v>68.4</v>
       </c>
       <c r="D47" t="n">
-        <v>16.9</v>
+        <v>20.2</v>
       </c>
       <c r="E47" t="n">
-        <v>52.9</v>
+        <v>48.2</v>
       </c>
       <c r="F47" t="n">
-        <v>16.9</v>
+        <v>20.2</v>
       </c>
       <c r="G47" t="n">
-        <v>22.4</v>
+        <v>22.7</v>
       </c>
       <c r="H47" t="n">
-        <v>7.5</v>
+        <v>8.7</v>
       </c>
       <c r="I47" t="n">
-        <v>76.2</v>
+        <v>73.1</v>
       </c>
       <c r="J47" t="n">
-        <v>9.5</v>
+        <v>7.7</v>
       </c>
       <c r="K47" t="n">
-        <v>28.6</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="48">
@@ -2899,31 +2923,31 @@
         <v>46</v>
       </c>
       <c r="C49" t="n">
-        <v>74.1</v>
+        <v>73.8</v>
       </c>
       <c r="D49" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="E49" t="n">
-        <v>57.7</v>
+        <v>57.3</v>
       </c>
       <c r="F49" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="G49" t="n">
-        <v>36.5</v>
+        <v>35.3</v>
       </c>
       <c r="H49" t="n">
-        <v>14.3</v>
+        <v>14.7</v>
       </c>
       <c r="I49" t="n">
-        <v>17.9</v>
+        <v>19.5</v>
       </c>
       <c r="J49" t="n">
-        <v>43.6</v>
+        <v>43.9</v>
       </c>
       <c r="K49" t="n">
-        <v>51.3</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="50">
@@ -4117,33 +4141,23 @@
       <c r="B84" t="s">
         <v>98</v>
       </c>
-      <c r="C84" t="n">
-        <v>56.8</v>
-      </c>
+      <c r="C84"/>
       <c r="D84" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E84" t="n">
-        <v>50.3</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="E84"/>
       <c r="F84" t="n">
-        <v>6.5</v>
+        <v>50</v>
       </c>
       <c r="G84" t="n">
-        <v>25.9</v>
+        <v>50</v>
       </c>
       <c r="H84" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="I84" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="J84" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="K84" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I84"/>
+      <c r="J84"/>
+      <c r="K84"/>
     </row>
     <row r="85">
       <c r="A85" t="s">
@@ -4153,31 +4167,31 @@
         <v>98</v>
       </c>
       <c r="C85" t="n">
-        <v>63.2</v>
+        <v>56.8</v>
       </c>
       <c r="D85" t="n">
-        <v>36.4</v>
+        <v>6.5</v>
       </c>
       <c r="E85" t="n">
-        <v>26.8</v>
+        <v>50.3</v>
       </c>
       <c r="F85" t="n">
-        <v>36.4</v>
+        <v>6.5</v>
       </c>
       <c r="G85" t="n">
-        <v>38.9</v>
+        <v>25.9</v>
       </c>
       <c r="H85" t="n">
-        <v>5.3</v>
+        <v>14.7</v>
       </c>
       <c r="I85" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="J85" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="K85" t="n">
         <v>50</v>
-      </c>
-      <c r="J85" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -4188,31 +4202,31 @@
         <v>98</v>
       </c>
       <c r="C86" t="n">
-        <v>85.2</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>33.3</v>
+        <v>54.5</v>
       </c>
       <c r="E86" t="n">
-        <v>51.9</v>
+        <v>-54.5</v>
       </c>
       <c r="F86" t="n">
-        <v>33.3</v>
+        <v>54.5</v>
       </c>
       <c r="G86" t="n">
-        <v>44.9</v>
+        <v>16.7</v>
       </c>
       <c r="H86" t="n">
-        <v>15.8</v>
+        <v>50</v>
       </c>
       <c r="I86" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>47.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -4223,31 +4237,31 @@
         <v>98</v>
       </c>
       <c r="C87" t="n">
-        <v>75.7</v>
+        <v>56.5</v>
       </c>
       <c r="D87" t="n">
-        <v>33.3</v>
+        <v>38.5</v>
       </c>
       <c r="E87" t="n">
-        <v>42.4</v>
+        <v>18</v>
       </c>
       <c r="F87" t="n">
-        <v>33.3</v>
+        <v>38.5</v>
       </c>
       <c r="G87" t="n">
-        <v>19.1</v>
+        <v>39.5</v>
       </c>
       <c r="H87" t="n">
-        <v>7.1</v>
+        <v>5</v>
       </c>
       <c r="I87" t="n">
-        <v>41.5</v>
+        <v>54.5</v>
       </c>
       <c r="J87" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>36.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -4258,31 +4272,31 @@
         <v>98</v>
       </c>
       <c r="C88" t="n">
-        <v>68.3</v>
+        <v>86.2</v>
       </c>
       <c r="D88" t="n">
-        <v>13.1</v>
+        <v>33.3</v>
       </c>
       <c r="E88" t="n">
-        <v>55.2</v>
+        <v>52.9</v>
       </c>
       <c r="F88" t="n">
-        <v>13.1</v>
+        <v>33.3</v>
       </c>
       <c r="G88" t="n">
-        <v>28.3</v>
+        <v>43.2</v>
       </c>
       <c r="H88" t="n">
-        <v>24.1</v>
+        <v>14.6</v>
       </c>
       <c r="I88" t="n">
-        <v>24.4</v>
+        <v>52.4</v>
       </c>
       <c r="J88" t="n">
-        <v>34.1</v>
+        <v>14.3</v>
       </c>
       <c r="K88" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="89">
@@ -4293,31 +4307,31 @@
         <v>98</v>
       </c>
       <c r="C89" t="n">
-        <v>68.5</v>
+        <v>75.7</v>
       </c>
       <c r="D89" t="n">
-        <v>28.4</v>
+        <v>33.3</v>
       </c>
       <c r="E89" t="n">
-        <v>40.1</v>
+        <v>42.4</v>
       </c>
       <c r="F89" t="n">
-        <v>28.4</v>
+        <v>33.3</v>
       </c>
       <c r="G89" t="n">
-        <v>25.4</v>
+        <v>19.1</v>
       </c>
       <c r="H89" t="n">
-        <v>10.1</v>
+        <v>7.1</v>
       </c>
       <c r="I89" t="n">
-        <v>38.6</v>
+        <v>41.5</v>
       </c>
       <c r="J89" t="n">
-        <v>34.1</v>
+        <v>22</v>
       </c>
       <c r="K89" t="n">
-        <v>52.3</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="90">
@@ -4328,31 +4342,31 @@
         <v>98</v>
       </c>
       <c r="C90" t="n">
-        <v>84.2</v>
+        <v>68.2</v>
       </c>
       <c r="D90" t="n">
-        <v>28.6</v>
+        <v>16.9</v>
       </c>
       <c r="E90" t="n">
-        <v>55.6</v>
+        <v>51.3</v>
       </c>
       <c r="F90" t="n">
-        <v>28.6</v>
+        <v>16.9</v>
       </c>
       <c r="G90" t="n">
-        <v>36.1</v>
+        <v>29.4</v>
       </c>
       <c r="H90" t="n">
-        <v>8.5</v>
+        <v>22.6</v>
       </c>
       <c r="I90" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="J90" t="n">
         <v>33.3</v>
       </c>
-      <c r="J90" t="n">
-        <v>36.7</v>
-      </c>
       <c r="K90" t="n">
-        <v>53.3</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="91">
@@ -4363,31 +4377,31 @@
         <v>98</v>
       </c>
       <c r="C91" t="n">
-        <v>75</v>
+        <v>67.9</v>
       </c>
       <c r="D91" t="n">
-        <v>50</v>
+        <v>31.6</v>
       </c>
       <c r="E91" t="n">
-        <v>25</v>
+        <v>36.3</v>
       </c>
       <c r="F91" t="n">
-        <v>50</v>
+        <v>31.6</v>
       </c>
       <c r="G91" t="n">
-        <v>3.3</v>
+        <v>24.2</v>
       </c>
       <c r="H91" t="n">
-        <v>6.7</v>
+        <v>9.5</v>
       </c>
       <c r="I91" t="n">
-        <v>45.5</v>
+        <v>38.8</v>
       </c>
       <c r="J91" t="n">
-        <v>18.2</v>
+        <v>30.6</v>
       </c>
       <c r="K91" t="n">
-        <v>36.4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="92">
@@ -4398,31 +4412,31 @@
         <v>98</v>
       </c>
       <c r="C92" t="n">
-        <v>45.2</v>
+        <v>85.7</v>
       </c>
       <c r="D92" t="n">
-        <v>15.4</v>
+        <v>29.8</v>
       </c>
       <c r="E92" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="F92" t="n">
         <v>29.8</v>
       </c>
-      <c r="F92" t="n">
-        <v>15.4</v>
-      </c>
       <c r="G92" t="n">
-        <v>40</v>
+        <v>36.8</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="I92" t="n">
-        <v>66.7</v>
+        <v>36.4</v>
       </c>
       <c r="J92" t="n">
-        <v>16.7</v>
+        <v>36.4</v>
       </c>
       <c r="K92" t="n">
-        <v>66.7</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="93">
@@ -4433,31 +4447,31 @@
         <v>98</v>
       </c>
       <c r="C93" t="n">
-        <v>77.6</v>
+        <v>75</v>
       </c>
       <c r="D93" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E93" t="n">
-        <v>48.6</v>
+        <v>25</v>
       </c>
       <c r="F93" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="G93" t="n">
-        <v>37.9</v>
+        <v>3.3</v>
       </c>
       <c r="H93" t="n">
-        <v>5.4</v>
+        <v>6.7</v>
       </c>
       <c r="I93" t="n">
-        <v>37.5</v>
+        <v>45.5</v>
       </c>
       <c r="J93" t="n">
-        <v>31.2</v>
+        <v>18.2</v>
       </c>
       <c r="K93" t="n">
-        <v>50</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="94">
@@ -4468,31 +4482,31 @@
         <v>98</v>
       </c>
       <c r="C94" t="n">
-        <v>64.3</v>
+        <v>48.6</v>
       </c>
       <c r="D94" t="n">
-        <v>19.4</v>
+        <v>28</v>
       </c>
       <c r="E94" t="n">
-        <v>44.9</v>
+        <v>20.6</v>
       </c>
       <c r="F94" t="n">
-        <v>19.4</v>
+        <v>28</v>
       </c>
       <c r="G94" t="n">
-        <v>17.3</v>
+        <v>34.5</v>
       </c>
       <c r="H94" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>36.4</v>
+        <v>66.7</v>
       </c>
       <c r="J94" t="n">
-        <v>23.6</v>
+        <v>22.2</v>
       </c>
       <c r="K94" t="n">
-        <v>41.8</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="95">
@@ -4503,31 +4517,31 @@
         <v>98</v>
       </c>
       <c r="C95" t="n">
-        <v>61.9</v>
+        <v>77.4</v>
       </c>
       <c r="D95" t="n">
-        <v>18.2</v>
+        <v>32.8</v>
       </c>
       <c r="E95" t="n">
-        <v>43.7</v>
+        <v>44.6</v>
       </c>
       <c r="F95" t="n">
-        <v>18.2</v>
+        <v>32.8</v>
       </c>
       <c r="G95" t="n">
-        <v>18.8</v>
+        <v>36.6</v>
       </c>
       <c r="H95" t="n">
-        <v>11.3</v>
+        <v>5</v>
       </c>
       <c r="I95" t="n">
-        <v>33.3</v>
+        <v>37.1</v>
       </c>
       <c r="J95" t="n">
-        <v>28.9</v>
+        <v>31.4</v>
       </c>
       <c r="K95" t="n">
-        <v>46.7</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="96">
@@ -4538,31 +4552,31 @@
         <v>98</v>
       </c>
       <c r="C96" t="n">
-        <v>61.7</v>
+        <v>64.4</v>
       </c>
       <c r="D96" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="E96" t="n">
-        <v>43.2</v>
+        <v>44.4</v>
       </c>
       <c r="F96" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="G96" t="n">
-        <v>18.4</v>
+        <v>16.7</v>
       </c>
       <c r="H96" t="n">
-        <v>10.8</v>
+        <v>7.7</v>
       </c>
       <c r="I96" t="n">
-        <v>57.5</v>
+        <v>36.2</v>
       </c>
       <c r="J96" t="n">
-        <v>25</v>
+        <v>24.1</v>
       </c>
       <c r="K96" t="n">
-        <v>56.1</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="97">
@@ -4570,104 +4584,104 @@
         <v>112</v>
       </c>
       <c r="B97" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C97" t="n">
-        <v>66.7</v>
+        <v>61.9</v>
       </c>
       <c r="D97" t="n">
-        <v>57.7</v>
+        <v>21.2</v>
       </c>
       <c r="E97" t="n">
-        <v>9</v>
+        <v>40.7</v>
       </c>
       <c r="F97" t="n">
-        <v>57.7</v>
+        <v>21.2</v>
       </c>
       <c r="G97" t="n">
-        <v>27.3</v>
+        <v>17.9</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="I97" t="n">
-        <v>44.4</v>
+        <v>35.4</v>
       </c>
       <c r="J97" t="n">
-        <v>44.4</v>
+        <v>27.1</v>
       </c>
       <c r="K97" t="n">
-        <v>55.6</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B98" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C98" t="n">
-        <v>100</v>
+        <v>60.4</v>
       </c>
       <c r="D98" t="n">
-        <v>16.7</v>
+        <v>16.1</v>
       </c>
       <c r="E98" t="n">
-        <v>83.3</v>
+        <v>44.3</v>
       </c>
       <c r="F98" t="n">
-        <v>16.7</v>
+        <v>16.1</v>
       </c>
       <c r="G98" t="n">
-        <v>12.5</v>
+        <v>18.4</v>
       </c>
       <c r="H98" t="n">
-        <v>16.7</v>
+        <v>11.8</v>
       </c>
       <c r="I98" t="n">
-        <v>60</v>
+        <v>57.5</v>
       </c>
       <c r="J98" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K98" t="n">
-        <v>60</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
+        <v>114</v>
+      </c>
+      <c r="B99" t="s">
         <v>115</v>
       </c>
-      <c r="B99" t="s">
-        <v>113</v>
-      </c>
       <c r="C99" t="n">
-        <v>65.5</v>
+        <v>53.8</v>
       </c>
       <c r="D99" t="n">
-        <v>17.9</v>
+        <v>53.7</v>
       </c>
       <c r="E99" t="n">
-        <v>47.6</v>
+        <v>0.1</v>
       </c>
       <c r="F99" t="n">
-        <v>17.9</v>
+        <v>53.7</v>
       </c>
       <c r="G99" t="n">
-        <v>5.3</v>
+        <v>26.7</v>
       </c>
       <c r="H99" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>35</v>
+        <v>46.7</v>
       </c>
       <c r="J99" t="n">
-        <v>30</v>
+        <v>33.3</v>
       </c>
       <c r="K99" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="100">
@@ -4675,34 +4689,34 @@
         <v>116</v>
       </c>
       <c r="B100" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C100" t="n">
-        <v>63.3</v>
+        <v>100</v>
       </c>
       <c r="D100" t="n">
-        <v>29.4</v>
+        <v>16.7</v>
       </c>
       <c r="E100" t="n">
-        <v>33.9</v>
+        <v>83.3</v>
       </c>
       <c r="F100" t="n">
-        <v>29.4</v>
+        <v>16.7</v>
       </c>
       <c r="G100" t="n">
-        <v>30.9</v>
+        <v>12.5</v>
       </c>
       <c r="H100" t="n">
-        <v>6.6</v>
+        <v>16.7</v>
       </c>
       <c r="I100" t="n">
-        <v>35.3</v>
+        <v>60</v>
       </c>
       <c r="J100" t="n">
-        <v>23.5</v>
+        <v>20</v>
       </c>
       <c r="K100" t="n">
-        <v>35.3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="101">
@@ -4710,69 +4724,63 @@
         <v>117</v>
       </c>
       <c r="B101" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C101" t="n">
-        <v>77.6</v>
+        <v>100</v>
       </c>
       <c r="D101" t="n">
-        <v>35.6</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="F101" t="n">
-        <v>35.6</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>27.4</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="I101" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="J101" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="K101" t="n">
-        <v>25.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I101"/>
+      <c r="J101"/>
+      <c r="K101"/>
     </row>
     <row r="102">
       <c r="A102" t="s">
         <v>118</v>
       </c>
       <c r="B102" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C102" t="n">
-        <v>56.9</v>
+        <v>66.7</v>
       </c>
       <c r="D102" t="n">
-        <v>28.1</v>
+        <v>23.5</v>
       </c>
       <c r="E102" t="n">
-        <v>28.8</v>
+        <v>43.2</v>
       </c>
       <c r="F102" t="n">
-        <v>28.1</v>
+        <v>23.5</v>
       </c>
       <c r="G102" t="n">
-        <v>15.8</v>
+        <v>10.4</v>
       </c>
       <c r="H102" t="n">
-        <v>6.9</v>
+        <v>14.7</v>
       </c>
       <c r="I102" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J102" t="n">
-        <v>12.2</v>
+        <v>32</v>
       </c>
       <c r="K102" t="n">
-        <v>51.2</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="103">
@@ -4780,26 +4788,34 @@
         <v>119</v>
       </c>
       <c r="B103" t="s">
-        <v>113</v>
-      </c>
-      <c r="C103"/>
-      <c r="D103"/>
-      <c r="E103"/>
-      <c r="F103"/>
+        <v>115</v>
+      </c>
+      <c r="C103" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="D103" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E103" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="F103" t="n">
+        <v>31.4</v>
+      </c>
       <c r="G103" t="n">
-        <v>33.3</v>
+        <v>32</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="I103" t="n">
-        <v>50</v>
+        <v>37.1</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="K103" t="n">
-        <v>0</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="104">
@@ -4807,34 +4823,34 @@
         <v>120</v>
       </c>
       <c r="B104" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C104" t="n">
-        <v>48.1</v>
+        <v>79.3</v>
       </c>
       <c r="D104" t="n">
-        <v>23.7</v>
+        <v>35.4</v>
       </c>
       <c r="E104" t="n">
-        <v>24.4</v>
+        <v>43.9</v>
       </c>
       <c r="F104" t="n">
-        <v>23.7</v>
+        <v>35.4</v>
       </c>
       <c r="G104" t="n">
-        <v>7.9</v>
+        <v>26.2</v>
       </c>
       <c r="H104" t="n">
-        <v>11.7</v>
+        <v>7.1</v>
       </c>
       <c r="I104" t="n">
-        <v>58.2</v>
+        <v>40.4</v>
       </c>
       <c r="J104" t="n">
-        <v>16.4</v>
+        <v>26.3</v>
       </c>
       <c r="K104" t="n">
-        <v>20.4</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="105">
@@ -4842,34 +4858,34 @@
         <v>121</v>
       </c>
       <c r="B105" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C105" t="n">
-        <v>80</v>
+        <v>58.3</v>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>28.3</v>
       </c>
       <c r="E105" t="n">
-        <v>68.9</v>
+        <v>30</v>
       </c>
       <c r="F105" t="n">
-        <v>11.1</v>
+        <v>28.3</v>
       </c>
       <c r="G105" t="n">
-        <v>39.5</v>
+        <v>17.7</v>
       </c>
       <c r="H105" t="n">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="I105" t="n">
-        <v>63.6</v>
+        <v>61</v>
       </c>
       <c r="J105" t="n">
-        <v>9.1</v>
+        <v>12.2</v>
       </c>
       <c r="K105" t="n">
-        <v>45.5</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="106">
@@ -4877,34 +4893,26 @@
         <v>122</v>
       </c>
       <c r="B106" t="s">
-        <v>113</v>
-      </c>
-      <c r="C106" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="D106" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="E106" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="F106" t="n">
-        <v>27.3</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="C106"/>
+      <c r="D106"/>
+      <c r="E106"/>
+      <c r="F106"/>
       <c r="G106" t="n">
-        <v>19.9</v>
+        <v>33.3</v>
       </c>
       <c r="H106" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>40.3</v>
+        <v>50</v>
       </c>
       <c r="J106" t="n">
-        <v>30.6</v>
+        <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>43.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -4912,34 +4920,34 @@
         <v>123</v>
       </c>
       <c r="B107" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C107" t="n">
-        <v>70</v>
+        <v>51.2</v>
       </c>
       <c r="D107" t="n">
-        <v>26.7</v>
+        <v>25.7</v>
       </c>
       <c r="E107" t="n">
-        <v>43.3</v>
+        <v>25.5</v>
       </c>
       <c r="F107" t="n">
-        <v>26.7</v>
+        <v>25.7</v>
       </c>
       <c r="G107" t="n">
+        <v>8</v>
+      </c>
+      <c r="H107" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I107" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="J107" t="n">
         <v>14.8</v>
       </c>
-      <c r="H107" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I107" t="n">
-        <v>60</v>
-      </c>
-      <c r="J107" t="n">
-        <v>30</v>
-      </c>
       <c r="K107" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="108">
@@ -4947,34 +4955,34 @@
         <v>124</v>
       </c>
       <c r="B108" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C108" t="n">
-        <v>59.5</v>
+        <v>80</v>
       </c>
       <c r="D108" t="n">
-        <v>20.9</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="n">
-        <v>38.6</v>
+        <v>68.9</v>
       </c>
       <c r="F108" t="n">
-        <v>20.9</v>
+        <v>11.1</v>
       </c>
       <c r="G108" t="n">
-        <v>18.6</v>
+        <v>39.5</v>
       </c>
       <c r="H108" t="n">
-        <v>12.1</v>
+        <v>10</v>
       </c>
       <c r="I108" t="n">
-        <v>50</v>
+        <v>63.6</v>
       </c>
       <c r="J108" t="n">
-        <v>25</v>
+        <v>9.1</v>
       </c>
       <c r="K108" t="n">
-        <v>52.6</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="109">
@@ -4982,34 +4990,34 @@
         <v>125</v>
       </c>
       <c r="B109" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C109" t="n">
-        <v>69</v>
+        <v>73.7</v>
       </c>
       <c r="D109" t="n">
-        <v>30.8</v>
+        <v>27.3</v>
       </c>
       <c r="E109" t="n">
-        <v>38.2</v>
+        <v>46.4</v>
       </c>
       <c r="F109" t="n">
-        <v>30.8</v>
+        <v>27.3</v>
       </c>
       <c r="G109" t="n">
-        <v>35.9</v>
+        <v>19.3</v>
       </c>
       <c r="H109" t="n">
-        <v>7.9</v>
+        <v>6.2</v>
       </c>
       <c r="I109" t="n">
-        <v>50</v>
+        <v>39.5</v>
       </c>
       <c r="J109" t="n">
-        <v>13</v>
+        <v>30.3</v>
       </c>
       <c r="K109" t="n">
-        <v>40.4</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="110">
@@ -5017,34 +5025,34 @@
         <v>126</v>
       </c>
       <c r="B110" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C110" t="n">
-        <v>74.4</v>
+        <v>70</v>
       </c>
       <c r="D110" t="n">
-        <v>22.9</v>
+        <v>26.7</v>
       </c>
       <c r="E110" t="n">
-        <v>51.5</v>
+        <v>43.3</v>
       </c>
       <c r="F110" t="n">
-        <v>22.9</v>
+        <v>26.7</v>
       </c>
       <c r="G110" t="n">
-        <v>29.7</v>
+        <v>14.8</v>
       </c>
       <c r="H110" t="n">
-        <v>10.7</v>
+        <v>12.5</v>
       </c>
       <c r="I110" t="n">
-        <v>43.1</v>
+        <v>60</v>
       </c>
       <c r="J110" t="n">
-        <v>27.5</v>
+        <v>30</v>
       </c>
       <c r="K110" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="111">
@@ -5052,34 +5060,34 @@
         <v>127</v>
       </c>
       <c r="B111" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C111" t="n">
-        <v>72.9</v>
+        <v>60.5</v>
       </c>
       <c r="D111" t="n">
-        <v>28.9</v>
+        <v>20.8</v>
       </c>
       <c r="E111" t="n">
-        <v>44</v>
+        <v>39.7</v>
       </c>
       <c r="F111" t="n">
-        <v>28.9</v>
+        <v>20.8</v>
       </c>
       <c r="G111" t="n">
-        <v>23.8</v>
+        <v>20</v>
       </c>
       <c r="H111" t="n">
-        <v>8.9</v>
+        <v>11.8</v>
       </c>
       <c r="I111" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J111" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="K111" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="112">
@@ -5087,26 +5095,34 @@
         <v>128</v>
       </c>
       <c r="B112" t="s">
-        <v>113</v>
-      </c>
-      <c r="C112"/>
-      <c r="D112"/>
-      <c r="E112"/>
-      <c r="F112"/>
+        <v>115</v>
+      </c>
+      <c r="C112" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="D112" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E112" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="F112" t="n">
+        <v>28.8</v>
+      </c>
       <c r="G112" t="n">
-        <v>33.3</v>
+        <v>34</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="I112" t="n">
-        <v>33.3</v>
+        <v>51</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="K112" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="113">
@@ -5114,34 +5130,34 @@
         <v>129</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C113" t="n">
-        <v>65.5</v>
+        <v>100</v>
       </c>
       <c r="D113" t="n">
-        <v>25.9</v>
+        <v>50</v>
       </c>
       <c r="E113" t="n">
-        <v>39.6</v>
+        <v>50</v>
       </c>
       <c r="F113" t="n">
-        <v>25.9</v>
+        <v>50</v>
       </c>
       <c r="G113" t="n">
-        <v>17.1</v>
+        <v>50</v>
       </c>
       <c r="H113" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>35.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -5149,174 +5165,160 @@
         <v>130</v>
       </c>
       <c r="B114" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="C114" t="n">
-        <v>100</v>
+        <v>74.4</v>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E114" t="n">
-        <v>100</v>
+        <v>49.4</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G114" t="n">
-        <v>50</v>
+        <v>28.9</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>41.8</v>
       </c>
       <c r="J114" t="n">
-        <v>0</v>
+        <v>25.5</v>
       </c>
       <c r="K114" t="n">
-        <v>100</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B115" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="C115" t="n">
-        <v>66.7</v>
+        <v>73.6</v>
       </c>
       <c r="D115" t="n">
-        <v>60</v>
+        <v>29.1</v>
       </c>
       <c r="E115" t="n">
-        <v>6.7</v>
+        <v>44.5</v>
       </c>
       <c r="F115" t="n">
-        <v>60</v>
+        <v>29.1</v>
       </c>
       <c r="G115" t="n">
-        <v>33.3</v>
+        <v>23.5</v>
       </c>
       <c r="H115" t="n">
-        <v>11.1</v>
+        <v>9.4</v>
       </c>
       <c r="I115" t="n">
-        <v>25</v>
+        <v>40.7</v>
       </c>
       <c r="J115" t="n">
-        <v>25</v>
+        <v>37.3</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B116" t="s">
-        <v>131</v>
-      </c>
-      <c r="C116" t="n">
-        <v>59.6</v>
-      </c>
-      <c r="D116" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="E116" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="F116" t="n">
-        <v>26.7</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="C116"/>
+      <c r="D116"/>
+      <c r="E116"/>
+      <c r="F116"/>
       <c r="G116" t="n">
-        <v>14.6</v>
+        <v>33.3</v>
       </c>
       <c r="H116" t="n">
-        <v>9.7</v>
+        <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>52.4</v>
+        <v>33.3</v>
       </c>
       <c r="J116" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B117" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="C117" t="n">
-        <v>35</v>
+        <v>69.7</v>
       </c>
       <c r="D117" t="n">
-        <v>13.3</v>
+        <v>23.8</v>
       </c>
       <c r="E117" t="n">
-        <v>21.7</v>
+        <v>45.9</v>
       </c>
       <c r="F117" t="n">
-        <v>13.3</v>
+        <v>23.8</v>
       </c>
       <c r="G117" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="I117" t="n">
-        <v>50</v>
+        <v>47.1</v>
       </c>
       <c r="J117" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
+        <v>134</v>
+      </c>
+      <c r="B118" t="s">
         <v>135</v>
       </c>
-      <c r="B118" t="s">
-        <v>131</v>
-      </c>
       <c r="C118" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="D118" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="E118" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="F118" t="n">
-        <v>16.7</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D118"/>
+      <c r="E118"/>
+      <c r="F118"/>
       <c r="G118" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="K118" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -5324,28 +5326,34 @@
         <v>136</v>
       </c>
       <c r="B119" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C119" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="D119"/>
-      <c r="E119"/>
-      <c r="F119"/>
+        <v>100</v>
+      </c>
+      <c r="D119" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="E119" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F119" t="n">
+        <v>57.1</v>
+      </c>
       <c r="G119" t="n">
-        <v>14.3</v>
+        <v>22.2</v>
       </c>
       <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
         <v>25</v>
       </c>
-      <c r="I119" t="n">
-        <v>66.7</v>
-      </c>
       <c r="J119" t="n">
         <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="120">
@@ -5353,34 +5361,34 @@
         <v>137</v>
       </c>
       <c r="B120" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C120" t="n">
-        <v>69.4</v>
+        <v>66.7</v>
       </c>
       <c r="D120" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="E120" t="n">
-        <v>40.4</v>
+        <v>6.7</v>
       </c>
       <c r="F120" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="G120" t="n">
-        <v>38.1</v>
+        <v>33.3</v>
       </c>
       <c r="H120" t="n">
-        <v>9.1</v>
+        <v>11.1</v>
       </c>
       <c r="I120" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="J120" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="K120" t="n">
-        <v>42.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -5388,34 +5396,34 @@
         <v>138</v>
       </c>
       <c r="B121" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C121" t="n">
-        <v>60</v>
+        <v>60.4</v>
       </c>
       <c r="D121" t="n">
-        <v>16.9</v>
+        <v>33.3</v>
       </c>
       <c r="E121" t="n">
-        <v>43.1</v>
+        <v>27.1</v>
       </c>
       <c r="F121" t="n">
-        <v>16.9</v>
+        <v>33.3</v>
       </c>
       <c r="G121" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H121" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I121" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="J121" t="n">
         <v>18.5</v>
       </c>
-      <c r="H121" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="I121" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="J121" t="n">
-        <v>14.8</v>
-      </c>
       <c r="K121" t="n">
-        <v>37</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="122">
@@ -5423,31 +5431,31 @@
         <v>139</v>
       </c>
       <c r="B122" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C122" t="n">
-        <v>66.7</v>
+        <v>35</v>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="E122" t="n">
-        <v>66.7</v>
+        <v>21.7</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="G122" t="n">
-        <v>18.2</v>
+        <v>33.3</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J122" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -5458,34 +5466,34 @@
         <v>140</v>
       </c>
       <c r="B123" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C123" t="n">
-        <v>61.5</v>
+        <v>70</v>
       </c>
       <c r="D123" t="n">
-        <v>20</v>
+        <v>31.4</v>
       </c>
       <c r="E123" t="n">
-        <v>41.5</v>
+        <v>38.6</v>
       </c>
       <c r="F123" t="n">
-        <v>20</v>
+        <v>31.4</v>
       </c>
       <c r="G123" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H123" t="n">
-        <v>12.5</v>
+        <v>14.3</v>
       </c>
       <c r="I123" t="n">
-        <v>88.9</v>
+        <v>85.7</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="K123" t="n">
-        <v>44.4</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="124">
@@ -5493,34 +5501,28 @@
         <v>141</v>
       </c>
       <c r="B124" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C124" t="n">
-        <v>51.9</v>
-      </c>
-      <c r="D124" t="n">
-        <v>15</v>
-      </c>
-      <c r="E124" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="F124" t="n">
-        <v>15</v>
-      </c>
+        <v>66.7</v>
+      </c>
+      <c r="D124"/>
+      <c r="E124"/>
+      <c r="F124"/>
       <c r="G124" t="n">
-        <v>30</v>
+        <v>14.3</v>
       </c>
       <c r="H124" t="n">
-        <v>13.3</v>
+        <v>25</v>
       </c>
       <c r="I124" t="n">
-        <v>71.4</v>
+        <v>66.7</v>
       </c>
       <c r="J124" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="125">
@@ -5528,34 +5530,34 @@
         <v>142</v>
       </c>
       <c r="B125" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C125" t="n">
-        <v>62.4</v>
+        <v>69.4</v>
       </c>
       <c r="D125" t="n">
-        <v>24.4</v>
+        <v>29</v>
       </c>
       <c r="E125" t="n">
-        <v>38</v>
+        <v>40.4</v>
       </c>
       <c r="F125" t="n">
-        <v>24.4</v>
+        <v>29</v>
       </c>
       <c r="G125" t="n">
-        <v>28.6</v>
+        <v>38.1</v>
       </c>
       <c r="H125" t="n">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="I125" t="n">
-        <v>35.3</v>
+        <v>33.3</v>
       </c>
       <c r="J125" t="n">
-        <v>23.5</v>
+        <v>37</v>
       </c>
       <c r="K125" t="n">
-        <v>55.9</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="126">
@@ -5563,34 +5565,34 @@
         <v>143</v>
       </c>
       <c r="B126" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C126" t="n">
-        <v>63.5</v>
+        <v>77.8</v>
       </c>
       <c r="D126" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="E126" t="n">
-        <v>41.1</v>
+        <v>55.6</v>
       </c>
       <c r="F126" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="G126" t="n">
-        <v>19.5</v>
+        <v>22.2</v>
       </c>
       <c r="H126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>59.5</v>
+        <v>33.3</v>
       </c>
       <c r="J126" t="n">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -5598,34 +5600,34 @@
         <v>144</v>
       </c>
       <c r="B127" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C127" t="n">
-        <v>53</v>
+        <v>60.6</v>
       </c>
       <c r="D127" t="n">
-        <v>18.8</v>
+        <v>25.6</v>
       </c>
       <c r="E127" t="n">
-        <v>34.2</v>
+        <v>35</v>
       </c>
       <c r="F127" t="n">
-        <v>18.8</v>
+        <v>25.6</v>
       </c>
       <c r="G127" t="n">
-        <v>22.4</v>
+        <v>19</v>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>9.3</v>
       </c>
       <c r="I127" t="n">
-        <v>38.7</v>
+        <v>60</v>
       </c>
       <c r="J127" t="n">
-        <v>25.8</v>
+        <v>14.3</v>
       </c>
       <c r="K127" t="n">
-        <v>48.4</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="128">
@@ -5633,34 +5635,34 @@
         <v>145</v>
       </c>
       <c r="B128" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C128" t="n">
-        <v>78.6</v>
+        <v>66.7</v>
       </c>
       <c r="D128" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>66.1</v>
+        <v>66.7</v>
       </c>
       <c r="F128" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>35.3</v>
+        <v>18.2</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>28.6</v>
+        <v>75</v>
       </c>
       <c r="J128" t="n">
-        <v>14.3</v>
+        <v>25</v>
       </c>
       <c r="K128" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -5668,34 +5670,34 @@
         <v>146</v>
       </c>
       <c r="B129" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C129" t="n">
-        <v>59.3</v>
+        <v>60</v>
       </c>
       <c r="D129" t="n">
-        <v>7.1</v>
+        <v>20</v>
       </c>
       <c r="E129" t="n">
-        <v>52.2</v>
+        <v>40</v>
       </c>
       <c r="F129" t="n">
-        <v>7.1</v>
+        <v>20</v>
       </c>
       <c r="G129" t="n">
-        <v>5.8</v>
+        <v>38.5</v>
       </c>
       <c r="H129" t="n">
-        <v>8.3</v>
+        <v>11.8</v>
       </c>
       <c r="I129" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="J129" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>35.3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="130">
@@ -5703,34 +5705,34 @@
         <v>147</v>
       </c>
       <c r="B130" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C130" t="n">
-        <v>63.2</v>
+        <v>51.9</v>
       </c>
       <c r="D130" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E130" t="n">
-        <v>18.2</v>
+        <v>36.9</v>
       </c>
       <c r="F130" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="G130" t="n">
-        <v>26.9</v>
+        <v>30</v>
       </c>
       <c r="H130" t="n">
-        <v>7.7</v>
+        <v>13.3</v>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>71.4</v>
       </c>
       <c r="J130" t="n">
-        <v>25</v>
+        <v>28.6</v>
       </c>
       <c r="K130" t="n">
-        <v>25</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="131">
@@ -5738,34 +5740,34 @@
         <v>148</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C131" t="n">
-        <v>74.4</v>
+        <v>63.6</v>
       </c>
       <c r="D131" t="n">
-        <v>12.5</v>
+        <v>26.3</v>
       </c>
       <c r="E131" t="n">
-        <v>61.9</v>
+        <v>37.3</v>
       </c>
       <c r="F131" t="n">
-        <v>12.5</v>
+        <v>26.3</v>
       </c>
       <c r="G131" t="n">
-        <v>28.4</v>
+        <v>28</v>
       </c>
       <c r="H131" t="n">
-        <v>19.3</v>
+        <v>8.1</v>
       </c>
       <c r="I131" t="n">
-        <v>31.2</v>
+        <v>36.1</v>
       </c>
       <c r="J131" t="n">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="K131" t="n">
-        <v>43.8</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="132">
@@ -5773,34 +5775,34 @@
         <v>149</v>
       </c>
       <c r="B132" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C132" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D132" t="n">
-        <v>28.3</v>
+        <v>33.3</v>
       </c>
       <c r="E132" t="n">
-        <v>46.7</v>
+        <v>66.7</v>
       </c>
       <c r="F132" t="n">
-        <v>28.3</v>
+        <v>33.3</v>
       </c>
       <c r="G132" t="n">
-        <v>12.4</v>
+        <v>11.1</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J132" t="n">
-        <v>21.7</v>
+        <v>40</v>
       </c>
       <c r="K132" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133">
@@ -5808,314 +5810,314 @@
         <v>150</v>
       </c>
       <c r="B133" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C133" t="n">
-        <v>71.3</v>
+        <v>64.4</v>
       </c>
       <c r="D133" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E133" t="n">
-        <v>51.3</v>
+        <v>37.4</v>
       </c>
       <c r="F133" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G133" t="n">
-        <v>32.7</v>
+        <v>21.4</v>
       </c>
       <c r="H133" t="n">
-        <v>9.7</v>
+        <v>1.7</v>
       </c>
       <c r="I133" t="n">
-        <v>50</v>
+        <v>61.9</v>
       </c>
       <c r="J133" t="n">
-        <v>20</v>
+        <v>21.4</v>
       </c>
       <c r="K133" t="n">
-        <v>38.2</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B134" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C134" t="n">
-        <v>70.5</v>
+        <v>100</v>
       </c>
       <c r="D134" t="n">
-        <v>25.3</v>
+        <v>20</v>
       </c>
       <c r="E134" t="n">
-        <v>45.2</v>
+        <v>80</v>
       </c>
       <c r="F134" t="n">
-        <v>25.3</v>
+        <v>20</v>
       </c>
       <c r="G134" t="n">
-        <v>17.1</v>
+        <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="J134" t="n">
-        <v>15.6</v>
+        <v>25</v>
       </c>
       <c r="K134" t="n">
-        <v>34.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B135" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C135" t="n">
-        <v>64.6</v>
+        <v>53.6</v>
       </c>
       <c r="D135" t="n">
-        <v>16.7</v>
+        <v>24.4</v>
       </c>
       <c r="E135" t="n">
-        <v>47.9</v>
+        <v>29.2</v>
       </c>
       <c r="F135" t="n">
-        <v>16.7</v>
+        <v>24.4</v>
       </c>
       <c r="G135" t="n">
-        <v>37.7</v>
+        <v>24</v>
       </c>
       <c r="H135" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>29.6</v>
+        <v>39.4</v>
       </c>
       <c r="J135" t="n">
-        <v>48.1</v>
+        <v>27.3</v>
       </c>
       <c r="K135" t="n">
-        <v>38.5</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B136" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C136" t="n">
-        <v>58.1</v>
+        <v>78.6</v>
       </c>
       <c r="D136" t="n">
-        <v>22</v>
+        <v>12.5</v>
       </c>
       <c r="E136" t="n">
-        <v>36.1</v>
+        <v>66.1</v>
       </c>
       <c r="F136" t="n">
-        <v>22</v>
+        <v>12.5</v>
       </c>
       <c r="G136" t="n">
-        <v>39.4</v>
+        <v>35.3</v>
       </c>
       <c r="H136" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>15.4</v>
+        <v>28.6</v>
       </c>
       <c r="J136" t="n">
-        <v>53.8</v>
+        <v>14.3</v>
       </c>
       <c r="K136" t="n">
-        <v>18.2</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B137" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C137" t="n">
-        <v>63.9</v>
+        <v>59.3</v>
       </c>
       <c r="D137" t="n">
-        <v>17.6</v>
+        <v>7.1</v>
       </c>
       <c r="E137" t="n">
-        <v>46.3</v>
+        <v>52.2</v>
       </c>
       <c r="F137" t="n">
-        <v>17.6</v>
+        <v>7.1</v>
       </c>
       <c r="G137" t="n">
-        <v>10.8</v>
+        <v>5.8</v>
       </c>
       <c r="H137" t="n">
-        <v>16.3</v>
+        <v>8.3</v>
       </c>
       <c r="I137" t="n">
-        <v>62.9</v>
+        <v>50</v>
       </c>
       <c r="J137" t="n">
-        <v>18.6</v>
+        <v>11.1</v>
       </c>
       <c r="K137" t="n">
-        <v>37.9</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B138" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C138" t="n">
-        <v>81.8</v>
+        <v>63.2</v>
       </c>
       <c r="D138" t="n">
-        <v>20.9</v>
+        <v>45</v>
       </c>
       <c r="E138" t="n">
-        <v>60.9</v>
+        <v>18.2</v>
       </c>
       <c r="F138" t="n">
-        <v>20.9</v>
+        <v>45</v>
       </c>
       <c r="G138" t="n">
-        <v>21.2</v>
+        <v>26.9</v>
       </c>
       <c r="H138" t="n">
-        <v>10.7</v>
+        <v>7.7</v>
       </c>
       <c r="I138" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>36.5</v>
+        <v>25</v>
       </c>
       <c r="K138" t="n">
-        <v>34.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B139" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C139" t="n">
-        <v>51.8</v>
+        <v>74.7</v>
       </c>
       <c r="D139" t="n">
-        <v>21.2</v>
+        <v>16</v>
       </c>
       <c r="E139" t="n">
-        <v>30.6</v>
+        <v>58.7</v>
       </c>
       <c r="F139" t="n">
-        <v>21.2</v>
+        <v>16</v>
       </c>
       <c r="G139" t="n">
-        <v>23.6</v>
+        <v>25.5</v>
       </c>
       <c r="H139" t="n">
-        <v>13.9</v>
+        <v>16.9</v>
       </c>
       <c r="I139" t="n">
-        <v>48.8</v>
+        <v>27.5</v>
       </c>
       <c r="J139" t="n">
-        <v>22</v>
+        <v>42.5</v>
       </c>
       <c r="K139" t="n">
-        <v>29.7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B140" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C140" t="n">
-        <v>55.3</v>
+        <v>74.4</v>
       </c>
       <c r="D140" t="n">
-        <v>21.5</v>
+        <v>31</v>
       </c>
       <c r="E140" t="n">
-        <v>33.8</v>
+        <v>43.4</v>
       </c>
       <c r="F140" t="n">
-        <v>21.5</v>
+        <v>31</v>
       </c>
       <c r="G140" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="H140" t="n">
-        <v>12.9</v>
+        <v>1.6</v>
       </c>
       <c r="I140" t="n">
-        <v>42.2</v>
+        <v>44.4</v>
       </c>
       <c r="J140" t="n">
-        <v>28.9</v>
+        <v>25.9</v>
       </c>
       <c r="K140" t="n">
-        <v>56.4</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
+        <v>158</v>
+      </c>
+      <c r="B141" t="s">
         <v>159</v>
       </c>
-      <c r="B141" t="s">
-        <v>151</v>
-      </c>
       <c r="C141" t="n">
-        <v>58.9</v>
+        <v>71.4</v>
       </c>
       <c r="D141" t="n">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="E141" t="n">
-        <v>36.4</v>
+        <v>51.4</v>
       </c>
       <c r="F141" t="n">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="G141" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="H141" t="n">
-        <v>7</v>
+        <v>11.8</v>
       </c>
       <c r="I141" t="n">
-        <v>61</v>
+        <v>52.4</v>
       </c>
       <c r="J141" t="n">
-        <v>15.6</v>
+        <v>19</v>
       </c>
       <c r="K141" t="n">
-        <v>30.1</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="142">
@@ -6123,34 +6125,34 @@
         <v>160</v>
       </c>
       <c r="B142" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C142" t="n">
-        <v>72.4</v>
+        <v>69.6</v>
       </c>
       <c r="D142" t="n">
-        <v>14.8</v>
+        <v>25.5</v>
       </c>
       <c r="E142" t="n">
-        <v>57.6</v>
+        <v>44.1</v>
       </c>
       <c r="F142" t="n">
-        <v>14.8</v>
+        <v>25.5</v>
       </c>
       <c r="G142" t="n">
-        <v>29.7</v>
+        <v>17.1</v>
       </c>
       <c r="H142" t="n">
-        <v>13.8</v>
+        <v>5.5</v>
       </c>
       <c r="I142" t="n">
-        <v>30.4</v>
+        <v>56.2</v>
       </c>
       <c r="J142" t="n">
-        <v>33.9</v>
+        <v>16.7</v>
       </c>
       <c r="K142" t="n">
-        <v>58.3</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="143">
@@ -6158,34 +6160,34 @@
         <v>161</v>
       </c>
       <c r="B143" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C143" t="n">
-        <v>75</v>
+        <v>64.6</v>
       </c>
       <c r="D143" t="n">
-        <v>28.3</v>
+        <v>16.7</v>
       </c>
       <c r="E143" t="n">
-        <v>46.7</v>
+        <v>47.9</v>
       </c>
       <c r="F143" t="n">
-        <v>28.3</v>
+        <v>16.7</v>
       </c>
       <c r="G143" t="n">
-        <v>38.7</v>
+        <v>37.7</v>
       </c>
       <c r="H143" t="n">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="I143" t="n">
-        <v>50</v>
+        <v>29.6</v>
       </c>
       <c r="J143" t="n">
-        <v>8.3</v>
+        <v>48.1</v>
       </c>
       <c r="K143" t="n">
-        <v>66.7</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="144">
@@ -6193,34 +6195,34 @@
         <v>162</v>
       </c>
       <c r="B144" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C144" t="n">
-        <v>75.2</v>
+        <v>59</v>
       </c>
       <c r="D144" t="n">
-        <v>21.8</v>
+        <v>20.3</v>
       </c>
       <c r="E144" t="n">
-        <v>53.4</v>
+        <v>38.7</v>
       </c>
       <c r="F144" t="n">
-        <v>21.8</v>
+        <v>20.3</v>
       </c>
       <c r="G144" t="n">
-        <v>19.7</v>
+        <v>38.1</v>
       </c>
       <c r="H144" t="n">
-        <v>5.8</v>
+        <v>15.6</v>
       </c>
       <c r="I144" t="n">
-        <v>32.3</v>
+        <v>18.8</v>
       </c>
       <c r="J144" t="n">
-        <v>30.6</v>
+        <v>50</v>
       </c>
       <c r="K144" t="n">
-        <v>48.1</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="145">
@@ -6228,90 +6230,370 @@
         <v>163</v>
       </c>
       <c r="B145" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C145" t="n">
-        <v>33.3</v>
+        <v>64.4</v>
       </c>
       <c r="D145" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E145" t="n">
-        <v>8.3</v>
+        <v>47.4</v>
       </c>
       <c r="F145" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="H145" t="n">
-        <v>0</v>
-      </c>
-      <c r="I145"/>
-      <c r="J145"/>
-      <c r="K145"/>
+        <v>17</v>
+      </c>
+      <c r="I145" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="J145" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="K145" t="n">
+        <v>37.3</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
         <v>164</v>
       </c>
       <c r="B146" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C146" t="n">
-        <v>0</v>
+        <v>81.6</v>
       </c>
       <c r="D146" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E146" t="n">
+        <v>59</v>
+      </c>
+      <c r="F146" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="G146" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H146" t="n">
+        <v>11</v>
+      </c>
+      <c r="I146" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="J146" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="K146" t="n">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>165</v>
+      </c>
+      <c r="B147" t="s">
+        <v>159</v>
+      </c>
+      <c r="C147" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="D147" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="E147" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="F147" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="G147" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="H147" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="I147" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="J147" t="n">
+        <v>22</v>
+      </c>
+      <c r="K147" t="n">
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>166</v>
+      </c>
+      <c r="B148" t="s">
+        <v>159</v>
+      </c>
+      <c r="C148" t="n">
+        <v>56</v>
+      </c>
+      <c r="D148" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="E148" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="F148" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G148" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H148" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="I148" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="J148" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="K148" t="n">
+        <v>53.5</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>167</v>
+      </c>
+      <c r="B149" t="s">
+        <v>159</v>
+      </c>
+      <c r="C149" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="D149" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E149" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="F149" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G149" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H149" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I149" t="n">
+        <v>58</v>
+      </c>
+      <c r="J149" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="K149" t="n">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>168</v>
+      </c>
+      <c r="B150" t="s">
+        <v>159</v>
+      </c>
+      <c r="C150" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="D150" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="E150" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="F150" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="G150" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H150" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="I150" t="n">
+        <v>30</v>
+      </c>
+      <c r="J150" t="n">
+        <v>35</v>
+      </c>
+      <c r="K150" t="n">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>169</v>
+      </c>
+      <c r="B151" t="s">
+        <v>159</v>
+      </c>
+      <c r="C151" t="n">
+        <v>74</v>
+      </c>
+      <c r="D151" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="E151" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="F151" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="G151" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="H151" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I151" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="J151" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="K151" t="n">
+        <v>69.2</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>170</v>
+      </c>
+      <c r="B152" t="s">
+        <v>159</v>
+      </c>
+      <c r="C152" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D152" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E152" t="n">
+        <v>51</v>
+      </c>
+      <c r="F152" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G152" t="n">
+        <v>19</v>
+      </c>
+      <c r="H152" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I152" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="J152" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="K152" t="n">
+        <v>45.6</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>171</v>
+      </c>
+      <c r="B153" t="s">
+        <v>159</v>
+      </c>
+      <c r="C153" t="n">
         <v>33.3</v>
       </c>
-      <c r="E146" t="n">
+      <c r="D153" t="n">
+        <v>25</v>
+      </c>
+      <c r="E153" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="F153" t="n">
+        <v>25</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153"/>
+      <c r="J153"/>
+      <c r="K153"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>172</v>
+      </c>
+      <c r="B154" t="s">
+        <v>159</v>
+      </c>
+      <c r="C154" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E154" t="n">
         <v>-33.3</v>
       </c>
-      <c r="F146" t="n">
+      <c r="F154" t="n">
         <v>33.3</v>
       </c>
-      <c r="G146" t="n">
+      <c r="G154" t="n">
         <v>100</v>
       </c>
-      <c r="H146" t="n">
-        <v>0</v>
-      </c>
-      <c r="I146"/>
-      <c r="J146"/>
-      <c r="K146"/>
-    </row>
-    <row r="147">
-      <c r="A147"/>
-      <c r="B147" t="s">
-        <v>165</v>
-      </c>
-      <c r="C147" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="D147" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E147" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="F147" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="G147" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="H147" t="n">
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154"/>
+      <c r="J154"/>
+      <c r="K154"/>
+    </row>
+    <row r="155">
+      <c r="A155"/>
+      <c r="B155" t="s">
+        <v>173</v>
+      </c>
+      <c r="C155" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="D155" t="n">
+        <v>26</v>
+      </c>
+      <c r="E155" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="F155" t="n">
+        <v>26</v>
+      </c>
+      <c r="G155" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="H155" t="n">
         <v>9.4</v>
       </c>
-      <c r="I147" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="J147" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="K147" t="n">
-        <v>39.4</v>
+      <c r="I155" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="J155" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="K155" t="n">
+        <v>37.6</v>
       </c>
     </row>
   </sheetData>
@@ -6343,22 +6625,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -6367,18 +6649,18 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -6448,7 +6730,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -6518,7 +6800,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -6553,7 +6835,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -6588,7 +6870,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -6658,7 +6940,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
@@ -6693,7 +6975,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -6728,7 +7010,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -6763,7 +7045,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -6831,7 +7113,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
@@ -6866,7 +7148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s">
         <v>31</v>
@@ -6901,7 +7183,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s">
         <v>31</v>
@@ -6936,7 +7218,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
@@ -6971,7 +7253,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B19" t="s">
         <v>31</v>
@@ -7006,7 +7288,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B20" t="s">
         <v>31</v>
@@ -7041,7 +7323,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B21" t="s">
         <v>31</v>
@@ -7076,7 +7358,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B22" t="s">
         <v>31</v>
@@ -7111,7 +7393,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B23" t="s">
         <v>31</v>
@@ -7146,7 +7428,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
@@ -7181,7 +7463,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
@@ -7216,7 +7498,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B26" t="s">
         <v>31</v>
@@ -7251,7 +7533,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="B27" t="s">
         <v>31</v>
@@ -7286,7 +7568,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B28" t="s">
         <v>31</v>
@@ -7321,7 +7603,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B29" t="s">
         <v>46</v>
@@ -7356,7 +7638,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B30" t="s">
         <v>46</v>
@@ -7426,7 +7708,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B32" t="s">
         <v>46</v>
@@ -7461,7 +7743,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B33" t="s">
         <v>46</v>
@@ -7496,7 +7778,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="B34" t="s">
         <v>46</v>
@@ -7531,7 +7813,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B35" t="s">
         <v>46</v>
@@ -7564,112 +7846,112 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="B36" t="s">
         <v>46</v>
       </c>
       <c r="C36" t="n">
-        <v>68.3</v>
+        <v>68.1</v>
       </c>
       <c r="D36" t="n">
-        <v>65.7</v>
+        <v>64.3</v>
       </c>
       <c r="E36" t="n">
-        <v>30.1</v>
+        <v>30.7</v>
       </c>
       <c r="F36" t="n">
-        <v>48</v>
+        <v>53.6</v>
       </c>
       <c r="G36" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="H36" t="n">
-        <v>62.8</v>
+        <v>60.4</v>
       </c>
       <c r="I36" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="J36" t="n">
-        <v>18.7</v>
+        <v>19.2</v>
       </c>
       <c r="K36" t="n">
-        <v>19</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B37" t="s">
         <v>46</v>
       </c>
       <c r="C37" t="n">
-        <v>58.3</v>
+        <v>59.1</v>
       </c>
       <c r="D37" t="n">
-        <v>62.1</v>
+        <v>62.9</v>
       </c>
       <c r="E37" t="n">
-        <v>15.6</v>
+        <v>19.6</v>
       </c>
       <c r="F37" t="n">
-        <v>45.5</v>
+        <v>48.1</v>
       </c>
       <c r="G37" t="n">
-        <v>11.7</v>
+        <v>12.1</v>
       </c>
       <c r="H37" t="n">
-        <v>52.5</v>
+        <v>50</v>
       </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
-        <v>27.3</v>
+        <v>30.4</v>
       </c>
       <c r="K37" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B38" t="s">
         <v>46</v>
       </c>
       <c r="C38" t="n">
-        <v>69.8</v>
+        <v>68.4</v>
       </c>
       <c r="D38" t="n">
-        <v>70.1</v>
+        <v>70.6</v>
       </c>
       <c r="E38" t="n">
-        <v>25.2</v>
+        <v>31.8</v>
       </c>
       <c r="F38" t="n">
-        <v>49.2</v>
+        <v>47.8</v>
       </c>
       <c r="G38" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="H38" t="n">
-        <v>28.6</v>
+        <v>31.9</v>
       </c>
       <c r="I38" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="J38" t="n">
-        <v>31</v>
+        <v>27.9</v>
       </c>
       <c r="K38" t="n">
-        <v>28.7</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="B39" t="s">
         <v>46</v>
@@ -7704,7 +7986,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B40" t="s">
         <v>46</v>
@@ -7739,7 +8021,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
@@ -7772,7 +8054,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B42" t="s">
         <v>46</v>
@@ -7807,7 +8089,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B43" t="s">
         <v>63</v>
@@ -7842,7 +8124,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B44" t="s">
         <v>63</v>
@@ -7877,7 +8159,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B45" t="s">
         <v>63</v>
@@ -7912,7 +8194,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B46" t="s">
         <v>63</v>
@@ -7945,7 +8227,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B47" t="s">
         <v>63</v>
@@ -7980,7 +8262,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B48" t="s">
         <v>63</v>
@@ -8015,7 +8297,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B49" t="s">
         <v>63</v>
@@ -8050,7 +8332,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B50" t="s">
         <v>63</v>
@@ -8085,7 +8367,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B51" t="s">
         <v>63</v>
@@ -8120,7 +8402,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B52" t="s">
         <v>63</v>
@@ -8155,7 +8437,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B53" t="s">
         <v>63</v>
@@ -8223,7 +8505,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B55" t="s">
         <v>63</v>
@@ -8291,7 +8573,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B57" t="s">
         <v>84</v>
@@ -8326,7 +8608,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B58" t="s">
         <v>84</v>
@@ -8361,7 +8643,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B59" t="s">
         <v>84</v>
@@ -8396,7 +8678,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B60" t="s">
         <v>84</v>
@@ -8431,7 +8713,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B61" t="s">
         <v>84</v>
@@ -8466,7 +8748,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B62" t="s">
         <v>84</v>
@@ -8501,7 +8783,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B63" t="s">
         <v>84</v>
@@ -8536,7 +8818,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B64" t="s">
         <v>84</v>
@@ -8571,7 +8853,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B65" t="s">
         <v>84</v>
@@ -8606,7 +8888,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B66" t="s">
         <v>84</v>
@@ -8641,7 +8923,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B67" t="s">
         <v>84</v>
@@ -8676,7 +8958,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B68" t="s">
         <v>84</v>
@@ -8711,112 +8993,112 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B69" t="s">
         <v>98</v>
       </c>
       <c r="C69" t="n">
-        <v>40</v>
+        <v>42.4</v>
       </c>
       <c r="D69" t="n">
-        <v>47.8</v>
+        <v>44.8</v>
       </c>
       <c r="E69" t="n">
-        <v>13.2</v>
+        <v>12.2</v>
       </c>
       <c r="F69" t="n">
-        <v>52.4</v>
+        <v>50</v>
       </c>
       <c r="G69" t="n">
-        <v>22</v>
+        <v>30.5</v>
       </c>
       <c r="H69" t="n">
-        <v>43.5</v>
+        <v>41.7</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="J69" t="n">
-        <v>34.8</v>
+        <v>32.9</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>-10.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B70" t="s">
         <v>98</v>
       </c>
       <c r="C70" t="n">
-        <v>73.7</v>
+        <v>70.3</v>
       </c>
       <c r="D70" t="n">
-        <v>65.2</v>
+        <v>61.8</v>
       </c>
       <c r="E70" t="n">
         <v>23.1</v>
       </c>
       <c r="F70" t="n">
-        <v>43.3</v>
+        <v>40.6</v>
       </c>
       <c r="G70" t="n">
-        <v>10.3</v>
+        <v>13.6</v>
       </c>
       <c r="H70" t="n">
-        <v>51.4</v>
+        <v>51.2</v>
       </c>
       <c r="I70" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="J70" t="n">
-        <v>29.3</v>
+        <v>28.8</v>
       </c>
       <c r="K70" t="n">
-        <v>12.1</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B71" t="s">
         <v>98</v>
       </c>
       <c r="C71" t="n">
-        <v>52.4</v>
+        <v>49</v>
       </c>
       <c r="D71" t="n">
-        <v>57.8</v>
+        <v>54.2</v>
       </c>
       <c r="E71" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F71" t="n">
-        <v>50</v>
+        <v>47.6</v>
       </c>
       <c r="G71" t="n">
-        <v>9.8</v>
+        <v>14</v>
       </c>
       <c r="H71" t="n">
-        <v>45.8</v>
+        <v>51.7</v>
       </c>
       <c r="I71" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K71" t="n">
-        <v>12.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B72" t="s">
         <v>98</v>
@@ -8849,7 +9131,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="B73" t="s">
         <v>98</v>
@@ -8884,7 +9166,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>235</v>
+        <v>101</v>
       </c>
       <c r="B74" t="s">
         <v>98</v>
@@ -8919,7 +9201,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B75" t="s">
         <v>98</v>
@@ -8954,40 +9236,42 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B76" t="s">
         <v>98</v>
       </c>
       <c r="C76" t="n">
-        <v>40</v>
+        <v>48.1</v>
       </c>
       <c r="D76" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="E76"/>
+        <v>51.3</v>
+      </c>
+      <c r="E76" t="n">
+        <v>31.7</v>
+      </c>
       <c r="F76" t="n">
-        <v>25</v>
+        <v>30.8</v>
       </c>
       <c r="G76" t="n">
-        <v>10</v>
+        <v>18.5</v>
       </c>
       <c r="H76" t="n">
-        <v>83.3</v>
+        <v>46.7</v>
       </c>
       <c r="I76" t="n">
-        <v>10</v>
+        <v>3.7</v>
       </c>
       <c r="J76" t="n">
-        <v>16.7</v>
+        <v>29.4</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B77" t="s">
         <v>98</v>
@@ -9022,7 +9306,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="B78" t="s">
         <v>98</v>
@@ -9057,7 +9341,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B79" t="s">
         <v>98</v>
@@ -9092,60 +9376,60 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="B80" t="s">
         <v>98</v>
       </c>
       <c r="C80" t="n">
-        <v>50.8</v>
+        <v>55.3</v>
       </c>
       <c r="D80" t="n">
-        <v>58.6</v>
+        <v>59.9</v>
       </c>
       <c r="E80" t="n">
-        <v>23.2</v>
+        <v>30.8</v>
       </c>
       <c r="F80" t="n">
-        <v>36.4</v>
+        <v>40</v>
       </c>
       <c r="G80" t="n">
-        <v>11.9</v>
+        <v>9.2</v>
       </c>
       <c r="H80" t="n">
-        <v>60</v>
+        <v>58.7</v>
       </c>
       <c r="I80" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
-        <v>21.8</v>
+        <v>24.1</v>
       </c>
       <c r="K80" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B81" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C81" t="n">
-        <v>66.7</v>
+        <v>70.4</v>
       </c>
       <c r="D81" t="n">
-        <v>65.9</v>
+        <v>68.2</v>
       </c>
       <c r="E81" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
       <c r="F81" t="n">
-        <v>25</v>
+        <v>30.8</v>
       </c>
       <c r="G81" t="n">
-        <v>12</v>
+        <v>10.7</v>
       </c>
       <c r="H81" t="n">
         <v>50</v>
@@ -9154,53 +9438,53 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>18.9</v>
+        <v>23.8</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B82" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C82" t="n">
-        <v>54.5</v>
+        <v>55.6</v>
       </c>
       <c r="D82" t="n">
-        <v>56.9</v>
+        <v>57.4</v>
       </c>
       <c r="E82" t="n">
-        <v>26.9</v>
+        <v>26.5</v>
       </c>
       <c r="F82" t="n">
-        <v>40</v>
+        <v>35.3</v>
       </c>
       <c r="G82" t="n">
-        <v>15.2</v>
+        <v>13.9</v>
       </c>
       <c r="H82" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="I82" t="n">
-        <v>9.1</v>
+        <v>8.3</v>
       </c>
       <c r="J82" t="n">
-        <v>33.9</v>
+        <v>31.1</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B83" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C83" t="n">
         <v>59.8</v>
@@ -9232,10 +9516,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="B84" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C84" t="n">
         <v>61.2</v>
@@ -9267,45 +9551,45 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B85" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C85" t="n">
-        <v>70</v>
+        <v>71.1</v>
       </c>
       <c r="D85" t="n">
-        <v>67.4</v>
+        <v>68.4</v>
       </c>
       <c r="E85" t="n">
-        <v>36.8</v>
+        <v>36.5</v>
       </c>
       <c r="F85" t="n">
-        <v>66.7</v>
+        <v>68.2</v>
       </c>
       <c r="G85" t="n">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="H85" t="n">
         <v>50</v>
       </c>
       <c r="I85" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J85" t="n">
-        <v>34.3</v>
+        <v>32.4</v>
       </c>
       <c r="K85" t="n">
-        <v>27.5</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B86" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C86" t="n">
         <v>57.8</v>
@@ -9337,10 +9621,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="B87" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C87" t="n">
         <v>71.9</v>
@@ -9372,10 +9656,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B88" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C88" t="n">
         <v>66.2</v>
@@ -9407,45 +9691,45 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B89" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C89" t="n">
-        <v>70.3</v>
+        <v>70.4</v>
       </c>
       <c r="D89" t="n">
-        <v>71.3</v>
+        <v>71.2</v>
       </c>
       <c r="E89" t="n">
-        <v>31.7</v>
+        <v>34.2</v>
       </c>
       <c r="F89" t="n">
-        <v>51.6</v>
+        <v>47.9</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>40.7</v>
+        <v>42.6</v>
       </c>
       <c r="I89" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J89" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="K89" t="n">
-        <v>22.1</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="B90" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C90" t="n">
         <v>63.8</v>
@@ -9477,45 +9761,45 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="B91" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C91" t="n">
         <v>50</v>
       </c>
       <c r="D91" t="n">
-        <v>52.6</v>
+        <v>54.4</v>
       </c>
       <c r="E91" t="n">
-        <v>10.3</v>
+        <v>14.3</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G91" t="n">
-        <v>17.9</v>
+        <v>15.6</v>
       </c>
       <c r="H91" t="n">
-        <v>40</v>
+        <v>40.9</v>
       </c>
       <c r="I91" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="J91" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="K91" t="n">
-        <v>-17.9</v>
+        <v>-9.4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B92" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C92" t="n">
         <v>50.9</v>
@@ -9547,10 +9831,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="B93" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C93" t="n">
         <v>52</v>
@@ -9582,908 +9866,941 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="B94" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C94" t="n">
-        <v>69.6</v>
+        <v>67.4</v>
       </c>
       <c r="D94" t="n">
-        <v>67.9</v>
+        <v>65.1</v>
       </c>
       <c r="E94" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F94" t="n">
-        <v>44.4</v>
+        <v>43.8</v>
       </c>
       <c r="G94" t="n">
         <v>8.7</v>
       </c>
       <c r="H94" t="n">
-        <v>35.3</v>
+        <v>37.1</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J94" t="n">
-        <v>20.5</v>
+        <v>16.9</v>
       </c>
       <c r="K94" t="n">
-        <v>8.7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B95" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C95" t="n">
-        <v>66.1</v>
+        <v>50</v>
       </c>
       <c r="D95" t="n">
-        <v>60.9</v>
+        <v>45.5</v>
       </c>
       <c r="E95" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="F95" t="n">
-        <v>11.5</v>
-      </c>
+        <v>22.2</v>
+      </c>
+      <c r="F95"/>
       <c r="G95" t="n">
-        <v>14.3</v>
+        <v>25</v>
       </c>
       <c r="H95" t="n">
-        <v>47.7</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>-8.9</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="B96" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C96" t="n">
-        <v>53.6</v>
+        <v>68.8</v>
       </c>
       <c r="D96" t="n">
-        <v>64.1</v>
+        <v>62.5</v>
       </c>
       <c r="E96" t="n">
-        <v>8.3</v>
+        <v>31.3</v>
       </c>
       <c r="F96" t="n">
-        <v>20</v>
+        <v>9.7</v>
       </c>
       <c r="G96" t="n">
-        <v>3.6</v>
+        <v>15.6</v>
       </c>
       <c r="H96" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I96" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J96" t="n">
-        <v>13.6</v>
+        <v>20.2</v>
       </c>
       <c r="K96" t="n">
-        <v>3.5</v>
+        <v>-10.9</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>141</v>
+        <v>263</v>
       </c>
       <c r="B97" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C97" t="n">
-        <v>51.2</v>
+        <v>53.6</v>
       </c>
       <c r="D97" t="n">
-        <v>56.6</v>
+        <v>64.1</v>
       </c>
       <c r="E97" t="n">
-        <v>24.5</v>
+        <v>8.3</v>
       </c>
       <c r="F97" t="n">
-        <v>34.8</v>
+        <v>20</v>
       </c>
       <c r="G97" t="n">
-        <v>20.9</v>
+        <v>3.6</v>
       </c>
       <c r="H97" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I97" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="J97" t="n">
-        <v>28.6</v>
+        <v>13.6</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>256</v>
+        <v>147</v>
       </c>
       <c r="B98" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C98" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="D98" t="n">
-        <v>58.3</v>
+        <v>57.7</v>
       </c>
       <c r="E98" t="n">
-        <v>26.9</v>
+        <v>29</v>
       </c>
       <c r="F98" t="n">
-        <v>14.3</v>
+        <v>32</v>
       </c>
       <c r="G98" t="n">
         <v>18.8</v>
       </c>
       <c r="H98" t="n">
-        <v>41.7</v>
+        <v>44</v>
       </c>
       <c r="I98" t="n">
-        <v>6.2</v>
+        <v>8.3</v>
       </c>
       <c r="J98" t="n">
-        <v>17.9</v>
+        <v>25</v>
       </c>
       <c r="K98" t="n">
-        <v>-12.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B99" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C99" t="n">
-        <v>52.6</v>
+        <v>66.7</v>
       </c>
       <c r="D99" t="n">
-        <v>56.2</v>
+        <v>62.1</v>
       </c>
       <c r="E99" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F99" t="n">
-        <v>10</v>
+        <v>9.1</v>
       </c>
       <c r="G99" t="n">
-        <v>15.8</v>
+        <v>12.5</v>
       </c>
       <c r="H99" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I99" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="J99" t="n">
-        <v>15.2</v>
+        <v>15.6</v>
       </c>
       <c r="K99" t="n">
-        <v>-10.5</v>
+        <v>-8.3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="B100" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C100" t="n">
-        <v>59.2</v>
+        <v>52.6</v>
       </c>
       <c r="D100" t="n">
-        <v>61.6</v>
+        <v>56.2</v>
       </c>
       <c r="E100" t="n">
-        <v>28.6</v>
+        <v>30</v>
       </c>
       <c r="F100" t="n">
-        <v>61.1</v>
+        <v>10</v>
       </c>
       <c r="G100" t="n">
-        <v>12.7</v>
+        <v>15.8</v>
       </c>
       <c r="H100" t="n">
-        <v>36.1</v>
+        <v>50</v>
       </c>
       <c r="I100" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="J100" t="n">
-        <v>32.8</v>
+        <v>15.2</v>
       </c>
       <c r="K100" t="n">
-        <v>18.3</v>
+        <v>-10.5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B101" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C101" t="n">
-        <v>55.6</v>
+        <v>59.2</v>
       </c>
       <c r="D101" t="n">
-        <v>61.3</v>
+        <v>61.6</v>
       </c>
       <c r="E101" t="n">
-        <v>26.9</v>
+        <v>28.6</v>
       </c>
       <c r="F101" t="n">
-        <v>36.4</v>
+        <v>61.1</v>
       </c>
       <c r="G101" t="n">
-        <v>16.7</v>
+        <v>12.7</v>
       </c>
       <c r="H101" t="n">
-        <v>40</v>
+        <v>36.1</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="J101" t="n">
-        <v>27.8</v>
+        <v>32.8</v>
       </c>
       <c r="K101" t="n">
-        <v>5.5</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B102" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C102" t="n">
-        <v>44</v>
+        <v>57.6</v>
       </c>
       <c r="D102" t="n">
-        <v>56.3</v>
+        <v>62.5</v>
       </c>
       <c r="E102" t="n">
-        <v>23.1</v>
+        <v>34.3</v>
       </c>
       <c r="F102" t="n">
-        <v>38.5</v>
+        <v>45</v>
       </c>
       <c r="G102" t="n">
-        <v>8</v>
+        <v>12.1</v>
       </c>
       <c r="H102" t="n">
         <v>50</v>
       </c>
       <c r="I102" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>26.5</v>
+        <v>36.4</v>
       </c>
       <c r="K102" t="n">
-        <v>12</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="B103" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C103" t="n">
-        <v>38.9</v>
+        <v>44</v>
       </c>
       <c r="D103" t="n">
-        <v>52</v>
+        <v>56.3</v>
       </c>
       <c r="E103" t="n">
-        <v>16.3</v>
+        <v>23.1</v>
       </c>
       <c r="F103" t="n">
-        <v>33.3</v>
+        <v>38.5</v>
       </c>
       <c r="G103" t="n">
-        <v>27.8</v>
+        <v>8</v>
       </c>
       <c r="H103" t="n">
-        <v>22.2</v>
+        <v>50</v>
       </c>
       <c r="I103" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="J103" t="n">
-        <v>31</v>
+        <v>26.5</v>
       </c>
       <c r="K103" t="n">
-        <v>-11.1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="B104" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C104" t="n">
-        <v>60.9</v>
+        <v>38.9</v>
       </c>
       <c r="D104" t="n">
-        <v>61.6</v>
+        <v>52</v>
       </c>
       <c r="E104" t="n">
-        <v>23.9</v>
+        <v>16.3</v>
       </c>
       <c r="F104" t="n">
-        <v>32.6</v>
+        <v>33.3</v>
       </c>
       <c r="G104" t="n">
-        <v>8</v>
+        <v>27.8</v>
       </c>
       <c r="H104" t="n">
-        <v>58.9</v>
+        <v>22.2</v>
       </c>
       <c r="I104" t="n">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="J104" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K104" t="n">
-        <v>9.2</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B105" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C105" t="n">
-        <v>57.8</v>
+        <v>62</v>
       </c>
       <c r="D105" t="n">
-        <v>60.9</v>
+        <v>63.2</v>
       </c>
       <c r="E105" t="n">
-        <v>20.1</v>
+        <v>26.6</v>
       </c>
       <c r="F105" t="n">
-        <v>40.5</v>
+        <v>27.8</v>
       </c>
       <c r="G105" t="n">
-        <v>4.3</v>
+        <v>8.3</v>
       </c>
       <c r="H105" t="n">
-        <v>40.9</v>
+        <v>57.3</v>
       </c>
       <c r="I105" t="n">
-        <v>7.8</v>
+        <v>2.8</v>
       </c>
       <c r="J105" t="n">
-        <v>15.3</v>
+        <v>22.8</v>
       </c>
       <c r="K105" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B106" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C106" t="n">
-        <v>64.2</v>
+        <v>57.8</v>
       </c>
       <c r="D106" t="n">
-        <v>68.7</v>
+        <v>60.8</v>
       </c>
       <c r="E106" t="n">
-        <v>25</v>
+        <v>21.6</v>
       </c>
       <c r="F106" t="n">
-        <v>46.3</v>
+        <v>39.5</v>
       </c>
       <c r="G106" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="H106" t="n">
-        <v>49.5</v>
+        <v>41.7</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J106" t="n">
-        <v>22.2</v>
+        <v>15.6</v>
       </c>
       <c r="K106" t="n">
-        <v>16</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B107" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C107" t="n">
-        <v>55.7</v>
+        <v>64.2</v>
       </c>
       <c r="D107" t="n">
-        <v>64.6</v>
+        <v>68.7</v>
       </c>
       <c r="E107" t="n">
-        <v>15.2</v>
+        <v>25</v>
       </c>
       <c r="F107" t="n">
-        <v>33.3</v>
+        <v>46.3</v>
       </c>
       <c r="G107" t="n">
-        <v>8.6</v>
+        <v>2.2</v>
       </c>
       <c r="H107" t="n">
-        <v>30.9</v>
+        <v>49.5</v>
       </c>
       <c r="I107" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>21.3</v>
+        <v>22.2</v>
       </c>
       <c r="K107" t="n">
-        <v>4.3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B108" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C108" t="n">
-        <v>59</v>
+        <v>55.7</v>
       </c>
       <c r="D108" t="n">
-        <v>67.1</v>
+        <v>64.6</v>
       </c>
       <c r="E108" t="n">
-        <v>39.6</v>
+        <v>15.2</v>
       </c>
       <c r="F108" t="n">
-        <v>72</v>
+        <v>33.3</v>
       </c>
       <c r="G108" t="n">
-        <v>5.3</v>
+        <v>8.6</v>
       </c>
       <c r="H108" t="n">
-        <v>50</v>
+        <v>30.9</v>
       </c>
       <c r="I108" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="J108" t="n">
-        <v>41.3</v>
+        <v>21.3</v>
       </c>
       <c r="K108" t="n">
-        <v>44.7</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>198</v>
+        <v>274</v>
       </c>
       <c r="B109" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C109" t="n">
-        <v>63.3</v>
+        <v>59</v>
       </c>
       <c r="D109" t="n">
-        <v>60.7</v>
+        <v>67.1</v>
       </c>
       <c r="E109" t="n">
-        <v>13.6</v>
+        <v>39.6</v>
       </c>
       <c r="F109" t="n">
-        <v>41.7</v>
+        <v>72</v>
       </c>
       <c r="G109" t="n">
-        <v>10.3</v>
+        <v>5.3</v>
       </c>
       <c r="H109" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="I109" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J109" t="n">
-        <v>29.2</v>
+        <v>41.3</v>
       </c>
       <c r="K109" t="n">
-        <v>6.9</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>267</v>
+        <v>206</v>
       </c>
       <c r="B110" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C110" t="n">
-        <v>63.6</v>
+        <v>62.5</v>
       </c>
       <c r="D110" t="n">
-        <v>62.2</v>
+        <v>61.2</v>
       </c>
       <c r="E110" t="n">
-        <v>34.7</v>
+        <v>26.9</v>
       </c>
       <c r="F110" t="n">
-        <v>44.4</v>
+        <v>36.4</v>
       </c>
       <c r="G110" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="H110" t="n">
-        <v>53.8</v>
+        <v>42.5</v>
       </c>
       <c r="I110" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="J110" t="n">
-        <v>43.2</v>
+        <v>26.8</v>
       </c>
       <c r="K110" t="n">
-        <v>20.5</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B111" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C111" t="n">
-        <v>84.6</v>
+        <v>63.6</v>
       </c>
       <c r="D111" t="n">
-        <v>74.4</v>
-      </c>
-      <c r="E111"/>
+        <v>62.2</v>
+      </c>
+      <c r="E111" t="n">
+        <v>34.7</v>
+      </c>
       <c r="F111" t="n">
-        <v>47.1</v>
+        <v>44.4</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="H111" t="n">
-        <v>45.2</v>
+        <v>53.8</v>
       </c>
       <c r="I111" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J111" t="n">
-        <v>28.4</v>
+        <v>43.2</v>
       </c>
       <c r="K111" t="n">
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B112" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C112" t="n">
-        <v>50</v>
+        <v>84.6</v>
       </c>
       <c r="D112" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="E112" t="n">
-        <v>0</v>
-      </c>
+        <v>74.4</v>
+      </c>
+      <c r="E112"/>
       <c r="F112" t="n">
-        <v>25</v>
+        <v>47.1</v>
       </c>
       <c r="G112" t="n">
-        <v>30.8</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>37.5</v>
+        <v>45.2</v>
       </c>
       <c r="I112" t="n">
-        <v>7.7</v>
+        <v>2.4</v>
       </c>
       <c r="J112" t="n">
-        <v>31.2</v>
+        <v>28.4</v>
       </c>
       <c r="K112" t="n">
-        <v>-23.1</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B113" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C113" t="n">
-        <v>60.7</v>
+        <v>50</v>
       </c>
       <c r="D113" t="n">
-        <v>62.4</v>
+        <v>45.1</v>
       </c>
       <c r="E113" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G113" t="n">
-        <v>17.9</v>
+        <v>30.8</v>
       </c>
       <c r="H113" t="n">
-        <v>56.2</v>
+        <v>37.5</v>
       </c>
       <c r="I113" t="n">
-        <v>3.6</v>
+        <v>7.7</v>
       </c>
       <c r="J113" t="n">
-        <v>28.9</v>
+        <v>31.2</v>
       </c>
       <c r="K113" t="n">
-        <v>3.5</v>
+        <v>-23.1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="B114" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C114" t="n">
-        <v>65.8</v>
+        <v>61.3</v>
       </c>
       <c r="D114" t="n">
-        <v>67.5</v>
+        <v>64.8</v>
       </c>
       <c r="E114" t="n">
-        <v>36.4</v>
+        <v>27.4</v>
       </c>
       <c r="F114" t="n">
-        <v>38.1</v>
+        <v>31.8</v>
       </c>
       <c r="G114" t="n">
-        <v>7.9</v>
+        <v>16.1</v>
       </c>
       <c r="H114" t="n">
-        <v>53.8</v>
+        <v>50</v>
       </c>
       <c r="I114" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J114" t="n">
-        <v>26.8</v>
+        <v>29.4</v>
       </c>
       <c r="K114" t="n">
-        <v>13.2</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B115" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C115" t="n">
-        <v>52.3</v>
+        <v>65.8</v>
       </c>
       <c r="D115" t="n">
-        <v>60.1</v>
+        <v>67.5</v>
       </c>
       <c r="E115" t="n">
-        <v>20.8</v>
+        <v>36.4</v>
       </c>
       <c r="F115" t="n">
-        <v>46.7</v>
+        <v>38.1</v>
       </c>
       <c r="G115" t="n">
-        <v>10.5</v>
+        <v>7.9</v>
       </c>
       <c r="H115" t="n">
-        <v>52.7</v>
+        <v>53.8</v>
       </c>
       <c r="I115" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J115" t="n">
-        <v>24.5</v>
+        <v>26.8</v>
       </c>
       <c r="K115" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="B116" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C116" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D116" t="n">
-        <v>56.7</v>
+        <v>60.6</v>
       </c>
       <c r="E116" t="n">
-        <v>14.3</v>
+        <v>26.2</v>
       </c>
       <c r="F116" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G116" t="n">
-        <v>22.2</v>
+        <v>10.4</v>
       </c>
       <c r="H116" t="n">
-        <v>20</v>
+        <v>54.8</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J116" t="n">
-        <v>25</v>
+        <v>23.6</v>
       </c>
       <c r="K116" t="n">
-        <v>0</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="B117" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C117" t="n">
         <v>66.7</v>
       </c>
       <c r="D117" t="n">
-        <v>67.7</v>
+        <v>56.7</v>
       </c>
       <c r="E117" t="n">
-        <v>26.1</v>
+        <v>14.3</v>
       </c>
       <c r="F117" t="n">
         <v>50</v>
       </c>
       <c r="G117" t="n">
-        <v>5.7</v>
+        <v>22.2</v>
       </c>
       <c r="H117" t="n">
-        <v>38.7</v>
+        <v>20</v>
       </c>
       <c r="I117" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>25.9</v>
+        <v>25</v>
       </c>
       <c r="K117" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B118" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C118" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D118" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="E118" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F118" t="n">
+        <v>50</v>
+      </c>
+      <c r="G118" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H118" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="I118" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J118" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="K118" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>283</v>
+      </c>
+      <c r="B119" t="s">
+        <v>159</v>
+      </c>
+      <c r="C119" t="n">
         <v>61.7</v>
       </c>
-      <c r="D118" t="n">
+      <c r="D119" t="n">
         <v>63.5</v>
       </c>
-      <c r="E118" t="n">
+      <c r="E119" t="n">
         <v>24.5</v>
       </c>
-      <c r="F118" t="n">
+      <c r="F119" t="n">
         <v>48</v>
       </c>
-      <c r="G118" t="n">
+      <c r="G119" t="n">
         <v>6.7</v>
       </c>
-      <c r="H118" t="n">
+      <c r="H119" t="n">
         <v>46.5</v>
       </c>
-      <c r="I118" t="n">
+      <c r="I119" t="n">
         <v>5</v>
       </c>
-      <c r="J118" t="n">
+      <c r="J119" t="n">
         <v>20.4</v>
       </c>
-      <c r="K118" t="n">
+      <c r="K119" t="n">
         <v>13.3</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119"/>
-      <c r="B119" t="s">
-        <v>165</v>
-      </c>
-      <c r="C119" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="D119" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="E119" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F119" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="G119" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H119" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="I119" t="n">
+    <row r="120">
+      <c r="A120"/>
+      <c r="B120" t="s">
+        <v>173</v>
+      </c>
+      <c r="C120" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="D120" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="E120" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F120" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="G120" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="H120" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="I120" t="n">
         <v>3.2</v>
       </c>
-      <c r="J119" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="K119" t="n">
-        <v>8.8</v>
+      <c r="J120" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="K120" t="n">
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/summary2026.xlsx
+++ b/data/summary2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="278">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -186,9 +186,6 @@
     <t xml:space="preserve">Owen Constantineau</t>
   </si>
   <si>
-    <t xml:space="preserve">Owen Costantineau</t>
-  </si>
-  <si>
     <t xml:space="preserve">Robert Mackie</t>
   </si>
   <si>
@@ -381,9 +378,6 @@
     <t xml:space="preserve">Jaden Babiuk</t>
   </si>
   <si>
-    <t xml:space="preserve">Jarret Burney</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jarrett Burney</t>
   </si>
   <si>
@@ -402,18 +396,12 @@
     <t xml:space="preserve">Starling Joseph</t>
   </si>
   <si>
-    <t xml:space="preserve">Trent Leniham</t>
-  </si>
-  <si>
     <t xml:space="preserve">Trent Lenihan</t>
   </si>
   <si>
     <t xml:space="preserve">Tucker Zdunich</t>
   </si>
   <si>
-    <t xml:space="preserve">Tucker Zdunrich</t>
-  </si>
-  <si>
     <t xml:space="preserve">Xavier Whittle</t>
   </si>
   <si>
@@ -438,15 +426,9 @@
     <t xml:space="preserve">Crixtian Taveras</t>
   </si>
   <si>
-    <t xml:space="preserve">Crixtian Taveres</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dennis Dei Baning</t>
   </si>
   <si>
-    <t xml:space="preserve">Dennis Dei Banning</t>
-  </si>
-  <si>
     <t xml:space="preserve">JJ Dutton</t>
   </si>
   <si>
@@ -678,6 +660,9 @@
     <t xml:space="preserve">Elvin Liriano</t>
   </si>
   <si>
+    <t xml:space="preserve">Gleyvin Pineda</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jacob Kush</t>
   </si>
   <si>
@@ -790,9 +775,6 @@
   </si>
   <si>
     <t xml:space="preserve">Alex Lanigan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cam Dimidjian</t>
   </si>
   <si>
     <t xml:space="preserve">Camden Dimidjian</t>
@@ -919,8 +901,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K155" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K155"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K149" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K149"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -1308,19 +1290,19 @@
         <v>40.4</v>
       </c>
       <c r="G2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="I2" t="n">
-        <v>41.9</v>
+        <v>43.8</v>
       </c>
       <c r="J2" t="n">
-        <v>25.8</v>
+        <v>25</v>
       </c>
       <c r="K2" t="n">
-        <v>45.2</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="3">
@@ -1368,19 +1350,19 @@
         <v>25.3</v>
       </c>
       <c r="G4" t="n">
-        <v>19.4</v>
+        <v>18.5</v>
       </c>
       <c r="H4" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="I4" t="n">
-        <v>39.5</v>
+        <v>42.9</v>
       </c>
       <c r="J4" t="n">
-        <v>21.1</v>
+        <v>19</v>
       </c>
       <c r="K4" t="n">
-        <v>27.3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -1438,19 +1420,19 @@
         <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>31.2</v>
+        <v>32.4</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="I6" t="n">
-        <v>45.5</v>
+        <v>45.7</v>
       </c>
       <c r="J6" t="n">
-        <v>27.3</v>
+        <v>26.1</v>
       </c>
       <c r="K6" t="n">
-        <v>35.9</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="7">
@@ -1473,19 +1455,19 @@
         <v>44.8</v>
       </c>
       <c r="G7" t="n">
-        <v>31.4</v>
+        <v>36.4</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>22.2</v>
+        <v>36.4</v>
       </c>
       <c r="J7" t="n">
-        <v>44.4</v>
+        <v>36.4</v>
       </c>
       <c r="K7" t="n">
-        <v>66.7</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="8">
@@ -1543,19 +1525,19 @@
         <v>16.9</v>
       </c>
       <c r="G9" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="H9" t="n">
-        <v>14</v>
+        <v>12.9</v>
       </c>
       <c r="I9" t="n">
-        <v>50</v>
+        <v>52.6</v>
       </c>
       <c r="J9" t="n">
-        <v>29.4</v>
+        <v>28.9</v>
       </c>
       <c r="K9" t="n">
-        <v>37.9</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="10">
@@ -1578,19 +1560,19 @@
         <v>16.5</v>
       </c>
       <c r="G10" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="H10" t="n">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="I10" t="n">
-        <v>42.1</v>
+        <v>42.5</v>
       </c>
       <c r="J10" t="n">
-        <v>42.1</v>
+        <v>42.5</v>
       </c>
       <c r="K10" t="n">
-        <v>45.5</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="11">
@@ -1716,19 +1698,19 @@
         <v>22.4</v>
       </c>
       <c r="G14" t="n">
-        <v>29.4</v>
+        <v>32.1</v>
       </c>
       <c r="H14" t="n">
-        <v>10.3</v>
+        <v>11.8</v>
       </c>
       <c r="I14" t="n">
-        <v>40</v>
+        <v>40.9</v>
       </c>
       <c r="J14" t="n">
-        <v>30</v>
+        <v>31.8</v>
       </c>
       <c r="K14" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="15">
@@ -1786,19 +1768,19 @@
         <v>26.2</v>
       </c>
       <c r="G16" t="n">
-        <v>22</v>
+        <v>24.6</v>
       </c>
       <c r="H16" t="n">
-        <v>9.2</v>
+        <v>10.1</v>
       </c>
       <c r="I16" t="n">
         <v>50</v>
       </c>
       <c r="J16" t="n">
-        <v>25</v>
+        <v>26.1</v>
       </c>
       <c r="K16" t="n">
-        <v>39.5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
@@ -1891,19 +1873,19 @@
         <v>41.7</v>
       </c>
       <c r="G19" t="n">
-        <v>30.9</v>
+        <v>28.7</v>
       </c>
       <c r="H19" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="I19" t="n">
-        <v>38.9</v>
+        <v>40</v>
       </c>
       <c r="J19" t="n">
-        <v>30.6</v>
+        <v>30</v>
       </c>
       <c r="K19" t="n">
-        <v>40.6</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="20">
@@ -2748,31 +2730,31 @@
         <v>46</v>
       </c>
       <c r="C44" t="n">
-        <v>68.6</v>
+        <v>67.9</v>
       </c>
       <c r="D44" t="n">
-        <v>16.3</v>
+        <v>19.2</v>
       </c>
       <c r="E44" t="n">
-        <v>52.3</v>
+        <v>48.7</v>
       </c>
       <c r="F44" t="n">
-        <v>16.3</v>
+        <v>19.2</v>
       </c>
       <c r="G44" t="n">
-        <v>29.6</v>
+        <v>31.2</v>
       </c>
       <c r="H44" t="n">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="I44" t="n">
-        <v>28.2</v>
+        <v>30</v>
       </c>
       <c r="J44" t="n">
-        <v>46.2</v>
+        <v>45</v>
       </c>
       <c r="K44" t="n">
-        <v>25.6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45">
@@ -2783,31 +2765,31 @@
         <v>46</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>70.6</v>
       </c>
       <c r="D45" t="n">
-        <v>57.1</v>
+        <v>30.8</v>
       </c>
       <c r="E45" t="n">
-        <v>-57.1</v>
+        <v>39.8</v>
       </c>
       <c r="F45" t="n">
-        <v>57.1</v>
+        <v>30.8</v>
       </c>
       <c r="G45" t="n">
-        <v>75</v>
+        <v>55.6</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="I45" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="46">
@@ -2818,31 +2800,31 @@
         <v>46</v>
       </c>
       <c r="C46" t="n">
-        <v>70.6</v>
+        <v>68.4</v>
       </c>
       <c r="D46" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="E46" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="F46" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="G46" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="H46" t="n">
+        <v>8.7</v>
+      </c>
+      <c r="I46" t="n">
+        <v>73.1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="K46" t="n">
         <v>30.8</v>
-      </c>
-      <c r="E46" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="F46" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="G46" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="H46" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="I46" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J46" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="K46" t="n">
-        <v>22.2</v>
       </c>
     </row>
     <row r="47">
@@ -2853,31 +2835,31 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>68.4</v>
+        <v>71.7</v>
       </c>
       <c r="D47" t="n">
-        <v>20.2</v>
+        <v>20.9</v>
       </c>
       <c r="E47" t="n">
-        <v>48.2</v>
+        <v>50.8</v>
       </c>
       <c r="F47" t="n">
-        <v>20.2</v>
+        <v>20.9</v>
       </c>
       <c r="G47" t="n">
-        <v>22.7</v>
+        <v>26.1</v>
       </c>
       <c r="H47" t="n">
-        <v>8.7</v>
+        <v>5.4</v>
       </c>
       <c r="I47" t="n">
-        <v>73.1</v>
+        <v>37</v>
       </c>
       <c r="J47" t="n">
-        <v>7.7</v>
+        <v>33.3</v>
       </c>
       <c r="K47" t="n">
-        <v>30.8</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="48">
@@ -2888,31 +2870,31 @@
         <v>46</v>
       </c>
       <c r="C48" t="n">
-        <v>71.7</v>
+        <v>73.8</v>
       </c>
       <c r="D48" t="n">
-        <v>20.9</v>
+        <v>16.5</v>
       </c>
       <c r="E48" t="n">
-        <v>50.8</v>
+        <v>57.3</v>
       </c>
       <c r="F48" t="n">
-        <v>20.9</v>
+        <v>16.5</v>
       </c>
       <c r="G48" t="n">
-        <v>26.1</v>
+        <v>35.3</v>
       </c>
       <c r="H48" t="n">
-        <v>5.4</v>
+        <v>14.7</v>
       </c>
       <c r="I48" t="n">
-        <v>37</v>
+        <v>19.5</v>
       </c>
       <c r="J48" t="n">
-        <v>33.3</v>
+        <v>43.9</v>
       </c>
       <c r="K48" t="n">
-        <v>38.9</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="49">
@@ -2920,69 +2902,69 @@
         <v>61</v>
       </c>
       <c r="B49" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="C49" t="n">
-        <v>73.8</v>
+        <v>72.7</v>
       </c>
       <c r="D49" t="n">
-        <v>16.5</v>
+        <v>16.1</v>
       </c>
       <c r="E49" t="n">
-        <v>57.3</v>
+        <v>56.6</v>
       </c>
       <c r="F49" t="n">
-        <v>16.5</v>
+        <v>16.1</v>
       </c>
       <c r="G49" t="n">
-        <v>35.3</v>
+        <v>28.6</v>
       </c>
       <c r="H49" t="n">
-        <v>14.7</v>
+        <v>8.9</v>
       </c>
       <c r="I49" t="n">
-        <v>19.5</v>
+        <v>50</v>
       </c>
       <c r="J49" t="n">
-        <v>43.9</v>
+        <v>18.8</v>
       </c>
       <c r="K49" t="n">
-        <v>48.8</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>63</v>
+      </c>
+      <c r="B50" t="s">
         <v>62</v>
       </c>
-      <c r="B50" t="s">
-        <v>63</v>
-      </c>
       <c r="C50" t="n">
-        <v>72.7</v>
+        <v>78.4</v>
       </c>
       <c r="D50" t="n">
-        <v>16.1</v>
+        <v>36.8</v>
       </c>
       <c r="E50" t="n">
-        <v>56.6</v>
+        <v>41.6</v>
       </c>
       <c r="F50" t="n">
-        <v>16.1</v>
+        <v>36.8</v>
       </c>
       <c r="G50" t="n">
-        <v>28.6</v>
+        <v>24.1</v>
       </c>
       <c r="H50" t="n">
-        <v>8.9</v>
+        <v>6</v>
       </c>
       <c r="I50" t="n">
-        <v>50</v>
+        <v>43.6</v>
       </c>
       <c r="J50" t="n">
-        <v>18.8</v>
+        <v>23.1</v>
       </c>
       <c r="K50" t="n">
-        <v>43.8</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="51">
@@ -2990,34 +2972,34 @@
         <v>64</v>
       </c>
       <c r="B51" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C51" t="n">
-        <v>78.4</v>
+        <v>44.2</v>
       </c>
       <c r="D51" t="n">
-        <v>36.8</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="n">
-        <v>41.6</v>
+        <v>31</v>
       </c>
       <c r="F51" t="n">
-        <v>36.8</v>
+        <v>13.2</v>
       </c>
       <c r="G51" t="n">
-        <v>25</v>
+        <v>31.7</v>
       </c>
       <c r="H51" t="n">
-        <v>4.3</v>
+        <v>14.8</v>
       </c>
       <c r="I51" t="n">
-        <v>38.9</v>
+        <v>57.7</v>
       </c>
       <c r="J51" t="n">
-        <v>25</v>
+        <v>15.4</v>
       </c>
       <c r="K51" t="n">
-        <v>38.9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52">
@@ -3025,34 +3007,34 @@
         <v>65</v>
       </c>
       <c r="B52" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C52" t="n">
-        <v>44.2</v>
+        <v>100</v>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="F52" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>32.2</v>
+        <v>30.8</v>
       </c>
       <c r="H52" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="I52" t="n">
-        <v>58.3</v>
+        <v>40</v>
       </c>
       <c r="J52" t="n">
-        <v>12.5</v>
+        <v>60</v>
       </c>
       <c r="K52" t="n">
-        <v>17.4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53">
@@ -3060,34 +3042,34 @@
         <v>66</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C53" t="n">
-        <v>100</v>
+        <v>55.2</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>48.5</v>
       </c>
       <c r="E53" t="n">
-        <v>100</v>
+        <v>6.7</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>48.5</v>
       </c>
       <c r="G53" t="n">
-        <v>25</v>
+        <v>31.1</v>
       </c>
       <c r="H53" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="I53" t="n">
-        <v>33.3</v>
+        <v>46.7</v>
       </c>
       <c r="J53" t="n">
-        <v>66.7</v>
+        <v>13.3</v>
       </c>
       <c r="K53" t="n">
-        <v>33.3</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="54">
@@ -3095,34 +3077,34 @@
         <v>67</v>
       </c>
       <c r="B54" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C54" t="n">
-        <v>55.2</v>
+        <v>57.1</v>
       </c>
       <c r="D54" t="n">
-        <v>48.5</v>
+        <v>7.7</v>
       </c>
       <c r="E54" t="n">
-        <v>6.7</v>
+        <v>49.4</v>
       </c>
       <c r="F54" t="n">
-        <v>48.5</v>
+        <v>7.7</v>
       </c>
       <c r="G54" t="n">
-        <v>34.2</v>
+        <v>14.3</v>
       </c>
       <c r="H54" t="n">
-        <v>4.8</v>
+        <v>28.6</v>
       </c>
       <c r="I54" t="n">
-        <v>41.7</v>
+        <v>100</v>
       </c>
       <c r="J54" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>33.3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55">
@@ -3130,34 +3112,34 @@
         <v>68</v>
       </c>
       <c r="B55" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C55" t="n">
-        <v>57.1</v>
+        <v>79.3</v>
       </c>
       <c r="D55" t="n">
-        <v>7.7</v>
+        <v>28.4</v>
       </c>
       <c r="E55" t="n">
-        <v>49.4</v>
+        <v>50.9</v>
       </c>
       <c r="F55" t="n">
-        <v>7.7</v>
+        <v>28.4</v>
       </c>
       <c r="G55" t="n">
-        <v>14.3</v>
+        <v>36.8</v>
       </c>
       <c r="H55" t="n">
-        <v>28.6</v>
+        <v>8.6</v>
       </c>
       <c r="I55" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K55" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56">
@@ -3165,34 +3147,34 @@
         <v>69</v>
       </c>
       <c r="B56" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C56" t="n">
-        <v>79.3</v>
+        <v>72.4</v>
       </c>
       <c r="D56" t="n">
-        <v>28.4</v>
+        <v>10</v>
       </c>
       <c r="E56" t="n">
-        <v>50.9</v>
+        <v>62.4</v>
       </c>
       <c r="F56" t="n">
-        <v>28.4</v>
+        <v>10</v>
       </c>
       <c r="G56" t="n">
-        <v>37</v>
+        <v>41.2</v>
       </c>
       <c r="H56" t="n">
-        <v>7.8</v>
+        <v>14.3</v>
       </c>
       <c r="I56" t="n">
-        <v>44.7</v>
+        <v>50</v>
       </c>
       <c r="J56" t="n">
-        <v>23.4</v>
+        <v>30</v>
       </c>
       <c r="K56" t="n">
-        <v>44.7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="57">
@@ -3200,34 +3182,34 @@
         <v>70</v>
       </c>
       <c r="B57" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C57" t="n">
-        <v>72.4</v>
+        <v>84.5</v>
       </c>
       <c r="D57" t="n">
-        <v>10</v>
+        <v>20.6</v>
       </c>
       <c r="E57" t="n">
-        <v>62.4</v>
+        <v>63.9</v>
       </c>
       <c r="F57" t="n">
-        <v>10</v>
+        <v>20.6</v>
       </c>
       <c r="G57" t="n">
-        <v>41.2</v>
+        <v>24.6</v>
       </c>
       <c r="H57" t="n">
-        <v>14.3</v>
+        <v>20</v>
       </c>
       <c r="I57" t="n">
-        <v>50</v>
+        <v>55.3</v>
       </c>
       <c r="J57" t="n">
-        <v>30</v>
+        <v>19.1</v>
       </c>
       <c r="K57" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58">
@@ -3235,34 +3217,34 @@
         <v>71</v>
       </c>
       <c r="B58" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C58" t="n">
-        <v>84.5</v>
+        <v>80</v>
       </c>
       <c r="D58" t="n">
-        <v>20.6</v>
+        <v>11.4</v>
       </c>
       <c r="E58" t="n">
-        <v>63.9</v>
+        <v>68.6</v>
       </c>
       <c r="F58" t="n">
-        <v>20.6</v>
+        <v>11.4</v>
       </c>
       <c r="G58" t="n">
-        <v>24.6</v>
+        <v>23.7</v>
       </c>
       <c r="H58" t="n">
-        <v>20</v>
+        <v>11.4</v>
       </c>
       <c r="I58" t="n">
-        <v>55.3</v>
+        <v>52.4</v>
       </c>
       <c r="J58" t="n">
-        <v>19.1</v>
+        <v>14.3</v>
       </c>
       <c r="K58" t="n">
-        <v>40</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="59">
@@ -3270,34 +3252,34 @@
         <v>72</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D59" t="n">
-        <v>11.4</v>
+        <v>50</v>
       </c>
       <c r="E59" t="n">
-        <v>68.6</v>
+        <v>50</v>
       </c>
       <c r="F59" t="n">
-        <v>11.4</v>
+        <v>50</v>
       </c>
       <c r="G59" t="n">
-        <v>23.7</v>
+        <v>25</v>
       </c>
       <c r="H59" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>52.4</v>
+        <v>100</v>
       </c>
       <c r="J59" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60">
@@ -3305,34 +3287,34 @@
         <v>73</v>
       </c>
       <c r="B60" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C60" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D60" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E60" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F60" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G60" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="61">
@@ -3340,34 +3322,34 @@
         <v>74</v>
       </c>
       <c r="B61" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C61" t="n">
-        <v>50</v>
+        <v>74.3</v>
       </c>
       <c r="D61" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>25</v>
+        <v>74.3</v>
       </c>
       <c r="F61" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="H61" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I61" t="n">
+        <v>60</v>
+      </c>
+      <c r="J61" t="n">
+        <v>10</v>
+      </c>
+      <c r="K61" t="n">
         <v>20</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>33.3</v>
       </c>
     </row>
     <row r="62">
@@ -3375,34 +3357,34 @@
         <v>75</v>
       </c>
       <c r="B62" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C62" t="n">
-        <v>74.3</v>
+        <v>69.6</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="E62" t="n">
-        <v>74.3</v>
+        <v>36.3</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G62" t="n">
-        <v>29.3</v>
+        <v>20</v>
       </c>
       <c r="H62" t="n">
-        <v>16.7</v>
+        <v>11.8</v>
       </c>
       <c r="I62" t="n">
-        <v>60</v>
+        <v>46.2</v>
       </c>
       <c r="J62" t="n">
-        <v>10</v>
+        <v>30.8</v>
       </c>
       <c r="K62" t="n">
-        <v>20</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="63">
@@ -3410,34 +3392,34 @@
         <v>76</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C63" t="n">
-        <v>69.6</v>
+        <v>75</v>
       </c>
       <c r="D63" t="n">
-        <v>33.3</v>
+        <v>30.8</v>
       </c>
       <c r="E63" t="n">
-        <v>36.3</v>
+        <v>44.2</v>
       </c>
       <c r="F63" t="n">
-        <v>33.3</v>
+        <v>30.8</v>
       </c>
       <c r="G63" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="H63" t="n">
         <v>20</v>
       </c>
-      <c r="H63" t="n">
-        <v>11.8</v>
-      </c>
       <c r="I63" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="J63" t="n">
-        <v>30.8</v>
+        <v>50</v>
       </c>
       <c r="K63" t="n">
-        <v>53.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64">
@@ -3445,34 +3427,34 @@
         <v>77</v>
       </c>
       <c r="B64" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C64" t="n">
-        <v>75</v>
+        <v>68.6</v>
       </c>
       <c r="D64" t="n">
-        <v>30.8</v>
+        <v>31.8</v>
       </c>
       <c r="E64" t="n">
-        <v>44.2</v>
+        <v>36.8</v>
       </c>
       <c r="F64" t="n">
-        <v>30.8</v>
+        <v>31.8</v>
       </c>
       <c r="G64" t="n">
-        <v>62.5</v>
+        <v>11.1</v>
       </c>
       <c r="H64" t="n">
-        <v>20</v>
+        <v>3.4</v>
       </c>
       <c r="I64" t="n">
-        <v>50</v>
+        <v>47.6</v>
       </c>
       <c r="J64" t="n">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="K64" t="n">
-        <v>100</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="65">
@@ -3480,34 +3462,34 @@
         <v>78</v>
       </c>
       <c r="B65" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C65" t="n">
-        <v>68.6</v>
+        <v>69.3</v>
       </c>
       <c r="D65" t="n">
-        <v>31.8</v>
+        <v>19.1</v>
       </c>
       <c r="E65" t="n">
-        <v>36.8</v>
+        <v>50.2</v>
       </c>
       <c r="F65" t="n">
-        <v>31.8</v>
+        <v>19.1</v>
       </c>
       <c r="G65" t="n">
-        <v>11.1</v>
+        <v>25.7</v>
       </c>
       <c r="H65" t="n">
-        <v>3.4</v>
+        <v>11.4</v>
       </c>
       <c r="I65" t="n">
-        <v>47.6</v>
+        <v>42.9</v>
       </c>
       <c r="J65" t="n">
-        <v>28.6</v>
+        <v>24.5</v>
       </c>
       <c r="K65" t="n">
-        <v>38.1</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="66">
@@ -3515,34 +3497,34 @@
         <v>79</v>
       </c>
       <c r="B66" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C66" t="n">
-        <v>69.3</v>
+        <v>80</v>
       </c>
       <c r="D66" t="n">
-        <v>19.1</v>
+        <v>40.8</v>
       </c>
       <c r="E66" t="n">
-        <v>50.2</v>
+        <v>39.2</v>
       </c>
       <c r="F66" t="n">
-        <v>19.1</v>
+        <v>40.8</v>
       </c>
       <c r="G66" t="n">
-        <v>26.7</v>
+        <v>24.7</v>
       </c>
       <c r="H66" t="n">
-        <v>12</v>
+        <v>3.8</v>
       </c>
       <c r="I66" t="n">
-        <v>42.6</v>
+        <v>34.6</v>
       </c>
       <c r="J66" t="n">
-        <v>25.5</v>
+        <v>44.2</v>
       </c>
       <c r="K66" t="n">
-        <v>34.8</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="67">
@@ -3550,34 +3532,34 @@
         <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C67" t="n">
-        <v>80</v>
+        <v>58.7</v>
       </c>
       <c r="D67" t="n">
-        <v>40.8</v>
+        <v>9.9</v>
       </c>
       <c r="E67" t="n">
-        <v>39.2</v>
+        <v>48.8</v>
       </c>
       <c r="F67" t="n">
-        <v>40.8</v>
+        <v>9.9</v>
       </c>
       <c r="G67" t="n">
-        <v>25.7</v>
+        <v>29.7</v>
       </c>
       <c r="H67" t="n">
-        <v>4</v>
+        <v>15.8</v>
       </c>
       <c r="I67" t="n">
-        <v>33.3</v>
+        <v>42.5</v>
       </c>
       <c r="J67" t="n">
-        <v>43.8</v>
+        <v>30</v>
       </c>
       <c r="K67" t="n">
-        <v>45.8</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="68">
@@ -3585,34 +3567,34 @@
         <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C68" t="n">
-        <v>58.7</v>
+        <v>71</v>
       </c>
       <c r="D68" t="n">
-        <v>9.9</v>
+        <v>23.4</v>
       </c>
       <c r="E68" t="n">
-        <v>48.8</v>
+        <v>47.6</v>
       </c>
       <c r="F68" t="n">
-        <v>9.9</v>
+        <v>23.4</v>
       </c>
       <c r="G68" t="n">
-        <v>31.1</v>
+        <v>34</v>
       </c>
       <c r="H68" t="n">
-        <v>16.7</v>
+        <v>7.5</v>
       </c>
       <c r="I68" t="n">
-        <v>42.1</v>
+        <v>46.7</v>
       </c>
       <c r="J68" t="n">
-        <v>28.9</v>
+        <v>26.7</v>
       </c>
       <c r="K68" t="n">
-        <v>22.9</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="69">
@@ -3620,69 +3602,69 @@
         <v>82</v>
       </c>
       <c r="B69" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="C69" t="n">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="D69" t="n">
-        <v>23.4</v>
+        <v>21.1</v>
       </c>
       <c r="E69" t="n">
-        <v>47.6</v>
+        <v>64.9</v>
       </c>
       <c r="F69" t="n">
-        <v>23.4</v>
+        <v>21.1</v>
       </c>
       <c r="G69" t="n">
-        <v>34.1</v>
+        <v>38.8</v>
       </c>
       <c r="H69" t="n">
-        <v>8.2</v>
+        <v>11.9</v>
       </c>
       <c r="I69" t="n">
-        <v>48.1</v>
+        <v>33.3</v>
       </c>
       <c r="J69" t="n">
-        <v>25.9</v>
+        <v>51.9</v>
       </c>
       <c r="K69" t="n">
-        <v>53.6</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
+        <v>84</v>
+      </c>
+      <c r="B70" t="s">
         <v>83</v>
       </c>
-      <c r="B70" t="s">
-        <v>84</v>
-      </c>
       <c r="C70" t="n">
-        <v>86</v>
+        <v>74.3</v>
       </c>
       <c r="D70" t="n">
-        <v>21.1</v>
+        <v>28.8</v>
       </c>
       <c r="E70" t="n">
-        <v>64.9</v>
+        <v>45.5</v>
       </c>
       <c r="F70" t="n">
-        <v>21.1</v>
+        <v>28.8</v>
       </c>
       <c r="G70" t="n">
-        <v>38.8</v>
+        <v>19.5</v>
       </c>
       <c r="H70" t="n">
-        <v>11.9</v>
+        <v>5.5</v>
       </c>
       <c r="I70" t="n">
-        <v>33.3</v>
+        <v>59</v>
       </c>
       <c r="J70" t="n">
-        <v>51.9</v>
+        <v>20.5</v>
       </c>
       <c r="K70" t="n">
-        <v>58.6</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="71">
@@ -3690,34 +3672,34 @@
         <v>85</v>
       </c>
       <c r="B71" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C71" t="n">
-        <v>74.3</v>
+        <v>78.8</v>
       </c>
       <c r="D71" t="n">
-        <v>28.8</v>
+        <v>31.2</v>
       </c>
       <c r="E71" t="n">
-        <v>45.5</v>
+        <v>47.6</v>
       </c>
       <c r="F71" t="n">
-        <v>28.8</v>
+        <v>31.2</v>
       </c>
       <c r="G71" t="n">
-        <v>19.5</v>
+        <v>34.3</v>
       </c>
       <c r="H71" t="n">
-        <v>5.5</v>
+        <v>10.1</v>
       </c>
       <c r="I71" t="n">
-        <v>59</v>
+        <v>42.5</v>
       </c>
       <c r="J71" t="n">
-        <v>20.5</v>
+        <v>25</v>
       </c>
       <c r="K71" t="n">
-        <v>43.2</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="72">
@@ -3725,34 +3707,34 @@
         <v>86</v>
       </c>
       <c r="B72" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C72" t="n">
-        <v>78.8</v>
+        <v>70.4</v>
       </c>
       <c r="D72" t="n">
-        <v>31.2</v>
+        <v>33.7</v>
       </c>
       <c r="E72" t="n">
-        <v>47.6</v>
+        <v>36.7</v>
       </c>
       <c r="F72" t="n">
-        <v>31.2</v>
+        <v>33.7</v>
       </c>
       <c r="G72" t="n">
-        <v>34.3</v>
+        <v>29.5</v>
       </c>
       <c r="H72" t="n">
-        <v>10.1</v>
+        <v>8.5</v>
       </c>
       <c r="I72" t="n">
-        <v>42.5</v>
+        <v>51.1</v>
       </c>
       <c r="J72" t="n">
-        <v>25</v>
+        <v>21.3</v>
       </c>
       <c r="K72" t="n">
-        <v>64.3</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="73">
@@ -3760,34 +3742,34 @@
         <v>87</v>
       </c>
       <c r="B73" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C73" t="n">
-        <v>70.4</v>
+        <v>76.8</v>
       </c>
       <c r="D73" t="n">
-        <v>33.7</v>
+        <v>42.5</v>
       </c>
       <c r="E73" t="n">
-        <v>36.7</v>
+        <v>34.3</v>
       </c>
       <c r="F73" t="n">
-        <v>33.7</v>
+        <v>42.5</v>
       </c>
       <c r="G73" t="n">
-        <v>29.5</v>
+        <v>24.3</v>
       </c>
       <c r="H73" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>51.1</v>
+        <v>36.1</v>
       </c>
       <c r="J73" t="n">
-        <v>21.3</v>
+        <v>27.9</v>
       </c>
       <c r="K73" t="n">
-        <v>48.9</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="74">
@@ -3795,34 +3777,34 @@
         <v>88</v>
       </c>
       <c r="B74" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C74" t="n">
-        <v>76.8</v>
+        <v>71.4</v>
       </c>
       <c r="D74" t="n">
-        <v>42.5</v>
+        <v>20</v>
       </c>
       <c r="E74" t="n">
-        <v>34.3</v>
+        <v>51.4</v>
       </c>
       <c r="F74" t="n">
-        <v>42.5</v>
+        <v>20</v>
       </c>
       <c r="G74" t="n">
-        <v>24.3</v>
+        <v>22</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="I74" t="n">
-        <v>36.1</v>
+        <v>31.9</v>
       </c>
       <c r="J74" t="n">
-        <v>27.9</v>
+        <v>38.3</v>
       </c>
       <c r="K74" t="n">
-        <v>70.2</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="75">
@@ -3830,34 +3812,34 @@
         <v>89</v>
       </c>
       <c r="B75" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C75" t="n">
-        <v>71.4</v>
+        <v>73.8</v>
       </c>
       <c r="D75" t="n">
-        <v>20</v>
+        <v>32.7</v>
       </c>
       <c r="E75" t="n">
-        <v>51.4</v>
+        <v>41.1</v>
       </c>
       <c r="F75" t="n">
-        <v>20</v>
+        <v>32.7</v>
       </c>
       <c r="G75" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H75" t="n">
-        <v>13.6</v>
+        <v>8.7</v>
       </c>
       <c r="I75" t="n">
-        <v>31.9</v>
+        <v>51.7</v>
       </c>
       <c r="J75" t="n">
-        <v>38.3</v>
+        <v>20.7</v>
       </c>
       <c r="K75" t="n">
-        <v>28.9</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="76">
@@ -3865,34 +3847,34 @@
         <v>90</v>
       </c>
       <c r="B76" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C76" t="n">
-        <v>73.8</v>
+        <v>100</v>
       </c>
       <c r="D76" t="n">
-        <v>32.7</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>41.1</v>
+        <v>100</v>
       </c>
       <c r="F76" t="n">
-        <v>32.7</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>32</v>
+        <v>46.2</v>
       </c>
       <c r="H76" t="n">
-        <v>8.7</v>
+        <v>33.3</v>
       </c>
       <c r="I76" t="n">
-        <v>51.7</v>
+        <v>100</v>
       </c>
       <c r="J76" t="n">
-        <v>20.7</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>29.6</v>
+        <v>100</v>
       </c>
     </row>
     <row r="77">
@@ -3900,34 +3882,34 @@
         <v>91</v>
       </c>
       <c r="B77" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C77" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>30.6</v>
       </c>
       <c r="E77" t="n">
-        <v>100</v>
+        <v>38.4</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>30.6</v>
       </c>
       <c r="G77" t="n">
-        <v>46.2</v>
+        <v>19</v>
       </c>
       <c r="H77" t="n">
-        <v>33.3</v>
+        <v>7.9</v>
       </c>
       <c r="I77" t="n">
-        <v>100</v>
+        <v>59.2</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>16.3</v>
       </c>
       <c r="K77" t="n">
-        <v>100</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="78">
@@ -3935,34 +3917,34 @@
         <v>92</v>
       </c>
       <c r="B78" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C78" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D78" t="n">
-        <v>30.6</v>
+        <v>46.5</v>
       </c>
       <c r="E78" t="n">
-        <v>38.4</v>
+        <v>25.5</v>
       </c>
       <c r="F78" t="n">
-        <v>30.6</v>
+        <v>46.5</v>
       </c>
       <c r="G78" t="n">
-        <v>19</v>
+        <v>23.7</v>
       </c>
       <c r="H78" t="n">
-        <v>7.9</v>
+        <v>10.8</v>
       </c>
       <c r="I78" t="n">
-        <v>59.2</v>
+        <v>48</v>
       </c>
       <c r="J78" t="n">
-        <v>16.3</v>
+        <v>32</v>
       </c>
       <c r="K78" t="n">
-        <v>44.9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="79">
@@ -3970,34 +3952,34 @@
         <v>93</v>
       </c>
       <c r="B79" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C79" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D79" t="n">
-        <v>46.5</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>25.5</v>
+        <v>75</v>
       </c>
       <c r="F79" t="n">
-        <v>46.5</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>23.7</v>
+        <v>22.2</v>
       </c>
       <c r="H79" t="n">
-        <v>10.8</v>
+        <v>25</v>
       </c>
       <c r="I79" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="J79" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="K79" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="80">
@@ -4005,34 +3987,34 @@
         <v>94</v>
       </c>
       <c r="B80" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C80" t="n">
-        <v>75</v>
+        <v>61.4</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>19.3</v>
       </c>
       <c r="E80" t="n">
-        <v>75</v>
+        <v>42.1</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>19.3</v>
       </c>
       <c r="G80" t="n">
-        <v>22.2</v>
+        <v>19.4</v>
       </c>
       <c r="H80" t="n">
-        <v>25</v>
+        <v>12.2</v>
       </c>
       <c r="I80" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="J80" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="K80" t="n">
-        <v>40</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="81">
@@ -4040,34 +4022,34 @@
         <v>95</v>
       </c>
       <c r="B81" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C81" t="n">
-        <v>61.4</v>
+        <v>41.3</v>
       </c>
       <c r="D81" t="n">
-        <v>19.3</v>
+        <v>23.7</v>
       </c>
       <c r="E81" t="n">
-        <v>42.1</v>
+        <v>17.6</v>
       </c>
       <c r="F81" t="n">
-        <v>19.3</v>
+        <v>23.7</v>
       </c>
       <c r="G81" t="n">
-        <v>19.4</v>
+        <v>28.9</v>
       </c>
       <c r="H81" t="n">
-        <v>12.2</v>
+        <v>3.6</v>
       </c>
       <c r="I81" t="n">
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="J81" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="K81" t="n">
-        <v>44.7</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="82">
@@ -4075,57 +4057,47 @@
         <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C82" t="n">
-        <v>41.3</v>
+        <v>50</v>
       </c>
       <c r="D82" t="n">
-        <v>23.7</v>
+        <v>50</v>
       </c>
       <c r="E82" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>23.7</v>
+        <v>50</v>
       </c>
       <c r="G82" t="n">
-        <v>28.9</v>
+        <v>100</v>
       </c>
       <c r="H82" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I82" t="n">
-        <v>75</v>
-      </c>
-      <c r="J82" t="n">
-        <v>25</v>
-      </c>
-      <c r="K82" t="n">
-        <v>26.3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I82"/>
+      <c r="J82"/>
+      <c r="K82"/>
     </row>
     <row r="83">
       <c r="A83" t="s">
+        <v>98</v>
+      </c>
+      <c r="B83" t="s">
         <v>97</v>
       </c>
-      <c r="B83" t="s">
-        <v>98</v>
-      </c>
-      <c r="C83" t="n">
-        <v>50</v>
-      </c>
+      <c r="C83"/>
       <c r="D83" t="n">
         <v>50</v>
       </c>
-      <c r="E83" t="n">
-        <v>0</v>
-      </c>
+      <c r="E83"/>
       <c r="F83" t="n">
         <v>50</v>
       </c>
       <c r="G83" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -4139,59 +4111,69 @@
         <v>99</v>
       </c>
       <c r="B84" t="s">
-        <v>98</v>
-      </c>
-      <c r="C84"/>
+        <v>97</v>
+      </c>
+      <c r="C84" t="n">
+        <v>56.8</v>
+      </c>
       <c r="D84" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E84" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="F84" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G84" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="H84" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="I84" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="J84" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="K84" t="n">
         <v>50</v>
       </c>
-      <c r="E84"/>
-      <c r="F84" t="n">
-        <v>50</v>
-      </c>
-      <c r="G84" t="n">
-        <v>50</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84"/>
-      <c r="J84"/>
-      <c r="K84"/>
     </row>
     <row r="85">
       <c r="A85" t="s">
         <v>100</v>
       </c>
       <c r="B85" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C85" t="n">
-        <v>56.8</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>6.5</v>
+        <v>54.5</v>
       </c>
       <c r="E85" t="n">
-        <v>50.3</v>
+        <v>-54.5</v>
       </c>
       <c r="F85" t="n">
-        <v>6.5</v>
+        <v>54.5</v>
       </c>
       <c r="G85" t="n">
-        <v>25.9</v>
+        <v>16.7</v>
       </c>
       <c r="H85" t="n">
-        <v>14.7</v>
+        <v>50</v>
       </c>
       <c r="I85" t="n">
-        <v>36.8</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>31.6</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -4199,28 +4181,28 @@
         <v>101</v>
       </c>
       <c r="B86" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>56.5</v>
       </c>
       <c r="D86" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="E86" t="n">
+        <v>18</v>
+      </c>
+      <c r="F86" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="G86" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="H86" t="n">
+        <v>5</v>
+      </c>
+      <c r="I86" t="n">
         <v>54.5</v>
-      </c>
-      <c r="E86" t="n">
-        <v>-54.5</v>
-      </c>
-      <c r="F86" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="G86" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="H86" t="n">
-        <v>50</v>
-      </c>
-      <c r="I86" t="n">
-        <v>0</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -4234,34 +4216,34 @@
         <v>102</v>
       </c>
       <c r="B87" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C87" t="n">
-        <v>56.5</v>
+        <v>86.2</v>
       </c>
       <c r="D87" t="n">
-        <v>38.5</v>
+        <v>33.3</v>
       </c>
       <c r="E87" t="n">
-        <v>18</v>
+        <v>52.9</v>
       </c>
       <c r="F87" t="n">
-        <v>38.5</v>
+        <v>33.3</v>
       </c>
       <c r="G87" t="n">
-        <v>39.5</v>
+        <v>43.2</v>
       </c>
       <c r="H87" t="n">
-        <v>5</v>
+        <v>14.6</v>
       </c>
       <c r="I87" t="n">
-        <v>54.5</v>
+        <v>52.4</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="88">
@@ -4269,34 +4251,34 @@
         <v>103</v>
       </c>
       <c r="B88" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C88" t="n">
-        <v>86.2</v>
+        <v>75.7</v>
       </c>
       <c r="D88" t="n">
         <v>33.3</v>
       </c>
       <c r="E88" t="n">
-        <v>52.9</v>
+        <v>42.4</v>
       </c>
       <c r="F88" t="n">
         <v>33.3</v>
       </c>
       <c r="G88" t="n">
-        <v>43.2</v>
+        <v>19.1</v>
       </c>
       <c r="H88" t="n">
-        <v>14.6</v>
+        <v>7.1</v>
       </c>
       <c r="I88" t="n">
-        <v>52.4</v>
+        <v>41.5</v>
       </c>
       <c r="J88" t="n">
-        <v>14.3</v>
+        <v>22</v>
       </c>
       <c r="K88" t="n">
-        <v>45</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="89">
@@ -4304,34 +4286,34 @@
         <v>104</v>
       </c>
       <c r="B89" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C89" t="n">
-        <v>75.7</v>
+        <v>68.2</v>
       </c>
       <c r="D89" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="E89" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="F89" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="G89" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="H89" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="I89" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="J89" t="n">
         <v>33.3</v>
       </c>
-      <c r="E89" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="F89" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G89" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="H89" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="I89" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="J89" t="n">
-        <v>22</v>
-      </c>
       <c r="K89" t="n">
-        <v>36.6</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="90">
@@ -4339,34 +4321,34 @@
         <v>105</v>
       </c>
       <c r="B90" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C90" t="n">
-        <v>68.2</v>
+        <v>67.9</v>
       </c>
       <c r="D90" t="n">
-        <v>16.9</v>
+        <v>31.6</v>
       </c>
       <c r="E90" t="n">
-        <v>51.3</v>
+        <v>36.3</v>
       </c>
       <c r="F90" t="n">
-        <v>16.9</v>
+        <v>31.6</v>
       </c>
       <c r="G90" t="n">
-        <v>29.4</v>
+        <v>24.2</v>
       </c>
       <c r="H90" t="n">
-        <v>22.6</v>
+        <v>9.5</v>
       </c>
       <c r="I90" t="n">
-        <v>26.7</v>
+        <v>38.8</v>
       </c>
       <c r="J90" t="n">
-        <v>33.3</v>
+        <v>30.6</v>
       </c>
       <c r="K90" t="n">
-        <v>39.5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="91">
@@ -4374,34 +4356,34 @@
         <v>106</v>
       </c>
       <c r="B91" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C91" t="n">
-        <v>67.9</v>
+        <v>85.7</v>
       </c>
       <c r="D91" t="n">
-        <v>31.6</v>
+        <v>29.8</v>
       </c>
       <c r="E91" t="n">
-        <v>36.3</v>
+        <v>55.9</v>
       </c>
       <c r="F91" t="n">
-        <v>31.6</v>
+        <v>29.8</v>
       </c>
       <c r="G91" t="n">
-        <v>24.2</v>
+        <v>36.8</v>
       </c>
       <c r="H91" t="n">
-        <v>9.5</v>
+        <v>7.9</v>
       </c>
       <c r="I91" t="n">
-        <v>38.8</v>
+        <v>36.4</v>
       </c>
       <c r="J91" t="n">
-        <v>30.6</v>
+        <v>36.4</v>
       </c>
       <c r="K91" t="n">
-        <v>49</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="92">
@@ -4409,34 +4391,34 @@
         <v>107</v>
       </c>
       <c r="B92" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C92" t="n">
-        <v>85.7</v>
+        <v>75</v>
       </c>
       <c r="D92" t="n">
-        <v>29.8</v>
+        <v>50</v>
       </c>
       <c r="E92" t="n">
-        <v>55.9</v>
+        <v>25</v>
       </c>
       <c r="F92" t="n">
-        <v>29.8</v>
+        <v>50</v>
       </c>
       <c r="G92" t="n">
-        <v>36.8</v>
+        <v>3.3</v>
       </c>
       <c r="H92" t="n">
-        <v>7.9</v>
+        <v>6.7</v>
       </c>
       <c r="I92" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="J92" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="K92" t="n">
         <v>36.4</v>
-      </c>
-      <c r="J92" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="K92" t="n">
-        <v>54.5</v>
       </c>
     </row>
     <row r="93">
@@ -4444,34 +4426,34 @@
         <v>108</v>
       </c>
       <c r="B93" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C93" t="n">
-        <v>75</v>
+        <v>48.6</v>
       </c>
       <c r="D93" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="E93" t="n">
-        <v>25</v>
+        <v>20.6</v>
       </c>
       <c r="F93" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="G93" t="n">
-        <v>3.3</v>
+        <v>34.5</v>
       </c>
       <c r="H93" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>45.5</v>
+        <v>66.7</v>
       </c>
       <c r="J93" t="n">
-        <v>18.2</v>
+        <v>22.2</v>
       </c>
       <c r="K93" t="n">
-        <v>36.4</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="94">
@@ -4479,34 +4461,34 @@
         <v>109</v>
       </c>
       <c r="B94" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C94" t="n">
+        <v>77.4</v>
+      </c>
+      <c r="D94" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E94" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="F94" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="G94" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="H94" t="n">
+        <v>5</v>
+      </c>
+      <c r="I94" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="J94" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="K94" t="n">
         <v>48.6</v>
-      </c>
-      <c r="D94" t="n">
-        <v>28</v>
-      </c>
-      <c r="E94" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="F94" t="n">
-        <v>28</v>
-      </c>
-      <c r="G94" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J94" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="K94" t="n">
-        <v>66.7</v>
       </c>
     </row>
     <row r="95">
@@ -4514,34 +4496,34 @@
         <v>110</v>
       </c>
       <c r="B95" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C95" t="n">
-        <v>77.4</v>
+        <v>64.4</v>
       </c>
       <c r="D95" t="n">
-        <v>32.8</v>
+        <v>20</v>
       </c>
       <c r="E95" t="n">
-        <v>44.6</v>
+        <v>44.4</v>
       </c>
       <c r="F95" t="n">
-        <v>32.8</v>
+        <v>20</v>
       </c>
       <c r="G95" t="n">
-        <v>36.6</v>
+        <v>16.7</v>
       </c>
       <c r="H95" t="n">
-        <v>5</v>
+        <v>7.7</v>
       </c>
       <c r="I95" t="n">
-        <v>37.1</v>
+        <v>36.2</v>
       </c>
       <c r="J95" t="n">
-        <v>31.4</v>
+        <v>24.1</v>
       </c>
       <c r="K95" t="n">
-        <v>48.6</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="96">
@@ -4549,34 +4531,34 @@
         <v>111</v>
       </c>
       <c r="B96" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C96" t="n">
-        <v>64.4</v>
+        <v>61.9</v>
       </c>
       <c r="D96" t="n">
-        <v>20</v>
+        <v>21.2</v>
       </c>
       <c r="E96" t="n">
-        <v>44.4</v>
+        <v>40.7</v>
       </c>
       <c r="F96" t="n">
-        <v>20</v>
+        <v>21.2</v>
       </c>
       <c r="G96" t="n">
-        <v>16.7</v>
+        <v>17.9</v>
       </c>
       <c r="H96" t="n">
-        <v>7.7</v>
+        <v>10.8</v>
       </c>
       <c r="I96" t="n">
-        <v>36.2</v>
+        <v>35.4</v>
       </c>
       <c r="J96" t="n">
-        <v>24.1</v>
+        <v>27.1</v>
       </c>
       <c r="K96" t="n">
-        <v>41.4</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="97">
@@ -4584,34 +4566,34 @@
         <v>112</v>
       </c>
       <c r="B97" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C97" t="n">
-        <v>61.9</v>
+        <v>60.4</v>
       </c>
       <c r="D97" t="n">
-        <v>21.2</v>
+        <v>16.1</v>
       </c>
       <c r="E97" t="n">
-        <v>40.7</v>
+        <v>44.3</v>
       </c>
       <c r="F97" t="n">
-        <v>21.2</v>
+        <v>16.1</v>
       </c>
       <c r="G97" t="n">
-        <v>17.9</v>
+        <v>18.4</v>
       </c>
       <c r="H97" t="n">
-        <v>10.8</v>
+        <v>11.8</v>
       </c>
       <c r="I97" t="n">
-        <v>35.4</v>
+        <v>57.5</v>
       </c>
       <c r="J97" t="n">
-        <v>27.1</v>
+        <v>25</v>
       </c>
       <c r="K97" t="n">
-        <v>43.8</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="98">
@@ -4619,69 +4601,69 @@
         <v>113</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="C98" t="n">
-        <v>60.4</v>
+        <v>53.8</v>
       </c>
       <c r="D98" t="n">
-        <v>16.1</v>
+        <v>53.7</v>
       </c>
       <c r="E98" t="n">
-        <v>44.3</v>
+        <v>0.1</v>
       </c>
       <c r="F98" t="n">
-        <v>16.1</v>
+        <v>53.7</v>
       </c>
       <c r="G98" t="n">
-        <v>18.4</v>
+        <v>26.7</v>
       </c>
       <c r="H98" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>57.5</v>
+        <v>46.7</v>
       </c>
       <c r="J98" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="K98" t="n">
-        <v>56.1</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
+        <v>115</v>
+      </c>
+      <c r="B99" t="s">
         <v>114</v>
       </c>
-      <c r="B99" t="s">
-        <v>115</v>
-      </c>
       <c r="C99" t="n">
-        <v>53.8</v>
+        <v>100</v>
       </c>
       <c r="D99" t="n">
-        <v>53.7</v>
+        <v>16.7</v>
       </c>
       <c r="E99" t="n">
-        <v>0.1</v>
+        <v>83.3</v>
       </c>
       <c r="F99" t="n">
-        <v>53.7</v>
+        <v>16.7</v>
       </c>
       <c r="G99" t="n">
-        <v>26.7</v>
+        <v>12.5</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I99" t="n">
-        <v>46.7</v>
+        <v>60</v>
       </c>
       <c r="J99" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="K99" t="n">
-        <v>46.7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="100">
@@ -4689,98 +4671,98 @@
         <v>116</v>
       </c>
       <c r="B100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C100" t="n">
         <v>100</v>
       </c>
       <c r="D100" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="F100" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I100" t="n">
-        <v>60</v>
-      </c>
-      <c r="J100" t="n">
-        <v>20</v>
-      </c>
-      <c r="K100" t="n">
-        <v>60</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I100"/>
+      <c r="J100"/>
+      <c r="K100"/>
     </row>
     <row r="101">
       <c r="A101" t="s">
         <v>117</v>
       </c>
       <c r="B101" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C101" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="E101" t="n">
-        <v>100</v>
+        <v>43.2</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101"/>
-      <c r="J101"/>
-      <c r="K101"/>
+        <v>14.7</v>
+      </c>
+      <c r="I101" t="n">
+        <v>36</v>
+      </c>
+      <c r="J101" t="n">
+        <v>32</v>
+      </c>
+      <c r="K101" t="n">
+        <v>52.2</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
         <v>118</v>
       </c>
       <c r="B102" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C102" t="n">
-        <v>66.7</v>
+        <v>63.9</v>
       </c>
       <c r="D102" t="n">
-        <v>23.5</v>
+        <v>31.4</v>
       </c>
       <c r="E102" t="n">
-        <v>43.2</v>
+        <v>32.5</v>
       </c>
       <c r="F102" t="n">
-        <v>23.5</v>
+        <v>31.4</v>
       </c>
       <c r="G102" t="n">
-        <v>10.4</v>
+        <v>32</v>
       </c>
       <c r="H102" t="n">
-        <v>14.7</v>
+        <v>6.5</v>
       </c>
       <c r="I102" t="n">
-        <v>36</v>
+        <v>37.1</v>
       </c>
       <c r="J102" t="n">
-        <v>32</v>
+        <v>22.9</v>
       </c>
       <c r="K102" t="n">
-        <v>52.2</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="103">
@@ -4788,34 +4770,34 @@
         <v>119</v>
       </c>
       <c r="B103" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C103" t="n">
-        <v>63.9</v>
+        <v>79.3</v>
       </c>
       <c r="D103" t="n">
-        <v>31.4</v>
+        <v>35.4</v>
       </c>
       <c r="E103" t="n">
-        <v>32.5</v>
+        <v>43.9</v>
       </c>
       <c r="F103" t="n">
-        <v>31.4</v>
+        <v>35.4</v>
       </c>
       <c r="G103" t="n">
-        <v>32</v>
+        <v>26.2</v>
       </c>
       <c r="H103" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="I103" t="n">
-        <v>37.1</v>
+        <v>40.4</v>
       </c>
       <c r="J103" t="n">
-        <v>22.9</v>
+        <v>26.3</v>
       </c>
       <c r="K103" t="n">
-        <v>37.1</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="104">
@@ -4823,34 +4805,34 @@
         <v>120</v>
       </c>
       <c r="B104" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C104" t="n">
-        <v>79.3</v>
+        <v>58.3</v>
       </c>
       <c r="D104" t="n">
-        <v>35.4</v>
+        <v>28.3</v>
       </c>
       <c r="E104" t="n">
-        <v>43.9</v>
+        <v>30</v>
       </c>
       <c r="F104" t="n">
-        <v>35.4</v>
+        <v>28.3</v>
       </c>
       <c r="G104" t="n">
-        <v>26.2</v>
+        <v>17.7</v>
       </c>
       <c r="H104" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="I104" t="n">
-        <v>40.4</v>
+        <v>61</v>
       </c>
       <c r="J104" t="n">
-        <v>26.3</v>
+        <v>12.2</v>
       </c>
       <c r="K104" t="n">
-        <v>26.8</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="105">
@@ -4858,34 +4840,34 @@
         <v>121</v>
       </c>
       <c r="B105" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C105" t="n">
-        <v>58.3</v>
+        <v>51.2</v>
       </c>
       <c r="D105" t="n">
-        <v>28.3</v>
+        <v>25.7</v>
       </c>
       <c r="E105" t="n">
-        <v>30</v>
+        <v>25.5</v>
       </c>
       <c r="F105" t="n">
-        <v>28.3</v>
+        <v>25.7</v>
       </c>
       <c r="G105" t="n">
-        <v>17.7</v>
+        <v>8.6</v>
       </c>
       <c r="H105" t="n">
-        <v>6.8</v>
+        <v>10.6</v>
       </c>
       <c r="I105" t="n">
-        <v>61</v>
+        <v>60.3</v>
       </c>
       <c r="J105" t="n">
-        <v>12.2</v>
+        <v>14.3</v>
       </c>
       <c r="K105" t="n">
-        <v>51.2</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="106">
@@ -4893,26 +4875,34 @@
         <v>122</v>
       </c>
       <c r="B106" t="s">
-        <v>115</v>
-      </c>
-      <c r="C106"/>
-      <c r="D106"/>
-      <c r="E106"/>
-      <c r="F106"/>
+        <v>114</v>
+      </c>
+      <c r="C106" t="n">
+        <v>80</v>
+      </c>
+      <c r="D106" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E106" t="n">
+        <v>68.9</v>
+      </c>
+      <c r="F106" t="n">
+        <v>11.1</v>
+      </c>
       <c r="G106" t="n">
-        <v>33.3</v>
+        <v>39.5</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I106" t="n">
-        <v>50</v>
+        <v>63.6</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="K106" t="n">
-        <v>0</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="107">
@@ -4920,34 +4910,34 @@
         <v>123</v>
       </c>
       <c r="B107" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C107" t="n">
-        <v>51.2</v>
+        <v>73.7</v>
       </c>
       <c r="D107" t="n">
-        <v>25.7</v>
+        <v>27.3</v>
       </c>
       <c r="E107" t="n">
-        <v>25.5</v>
+        <v>46.4</v>
       </c>
       <c r="F107" t="n">
-        <v>25.7</v>
+        <v>27.3</v>
       </c>
       <c r="G107" t="n">
-        <v>8</v>
+        <v>19.3</v>
       </c>
       <c r="H107" t="n">
-        <v>10.8</v>
+        <v>6.2</v>
       </c>
       <c r="I107" t="n">
-        <v>60.7</v>
+        <v>39.5</v>
       </c>
       <c r="J107" t="n">
-        <v>14.8</v>
+        <v>30.3</v>
       </c>
       <c r="K107" t="n">
-        <v>25</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="108">
@@ -4955,34 +4945,34 @@
         <v>124</v>
       </c>
       <c r="B108" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C108" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>26.7</v>
       </c>
       <c r="E108" t="n">
-        <v>68.9</v>
+        <v>43.3</v>
       </c>
       <c r="F108" t="n">
-        <v>11.1</v>
+        <v>26.7</v>
       </c>
       <c r="G108" t="n">
-        <v>39.5</v>
+        <v>14.8</v>
       </c>
       <c r="H108" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I108" t="n">
+        <v>60</v>
+      </c>
+      <c r="J108" t="n">
+        <v>30</v>
+      </c>
+      <c r="K108" t="n">
         <v>10</v>
-      </c>
-      <c r="I108" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="J108" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="K108" t="n">
-        <v>45.5</v>
       </c>
     </row>
     <row r="109">
@@ -4990,34 +4980,34 @@
         <v>125</v>
       </c>
       <c r="B109" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C109" t="n">
-        <v>73.7</v>
+        <v>60.5</v>
       </c>
       <c r="D109" t="n">
-        <v>27.3</v>
+        <v>20.8</v>
       </c>
       <c r="E109" t="n">
-        <v>46.4</v>
+        <v>39.7</v>
       </c>
       <c r="F109" t="n">
-        <v>27.3</v>
+        <v>20.8</v>
       </c>
       <c r="G109" t="n">
-        <v>19.3</v>
+        <v>20</v>
       </c>
       <c r="H109" t="n">
-        <v>6.2</v>
+        <v>11.8</v>
       </c>
       <c r="I109" t="n">
-        <v>39.5</v>
+        <v>50</v>
       </c>
       <c r="J109" t="n">
-        <v>30.3</v>
+        <v>25</v>
       </c>
       <c r="K109" t="n">
-        <v>42.1</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="110">
@@ -5025,34 +5015,34 @@
         <v>126</v>
       </c>
       <c r="B110" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C110" t="n">
-        <v>70</v>
+        <v>70.5</v>
       </c>
       <c r="D110" t="n">
-        <v>26.7</v>
+        <v>28.8</v>
       </c>
       <c r="E110" t="n">
-        <v>43.3</v>
+        <v>41.7</v>
       </c>
       <c r="F110" t="n">
-        <v>26.7</v>
+        <v>28.8</v>
       </c>
       <c r="G110" t="n">
-        <v>14.8</v>
+        <v>34</v>
       </c>
       <c r="H110" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="I110" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J110" t="n">
-        <v>30</v>
+        <v>14.3</v>
       </c>
       <c r="K110" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
     </row>
     <row r="111">
@@ -5060,34 +5050,34 @@
         <v>127</v>
       </c>
       <c r="B111" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C111" t="n">
-        <v>60.5</v>
+        <v>74.7</v>
       </c>
       <c r="D111" t="n">
-        <v>20.8</v>
+        <v>25.4</v>
       </c>
       <c r="E111" t="n">
-        <v>39.7</v>
+        <v>49.3</v>
       </c>
       <c r="F111" t="n">
-        <v>20.8</v>
+        <v>25.4</v>
       </c>
       <c r="G111" t="n">
-        <v>20</v>
+        <v>29.2</v>
       </c>
       <c r="H111" t="n">
-        <v>11.8</v>
+        <v>10.1</v>
       </c>
       <c r="I111" t="n">
-        <v>50</v>
+        <v>41.1</v>
       </c>
       <c r="J111" t="n">
         <v>25</v>
       </c>
       <c r="K111" t="n">
-        <v>52.6</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="112">
@@ -5095,34 +5085,34 @@
         <v>128</v>
       </c>
       <c r="B112" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C112" t="n">
-        <v>70.5</v>
+        <v>73.6</v>
       </c>
       <c r="D112" t="n">
-        <v>28.8</v>
+        <v>29.1</v>
       </c>
       <c r="E112" t="n">
-        <v>41.7</v>
+        <v>44.5</v>
       </c>
       <c r="F112" t="n">
-        <v>28.8</v>
+        <v>29.1</v>
       </c>
       <c r="G112" t="n">
-        <v>34</v>
+        <v>24.3</v>
       </c>
       <c r="H112" t="n">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="I112" t="n">
-        <v>51</v>
+        <v>40.3</v>
       </c>
       <c r="J112" t="n">
-        <v>14.3</v>
+        <v>35.5</v>
       </c>
       <c r="K112" t="n">
-        <v>38</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="113">
@@ -5130,34 +5120,34 @@
         <v>129</v>
       </c>
       <c r="B113" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C113" t="n">
-        <v>100</v>
+        <v>69.7</v>
       </c>
       <c r="D113" t="n">
-        <v>50</v>
+        <v>23.8</v>
       </c>
       <c r="E113" t="n">
-        <v>50</v>
+        <v>45.9</v>
       </c>
       <c r="F113" t="n">
-        <v>50</v>
+        <v>23.8</v>
       </c>
       <c r="G113" t="n">
-        <v>50</v>
+        <v>16.7</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>47.1</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="K113" t="n">
-        <v>0</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="114">
@@ -5165,93 +5155,95 @@
         <v>130</v>
       </c>
       <c r="B114" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C114" t="n">
-        <v>74.4</v>
-      </c>
-      <c r="D114" t="n">
-        <v>25</v>
-      </c>
-      <c r="E114" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="F114" t="n">
-        <v>25</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D114"/>
+      <c r="E114"/>
+      <c r="F114"/>
       <c r="G114" t="n">
-        <v>28.9</v>
+        <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>41.8</v>
+        <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>25.5</v>
+        <v>100</v>
       </c>
       <c r="K114" t="n">
-        <v>48.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
+        <v>132</v>
+      </c>
+      <c r="B115" t="s">
         <v>131</v>
       </c>
-      <c r="B115" t="s">
-        <v>115</v>
-      </c>
       <c r="C115" t="n">
-        <v>73.6</v>
+        <v>100</v>
       </c>
       <c r="D115" t="n">
-        <v>29.1</v>
+        <v>57.1</v>
       </c>
       <c r="E115" t="n">
-        <v>44.5</v>
+        <v>42.9</v>
       </c>
       <c r="F115" t="n">
-        <v>29.1</v>
+        <v>57.1</v>
       </c>
       <c r="G115" t="n">
-        <v>23.5</v>
+        <v>22.2</v>
       </c>
       <c r="H115" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>40.7</v>
+        <v>25</v>
       </c>
       <c r="J115" t="n">
-        <v>37.3</v>
+        <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>54.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B116" t="s">
-        <v>115</v>
-      </c>
-      <c r="C116"/>
-      <c r="D116"/>
-      <c r="E116"/>
-      <c r="F116"/>
+        <v>131</v>
+      </c>
+      <c r="C116" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D116" t="n">
+        <v>60</v>
+      </c>
+      <c r="E116" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F116" t="n">
+        <v>60</v>
+      </c>
       <c r="G116" t="n">
         <v>33.3</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I116" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -5259,63 +5251,69 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B117" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C117" t="n">
-        <v>69.7</v>
+        <v>60.4</v>
       </c>
       <c r="D117" t="n">
-        <v>23.8</v>
+        <v>33.3</v>
       </c>
       <c r="E117" t="n">
-        <v>45.9</v>
+        <v>27.1</v>
       </c>
       <c r="F117" t="n">
-        <v>23.8</v>
+        <v>33.3</v>
       </c>
       <c r="G117" t="n">
-        <v>16.7</v>
+        <v>13.1</v>
       </c>
       <c r="H117" t="n">
-        <v>15.4</v>
+        <v>7.7</v>
       </c>
       <c r="I117" t="n">
-        <v>47.1</v>
+        <v>51.9</v>
       </c>
       <c r="J117" t="n">
-        <v>5.9</v>
+        <v>18.5</v>
       </c>
       <c r="K117" t="n">
-        <v>35.3</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B118" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C118" t="n">
-        <v>100</v>
-      </c>
-      <c r="D118"/>
-      <c r="E118"/>
-      <c r="F118"/>
+        <v>35</v>
+      </c>
+      <c r="D118" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E118" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="F118" t="n">
+        <v>13.3</v>
+      </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J118" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -5326,34 +5324,34 @@
         <v>136</v>
       </c>
       <c r="B119" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C119" t="n">
-        <v>100</v>
+        <v>69.6</v>
       </c>
       <c r="D119" t="n">
-        <v>57.1</v>
+        <v>31.4</v>
       </c>
       <c r="E119" t="n">
-        <v>42.9</v>
+        <v>38.2</v>
       </c>
       <c r="F119" t="n">
-        <v>57.1</v>
+        <v>31.4</v>
       </c>
       <c r="G119" t="n">
-        <v>22.2</v>
+        <v>40.6</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I119" t="n">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K119" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="120">
@@ -5361,34 +5359,34 @@
         <v>137</v>
       </c>
       <c r="B120" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C120" t="n">
-        <v>66.7</v>
+        <v>70.4</v>
       </c>
       <c r="D120" t="n">
-        <v>60</v>
+        <v>28.2</v>
       </c>
       <c r="E120" t="n">
-        <v>6.7</v>
+        <v>42.2</v>
       </c>
       <c r="F120" t="n">
-        <v>60</v>
+        <v>28.2</v>
       </c>
       <c r="G120" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="H120" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="I120" t="n">
         <v>33.3</v>
       </c>
-      <c r="H120" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="I120" t="n">
-        <v>25</v>
-      </c>
       <c r="J120" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="K120" t="n">
-        <v>0</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="121">
@@ -5396,34 +5394,34 @@
         <v>138</v>
       </c>
       <c r="B121" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C121" t="n">
-        <v>60.4</v>
+        <v>60.6</v>
       </c>
       <c r="D121" t="n">
-        <v>33.3</v>
+        <v>25.6</v>
       </c>
       <c r="E121" t="n">
-        <v>27.1</v>
+        <v>35</v>
       </c>
       <c r="F121" t="n">
-        <v>33.3</v>
+        <v>25.6</v>
       </c>
       <c r="G121" t="n">
-        <v>13.1</v>
+        <v>19</v>
       </c>
       <c r="H121" t="n">
-        <v>7.7</v>
+        <v>9.3</v>
       </c>
       <c r="I121" t="n">
-        <v>51.9</v>
+        <v>60</v>
       </c>
       <c r="J121" t="n">
-        <v>18.5</v>
+        <v>14.3</v>
       </c>
       <c r="K121" t="n">
-        <v>42.3</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="122">
@@ -5431,31 +5429,31 @@
         <v>139</v>
       </c>
       <c r="B122" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C122" t="n">
-        <v>35</v>
+        <v>66.7</v>
       </c>
       <c r="D122" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="E122" t="n">
-        <v>21.7</v>
+        <v>66.7</v>
       </c>
       <c r="F122" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>33.3</v>
+        <v>18.2</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J122" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -5466,34 +5464,34 @@
         <v>140</v>
       </c>
       <c r="B123" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C123" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D123" t="n">
-        <v>31.4</v>
+        <v>20</v>
       </c>
       <c r="E123" t="n">
-        <v>38.6</v>
+        <v>40</v>
       </c>
       <c r="F123" t="n">
-        <v>31.4</v>
+        <v>20</v>
       </c>
       <c r="G123" t="n">
-        <v>48</v>
+        <v>38.5</v>
       </c>
       <c r="H123" t="n">
-        <v>14.3</v>
+        <v>11.8</v>
       </c>
       <c r="I123" t="n">
-        <v>85.7</v>
+        <v>90</v>
       </c>
       <c r="J123" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>57.1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="124">
@@ -5501,28 +5499,34 @@
         <v>141</v>
       </c>
       <c r="B124" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C124" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="D124"/>
-      <c r="E124"/>
-      <c r="F124"/>
+        <v>51.9</v>
+      </c>
+      <c r="D124" t="n">
+        <v>15</v>
+      </c>
+      <c r="E124" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="F124" t="n">
+        <v>15</v>
+      </c>
       <c r="G124" t="n">
-        <v>14.3</v>
+        <v>30</v>
       </c>
       <c r="H124" t="n">
-        <v>25</v>
+        <v>13.3</v>
       </c>
       <c r="I124" t="n">
-        <v>66.7</v>
+        <v>71.4</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="K124" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="125">
@@ -5530,34 +5534,34 @@
         <v>142</v>
       </c>
       <c r="B125" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C125" t="n">
-        <v>69.4</v>
+        <v>63.6</v>
       </c>
       <c r="D125" t="n">
-        <v>29</v>
+        <v>26.3</v>
       </c>
       <c r="E125" t="n">
-        <v>40.4</v>
+        <v>37.3</v>
       </c>
       <c r="F125" t="n">
-        <v>29</v>
+        <v>26.3</v>
       </c>
       <c r="G125" t="n">
-        <v>38.1</v>
+        <v>28</v>
       </c>
       <c r="H125" t="n">
-        <v>9.1</v>
+        <v>8.1</v>
       </c>
       <c r="I125" t="n">
-        <v>33.3</v>
+        <v>36.1</v>
       </c>
       <c r="J125" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="K125" t="n">
-        <v>42.3</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="126">
@@ -5565,34 +5569,34 @@
         <v>143</v>
       </c>
       <c r="B126" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C126" t="n">
-        <v>77.8</v>
+        <v>100</v>
       </c>
       <c r="D126" t="n">
-        <v>22.2</v>
+        <v>33.3</v>
       </c>
       <c r="E126" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="F126" t="n">
-        <v>22.2</v>
+        <v>33.3</v>
       </c>
       <c r="G126" t="n">
-        <v>22.2</v>
+        <v>11.1</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K126" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="127">
@@ -5600,34 +5604,34 @@
         <v>144</v>
       </c>
       <c r="B127" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C127" t="n">
-        <v>60.6</v>
+        <v>64.4</v>
       </c>
       <c r="D127" t="n">
-        <v>25.6</v>
+        <v>27</v>
       </c>
       <c r="E127" t="n">
-        <v>35</v>
+        <v>37.4</v>
       </c>
       <c r="F127" t="n">
-        <v>25.6</v>
+        <v>27</v>
       </c>
       <c r="G127" t="n">
-        <v>19</v>
+        <v>21.4</v>
       </c>
       <c r="H127" t="n">
-        <v>9.3</v>
+        <v>1.7</v>
       </c>
       <c r="I127" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="J127" t="n">
-        <v>14.3</v>
+        <v>21.4</v>
       </c>
       <c r="K127" t="n">
-        <v>34.3</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="128">
@@ -5635,28 +5639,28 @@
         <v>145</v>
       </c>
       <c r="B128" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C128" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E128" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G128" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J128" t="n">
         <v>25</v>
@@ -5670,34 +5674,34 @@
         <v>146</v>
       </c>
       <c r="B129" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C129" t="n">
-        <v>60</v>
+        <v>53.6</v>
       </c>
       <c r="D129" t="n">
-        <v>20</v>
+        <v>24.4</v>
       </c>
       <c r="E129" t="n">
-        <v>40</v>
+        <v>29.2</v>
       </c>
       <c r="F129" t="n">
-        <v>20</v>
+        <v>24.4</v>
       </c>
       <c r="G129" t="n">
-        <v>38.5</v>
+        <v>24</v>
       </c>
       <c r="H129" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>90</v>
+        <v>39.4</v>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="K129" t="n">
-        <v>40</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="130">
@@ -5705,34 +5709,34 @@
         <v>147</v>
       </c>
       <c r="B130" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C130" t="n">
-        <v>51.9</v>
+        <v>78.6</v>
       </c>
       <c r="D130" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="E130" t="n">
-        <v>36.9</v>
+        <v>66.1</v>
       </c>
       <c r="F130" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="G130" t="n">
-        <v>30</v>
+        <v>35.3</v>
       </c>
       <c r="H130" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>71.4</v>
+        <v>28.6</v>
       </c>
       <c r="J130" t="n">
-        <v>28.6</v>
+        <v>14.3</v>
       </c>
       <c r="K130" t="n">
-        <v>57.1</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="131">
@@ -5740,34 +5744,34 @@
         <v>148</v>
       </c>
       <c r="B131" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C131" t="n">
-        <v>63.6</v>
+        <v>59.3</v>
       </c>
       <c r="D131" t="n">
-        <v>26.3</v>
+        <v>7.1</v>
       </c>
       <c r="E131" t="n">
-        <v>37.3</v>
+        <v>52.2</v>
       </c>
       <c r="F131" t="n">
-        <v>26.3</v>
+        <v>7.1</v>
       </c>
       <c r="G131" t="n">
-        <v>28</v>
+        <v>5.8</v>
       </c>
       <c r="H131" t="n">
-        <v>8.1</v>
+        <v>8.3</v>
       </c>
       <c r="I131" t="n">
-        <v>36.1</v>
+        <v>50</v>
       </c>
       <c r="J131" t="n">
-        <v>25</v>
+        <v>11.1</v>
       </c>
       <c r="K131" t="n">
-        <v>55.6</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="132">
@@ -5775,34 +5779,34 @@
         <v>149</v>
       </c>
       <c r="B132" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C132" t="n">
-        <v>100</v>
+        <v>63.2</v>
       </c>
       <c r="D132" t="n">
-        <v>33.3</v>
+        <v>45</v>
       </c>
       <c r="E132" t="n">
-        <v>66.7</v>
+        <v>18.2</v>
       </c>
       <c r="F132" t="n">
-        <v>33.3</v>
+        <v>45</v>
       </c>
       <c r="G132" t="n">
-        <v>11.1</v>
+        <v>26.9</v>
       </c>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="I132" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="K132" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="133">
@@ -5810,34 +5814,34 @@
         <v>150</v>
       </c>
       <c r="B133" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C133" t="n">
-        <v>64.4</v>
+        <v>74.7</v>
       </c>
       <c r="D133" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E133" t="n">
-        <v>37.4</v>
+        <v>58.7</v>
       </c>
       <c r="F133" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G133" t="n">
-        <v>21.4</v>
+        <v>25.5</v>
       </c>
       <c r="H133" t="n">
-        <v>1.7</v>
+        <v>16.9</v>
       </c>
       <c r="I133" t="n">
-        <v>61.9</v>
+        <v>27.5</v>
       </c>
       <c r="J133" t="n">
-        <v>21.4</v>
+        <v>42.5</v>
       </c>
       <c r="K133" t="n">
-        <v>31.7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="134">
@@ -5845,34 +5849,34 @@
         <v>151</v>
       </c>
       <c r="B134" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C134" t="n">
-        <v>100</v>
+        <v>74.4</v>
       </c>
       <c r="D134" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E134" t="n">
-        <v>80</v>
+        <v>43.4</v>
       </c>
       <c r="F134" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="H134" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="I134" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="J134" t="n">
-        <v>25</v>
+        <v>25.9</v>
       </c>
       <c r="K134" t="n">
-        <v>0</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="135">
@@ -5880,244 +5884,244 @@
         <v>152</v>
       </c>
       <c r="B135" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="C135" t="n">
-        <v>53.6</v>
+        <v>71.4</v>
       </c>
       <c r="D135" t="n">
-        <v>24.4</v>
+        <v>20</v>
       </c>
       <c r="E135" t="n">
-        <v>29.2</v>
+        <v>51.4</v>
       </c>
       <c r="F135" t="n">
-        <v>24.4</v>
+        <v>20</v>
       </c>
       <c r="G135" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H135" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="I135" t="n">
-        <v>39.4</v>
+        <v>52.4</v>
       </c>
       <c r="J135" t="n">
-        <v>27.3</v>
+        <v>19</v>
       </c>
       <c r="K135" t="n">
-        <v>45.5</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
+        <v>154</v>
+      </c>
+      <c r="B136" t="s">
         <v>153</v>
       </c>
-      <c r="B136" t="s">
-        <v>135</v>
-      </c>
       <c r="C136" t="n">
-        <v>78.6</v>
+        <v>69.6</v>
       </c>
       <c r="D136" t="n">
-        <v>12.5</v>
+        <v>25.5</v>
       </c>
       <c r="E136" t="n">
-        <v>66.1</v>
+        <v>44.1</v>
       </c>
       <c r="F136" t="n">
-        <v>12.5</v>
+        <v>25.5</v>
       </c>
       <c r="G136" t="n">
-        <v>35.3</v>
+        <v>17.1</v>
       </c>
       <c r="H136" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="I136" t="n">
-        <v>28.6</v>
+        <v>56.2</v>
       </c>
       <c r="J136" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="K136" t="n">
-        <v>14.3</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B137" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="C137" t="n">
-        <v>59.3</v>
+        <v>64.6</v>
       </c>
       <c r="D137" t="n">
-        <v>7.1</v>
+        <v>16.7</v>
       </c>
       <c r="E137" t="n">
-        <v>52.2</v>
+        <v>47.9</v>
       </c>
       <c r="F137" t="n">
-        <v>7.1</v>
+        <v>16.7</v>
       </c>
       <c r="G137" t="n">
-        <v>5.8</v>
+        <v>37.7</v>
       </c>
       <c r="H137" t="n">
-        <v>8.3</v>
+        <v>12.5</v>
       </c>
       <c r="I137" t="n">
-        <v>50</v>
+        <v>29.6</v>
       </c>
       <c r="J137" t="n">
-        <v>11.1</v>
+        <v>48.1</v>
       </c>
       <c r="K137" t="n">
-        <v>35.3</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B138" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="C138" t="n">
-        <v>63.2</v>
+        <v>59</v>
       </c>
       <c r="D138" t="n">
-        <v>45</v>
+        <v>20.3</v>
       </c>
       <c r="E138" t="n">
-        <v>18.2</v>
+        <v>38.7</v>
       </c>
       <c r="F138" t="n">
-        <v>45</v>
+        <v>20.3</v>
       </c>
       <c r="G138" t="n">
-        <v>26.9</v>
+        <v>38.1</v>
       </c>
       <c r="H138" t="n">
-        <v>7.7</v>
+        <v>15.6</v>
       </c>
       <c r="I138" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="J138" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K138" t="n">
-        <v>25</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B139" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="C139" t="n">
-        <v>74.7</v>
+        <v>64.4</v>
       </c>
       <c r="D139" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E139" t="n">
-        <v>58.7</v>
+        <v>47.4</v>
       </c>
       <c r="F139" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G139" t="n">
-        <v>25.5</v>
+        <v>10.7</v>
       </c>
       <c r="H139" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="I139" t="n">
-        <v>27.5</v>
+        <v>63.4</v>
       </c>
       <c r="J139" t="n">
-        <v>42.5</v>
+        <v>18.3</v>
       </c>
       <c r="K139" t="n">
-        <v>40</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B140" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="C140" t="n">
-        <v>74.4</v>
+        <v>81.6</v>
       </c>
       <c r="D140" t="n">
-        <v>31</v>
+        <v>22.6</v>
       </c>
       <c r="E140" t="n">
-        <v>43.4</v>
+        <v>59</v>
       </c>
       <c r="F140" t="n">
-        <v>31</v>
+        <v>22.6</v>
       </c>
       <c r="G140" t="n">
-        <v>10.5</v>
+        <v>21.5</v>
       </c>
       <c r="H140" t="n">
-        <v>1.6</v>
+        <v>11</v>
       </c>
       <c r="I140" t="n">
-        <v>44.4</v>
+        <v>35.3</v>
       </c>
       <c r="J140" t="n">
-        <v>25.9</v>
+        <v>35.3</v>
       </c>
       <c r="K140" t="n">
-        <v>35.2</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B141" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C141" t="n">
-        <v>71.4</v>
+        <v>51.8</v>
       </c>
       <c r="D141" t="n">
-        <v>20</v>
+        <v>21.2</v>
       </c>
       <c r="E141" t="n">
-        <v>51.4</v>
+        <v>30.6</v>
       </c>
       <c r="F141" t="n">
-        <v>20</v>
+        <v>21.2</v>
       </c>
       <c r="G141" t="n">
-        <v>33</v>
+        <v>23.6</v>
       </c>
       <c r="H141" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="I141" t="n">
-        <v>52.4</v>
+        <v>48.8</v>
       </c>
       <c r="J141" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K141" t="n">
-        <v>38.9</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="142">
@@ -6125,34 +6129,34 @@
         <v>160</v>
       </c>
       <c r="B142" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C142" t="n">
-        <v>69.6</v>
+        <v>56</v>
       </c>
       <c r="D142" t="n">
-        <v>25.5</v>
+        <v>21.4</v>
       </c>
       <c r="E142" t="n">
-        <v>44.1</v>
+        <v>34.6</v>
       </c>
       <c r="F142" t="n">
-        <v>25.5</v>
+        <v>21.4</v>
       </c>
       <c r="G142" t="n">
-        <v>17.1</v>
+        <v>12.5</v>
       </c>
       <c r="H142" t="n">
-        <v>5.5</v>
+        <v>15.9</v>
       </c>
       <c r="I142" t="n">
-        <v>56.2</v>
+        <v>44.9</v>
       </c>
       <c r="J142" t="n">
-        <v>16.7</v>
+        <v>26.5</v>
       </c>
       <c r="K142" t="n">
-        <v>36.4</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="143">
@@ -6160,34 +6164,34 @@
         <v>161</v>
       </c>
       <c r="B143" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C143" t="n">
-        <v>64.6</v>
+        <v>58.4</v>
       </c>
       <c r="D143" t="n">
-        <v>16.7</v>
+        <v>22.2</v>
       </c>
       <c r="E143" t="n">
-        <v>47.9</v>
+        <v>36.2</v>
       </c>
       <c r="F143" t="n">
-        <v>16.7</v>
+        <v>22.2</v>
       </c>
       <c r="G143" t="n">
-        <v>37.7</v>
+        <v>9.6</v>
       </c>
       <c r="H143" t="n">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="I143" t="n">
-        <v>29.6</v>
+        <v>58</v>
       </c>
       <c r="J143" t="n">
-        <v>48.1</v>
+        <v>18.5</v>
       </c>
       <c r="K143" t="n">
-        <v>38.5</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="144">
@@ -6195,34 +6199,34 @@
         <v>162</v>
       </c>
       <c r="B144" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C144" t="n">
-        <v>59</v>
+        <v>72.3</v>
       </c>
       <c r="D144" t="n">
-        <v>20.3</v>
+        <v>16.2</v>
       </c>
       <c r="E144" t="n">
-        <v>38.7</v>
+        <v>56.1</v>
       </c>
       <c r="F144" t="n">
-        <v>20.3</v>
+        <v>16.2</v>
       </c>
       <c r="G144" t="n">
-        <v>38.1</v>
+        <v>28.6</v>
       </c>
       <c r="H144" t="n">
-        <v>15.6</v>
+        <v>14.7</v>
       </c>
       <c r="I144" t="n">
-        <v>18.8</v>
+        <v>30</v>
       </c>
       <c r="J144" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="K144" t="n">
-        <v>21.4</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="145">
@@ -6230,34 +6234,34 @@
         <v>163</v>
       </c>
       <c r="B145" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C145" t="n">
-        <v>64.4</v>
+        <v>74</v>
       </c>
       <c r="D145" t="n">
-        <v>17</v>
+        <v>35.7</v>
       </c>
       <c r="E145" t="n">
-        <v>47.4</v>
+        <v>38.3</v>
       </c>
       <c r="F145" t="n">
-        <v>17</v>
+        <v>35.7</v>
       </c>
       <c r="G145" t="n">
-        <v>10.7</v>
+        <v>42.3</v>
       </c>
       <c r="H145" t="n">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="I145" t="n">
-        <v>63.4</v>
+        <v>46.2</v>
       </c>
       <c r="J145" t="n">
-        <v>18.3</v>
+        <v>7.7</v>
       </c>
       <c r="K145" t="n">
-        <v>37.3</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="146">
@@ -6265,34 +6269,34 @@
         <v>164</v>
       </c>
       <c r="B146" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C146" t="n">
-        <v>81.6</v>
+        <v>74.5</v>
       </c>
       <c r="D146" t="n">
-        <v>22.6</v>
+        <v>23.5</v>
       </c>
       <c r="E146" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="F146" t="n">
-        <v>22.6</v>
+        <v>23.5</v>
       </c>
       <c r="G146" t="n">
-        <v>21.5</v>
+        <v>19</v>
       </c>
       <c r="H146" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="I146" t="n">
-        <v>35.3</v>
+        <v>32.3</v>
       </c>
       <c r="J146" t="n">
-        <v>35.3</v>
+        <v>30.8</v>
       </c>
       <c r="K146" t="n">
-        <v>36.5</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="147">
@@ -6300,300 +6304,90 @@
         <v>165</v>
       </c>
       <c r="B147" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C147" t="n">
-        <v>51.8</v>
+        <v>33.3</v>
       </c>
       <c r="D147" t="n">
-        <v>21.2</v>
+        <v>25</v>
       </c>
       <c r="E147" t="n">
-        <v>30.6</v>
+        <v>8.3</v>
       </c>
       <c r="F147" t="n">
-        <v>21.2</v>
+        <v>25</v>
       </c>
       <c r="G147" t="n">
-        <v>23.6</v>
+        <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="I147" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="J147" t="n">
-        <v>22</v>
-      </c>
-      <c r="K147" t="n">
-        <v>29.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I147"/>
+      <c r="J147"/>
+      <c r="K147"/>
     </row>
     <row r="148">
       <c r="A148" t="s">
         <v>166</v>
       </c>
       <c r="B148" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C148" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>21.4</v>
+        <v>33.3</v>
       </c>
       <c r="E148" t="n">
-        <v>34.6</v>
+        <v>-33.3</v>
       </c>
       <c r="F148" t="n">
-        <v>21.4</v>
+        <v>33.3</v>
       </c>
       <c r="G148" t="n">
-        <v>12.5</v>
+        <v>100</v>
       </c>
       <c r="H148" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="I148" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="J148" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="K148" t="n">
-        <v>53.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I148"/>
+      <c r="J148"/>
+      <c r="K148"/>
     </row>
     <row r="149">
-      <c r="A149" t="s">
+      <c r="A149"/>
+      <c r="B149" t="s">
         <v>167</v>
       </c>
-      <c r="B149" t="s">
-        <v>159</v>
-      </c>
       <c r="C149" t="n">
-        <v>58.4</v>
+        <v>68.5</v>
       </c>
       <c r="D149" t="n">
-        <v>22.2</v>
+        <v>25.7</v>
       </c>
       <c r="E149" t="n">
-        <v>36.2</v>
+        <v>42.4</v>
       </c>
       <c r="F149" t="n">
-        <v>22.2</v>
+        <v>25.7</v>
       </c>
       <c r="G149" t="n">
-        <v>9.6</v>
+        <v>26.4</v>
       </c>
       <c r="H149" t="n">
-        <v>8.4</v>
+        <v>9.7</v>
       </c>
       <c r="I149" t="n">
-        <v>58</v>
+        <v>48.1</v>
       </c>
       <c r="J149" t="n">
-        <v>18.5</v>
+        <v>24.2</v>
       </c>
       <c r="K149" t="n">
-        <v>31.2</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>168</v>
-      </c>
-      <c r="B150" t="s">
-        <v>159</v>
-      </c>
-      <c r="C150" t="n">
-        <v>72.3</v>
-      </c>
-      <c r="D150" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="E150" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="F150" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="G150" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="H150" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="I150" t="n">
-        <v>30</v>
-      </c>
-      <c r="J150" t="n">
-        <v>35</v>
-      </c>
-      <c r="K150" t="n">
-        <v>57.7</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>169</v>
-      </c>
-      <c r="B151" t="s">
-        <v>159</v>
-      </c>
-      <c r="C151" t="n">
-        <v>74</v>
-      </c>
-      <c r="D151" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="E151" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="F151" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="G151" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="H151" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I151" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="J151" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="K151" t="n">
-        <v>69.2</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>170</v>
-      </c>
-      <c r="B152" t="s">
-        <v>159</v>
-      </c>
-      <c r="C152" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="D152" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E152" t="n">
-        <v>51</v>
-      </c>
-      <c r="F152" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G152" t="n">
-        <v>19</v>
-      </c>
-      <c r="H152" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="I152" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="J152" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="K152" t="n">
-        <v>45.6</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>171</v>
-      </c>
-      <c r="B153" t="s">
-        <v>159</v>
-      </c>
-      <c r="C153" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="D153" t="n">
-        <v>25</v>
-      </c>
-      <c r="E153" t="n">
-        <v>8.3</v>
-      </c>
-      <c r="F153" t="n">
-        <v>25</v>
-      </c>
-      <c r="G153" t="n">
-        <v>0</v>
-      </c>
-      <c r="H153" t="n">
-        <v>0</v>
-      </c>
-      <c r="I153"/>
-      <c r="J153"/>
-      <c r="K153"/>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>172</v>
-      </c>
-      <c r="B154" t="s">
-        <v>159</v>
-      </c>
-      <c r="C154" t="n">
-        <v>0</v>
-      </c>
-      <c r="D154" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="E154" t="n">
-        <v>-33.3</v>
-      </c>
-      <c r="F154" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G154" t="n">
-        <v>100</v>
-      </c>
-      <c r="H154" t="n">
-        <v>0</v>
-      </c>
-      <c r="I154"/>
-      <c r="J154"/>
-      <c r="K154"/>
-    </row>
-    <row r="155">
-      <c r="A155"/>
-      <c r="B155" t="s">
-        <v>173</v>
-      </c>
-      <c r="C155" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="D155" t="n">
-        <v>26</v>
-      </c>
-      <c r="E155" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="F155" t="n">
-        <v>26</v>
-      </c>
-      <c r="G155" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="H155" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="I155" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="J155" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="K155" t="n">
-        <v>37.6</v>
+        <v>38.6</v>
       </c>
     </row>
   </sheetData>
@@ -6625,22 +6419,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -6649,18 +6443,18 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -6730,7 +6524,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -6765,42 +6559,42 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>47.3</v>
+        <v>48.2</v>
       </c>
       <c r="D5" t="n">
-        <v>55.3</v>
+        <v>55.7</v>
       </c>
       <c r="E5" t="n">
         <v>24.3</v>
       </c>
       <c r="F5" t="n">
-        <v>34.6</v>
+        <v>33.3</v>
       </c>
       <c r="G5" t="n">
-        <v>18.9</v>
+        <v>18.2</v>
       </c>
       <c r="H5" t="n">
-        <v>40.6</v>
+        <v>44.1</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J5" t="n">
-        <v>23.6</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.9</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -6835,7 +6629,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -6870,7 +6664,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -6940,42 +6734,42 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>60.2</v>
+        <v>57.5</v>
       </c>
       <c r="D10" t="n">
-        <v>62.1</v>
+        <v>61.3</v>
       </c>
       <c r="E10" t="n">
         <v>20.2</v>
       </c>
       <c r="F10" t="n">
-        <v>25.6</v>
+        <v>28.3</v>
       </c>
       <c r="G10" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="H10" t="n">
-        <v>33.3</v>
+        <v>37.5</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J10" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="K10" t="n">
-        <v>6.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -7010,42 +6804,42 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D12" t="n">
-        <v>63.5</v>
+        <v>62.2</v>
       </c>
       <c r="E12" t="n">
         <v>15.4</v>
       </c>
       <c r="F12" t="n">
-        <v>46.4</v>
+        <v>46.7</v>
       </c>
       <c r="G12" t="n">
-        <v>10.6</v>
+        <v>13.2</v>
       </c>
       <c r="H12" t="n">
-        <v>50</v>
+        <v>51.7</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>40.3</v>
+        <v>39.2</v>
       </c>
       <c r="K12" t="n">
-        <v>17.1</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -7113,7 +6907,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
@@ -7148,7 +6942,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s">
         <v>31</v>
@@ -7183,7 +6977,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s">
         <v>31</v>
@@ -7218,7 +7012,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
@@ -7253,7 +7047,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B19" t="s">
         <v>31</v>
@@ -7288,7 +7082,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B20" t="s">
         <v>31</v>
@@ -7323,7 +7117,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B21" t="s">
         <v>31</v>
@@ -7358,7 +7152,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B22" t="s">
         <v>31</v>
@@ -7393,7 +7187,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="B23" t="s">
         <v>31</v>
@@ -7428,7 +7222,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
@@ -7463,7 +7257,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
@@ -7498,7 +7292,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B26" t="s">
         <v>31</v>
@@ -7533,7 +7327,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B27" t="s">
         <v>31</v>
@@ -7568,7 +7362,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B28" t="s">
         <v>31</v>
@@ -7603,7 +7397,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B29" t="s">
         <v>46</v>
@@ -7638,7 +7432,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B30" t="s">
         <v>46</v>
@@ -7708,7 +7502,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B32" t="s">
         <v>46</v>
@@ -7743,7 +7537,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="B33" t="s">
         <v>46</v>
@@ -7778,7 +7572,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B34" t="s">
         <v>46</v>
@@ -7813,7 +7607,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B35" t="s">
         <v>46</v>
@@ -7846,7 +7640,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B36" t="s">
         <v>46</v>
@@ -7881,7 +7675,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B37" t="s">
         <v>46</v>
@@ -7916,7 +7710,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B38" t="s">
         <v>46</v>
@@ -7951,7 +7745,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B39" t="s">
         <v>46</v>
@@ -7986,7 +7780,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B40" t="s">
         <v>46</v>
@@ -8021,7 +7815,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
@@ -8054,7 +7848,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B42" t="s">
         <v>46</v>
@@ -8089,10 +7883,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C43" t="n">
         <v>59.8</v>
@@ -8124,45 +7918,45 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B44" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C44" t="n">
-        <v>74.1</v>
+        <v>73.3</v>
       </c>
       <c r="D44" t="n">
-        <v>76.2</v>
+        <v>76.3</v>
       </c>
       <c r="E44" t="n">
         <v>52.9</v>
       </c>
       <c r="F44" t="n">
-        <v>66.7</v>
+        <v>68.8</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>42.9</v>
+        <v>37.5</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>44.9</v>
+        <v>46.4</v>
       </c>
       <c r="K44" t="n">
-        <v>37</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="B45" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C45" t="n">
         <v>50</v>
@@ -8194,10 +7988,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C46" t="n">
         <v>66.7</v>
@@ -8227,45 +8021,45 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B47" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C47" t="n">
-        <v>60.6</v>
+        <v>62.1</v>
       </c>
       <c r="D47" t="n">
-        <v>67.7</v>
+        <v>66.7</v>
       </c>
       <c r="E47" t="n">
         <v>18.7</v>
       </c>
       <c r="F47" t="n">
-        <v>33.3</v>
+        <v>35.2</v>
       </c>
       <c r="G47" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="H47" t="n">
-        <v>37.3</v>
+        <v>44.7</v>
       </c>
       <c r="I47" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J47" t="n">
-        <v>19.3</v>
+        <v>22.1</v>
       </c>
       <c r="K47" t="n">
-        <v>11.9</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C48" t="n">
         <v>50.4</v>
@@ -8297,1614 +8091,1612 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B49" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C49" t="n">
-        <v>65.6</v>
+        <v>50</v>
       </c>
       <c r="D49" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="E49" t="n">
-        <v>32</v>
-      </c>
+        <v>46.2</v>
+      </c>
+      <c r="E49"/>
       <c r="F49" t="n">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="G49" t="n">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="H49" t="n">
-        <v>34.8</v>
+        <v>50</v>
       </c>
       <c r="I49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>16.9</v>
+        <v>50</v>
       </c>
       <c r="K49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B50" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C50" t="n">
-        <v>63.2</v>
+        <v>65.6</v>
       </c>
       <c r="D50" t="n">
-        <v>66.5</v>
+        <v>64.2</v>
       </c>
       <c r="E50" t="n">
-        <v>26.2</v>
+        <v>32</v>
       </c>
       <c r="F50" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="G50" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="H50" t="n">
-        <v>63.2</v>
+        <v>34.8</v>
       </c>
       <c r="I50" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="J50" t="n">
-        <v>32.4</v>
+        <v>16.9</v>
       </c>
       <c r="K50" t="n">
-        <v>15.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B51" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C51" t="n">
-        <v>60.5</v>
+        <v>61.7</v>
       </c>
       <c r="D51" t="n">
-        <v>61.7</v>
+        <v>67</v>
       </c>
       <c r="E51" t="n">
-        <v>6.2</v>
+        <v>26.2</v>
       </c>
       <c r="F51" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5</v>
+      </c>
+      <c r="H51" t="n">
+        <v>64.1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>5</v>
+      </c>
+      <c r="J51" t="n">
         <v>33.3</v>
       </c>
-      <c r="G51" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="H51" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="I51" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J51" t="n">
-        <v>20.9</v>
-      </c>
       <c r="K51" t="n">
-        <v>5.3</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B52" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C52" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="D52" t="n">
         <v>61.7</v>
       </c>
-      <c r="D52" t="n">
-        <v>67</v>
-      </c>
       <c r="E52" t="n">
-        <v>42.1</v>
+        <v>6.2</v>
       </c>
       <c r="F52" t="n">
-        <v>26.9</v>
+        <v>33.3</v>
       </c>
       <c r="G52" t="n">
-        <v>3.3</v>
+        <v>7.9</v>
       </c>
       <c r="H52" t="n">
-        <v>54.2</v>
+        <v>55.2</v>
       </c>
       <c r="I52" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="J52" t="n">
-        <v>19.8</v>
+        <v>20.9</v>
       </c>
       <c r="K52" t="n">
-        <v>8.2</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C53" t="n">
-        <v>62.2</v>
+        <v>61.7</v>
       </c>
       <c r="D53" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="E53"/>
+        <v>67</v>
+      </c>
+      <c r="E53" t="n">
+        <v>42.1</v>
+      </c>
       <c r="F53" t="n">
-        <v>31.2</v>
+        <v>26.9</v>
       </c>
       <c r="G53" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="H53" t="n">
-        <v>22.2</v>
+        <v>54.2</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="J53" t="n">
-        <v>19.4</v>
+        <v>19.8</v>
       </c>
       <c r="K53" t="n">
-        <v>10.8</v>
+        <v>8.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>79</v>
+        <v>220</v>
       </c>
       <c r="B54" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C54" t="n">
-        <v>30</v>
+        <v>62.2</v>
       </c>
       <c r="D54" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="E54" t="n">
-        <v>46.7</v>
-      </c>
+        <v>65.3</v>
+      </c>
+      <c r="E54"/>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="H54" t="n">
-        <v>25</v>
+        <v>22.2</v>
       </c>
       <c r="I54" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>19.4</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>226</v>
+        <v>78</v>
       </c>
       <c r="B55" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C55" t="n">
-        <v>37.5</v>
+        <v>30</v>
       </c>
       <c r="D55" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="E55"/>
+        <v>60.6</v>
+      </c>
+      <c r="E55" t="n">
+        <v>46.7</v>
+      </c>
       <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
         <v>25</v>
       </c>
-      <c r="G55" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="H55" t="n">
-        <v>71.4</v>
-      </c>
       <c r="I55" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>38.1</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>-18.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>81</v>
+        <v>221</v>
       </c>
       <c r="B56" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C56" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="D56" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="E56" t="n">
-        <v>37.5</v>
-      </c>
+        <v>45.5</v>
+      </c>
+      <c r="E56"/>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="H56" t="n">
-        <v>20</v>
+        <v>71.4</v>
       </c>
       <c r="I56" t="n">
-        <v>40</v>
+        <v>6.2</v>
       </c>
       <c r="J56" t="n">
-        <v>14.3</v>
+        <v>38.1</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>-18.7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>227</v>
+        <v>80</v>
       </c>
       <c r="B57" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="C57" t="n">
-        <v>69.5</v>
+        <v>40</v>
       </c>
       <c r="D57" t="n">
-        <v>68.7</v>
+        <v>57.1</v>
       </c>
       <c r="E57" t="n">
-        <v>27.9</v>
+        <v>37.5</v>
       </c>
       <c r="F57" t="n">
-        <v>48.3</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>54.3</v>
+        <v>20</v>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>40</v>
       </c>
       <c r="J57" t="n">
-        <v>24.4</v>
+        <v>14.3</v>
       </c>
       <c r="K57" t="n">
-        <v>20.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B58" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C58" t="n">
-        <v>68.2</v>
+        <v>69.5</v>
       </c>
       <c r="D58" t="n">
-        <v>67.2</v>
+        <v>68.7</v>
       </c>
       <c r="E58" t="n">
-        <v>9.5</v>
+        <v>27.9</v>
       </c>
       <c r="F58" t="n">
-        <v>50</v>
+        <v>48.3</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="H58" t="n">
-        <v>37.5</v>
+        <v>54.3</v>
       </c>
       <c r="I58" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J58" t="n">
-        <v>6.7</v>
+        <v>24.4</v>
       </c>
       <c r="K58" t="n">
-        <v>9.1</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B59" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C59" t="n">
-        <v>50</v>
+        <v>68.2</v>
       </c>
       <c r="D59" t="n">
-        <v>64.3</v>
+        <v>67.2</v>
       </c>
       <c r="E59" t="n">
-        <v>22.2</v>
+        <v>9.5</v>
       </c>
       <c r="F59" t="n">
         <v>50</v>
       </c>
       <c r="G59" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="J59" t="n">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="K59" t="n">
-        <v>12.5</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B60" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>46.4</v>
+        <v>50</v>
       </c>
       <c r="D60" t="n">
-        <v>58</v>
+        <v>64.3</v>
       </c>
       <c r="E60" t="n">
-        <v>23.3</v>
+        <v>22.2</v>
       </c>
       <c r="F60" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="G60" t="n">
-        <v>14.3</v>
+        <v>12.5</v>
       </c>
       <c r="H60" t="n">
-        <v>56.2</v>
+        <v>40</v>
       </c>
       <c r="I60" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>21.4</v>
+        <v>7.7</v>
       </c>
       <c r="K60" t="n">
-        <v>3.6</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B61" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C61" t="n">
-        <v>64.7</v>
+        <v>46.4</v>
       </c>
       <c r="D61" t="n">
-        <v>65.1</v>
+        <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>53.3</v>
+        <v>23.3</v>
       </c>
       <c r="F61" t="n">
-        <v>53.3</v>
+        <v>45.5</v>
       </c>
       <c r="G61" t="n">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
       <c r="H61" t="n">
-        <v>52.9</v>
+        <v>56.2</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="J61" t="n">
-        <v>28.9</v>
+        <v>21.4</v>
       </c>
       <c r="K61" t="n">
-        <v>8.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B62" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C62" t="n">
-        <v>61.1</v>
+        <v>64.7</v>
       </c>
       <c r="D62" t="n">
-        <v>63</v>
+        <v>65.1</v>
       </c>
       <c r="E62" t="n">
-        <v>17.6</v>
+        <v>53.3</v>
       </c>
       <c r="F62" t="n">
-        <v>55</v>
+        <v>53.3</v>
       </c>
       <c r="G62" t="n">
-        <v>7.1</v>
+        <v>14.7</v>
       </c>
       <c r="H62" t="n">
-        <v>56.5</v>
+        <v>52.9</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>36.2</v>
+        <v>28.9</v>
       </c>
       <c r="K62" t="n">
-        <v>22.1</v>
+        <v>8.8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B63" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C63" t="n">
-        <v>69.4</v>
+        <v>61.1</v>
       </c>
       <c r="D63" t="n">
-        <v>59.8</v>
+        <v>63</v>
       </c>
       <c r="E63" t="n">
-        <v>25.2</v>
+        <v>17.6</v>
       </c>
       <c r="F63" t="n">
-        <v>61.7</v>
+        <v>55</v>
       </c>
       <c r="G63" t="n">
-        <v>11</v>
+        <v>7.1</v>
       </c>
       <c r="H63" t="n">
-        <v>57.7</v>
+        <v>56.5</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
-        <v>43.9</v>
+        <v>36.2</v>
       </c>
       <c r="K63" t="n">
-        <v>28.7</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B64" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C64" t="n">
-        <v>58.3</v>
+        <v>69.4</v>
       </c>
       <c r="D64" t="n">
-        <v>65.6</v>
+        <v>59.8</v>
       </c>
       <c r="E64" t="n">
-        <v>43.5</v>
+        <v>25.2</v>
       </c>
       <c r="F64" t="n">
-        <v>7.7</v>
+        <v>61.7</v>
       </c>
       <c r="G64" t="n">
-        <v>8.3</v>
+        <v>11</v>
       </c>
       <c r="H64" t="n">
-        <v>42.9</v>
+        <v>57.7</v>
       </c>
       <c r="I64" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>21.1</v>
+        <v>43.9</v>
       </c>
       <c r="K64" t="n">
-        <v>-4.1</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B65" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C65" t="n">
-        <v>66.7</v>
+        <v>58.3</v>
       </c>
       <c r="D65" t="n">
-        <v>63.1</v>
+        <v>65.6</v>
       </c>
       <c r="E65" t="n">
-        <v>26.9</v>
+        <v>43.5</v>
       </c>
       <c r="F65" t="n">
-        <v>50</v>
+        <v>7.7</v>
       </c>
       <c r="G65" t="n">
-        <v>16.7</v>
+        <v>8.3</v>
       </c>
       <c r="H65" t="n">
-        <v>44.4</v>
+        <v>42.9</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="J65" t="n">
-        <v>35.7</v>
+        <v>21.1</v>
       </c>
       <c r="K65" t="n">
-        <v>11.1</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B66" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C66" t="n">
-        <v>65</v>
+        <v>66.7</v>
       </c>
       <c r="D66" t="n">
-        <v>66.5</v>
+        <v>63.1</v>
       </c>
       <c r="E66" t="n">
-        <v>34</v>
+        <v>26.9</v>
       </c>
       <c r="F66" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G66" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="H66" t="n">
-        <v>61</v>
+        <v>44.4</v>
       </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>28.4</v>
+        <v>35.7</v>
       </c>
       <c r="K66" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B67" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C67" t="n">
-        <v>63.1</v>
+        <v>65</v>
       </c>
       <c r="D67" t="n">
-        <v>62.4</v>
+        <v>66.5</v>
       </c>
       <c r="E67" t="n">
-        <v>31.7</v>
+        <v>34</v>
       </c>
       <c r="F67" t="n">
-        <v>52.7</v>
+        <v>40</v>
       </c>
       <c r="G67" t="n">
-        <v>8.9</v>
+        <v>10</v>
       </c>
       <c r="H67" t="n">
-        <v>38.2</v>
+        <v>61</v>
       </c>
       <c r="I67" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="J67" t="n">
-        <v>28</v>
+        <v>28.4</v>
       </c>
       <c r="K67" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B68" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C68" t="n">
-        <v>64.5</v>
+        <v>63.1</v>
       </c>
       <c r="D68" t="n">
-        <v>64.8</v>
+        <v>62.4</v>
       </c>
       <c r="E68" t="n">
-        <v>30</v>
+        <v>31.7</v>
       </c>
       <c r="F68" t="n">
-        <v>30.8</v>
+        <v>52.7</v>
       </c>
       <c r="G68" t="n">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="H68" t="n">
-        <v>40</v>
+        <v>38.2</v>
       </c>
       <c r="I68" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J68" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K68" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B69" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="C69" t="n">
-        <v>42.4</v>
+        <v>64.5</v>
       </c>
       <c r="D69" t="n">
-        <v>44.8</v>
+        <v>64.8</v>
       </c>
       <c r="E69" t="n">
-        <v>12.2</v>
+        <v>30</v>
       </c>
       <c r="F69" t="n">
-        <v>50</v>
+        <v>30.8</v>
       </c>
       <c r="G69" t="n">
-        <v>30.5</v>
+        <v>9.4</v>
       </c>
       <c r="H69" t="n">
-        <v>41.7</v>
+        <v>40</v>
       </c>
       <c r="I69" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J69" t="n">
-        <v>32.9</v>
+        <v>20</v>
       </c>
       <c r="K69" t="n">
-        <v>-10.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B70" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C70" t="n">
-        <v>70.3</v>
+        <v>42.4</v>
       </c>
       <c r="D70" t="n">
-        <v>61.8</v>
+        <v>44.8</v>
       </c>
       <c r="E70" t="n">
-        <v>23.1</v>
+        <v>12.2</v>
       </c>
       <c r="F70" t="n">
-        <v>40.6</v>
+        <v>50</v>
       </c>
       <c r="G70" t="n">
-        <v>13.6</v>
+        <v>30.5</v>
       </c>
       <c r="H70" t="n">
-        <v>51.2</v>
+        <v>41.7</v>
       </c>
       <c r="I70" t="n">
-        <v>7.6</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
-        <v>28.8</v>
+        <v>32.9</v>
       </c>
       <c r="K70" t="n">
-        <v>6.1</v>
+        <v>-10.2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>182</v>
+        <v>235</v>
       </c>
       <c r="B71" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C71" t="n">
-        <v>49</v>
+        <v>70.3</v>
       </c>
       <c r="D71" t="n">
-        <v>54.2</v>
+        <v>61.8</v>
       </c>
       <c r="E71" t="n">
-        <v>19</v>
+        <v>23.1</v>
       </c>
       <c r="F71" t="n">
-        <v>47.6</v>
+        <v>40.6</v>
       </c>
       <c r="G71" t="n">
-        <v>14</v>
+        <v>13.6</v>
       </c>
       <c r="H71" t="n">
-        <v>51.7</v>
+        <v>51.2</v>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>7.6</v>
       </c>
       <c r="J71" t="n">
-        <v>26</v>
+        <v>28.8</v>
       </c>
       <c r="K71" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>241</v>
+        <v>176</v>
       </c>
       <c r="B72" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C72" t="n">
-        <v>28.6</v>
+        <v>49</v>
       </c>
       <c r="D72" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="E72"/>
+        <v>54.2</v>
+      </c>
+      <c r="E72" t="n">
+        <v>19</v>
+      </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>47.6</v>
       </c>
       <c r="G72" t="n">
-        <v>42.9</v>
+        <v>14</v>
       </c>
       <c r="H72" t="n">
-        <v>25</v>
+        <v>51.7</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
-        <v>14.3</v>
+        <v>26</v>
       </c>
       <c r="K72" t="n">
-        <v>-42.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B73" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C73" t="n">
-        <v>48.6</v>
+        <v>28.6</v>
       </c>
       <c r="D73" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="E73" t="n">
-        <v>22.6</v>
-      </c>
+        <v>41.9</v>
+      </c>
+      <c r="E73"/>
       <c r="F73" t="n">
-        <v>41.5</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>14.9</v>
+        <v>42.9</v>
       </c>
       <c r="H73" t="n">
-        <v>32.6</v>
+        <v>25</v>
       </c>
       <c r="I73" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>33.6</v>
+        <v>14.3</v>
       </c>
       <c r="K73" t="n">
-        <v>8.1</v>
+        <v>-42.9</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>101</v>
+        <v>237</v>
       </c>
       <c r="B74" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C74" t="n">
-        <v>57.4</v>
+        <v>48.6</v>
       </c>
       <c r="D74" t="n">
-        <v>57.6</v>
+        <v>56.4</v>
       </c>
       <c r="E74" t="n">
-        <v>21.9</v>
+        <v>22.6</v>
       </c>
       <c r="F74" t="n">
-        <v>22.2</v>
+        <v>41.5</v>
       </c>
       <c r="G74" t="n">
-        <v>8.2</v>
+        <v>14.9</v>
       </c>
       <c r="H74" t="n">
-        <v>42.9</v>
+        <v>32.6</v>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="J74" t="n">
-        <v>21.8</v>
+        <v>33.6</v>
       </c>
       <c r="K74" t="n">
-        <v>4</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>207</v>
+        <v>100</v>
       </c>
       <c r="B75" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C75" t="n">
-        <v>63.6</v>
+        <v>57.4</v>
       </c>
       <c r="D75" t="n">
-        <v>66.7</v>
+        <v>57.6</v>
       </c>
       <c r="E75" t="n">
-        <v>20.2</v>
+        <v>21.9</v>
       </c>
       <c r="F75" t="n">
-        <v>43.6</v>
+        <v>22.2</v>
       </c>
       <c r="G75" t="n">
-        <v>5.8</v>
+        <v>8.2</v>
       </c>
       <c r="H75" t="n">
-        <v>46.5</v>
+        <v>42.9</v>
       </c>
       <c r="I75" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
-        <v>22.6</v>
+        <v>21.8</v>
       </c>
       <c r="K75" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>243</v>
+        <v>201</v>
       </c>
       <c r="B76" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C76" t="n">
-        <v>48.1</v>
+        <v>63.6</v>
       </c>
       <c r="D76" t="n">
-        <v>51.3</v>
+        <v>66.7</v>
       </c>
       <c r="E76" t="n">
-        <v>31.7</v>
+        <v>20.2</v>
       </c>
       <c r="F76" t="n">
-        <v>30.8</v>
+        <v>43.6</v>
       </c>
       <c r="G76" t="n">
-        <v>18.5</v>
+        <v>5.8</v>
       </c>
       <c r="H76" t="n">
-        <v>46.7</v>
+        <v>46.5</v>
       </c>
       <c r="I76" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="J76" t="n">
-        <v>29.4</v>
+        <v>22.6</v>
       </c>
       <c r="K76" t="n">
-        <v>-3.7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B77" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C77" t="n">
-        <v>68.2</v>
+        <v>48.1</v>
       </c>
       <c r="D77" t="n">
-        <v>66.2</v>
+        <v>51.3</v>
       </c>
       <c r="E77" t="n">
-        <v>26.1</v>
+        <v>31.7</v>
       </c>
       <c r="F77" t="n">
-        <v>33.3</v>
+        <v>30.8</v>
       </c>
       <c r="G77" t="n">
-        <v>8.2</v>
+        <v>18.5</v>
       </c>
       <c r="H77" t="n">
-        <v>45</v>
+        <v>46.7</v>
       </c>
       <c r="I77" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="J77" t="n">
-        <v>25</v>
+        <v>29.4</v>
       </c>
       <c r="K77" t="n">
-        <v>8.3</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B78" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C78" t="n">
-        <v>63.6</v>
+        <v>68.2</v>
       </c>
       <c r="D78" t="n">
-        <v>63.1</v>
+        <v>66.2</v>
       </c>
       <c r="E78" t="n">
-        <v>35.4</v>
+        <v>26.1</v>
       </c>
       <c r="F78" t="n">
-        <v>38.5</v>
+        <v>33.3</v>
       </c>
       <c r="G78" t="n">
-        <v>9.1</v>
+        <v>8.2</v>
       </c>
       <c r="H78" t="n">
-        <v>54.5</v>
+        <v>45</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="J78" t="n">
-        <v>23.5</v>
+        <v>25</v>
       </c>
       <c r="K78" t="n">
-        <v>13.6</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B79" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C79" t="n">
-        <v>52.2</v>
+        <v>63.6</v>
       </c>
       <c r="D79" t="n">
-        <v>55.6</v>
+        <v>63.1</v>
       </c>
       <c r="E79" t="n">
-        <v>24.5</v>
+        <v>35.4</v>
       </c>
       <c r="F79" t="n">
-        <v>40.4</v>
+        <v>38.5</v>
       </c>
       <c r="G79" t="n">
-        <v>10.5</v>
+        <v>9.1</v>
       </c>
       <c r="H79" t="n">
-        <v>26.4</v>
+        <v>54.5</v>
       </c>
       <c r="I79" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>25.3</v>
+        <v>23.5</v>
       </c>
       <c r="K79" t="n">
-        <v>7.9</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B80" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C80" t="n">
-        <v>55.3</v>
+        <v>52.2</v>
       </c>
       <c r="D80" t="n">
-        <v>59.9</v>
+        <v>55.6</v>
       </c>
       <c r="E80" t="n">
-        <v>30.8</v>
+        <v>24.5</v>
       </c>
       <c r="F80" t="n">
-        <v>40</v>
+        <v>40.4</v>
       </c>
       <c r="G80" t="n">
-        <v>9.2</v>
+        <v>10.5</v>
       </c>
       <c r="H80" t="n">
-        <v>58.7</v>
+        <v>26.4</v>
       </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>6.1</v>
       </c>
       <c r="J80" t="n">
-        <v>24.1</v>
+        <v>25.3</v>
       </c>
       <c r="K80" t="n">
-        <v>14.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B81" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="C81" t="n">
-        <v>70.4</v>
+        <v>55.3</v>
       </c>
       <c r="D81" t="n">
-        <v>68.2</v>
+        <v>59.9</v>
       </c>
       <c r="E81" t="n">
-        <v>42.9</v>
+        <v>30.8</v>
       </c>
       <c r="F81" t="n">
-        <v>30.8</v>
+        <v>40</v>
       </c>
       <c r="G81" t="n">
-        <v>10.7</v>
+        <v>9.2</v>
       </c>
       <c r="H81" t="n">
-        <v>50</v>
+        <v>58.7</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
-        <v>23.8</v>
+        <v>24.1</v>
       </c>
       <c r="K81" t="n">
-        <v>3.6</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B82" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C82" t="n">
-        <v>55.6</v>
+        <v>70.4</v>
       </c>
       <c r="D82" t="n">
-        <v>57.4</v>
+        <v>68.2</v>
       </c>
       <c r="E82" t="n">
-        <v>26.5</v>
+        <v>42.9</v>
       </c>
       <c r="F82" t="n">
-        <v>35.3</v>
+        <v>30.8</v>
       </c>
       <c r="G82" t="n">
-        <v>13.9</v>
+        <v>10.7</v>
       </c>
       <c r="H82" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="I82" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>31.1</v>
+        <v>23.8</v>
       </c>
       <c r="K82" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B83" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C83" t="n">
-        <v>59.8</v>
+        <v>55.6</v>
       </c>
       <c r="D83" t="n">
-        <v>65.7</v>
+        <v>57.4</v>
       </c>
       <c r="E83" t="n">
-        <v>24.5</v>
+        <v>26.5</v>
       </c>
       <c r="F83" t="n">
-        <v>43.2</v>
+        <v>35.3</v>
       </c>
       <c r="G83" t="n">
-        <v>5.3</v>
+        <v>13.9</v>
       </c>
       <c r="H83" t="n">
-        <v>48.8</v>
+        <v>32</v>
       </c>
       <c r="I83" t="n">
-        <v>2.7</v>
+        <v>8.3</v>
       </c>
       <c r="J83" t="n">
-        <v>19.8</v>
+        <v>31.1</v>
       </c>
       <c r="K83" t="n">
-        <v>8.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B84" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C84" t="n">
-        <v>61.2</v>
+        <v>59.8</v>
       </c>
       <c r="D84" t="n">
-        <v>64.6</v>
+        <v>65.7</v>
       </c>
       <c r="E84" t="n">
-        <v>35.2</v>
+        <v>24.5</v>
       </c>
       <c r="F84" t="n">
-        <v>66.7</v>
+        <v>43.2</v>
       </c>
       <c r="G84" t="n">
-        <v>10.2</v>
+        <v>5.3</v>
       </c>
       <c r="H84" t="n">
-        <v>60</v>
+        <v>48.8</v>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J84" t="n">
-        <v>36.8</v>
+        <v>19.8</v>
       </c>
       <c r="K84" t="n">
-        <v>26.5</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="B85" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C85" t="n">
-        <v>71.1</v>
+        <v>61.2</v>
       </c>
       <c r="D85" t="n">
-        <v>68.4</v>
+        <v>64.6</v>
       </c>
       <c r="E85" t="n">
-        <v>36.5</v>
+        <v>35.2</v>
       </c>
       <c r="F85" t="n">
-        <v>68.2</v>
+        <v>66.7</v>
       </c>
       <c r="G85" t="n">
-        <v>6.7</v>
+        <v>10.2</v>
       </c>
       <c r="H85" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I85" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
-        <v>32.4</v>
+        <v>36.8</v>
       </c>
       <c r="K85" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B86" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C86" t="n">
-        <v>57.8</v>
+        <v>71.1</v>
       </c>
       <c r="D86" t="n">
-        <v>64.2</v>
+        <v>68.4</v>
       </c>
       <c r="E86" t="n">
-        <v>24.4</v>
+        <v>36.5</v>
       </c>
       <c r="F86" t="n">
-        <v>25</v>
+        <v>68.2</v>
       </c>
       <c r="G86" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="H86" t="n">
-        <v>67.6</v>
+        <v>50</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="J86" t="n">
-        <v>17.9</v>
+        <v>32.4</v>
       </c>
       <c r="K86" t="n">
-        <v>6.5</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B87" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C87" t="n">
-        <v>71.9</v>
+        <v>57.8</v>
       </c>
       <c r="D87" t="n">
-        <v>67.5</v>
+        <v>64.2</v>
       </c>
       <c r="E87" t="n">
-        <v>42.5</v>
+        <v>24.4</v>
       </c>
       <c r="F87" t="n">
-        <v>58.8</v>
+        <v>25</v>
       </c>
       <c r="G87" t="n">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="H87" t="n">
-        <v>50</v>
+        <v>67.6</v>
       </c>
       <c r="I87" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>38.1</v>
+        <v>17.9</v>
       </c>
       <c r="K87" t="n">
-        <v>18.7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B88" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C88" t="n">
-        <v>66.2</v>
+        <v>71.9</v>
       </c>
       <c r="D88" t="n">
-        <v>64.6</v>
+        <v>67.5</v>
       </c>
       <c r="E88" t="n">
-        <v>27.1</v>
+        <v>42.5</v>
       </c>
       <c r="F88" t="n">
-        <v>36.7</v>
+        <v>58.8</v>
       </c>
       <c r="G88" t="n">
-        <v>10.3</v>
+        <v>12.5</v>
       </c>
       <c r="H88" t="n">
-        <v>43.6</v>
+        <v>50</v>
       </c>
       <c r="I88" t="n">
-        <v>2.8</v>
+        <v>6.2</v>
       </c>
       <c r="J88" t="n">
-        <v>22</v>
+        <v>38.1</v>
       </c>
       <c r="K88" t="n">
-        <v>4.9</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B89" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C89" t="n">
-        <v>70.4</v>
+        <v>66.2</v>
       </c>
       <c r="D89" t="n">
-        <v>71.2</v>
+        <v>64.6</v>
       </c>
       <c r="E89" t="n">
-        <v>34.2</v>
+        <v>27.1</v>
       </c>
       <c r="F89" t="n">
-        <v>47.9</v>
+        <v>36.7</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="H89" t="n">
-        <v>42.6</v>
+        <v>43.6</v>
       </c>
       <c r="I89" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J89" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K89" t="n">
-        <v>20.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B90" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C90" t="n">
-        <v>63.8</v>
+        <v>70.4</v>
       </c>
       <c r="D90" t="n">
-        <v>61.6</v>
+        <v>71.2</v>
       </c>
       <c r="E90" t="n">
-        <v>17.9</v>
+        <v>34.2</v>
       </c>
       <c r="F90" t="n">
-        <v>59</v>
+        <v>47.9</v>
       </c>
       <c r="G90" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>40</v>
+        <v>42.6</v>
       </c>
       <c r="I90" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J90" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="K90" t="n">
-        <v>24.2</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B91" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>50</v>
+        <v>63.8</v>
       </c>
       <c r="D91" t="n">
-        <v>54.4</v>
+        <v>61.6</v>
       </c>
       <c r="E91" t="n">
-        <v>14.3</v>
+        <v>17.9</v>
       </c>
       <c r="F91" t="n">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="G91" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="H91" t="n">
-        <v>40.9</v>
+        <v>40</v>
       </c>
       <c r="I91" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="J91" t="n">
-        <v>16.3</v>
+        <v>32</v>
       </c>
       <c r="K91" t="n">
-        <v>-9.4</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>136</v>
+        <v>253</v>
       </c>
       <c r="B92" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C92" t="n">
-        <v>50.9</v>
+        <v>50</v>
       </c>
       <c r="D92" t="n">
-        <v>59.1</v>
+        <v>54.4</v>
       </c>
       <c r="E92" t="n">
-        <v>15.9</v>
+        <v>14.3</v>
       </c>
       <c r="F92" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G92" t="n">
-        <v>12.7</v>
+        <v>15.6</v>
       </c>
       <c r="H92" t="n">
-        <v>42.5</v>
+        <v>40.9</v>
       </c>
       <c r="I92" t="n">
-        <v>7.3</v>
+        <v>3.1</v>
       </c>
       <c r="J92" t="n">
-        <v>23.8</v>
+        <v>16.3</v>
       </c>
       <c r="K92" t="n">
-        <v>1.8</v>
+        <v>-9.4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>259</v>
+        <v>132</v>
       </c>
       <c r="B93" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C93" t="n">
-        <v>52</v>
+        <v>50.9</v>
       </c>
       <c r="D93" t="n">
-        <v>65.3</v>
+        <v>59.1</v>
       </c>
       <c r="E93" t="n">
-        <v>25</v>
+        <v>15.9</v>
       </c>
       <c r="F93" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="G93" t="n">
-        <v>7.7</v>
+        <v>12.7</v>
       </c>
       <c r="H93" t="n">
-        <v>38.9</v>
+        <v>42.5</v>
       </c>
       <c r="I93" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J93" t="n">
-        <v>20</v>
+        <v>23.8</v>
       </c>
       <c r="K93" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B94" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C94" t="n">
-        <v>67.4</v>
+        <v>62</v>
       </c>
       <c r="D94" t="n">
-        <v>65.1</v>
+        <v>65.2</v>
       </c>
       <c r="E94" t="n">
-        <v>23</v>
+        <v>23.8</v>
       </c>
       <c r="F94" t="n">
-        <v>43.8</v>
+        <v>35.7</v>
       </c>
       <c r="G94" t="n">
-        <v>8.7</v>
+        <v>8.3</v>
       </c>
       <c r="H94" t="n">
-        <v>37.1</v>
+        <v>37.7</v>
       </c>
       <c r="I94" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="J94" t="n">
-        <v>16.9</v>
+        <v>18.1</v>
       </c>
       <c r="K94" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B95" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C95" t="n">
         <v>50</v>
@@ -9934,10 +9726,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B96" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C96" t="n">
         <v>68.8</v>
@@ -9969,10 +9761,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B97" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C97" t="n">
         <v>53.6</v>
@@ -10004,10 +9796,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B98" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C98" t="n">
         <v>50</v>
@@ -10039,10 +9831,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B99" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C99" t="n">
         <v>66.7</v>
@@ -10074,10 +9866,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B100" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C100" t="n">
         <v>52.6</v>
@@ -10109,10 +9901,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B101" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C101" t="n">
         <v>59.2</v>
@@ -10144,10 +9936,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B102" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C102" t="n">
         <v>57.6</v>
@@ -10179,10 +9971,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B103" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C103" t="n">
         <v>44</v>
@@ -10214,10 +10006,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B104" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C104" t="n">
         <v>38.9</v>
@@ -10249,10 +10041,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="B105" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C105" t="n">
         <v>62</v>
@@ -10284,10 +10076,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B106" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C106" t="n">
         <v>57.8</v>
@@ -10319,10 +10111,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B107" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C107" t="n">
         <v>64.2</v>
@@ -10354,10 +10146,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B108" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C108" t="n">
         <v>55.7</v>
@@ -10389,10 +10181,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B109" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C109" t="n">
         <v>59</v>
@@ -10424,10 +10216,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B110" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C110" t="n">
         <v>62.5</v>
@@ -10459,10 +10251,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B111" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C111" t="n">
         <v>63.6</v>
@@ -10494,10 +10286,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="B112" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C112" t="n">
         <v>84.6</v>
@@ -10527,10 +10319,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="B113" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C113" t="n">
         <v>50</v>
@@ -10562,10 +10354,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B114" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C114" t="n">
         <v>61.3</v>
@@ -10597,10 +10389,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B115" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C115" t="n">
         <v>65.8</v>
@@ -10632,10 +10424,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="B116" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C116" t="n">
         <v>50</v>
@@ -10667,10 +10459,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B117" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C117" t="n">
         <v>66.7</v>
@@ -10702,10 +10494,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B118" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C118" t="n">
         <v>66.7</v>
@@ -10737,10 +10529,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B119" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C119" t="n">
         <v>61.7</v>
@@ -10773,34 +10565,34 @@
     <row r="120">
       <c r="A120"/>
       <c r="B120" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C120" t="n">
-        <v>57.7</v>
+        <v>57.6</v>
       </c>
       <c r="D120" t="n">
-        <v>61.1</v>
+        <v>60.9</v>
       </c>
       <c r="E120" t="n">
         <v>24.4</v>
       </c>
       <c r="F120" t="n">
-        <v>38.4</v>
+        <v>39.1</v>
       </c>
       <c r="G120" t="n">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
       <c r="H120" t="n">
-        <v>46.1</v>
+        <v>46.3</v>
       </c>
       <c r="I120" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J120" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="K120" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/summary2026.xlsx
+++ b/data/summary2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="279">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -226,6 +226,9 @@
   </si>
   <si>
     <t xml:space="preserve">Garrett Takamatsu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J.D Williams</t>
   </si>
   <si>
     <t xml:space="preserve">J.D. Williams</t>
@@ -901,8 +904,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K149" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K149"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K150" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K150"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -1896,31 +1899,31 @@
         <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>70.6</v>
+        <v>72.2</v>
       </c>
       <c r="D20" t="n">
         <v>26.3</v>
       </c>
       <c r="E20" t="n">
-        <v>44.3</v>
+        <v>45.9</v>
       </c>
       <c r="F20" t="n">
         <v>26.3</v>
       </c>
       <c r="G20" t="n">
-        <v>55.6</v>
+        <v>52.6</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="K20" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21">
@@ -1931,31 +1934,31 @@
         <v>31</v>
       </c>
       <c r="C21" t="n">
-        <v>71.7</v>
+        <v>70.8</v>
       </c>
       <c r="D21" t="n">
-        <v>28</v>
+        <v>29.3</v>
       </c>
       <c r="E21" t="n">
-        <v>43.7</v>
+        <v>41.5</v>
       </c>
       <c r="F21" t="n">
-        <v>28</v>
+        <v>29.3</v>
       </c>
       <c r="G21" t="n">
-        <v>20.3</v>
+        <v>20.6</v>
       </c>
       <c r="H21" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="I21" t="n">
-        <v>30</v>
+        <v>31.2</v>
       </c>
       <c r="J21" t="n">
-        <v>26.7</v>
+        <v>28.1</v>
       </c>
       <c r="K21" t="n">
-        <v>46.4</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="22">
@@ -1966,31 +1969,31 @@
         <v>31</v>
       </c>
       <c r="C22" t="n">
-        <v>54.7</v>
+        <v>57.8</v>
       </c>
       <c r="D22" t="n">
-        <v>25</v>
+        <v>26.1</v>
       </c>
       <c r="E22" t="n">
-        <v>29.7</v>
+        <v>31.7</v>
       </c>
       <c r="F22" t="n">
-        <v>25</v>
+        <v>26.1</v>
       </c>
       <c r="G22" t="n">
-        <v>37.3</v>
+        <v>35.1</v>
       </c>
       <c r="H22" t="n">
-        <v>15.4</v>
+        <v>14.3</v>
       </c>
       <c r="I22" t="n">
-        <v>34.6</v>
+        <v>33.3</v>
       </c>
       <c r="J22" t="n">
-        <v>38.5</v>
+        <v>40</v>
       </c>
       <c r="K22" t="n">
-        <v>33.3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
@@ -2001,31 +2004,31 @@
         <v>31</v>
       </c>
       <c r="C23" t="n">
-        <v>64.1</v>
+        <v>65.9</v>
       </c>
       <c r="D23" t="n">
-        <v>26.5</v>
+        <v>25.3</v>
       </c>
       <c r="E23" t="n">
-        <v>37.6</v>
+        <v>40.6</v>
       </c>
       <c r="F23" t="n">
-        <v>26.5</v>
+        <v>25.3</v>
       </c>
       <c r="G23" t="n">
-        <v>29.1</v>
+        <v>28</v>
       </c>
       <c r="H23" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="I23" t="n">
-        <v>56.2</v>
+        <v>55.6</v>
       </c>
       <c r="J23" t="n">
-        <v>9.4</v>
+        <v>8.3</v>
       </c>
       <c r="K23" t="n">
-        <v>38.7</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="24">
@@ -2036,31 +2039,31 @@
         <v>31</v>
       </c>
       <c r="C24" t="n">
-        <v>75</v>
+        <v>73.7</v>
       </c>
       <c r="D24" t="n">
-        <v>28.6</v>
+        <v>42.1</v>
       </c>
       <c r="E24" t="n">
-        <v>46.4</v>
+        <v>31.6</v>
       </c>
       <c r="F24" t="n">
-        <v>28.6</v>
+        <v>42.1</v>
       </c>
       <c r="G24" t="n">
-        <v>30.4</v>
+        <v>26.7</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>20</v>
+        <v>23.1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="K24" t="n">
-        <v>30</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="25">
@@ -2071,31 +2074,31 @@
         <v>31</v>
       </c>
       <c r="C25" t="n">
-        <v>72.6</v>
+        <v>71.4</v>
       </c>
       <c r="D25" t="n">
-        <v>32.4</v>
+        <v>34.5</v>
       </c>
       <c r="E25" t="n">
-        <v>40.2</v>
+        <v>36.9</v>
       </c>
       <c r="F25" t="n">
-        <v>32.4</v>
+        <v>34.5</v>
       </c>
       <c r="G25" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="H25" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="I25" t="n">
-        <v>54.8</v>
+        <v>52.2</v>
       </c>
       <c r="J25" t="n">
-        <v>11.9</v>
+        <v>15.2</v>
       </c>
       <c r="K25" t="n">
-        <v>42.9</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="26">
@@ -2176,31 +2179,31 @@
         <v>31</v>
       </c>
       <c r="C28" t="n">
-        <v>63.4</v>
+        <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>21.1</v>
+        <v>22.4</v>
       </c>
       <c r="E28" t="n">
-        <v>42.3</v>
+        <v>41.6</v>
       </c>
       <c r="F28" t="n">
-        <v>21.1</v>
+        <v>22.4</v>
       </c>
       <c r="G28" t="n">
-        <v>22.5</v>
+        <v>20.8</v>
       </c>
       <c r="H28" t="n">
-        <v>17.7</v>
+        <v>16.4</v>
       </c>
       <c r="I28" t="n">
-        <v>46.9</v>
+        <v>48.6</v>
       </c>
       <c r="J28" t="n">
-        <v>12.5</v>
+        <v>10.8</v>
       </c>
       <c r="K28" t="n">
-        <v>45.2</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="29">
@@ -2211,31 +2214,31 @@
         <v>31</v>
       </c>
       <c r="C29" t="n">
-        <v>63.8</v>
+        <v>63.9</v>
       </c>
       <c r="D29" t="n">
-        <v>23.9</v>
+        <v>27.3</v>
       </c>
       <c r="E29" t="n">
-        <v>39.9</v>
+        <v>36.6</v>
       </c>
       <c r="F29" t="n">
-        <v>23.9</v>
+        <v>27.3</v>
       </c>
       <c r="G29" t="n">
-        <v>27.8</v>
+        <v>25.9</v>
       </c>
       <c r="H29" t="n">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="I29" t="n">
-        <v>48.3</v>
+        <v>43.8</v>
       </c>
       <c r="J29" t="n">
-        <v>20.7</v>
+        <v>25</v>
       </c>
       <c r="K29" t="n">
-        <v>40</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="30">
@@ -2281,31 +2284,31 @@
         <v>31</v>
       </c>
       <c r="C31" t="n">
-        <v>63</v>
+        <v>64.9</v>
       </c>
       <c r="D31" t="n">
-        <v>26.6</v>
+        <v>26.8</v>
       </c>
       <c r="E31" t="n">
-        <v>36.4</v>
+        <v>38.1</v>
       </c>
       <c r="F31" t="n">
-        <v>26.6</v>
+        <v>26.8</v>
       </c>
       <c r="G31" t="n">
-        <v>20.3</v>
+        <v>18.9</v>
       </c>
       <c r="H31" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="I31" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="J31" t="n">
-        <v>18.2</v>
+        <v>20</v>
       </c>
       <c r="K31" t="n">
-        <v>33.3</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="32">
@@ -2316,31 +2319,31 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>70.1</v>
+        <v>70.8</v>
       </c>
       <c r="D32" t="n">
-        <v>28.4</v>
+        <v>27.1</v>
       </c>
       <c r="E32" t="n">
-        <v>41.7</v>
+        <v>43.7</v>
       </c>
       <c r="F32" t="n">
-        <v>28.4</v>
+        <v>27.1</v>
       </c>
       <c r="G32" t="n">
-        <v>32.6</v>
+        <v>31.5</v>
       </c>
       <c r="H32" t="n">
-        <v>6.1</v>
+        <v>7.4</v>
       </c>
       <c r="I32" t="n">
-        <v>62.5</v>
+        <v>55.6</v>
       </c>
       <c r="J32" t="n">
-        <v>21.9</v>
+        <v>19.4</v>
       </c>
       <c r="K32" t="n">
-        <v>48.3</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="33">
@@ -2351,31 +2354,31 @@
         <v>31</v>
       </c>
       <c r="C33" t="n">
-        <v>84.2</v>
+        <v>81.8</v>
       </c>
       <c r="D33" t="n">
-        <v>47.8</v>
+        <v>41</v>
       </c>
       <c r="E33" t="n">
-        <v>36.4</v>
+        <v>40.8</v>
       </c>
       <c r="F33" t="n">
-        <v>47.8</v>
+        <v>41</v>
       </c>
       <c r="G33" t="n">
-        <v>34.8</v>
+        <v>35.8</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="I33" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="J33" t="n">
-        <v>53.3</v>
+        <v>44.4</v>
       </c>
       <c r="K33" t="n">
-        <v>17.6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34">
@@ -2386,22 +2389,22 @@
         <v>46</v>
       </c>
       <c r="C34" t="n">
-        <v>71.9</v>
+        <v>73.2</v>
       </c>
       <c r="D34" t="n">
-        <v>29.3</v>
+        <v>32.4</v>
       </c>
       <c r="E34" t="n">
-        <v>42.6</v>
+        <v>40.8</v>
       </c>
       <c r="F34" t="n">
-        <v>29.3</v>
+        <v>32.4</v>
       </c>
       <c r="G34" t="n">
-        <v>36.1</v>
+        <v>40.5</v>
       </c>
       <c r="H34" t="n">
-        <v>10.3</v>
+        <v>9.8</v>
       </c>
       <c r="I34" t="n">
         <v>65.4</v>
@@ -2421,31 +2424,31 @@
         <v>46</v>
       </c>
       <c r="C35" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D35" t="n">
-        <v>23.2</v>
+        <v>24</v>
       </c>
       <c r="E35" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="F35" t="n">
-        <v>23.2</v>
+        <v>24</v>
       </c>
       <c r="G35" t="n">
-        <v>17.1</v>
+        <v>18.2</v>
       </c>
       <c r="H35" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="I35" t="n">
-        <v>39.7</v>
+        <v>37.3</v>
       </c>
       <c r="J35" t="n">
-        <v>36.5</v>
+        <v>34.3</v>
       </c>
       <c r="K35" t="n">
-        <v>44.4</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="36">
@@ -2485,31 +2488,31 @@
         <v>46</v>
       </c>
       <c r="C37" t="n">
-        <v>68.4</v>
+        <v>69.7</v>
       </c>
       <c r="D37" t="n">
-        <v>19.4</v>
+        <v>21.7</v>
       </c>
       <c r="E37" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F37" t="n">
-        <v>19.4</v>
+        <v>21.7</v>
       </c>
       <c r="G37" t="n">
-        <v>12.9</v>
+        <v>12</v>
       </c>
       <c r="H37" t="n">
-        <v>10.4</v>
+        <v>9.7</v>
       </c>
       <c r="I37" t="n">
-        <v>57.1</v>
+        <v>54.1</v>
       </c>
       <c r="J37" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="K37" t="n">
-        <v>26.8</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="38">
@@ -2523,28 +2526,28 @@
         <v>77</v>
       </c>
       <c r="D38" t="n">
-        <v>32.7</v>
+        <v>34.2</v>
       </c>
       <c r="E38" t="n">
-        <v>44.3</v>
+        <v>42.8</v>
       </c>
       <c r="F38" t="n">
-        <v>32.7</v>
+        <v>34.2</v>
       </c>
       <c r="G38" t="n">
-        <v>25.8</v>
+        <v>25</v>
       </c>
       <c r="H38" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="I38" t="n">
-        <v>46.4</v>
+        <v>45</v>
       </c>
       <c r="J38" t="n">
-        <v>33.9</v>
+        <v>31.7</v>
       </c>
       <c r="K38" t="n">
-        <v>38.9</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="39">
@@ -2555,16 +2558,16 @@
         <v>46</v>
       </c>
       <c r="C39" t="n">
-        <v>71.4</v>
+        <v>62.5</v>
       </c>
       <c r="D39" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="E39" t="n">
-        <v>15.8</v>
+        <v>12.5</v>
       </c>
       <c r="F39" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -2573,13 +2576,13 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="J39" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="K39" t="n">
-        <v>12.5</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="40">
@@ -2590,31 +2593,31 @@
         <v>46</v>
       </c>
       <c r="C40" t="n">
-        <v>60.5</v>
+        <v>59.8</v>
       </c>
       <c r="D40" t="n">
-        <v>28.7</v>
+        <v>30.3</v>
       </c>
       <c r="E40" t="n">
-        <v>31.8</v>
+        <v>29.5</v>
       </c>
       <c r="F40" t="n">
-        <v>28.7</v>
+        <v>30.3</v>
       </c>
       <c r="G40" t="n">
-        <v>20.7</v>
+        <v>19.8</v>
       </c>
       <c r="H40" t="n">
-        <v>11.6</v>
+        <v>10.8</v>
       </c>
       <c r="I40" t="n">
-        <v>53.2</v>
+        <v>53.8</v>
       </c>
       <c r="J40" t="n">
-        <v>12.8</v>
+        <v>15.4</v>
       </c>
       <c r="K40" t="n">
-        <v>19.1</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="41">
@@ -2660,31 +2663,31 @@
         <v>46</v>
       </c>
       <c r="C42" t="n">
-        <v>72.7</v>
+        <v>73.8</v>
       </c>
       <c r="D42" t="n">
-        <v>44.8</v>
+        <v>46.8</v>
       </c>
       <c r="E42" t="n">
-        <v>27.9</v>
+        <v>27</v>
       </c>
       <c r="F42" t="n">
-        <v>44.8</v>
+        <v>46.8</v>
       </c>
       <c r="G42" t="n">
-        <v>39.7</v>
+        <v>36.9</v>
       </c>
       <c r="H42" t="n">
-        <v>10</v>
+        <v>9.1</v>
       </c>
       <c r="I42" t="n">
         <v>50</v>
       </c>
       <c r="J42" t="n">
-        <v>27.8</v>
+        <v>30</v>
       </c>
       <c r="K42" t="n">
-        <v>55.6</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43">
@@ -2733,28 +2736,28 @@
         <v>67.9</v>
       </c>
       <c r="D44" t="n">
-        <v>19.2</v>
+        <v>21.1</v>
       </c>
       <c r="E44" t="n">
-        <v>48.7</v>
+        <v>46.8</v>
       </c>
       <c r="F44" t="n">
-        <v>19.2</v>
+        <v>21.1</v>
       </c>
       <c r="G44" t="n">
-        <v>31.2</v>
+        <v>31.4</v>
       </c>
       <c r="H44" t="n">
-        <v>12.1</v>
+        <v>12.9</v>
       </c>
       <c r="I44" t="n">
-        <v>30</v>
+        <v>33.3</v>
       </c>
       <c r="J44" t="n">
-        <v>45</v>
+        <v>42.9</v>
       </c>
       <c r="K44" t="n">
-        <v>25</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="45">
@@ -2765,31 +2768,31 @@
         <v>46</v>
       </c>
       <c r="C45" t="n">
-        <v>70.6</v>
+        <v>68.4</v>
       </c>
       <c r="D45" t="n">
-        <v>30.8</v>
+        <v>34.3</v>
       </c>
       <c r="E45" t="n">
-        <v>39.8</v>
+        <v>34.1</v>
       </c>
       <c r="F45" t="n">
-        <v>30.8</v>
+        <v>34.3</v>
       </c>
       <c r="G45" t="n">
-        <v>55.6</v>
+        <v>53.7</v>
       </c>
       <c r="H45" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="I45" t="n">
-        <v>66.7</v>
+        <v>63.6</v>
       </c>
       <c r="J45" t="n">
-        <v>22.2</v>
+        <v>18.2</v>
       </c>
       <c r="K45" t="n">
-        <v>22.2</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="46">
@@ -2870,31 +2873,31 @@
         <v>46</v>
       </c>
       <c r="C48" t="n">
-        <v>73.8</v>
+        <v>74.8</v>
       </c>
       <c r="D48" t="n">
-        <v>16.5</v>
+        <v>19.7</v>
       </c>
       <c r="E48" t="n">
-        <v>57.3</v>
+        <v>55.1</v>
       </c>
       <c r="F48" t="n">
-        <v>16.5</v>
+        <v>19.7</v>
       </c>
       <c r="G48" t="n">
-        <v>35.3</v>
+        <v>35.1</v>
       </c>
       <c r="H48" t="n">
-        <v>14.7</v>
+        <v>13.8</v>
       </c>
       <c r="I48" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>43.9</v>
+        <v>42.2</v>
       </c>
       <c r="K48" t="n">
-        <v>48.8</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="49">
@@ -2908,28 +2911,28 @@
         <v>72.7</v>
       </c>
       <c r="D49" t="n">
-        <v>16.1</v>
+        <v>29.8</v>
       </c>
       <c r="E49" t="n">
-        <v>56.6</v>
+        <v>42.9</v>
       </c>
       <c r="F49" t="n">
-        <v>16.1</v>
+        <v>29.8</v>
       </c>
       <c r="G49" t="n">
-        <v>28.6</v>
+        <v>30.7</v>
       </c>
       <c r="H49" t="n">
-        <v>8.9</v>
+        <v>10.2</v>
       </c>
       <c r="I49" t="n">
-        <v>50</v>
+        <v>54.3</v>
       </c>
       <c r="J49" t="n">
-        <v>18.8</v>
+        <v>17.1</v>
       </c>
       <c r="K49" t="n">
-        <v>43.8</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="50">
@@ -2940,31 +2943,31 @@
         <v>62</v>
       </c>
       <c r="C50" t="n">
-        <v>78.4</v>
+        <v>75.6</v>
       </c>
       <c r="D50" t="n">
-        <v>36.8</v>
+        <v>50</v>
       </c>
       <c r="E50" t="n">
-        <v>41.6</v>
+        <v>25.6</v>
       </c>
       <c r="F50" t="n">
-        <v>36.8</v>
+        <v>50</v>
       </c>
       <c r="G50" t="n">
-        <v>24.1</v>
+        <v>20.9</v>
       </c>
       <c r="H50" t="n">
         <v>6</v>
       </c>
       <c r="I50" t="n">
-        <v>43.6</v>
+        <v>42.5</v>
       </c>
       <c r="J50" t="n">
-        <v>23.1</v>
+        <v>22.5</v>
       </c>
       <c r="K50" t="n">
-        <v>35.9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51">
@@ -2975,31 +2978,31 @@
         <v>62</v>
       </c>
       <c r="C51" t="n">
-        <v>44.2</v>
+        <v>50</v>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E51" t="n">
-        <v>31</v>
+        <v>32.6</v>
       </c>
       <c r="F51" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="G51" t="n">
-        <v>31.7</v>
+        <v>29.4</v>
       </c>
       <c r="H51" t="n">
-        <v>14.8</v>
+        <v>14.5</v>
       </c>
       <c r="I51" t="n">
-        <v>57.7</v>
+        <v>60.7</v>
       </c>
       <c r="J51" t="n">
-        <v>15.4</v>
+        <v>14.3</v>
       </c>
       <c r="K51" t="n">
-        <v>16</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="52">
@@ -3013,19 +3016,19 @@
         <v>100</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="E52" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G52" t="n">
-        <v>30.8</v>
+        <v>43.8</v>
       </c>
       <c r="H52" t="n">
-        <v>25</v>
+        <v>22.2</v>
       </c>
       <c r="I52" t="n">
         <v>40</v>
@@ -3083,19 +3086,19 @@
         <v>57.1</v>
       </c>
       <c r="D54" t="n">
-        <v>7.7</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="n">
-        <v>49.4</v>
+        <v>44.6</v>
       </c>
       <c r="F54" t="n">
-        <v>7.7</v>
+        <v>12.5</v>
       </c>
       <c r="G54" t="n">
         <v>14.3</v>
       </c>
       <c r="H54" t="n">
-        <v>28.6</v>
+        <v>16.7</v>
       </c>
       <c r="I54" t="n">
         <v>100</v>
@@ -3115,31 +3118,31 @@
         <v>62</v>
       </c>
       <c r="C55" t="n">
-        <v>79.3</v>
+        <v>77.1</v>
       </c>
       <c r="D55" t="n">
-        <v>28.4</v>
+        <v>30.3</v>
       </c>
       <c r="E55" t="n">
-        <v>50.9</v>
+        <v>46.8</v>
       </c>
       <c r="F55" t="n">
-        <v>28.4</v>
+        <v>30.3</v>
       </c>
       <c r="G55" t="n">
-        <v>36.8</v>
+        <v>35.9</v>
       </c>
       <c r="H55" t="n">
-        <v>8.6</v>
+        <v>9.9</v>
       </c>
       <c r="I55" t="n">
-        <v>46</v>
+        <v>47.1</v>
       </c>
       <c r="J55" t="n">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="K55" t="n">
-        <v>46</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="56">
@@ -3185,31 +3188,31 @@
         <v>62</v>
       </c>
       <c r="C57" t="n">
-        <v>84.5</v>
+        <v>83.7</v>
       </c>
       <c r="D57" t="n">
-        <v>20.6</v>
+        <v>21.2</v>
       </c>
       <c r="E57" t="n">
-        <v>63.9</v>
+        <v>62.5</v>
       </c>
       <c r="F57" t="n">
-        <v>20.6</v>
+        <v>21.2</v>
       </c>
       <c r="G57" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="H57" t="n">
         <v>20</v>
       </c>
       <c r="I57" t="n">
-        <v>55.3</v>
+        <v>55.6</v>
       </c>
       <c r="J57" t="n">
-        <v>19.1</v>
+        <v>20</v>
       </c>
       <c r="K57" t="n">
-        <v>40</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="58">
@@ -3219,32 +3222,28 @@
       <c r="B58" t="s">
         <v>62</v>
       </c>
-      <c r="C58" t="n">
-        <v>80</v>
-      </c>
+      <c r="C58"/>
       <c r="D58" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="E58" t="n">
-        <v>68.6</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="E58"/>
       <c r="F58" t="n">
-        <v>11.4</v>
+        <v>40</v>
       </c>
       <c r="G58" t="n">
-        <v>23.7</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>52.4</v>
+        <v>50</v>
       </c>
       <c r="J58" t="n">
-        <v>14.3</v>
+        <v>50</v>
       </c>
       <c r="K58" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59">
@@ -3255,31 +3254,31 @@
         <v>62</v>
       </c>
       <c r="C59" t="n">
-        <v>100</v>
+        <v>76.9</v>
       </c>
       <c r="D59" t="n">
-        <v>50</v>
+        <v>11.4</v>
       </c>
       <c r="E59" t="n">
-        <v>50</v>
+        <v>65.5</v>
       </c>
       <c r="F59" t="n">
-        <v>50</v>
+        <v>11.4</v>
       </c>
       <c r="G59" t="n">
-        <v>25</v>
+        <v>27.1</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="I59" t="n">
-        <v>100</v>
+        <v>52.9</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="K59" t="n">
-        <v>100</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="60">
@@ -3290,31 +3289,31 @@
         <v>62</v>
       </c>
       <c r="C60" t="n">
+        <v>100</v>
+      </c>
+      <c r="D60" t="n">
         <v>50</v>
       </c>
-      <c r="D60" t="n">
+      <c r="E60" t="n">
+        <v>50</v>
+      </c>
+      <c r="F60" t="n">
+        <v>50</v>
+      </c>
+      <c r="G60" t="n">
         <v>25</v>
       </c>
-      <c r="E60" t="n">
-        <v>25</v>
-      </c>
-      <c r="F60" t="n">
-        <v>25</v>
-      </c>
-      <c r="G60" t="n">
-        <v>20</v>
-      </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="61">
@@ -3325,31 +3324,31 @@
         <v>62</v>
       </c>
       <c r="C61" t="n">
-        <v>74.3</v>
+        <v>33.3</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="E61" t="n">
-        <v>74.3</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G61" t="n">
-        <v>29.3</v>
+        <v>25</v>
       </c>
       <c r="H61" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J61" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62">
@@ -3360,31 +3359,31 @@
         <v>62</v>
       </c>
       <c r="C62" t="n">
-        <v>69.6</v>
+        <v>74.1</v>
       </c>
       <c r="D62" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>36.3</v>
+        <v>74.1</v>
       </c>
       <c r="F62" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>20</v>
+        <v>31.4</v>
       </c>
       <c r="H62" t="n">
-        <v>11.8</v>
+        <v>18.8</v>
       </c>
       <c r="I62" t="n">
-        <v>46.2</v>
+        <v>62.5</v>
       </c>
       <c r="J62" t="n">
-        <v>30.8</v>
+        <v>12.5</v>
       </c>
       <c r="K62" t="n">
-        <v>53.8</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="63">
@@ -3395,31 +3394,31 @@
         <v>62</v>
       </c>
       <c r="C63" t="n">
-        <v>75</v>
+        <v>69.6</v>
       </c>
       <c r="D63" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E63" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="F63" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G63" t="n">
+        <v>20</v>
+      </c>
+      <c r="H63" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I63" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="J63" t="n">
         <v>30.8</v>
       </c>
-      <c r="E63" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="F63" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="G63" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="H63" t="n">
-        <v>20</v>
-      </c>
-      <c r="I63" t="n">
-        <v>50</v>
-      </c>
-      <c r="J63" t="n">
-        <v>50</v>
-      </c>
       <c r="K63" t="n">
-        <v>100</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="64">
@@ -3430,31 +3429,31 @@
         <v>62</v>
       </c>
       <c r="C64" t="n">
-        <v>68.6</v>
+        <v>75</v>
       </c>
       <c r="D64" t="n">
-        <v>31.8</v>
+        <v>40</v>
       </c>
       <c r="E64" t="n">
-        <v>36.8</v>
+        <v>35</v>
       </c>
       <c r="F64" t="n">
-        <v>31.8</v>
+        <v>40</v>
       </c>
       <c r="G64" t="n">
-        <v>11.1</v>
+        <v>60</v>
       </c>
       <c r="H64" t="n">
-        <v>3.4</v>
+        <v>16.7</v>
       </c>
       <c r="I64" t="n">
-        <v>47.6</v>
+        <v>66.7</v>
       </c>
       <c r="J64" t="n">
-        <v>28.6</v>
+        <v>33.3</v>
       </c>
       <c r="K64" t="n">
-        <v>38.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65">
@@ -3465,31 +3464,31 @@
         <v>62</v>
       </c>
       <c r="C65" t="n">
-        <v>69.3</v>
+        <v>68.6</v>
       </c>
       <c r="D65" t="n">
-        <v>19.1</v>
+        <v>31.8</v>
       </c>
       <c r="E65" t="n">
-        <v>50.2</v>
+        <v>36.8</v>
       </c>
       <c r="F65" t="n">
-        <v>19.1</v>
+        <v>31.8</v>
       </c>
       <c r="G65" t="n">
-        <v>25.7</v>
+        <v>11.1</v>
       </c>
       <c r="H65" t="n">
-        <v>11.4</v>
+        <v>3.4</v>
       </c>
       <c r="I65" t="n">
-        <v>42.9</v>
+        <v>47.6</v>
       </c>
       <c r="J65" t="n">
-        <v>24.5</v>
+        <v>28.6</v>
       </c>
       <c r="K65" t="n">
-        <v>35.4</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="66">
@@ -3500,31 +3499,31 @@
         <v>62</v>
       </c>
       <c r="C66" t="n">
-        <v>80</v>
+        <v>71.4</v>
       </c>
       <c r="D66" t="n">
-        <v>40.8</v>
+        <v>23.9</v>
       </c>
       <c r="E66" t="n">
-        <v>39.2</v>
+        <v>47.5</v>
       </c>
       <c r="F66" t="n">
-        <v>40.8</v>
+        <v>23.9</v>
       </c>
       <c r="G66" t="n">
-        <v>24.7</v>
+        <v>27.1</v>
       </c>
       <c r="H66" t="n">
-        <v>3.8</v>
+        <v>10.1</v>
       </c>
       <c r="I66" t="n">
-        <v>34.6</v>
+        <v>40</v>
       </c>
       <c r="J66" t="n">
-        <v>44.2</v>
+        <v>28</v>
       </c>
       <c r="K66" t="n">
-        <v>46.2</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="67">
@@ -3535,31 +3534,31 @@
         <v>62</v>
       </c>
       <c r="C67" t="n">
-        <v>58.7</v>
+        <v>79.3</v>
       </c>
       <c r="D67" t="n">
-        <v>9.9</v>
+        <v>45.8</v>
       </c>
       <c r="E67" t="n">
-        <v>48.8</v>
+        <v>33.5</v>
       </c>
       <c r="F67" t="n">
-        <v>9.9</v>
+        <v>45.8</v>
       </c>
       <c r="G67" t="n">
-        <v>29.7</v>
+        <v>22.8</v>
       </c>
       <c r="H67" t="n">
-        <v>15.8</v>
+        <v>3.8</v>
       </c>
       <c r="I67" t="n">
-        <v>42.5</v>
+        <v>38.9</v>
       </c>
       <c r="J67" t="n">
-        <v>30</v>
+        <v>40.7</v>
       </c>
       <c r="K67" t="n">
-        <v>21.6</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="68">
@@ -3570,31 +3569,31 @@
         <v>62</v>
       </c>
       <c r="C68" t="n">
-        <v>71</v>
+        <v>56.5</v>
       </c>
       <c r="D68" t="n">
-        <v>23.4</v>
+        <v>15.7</v>
       </c>
       <c r="E68" t="n">
-        <v>47.6</v>
+        <v>40.8</v>
       </c>
       <c r="F68" t="n">
-        <v>23.4</v>
+        <v>15.7</v>
       </c>
       <c r="G68" t="n">
-        <v>34</v>
+        <v>30.7</v>
       </c>
       <c r="H68" t="n">
-        <v>7.5</v>
+        <v>15.4</v>
       </c>
       <c r="I68" t="n">
-        <v>46.7</v>
+        <v>45</v>
       </c>
       <c r="J68" t="n">
-        <v>26.7</v>
+        <v>30</v>
       </c>
       <c r="K68" t="n">
-        <v>51.6</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="69">
@@ -3602,69 +3601,69 @@
         <v>82</v>
       </c>
       <c r="B69" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="C69" t="n">
-        <v>86</v>
+        <v>70.4</v>
       </c>
       <c r="D69" t="n">
-        <v>21.1</v>
+        <v>30.6</v>
       </c>
       <c r="E69" t="n">
-        <v>64.9</v>
+        <v>39.8</v>
       </c>
       <c r="F69" t="n">
-        <v>21.1</v>
+        <v>30.6</v>
       </c>
       <c r="G69" t="n">
-        <v>38.8</v>
+        <v>33.3</v>
       </c>
       <c r="H69" t="n">
-        <v>11.9</v>
+        <v>7.5</v>
       </c>
       <c r="I69" t="n">
-        <v>33.3</v>
+        <v>45.2</v>
       </c>
       <c r="J69" t="n">
-        <v>51.9</v>
+        <v>25.8</v>
       </c>
       <c r="K69" t="n">
-        <v>58.6</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
+        <v>83</v>
+      </c>
+      <c r="B70" t="s">
         <v>84</v>
       </c>
-      <c r="B70" t="s">
-        <v>83</v>
-      </c>
       <c r="C70" t="n">
-        <v>74.3</v>
+        <v>86</v>
       </c>
       <c r="D70" t="n">
-        <v>28.8</v>
+        <v>21.1</v>
       </c>
       <c r="E70" t="n">
-        <v>45.5</v>
+        <v>64.9</v>
       </c>
       <c r="F70" t="n">
-        <v>28.8</v>
+        <v>21.1</v>
       </c>
       <c r="G70" t="n">
-        <v>19.5</v>
+        <v>38.8</v>
       </c>
       <c r="H70" t="n">
-        <v>5.5</v>
+        <v>11.9</v>
       </c>
       <c r="I70" t="n">
-        <v>59</v>
+        <v>33.3</v>
       </c>
       <c r="J70" t="n">
-        <v>20.5</v>
+        <v>51.9</v>
       </c>
       <c r="K70" t="n">
-        <v>43.2</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="71">
@@ -3672,34 +3671,34 @@
         <v>85</v>
       </c>
       <c r="B71" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C71" t="n">
-        <v>78.8</v>
+        <v>74.3</v>
       </c>
       <c r="D71" t="n">
-        <v>31.2</v>
+        <v>28.8</v>
       </c>
       <c r="E71" t="n">
-        <v>47.6</v>
+        <v>45.5</v>
       </c>
       <c r="F71" t="n">
-        <v>31.2</v>
+        <v>28.8</v>
       </c>
       <c r="G71" t="n">
-        <v>34.3</v>
+        <v>19.5</v>
       </c>
       <c r="H71" t="n">
-        <v>10.1</v>
+        <v>5.5</v>
       </c>
       <c r="I71" t="n">
-        <v>42.5</v>
+        <v>59</v>
       </c>
       <c r="J71" t="n">
-        <v>25</v>
+        <v>20.5</v>
       </c>
       <c r="K71" t="n">
-        <v>64.3</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="72">
@@ -3707,34 +3706,34 @@
         <v>86</v>
       </c>
       <c r="B72" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C72" t="n">
-        <v>70.4</v>
+        <v>78.8</v>
       </c>
       <c r="D72" t="n">
-        <v>33.7</v>
+        <v>31.2</v>
       </c>
       <c r="E72" t="n">
-        <v>36.7</v>
+        <v>47.6</v>
       </c>
       <c r="F72" t="n">
-        <v>33.7</v>
+        <v>31.2</v>
       </c>
       <c r="G72" t="n">
-        <v>29.5</v>
+        <v>34.3</v>
       </c>
       <c r="H72" t="n">
-        <v>8.5</v>
+        <v>10.1</v>
       </c>
       <c r="I72" t="n">
-        <v>51.1</v>
+        <v>42.5</v>
       </c>
       <c r="J72" t="n">
-        <v>21.3</v>
+        <v>25</v>
       </c>
       <c r="K72" t="n">
-        <v>48.9</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="73">
@@ -3742,34 +3741,34 @@
         <v>87</v>
       </c>
       <c r="B73" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C73" t="n">
-        <v>76.8</v>
+        <v>70.4</v>
       </c>
       <c r="D73" t="n">
-        <v>42.5</v>
+        <v>33.7</v>
       </c>
       <c r="E73" t="n">
-        <v>34.3</v>
+        <v>36.7</v>
       </c>
       <c r="F73" t="n">
-        <v>42.5</v>
+        <v>33.7</v>
       </c>
       <c r="G73" t="n">
-        <v>24.3</v>
+        <v>29.5</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="I73" t="n">
-        <v>36.1</v>
+        <v>51.1</v>
       </c>
       <c r="J73" t="n">
-        <v>27.9</v>
+        <v>21.3</v>
       </c>
       <c r="K73" t="n">
-        <v>70.2</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="74">
@@ -3777,34 +3776,34 @@
         <v>88</v>
       </c>
       <c r="B74" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C74" t="n">
-        <v>71.4</v>
+        <v>76.8</v>
       </c>
       <c r="D74" t="n">
-        <v>20</v>
+        <v>42.5</v>
       </c>
       <c r="E74" t="n">
-        <v>51.4</v>
+        <v>34.3</v>
       </c>
       <c r="F74" t="n">
-        <v>20</v>
+        <v>42.5</v>
       </c>
       <c r="G74" t="n">
-        <v>22</v>
+        <v>24.3</v>
       </c>
       <c r="H74" t="n">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>31.9</v>
+        <v>36.1</v>
       </c>
       <c r="J74" t="n">
-        <v>38.3</v>
+        <v>27.9</v>
       </c>
       <c r="K74" t="n">
-        <v>28.9</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="75">
@@ -3812,34 +3811,34 @@
         <v>89</v>
       </c>
       <c r="B75" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C75" t="n">
-        <v>73.8</v>
+        <v>71.4</v>
       </c>
       <c r="D75" t="n">
-        <v>32.7</v>
+        <v>20</v>
       </c>
       <c r="E75" t="n">
-        <v>41.1</v>
+        <v>51.4</v>
       </c>
       <c r="F75" t="n">
-        <v>32.7</v>
+        <v>20</v>
       </c>
       <c r="G75" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H75" t="n">
-        <v>8.7</v>
+        <v>13.6</v>
       </c>
       <c r="I75" t="n">
-        <v>51.7</v>
+        <v>31.9</v>
       </c>
       <c r="J75" t="n">
-        <v>20.7</v>
+        <v>38.3</v>
       </c>
       <c r="K75" t="n">
-        <v>29.6</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="76">
@@ -3847,34 +3846,34 @@
         <v>90</v>
       </c>
       <c r="B76" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C76" t="n">
-        <v>100</v>
+        <v>73.8</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>32.7</v>
       </c>
       <c r="E76" t="n">
-        <v>100</v>
+        <v>41.1</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>32.7</v>
       </c>
       <c r="G76" t="n">
-        <v>46.2</v>
+        <v>32</v>
       </c>
       <c r="H76" t="n">
-        <v>33.3</v>
+        <v>8.7</v>
       </c>
       <c r="I76" t="n">
-        <v>100</v>
+        <v>51.7</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>20.7</v>
       </c>
       <c r="K76" t="n">
-        <v>100</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="77">
@@ -3882,34 +3881,34 @@
         <v>91</v>
       </c>
       <c r="B77" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C77" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="D77" t="n">
-        <v>30.6</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>38.4</v>
+        <v>100</v>
       </c>
       <c r="F77" t="n">
-        <v>30.6</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>19</v>
+        <v>46.2</v>
       </c>
       <c r="H77" t="n">
-        <v>7.9</v>
+        <v>33.3</v>
       </c>
       <c r="I77" t="n">
-        <v>59.2</v>
+        <v>100</v>
       </c>
       <c r="J77" t="n">
-        <v>16.3</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>44.9</v>
+        <v>100</v>
       </c>
     </row>
     <row r="78">
@@ -3917,34 +3916,34 @@
         <v>92</v>
       </c>
       <c r="B78" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C78" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D78" t="n">
-        <v>46.5</v>
+        <v>30.6</v>
       </c>
       <c r="E78" t="n">
-        <v>25.5</v>
+        <v>38.4</v>
       </c>
       <c r="F78" t="n">
-        <v>46.5</v>
+        <v>30.6</v>
       </c>
       <c r="G78" t="n">
-        <v>23.7</v>
+        <v>19</v>
       </c>
       <c r="H78" t="n">
-        <v>10.8</v>
+        <v>7.9</v>
       </c>
       <c r="I78" t="n">
-        <v>48</v>
+        <v>59.2</v>
       </c>
       <c r="J78" t="n">
-        <v>32</v>
+        <v>16.3</v>
       </c>
       <c r="K78" t="n">
-        <v>60</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="79">
@@ -3952,34 +3951,34 @@
         <v>93</v>
       </c>
       <c r="B79" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C79" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>46.5</v>
       </c>
       <c r="E79" t="n">
-        <v>75</v>
+        <v>25.5</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>46.5</v>
       </c>
       <c r="G79" t="n">
-        <v>22.2</v>
+        <v>23.7</v>
       </c>
       <c r="H79" t="n">
-        <v>25</v>
+        <v>10.8</v>
       </c>
       <c r="I79" t="n">
+        <v>48</v>
+      </c>
+      <c r="J79" t="n">
+        <v>32</v>
+      </c>
+      <c r="K79" t="n">
         <v>60</v>
-      </c>
-      <c r="J79" t="n">
-        <v>20</v>
-      </c>
-      <c r="K79" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="80">
@@ -3987,34 +3986,34 @@
         <v>94</v>
       </c>
       <c r="B80" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C80" t="n">
-        <v>61.4</v>
+        <v>75</v>
       </c>
       <c r="D80" t="n">
-        <v>19.3</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>42.1</v>
+        <v>75</v>
       </c>
       <c r="F80" t="n">
-        <v>19.3</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>19.4</v>
+        <v>22.2</v>
       </c>
       <c r="H80" t="n">
-        <v>12.2</v>
+        <v>25</v>
       </c>
       <c r="I80" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="J80" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="K80" t="n">
-        <v>44.7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="81">
@@ -4022,34 +4021,34 @@
         <v>95</v>
       </c>
       <c r="B81" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C81" t="n">
-        <v>41.3</v>
+        <v>61.4</v>
       </c>
       <c r="D81" t="n">
-        <v>23.7</v>
+        <v>19.3</v>
       </c>
       <c r="E81" t="n">
-        <v>17.6</v>
+        <v>42.1</v>
       </c>
       <c r="F81" t="n">
-        <v>23.7</v>
+        <v>19.3</v>
       </c>
       <c r="G81" t="n">
-        <v>28.9</v>
+        <v>19.4</v>
       </c>
       <c r="H81" t="n">
-        <v>3.6</v>
+        <v>12.2</v>
       </c>
       <c r="I81" t="n">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="J81" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="K81" t="n">
-        <v>26.3</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="82">
@@ -4057,47 +4056,57 @@
         <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="C82" t="n">
-        <v>50</v>
+        <v>41.3</v>
       </c>
       <c r="D82" t="n">
-        <v>50</v>
+        <v>23.7</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="F82" t="n">
-        <v>50</v>
+        <v>23.7</v>
       </c>
       <c r="G82" t="n">
-        <v>100</v>
+        <v>28.9</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82"/>
-      <c r="J82"/>
-      <c r="K82"/>
+        <v>3.6</v>
+      </c>
+      <c r="I82" t="n">
+        <v>75</v>
+      </c>
+      <c r="J82" t="n">
+        <v>25</v>
+      </c>
+      <c r="K82" t="n">
+        <v>26.3</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
+        <v>97</v>
+      </c>
+      <c r="B83" t="s">
         <v>98</v>
       </c>
-      <c r="B83" t="s">
-        <v>97</v>
-      </c>
-      <c r="C83"/>
+      <c r="C83" t="n">
+        <v>50</v>
+      </c>
       <c r="D83" t="n">
         <v>50</v>
       </c>
-      <c r="E83"/>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
       <c r="F83" t="n">
         <v>50</v>
       </c>
       <c r="G83" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -4111,69 +4120,59 @@
         <v>99</v>
       </c>
       <c r="B84" t="s">
-        <v>97</v>
-      </c>
-      <c r="C84" t="n">
-        <v>56.8</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="C84"/>
       <c r="D84" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E84" t="n">
-        <v>50.3</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="E84"/>
       <c r="F84" t="n">
-        <v>6.5</v>
+        <v>50</v>
       </c>
       <c r="G84" t="n">
-        <v>25.9</v>
+        <v>50</v>
       </c>
       <c r="H84" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="I84" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="J84" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="K84" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I84"/>
+      <c r="J84"/>
+      <c r="K84"/>
     </row>
     <row r="85">
       <c r="A85" t="s">
         <v>100</v>
       </c>
       <c r="B85" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>56.8</v>
       </c>
       <c r="D85" t="n">
-        <v>54.5</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="n">
-        <v>-54.5</v>
+        <v>45.7</v>
       </c>
       <c r="F85" t="n">
-        <v>54.5</v>
+        <v>11.1</v>
       </c>
       <c r="G85" t="n">
-        <v>16.7</v>
+        <v>26.7</v>
       </c>
       <c r="H85" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I85" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="J85" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="K85" t="n">
         <v>50</v>
-      </c>
-      <c r="I85" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -4181,28 +4180,28 @@
         <v>101</v>
       </c>
       <c r="B86" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C86" t="n">
-        <v>56.5</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>38.5</v>
+        <v>54.5</v>
       </c>
       <c r="E86" t="n">
-        <v>18</v>
+        <v>-54.5</v>
       </c>
       <c r="F86" t="n">
-        <v>38.5</v>
+        <v>54.5</v>
       </c>
       <c r="G86" t="n">
-        <v>39.5</v>
+        <v>16.7</v>
       </c>
       <c r="H86" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="I86" t="n">
-        <v>54.5</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -4216,34 +4215,34 @@
         <v>102</v>
       </c>
       <c r="B87" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C87" t="n">
-        <v>86.2</v>
+        <v>56.5</v>
       </c>
       <c r="D87" t="n">
-        <v>33.3</v>
+        <v>54.5</v>
       </c>
       <c r="E87" t="n">
-        <v>52.9</v>
+        <v>2</v>
       </c>
       <c r="F87" t="n">
-        <v>33.3</v>
+        <v>54.5</v>
       </c>
       <c r="G87" t="n">
-        <v>43.2</v>
+        <v>37.8</v>
       </c>
       <c r="H87" t="n">
-        <v>14.6</v>
+        <v>4.3</v>
       </c>
       <c r="I87" t="n">
-        <v>52.4</v>
+        <v>53.8</v>
       </c>
       <c r="J87" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>45</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="88">
@@ -4251,34 +4250,34 @@
         <v>103</v>
       </c>
       <c r="B88" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C88" t="n">
-        <v>75.7</v>
+        <v>86.2</v>
       </c>
       <c r="D88" t="n">
         <v>33.3</v>
       </c>
       <c r="E88" t="n">
-        <v>42.4</v>
+        <v>52.9</v>
       </c>
       <c r="F88" t="n">
         <v>33.3</v>
       </c>
       <c r="G88" t="n">
-        <v>19.1</v>
+        <v>43.2</v>
       </c>
       <c r="H88" t="n">
-        <v>7.1</v>
+        <v>14.6</v>
       </c>
       <c r="I88" t="n">
-        <v>41.5</v>
+        <v>52.4</v>
       </c>
       <c r="J88" t="n">
-        <v>22</v>
+        <v>14.3</v>
       </c>
       <c r="K88" t="n">
-        <v>36.6</v>
+        <v>45</v>
       </c>
     </row>
     <row r="89">
@@ -4286,34 +4285,34 @@
         <v>104</v>
       </c>
       <c r="B89" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C89" t="n">
-        <v>68.2</v>
+        <v>75.7</v>
       </c>
       <c r="D89" t="n">
-        <v>16.9</v>
+        <v>33.9</v>
       </c>
       <c r="E89" t="n">
-        <v>51.3</v>
+        <v>41.8</v>
       </c>
       <c r="F89" t="n">
-        <v>16.9</v>
+        <v>33.9</v>
       </c>
       <c r="G89" t="n">
-        <v>29.4</v>
+        <v>18.2</v>
       </c>
       <c r="H89" t="n">
-        <v>22.6</v>
+        <v>6.7</v>
       </c>
       <c r="I89" t="n">
-        <v>26.7</v>
+        <v>43.2</v>
       </c>
       <c r="J89" t="n">
-        <v>33.3</v>
+        <v>20.5</v>
       </c>
       <c r="K89" t="n">
-        <v>39.5</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="90">
@@ -4321,34 +4320,34 @@
         <v>105</v>
       </c>
       <c r="B90" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C90" t="n">
-        <v>67.9</v>
+        <v>68.1</v>
       </c>
       <c r="D90" t="n">
-        <v>31.6</v>
+        <v>16.3</v>
       </c>
       <c r="E90" t="n">
-        <v>36.3</v>
+        <v>51.8</v>
       </c>
       <c r="F90" t="n">
-        <v>31.6</v>
+        <v>16.3</v>
       </c>
       <c r="G90" t="n">
-        <v>24.2</v>
+        <v>28.8</v>
       </c>
       <c r="H90" t="n">
-        <v>9.5</v>
+        <v>22.7</v>
       </c>
       <c r="I90" t="n">
-        <v>38.8</v>
+        <v>27.1</v>
       </c>
       <c r="J90" t="n">
-        <v>30.6</v>
+        <v>35.4</v>
       </c>
       <c r="K90" t="n">
-        <v>49</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="91">
@@ -4356,34 +4355,34 @@
         <v>106</v>
       </c>
       <c r="B91" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C91" t="n">
-        <v>85.7</v>
+        <v>65.5</v>
       </c>
       <c r="D91" t="n">
-        <v>29.8</v>
+        <v>32.6</v>
       </c>
       <c r="E91" t="n">
-        <v>55.9</v>
+        <v>32.9</v>
       </c>
       <c r="F91" t="n">
-        <v>29.8</v>
+        <v>32.6</v>
       </c>
       <c r="G91" t="n">
-        <v>36.8</v>
+        <v>23.2</v>
       </c>
       <c r="H91" t="n">
-        <v>7.9</v>
+        <v>9.1</v>
       </c>
       <c r="I91" t="n">
-        <v>36.4</v>
+        <v>42.3</v>
       </c>
       <c r="J91" t="n">
-        <v>36.4</v>
+        <v>28.8</v>
       </c>
       <c r="K91" t="n">
-        <v>54.5</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="92">
@@ -4391,34 +4390,34 @@
         <v>107</v>
       </c>
       <c r="B92" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C92" t="n">
-        <v>75</v>
+        <v>87.2</v>
       </c>
       <c r="D92" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="E92" t="n">
-        <v>25</v>
+        <v>59.2</v>
       </c>
       <c r="F92" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="G92" t="n">
-        <v>3.3</v>
+        <v>36.9</v>
       </c>
       <c r="H92" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="I92" t="n">
-        <v>45.5</v>
+        <v>37.1</v>
       </c>
       <c r="J92" t="n">
-        <v>18.2</v>
+        <v>37.1</v>
       </c>
       <c r="K92" t="n">
-        <v>36.4</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="93">
@@ -4426,34 +4425,34 @@
         <v>108</v>
       </c>
       <c r="B93" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C93" t="n">
-        <v>48.6</v>
+        <v>75</v>
       </c>
       <c r="D93" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="E93" t="n">
-        <v>20.6</v>
+        <v>25</v>
       </c>
       <c r="F93" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="G93" t="n">
-        <v>34.5</v>
+        <v>3.3</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="I93" t="n">
-        <v>66.7</v>
+        <v>45.5</v>
       </c>
       <c r="J93" t="n">
-        <v>22.2</v>
+        <v>18.2</v>
       </c>
       <c r="K93" t="n">
-        <v>66.7</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="94">
@@ -4461,34 +4460,34 @@
         <v>109</v>
       </c>
       <c r="B94" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C94" t="n">
-        <v>77.4</v>
+        <v>48.6</v>
       </c>
       <c r="D94" t="n">
-        <v>32.8</v>
+        <v>28</v>
       </c>
       <c r="E94" t="n">
-        <v>44.6</v>
+        <v>20.6</v>
       </c>
       <c r="F94" t="n">
-        <v>32.8</v>
+        <v>28</v>
       </c>
       <c r="G94" t="n">
-        <v>36.6</v>
+        <v>34.5</v>
       </c>
       <c r="H94" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>37.1</v>
+        <v>66.7</v>
       </c>
       <c r="J94" t="n">
-        <v>31.4</v>
+        <v>22.2</v>
       </c>
       <c r="K94" t="n">
-        <v>48.6</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="95">
@@ -4496,34 +4495,34 @@
         <v>110</v>
       </c>
       <c r="B95" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C95" t="n">
-        <v>64.4</v>
+        <v>76.4</v>
       </c>
       <c r="D95" t="n">
-        <v>20</v>
+        <v>32.9</v>
       </c>
       <c r="E95" t="n">
-        <v>44.4</v>
+        <v>43.5</v>
       </c>
       <c r="F95" t="n">
-        <v>20</v>
+        <v>32.9</v>
       </c>
       <c r="G95" t="n">
-        <v>16.7</v>
+        <v>36.5</v>
       </c>
       <c r="H95" t="n">
-        <v>7.7</v>
+        <v>4.8</v>
       </c>
       <c r="I95" t="n">
-        <v>36.2</v>
+        <v>38.9</v>
       </c>
       <c r="J95" t="n">
-        <v>24.1</v>
+        <v>30.6</v>
       </c>
       <c r="K95" t="n">
-        <v>41.4</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="96">
@@ -4531,34 +4530,34 @@
         <v>111</v>
       </c>
       <c r="B96" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C96" t="n">
-        <v>61.9</v>
+        <v>65.3</v>
       </c>
       <c r="D96" t="n">
         <v>21.2</v>
       </c>
       <c r="E96" t="n">
-        <v>40.7</v>
+        <v>44.1</v>
       </c>
       <c r="F96" t="n">
         <v>21.2</v>
       </c>
       <c r="G96" t="n">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
       <c r="H96" t="n">
-        <v>10.8</v>
+        <v>8.5</v>
       </c>
       <c r="I96" t="n">
-        <v>35.4</v>
+        <v>38.3</v>
       </c>
       <c r="J96" t="n">
-        <v>27.1</v>
+        <v>23.3</v>
       </c>
       <c r="K96" t="n">
-        <v>43.8</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="97">
@@ -4566,34 +4565,34 @@
         <v>112</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C97" t="n">
-        <v>60.4</v>
+        <v>60</v>
       </c>
       <c r="D97" t="n">
-        <v>16.1</v>
+        <v>22.8</v>
       </c>
       <c r="E97" t="n">
-        <v>44.3</v>
+        <v>37.2</v>
       </c>
       <c r="F97" t="n">
-        <v>16.1</v>
+        <v>22.8</v>
       </c>
       <c r="G97" t="n">
-        <v>18.4</v>
+        <v>17.6</v>
       </c>
       <c r="H97" t="n">
-        <v>11.8</v>
+        <v>10.1</v>
       </c>
       <c r="I97" t="n">
-        <v>57.5</v>
+        <v>37.3</v>
       </c>
       <c r="J97" t="n">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="K97" t="n">
-        <v>56.1</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="98">
@@ -4601,69 +4600,69 @@
         <v>113</v>
       </c>
       <c r="B98" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C98" t="n">
-        <v>53.8</v>
+        <v>60.4</v>
       </c>
       <c r="D98" t="n">
-        <v>53.7</v>
+        <v>16.2</v>
       </c>
       <c r="E98" t="n">
-        <v>0.1</v>
+        <v>44.2</v>
       </c>
       <c r="F98" t="n">
-        <v>53.7</v>
+        <v>16.2</v>
       </c>
       <c r="G98" t="n">
-        <v>26.7</v>
+        <v>19.8</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="I98" t="n">
-        <v>46.7</v>
+        <v>58.5</v>
       </c>
       <c r="J98" t="n">
-        <v>33.3</v>
+        <v>24.4</v>
       </c>
       <c r="K98" t="n">
-        <v>46.7</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
+        <v>114</v>
+      </c>
+      <c r="B99" t="s">
         <v>115</v>
       </c>
-      <c r="B99" t="s">
-        <v>114</v>
-      </c>
       <c r="C99" t="n">
-        <v>100</v>
+        <v>53.8</v>
       </c>
       <c r="D99" t="n">
-        <v>16.7</v>
+        <v>53.7</v>
       </c>
       <c r="E99" t="n">
-        <v>83.3</v>
+        <v>0.1</v>
       </c>
       <c r="F99" t="n">
-        <v>16.7</v>
+        <v>53.7</v>
       </c>
       <c r="G99" t="n">
-        <v>12.5</v>
+        <v>26.7</v>
       </c>
       <c r="H99" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>60</v>
+        <v>46.7</v>
       </c>
       <c r="J99" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="K99" t="n">
-        <v>60</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="100">
@@ -4671,98 +4670,98 @@
         <v>116</v>
       </c>
       <c r="B100" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C100" t="n">
         <v>100</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E100" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100"/>
-      <c r="J100"/>
-      <c r="K100"/>
+        <v>16.7</v>
+      </c>
+      <c r="I100" t="n">
+        <v>60</v>
+      </c>
+      <c r="J100" t="n">
+        <v>20</v>
+      </c>
+      <c r="K100" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
         <v>117</v>
       </c>
       <c r="B101" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C101" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="D101" t="n">
-        <v>23.5</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>43.2</v>
+        <v>100</v>
       </c>
       <c r="F101" t="n">
-        <v>23.5</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="I101" t="n">
-        <v>36</v>
-      </c>
-      <c r="J101" t="n">
-        <v>32</v>
-      </c>
-      <c r="K101" t="n">
-        <v>52.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I101"/>
+      <c r="J101"/>
+      <c r="K101"/>
     </row>
     <row r="102">
       <c r="A102" t="s">
         <v>118</v>
       </c>
       <c r="B102" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C102" t="n">
-        <v>63.9</v>
+        <v>66.7</v>
       </c>
       <c r="D102" t="n">
-        <v>31.4</v>
+        <v>23.5</v>
       </c>
       <c r="E102" t="n">
-        <v>32.5</v>
+        <v>43.2</v>
       </c>
       <c r="F102" t="n">
-        <v>31.4</v>
+        <v>23.5</v>
       </c>
       <c r="G102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="H102" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="I102" t="n">
+        <v>36</v>
+      </c>
+      <c r="J102" t="n">
         <v>32</v>
       </c>
-      <c r="H102" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I102" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="J102" t="n">
-        <v>22.9</v>
-      </c>
       <c r="K102" t="n">
-        <v>37.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="103">
@@ -4770,34 +4769,34 @@
         <v>119</v>
       </c>
       <c r="B103" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C103" t="n">
-        <v>79.3</v>
+        <v>63.9</v>
       </c>
       <c r="D103" t="n">
-        <v>35.4</v>
+        <v>31.4</v>
       </c>
       <c r="E103" t="n">
-        <v>43.9</v>
+        <v>32.5</v>
       </c>
       <c r="F103" t="n">
-        <v>35.4</v>
+        <v>31.4</v>
       </c>
       <c r="G103" t="n">
-        <v>26.2</v>
+        <v>32</v>
       </c>
       <c r="H103" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="I103" t="n">
-        <v>40.4</v>
+        <v>37.1</v>
       </c>
       <c r="J103" t="n">
-        <v>26.3</v>
+        <v>22.9</v>
       </c>
       <c r="K103" t="n">
-        <v>26.8</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="104">
@@ -4805,34 +4804,34 @@
         <v>120</v>
       </c>
       <c r="B104" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C104" t="n">
-        <v>58.3</v>
+        <v>79.3</v>
       </c>
       <c r="D104" t="n">
-        <v>28.3</v>
+        <v>35.4</v>
       </c>
       <c r="E104" t="n">
-        <v>30</v>
+        <v>43.9</v>
       </c>
       <c r="F104" t="n">
-        <v>28.3</v>
+        <v>35.4</v>
       </c>
       <c r="G104" t="n">
-        <v>17.7</v>
+        <v>26.2</v>
       </c>
       <c r="H104" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="I104" t="n">
-        <v>61</v>
+        <v>40.4</v>
       </c>
       <c r="J104" t="n">
-        <v>12.2</v>
+        <v>26.3</v>
       </c>
       <c r="K104" t="n">
-        <v>51.2</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="105">
@@ -4840,34 +4839,34 @@
         <v>121</v>
       </c>
       <c r="B105" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C105" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="D105" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E105" t="n">
+        <v>30</v>
+      </c>
+      <c r="F105" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="G105" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="H105" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I105" t="n">
+        <v>61</v>
+      </c>
+      <c r="J105" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="K105" t="n">
         <v>51.2</v>
-      </c>
-      <c r="D105" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E105" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="F105" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="G105" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H105" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="I105" t="n">
-        <v>60.3</v>
-      </c>
-      <c r="J105" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K105" t="n">
-        <v>24.2</v>
       </c>
     </row>
     <row r="106">
@@ -4875,34 +4874,34 @@
         <v>122</v>
       </c>
       <c r="B106" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C106" t="n">
-        <v>80</v>
+        <v>51.2</v>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>25.7</v>
       </c>
       <c r="E106" t="n">
-        <v>68.9</v>
+        <v>25.5</v>
       </c>
       <c r="F106" t="n">
-        <v>11.1</v>
+        <v>25.7</v>
       </c>
       <c r="G106" t="n">
-        <v>39.5</v>
+        <v>8.6</v>
       </c>
       <c r="H106" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="I106" t="n">
-        <v>63.6</v>
+        <v>60.3</v>
       </c>
       <c r="J106" t="n">
-        <v>9.1</v>
+        <v>14.3</v>
       </c>
       <c r="K106" t="n">
-        <v>45.5</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="107">
@@ -4910,34 +4909,34 @@
         <v>123</v>
       </c>
       <c r="B107" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C107" t="n">
-        <v>73.7</v>
+        <v>80</v>
       </c>
       <c r="D107" t="n">
-        <v>27.3</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="n">
-        <v>46.4</v>
+        <v>68.9</v>
       </c>
       <c r="F107" t="n">
-        <v>27.3</v>
+        <v>11.1</v>
       </c>
       <c r="G107" t="n">
-        <v>19.3</v>
+        <v>39.5</v>
       </c>
       <c r="H107" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="I107" t="n">
-        <v>39.5</v>
+        <v>63.6</v>
       </c>
       <c r="J107" t="n">
-        <v>30.3</v>
+        <v>9.1</v>
       </c>
       <c r="K107" t="n">
-        <v>42.1</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="108">
@@ -4945,34 +4944,34 @@
         <v>124</v>
       </c>
       <c r="B108" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C108" t="n">
-        <v>70</v>
+        <v>73.7</v>
       </c>
       <c r="D108" t="n">
-        <v>26.7</v>
+        <v>27.3</v>
       </c>
       <c r="E108" t="n">
-        <v>43.3</v>
+        <v>46.4</v>
       </c>
       <c r="F108" t="n">
-        <v>26.7</v>
+        <v>27.3</v>
       </c>
       <c r="G108" t="n">
-        <v>14.8</v>
+        <v>19.3</v>
       </c>
       <c r="H108" t="n">
-        <v>12.5</v>
+        <v>6.2</v>
       </c>
       <c r="I108" t="n">
-        <v>60</v>
+        <v>39.5</v>
       </c>
       <c r="J108" t="n">
-        <v>30</v>
+        <v>30.3</v>
       </c>
       <c r="K108" t="n">
-        <v>10</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="109">
@@ -4980,34 +4979,34 @@
         <v>125</v>
       </c>
       <c r="B109" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C109" t="n">
-        <v>60.5</v>
+        <v>70</v>
       </c>
       <c r="D109" t="n">
-        <v>20.8</v>
+        <v>26.7</v>
       </c>
       <c r="E109" t="n">
-        <v>39.7</v>
+        <v>43.3</v>
       </c>
       <c r="F109" t="n">
-        <v>20.8</v>
+        <v>26.7</v>
       </c>
       <c r="G109" t="n">
-        <v>20</v>
+        <v>14.8</v>
       </c>
       <c r="H109" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="I109" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J109" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K109" t="n">
-        <v>52.6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="110">
@@ -5015,34 +5014,34 @@
         <v>126</v>
       </c>
       <c r="B110" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C110" t="n">
-        <v>70.5</v>
+        <v>60.5</v>
       </c>
       <c r="D110" t="n">
-        <v>28.8</v>
+        <v>20.8</v>
       </c>
       <c r="E110" t="n">
-        <v>41.7</v>
+        <v>39.7</v>
       </c>
       <c r="F110" t="n">
-        <v>28.8</v>
+        <v>20.8</v>
       </c>
       <c r="G110" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="H110" t="n">
-        <v>8.6</v>
+        <v>11.8</v>
       </c>
       <c r="I110" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J110" t="n">
-        <v>14.3</v>
+        <v>25</v>
       </c>
       <c r="K110" t="n">
-        <v>38</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="111">
@@ -5050,34 +5049,34 @@
         <v>127</v>
       </c>
       <c r="B111" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C111" t="n">
-        <v>74.7</v>
+        <v>70.5</v>
       </c>
       <c r="D111" t="n">
-        <v>25.4</v>
+        <v>28.8</v>
       </c>
       <c r="E111" t="n">
-        <v>49.3</v>
+        <v>41.7</v>
       </c>
       <c r="F111" t="n">
-        <v>25.4</v>
+        <v>28.8</v>
       </c>
       <c r="G111" t="n">
-        <v>29.2</v>
+        <v>34</v>
       </c>
       <c r="H111" t="n">
-        <v>10.1</v>
+        <v>8.6</v>
       </c>
       <c r="I111" t="n">
-        <v>41.1</v>
+        <v>51</v>
       </c>
       <c r="J111" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
       <c r="K111" t="n">
-        <v>47.3</v>
+        <v>38</v>
       </c>
     </row>
     <row r="112">
@@ -5085,34 +5084,34 @@
         <v>128</v>
       </c>
       <c r="B112" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C112" t="n">
-        <v>73.6</v>
+        <v>74.7</v>
       </c>
       <c r="D112" t="n">
-        <v>29.1</v>
+        <v>25.4</v>
       </c>
       <c r="E112" t="n">
-        <v>44.5</v>
+        <v>49.3</v>
       </c>
       <c r="F112" t="n">
-        <v>29.1</v>
+        <v>25.4</v>
       </c>
       <c r="G112" t="n">
-        <v>24.3</v>
+        <v>29.2</v>
       </c>
       <c r="H112" t="n">
-        <v>8.9</v>
+        <v>10.1</v>
       </c>
       <c r="I112" t="n">
-        <v>40.3</v>
+        <v>41.1</v>
       </c>
       <c r="J112" t="n">
-        <v>35.5</v>
+        <v>25</v>
       </c>
       <c r="K112" t="n">
-        <v>51.6</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="113">
@@ -5120,34 +5119,34 @@
         <v>129</v>
       </c>
       <c r="B113" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C113" t="n">
-        <v>69.7</v>
+        <v>73.6</v>
       </c>
       <c r="D113" t="n">
-        <v>23.8</v>
+        <v>29.1</v>
       </c>
       <c r="E113" t="n">
-        <v>45.9</v>
+        <v>44.5</v>
       </c>
       <c r="F113" t="n">
-        <v>23.8</v>
+        <v>29.1</v>
       </c>
       <c r="G113" t="n">
-        <v>16.7</v>
+        <v>24.3</v>
       </c>
       <c r="H113" t="n">
-        <v>15.4</v>
+        <v>8.9</v>
       </c>
       <c r="I113" t="n">
-        <v>47.1</v>
+        <v>40.3</v>
       </c>
       <c r="J113" t="n">
-        <v>5.9</v>
+        <v>35.5</v>
       </c>
       <c r="K113" t="n">
-        <v>35.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="114">
@@ -5155,63 +5154,63 @@
         <v>130</v>
       </c>
       <c r="B114" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="C114" t="n">
-        <v>100</v>
-      </c>
-      <c r="D114"/>
-      <c r="E114"/>
-      <c r="F114"/>
+        <v>69.7</v>
+      </c>
+      <c r="D114" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E114" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="F114" t="n">
+        <v>23.8</v>
+      </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>47.1</v>
       </c>
       <c r="J114" t="n">
-        <v>100</v>
+        <v>5.9</v>
       </c>
       <c r="K114" t="n">
-        <v>0</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
+        <v>131</v>
+      </c>
+      <c r="B115" t="s">
         <v>132</v>
-      </c>
-      <c r="B115" t="s">
-        <v>131</v>
       </c>
       <c r="C115" t="n">
         <v>100</v>
       </c>
-      <c r="D115" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="E115" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="F115" t="n">
-        <v>57.1</v>
-      </c>
+      <c r="D115"/>
+      <c r="E115"/>
+      <c r="F115"/>
       <c r="G115" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K115" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -5219,34 +5218,34 @@
         <v>133</v>
       </c>
       <c r="B116" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C116" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="D116" t="n">
-        <v>60</v>
+        <v>57.1</v>
       </c>
       <c r="E116" t="n">
-        <v>6.7</v>
+        <v>42.9</v>
       </c>
       <c r="F116" t="n">
-        <v>60</v>
+        <v>57.1</v>
       </c>
       <c r="G116" t="n">
-        <v>33.3</v>
+        <v>22.2</v>
       </c>
       <c r="H116" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I116" t="n">
         <v>25</v>
       </c>
       <c r="J116" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="117">
@@ -5254,34 +5253,34 @@
         <v>134</v>
       </c>
       <c r="B117" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C117" t="n">
-        <v>60.4</v>
+        <v>66.7</v>
       </c>
       <c r="D117" t="n">
+        <v>60</v>
+      </c>
+      <c r="E117" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F117" t="n">
+        <v>60</v>
+      </c>
+      <c r="G117" t="n">
         <v>33.3</v>
       </c>
-      <c r="E117" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="F117" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G117" t="n">
-        <v>13.1</v>
-      </c>
       <c r="H117" t="n">
-        <v>7.7</v>
+        <v>11.1</v>
       </c>
       <c r="I117" t="n">
-        <v>51.9</v>
+        <v>25</v>
       </c>
       <c r="J117" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="K117" t="n">
-        <v>42.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -5289,34 +5288,34 @@
         <v>135</v>
       </c>
       <c r="B118" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C118" t="n">
-        <v>35</v>
+        <v>60.4</v>
       </c>
       <c r="D118" t="n">
-        <v>13.3</v>
+        <v>33.3</v>
       </c>
       <c r="E118" t="n">
-        <v>21.7</v>
+        <v>27.1</v>
       </c>
       <c r="F118" t="n">
-        <v>13.3</v>
+        <v>33.3</v>
       </c>
       <c r="G118" t="n">
-        <v>33.3</v>
+        <v>13.1</v>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="I118" t="n">
-        <v>50</v>
+        <v>51.9</v>
       </c>
       <c r="J118" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="K118" t="n">
-        <v>0</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="119">
@@ -5324,34 +5323,34 @@
         <v>136</v>
       </c>
       <c r="B119" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C119" t="n">
-        <v>69.6</v>
+        <v>35</v>
       </c>
       <c r="D119" t="n">
-        <v>31.4</v>
+        <v>13.3</v>
       </c>
       <c r="E119" t="n">
-        <v>38.2</v>
+        <v>21.7</v>
       </c>
       <c r="F119" t="n">
-        <v>31.4</v>
+        <v>13.3</v>
       </c>
       <c r="G119" t="n">
-        <v>40.6</v>
+        <v>33.3</v>
       </c>
       <c r="H119" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J119" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -5359,34 +5358,34 @@
         <v>137</v>
       </c>
       <c r="B120" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C120" t="n">
-        <v>70.4</v>
+        <v>69.6</v>
       </c>
       <c r="D120" t="n">
-        <v>28.2</v>
+        <v>31.4</v>
       </c>
       <c r="E120" t="n">
-        <v>42.2</v>
+        <v>38.2</v>
       </c>
       <c r="F120" t="n">
-        <v>28.2</v>
+        <v>31.4</v>
       </c>
       <c r="G120" t="n">
-        <v>36.6</v>
+        <v>40.6</v>
       </c>
       <c r="H120" t="n">
-        <v>8.3</v>
+        <v>16.7</v>
       </c>
       <c r="I120" t="n">
-        <v>33.3</v>
+        <v>80</v>
       </c>
       <c r="J120" t="n">
-        <v>33.3</v>
+        <v>10</v>
       </c>
       <c r="K120" t="n">
-        <v>37.9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="121">
@@ -5394,34 +5393,34 @@
         <v>138</v>
       </c>
       <c r="B121" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C121" t="n">
-        <v>60.6</v>
+        <v>70.4</v>
       </c>
       <c r="D121" t="n">
-        <v>25.6</v>
+        <v>28.2</v>
       </c>
       <c r="E121" t="n">
-        <v>35</v>
+        <v>42.2</v>
       </c>
       <c r="F121" t="n">
-        <v>25.6</v>
+        <v>28.2</v>
       </c>
       <c r="G121" t="n">
-        <v>19</v>
+        <v>36.6</v>
       </c>
       <c r="H121" t="n">
-        <v>9.3</v>
+        <v>8.3</v>
       </c>
       <c r="I121" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
       <c r="J121" t="n">
-        <v>14.3</v>
+        <v>33.3</v>
       </c>
       <c r="K121" t="n">
-        <v>34.3</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="122">
@@ -5429,34 +5428,34 @@
         <v>139</v>
       </c>
       <c r="B122" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C122" t="n">
-        <v>66.7</v>
+        <v>60.6</v>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
+        <v>25.6</v>
       </c>
       <c r="E122" t="n">
-        <v>66.7</v>
+        <v>35</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>25.6</v>
       </c>
       <c r="G122" t="n">
-        <v>18.2</v>
+        <v>19</v>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>9.3</v>
       </c>
       <c r="I122" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="J122" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
       <c r="K122" t="n">
-        <v>0</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="123">
@@ -5464,34 +5463,34 @@
         <v>140</v>
       </c>
       <c r="B123" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C123" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="D123" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E123" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="F123" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>38.5</v>
+        <v>18.2</v>
       </c>
       <c r="H123" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K123" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -5499,34 +5498,34 @@
         <v>141</v>
       </c>
       <c r="B124" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C124" t="n">
-        <v>51.9</v>
+        <v>60</v>
       </c>
       <c r="D124" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E124" t="n">
-        <v>36.9</v>
+        <v>40</v>
       </c>
       <c r="F124" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G124" t="n">
-        <v>30</v>
+        <v>38.5</v>
       </c>
       <c r="H124" t="n">
-        <v>13.3</v>
+        <v>11.8</v>
       </c>
       <c r="I124" t="n">
-        <v>71.4</v>
+        <v>90</v>
       </c>
       <c r="J124" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>57.1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="125">
@@ -5534,34 +5533,34 @@
         <v>142</v>
       </c>
       <c r="B125" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C125" t="n">
-        <v>63.6</v>
+        <v>51.9</v>
       </c>
       <c r="D125" t="n">
-        <v>26.3</v>
+        <v>15</v>
       </c>
       <c r="E125" t="n">
-        <v>37.3</v>
+        <v>36.9</v>
       </c>
       <c r="F125" t="n">
-        <v>26.3</v>
+        <v>15</v>
       </c>
       <c r="G125" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H125" t="n">
-        <v>8.1</v>
+        <v>13.3</v>
       </c>
       <c r="I125" t="n">
-        <v>36.1</v>
+        <v>71.4</v>
       </c>
       <c r="J125" t="n">
-        <v>25</v>
+        <v>28.6</v>
       </c>
       <c r="K125" t="n">
-        <v>55.6</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="126">
@@ -5569,34 +5568,34 @@
         <v>143</v>
       </c>
       <c r="B126" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C126" t="n">
-        <v>100</v>
+        <v>63.6</v>
       </c>
       <c r="D126" t="n">
-        <v>33.3</v>
+        <v>26.3</v>
       </c>
       <c r="E126" t="n">
-        <v>66.7</v>
+        <v>37.3</v>
       </c>
       <c r="F126" t="n">
-        <v>33.3</v>
+        <v>26.3</v>
       </c>
       <c r="G126" t="n">
-        <v>11.1</v>
+        <v>28</v>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="I126" t="n">
-        <v>20</v>
+        <v>36.1</v>
       </c>
       <c r="J126" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="K126" t="n">
-        <v>20</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="127">
@@ -5604,34 +5603,34 @@
         <v>144</v>
       </c>
       <c r="B127" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C127" t="n">
-        <v>64.4</v>
+        <v>100</v>
       </c>
       <c r="D127" t="n">
-        <v>27</v>
+        <v>33.3</v>
       </c>
       <c r="E127" t="n">
-        <v>37.4</v>
+        <v>66.7</v>
       </c>
       <c r="F127" t="n">
-        <v>27</v>
+        <v>33.3</v>
       </c>
       <c r="G127" t="n">
-        <v>21.4</v>
+        <v>11.1</v>
       </c>
       <c r="H127" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>61.9</v>
+        <v>20</v>
       </c>
       <c r="J127" t="n">
-        <v>21.4</v>
+        <v>40</v>
       </c>
       <c r="K127" t="n">
-        <v>31.7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="128">
@@ -5639,34 +5638,34 @@
         <v>145</v>
       </c>
       <c r="B128" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C128" t="n">
-        <v>100</v>
+        <v>64.4</v>
       </c>
       <c r="D128" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E128" t="n">
-        <v>80</v>
+        <v>37.4</v>
       </c>
       <c r="F128" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="I128" t="n">
-        <v>50</v>
+        <v>61.9</v>
       </c>
       <c r="J128" t="n">
-        <v>25</v>
+        <v>21.4</v>
       </c>
       <c r="K128" t="n">
-        <v>0</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="129">
@@ -5674,34 +5673,34 @@
         <v>146</v>
       </c>
       <c r="B129" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C129" t="n">
-        <v>53.6</v>
+        <v>100</v>
       </c>
       <c r="D129" t="n">
-        <v>24.4</v>
+        <v>20</v>
       </c>
       <c r="E129" t="n">
-        <v>29.2</v>
+        <v>80</v>
       </c>
       <c r="F129" t="n">
-        <v>24.4</v>
+        <v>20</v>
       </c>
       <c r="G129" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>39.4</v>
+        <v>50</v>
       </c>
       <c r="J129" t="n">
-        <v>27.3</v>
+        <v>25</v>
       </c>
       <c r="K129" t="n">
-        <v>45.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -5709,34 +5708,34 @@
         <v>147</v>
       </c>
       <c r="B130" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C130" t="n">
-        <v>78.6</v>
+        <v>53.6</v>
       </c>
       <c r="D130" t="n">
-        <v>12.5</v>
+        <v>24.4</v>
       </c>
       <c r="E130" t="n">
-        <v>66.1</v>
+        <v>29.2</v>
       </c>
       <c r="F130" t="n">
-        <v>12.5</v>
+        <v>24.4</v>
       </c>
       <c r="G130" t="n">
-        <v>35.3</v>
+        <v>24</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>28.6</v>
+        <v>39.4</v>
       </c>
       <c r="J130" t="n">
-        <v>14.3</v>
+        <v>27.3</v>
       </c>
       <c r="K130" t="n">
-        <v>14.3</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="131">
@@ -5744,34 +5743,34 @@
         <v>148</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C131" t="n">
-        <v>59.3</v>
+        <v>78.6</v>
       </c>
       <c r="D131" t="n">
-        <v>7.1</v>
+        <v>12.5</v>
       </c>
       <c r="E131" t="n">
-        <v>52.2</v>
+        <v>66.1</v>
       </c>
       <c r="F131" t="n">
-        <v>7.1</v>
+        <v>12.5</v>
       </c>
       <c r="G131" t="n">
-        <v>5.8</v>
+        <v>35.3</v>
       </c>
       <c r="H131" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="J131" t="n">
-        <v>11.1</v>
+        <v>14.3</v>
       </c>
       <c r="K131" t="n">
-        <v>35.3</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="132">
@@ -5779,34 +5778,34 @@
         <v>149</v>
       </c>
       <c r="B132" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C132" t="n">
-        <v>63.2</v>
+        <v>59.3</v>
       </c>
       <c r="D132" t="n">
-        <v>45</v>
+        <v>7.1</v>
       </c>
       <c r="E132" t="n">
-        <v>18.2</v>
+        <v>52.2</v>
       </c>
       <c r="F132" t="n">
-        <v>45</v>
+        <v>7.1</v>
       </c>
       <c r="G132" t="n">
-        <v>26.9</v>
+        <v>5.8</v>
       </c>
       <c r="H132" t="n">
-        <v>7.7</v>
+        <v>8.3</v>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J132" t="n">
-        <v>25</v>
+        <v>11.1</v>
       </c>
       <c r="K132" t="n">
-        <v>25</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="133">
@@ -5814,34 +5813,34 @@
         <v>150</v>
       </c>
       <c r="B133" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C133" t="n">
-        <v>74.7</v>
+        <v>63.2</v>
       </c>
       <c r="D133" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="E133" t="n">
-        <v>58.7</v>
+        <v>18.2</v>
       </c>
       <c r="F133" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G133" t="n">
-        <v>25.5</v>
+        <v>26.9</v>
       </c>
       <c r="H133" t="n">
-        <v>16.9</v>
+        <v>7.7</v>
       </c>
       <c r="I133" t="n">
-        <v>27.5</v>
+        <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>42.5</v>
+        <v>25</v>
       </c>
       <c r="K133" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="134">
@@ -5849,34 +5848,34 @@
         <v>151</v>
       </c>
       <c r="B134" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C134" t="n">
-        <v>74.4</v>
+        <v>74.7</v>
       </c>
       <c r="D134" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="E134" t="n">
-        <v>43.4</v>
+        <v>58.7</v>
       </c>
       <c r="F134" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G134" t="n">
-        <v>10.5</v>
+        <v>25.5</v>
       </c>
       <c r="H134" t="n">
-        <v>1.6</v>
+        <v>16.9</v>
       </c>
       <c r="I134" t="n">
-        <v>44.4</v>
+        <v>27.5</v>
       </c>
       <c r="J134" t="n">
-        <v>25.9</v>
+        <v>42.5</v>
       </c>
       <c r="K134" t="n">
-        <v>35.2</v>
+        <v>40</v>
       </c>
     </row>
     <row r="135">
@@ -5884,69 +5883,69 @@
         <v>152</v>
       </c>
       <c r="B135" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="C135" t="n">
-        <v>71.4</v>
+        <v>74.4</v>
       </c>
       <c r="D135" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E135" t="n">
-        <v>51.4</v>
+        <v>43.4</v>
       </c>
       <c r="F135" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G135" t="n">
-        <v>33</v>
+        <v>10.5</v>
       </c>
       <c r="H135" t="n">
-        <v>11.8</v>
+        <v>1.6</v>
       </c>
       <c r="I135" t="n">
-        <v>52.4</v>
+        <v>44.4</v>
       </c>
       <c r="J135" t="n">
-        <v>19</v>
+        <v>25.9</v>
       </c>
       <c r="K135" t="n">
-        <v>38.9</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
+        <v>153</v>
+      </c>
+      <c r="B136" t="s">
         <v>154</v>
       </c>
-      <c r="B136" t="s">
-        <v>153</v>
-      </c>
       <c r="C136" t="n">
-        <v>69.6</v>
+        <v>73.4</v>
       </c>
       <c r="D136" t="n">
-        <v>25.5</v>
+        <v>22.6</v>
       </c>
       <c r="E136" t="n">
-        <v>44.1</v>
+        <v>50.8</v>
       </c>
       <c r="F136" t="n">
-        <v>25.5</v>
+        <v>22.6</v>
       </c>
       <c r="G136" t="n">
-        <v>17.1</v>
+        <v>33</v>
       </c>
       <c r="H136" t="n">
-        <v>5.5</v>
+        <v>9.7</v>
       </c>
       <c r="I136" t="n">
-        <v>56.2</v>
+        <v>53.8</v>
       </c>
       <c r="J136" t="n">
-        <v>16.7</v>
+        <v>20.5</v>
       </c>
       <c r="K136" t="n">
-        <v>36.4</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="137">
@@ -5954,34 +5953,34 @@
         <v>155</v>
       </c>
       <c r="B137" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C137" t="n">
-        <v>64.6</v>
+        <v>69.6</v>
       </c>
       <c r="D137" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E137" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="F137" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G137" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="H137" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I137" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="J137" t="n">
         <v>16.7</v>
       </c>
-      <c r="E137" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="F137" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="G137" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="H137" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I137" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="J137" t="n">
-        <v>48.1</v>
-      </c>
       <c r="K137" t="n">
-        <v>38.5</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="138">
@@ -5989,34 +5988,34 @@
         <v>156</v>
       </c>
       <c r="B138" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C138" t="n">
-        <v>59</v>
+        <v>64.6</v>
       </c>
       <c r="D138" t="n">
-        <v>20.3</v>
+        <v>16.7</v>
       </c>
       <c r="E138" t="n">
-        <v>38.7</v>
+        <v>47.9</v>
       </c>
       <c r="F138" t="n">
-        <v>20.3</v>
+        <v>16.7</v>
       </c>
       <c r="G138" t="n">
-        <v>38.1</v>
+        <v>37.7</v>
       </c>
       <c r="H138" t="n">
-        <v>15.6</v>
+        <v>12.5</v>
       </c>
       <c r="I138" t="n">
-        <v>18.8</v>
+        <v>29.6</v>
       </c>
       <c r="J138" t="n">
-        <v>50</v>
+        <v>48.1</v>
       </c>
       <c r="K138" t="n">
-        <v>21.4</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="139">
@@ -6024,34 +6023,34 @@
         <v>157</v>
       </c>
       <c r="B139" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C139" t="n">
-        <v>64.4</v>
+        <v>57.9</v>
       </c>
       <c r="D139" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E139" t="n">
-        <v>47.4</v>
+        <v>37.9</v>
       </c>
       <c r="F139" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G139" t="n">
-        <v>10.7</v>
+        <v>40</v>
       </c>
       <c r="H139" t="n">
-        <v>17</v>
+        <v>16.7</v>
       </c>
       <c r="I139" t="n">
-        <v>63.4</v>
+        <v>21.4</v>
       </c>
       <c r="J139" t="n">
-        <v>18.3</v>
+        <v>50</v>
       </c>
       <c r="K139" t="n">
-        <v>37.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="140">
@@ -6059,34 +6058,34 @@
         <v>158</v>
       </c>
       <c r="B140" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C140" t="n">
-        <v>81.6</v>
+        <v>64.7</v>
       </c>
       <c r="D140" t="n">
-        <v>22.6</v>
+        <v>17.2</v>
       </c>
       <c r="E140" t="n">
-        <v>59</v>
+        <v>47.5</v>
       </c>
       <c r="F140" t="n">
-        <v>22.6</v>
+        <v>17.2</v>
       </c>
       <c r="G140" t="n">
-        <v>21.5</v>
+        <v>10.7</v>
       </c>
       <c r="H140" t="n">
-        <v>11</v>
+        <v>18.1</v>
       </c>
       <c r="I140" t="n">
-        <v>35.3</v>
+        <v>64.6</v>
       </c>
       <c r="J140" t="n">
-        <v>35.3</v>
+        <v>18.5</v>
       </c>
       <c r="K140" t="n">
-        <v>36.5</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="141">
@@ -6094,34 +6093,34 @@
         <v>159</v>
       </c>
       <c r="B141" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C141" t="n">
-        <v>51.8</v>
+        <v>81</v>
       </c>
       <c r="D141" t="n">
-        <v>21.2</v>
+        <v>23.3</v>
       </c>
       <c r="E141" t="n">
-        <v>30.6</v>
+        <v>57.7</v>
       </c>
       <c r="F141" t="n">
-        <v>21.2</v>
+        <v>23.3</v>
       </c>
       <c r="G141" t="n">
-        <v>23.6</v>
+        <v>22.1</v>
       </c>
       <c r="H141" t="n">
-        <v>13.9</v>
+        <v>10.6</v>
       </c>
       <c r="I141" t="n">
-        <v>48.8</v>
+        <v>34.9</v>
       </c>
       <c r="J141" t="n">
-        <v>22</v>
+        <v>34.9</v>
       </c>
       <c r="K141" t="n">
-        <v>29.7</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="142">
@@ -6129,34 +6128,34 @@
         <v>160</v>
       </c>
       <c r="B142" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C142" t="n">
-        <v>56</v>
+        <v>53.5</v>
       </c>
       <c r="D142" t="n">
-        <v>21.4</v>
+        <v>20.5</v>
       </c>
       <c r="E142" t="n">
-        <v>34.6</v>
+        <v>33</v>
       </c>
       <c r="F142" t="n">
-        <v>21.4</v>
+        <v>20.5</v>
       </c>
       <c r="G142" t="n">
-        <v>12.5</v>
+        <v>23.5</v>
       </c>
       <c r="H142" t="n">
-        <v>15.9</v>
+        <v>13.9</v>
       </c>
       <c r="I142" t="n">
-        <v>44.9</v>
+        <v>51.3</v>
       </c>
       <c r="J142" t="n">
-        <v>26.5</v>
+        <v>23.1</v>
       </c>
       <c r="K142" t="n">
-        <v>53.5</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="143">
@@ -6164,34 +6163,34 @@
         <v>161</v>
       </c>
       <c r="B143" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C143" t="n">
-        <v>58.4</v>
+        <v>54</v>
       </c>
       <c r="D143" t="n">
-        <v>22.2</v>
+        <v>21.2</v>
       </c>
       <c r="E143" t="n">
-        <v>36.2</v>
+        <v>32.8</v>
       </c>
       <c r="F143" t="n">
-        <v>22.2</v>
+        <v>21.2</v>
       </c>
       <c r="G143" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="H143" t="n">
-        <v>8.4</v>
+        <v>17.7</v>
       </c>
       <c r="I143" t="n">
-        <v>58</v>
+        <v>43.2</v>
       </c>
       <c r="J143" t="n">
-        <v>18.5</v>
+        <v>27.3</v>
       </c>
       <c r="K143" t="n">
-        <v>31.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="144">
@@ -6199,34 +6198,34 @@
         <v>162</v>
       </c>
       <c r="B144" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C144" t="n">
-        <v>72.3</v>
+        <v>57.8</v>
       </c>
       <c r="D144" t="n">
-        <v>16.2</v>
+        <v>23</v>
       </c>
       <c r="E144" t="n">
-        <v>56.1</v>
+        <v>34.8</v>
       </c>
       <c r="F144" t="n">
-        <v>16.2</v>
+        <v>23</v>
       </c>
       <c r="G144" t="n">
-        <v>28.6</v>
+        <v>9.5</v>
       </c>
       <c r="H144" t="n">
-        <v>14.7</v>
+        <v>7.9</v>
       </c>
       <c r="I144" t="n">
-        <v>30</v>
+        <v>59.2</v>
       </c>
       <c r="J144" t="n">
-        <v>35</v>
+        <v>18.4</v>
       </c>
       <c r="K144" t="n">
-        <v>57.7</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="145">
@@ -6234,34 +6233,34 @@
         <v>163</v>
       </c>
       <c r="B145" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C145" t="n">
-        <v>74</v>
+        <v>72.6</v>
       </c>
       <c r="D145" t="n">
-        <v>35.7</v>
+        <v>17.5</v>
       </c>
       <c r="E145" t="n">
-        <v>38.3</v>
+        <v>55.1</v>
       </c>
       <c r="F145" t="n">
-        <v>35.7</v>
+        <v>17.5</v>
       </c>
       <c r="G145" t="n">
-        <v>42.3</v>
+        <v>27.3</v>
       </c>
       <c r="H145" t="n">
         <v>13.5</v>
       </c>
       <c r="I145" t="n">
-        <v>46.2</v>
+        <v>30.5</v>
       </c>
       <c r="J145" t="n">
-        <v>7.7</v>
+        <v>33.9</v>
       </c>
       <c r="K145" t="n">
-        <v>69.2</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="146">
@@ -6269,34 +6268,34 @@
         <v>164</v>
       </c>
       <c r="B146" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C146" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="D146" t="n">
-        <v>23.5</v>
+        <v>40</v>
       </c>
       <c r="E146" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="F146" t="n">
-        <v>23.5</v>
+        <v>40</v>
       </c>
       <c r="G146" t="n">
-        <v>19</v>
+        <v>42.5</v>
       </c>
       <c r="H146" t="n">
-        <v>7.6</v>
+        <v>8.8</v>
       </c>
       <c r="I146" t="n">
-        <v>32.3</v>
+        <v>46.2</v>
       </c>
       <c r="J146" t="n">
-        <v>30.8</v>
+        <v>7.7</v>
       </c>
       <c r="K146" t="n">
-        <v>45.6</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="147">
@@ -6304,51 +6303,57 @@
         <v>165</v>
       </c>
       <c r="B147" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C147" t="n">
-        <v>33.3</v>
+        <v>75</v>
       </c>
       <c r="D147" t="n">
-        <v>25</v>
+        <v>24.3</v>
       </c>
       <c r="E147" t="n">
-        <v>8.3</v>
+        <v>50.7</v>
       </c>
       <c r="F147" t="n">
-        <v>25</v>
+        <v>24.3</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>17.3</v>
       </c>
       <c r="H147" t="n">
-        <v>0</v>
-      </c>
-      <c r="I147"/>
-      <c r="J147"/>
-      <c r="K147"/>
+        <v>8</v>
+      </c>
+      <c r="I147" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="J147" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="K147" t="n">
+        <v>44.4</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
         <v>166</v>
       </c>
       <c r="B148" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="D148" t="n">
         <v>33.3</v>
       </c>
       <c r="E148" t="n">
-        <v>-33.3</v>
+        <v>4.2</v>
       </c>
       <c r="F148" t="n">
         <v>33.3</v>
       </c>
       <c r="G148" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -6358,36 +6363,65 @@
       <c r="K148"/>
     </row>
     <row r="149">
-      <c r="A149"/>
+      <c r="A149" t="s">
+        <v>167</v>
+      </c>
       <c r="B149" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="C149" t="n">
-        <v>68.5</v>
+        <v>0</v>
       </c>
       <c r="D149" t="n">
-        <v>25.7</v>
+        <v>33.3</v>
       </c>
       <c r="E149" t="n">
-        <v>42.4</v>
+        <v>-33.3</v>
       </c>
       <c r="F149" t="n">
-        <v>25.7</v>
+        <v>33.3</v>
       </c>
       <c r="G149" t="n">
-        <v>26.4</v>
+        <v>100</v>
       </c>
       <c r="H149" t="n">
-        <v>9.7</v>
-      </c>
-      <c r="I149" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149"/>
+      <c r="J149"/>
+      <c r="K149"/>
+    </row>
+    <row r="150">
+      <c r="A150"/>
+      <c r="B150" t="s">
+        <v>168</v>
+      </c>
+      <c r="C150" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="D150" t="n">
+        <v>27</v>
+      </c>
+      <c r="E150" t="n">
+        <v>41</v>
+      </c>
+      <c r="F150" t="n">
+        <v>27</v>
+      </c>
+      <c r="G150" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="H150" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I150" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="J150" t="n">
         <v>24.2</v>
       </c>
-      <c r="K149" t="n">
-        <v>38.6</v>
+      <c r="K150" t="n">
+        <v>39.2</v>
       </c>
     </row>
   </sheetData>
@@ -6419,22 +6453,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -6443,18 +6477,18 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -6524,7 +6558,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -6559,7 +6593,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -6594,7 +6628,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -6629,7 +6663,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -6664,7 +6698,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -6734,7 +6768,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
@@ -6769,7 +6803,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -6804,7 +6838,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -6839,7 +6873,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -6907,7 +6941,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
@@ -6942,42 +6976,42 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s">
         <v>31</v>
       </c>
       <c r="C16" t="n">
-        <v>53.7</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>51.7</v>
+        <v>53.5</v>
       </c>
       <c r="E16" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="F16" t="n">
-        <v>34.8</v>
+        <v>38.5</v>
       </c>
       <c r="G16" t="n">
-        <v>34.1</v>
+        <v>29.8</v>
       </c>
       <c r="H16" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
-        <v>28.6</v>
+        <v>27.1</v>
       </c>
       <c r="K16" t="n">
-        <v>-14.6</v>
+        <v>-8.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s">
         <v>31</v>
@@ -7012,7 +7046,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
@@ -7047,7 +7081,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B19" t="s">
         <v>31</v>
@@ -7082,7 +7116,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B20" t="s">
         <v>31</v>
@@ -7117,42 +7151,42 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B21" t="s">
         <v>31</v>
       </c>
       <c r="C21" t="n">
-        <v>58.2</v>
+        <v>57</v>
       </c>
       <c r="D21" t="n">
-        <v>63</v>
+        <v>62.2</v>
       </c>
       <c r="E21" t="n">
-        <v>10.9</v>
+        <v>19.4</v>
       </c>
       <c r="F21" t="n">
-        <v>47.2</v>
+        <v>44.2</v>
       </c>
       <c r="G21" t="n">
-        <v>14.9</v>
+        <v>15.2</v>
       </c>
       <c r="H21" t="n">
-        <v>54.5</v>
+        <v>51.2</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>34.4</v>
+        <v>34</v>
       </c>
       <c r="K21" t="n">
-        <v>10.5</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B22" t="s">
         <v>31</v>
@@ -7187,7 +7221,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B23" t="s">
         <v>31</v>
@@ -7222,42 +7256,42 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
       </c>
       <c r="C24" t="n">
-        <v>53.7</v>
+        <v>52.5</v>
       </c>
       <c r="D24" t="n">
-        <v>63.8</v>
+        <v>64</v>
       </c>
       <c r="E24" t="n">
-        <v>31.3</v>
+        <v>34.4</v>
       </c>
       <c r="F24" t="n">
-        <v>34.8</v>
+        <v>33.3</v>
       </c>
       <c r="G24" t="n">
-        <v>9.3</v>
+        <v>8.2</v>
       </c>
       <c r="H24" t="n">
-        <v>56.4</v>
+        <v>55.6</v>
       </c>
       <c r="I24" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J24" t="n">
-        <v>22.8</v>
+        <v>20.4</v>
       </c>
       <c r="K24" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
@@ -7292,42 +7326,42 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B26" t="s">
         <v>31</v>
       </c>
       <c r="C26" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D26" t="n">
-        <v>56.3</v>
+        <v>58.2</v>
       </c>
       <c r="E26" t="n">
-        <v>29.1</v>
+        <v>32.8</v>
       </c>
       <c r="F26" t="n">
-        <v>21.4</v>
+        <v>18.8</v>
       </c>
       <c r="G26" t="n">
-        <v>16.1</v>
+        <v>13.7</v>
       </c>
       <c r="H26" t="n">
-        <v>44.2</v>
+        <v>42.6</v>
       </c>
       <c r="I26" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="J26" t="n">
-        <v>22.2</v>
+        <v>25.9</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.8</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B27" t="s">
         <v>31</v>
@@ -7362,7 +7396,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B28" t="s">
         <v>31</v>
@@ -7397,7 +7431,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B29" t="s">
         <v>46</v>
@@ -7432,37 +7466,37 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B30" t="s">
         <v>46</v>
       </c>
       <c r="C30" t="n">
-        <v>57.8</v>
+        <v>55.6</v>
       </c>
       <c r="D30" t="n">
-        <v>55.5</v>
+        <v>57.6</v>
       </c>
       <c r="E30" t="n">
-        <v>13.6</v>
+        <v>17.1</v>
       </c>
       <c r="F30" t="n">
-        <v>37.5</v>
+        <v>32.1</v>
       </c>
       <c r="G30" t="n">
-        <v>13</v>
+        <v>10.9</v>
       </c>
       <c r="H30" t="n">
-        <v>53.3</v>
+        <v>48.7</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>26.9</v>
+        <v>23.9</v>
       </c>
       <c r="K30" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="31">
@@ -7502,7 +7536,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B32" t="s">
         <v>46</v>
@@ -7537,7 +7571,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B33" t="s">
         <v>46</v>
@@ -7572,7 +7606,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B34" t="s">
         <v>46</v>
@@ -7607,7 +7641,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B35" t="s">
         <v>46</v>
@@ -7640,42 +7674,42 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B36" t="s">
         <v>46</v>
       </c>
       <c r="C36" t="n">
-        <v>68.1</v>
+        <v>67.6</v>
       </c>
       <c r="D36" t="n">
-        <v>64.3</v>
+        <v>64.1</v>
       </c>
       <c r="E36" t="n">
-        <v>30.7</v>
+        <v>30.3</v>
       </c>
       <c r="F36" t="n">
-        <v>53.6</v>
+        <v>51.7</v>
       </c>
       <c r="G36" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="H36" t="n">
-        <v>60.4</v>
+        <v>62</v>
       </c>
       <c r="I36" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J36" t="n">
-        <v>19.2</v>
+        <v>18.7</v>
       </c>
       <c r="K36" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B37" t="s">
         <v>46</v>
@@ -7710,7 +7744,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B38" t="s">
         <v>46</v>
@@ -7745,7 +7779,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B39" t="s">
         <v>46</v>
@@ -7780,7 +7814,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B40" t="s">
         <v>46</v>
@@ -7789,25 +7823,25 @@
         <v>59.7</v>
       </c>
       <c r="D40" t="n">
-        <v>63.4</v>
+        <v>63.6</v>
       </c>
       <c r="E40" t="n">
-        <v>15.3</v>
+        <v>18.8</v>
       </c>
       <c r="F40" t="n">
-        <v>42.5</v>
+        <v>43.2</v>
       </c>
       <c r="G40" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="H40" t="n">
         <v>51</v>
       </c>
       <c r="I40" t="n">
-        <v>8.2</v>
+        <v>9</v>
       </c>
       <c r="J40" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="K40" t="n">
         <v>19.2</v>
@@ -7815,7 +7849,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
@@ -7848,77 +7882,77 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B42" t="s">
         <v>46</v>
       </c>
       <c r="C42" t="n">
-        <v>51</v>
+        <v>51.6</v>
       </c>
       <c r="D42" t="n">
-        <v>55.9</v>
+        <v>57.1</v>
       </c>
       <c r="E42" t="n">
-        <v>16.8</v>
+        <v>22.4</v>
       </c>
       <c r="F42" t="n">
-        <v>25.7</v>
+        <v>22.2</v>
       </c>
       <c r="G42" t="n">
-        <v>10.2</v>
+        <v>9.8</v>
       </c>
       <c r="H42" t="n">
-        <v>37.8</v>
+        <v>36.5</v>
       </c>
       <c r="I42" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="J42" t="n">
-        <v>11</v>
+        <v>11.9</v>
       </c>
       <c r="K42" t="n">
-        <v>-1</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B43" t="s">
         <v>62</v>
       </c>
       <c r="C43" t="n">
-        <v>59.8</v>
+        <v>60</v>
       </c>
       <c r="D43" t="n">
-        <v>56.9</v>
+        <v>57.4</v>
       </c>
       <c r="E43" t="n">
-        <v>15.3</v>
+        <v>16.9</v>
       </c>
       <c r="F43" t="n">
-        <v>36.5</v>
+        <v>35.6</v>
       </c>
       <c r="G43" t="n">
-        <v>14</v>
+        <v>13.6</v>
       </c>
       <c r="H43" t="n">
-        <v>32.1</v>
+        <v>31.2</v>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
-        <v>28.8</v>
+        <v>28.4</v>
       </c>
       <c r="K43" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B44" t="s">
         <v>62</v>
@@ -7953,42 +7987,42 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B45" t="s">
         <v>62</v>
       </c>
       <c r="C45" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="D45" t="n">
-        <v>59.3</v>
+        <v>60.2</v>
       </c>
       <c r="E45" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="F45" t="n">
         <v>50</v>
       </c>
       <c r="G45" t="n">
-        <v>13.3</v>
+        <v>13.9</v>
       </c>
       <c r="H45" t="n">
-        <v>50</v>
+        <v>47.1</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="J45" t="n">
-        <v>40</v>
+        <v>37.8</v>
       </c>
       <c r="K45" t="n">
-        <v>20</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B46" t="s">
         <v>62</v>
@@ -8021,77 +8055,77 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B47" t="s">
         <v>62</v>
       </c>
       <c r="C47" t="n">
-        <v>62.1</v>
+        <v>63.1</v>
       </c>
       <c r="D47" t="n">
-        <v>66.7</v>
+        <v>66.8</v>
       </c>
       <c r="E47" t="n">
-        <v>18.7</v>
+        <v>22</v>
       </c>
       <c r="F47" t="n">
-        <v>35.2</v>
+        <v>35.4</v>
       </c>
       <c r="G47" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="H47" t="n">
-        <v>44.7</v>
+        <v>45.5</v>
       </c>
       <c r="I47" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J47" t="n">
         <v>22.1</v>
       </c>
       <c r="K47" t="n">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B48" t="s">
         <v>62</v>
       </c>
       <c r="C48" t="n">
-        <v>50.4</v>
+        <v>53.4</v>
       </c>
       <c r="D48" t="n">
-        <v>57.3</v>
+        <v>59.7</v>
       </c>
       <c r="E48" t="n">
-        <v>20.3</v>
+        <v>23.8</v>
       </c>
       <c r="F48" t="n">
-        <v>41.5</v>
+        <v>42.9</v>
       </c>
       <c r="G48" t="n">
-        <v>17.1</v>
+        <v>14.6</v>
       </c>
       <c r="H48" t="n">
-        <v>38.9</v>
+        <v>37.7</v>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J48" t="n">
-        <v>33.9</v>
+        <v>34.2</v>
       </c>
       <c r="K48" t="n">
-        <v>1.6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B49" t="s">
         <v>62</v>
@@ -8124,7 +8158,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B50" t="s">
         <v>62</v>
@@ -8159,7 +8193,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B51" t="s">
         <v>62</v>
@@ -8194,7 +8228,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B52" t="s">
         <v>62</v>
@@ -8229,42 +8263,42 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B53" t="s">
         <v>62</v>
       </c>
       <c r="C53" t="n">
-        <v>61.7</v>
+        <v>66.7</v>
       </c>
       <c r="D53" t="n">
-        <v>67</v>
+        <v>68.2</v>
       </c>
       <c r="E53" t="n">
-        <v>42.1</v>
+        <v>41</v>
       </c>
       <c r="F53" t="n">
-        <v>26.9</v>
+        <v>36.8</v>
       </c>
       <c r="G53" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="H53" t="n">
-        <v>54.2</v>
+        <v>59.4</v>
       </c>
       <c r="I53" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="K53" t="n">
-        <v>8.2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B54" t="s">
         <v>62</v>
@@ -8297,7 +8331,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B55" t="s">
         <v>62</v>
@@ -8332,40 +8366,42 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B56" t="s">
         <v>62</v>
       </c>
       <c r="C56" t="n">
-        <v>37.5</v>
+        <v>42.1</v>
       </c>
       <c r="D56" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="E56"/>
+        <v>48.7</v>
+      </c>
+      <c r="E56" t="n">
+        <v>50</v>
+      </c>
       <c r="F56" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="G56" t="n">
-        <v>31.2</v>
+        <v>26.3</v>
       </c>
       <c r="H56" t="n">
-        <v>71.4</v>
+        <v>75</v>
       </c>
       <c r="I56" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="J56" t="n">
-        <v>38.1</v>
+        <v>40.7</v>
       </c>
       <c r="K56" t="n">
-        <v>-18.7</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B57" t="s">
         <v>62</v>
@@ -8400,10 +8436,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B58" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C58" t="n">
         <v>69.5</v>
@@ -8435,10 +8471,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B59" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C59" t="n">
         <v>68.2</v>
@@ -8470,10 +8506,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B60" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C60" t="n">
         <v>50</v>
@@ -8505,10 +8541,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B61" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C61" t="n">
         <v>46.4</v>
@@ -8540,10 +8576,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B62" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C62" t="n">
         <v>64.7</v>
@@ -8575,10 +8611,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B63" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C63" t="n">
         <v>61.1</v>
@@ -8610,10 +8646,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B64" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C64" t="n">
         <v>69.4</v>
@@ -8645,10 +8681,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B65" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C65" t="n">
         <v>58.3</v>
@@ -8680,10 +8716,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B66" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C66" t="n">
         <v>66.7</v>
@@ -8715,10 +8751,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B67" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C67" t="n">
         <v>65</v>
@@ -8750,10 +8786,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B68" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C68" t="n">
         <v>63.1</v>
@@ -8785,10 +8821,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B69" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C69" t="n">
         <v>64.5</v>
@@ -8820,10 +8856,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B70" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C70" t="n">
         <v>42.4</v>
@@ -8855,10 +8891,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B71" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C71" t="n">
         <v>70.3</v>
@@ -8890,10 +8926,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B72" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C72" t="n">
         <v>49</v>
@@ -8925,10 +8961,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B73" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C73" t="n">
         <v>28.6</v>
@@ -8958,10 +8994,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B74" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C74" t="n">
         <v>48.6</v>
@@ -8993,10 +9029,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B75" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C75" t="n">
         <v>57.4</v>
@@ -9028,45 +9064,45 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B76" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C76" t="n">
-        <v>63.6</v>
+        <v>64.9</v>
       </c>
       <c r="D76" t="n">
-        <v>66.7</v>
+        <v>67.1</v>
       </c>
       <c r="E76" t="n">
-        <v>20.2</v>
+        <v>32.5</v>
       </c>
       <c r="F76" t="n">
-        <v>43.6</v>
+        <v>42.2</v>
       </c>
       <c r="G76" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="H76" t="n">
-        <v>46.5</v>
+        <v>45.9</v>
       </c>
       <c r="I76" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="J76" t="n">
-        <v>22.6</v>
+        <v>21.8</v>
       </c>
       <c r="K76" t="n">
-        <v>14</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B77" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C77" t="n">
         <v>48.1</v>
@@ -9098,45 +9134,45 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B78" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C78" t="n">
-        <v>68.2</v>
+        <v>68</v>
       </c>
       <c r="D78" t="n">
-        <v>66.2</v>
+        <v>65.9</v>
       </c>
       <c r="E78" t="n">
-        <v>26.1</v>
+        <v>41.9</v>
       </c>
       <c r="F78" t="n">
-        <v>33.3</v>
+        <v>36.7</v>
       </c>
       <c r="G78" t="n">
-        <v>8.2</v>
+        <v>9</v>
       </c>
       <c r="H78" t="n">
-        <v>45</v>
+        <v>46.4</v>
       </c>
       <c r="I78" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="J78" t="n">
-        <v>25</v>
+        <v>27.4</v>
       </c>
       <c r="K78" t="n">
-        <v>8.3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B79" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C79" t="n">
         <v>63.6</v>
@@ -9168,10 +9204,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B80" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C80" t="n">
         <v>52.2</v>
@@ -9203,10 +9239,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B81" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C81" t="n">
         <v>55.3</v>
@@ -9238,10 +9274,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B82" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C82" t="n">
         <v>70.4</v>
@@ -9273,10 +9309,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B83" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C83" t="n">
         <v>55.6</v>
@@ -9308,10 +9344,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B84" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C84" t="n">
         <v>59.8</v>
@@ -9343,10 +9379,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B85" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C85" t="n">
         <v>61.2</v>
@@ -9378,10 +9414,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B86" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C86" t="n">
         <v>71.1</v>
@@ -9413,10 +9449,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B87" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C87" t="n">
         <v>57.8</v>
@@ -9448,10 +9484,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B88" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C88" t="n">
         <v>71.9</v>
@@ -9483,10 +9519,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B89" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C89" t="n">
         <v>66.2</v>
@@ -9518,10 +9554,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B90" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C90" t="n">
         <v>70.4</v>
@@ -9553,10 +9589,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B91" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C91" t="n">
         <v>63.8</v>
@@ -9588,10 +9624,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B92" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C92" t="n">
         <v>50</v>
@@ -9623,10 +9659,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
+        <v>133</v>
+      </c>
+      <c r="B93" t="s">
         <v>132</v>
-      </c>
-      <c r="B93" t="s">
-        <v>131</v>
       </c>
       <c r="C93" t="n">
         <v>50.9</v>
@@ -9658,10 +9694,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B94" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C94" t="n">
         <v>62</v>
@@ -9693,10 +9729,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B95" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C95" t="n">
         <v>50</v>
@@ -9726,10 +9762,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B96" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C96" t="n">
         <v>68.8</v>
@@ -9761,10 +9797,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B97" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C97" t="n">
         <v>53.6</v>
@@ -9796,10 +9832,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B98" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C98" t="n">
         <v>50</v>
@@ -9831,10 +9867,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B99" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C99" t="n">
         <v>66.7</v>
@@ -9866,10 +9902,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B100" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C100" t="n">
         <v>52.6</v>
@@ -9901,10 +9937,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B101" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C101" t="n">
         <v>59.2</v>
@@ -9936,10 +9972,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B102" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C102" t="n">
         <v>57.6</v>
@@ -9971,10 +10007,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B103" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C103" t="n">
         <v>44</v>
@@ -10006,10 +10042,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B104" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C104" t="n">
         <v>38.9</v>
@@ -10041,10 +10077,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B105" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C105" t="n">
         <v>62</v>
@@ -10076,10 +10112,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B106" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C106" t="n">
         <v>57.8</v>
@@ -10111,10 +10147,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B107" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C107" t="n">
         <v>64.2</v>
@@ -10146,45 +10182,45 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B108" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C108" t="n">
-        <v>55.7</v>
+        <v>55.4</v>
       </c>
       <c r="D108" t="n">
-        <v>64.6</v>
+        <v>64.7</v>
       </c>
       <c r="E108" t="n">
-        <v>15.2</v>
+        <v>16.9</v>
       </c>
       <c r="F108" t="n">
-        <v>33.3</v>
+        <v>34.6</v>
       </c>
       <c r="G108" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
       <c r="H108" t="n">
-        <v>30.9</v>
+        <v>31.4</v>
       </c>
       <c r="I108" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J108" t="n">
-        <v>21.3</v>
+        <v>21.6</v>
       </c>
       <c r="K108" t="n">
-        <v>4.3</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B109" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C109" t="n">
         <v>59</v>
@@ -10216,10 +10252,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B110" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C110" t="n">
         <v>62.5</v>
@@ -10251,34 +10287,34 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B111" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C111" t="n">
-        <v>63.6</v>
+        <v>64.1</v>
       </c>
       <c r="D111" t="n">
-        <v>62.2</v>
+        <v>62.1</v>
       </c>
       <c r="E111" t="n">
-        <v>34.7</v>
+        <v>35.6</v>
       </c>
       <c r="F111" t="n">
-        <v>44.4</v>
+        <v>45.8</v>
       </c>
       <c r="G111" t="n">
-        <v>6.8</v>
+        <v>7.7</v>
       </c>
       <c r="H111" t="n">
-        <v>53.8</v>
+        <v>50</v>
       </c>
       <c r="I111" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J111" t="n">
-        <v>43.2</v>
+        <v>42.9</v>
       </c>
       <c r="K111" t="n">
         <v>20.5</v>
@@ -10286,10 +10322,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B112" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C112" t="n">
         <v>84.6</v>
@@ -10319,10 +10355,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B113" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C113" t="n">
         <v>50</v>
@@ -10354,10 +10390,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B114" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C114" t="n">
         <v>61.3</v>
@@ -10389,10 +10425,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B115" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C115" t="n">
         <v>65.8</v>
@@ -10424,45 +10460,45 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B116" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C116" t="n">
-        <v>50</v>
+        <v>50.6</v>
       </c>
       <c r="D116" t="n">
-        <v>60.6</v>
+        <v>60.3</v>
       </c>
       <c r="E116" t="n">
-        <v>26.2</v>
+        <v>28.6</v>
       </c>
       <c r="F116" t="n">
-        <v>46</v>
+        <v>44.7</v>
       </c>
       <c r="G116" t="n">
-        <v>10.4</v>
+        <v>11.2</v>
       </c>
       <c r="H116" t="n">
-        <v>54.8</v>
+        <v>59.6</v>
       </c>
       <c r="I116" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J116" t="n">
-        <v>23.6</v>
+        <v>25</v>
       </c>
       <c r="K116" t="n">
-        <v>13.6</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B117" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C117" t="n">
         <v>66.7</v>
@@ -10494,45 +10530,45 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B118" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C118" t="n">
-        <v>66.7</v>
+        <v>68.5</v>
       </c>
       <c r="D118" t="n">
-        <v>67.7</v>
+        <v>68.9</v>
       </c>
       <c r="E118" t="n">
-        <v>26.1</v>
+        <v>28.4</v>
       </c>
       <c r="F118" t="n">
-        <v>50</v>
+        <v>50.8</v>
       </c>
       <c r="G118" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="H118" t="n">
-        <v>38.7</v>
+        <v>40.2</v>
       </c>
       <c r="I118" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J118" t="n">
-        <v>25.9</v>
+        <v>25.2</v>
       </c>
       <c r="K118" t="n">
-        <v>17</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B119" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C119" t="n">
         <v>61.7</v>
@@ -10565,34 +10601,34 @@
     <row r="120">
       <c r="A120"/>
       <c r="B120" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C120" t="n">
-        <v>57.6</v>
+        <v>57.7</v>
       </c>
       <c r="D120" t="n">
-        <v>60.9</v>
+        <v>61</v>
       </c>
       <c r="E120" t="n">
-        <v>24.4</v>
+        <v>25.4</v>
       </c>
       <c r="F120" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="G120" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="H120" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
       <c r="I120" t="n">
         <v>3.1</v>
       </c>
       <c r="J120" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="K120" t="n">
-        <v>8.4</v>
+        <v>8.7</v>
       </c>
     </row>
   </sheetData>

--- a/data/summary2026.xlsx
+++ b/data/summary2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="278">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -226,9 +226,6 @@
   </si>
   <si>
     <t xml:space="preserve">Garrett Takamatsu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J.D Williams</t>
   </si>
   <si>
     <t xml:space="preserve">J.D. Williams</t>
@@ -904,8 +901,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K150" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K150"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K149" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K149"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -3222,28 +3219,32 @@
       <c r="B58" t="s">
         <v>62</v>
       </c>
-      <c r="C58"/>
+      <c r="C58" t="n">
+        <v>76.9</v>
+      </c>
       <c r="D58" t="n">
-        <v>40</v>
-      </c>
-      <c r="E58"/>
+        <v>17.8</v>
+      </c>
+      <c r="E58" t="n">
+        <v>59.1</v>
+      </c>
       <c r="F58" t="n">
-        <v>40</v>
+        <v>17.8</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>24.1</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="I58" t="n">
-        <v>50</v>
+        <v>52.4</v>
       </c>
       <c r="J58" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="K58" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="59">
@@ -3254,31 +3255,31 @@
         <v>62</v>
       </c>
       <c r="C59" t="n">
-        <v>76.9</v>
+        <v>100</v>
       </c>
       <c r="D59" t="n">
-        <v>11.4</v>
+        <v>50</v>
       </c>
       <c r="E59" t="n">
-        <v>65.5</v>
+        <v>50</v>
       </c>
       <c r="F59" t="n">
-        <v>11.4</v>
+        <v>50</v>
       </c>
       <c r="G59" t="n">
-        <v>27.1</v>
+        <v>25</v>
       </c>
       <c r="H59" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>52.9</v>
+        <v>100</v>
       </c>
       <c r="J59" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>58.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60">
@@ -3289,16 +3290,16 @@
         <v>62</v>
       </c>
       <c r="C60" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="D60" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="E60" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="G60" t="n">
         <v>25</v>
@@ -3307,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61">
@@ -3324,31 +3325,31 @@
         <v>62</v>
       </c>
       <c r="C61" t="n">
-        <v>33.3</v>
+        <v>74.1</v>
       </c>
       <c r="D61" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>74.1</v>
       </c>
       <c r="F61" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>25</v>
+        <v>31.4</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="I61" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="K61" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="62">
@@ -3359,31 +3360,31 @@
         <v>62</v>
       </c>
       <c r="C62" t="n">
-        <v>74.1</v>
+        <v>69.6</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="E62" t="n">
-        <v>74.1</v>
+        <v>36.3</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G62" t="n">
-        <v>31.4</v>
+        <v>20</v>
       </c>
       <c r="H62" t="n">
-        <v>18.8</v>
+        <v>11.8</v>
       </c>
       <c r="I62" t="n">
-        <v>62.5</v>
+        <v>46.2</v>
       </c>
       <c r="J62" t="n">
-        <v>12.5</v>
+        <v>30.8</v>
       </c>
       <c r="K62" t="n">
-        <v>12.5</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="63">
@@ -3394,31 +3395,31 @@
         <v>62</v>
       </c>
       <c r="C63" t="n">
-        <v>69.6</v>
+        <v>75</v>
       </c>
       <c r="D63" t="n">
+        <v>40</v>
+      </c>
+      <c r="E63" t="n">
+        <v>35</v>
+      </c>
+      <c r="F63" t="n">
+        <v>40</v>
+      </c>
+      <c r="G63" t="n">
+        <v>60</v>
+      </c>
+      <c r="H63" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I63" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J63" t="n">
         <v>33.3</v>
       </c>
-      <c r="E63" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="F63" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G63" t="n">
-        <v>20</v>
-      </c>
-      <c r="H63" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="I63" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="J63" t="n">
-        <v>30.8</v>
-      </c>
       <c r="K63" t="n">
-        <v>53.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64">
@@ -3429,31 +3430,31 @@
         <v>62</v>
       </c>
       <c r="C64" t="n">
-        <v>75</v>
+        <v>68.6</v>
       </c>
       <c r="D64" t="n">
-        <v>40</v>
+        <v>31.8</v>
       </c>
       <c r="E64" t="n">
-        <v>35</v>
+        <v>36.8</v>
       </c>
       <c r="F64" t="n">
-        <v>40</v>
+        <v>31.8</v>
       </c>
       <c r="G64" t="n">
-        <v>60</v>
+        <v>11.1</v>
       </c>
       <c r="H64" t="n">
-        <v>16.7</v>
+        <v>3.4</v>
       </c>
       <c r="I64" t="n">
-        <v>66.7</v>
+        <v>47.6</v>
       </c>
       <c r="J64" t="n">
-        <v>33.3</v>
+        <v>28.6</v>
       </c>
       <c r="K64" t="n">
-        <v>100</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="65">
@@ -3464,31 +3465,31 @@
         <v>62</v>
       </c>
       <c r="C65" t="n">
-        <v>68.6</v>
+        <v>71.4</v>
       </c>
       <c r="D65" t="n">
-        <v>31.8</v>
+        <v>23.9</v>
       </c>
       <c r="E65" t="n">
-        <v>36.8</v>
+        <v>47.5</v>
       </c>
       <c r="F65" t="n">
-        <v>31.8</v>
+        <v>23.9</v>
       </c>
       <c r="G65" t="n">
-        <v>11.1</v>
+        <v>27.1</v>
       </c>
       <c r="H65" t="n">
-        <v>3.4</v>
+        <v>10.1</v>
       </c>
       <c r="I65" t="n">
-        <v>47.6</v>
+        <v>40</v>
       </c>
       <c r="J65" t="n">
-        <v>28.6</v>
+        <v>28</v>
       </c>
       <c r="K65" t="n">
-        <v>38.1</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="66">
@@ -3499,31 +3500,31 @@
         <v>62</v>
       </c>
       <c r="C66" t="n">
-        <v>71.4</v>
+        <v>79.3</v>
       </c>
       <c r="D66" t="n">
-        <v>23.9</v>
+        <v>45.8</v>
       </c>
       <c r="E66" t="n">
-        <v>47.5</v>
+        <v>33.5</v>
       </c>
       <c r="F66" t="n">
-        <v>23.9</v>
+        <v>45.8</v>
       </c>
       <c r="G66" t="n">
-        <v>27.1</v>
+        <v>22.8</v>
       </c>
       <c r="H66" t="n">
-        <v>10.1</v>
+        <v>3.8</v>
       </c>
       <c r="I66" t="n">
-        <v>40</v>
+        <v>38.9</v>
       </c>
       <c r="J66" t="n">
-        <v>28</v>
+        <v>40.7</v>
       </c>
       <c r="K66" t="n">
-        <v>36.7</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="67">
@@ -3534,31 +3535,31 @@
         <v>62</v>
       </c>
       <c r="C67" t="n">
-        <v>79.3</v>
+        <v>56.5</v>
       </c>
       <c r="D67" t="n">
-        <v>45.8</v>
+        <v>15.7</v>
       </c>
       <c r="E67" t="n">
-        <v>33.5</v>
+        <v>40.8</v>
       </c>
       <c r="F67" t="n">
-        <v>45.8</v>
+        <v>15.7</v>
       </c>
       <c r="G67" t="n">
-        <v>22.8</v>
+        <v>30.7</v>
       </c>
       <c r="H67" t="n">
-        <v>3.8</v>
+        <v>15.4</v>
       </c>
       <c r="I67" t="n">
-        <v>38.9</v>
+        <v>45</v>
       </c>
       <c r="J67" t="n">
-        <v>40.7</v>
+        <v>30</v>
       </c>
       <c r="K67" t="n">
-        <v>48.1</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="68">
@@ -3569,31 +3570,31 @@
         <v>62</v>
       </c>
       <c r="C68" t="n">
-        <v>56.5</v>
+        <v>70.4</v>
       </c>
       <c r="D68" t="n">
-        <v>15.7</v>
+        <v>30.6</v>
       </c>
       <c r="E68" t="n">
-        <v>40.8</v>
+        <v>39.8</v>
       </c>
       <c r="F68" t="n">
-        <v>15.7</v>
+        <v>30.6</v>
       </c>
       <c r="G68" t="n">
-        <v>30.7</v>
+        <v>33.3</v>
       </c>
       <c r="H68" t="n">
-        <v>15.4</v>
+        <v>7.5</v>
       </c>
       <c r="I68" t="n">
-        <v>45</v>
+        <v>45.2</v>
       </c>
       <c r="J68" t="n">
-        <v>30</v>
+        <v>25.8</v>
       </c>
       <c r="K68" t="n">
-        <v>21.6</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="69">
@@ -3601,69 +3602,69 @@
         <v>82</v>
       </c>
       <c r="B69" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="C69" t="n">
-        <v>70.4</v>
+        <v>86</v>
       </c>
       <c r="D69" t="n">
-        <v>30.6</v>
+        <v>21.1</v>
       </c>
       <c r="E69" t="n">
-        <v>39.8</v>
+        <v>64.9</v>
       </c>
       <c r="F69" t="n">
-        <v>30.6</v>
+        <v>21.1</v>
       </c>
       <c r="G69" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="H69" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="I69" t="n">
         <v>33.3</v>
       </c>
-      <c r="H69" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I69" t="n">
-        <v>45.2</v>
-      </c>
       <c r="J69" t="n">
-        <v>25.8</v>
+        <v>51.9</v>
       </c>
       <c r="K69" t="n">
-        <v>53.1</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
+        <v>84</v>
+      </c>
+      <c r="B70" t="s">
         <v>83</v>
       </c>
-      <c r="B70" t="s">
-        <v>84</v>
-      </c>
       <c r="C70" t="n">
-        <v>86</v>
+        <v>74.3</v>
       </c>
       <c r="D70" t="n">
-        <v>21.1</v>
+        <v>28.8</v>
       </c>
       <c r="E70" t="n">
-        <v>64.9</v>
+        <v>45.5</v>
       </c>
       <c r="F70" t="n">
-        <v>21.1</v>
+        <v>28.8</v>
       </c>
       <c r="G70" t="n">
-        <v>38.8</v>
+        <v>19.5</v>
       </c>
       <c r="H70" t="n">
-        <v>11.9</v>
+        <v>5.5</v>
       </c>
       <c r="I70" t="n">
-        <v>33.3</v>
+        <v>59</v>
       </c>
       <c r="J70" t="n">
-        <v>51.9</v>
+        <v>20.5</v>
       </c>
       <c r="K70" t="n">
-        <v>58.6</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="71">
@@ -3671,34 +3672,34 @@
         <v>85</v>
       </c>
       <c r="B71" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C71" t="n">
-        <v>74.3</v>
+        <v>78.8</v>
       </c>
       <c r="D71" t="n">
-        <v>28.8</v>
+        <v>31.2</v>
       </c>
       <c r="E71" t="n">
-        <v>45.5</v>
+        <v>47.6</v>
       </c>
       <c r="F71" t="n">
-        <v>28.8</v>
+        <v>31.2</v>
       </c>
       <c r="G71" t="n">
-        <v>19.5</v>
+        <v>34.3</v>
       </c>
       <c r="H71" t="n">
-        <v>5.5</v>
+        <v>10.1</v>
       </c>
       <c r="I71" t="n">
-        <v>59</v>
+        <v>42.5</v>
       </c>
       <c r="J71" t="n">
-        <v>20.5</v>
+        <v>25</v>
       </c>
       <c r="K71" t="n">
-        <v>43.2</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="72">
@@ -3706,34 +3707,34 @@
         <v>86</v>
       </c>
       <c r="B72" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C72" t="n">
-        <v>78.8</v>
+        <v>70.4</v>
       </c>
       <c r="D72" t="n">
-        <v>31.2</v>
+        <v>33.7</v>
       </c>
       <c r="E72" t="n">
-        <v>47.6</v>
+        <v>36.7</v>
       </c>
       <c r="F72" t="n">
-        <v>31.2</v>
+        <v>33.7</v>
       </c>
       <c r="G72" t="n">
-        <v>34.3</v>
+        <v>29.5</v>
       </c>
       <c r="H72" t="n">
-        <v>10.1</v>
+        <v>8.5</v>
       </c>
       <c r="I72" t="n">
-        <v>42.5</v>
+        <v>51.1</v>
       </c>
       <c r="J72" t="n">
-        <v>25</v>
+        <v>21.3</v>
       </c>
       <c r="K72" t="n">
-        <v>64.3</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="73">
@@ -3741,34 +3742,34 @@
         <v>87</v>
       </c>
       <c r="B73" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C73" t="n">
-        <v>70.4</v>
+        <v>76.8</v>
       </c>
       <c r="D73" t="n">
-        <v>33.7</v>
+        <v>42.5</v>
       </c>
       <c r="E73" t="n">
-        <v>36.7</v>
+        <v>34.3</v>
       </c>
       <c r="F73" t="n">
-        <v>33.7</v>
+        <v>42.5</v>
       </c>
       <c r="G73" t="n">
-        <v>29.5</v>
+        <v>24.3</v>
       </c>
       <c r="H73" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>51.1</v>
+        <v>36.1</v>
       </c>
       <c r="J73" t="n">
-        <v>21.3</v>
+        <v>27.9</v>
       </c>
       <c r="K73" t="n">
-        <v>48.9</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="74">
@@ -3776,34 +3777,34 @@
         <v>88</v>
       </c>
       <c r="B74" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C74" t="n">
-        <v>76.8</v>
+        <v>71.4</v>
       </c>
       <c r="D74" t="n">
-        <v>42.5</v>
+        <v>20</v>
       </c>
       <c r="E74" t="n">
-        <v>34.3</v>
+        <v>51.4</v>
       </c>
       <c r="F74" t="n">
-        <v>42.5</v>
+        <v>20</v>
       </c>
       <c r="G74" t="n">
-        <v>24.3</v>
+        <v>22</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="I74" t="n">
-        <v>36.1</v>
+        <v>31.9</v>
       </c>
       <c r="J74" t="n">
-        <v>27.9</v>
+        <v>38.3</v>
       </c>
       <c r="K74" t="n">
-        <v>70.2</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="75">
@@ -3811,34 +3812,34 @@
         <v>89</v>
       </c>
       <c r="B75" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C75" t="n">
-        <v>71.4</v>
+        <v>73.8</v>
       </c>
       <c r="D75" t="n">
-        <v>20</v>
+        <v>32.7</v>
       </c>
       <c r="E75" t="n">
-        <v>51.4</v>
+        <v>41.1</v>
       </c>
       <c r="F75" t="n">
-        <v>20</v>
+        <v>32.7</v>
       </c>
       <c r="G75" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H75" t="n">
-        <v>13.6</v>
+        <v>8.7</v>
       </c>
       <c r="I75" t="n">
-        <v>31.9</v>
+        <v>51.7</v>
       </c>
       <c r="J75" t="n">
-        <v>38.3</v>
+        <v>20.7</v>
       </c>
       <c r="K75" t="n">
-        <v>28.9</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="76">
@@ -3846,34 +3847,34 @@
         <v>90</v>
       </c>
       <c r="B76" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C76" t="n">
-        <v>73.8</v>
+        <v>100</v>
       </c>
       <c r="D76" t="n">
-        <v>32.7</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>41.1</v>
+        <v>100</v>
       </c>
       <c r="F76" t="n">
-        <v>32.7</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>32</v>
+        <v>46.2</v>
       </c>
       <c r="H76" t="n">
-        <v>8.7</v>
+        <v>33.3</v>
       </c>
       <c r="I76" t="n">
-        <v>51.7</v>
+        <v>100</v>
       </c>
       <c r="J76" t="n">
-        <v>20.7</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>29.6</v>
+        <v>100</v>
       </c>
     </row>
     <row r="77">
@@ -3881,34 +3882,34 @@
         <v>91</v>
       </c>
       <c r="B77" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C77" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>30.6</v>
       </c>
       <c r="E77" t="n">
-        <v>100</v>
+        <v>38.4</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>30.6</v>
       </c>
       <c r="G77" t="n">
-        <v>46.2</v>
+        <v>19</v>
       </c>
       <c r="H77" t="n">
-        <v>33.3</v>
+        <v>7.9</v>
       </c>
       <c r="I77" t="n">
-        <v>100</v>
+        <v>59.2</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>16.3</v>
       </c>
       <c r="K77" t="n">
-        <v>100</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="78">
@@ -3916,34 +3917,34 @@
         <v>92</v>
       </c>
       <c r="B78" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C78" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D78" t="n">
-        <v>30.6</v>
+        <v>46.5</v>
       </c>
       <c r="E78" t="n">
-        <v>38.4</v>
+        <v>25.5</v>
       </c>
       <c r="F78" t="n">
-        <v>30.6</v>
+        <v>46.5</v>
       </c>
       <c r="G78" t="n">
-        <v>19</v>
+        <v>23.7</v>
       </c>
       <c r="H78" t="n">
-        <v>7.9</v>
+        <v>10.8</v>
       </c>
       <c r="I78" t="n">
-        <v>59.2</v>
+        <v>48</v>
       </c>
       <c r="J78" t="n">
-        <v>16.3</v>
+        <v>32</v>
       </c>
       <c r="K78" t="n">
-        <v>44.9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="79">
@@ -3951,34 +3952,34 @@
         <v>93</v>
       </c>
       <c r="B79" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C79" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D79" t="n">
-        <v>46.5</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>25.5</v>
+        <v>75</v>
       </c>
       <c r="F79" t="n">
-        <v>46.5</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>23.7</v>
+        <v>22.2</v>
       </c>
       <c r="H79" t="n">
-        <v>10.8</v>
+        <v>25</v>
       </c>
       <c r="I79" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="J79" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="K79" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="80">
@@ -3986,34 +3987,34 @@
         <v>94</v>
       </c>
       <c r="B80" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C80" t="n">
-        <v>75</v>
+        <v>61.4</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>19.3</v>
       </c>
       <c r="E80" t="n">
-        <v>75</v>
+        <v>42.1</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>19.3</v>
       </c>
       <c r="G80" t="n">
-        <v>22.2</v>
+        <v>19.4</v>
       </c>
       <c r="H80" t="n">
-        <v>25</v>
+        <v>12.2</v>
       </c>
       <c r="I80" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="J80" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="K80" t="n">
-        <v>40</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="81">
@@ -4021,34 +4022,34 @@
         <v>95</v>
       </c>
       <c r="B81" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C81" t="n">
-        <v>61.4</v>
+        <v>41.3</v>
       </c>
       <c r="D81" t="n">
-        <v>19.3</v>
+        <v>23.7</v>
       </c>
       <c r="E81" t="n">
-        <v>42.1</v>
+        <v>17.6</v>
       </c>
       <c r="F81" t="n">
-        <v>19.3</v>
+        <v>23.7</v>
       </c>
       <c r="G81" t="n">
-        <v>19.4</v>
+        <v>28.9</v>
       </c>
       <c r="H81" t="n">
-        <v>12.2</v>
+        <v>3.6</v>
       </c>
       <c r="I81" t="n">
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="J81" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="K81" t="n">
-        <v>44.7</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="82">
@@ -4056,57 +4057,47 @@
         <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C82" t="n">
-        <v>41.3</v>
+        <v>50</v>
       </c>
       <c r="D82" t="n">
-        <v>23.7</v>
+        <v>50</v>
       </c>
       <c r="E82" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>23.7</v>
+        <v>50</v>
       </c>
       <c r="G82" t="n">
-        <v>28.9</v>
+        <v>100</v>
       </c>
       <c r="H82" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I82" t="n">
-        <v>75</v>
-      </c>
-      <c r="J82" t="n">
-        <v>25</v>
-      </c>
-      <c r="K82" t="n">
-        <v>26.3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I82"/>
+      <c r="J82"/>
+      <c r="K82"/>
     </row>
     <row r="83">
       <c r="A83" t="s">
+        <v>98</v>
+      </c>
+      <c r="B83" t="s">
         <v>97</v>
       </c>
-      <c r="B83" t="s">
-        <v>98</v>
-      </c>
-      <c r="C83" t="n">
-        <v>50</v>
-      </c>
+      <c r="C83"/>
       <c r="D83" t="n">
         <v>50</v>
       </c>
-      <c r="E83" t="n">
-        <v>0</v>
-      </c>
+      <c r="E83"/>
       <c r="F83" t="n">
         <v>50</v>
       </c>
       <c r="G83" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -4120,59 +4111,69 @@
         <v>99</v>
       </c>
       <c r="B84" t="s">
-        <v>98</v>
-      </c>
-      <c r="C84"/>
+        <v>97</v>
+      </c>
+      <c r="C84" t="n">
+        <v>56.8</v>
+      </c>
       <c r="D84" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E84" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="F84" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G84" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="H84" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I84" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="J84" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="K84" t="n">
         <v>50</v>
       </c>
-      <c r="E84"/>
-      <c r="F84" t="n">
-        <v>50</v>
-      </c>
-      <c r="G84" t="n">
-        <v>50</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84"/>
-      <c r="J84"/>
-      <c r="K84"/>
     </row>
     <row r="85">
       <c r="A85" t="s">
         <v>100</v>
       </c>
       <c r="B85" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C85" t="n">
-        <v>56.8</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>54.5</v>
       </c>
       <c r="E85" t="n">
-        <v>45.7</v>
+        <v>-54.5</v>
       </c>
       <c r="F85" t="n">
-        <v>11.1</v>
+        <v>54.5</v>
       </c>
       <c r="G85" t="n">
-        <v>26.7</v>
+        <v>16.7</v>
       </c>
       <c r="H85" t="n">
-        <v>14.3</v>
+        <v>50</v>
       </c>
       <c r="I85" t="n">
-        <v>36.8</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>31.6</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -4180,34 +4181,34 @@
         <v>101</v>
       </c>
       <c r="B86" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>56.5</v>
       </c>
       <c r="D86" t="n">
         <v>54.5</v>
       </c>
       <c r="E86" t="n">
-        <v>-54.5</v>
+        <v>2</v>
       </c>
       <c r="F86" t="n">
         <v>54.5</v>
       </c>
       <c r="G86" t="n">
-        <v>16.7</v>
+        <v>37.8</v>
       </c>
       <c r="H86" t="n">
-        <v>50</v>
+        <v>4.3</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>53.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="87">
@@ -4215,34 +4216,34 @@
         <v>102</v>
       </c>
       <c r="B87" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C87" t="n">
-        <v>56.5</v>
+        <v>86.2</v>
       </c>
       <c r="D87" t="n">
-        <v>54.5</v>
+        <v>33.3</v>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>52.9</v>
       </c>
       <c r="F87" t="n">
-        <v>54.5</v>
+        <v>33.3</v>
       </c>
       <c r="G87" t="n">
-        <v>37.8</v>
+        <v>43.2</v>
       </c>
       <c r="H87" t="n">
-        <v>4.3</v>
+        <v>14.6</v>
       </c>
       <c r="I87" t="n">
-        <v>53.8</v>
+        <v>52.4</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="K87" t="n">
-        <v>8.3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="88">
@@ -4250,34 +4251,34 @@
         <v>103</v>
       </c>
       <c r="B88" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C88" t="n">
-        <v>86.2</v>
+        <v>75.7</v>
       </c>
       <c r="D88" t="n">
-        <v>33.3</v>
+        <v>33.9</v>
       </c>
       <c r="E88" t="n">
-        <v>52.9</v>
+        <v>41.8</v>
       </c>
       <c r="F88" t="n">
-        <v>33.3</v>
+        <v>33.9</v>
       </c>
       <c r="G88" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H88" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I88" t="n">
         <v>43.2</v>
       </c>
-      <c r="H88" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="I88" t="n">
-        <v>52.4</v>
-      </c>
       <c r="J88" t="n">
-        <v>14.3</v>
+        <v>20.5</v>
       </c>
       <c r="K88" t="n">
-        <v>45</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="89">
@@ -4285,34 +4286,34 @@
         <v>104</v>
       </c>
       <c r="B89" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C89" t="n">
-        <v>75.7</v>
+        <v>68.1</v>
       </c>
       <c r="D89" t="n">
-        <v>33.9</v>
+        <v>16.3</v>
       </c>
       <c r="E89" t="n">
-        <v>41.8</v>
+        <v>51.8</v>
       </c>
       <c r="F89" t="n">
-        <v>33.9</v>
+        <v>16.3</v>
       </c>
       <c r="G89" t="n">
-        <v>18.2</v>
+        <v>28.8</v>
       </c>
       <c r="H89" t="n">
-        <v>6.7</v>
+        <v>22.7</v>
       </c>
       <c r="I89" t="n">
-        <v>43.2</v>
+        <v>27.1</v>
       </c>
       <c r="J89" t="n">
-        <v>20.5</v>
+        <v>35.4</v>
       </c>
       <c r="K89" t="n">
-        <v>38.6</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="90">
@@ -4320,34 +4321,34 @@
         <v>105</v>
       </c>
       <c r="B90" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C90" t="n">
-        <v>68.1</v>
+        <v>65.5</v>
       </c>
       <c r="D90" t="n">
-        <v>16.3</v>
+        <v>32.6</v>
       </c>
       <c r="E90" t="n">
-        <v>51.8</v>
+        <v>32.9</v>
       </c>
       <c r="F90" t="n">
-        <v>16.3</v>
+        <v>32.6</v>
       </c>
       <c r="G90" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="H90" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="I90" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="J90" t="n">
         <v>28.8</v>
       </c>
-      <c r="H90" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I90" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="J90" t="n">
-        <v>35.4</v>
-      </c>
       <c r="K90" t="n">
-        <v>41.3</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="91">
@@ -4355,34 +4356,34 @@
         <v>106</v>
       </c>
       <c r="B91" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C91" t="n">
-        <v>65.5</v>
+        <v>87.2</v>
       </c>
       <c r="D91" t="n">
-        <v>32.6</v>
+        <v>28</v>
       </c>
       <c r="E91" t="n">
-        <v>32.9</v>
+        <v>59.2</v>
       </c>
       <c r="F91" t="n">
-        <v>32.6</v>
+        <v>28</v>
       </c>
       <c r="G91" t="n">
-        <v>23.2</v>
+        <v>36.9</v>
       </c>
       <c r="H91" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
       <c r="I91" t="n">
-        <v>42.3</v>
+        <v>37.1</v>
       </c>
       <c r="J91" t="n">
-        <v>28.8</v>
+        <v>37.1</v>
       </c>
       <c r="K91" t="n">
-        <v>46.2</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="92">
@@ -4390,34 +4391,34 @@
         <v>107</v>
       </c>
       <c r="B92" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C92" t="n">
-        <v>87.2</v>
+        <v>75</v>
       </c>
       <c r="D92" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="E92" t="n">
-        <v>59.2</v>
+        <v>25</v>
       </c>
       <c r="F92" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="G92" t="n">
-        <v>36.9</v>
+        <v>3.3</v>
       </c>
       <c r="H92" t="n">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="I92" t="n">
-        <v>37.1</v>
+        <v>45.5</v>
       </c>
       <c r="J92" t="n">
-        <v>37.1</v>
+        <v>18.2</v>
       </c>
       <c r="K92" t="n">
-        <v>54.3</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="93">
@@ -4425,34 +4426,34 @@
         <v>108</v>
       </c>
       <c r="B93" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C93" t="n">
-        <v>75</v>
+        <v>48.6</v>
       </c>
       <c r="D93" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="E93" t="n">
-        <v>25</v>
+        <v>20.6</v>
       </c>
       <c r="F93" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="G93" t="n">
-        <v>3.3</v>
+        <v>34.5</v>
       </c>
       <c r="H93" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>45.5</v>
+        <v>66.7</v>
       </c>
       <c r="J93" t="n">
-        <v>18.2</v>
+        <v>22.2</v>
       </c>
       <c r="K93" t="n">
-        <v>36.4</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="94">
@@ -4460,34 +4461,34 @@
         <v>109</v>
       </c>
       <c r="B94" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C94" t="n">
-        <v>48.6</v>
+        <v>76.4</v>
       </c>
       <c r="D94" t="n">
-        <v>28</v>
+        <v>32.9</v>
       </c>
       <c r="E94" t="n">
-        <v>20.6</v>
+        <v>43.5</v>
       </c>
       <c r="F94" t="n">
-        <v>28</v>
+        <v>32.9</v>
       </c>
       <c r="G94" t="n">
-        <v>34.5</v>
+        <v>36.5</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I94" t="n">
-        <v>66.7</v>
+        <v>38.9</v>
       </c>
       <c r="J94" t="n">
-        <v>22.2</v>
+        <v>30.6</v>
       </c>
       <c r="K94" t="n">
-        <v>66.7</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="95">
@@ -4495,34 +4496,34 @@
         <v>110</v>
       </c>
       <c r="B95" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C95" t="n">
-        <v>76.4</v>
+        <v>65.3</v>
       </c>
       <c r="D95" t="n">
-        <v>32.9</v>
+        <v>21.2</v>
       </c>
       <c r="E95" t="n">
-        <v>43.5</v>
+        <v>44.1</v>
       </c>
       <c r="F95" t="n">
-        <v>32.9</v>
+        <v>21.2</v>
       </c>
       <c r="G95" t="n">
-        <v>36.5</v>
+        <v>17.4</v>
       </c>
       <c r="H95" t="n">
-        <v>4.8</v>
+        <v>8.5</v>
       </c>
       <c r="I95" t="n">
-        <v>38.9</v>
+        <v>38.3</v>
       </c>
       <c r="J95" t="n">
-        <v>30.6</v>
+        <v>23.3</v>
       </c>
       <c r="K95" t="n">
-        <v>47.2</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="96">
@@ -4530,34 +4531,34 @@
         <v>111</v>
       </c>
       <c r="B96" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C96" t="n">
-        <v>65.3</v>
+        <v>60</v>
       </c>
       <c r="D96" t="n">
-        <v>21.2</v>
+        <v>22.8</v>
       </c>
       <c r="E96" t="n">
-        <v>44.1</v>
+        <v>37.2</v>
       </c>
       <c r="F96" t="n">
-        <v>21.2</v>
+        <v>22.8</v>
       </c>
       <c r="G96" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="H96" t="n">
-        <v>8.5</v>
+        <v>10.1</v>
       </c>
       <c r="I96" t="n">
-        <v>38.3</v>
+        <v>37.3</v>
       </c>
       <c r="J96" t="n">
-        <v>23.3</v>
+        <v>27.5</v>
       </c>
       <c r="K96" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="97">
@@ -4565,34 +4566,34 @@
         <v>112</v>
       </c>
       <c r="B97" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C97" t="n">
-        <v>60</v>
+        <v>60.4</v>
       </c>
       <c r="D97" t="n">
-        <v>22.8</v>
+        <v>16.2</v>
       </c>
       <c r="E97" t="n">
-        <v>37.2</v>
+        <v>44.2</v>
       </c>
       <c r="F97" t="n">
-        <v>22.8</v>
+        <v>16.2</v>
       </c>
       <c r="G97" t="n">
-        <v>17.6</v>
+        <v>19.8</v>
       </c>
       <c r="H97" t="n">
-        <v>10.1</v>
+        <v>11.3</v>
       </c>
       <c r="I97" t="n">
-        <v>37.3</v>
+        <v>58.5</v>
       </c>
       <c r="J97" t="n">
-        <v>27.5</v>
+        <v>24.4</v>
       </c>
       <c r="K97" t="n">
-        <v>43.1</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="98">
@@ -4600,69 +4601,69 @@
         <v>113</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="C98" t="n">
-        <v>60.4</v>
+        <v>53.8</v>
       </c>
       <c r="D98" t="n">
-        <v>16.2</v>
+        <v>53.7</v>
       </c>
       <c r="E98" t="n">
-        <v>44.2</v>
+        <v>0.1</v>
       </c>
       <c r="F98" t="n">
-        <v>16.2</v>
+        <v>53.7</v>
       </c>
       <c r="G98" t="n">
-        <v>19.8</v>
+        <v>26.7</v>
       </c>
       <c r="H98" t="n">
-        <v>11.3</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>58.5</v>
+        <v>46.7</v>
       </c>
       <c r="J98" t="n">
-        <v>24.4</v>
+        <v>33.3</v>
       </c>
       <c r="K98" t="n">
-        <v>57.1</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
+        <v>115</v>
+      </c>
+      <c r="B99" t="s">
         <v>114</v>
       </c>
-      <c r="B99" t="s">
-        <v>115</v>
-      </c>
       <c r="C99" t="n">
-        <v>53.8</v>
+        <v>100</v>
       </c>
       <c r="D99" t="n">
-        <v>53.7</v>
+        <v>16.7</v>
       </c>
       <c r="E99" t="n">
-        <v>0.1</v>
+        <v>83.3</v>
       </c>
       <c r="F99" t="n">
-        <v>53.7</v>
+        <v>16.7</v>
       </c>
       <c r="G99" t="n">
-        <v>26.7</v>
+        <v>12.5</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I99" t="n">
-        <v>46.7</v>
+        <v>60</v>
       </c>
       <c r="J99" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="K99" t="n">
-        <v>46.7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="100">
@@ -4670,98 +4671,98 @@
         <v>116</v>
       </c>
       <c r="B100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C100" t="n">
         <v>100</v>
       </c>
       <c r="D100" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="F100" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I100" t="n">
-        <v>60</v>
-      </c>
-      <c r="J100" t="n">
-        <v>20</v>
-      </c>
-      <c r="K100" t="n">
-        <v>60</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I100"/>
+      <c r="J100"/>
+      <c r="K100"/>
     </row>
     <row r="101">
       <c r="A101" t="s">
         <v>117</v>
       </c>
       <c r="B101" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C101" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="E101" t="n">
-        <v>100</v>
+        <v>43.2</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101"/>
-      <c r="J101"/>
-      <c r="K101"/>
+        <v>14.7</v>
+      </c>
+      <c r="I101" t="n">
+        <v>36</v>
+      </c>
+      <c r="J101" t="n">
+        <v>32</v>
+      </c>
+      <c r="K101" t="n">
+        <v>52.2</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
         <v>118</v>
       </c>
       <c r="B102" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C102" t="n">
-        <v>66.7</v>
+        <v>63.9</v>
       </c>
       <c r="D102" t="n">
-        <v>23.5</v>
+        <v>31.4</v>
       </c>
       <c r="E102" t="n">
-        <v>43.2</v>
+        <v>32.5</v>
       </c>
       <c r="F102" t="n">
-        <v>23.5</v>
+        <v>31.4</v>
       </c>
       <c r="G102" t="n">
-        <v>10.4</v>
+        <v>32</v>
       </c>
       <c r="H102" t="n">
-        <v>14.7</v>
+        <v>6.5</v>
       </c>
       <c r="I102" t="n">
-        <v>36</v>
+        <v>37.1</v>
       </c>
       <c r="J102" t="n">
-        <v>32</v>
+        <v>22.9</v>
       </c>
       <c r="K102" t="n">
-        <v>52.2</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="103">
@@ -4769,34 +4770,34 @@
         <v>119</v>
       </c>
       <c r="B103" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C103" t="n">
-        <v>63.9</v>
+        <v>79.3</v>
       </c>
       <c r="D103" t="n">
-        <v>31.4</v>
+        <v>35.4</v>
       </c>
       <c r="E103" t="n">
-        <v>32.5</v>
+        <v>43.9</v>
       </c>
       <c r="F103" t="n">
-        <v>31.4</v>
+        <v>35.4</v>
       </c>
       <c r="G103" t="n">
-        <v>32</v>
+        <v>26.2</v>
       </c>
       <c r="H103" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="I103" t="n">
-        <v>37.1</v>
+        <v>40.4</v>
       </c>
       <c r="J103" t="n">
-        <v>22.9</v>
+        <v>26.3</v>
       </c>
       <c r="K103" t="n">
-        <v>37.1</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="104">
@@ -4804,34 +4805,34 @@
         <v>120</v>
       </c>
       <c r="B104" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C104" t="n">
-        <v>79.3</v>
+        <v>58.3</v>
       </c>
       <c r="D104" t="n">
-        <v>35.4</v>
+        <v>28.3</v>
       </c>
       <c r="E104" t="n">
-        <v>43.9</v>
+        <v>30</v>
       </c>
       <c r="F104" t="n">
-        <v>35.4</v>
+        <v>28.3</v>
       </c>
       <c r="G104" t="n">
-        <v>26.2</v>
+        <v>17.7</v>
       </c>
       <c r="H104" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="I104" t="n">
-        <v>40.4</v>
+        <v>61</v>
       </c>
       <c r="J104" t="n">
-        <v>26.3</v>
+        <v>12.2</v>
       </c>
       <c r="K104" t="n">
-        <v>26.8</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="105">
@@ -4839,34 +4840,34 @@
         <v>121</v>
       </c>
       <c r="B105" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C105" t="n">
-        <v>58.3</v>
+        <v>51.2</v>
       </c>
       <c r="D105" t="n">
-        <v>28.3</v>
+        <v>25.7</v>
       </c>
       <c r="E105" t="n">
-        <v>30</v>
+        <v>25.5</v>
       </c>
       <c r="F105" t="n">
-        <v>28.3</v>
+        <v>25.7</v>
       </c>
       <c r="G105" t="n">
-        <v>17.7</v>
+        <v>8.6</v>
       </c>
       <c r="H105" t="n">
-        <v>6.8</v>
+        <v>10.6</v>
       </c>
       <c r="I105" t="n">
-        <v>61</v>
+        <v>60.3</v>
       </c>
       <c r="J105" t="n">
-        <v>12.2</v>
+        <v>14.3</v>
       </c>
       <c r="K105" t="n">
-        <v>51.2</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="106">
@@ -4874,34 +4875,34 @@
         <v>122</v>
       </c>
       <c r="B106" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C106" t="n">
-        <v>51.2</v>
+        <v>80</v>
       </c>
       <c r="D106" t="n">
-        <v>25.7</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="n">
-        <v>25.5</v>
+        <v>68.9</v>
       </c>
       <c r="F106" t="n">
-        <v>25.7</v>
+        <v>11.1</v>
       </c>
       <c r="G106" t="n">
-        <v>8.6</v>
+        <v>39.5</v>
       </c>
       <c r="H106" t="n">
-        <v>10.6</v>
+        <v>10</v>
       </c>
       <c r="I106" t="n">
-        <v>60.3</v>
+        <v>63.6</v>
       </c>
       <c r="J106" t="n">
-        <v>14.3</v>
+        <v>9.1</v>
       </c>
       <c r="K106" t="n">
-        <v>24.2</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="107">
@@ -4909,34 +4910,34 @@
         <v>123</v>
       </c>
       <c r="B107" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C107" t="n">
-        <v>80</v>
+        <v>73.7</v>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>27.3</v>
       </c>
       <c r="E107" t="n">
-        <v>68.9</v>
+        <v>46.4</v>
       </c>
       <c r="F107" t="n">
-        <v>11.1</v>
+        <v>27.3</v>
       </c>
       <c r="G107" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="H107" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I107" t="n">
         <v>39.5</v>
       </c>
-      <c r="H107" t="n">
-        <v>10</v>
-      </c>
-      <c r="I107" t="n">
-        <v>63.6</v>
-      </c>
       <c r="J107" t="n">
-        <v>9.1</v>
+        <v>30.3</v>
       </c>
       <c r="K107" t="n">
-        <v>45.5</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="108">
@@ -4944,34 +4945,34 @@
         <v>124</v>
       </c>
       <c r="B108" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C108" t="n">
-        <v>73.7</v>
+        <v>70</v>
       </c>
       <c r="D108" t="n">
-        <v>27.3</v>
+        <v>26.7</v>
       </c>
       <c r="E108" t="n">
-        <v>46.4</v>
+        <v>43.3</v>
       </c>
       <c r="F108" t="n">
-        <v>27.3</v>
+        <v>26.7</v>
       </c>
       <c r="G108" t="n">
-        <v>19.3</v>
+        <v>14.8</v>
       </c>
       <c r="H108" t="n">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="I108" t="n">
-        <v>39.5</v>
+        <v>60</v>
       </c>
       <c r="J108" t="n">
-        <v>30.3</v>
+        <v>30</v>
       </c>
       <c r="K108" t="n">
-        <v>42.1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="109">
@@ -4979,34 +4980,34 @@
         <v>125</v>
       </c>
       <c r="B109" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C109" t="n">
-        <v>70</v>
+        <v>60.5</v>
       </c>
       <c r="D109" t="n">
-        <v>26.7</v>
+        <v>20.8</v>
       </c>
       <c r="E109" t="n">
-        <v>43.3</v>
+        <v>39.7</v>
       </c>
       <c r="F109" t="n">
-        <v>26.7</v>
+        <v>20.8</v>
       </c>
       <c r="G109" t="n">
-        <v>14.8</v>
+        <v>20</v>
       </c>
       <c r="H109" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="I109" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J109" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K109" t="n">
-        <v>10</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="110">
@@ -5014,34 +5015,34 @@
         <v>126</v>
       </c>
       <c r="B110" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C110" t="n">
-        <v>60.5</v>
+        <v>70.5</v>
       </c>
       <c r="D110" t="n">
-        <v>20.8</v>
+        <v>28.8</v>
       </c>
       <c r="E110" t="n">
-        <v>39.7</v>
+        <v>41.7</v>
       </c>
       <c r="F110" t="n">
-        <v>20.8</v>
+        <v>28.8</v>
       </c>
       <c r="G110" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="H110" t="n">
-        <v>11.8</v>
+        <v>8.6</v>
       </c>
       <c r="I110" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J110" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
       <c r="K110" t="n">
-        <v>52.6</v>
+        <v>38</v>
       </c>
     </row>
     <row r="111">
@@ -5049,34 +5050,34 @@
         <v>127</v>
       </c>
       <c r="B111" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C111" t="n">
-        <v>70.5</v>
+        <v>74.7</v>
       </c>
       <c r="D111" t="n">
-        <v>28.8</v>
+        <v>25.4</v>
       </c>
       <c r="E111" t="n">
-        <v>41.7</v>
+        <v>49.3</v>
       </c>
       <c r="F111" t="n">
-        <v>28.8</v>
+        <v>25.4</v>
       </c>
       <c r="G111" t="n">
-        <v>34</v>
+        <v>29.2</v>
       </c>
       <c r="H111" t="n">
-        <v>8.6</v>
+        <v>10.1</v>
       </c>
       <c r="I111" t="n">
-        <v>51</v>
+        <v>41.1</v>
       </c>
       <c r="J111" t="n">
-        <v>14.3</v>
+        <v>25</v>
       </c>
       <c r="K111" t="n">
-        <v>38</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="112">
@@ -5084,34 +5085,34 @@
         <v>128</v>
       </c>
       <c r="B112" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C112" t="n">
-        <v>74.7</v>
+        <v>73.6</v>
       </c>
       <c r="D112" t="n">
-        <v>25.4</v>
+        <v>29.1</v>
       </c>
       <c r="E112" t="n">
-        <v>49.3</v>
+        <v>44.5</v>
       </c>
       <c r="F112" t="n">
-        <v>25.4</v>
+        <v>29.1</v>
       </c>
       <c r="G112" t="n">
-        <v>29.2</v>
+        <v>24.3</v>
       </c>
       <c r="H112" t="n">
-        <v>10.1</v>
+        <v>8.9</v>
       </c>
       <c r="I112" t="n">
-        <v>41.1</v>
+        <v>40.3</v>
       </c>
       <c r="J112" t="n">
-        <v>25</v>
+        <v>35.5</v>
       </c>
       <c r="K112" t="n">
-        <v>47.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="113">
@@ -5119,34 +5120,34 @@
         <v>129</v>
       </c>
       <c r="B113" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C113" t="n">
-        <v>73.6</v>
+        <v>69.7</v>
       </c>
       <c r="D113" t="n">
-        <v>29.1</v>
+        <v>23.8</v>
       </c>
       <c r="E113" t="n">
-        <v>44.5</v>
+        <v>45.9</v>
       </c>
       <c r="F113" t="n">
-        <v>29.1</v>
+        <v>23.8</v>
       </c>
       <c r="G113" t="n">
-        <v>24.3</v>
+        <v>16.7</v>
       </c>
       <c r="H113" t="n">
-        <v>8.9</v>
+        <v>15.4</v>
       </c>
       <c r="I113" t="n">
-        <v>40.3</v>
+        <v>47.1</v>
       </c>
       <c r="J113" t="n">
-        <v>35.5</v>
+        <v>5.9</v>
       </c>
       <c r="K113" t="n">
-        <v>51.6</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="114">
@@ -5154,63 +5155,63 @@
         <v>130</v>
       </c>
       <c r="B114" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C114" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="D114" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="E114" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="F114" t="n">
-        <v>23.8</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D114"/>
+      <c r="E114"/>
+      <c r="F114"/>
       <c r="G114" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>47.1</v>
+        <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>5.9</v>
+        <v>100</v>
       </c>
       <c r="K114" t="n">
-        <v>35.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
+        <v>132</v>
+      </c>
+      <c r="B115" t="s">
         <v>131</v>
-      </c>
-      <c r="B115" t="s">
-        <v>132</v>
       </c>
       <c r="C115" t="n">
         <v>100</v>
       </c>
-      <c r="D115"/>
-      <c r="E115"/>
-      <c r="F115"/>
+      <c r="D115" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="E115" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F115" t="n">
+        <v>57.1</v>
+      </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J115" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="116">
@@ -5218,34 +5219,34 @@
         <v>133</v>
       </c>
       <c r="B116" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C116" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="D116" t="n">
-        <v>57.1</v>
+        <v>60</v>
       </c>
       <c r="E116" t="n">
-        <v>42.9</v>
+        <v>6.7</v>
       </c>
       <c r="F116" t="n">
-        <v>57.1</v>
+        <v>60</v>
       </c>
       <c r="G116" t="n">
-        <v>22.2</v>
+        <v>33.3</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I116" t="n">
         <v>25</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K116" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -5253,34 +5254,34 @@
         <v>134</v>
       </c>
       <c r="B117" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C117" t="n">
-        <v>66.7</v>
+        <v>60.4</v>
       </c>
       <c r="D117" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
       <c r="E117" t="n">
-        <v>6.7</v>
+        <v>27.1</v>
       </c>
       <c r="F117" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
       <c r="G117" t="n">
-        <v>33.3</v>
+        <v>13.1</v>
       </c>
       <c r="H117" t="n">
-        <v>11.1</v>
+        <v>7.7</v>
       </c>
       <c r="I117" t="n">
-        <v>25</v>
+        <v>51.9</v>
       </c>
       <c r="J117" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="118">
@@ -5288,34 +5289,34 @@
         <v>135</v>
       </c>
       <c r="B118" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C118" t="n">
-        <v>60.4</v>
+        <v>35</v>
       </c>
       <c r="D118" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E118" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="F118" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="G118" t="n">
         <v>33.3</v>
       </c>
-      <c r="E118" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="F118" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G118" t="n">
-        <v>13.1</v>
-      </c>
       <c r="H118" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>51.9</v>
+        <v>50</v>
       </c>
       <c r="J118" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>42.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -5323,34 +5324,34 @@
         <v>136</v>
       </c>
       <c r="B119" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C119" t="n">
-        <v>35</v>
+        <v>69.6</v>
       </c>
       <c r="D119" t="n">
-        <v>13.3</v>
+        <v>31.4</v>
       </c>
       <c r="E119" t="n">
-        <v>21.7</v>
+        <v>38.2</v>
       </c>
       <c r="F119" t="n">
-        <v>13.3</v>
+        <v>31.4</v>
       </c>
       <c r="G119" t="n">
-        <v>33.3</v>
+        <v>40.6</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I119" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K119" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="120">
@@ -5358,34 +5359,34 @@
         <v>137</v>
       </c>
       <c r="B120" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C120" t="n">
-        <v>69.6</v>
+        <v>70.4</v>
       </c>
       <c r="D120" t="n">
-        <v>31.4</v>
+        <v>28.2</v>
       </c>
       <c r="E120" t="n">
-        <v>38.2</v>
+        <v>42.2</v>
       </c>
       <c r="F120" t="n">
-        <v>31.4</v>
+        <v>28.2</v>
       </c>
       <c r="G120" t="n">
-        <v>40.6</v>
+        <v>36.6</v>
       </c>
       <c r="H120" t="n">
-        <v>16.7</v>
+        <v>8.3</v>
       </c>
       <c r="I120" t="n">
-        <v>80</v>
+        <v>33.3</v>
       </c>
       <c r="J120" t="n">
-        <v>10</v>
+        <v>33.3</v>
       </c>
       <c r="K120" t="n">
-        <v>60</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="121">
@@ -5393,34 +5394,34 @@
         <v>138</v>
       </c>
       <c r="B121" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C121" t="n">
-        <v>70.4</v>
+        <v>60.6</v>
       </c>
       <c r="D121" t="n">
-        <v>28.2</v>
+        <v>25.6</v>
       </c>
       <c r="E121" t="n">
-        <v>42.2</v>
+        <v>35</v>
       </c>
       <c r="F121" t="n">
-        <v>28.2</v>
+        <v>25.6</v>
       </c>
       <c r="G121" t="n">
-        <v>36.6</v>
+        <v>19</v>
       </c>
       <c r="H121" t="n">
-        <v>8.3</v>
+        <v>9.3</v>
       </c>
       <c r="I121" t="n">
-        <v>33.3</v>
+        <v>60</v>
       </c>
       <c r="J121" t="n">
-        <v>33.3</v>
+        <v>14.3</v>
       </c>
       <c r="K121" t="n">
-        <v>37.9</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="122">
@@ -5428,34 +5429,34 @@
         <v>139</v>
       </c>
       <c r="B122" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C122" t="n">
-        <v>60.6</v>
+        <v>66.7</v>
       </c>
       <c r="D122" t="n">
-        <v>25.6</v>
+        <v>0</v>
       </c>
       <c r="E122" t="n">
-        <v>35</v>
+        <v>66.7</v>
       </c>
       <c r="F122" t="n">
-        <v>25.6</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>19</v>
+        <v>18.2</v>
       </c>
       <c r="H122" t="n">
-        <v>9.3</v>
+        <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="J122" t="n">
-        <v>14.3</v>
+        <v>25</v>
       </c>
       <c r="K122" t="n">
-        <v>34.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -5463,34 +5464,34 @@
         <v>140</v>
       </c>
       <c r="B123" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C123" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E123" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G123" t="n">
-        <v>18.2</v>
+        <v>38.5</v>
       </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="I123" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="J123" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="124">
@@ -5498,34 +5499,34 @@
         <v>141</v>
       </c>
       <c r="B124" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C124" t="n">
-        <v>60</v>
+        <v>51.9</v>
       </c>
       <c r="D124" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E124" t="n">
-        <v>40</v>
+        <v>36.9</v>
       </c>
       <c r="F124" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G124" t="n">
-        <v>38.5</v>
+        <v>30</v>
       </c>
       <c r="H124" t="n">
-        <v>11.8</v>
+        <v>13.3</v>
       </c>
       <c r="I124" t="n">
-        <v>90</v>
+        <v>71.4</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="K124" t="n">
-        <v>40</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="125">
@@ -5533,34 +5534,34 @@
         <v>142</v>
       </c>
       <c r="B125" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C125" t="n">
-        <v>51.9</v>
+        <v>63.6</v>
       </c>
       <c r="D125" t="n">
-        <v>15</v>
+        <v>26.3</v>
       </c>
       <c r="E125" t="n">
-        <v>36.9</v>
+        <v>37.3</v>
       </c>
       <c r="F125" t="n">
-        <v>15</v>
+        <v>26.3</v>
       </c>
       <c r="G125" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H125" t="n">
-        <v>13.3</v>
+        <v>8.1</v>
       </c>
       <c r="I125" t="n">
-        <v>71.4</v>
+        <v>36.1</v>
       </c>
       <c r="J125" t="n">
-        <v>28.6</v>
+        <v>25</v>
       </c>
       <c r="K125" t="n">
-        <v>57.1</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="126">
@@ -5568,34 +5569,34 @@
         <v>143</v>
       </c>
       <c r="B126" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C126" t="n">
-        <v>63.6</v>
+        <v>100</v>
       </c>
       <c r="D126" t="n">
-        <v>26.3</v>
+        <v>33.3</v>
       </c>
       <c r="E126" t="n">
-        <v>37.3</v>
+        <v>66.7</v>
       </c>
       <c r="F126" t="n">
-        <v>26.3</v>
+        <v>33.3</v>
       </c>
       <c r="G126" t="n">
-        <v>28</v>
+        <v>11.1</v>
       </c>
       <c r="H126" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>36.1</v>
+        <v>20</v>
       </c>
       <c r="J126" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="K126" t="n">
-        <v>55.6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="127">
@@ -5603,34 +5604,34 @@
         <v>144</v>
       </c>
       <c r="B127" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C127" t="n">
-        <v>100</v>
+        <v>64.4</v>
       </c>
       <c r="D127" t="n">
-        <v>33.3</v>
+        <v>27</v>
       </c>
       <c r="E127" t="n">
-        <v>66.7</v>
+        <v>37.4</v>
       </c>
       <c r="F127" t="n">
-        <v>33.3</v>
+        <v>27</v>
       </c>
       <c r="G127" t="n">
-        <v>11.1</v>
+        <v>21.4</v>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="I127" t="n">
-        <v>20</v>
+        <v>61.9</v>
       </c>
       <c r="J127" t="n">
-        <v>40</v>
+        <v>21.4</v>
       </c>
       <c r="K127" t="n">
-        <v>20</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="128">
@@ -5638,34 +5639,34 @@
         <v>145</v>
       </c>
       <c r="B128" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C128" t="n">
-        <v>64.4</v>
+        <v>100</v>
       </c>
       <c r="D128" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E128" t="n">
-        <v>37.4</v>
+        <v>80</v>
       </c>
       <c r="F128" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G128" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>61.9</v>
+        <v>50</v>
       </c>
       <c r="J128" t="n">
-        <v>21.4</v>
+        <v>25</v>
       </c>
       <c r="K128" t="n">
-        <v>31.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -5673,34 +5674,34 @@
         <v>146</v>
       </c>
       <c r="B129" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C129" t="n">
-        <v>100</v>
+        <v>53.6</v>
       </c>
       <c r="D129" t="n">
-        <v>20</v>
+        <v>24.4</v>
       </c>
       <c r="E129" t="n">
-        <v>80</v>
+        <v>29.2</v>
       </c>
       <c r="F129" t="n">
-        <v>20</v>
+        <v>24.4</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>50</v>
+        <v>39.4</v>
       </c>
       <c r="J129" t="n">
-        <v>25</v>
+        <v>27.3</v>
       </c>
       <c r="K129" t="n">
-        <v>0</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="130">
@@ -5708,34 +5709,34 @@
         <v>147</v>
       </c>
       <c r="B130" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C130" t="n">
-        <v>53.6</v>
+        <v>78.6</v>
       </c>
       <c r="D130" t="n">
-        <v>24.4</v>
+        <v>12.5</v>
       </c>
       <c r="E130" t="n">
-        <v>29.2</v>
+        <v>66.1</v>
       </c>
       <c r="F130" t="n">
-        <v>24.4</v>
+        <v>12.5</v>
       </c>
       <c r="G130" t="n">
-        <v>24</v>
+        <v>35.3</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>39.4</v>
+        <v>28.6</v>
       </c>
       <c r="J130" t="n">
-        <v>27.3</v>
+        <v>14.3</v>
       </c>
       <c r="K130" t="n">
-        <v>45.5</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="131">
@@ -5743,34 +5744,34 @@
         <v>148</v>
       </c>
       <c r="B131" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C131" t="n">
-        <v>78.6</v>
+        <v>59.3</v>
       </c>
       <c r="D131" t="n">
-        <v>12.5</v>
+        <v>7.1</v>
       </c>
       <c r="E131" t="n">
-        <v>66.1</v>
+        <v>52.2</v>
       </c>
       <c r="F131" t="n">
-        <v>12.5</v>
+        <v>7.1</v>
       </c>
       <c r="G131" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H131" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="I131" t="n">
+        <v>50</v>
+      </c>
+      <c r="J131" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="K131" t="n">
         <v>35.3</v>
-      </c>
-      <c r="H131" t="n">
-        <v>0</v>
-      </c>
-      <c r="I131" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="J131" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K131" t="n">
-        <v>14.3</v>
       </c>
     </row>
     <row r="132">
@@ -5778,34 +5779,34 @@
         <v>149</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C132" t="n">
-        <v>59.3</v>
+        <v>63.2</v>
       </c>
       <c r="D132" t="n">
-        <v>7.1</v>
+        <v>45</v>
       </c>
       <c r="E132" t="n">
-        <v>52.2</v>
+        <v>18.2</v>
       </c>
       <c r="F132" t="n">
-        <v>7.1</v>
+        <v>45</v>
       </c>
       <c r="G132" t="n">
-        <v>5.8</v>
+        <v>26.9</v>
       </c>
       <c r="H132" t="n">
-        <v>8.3</v>
+        <v>7.7</v>
       </c>
       <c r="I132" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>11.1</v>
+        <v>25</v>
       </c>
       <c r="K132" t="n">
-        <v>35.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="133">
@@ -5813,34 +5814,34 @@
         <v>150</v>
       </c>
       <c r="B133" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C133" t="n">
-        <v>63.2</v>
+        <v>74.7</v>
       </c>
       <c r="D133" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="E133" t="n">
-        <v>18.2</v>
+        <v>58.7</v>
       </c>
       <c r="F133" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="G133" t="n">
-        <v>26.9</v>
+        <v>25.5</v>
       </c>
       <c r="H133" t="n">
-        <v>7.7</v>
+        <v>16.9</v>
       </c>
       <c r="I133" t="n">
-        <v>0</v>
+        <v>27.5</v>
       </c>
       <c r="J133" t="n">
-        <v>25</v>
+        <v>42.5</v>
       </c>
       <c r="K133" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="134">
@@ -5848,34 +5849,34 @@
         <v>151</v>
       </c>
       <c r="B134" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C134" t="n">
-        <v>74.7</v>
+        <v>74.4</v>
       </c>
       <c r="D134" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E134" t="n">
-        <v>58.7</v>
+        <v>43.4</v>
       </c>
       <c r="F134" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G134" t="n">
-        <v>25.5</v>
+        <v>10.5</v>
       </c>
       <c r="H134" t="n">
-        <v>16.9</v>
+        <v>1.6</v>
       </c>
       <c r="I134" t="n">
-        <v>27.5</v>
+        <v>44.4</v>
       </c>
       <c r="J134" t="n">
-        <v>42.5</v>
+        <v>25.9</v>
       </c>
       <c r="K134" t="n">
-        <v>40</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="135">
@@ -5883,69 +5884,69 @@
         <v>152</v>
       </c>
       <c r="B135" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="C135" t="n">
-        <v>74.4</v>
+        <v>73.4</v>
       </c>
       <c r="D135" t="n">
-        <v>31</v>
+        <v>22.6</v>
       </c>
       <c r="E135" t="n">
-        <v>43.4</v>
+        <v>50.8</v>
       </c>
       <c r="F135" t="n">
-        <v>31</v>
+        <v>22.6</v>
       </c>
       <c r="G135" t="n">
-        <v>10.5</v>
+        <v>33</v>
       </c>
       <c r="H135" t="n">
-        <v>1.6</v>
+        <v>9.7</v>
       </c>
       <c r="I135" t="n">
-        <v>44.4</v>
+        <v>53.8</v>
       </c>
       <c r="J135" t="n">
-        <v>25.9</v>
+        <v>20.5</v>
       </c>
       <c r="K135" t="n">
-        <v>35.2</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
+        <v>154</v>
+      </c>
+      <c r="B136" t="s">
         <v>153</v>
       </c>
-      <c r="B136" t="s">
-        <v>154</v>
-      </c>
       <c r="C136" t="n">
-        <v>73.4</v>
+        <v>69.6</v>
       </c>
       <c r="D136" t="n">
-        <v>22.6</v>
+        <v>25.5</v>
       </c>
       <c r="E136" t="n">
-        <v>50.8</v>
+        <v>44.1</v>
       </c>
       <c r="F136" t="n">
-        <v>22.6</v>
+        <v>25.5</v>
       </c>
       <c r="G136" t="n">
-        <v>33</v>
+        <v>17.1</v>
       </c>
       <c r="H136" t="n">
-        <v>9.7</v>
+        <v>5.5</v>
       </c>
       <c r="I136" t="n">
-        <v>53.8</v>
+        <v>56.2</v>
       </c>
       <c r="J136" t="n">
-        <v>20.5</v>
+        <v>16.7</v>
       </c>
       <c r="K136" t="n">
-        <v>39.4</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="137">
@@ -5953,34 +5954,34 @@
         <v>155</v>
       </c>
       <c r="B137" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C137" t="n">
-        <v>69.6</v>
+        <v>64.6</v>
       </c>
       <c r="D137" t="n">
-        <v>25.5</v>
+        <v>16.7</v>
       </c>
       <c r="E137" t="n">
-        <v>44.1</v>
+        <v>47.9</v>
       </c>
       <c r="F137" t="n">
-        <v>25.5</v>
+        <v>16.7</v>
       </c>
       <c r="G137" t="n">
-        <v>17.1</v>
+        <v>37.7</v>
       </c>
       <c r="H137" t="n">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="I137" t="n">
-        <v>56.2</v>
+        <v>29.6</v>
       </c>
       <c r="J137" t="n">
-        <v>16.7</v>
+        <v>48.1</v>
       </c>
       <c r="K137" t="n">
-        <v>36.4</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="138">
@@ -5988,34 +5989,34 @@
         <v>156</v>
       </c>
       <c r="B138" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C138" t="n">
-        <v>64.6</v>
+        <v>57.9</v>
       </c>
       <c r="D138" t="n">
+        <v>20</v>
+      </c>
+      <c r="E138" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="F138" t="n">
+        <v>20</v>
+      </c>
+      <c r="G138" t="n">
+        <v>40</v>
+      </c>
+      <c r="H138" t="n">
         <v>16.7</v>
       </c>
-      <c r="E138" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="F138" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="G138" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="H138" t="n">
-        <v>12.5</v>
-      </c>
       <c r="I138" t="n">
-        <v>29.6</v>
+        <v>21.4</v>
       </c>
       <c r="J138" t="n">
-        <v>48.1</v>
+        <v>50</v>
       </c>
       <c r="K138" t="n">
-        <v>38.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="139">
@@ -6023,34 +6024,34 @@
         <v>157</v>
       </c>
       <c r="B139" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C139" t="n">
-        <v>57.9</v>
+        <v>64.7</v>
       </c>
       <c r="D139" t="n">
-        <v>20</v>
+        <v>17.2</v>
       </c>
       <c r="E139" t="n">
-        <v>37.9</v>
+        <v>47.5</v>
       </c>
       <c r="F139" t="n">
-        <v>20</v>
+        <v>17.2</v>
       </c>
       <c r="G139" t="n">
-        <v>40</v>
+        <v>10.7</v>
       </c>
       <c r="H139" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="I139" t="n">
-        <v>21.4</v>
+        <v>64.6</v>
       </c>
       <c r="J139" t="n">
-        <v>50</v>
+        <v>18.5</v>
       </c>
       <c r="K139" t="n">
-        <v>25</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="140">
@@ -6058,34 +6059,34 @@
         <v>158</v>
       </c>
       <c r="B140" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C140" t="n">
-        <v>64.7</v>
+        <v>81</v>
       </c>
       <c r="D140" t="n">
-        <v>17.2</v>
+        <v>23.3</v>
       </c>
       <c r="E140" t="n">
-        <v>47.5</v>
+        <v>57.7</v>
       </c>
       <c r="F140" t="n">
-        <v>17.2</v>
+        <v>23.3</v>
       </c>
       <c r="G140" t="n">
-        <v>10.7</v>
+        <v>22.1</v>
       </c>
       <c r="H140" t="n">
-        <v>18.1</v>
+        <v>10.6</v>
       </c>
       <c r="I140" t="n">
-        <v>64.6</v>
+        <v>34.9</v>
       </c>
       <c r="J140" t="n">
-        <v>18.5</v>
+        <v>34.9</v>
       </c>
       <c r="K140" t="n">
-        <v>37.7</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="141">
@@ -6093,34 +6094,34 @@
         <v>159</v>
       </c>
       <c r="B141" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C141" t="n">
-        <v>81</v>
+        <v>53.5</v>
       </c>
       <c r="D141" t="n">
-        <v>23.3</v>
+        <v>20.5</v>
       </c>
       <c r="E141" t="n">
-        <v>57.7</v>
+        <v>33</v>
       </c>
       <c r="F141" t="n">
-        <v>23.3</v>
+        <v>20.5</v>
       </c>
       <c r="G141" t="n">
-        <v>22.1</v>
+        <v>23.5</v>
       </c>
       <c r="H141" t="n">
-        <v>10.6</v>
+        <v>13.9</v>
       </c>
       <c r="I141" t="n">
-        <v>34.9</v>
+        <v>51.3</v>
       </c>
       <c r="J141" t="n">
-        <v>34.9</v>
+        <v>23.1</v>
       </c>
       <c r="K141" t="n">
-        <v>37.9</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="142">
@@ -6128,34 +6129,34 @@
         <v>160</v>
       </c>
       <c r="B142" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C142" t="n">
-        <v>53.5</v>
+        <v>54</v>
       </c>
       <c r="D142" t="n">
-        <v>20.5</v>
+        <v>21.2</v>
       </c>
       <c r="E142" t="n">
-        <v>33</v>
+        <v>32.8</v>
       </c>
       <c r="F142" t="n">
-        <v>20.5</v>
+        <v>21.2</v>
       </c>
       <c r="G142" t="n">
-        <v>23.5</v>
+        <v>13</v>
       </c>
       <c r="H142" t="n">
-        <v>13.9</v>
+        <v>17.7</v>
       </c>
       <c r="I142" t="n">
-        <v>51.3</v>
+        <v>43.2</v>
       </c>
       <c r="J142" t="n">
-        <v>23.1</v>
+        <v>27.3</v>
       </c>
       <c r="K142" t="n">
-        <v>28.6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="143">
@@ -6163,34 +6164,34 @@
         <v>161</v>
       </c>
       <c r="B143" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C143" t="n">
-        <v>54</v>
+        <v>57.8</v>
       </c>
       <c r="D143" t="n">
-        <v>21.2</v>
+        <v>23</v>
       </c>
       <c r="E143" t="n">
-        <v>32.8</v>
+        <v>34.8</v>
       </c>
       <c r="F143" t="n">
-        <v>21.2</v>
+        <v>23</v>
       </c>
       <c r="G143" t="n">
-        <v>13</v>
+        <v>9.5</v>
       </c>
       <c r="H143" t="n">
-        <v>17.7</v>
+        <v>7.9</v>
       </c>
       <c r="I143" t="n">
-        <v>43.2</v>
+        <v>59.2</v>
       </c>
       <c r="J143" t="n">
-        <v>27.3</v>
+        <v>18.4</v>
       </c>
       <c r="K143" t="n">
-        <v>50</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="144">
@@ -6198,34 +6199,34 @@
         <v>162</v>
       </c>
       <c r="B144" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C144" t="n">
-        <v>57.8</v>
+        <v>72.6</v>
       </c>
       <c r="D144" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="E144" t="n">
-        <v>34.8</v>
+        <v>55.1</v>
       </c>
       <c r="F144" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="G144" t="n">
-        <v>9.5</v>
+        <v>27.3</v>
       </c>
       <c r="H144" t="n">
-        <v>7.9</v>
+        <v>13.5</v>
       </c>
       <c r="I144" t="n">
-        <v>59.2</v>
+        <v>30.5</v>
       </c>
       <c r="J144" t="n">
-        <v>18.4</v>
+        <v>33.9</v>
       </c>
       <c r="K144" t="n">
-        <v>29.2</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="145">
@@ -6233,34 +6234,34 @@
         <v>163</v>
       </c>
       <c r="B145" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C145" t="n">
-        <v>72.6</v>
+        <v>75</v>
       </c>
       <c r="D145" t="n">
-        <v>17.5</v>
+        <v>40</v>
       </c>
       <c r="E145" t="n">
-        <v>55.1</v>
+        <v>35</v>
       </c>
       <c r="F145" t="n">
-        <v>17.5</v>
+        <v>40</v>
       </c>
       <c r="G145" t="n">
-        <v>27.3</v>
+        <v>42.5</v>
       </c>
       <c r="H145" t="n">
-        <v>13.5</v>
+        <v>8.8</v>
       </c>
       <c r="I145" t="n">
-        <v>30.5</v>
+        <v>46.2</v>
       </c>
       <c r="J145" t="n">
-        <v>33.9</v>
+        <v>7.7</v>
       </c>
       <c r="K145" t="n">
-        <v>56.9</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="146">
@@ -6268,34 +6269,34 @@
         <v>164</v>
       </c>
       <c r="B146" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C146" t="n">
         <v>75</v>
       </c>
       <c r="D146" t="n">
-        <v>40</v>
+        <v>24.3</v>
       </c>
       <c r="E146" t="n">
-        <v>35</v>
+        <v>50.7</v>
       </c>
       <c r="F146" t="n">
-        <v>40</v>
+        <v>24.3</v>
       </c>
       <c r="G146" t="n">
-        <v>42.5</v>
+        <v>17.3</v>
       </c>
       <c r="H146" t="n">
-        <v>8.8</v>
+        <v>8</v>
       </c>
       <c r="I146" t="n">
-        <v>46.2</v>
+        <v>32.3</v>
       </c>
       <c r="J146" t="n">
-        <v>7.7</v>
+        <v>30.6</v>
       </c>
       <c r="K146" t="n">
-        <v>69.2</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="147">
@@ -6303,57 +6304,51 @@
         <v>165</v>
       </c>
       <c r="B147" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C147" t="n">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="D147" t="n">
-        <v>24.3</v>
+        <v>33.3</v>
       </c>
       <c r="E147" t="n">
-        <v>50.7</v>
+        <v>4.2</v>
       </c>
       <c r="F147" t="n">
-        <v>24.3</v>
+        <v>33.3</v>
       </c>
       <c r="G147" t="n">
-        <v>17.3</v>
+        <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>8</v>
-      </c>
-      <c r="I147" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="J147" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="K147" t="n">
-        <v>44.4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I147"/>
+      <c r="J147"/>
+      <c r="K147"/>
     </row>
     <row r="148">
       <c r="A148" t="s">
         <v>166</v>
       </c>
       <c r="B148" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C148" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="D148" t="n">
         <v>33.3</v>
       </c>
       <c r="E148" t="n">
-        <v>4.2</v>
+        <v>-33.3</v>
       </c>
       <c r="F148" t="n">
         <v>33.3</v>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -6363,65 +6358,36 @@
       <c r="K148"/>
     </row>
     <row r="149">
-      <c r="A149" t="s">
+      <c r="A149"/>
+      <c r="B149" t="s">
         <v>167</v>
       </c>
-      <c r="B149" t="s">
-        <v>154</v>
-      </c>
       <c r="C149" t="n">
-        <v>0</v>
+        <v>68.3</v>
       </c>
       <c r="D149" t="n">
-        <v>33.3</v>
+        <v>27</v>
       </c>
       <c r="E149" t="n">
-        <v>-33.3</v>
+        <v>41</v>
       </c>
       <c r="F149" t="n">
-        <v>33.3</v>
+        <v>27</v>
       </c>
       <c r="G149" t="n">
-        <v>100</v>
+        <v>26.4</v>
       </c>
       <c r="H149" t="n">
-        <v>0</v>
-      </c>
-      <c r="I149"/>
-      <c r="J149"/>
-      <c r="K149"/>
-    </row>
-    <row r="150">
-      <c r="A150"/>
-      <c r="B150" t="s">
-        <v>168</v>
-      </c>
-      <c r="C150" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="D150" t="n">
-        <v>27</v>
-      </c>
-      <c r="E150" t="n">
-        <v>41</v>
-      </c>
-      <c r="F150" t="n">
-        <v>27</v>
-      </c>
-      <c r="G150" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="H150" t="n">
         <v>9.5</v>
       </c>
-      <c r="I150" t="n">
+      <c r="I149" t="n">
         <v>48.5</v>
       </c>
-      <c r="J150" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="K150" t="n">
-        <v>39.2</v>
+      <c r="J149" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="K149" t="n">
+        <v>39.1</v>
       </c>
     </row>
   </sheetData>
@@ -6453,22 +6419,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>171</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -6477,18 +6443,18 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -6558,7 +6524,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -6593,7 +6559,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -6628,7 +6594,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -6663,7 +6629,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -6698,7 +6664,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -6768,7 +6734,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
@@ -6803,7 +6769,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -6838,7 +6804,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -6873,7 +6839,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -6941,7 +6907,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
@@ -6976,7 +6942,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s">
         <v>31</v>
@@ -7011,7 +6977,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s">
         <v>31</v>
@@ -7046,7 +7012,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
@@ -7081,7 +7047,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B19" t="s">
         <v>31</v>
@@ -7116,7 +7082,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B20" t="s">
         <v>31</v>
@@ -7151,7 +7117,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B21" t="s">
         <v>31</v>
@@ -7186,7 +7152,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B22" t="s">
         <v>31</v>
@@ -7221,7 +7187,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B23" t="s">
         <v>31</v>
@@ -7256,7 +7222,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
@@ -7291,7 +7257,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
@@ -7326,7 +7292,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B26" t="s">
         <v>31</v>
@@ -7361,7 +7327,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B27" t="s">
         <v>31</v>
@@ -7396,7 +7362,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B28" t="s">
         <v>31</v>
@@ -7431,7 +7397,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B29" t="s">
         <v>46</v>
@@ -7466,7 +7432,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B30" t="s">
         <v>46</v>
@@ -7536,7 +7502,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B32" t="s">
         <v>46</v>
@@ -7571,7 +7537,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B33" t="s">
         <v>46</v>
@@ -7606,7 +7572,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B34" t="s">
         <v>46</v>
@@ -7641,7 +7607,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B35" t="s">
         <v>46</v>
@@ -7674,7 +7640,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B36" t="s">
         <v>46</v>
@@ -7709,7 +7675,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B37" t="s">
         <v>46</v>
@@ -7744,7 +7710,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B38" t="s">
         <v>46</v>
@@ -7779,7 +7745,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B39" t="s">
         <v>46</v>
@@ -7814,7 +7780,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B40" t="s">
         <v>46</v>
@@ -7849,7 +7815,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
@@ -7882,7 +7848,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B42" t="s">
         <v>46</v>
@@ -7917,7 +7883,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B43" t="s">
         <v>62</v>
@@ -7952,7 +7918,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B44" t="s">
         <v>62</v>
@@ -7987,7 +7953,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B45" t="s">
         <v>62</v>
@@ -8022,7 +7988,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B46" t="s">
         <v>62</v>
@@ -8055,7 +8021,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B47" t="s">
         <v>62</v>
@@ -8090,7 +8056,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B48" t="s">
         <v>62</v>
@@ -8125,7 +8091,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B49" t="s">
         <v>62</v>
@@ -8158,7 +8124,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B50" t="s">
         <v>62</v>
@@ -8193,7 +8159,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B51" t="s">
         <v>62</v>
@@ -8228,7 +8194,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B52" t="s">
         <v>62</v>
@@ -8263,7 +8229,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B53" t="s">
         <v>62</v>
@@ -8298,7 +8264,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B54" t="s">
         <v>62</v>
@@ -8331,7 +8297,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B55" t="s">
         <v>62</v>
@@ -8366,7 +8332,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B56" t="s">
         <v>62</v>
@@ -8401,7 +8367,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B57" t="s">
         <v>62</v>
@@ -8436,10 +8402,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B58" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C58" t="n">
         <v>69.5</v>
@@ -8471,10 +8437,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B59" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C59" t="n">
         <v>68.2</v>
@@ -8506,10 +8472,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B60" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C60" t="n">
         <v>50</v>
@@ -8541,10 +8507,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B61" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C61" t="n">
         <v>46.4</v>
@@ -8576,10 +8542,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B62" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C62" t="n">
         <v>64.7</v>
@@ -8611,10 +8577,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B63" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C63" t="n">
         <v>61.1</v>
@@ -8646,10 +8612,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B64" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C64" t="n">
         <v>69.4</v>
@@ -8681,10 +8647,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B65" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C65" t="n">
         <v>58.3</v>
@@ -8716,10 +8682,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B66" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C66" t="n">
         <v>66.7</v>
@@ -8751,10 +8717,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B67" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C67" t="n">
         <v>65</v>
@@ -8786,10 +8752,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B68" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C68" t="n">
         <v>63.1</v>
@@ -8821,10 +8787,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B69" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C69" t="n">
         <v>64.5</v>
@@ -8856,10 +8822,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B70" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C70" t="n">
         <v>42.4</v>
@@ -8891,10 +8857,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B71" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C71" t="n">
         <v>70.3</v>
@@ -8926,10 +8892,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B72" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C72" t="n">
         <v>49</v>
@@ -8961,10 +8927,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B73" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C73" t="n">
         <v>28.6</v>
@@ -8994,10 +8960,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B74" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C74" t="n">
         <v>48.6</v>
@@ -9029,10 +8995,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B75" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C75" t="n">
         <v>57.4</v>
@@ -9064,10 +9030,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B76" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C76" t="n">
         <v>64.9</v>
@@ -9099,10 +9065,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B77" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C77" t="n">
         <v>48.1</v>
@@ -9134,10 +9100,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B78" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C78" t="n">
         <v>68</v>
@@ -9169,10 +9135,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B79" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C79" t="n">
         <v>63.6</v>
@@ -9204,10 +9170,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B80" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C80" t="n">
         <v>52.2</v>
@@ -9239,10 +9205,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B81" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C81" t="n">
         <v>55.3</v>
@@ -9274,10 +9240,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B82" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C82" t="n">
         <v>70.4</v>
@@ -9309,10 +9275,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B83" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C83" t="n">
         <v>55.6</v>
@@ -9344,10 +9310,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B84" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C84" t="n">
         <v>59.8</v>
@@ -9379,10 +9345,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B85" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C85" t="n">
         <v>61.2</v>
@@ -9414,10 +9380,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B86" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C86" t="n">
         <v>71.1</v>
@@ -9449,10 +9415,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B87" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C87" t="n">
         <v>57.8</v>
@@ -9484,10 +9450,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B88" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C88" t="n">
         <v>71.9</v>
@@ -9519,10 +9485,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B89" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C89" t="n">
         <v>66.2</v>
@@ -9554,10 +9520,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B90" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C90" t="n">
         <v>70.4</v>
@@ -9589,10 +9555,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B91" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C91" t="n">
         <v>63.8</v>
@@ -9624,10 +9590,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B92" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C92" t="n">
         <v>50</v>
@@ -9659,10 +9625,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B93" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C93" t="n">
         <v>50.9</v>
@@ -9694,10 +9660,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B94" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C94" t="n">
         <v>62</v>
@@ -9729,10 +9695,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B95" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C95" t="n">
         <v>50</v>
@@ -9762,10 +9728,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B96" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C96" t="n">
         <v>68.8</v>
@@ -9797,10 +9763,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B97" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C97" t="n">
         <v>53.6</v>
@@ -9832,10 +9798,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B98" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C98" t="n">
         <v>50</v>
@@ -9867,10 +9833,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B99" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C99" t="n">
         <v>66.7</v>
@@ -9902,10 +9868,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B100" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C100" t="n">
         <v>52.6</v>
@@ -9937,10 +9903,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B101" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C101" t="n">
         <v>59.2</v>
@@ -9972,10 +9938,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B102" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C102" t="n">
         <v>57.6</v>
@@ -10007,10 +9973,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B103" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C103" t="n">
         <v>44</v>
@@ -10042,10 +10008,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B104" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C104" t="n">
         <v>38.9</v>
@@ -10077,10 +10043,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B105" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C105" t="n">
         <v>62</v>
@@ -10112,10 +10078,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B106" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C106" t="n">
         <v>57.8</v>
@@ -10147,10 +10113,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B107" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C107" t="n">
         <v>64.2</v>
@@ -10182,10 +10148,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B108" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C108" t="n">
         <v>55.4</v>
@@ -10217,10 +10183,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B109" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C109" t="n">
         <v>59</v>
@@ -10252,10 +10218,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B110" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C110" t="n">
         <v>62.5</v>
@@ -10287,10 +10253,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B111" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C111" t="n">
         <v>64.1</v>
@@ -10322,10 +10288,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B112" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C112" t="n">
         <v>84.6</v>
@@ -10355,10 +10321,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B113" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C113" t="n">
         <v>50</v>
@@ -10390,10 +10356,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B114" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C114" t="n">
         <v>61.3</v>
@@ -10425,10 +10391,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B115" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C115" t="n">
         <v>65.8</v>
@@ -10460,10 +10426,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B116" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C116" t="n">
         <v>50.6</v>
@@ -10495,10 +10461,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B117" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C117" t="n">
         <v>66.7</v>
@@ -10530,10 +10496,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B118" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C118" t="n">
         <v>68.5</v>
@@ -10565,10 +10531,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B119" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C119" t="n">
         <v>61.7</v>
@@ -10601,7 +10567,7 @@
     <row r="120">
       <c r="A120"/>
       <c r="B120" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C120" t="n">
         <v>57.7</v>

--- a/data/summary2026.xlsx
+++ b/data/summary2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="277">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -448,9 +448,6 @@
   </si>
   <si>
     <t xml:space="preserve">Matt Brandt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matt Fabian</t>
   </si>
   <si>
     <t xml:space="preserve">Matthew Fabian</t>
@@ -901,8 +898,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K149" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K149"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K148" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K148"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -5642,31 +5639,31 @@
         <v>131</v>
       </c>
       <c r="C128" t="n">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="D128" t="n">
-        <v>20</v>
+        <v>23.9</v>
       </c>
       <c r="E128" t="n">
-        <v>80</v>
+        <v>31.7</v>
       </c>
       <c r="F128" t="n">
-        <v>20</v>
+        <v>23.9</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>50</v>
+        <v>40.5</v>
       </c>
       <c r="J128" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K128" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="129">
@@ -5677,31 +5674,31 @@
         <v>131</v>
       </c>
       <c r="C129" t="n">
-        <v>53.6</v>
+        <v>78.6</v>
       </c>
       <c r="D129" t="n">
-        <v>24.4</v>
+        <v>12.5</v>
       </c>
       <c r="E129" t="n">
-        <v>29.2</v>
+        <v>66.1</v>
       </c>
       <c r="F129" t="n">
-        <v>24.4</v>
+        <v>12.5</v>
       </c>
       <c r="G129" t="n">
-        <v>24</v>
+        <v>35.3</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>39.4</v>
+        <v>28.6</v>
       </c>
       <c r="J129" t="n">
-        <v>27.3</v>
+        <v>14.3</v>
       </c>
       <c r="K129" t="n">
-        <v>45.5</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="130">
@@ -5712,31 +5709,31 @@
         <v>131</v>
       </c>
       <c r="C130" t="n">
-        <v>78.6</v>
+        <v>59.3</v>
       </c>
       <c r="D130" t="n">
-        <v>12.5</v>
+        <v>7.1</v>
       </c>
       <c r="E130" t="n">
-        <v>66.1</v>
+        <v>52.2</v>
       </c>
       <c r="F130" t="n">
-        <v>12.5</v>
+        <v>7.1</v>
       </c>
       <c r="G130" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H130" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="I130" t="n">
+        <v>50</v>
+      </c>
+      <c r="J130" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="K130" t="n">
         <v>35.3</v>
-      </c>
-      <c r="H130" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="J130" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K130" t="n">
-        <v>14.3</v>
       </c>
     </row>
     <row r="131">
@@ -5747,31 +5744,31 @@
         <v>131</v>
       </c>
       <c r="C131" t="n">
-        <v>59.3</v>
+        <v>63.2</v>
       </c>
       <c r="D131" t="n">
-        <v>7.1</v>
+        <v>45</v>
       </c>
       <c r="E131" t="n">
-        <v>52.2</v>
+        <v>18.2</v>
       </c>
       <c r="F131" t="n">
-        <v>7.1</v>
+        <v>45</v>
       </c>
       <c r="G131" t="n">
-        <v>5.8</v>
+        <v>26.9</v>
       </c>
       <c r="H131" t="n">
-        <v>8.3</v>
+        <v>7.7</v>
       </c>
       <c r="I131" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>11.1</v>
+        <v>25</v>
       </c>
       <c r="K131" t="n">
-        <v>35.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="132">
@@ -5782,31 +5779,31 @@
         <v>131</v>
       </c>
       <c r="C132" t="n">
-        <v>63.2</v>
+        <v>74.7</v>
       </c>
       <c r="D132" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="E132" t="n">
-        <v>18.2</v>
+        <v>58.7</v>
       </c>
       <c r="F132" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="G132" t="n">
-        <v>26.9</v>
+        <v>25.5</v>
       </c>
       <c r="H132" t="n">
-        <v>7.7</v>
+        <v>16.9</v>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>27.5</v>
       </c>
       <c r="J132" t="n">
-        <v>25</v>
+        <v>42.5</v>
       </c>
       <c r="K132" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="133">
@@ -5817,31 +5814,31 @@
         <v>131</v>
       </c>
       <c r="C133" t="n">
-        <v>74.7</v>
+        <v>74.4</v>
       </c>
       <c r="D133" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E133" t="n">
-        <v>58.7</v>
+        <v>43.4</v>
       </c>
       <c r="F133" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G133" t="n">
-        <v>25.5</v>
+        <v>10.5</v>
       </c>
       <c r="H133" t="n">
-        <v>16.9</v>
+        <v>1.6</v>
       </c>
       <c r="I133" t="n">
-        <v>27.5</v>
+        <v>44.4</v>
       </c>
       <c r="J133" t="n">
-        <v>42.5</v>
+        <v>25.9</v>
       </c>
       <c r="K133" t="n">
-        <v>40</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="134">
@@ -5849,69 +5846,69 @@
         <v>151</v>
       </c>
       <c r="B134" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="C134" t="n">
-        <v>74.4</v>
+        <v>73.4</v>
       </c>
       <c r="D134" t="n">
-        <v>31</v>
+        <v>22.6</v>
       </c>
       <c r="E134" t="n">
-        <v>43.4</v>
+        <v>50.8</v>
       </c>
       <c r="F134" t="n">
-        <v>31</v>
+        <v>22.6</v>
       </c>
       <c r="G134" t="n">
-        <v>10.5</v>
+        <v>33</v>
       </c>
       <c r="H134" t="n">
-        <v>1.6</v>
+        <v>9.7</v>
       </c>
       <c r="I134" t="n">
-        <v>44.4</v>
+        <v>53.8</v>
       </c>
       <c r="J134" t="n">
-        <v>25.9</v>
+        <v>20.5</v>
       </c>
       <c r="K134" t="n">
-        <v>35.2</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
+        <v>153</v>
+      </c>
+      <c r="B135" t="s">
         <v>152</v>
       </c>
-      <c r="B135" t="s">
-        <v>153</v>
-      </c>
       <c r="C135" t="n">
-        <v>73.4</v>
+        <v>69.6</v>
       </c>
       <c r="D135" t="n">
-        <v>22.6</v>
+        <v>25.5</v>
       </c>
       <c r="E135" t="n">
-        <v>50.8</v>
+        <v>44.1</v>
       </c>
       <c r="F135" t="n">
-        <v>22.6</v>
+        <v>25.5</v>
       </c>
       <c r="G135" t="n">
-        <v>33</v>
+        <v>17.1</v>
       </c>
       <c r="H135" t="n">
-        <v>9.7</v>
+        <v>5.5</v>
       </c>
       <c r="I135" t="n">
-        <v>53.8</v>
+        <v>56.2</v>
       </c>
       <c r="J135" t="n">
-        <v>20.5</v>
+        <v>16.7</v>
       </c>
       <c r="K135" t="n">
-        <v>39.4</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="136">
@@ -5919,34 +5916,34 @@
         <v>154</v>
       </c>
       <c r="B136" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C136" t="n">
-        <v>69.6</v>
+        <v>64.6</v>
       </c>
       <c r="D136" t="n">
-        <v>25.5</v>
+        <v>16.7</v>
       </c>
       <c r="E136" t="n">
-        <v>44.1</v>
+        <v>47.9</v>
       </c>
       <c r="F136" t="n">
-        <v>25.5</v>
+        <v>16.7</v>
       </c>
       <c r="G136" t="n">
-        <v>17.1</v>
+        <v>37.7</v>
       </c>
       <c r="H136" t="n">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="I136" t="n">
-        <v>56.2</v>
+        <v>29.6</v>
       </c>
       <c r="J136" t="n">
-        <v>16.7</v>
+        <v>48.1</v>
       </c>
       <c r="K136" t="n">
-        <v>36.4</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="137">
@@ -5954,34 +5951,34 @@
         <v>155</v>
       </c>
       <c r="B137" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C137" t="n">
-        <v>64.6</v>
+        <v>57.9</v>
       </c>
       <c r="D137" t="n">
+        <v>20</v>
+      </c>
+      <c r="E137" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="F137" t="n">
+        <v>20</v>
+      </c>
+      <c r="G137" t="n">
+        <v>40</v>
+      </c>
+      <c r="H137" t="n">
         <v>16.7</v>
       </c>
-      <c r="E137" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="F137" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="G137" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="H137" t="n">
-        <v>12.5</v>
-      </c>
       <c r="I137" t="n">
-        <v>29.6</v>
+        <v>21.4</v>
       </c>
       <c r="J137" t="n">
-        <v>48.1</v>
+        <v>50</v>
       </c>
       <c r="K137" t="n">
-        <v>38.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="138">
@@ -5989,34 +5986,34 @@
         <v>156</v>
       </c>
       <c r="B138" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C138" t="n">
-        <v>57.9</v>
+        <v>64.7</v>
       </c>
       <c r="D138" t="n">
-        <v>20</v>
+        <v>17.2</v>
       </c>
       <c r="E138" t="n">
-        <v>37.9</v>
+        <v>47.5</v>
       </c>
       <c r="F138" t="n">
-        <v>20</v>
+        <v>17.2</v>
       </c>
       <c r="G138" t="n">
-        <v>40</v>
+        <v>10.7</v>
       </c>
       <c r="H138" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="I138" t="n">
-        <v>21.4</v>
+        <v>64.6</v>
       </c>
       <c r="J138" t="n">
-        <v>50</v>
+        <v>18.5</v>
       </c>
       <c r="K138" t="n">
-        <v>25</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="139">
@@ -6024,34 +6021,34 @@
         <v>157</v>
       </c>
       <c r="B139" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C139" t="n">
-        <v>64.7</v>
+        <v>81</v>
       </c>
       <c r="D139" t="n">
-        <v>17.2</v>
+        <v>23.3</v>
       </c>
       <c r="E139" t="n">
-        <v>47.5</v>
+        <v>57.7</v>
       </c>
       <c r="F139" t="n">
-        <v>17.2</v>
+        <v>23.3</v>
       </c>
       <c r="G139" t="n">
-        <v>10.7</v>
+        <v>22.1</v>
       </c>
       <c r="H139" t="n">
-        <v>18.1</v>
+        <v>10.6</v>
       </c>
       <c r="I139" t="n">
-        <v>64.6</v>
+        <v>34.9</v>
       </c>
       <c r="J139" t="n">
-        <v>18.5</v>
+        <v>34.9</v>
       </c>
       <c r="K139" t="n">
-        <v>37.7</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="140">
@@ -6059,34 +6056,34 @@
         <v>158</v>
       </c>
       <c r="B140" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C140" t="n">
-        <v>81</v>
+        <v>53.5</v>
       </c>
       <c r="D140" t="n">
-        <v>23.3</v>
+        <v>20.5</v>
       </c>
       <c r="E140" t="n">
-        <v>57.7</v>
+        <v>33</v>
       </c>
       <c r="F140" t="n">
-        <v>23.3</v>
+        <v>20.5</v>
       </c>
       <c r="G140" t="n">
-        <v>22.1</v>
+        <v>23.5</v>
       </c>
       <c r="H140" t="n">
-        <v>10.6</v>
+        <v>13.9</v>
       </c>
       <c r="I140" t="n">
-        <v>34.9</v>
+        <v>51.3</v>
       </c>
       <c r="J140" t="n">
-        <v>34.9</v>
+        <v>23.1</v>
       </c>
       <c r="K140" t="n">
-        <v>37.9</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="141">
@@ -6094,34 +6091,34 @@
         <v>159</v>
       </c>
       <c r="B141" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C141" t="n">
-        <v>53.5</v>
+        <v>54</v>
       </c>
       <c r="D141" t="n">
-        <v>20.5</v>
+        <v>21.2</v>
       </c>
       <c r="E141" t="n">
-        <v>33</v>
+        <v>32.8</v>
       </c>
       <c r="F141" t="n">
-        <v>20.5</v>
+        <v>21.2</v>
       </c>
       <c r="G141" t="n">
-        <v>23.5</v>
+        <v>13</v>
       </c>
       <c r="H141" t="n">
-        <v>13.9</v>
+        <v>17.7</v>
       </c>
       <c r="I141" t="n">
-        <v>51.3</v>
+        <v>43.2</v>
       </c>
       <c r="J141" t="n">
-        <v>23.1</v>
+        <v>27.3</v>
       </c>
       <c r="K141" t="n">
-        <v>28.6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="142">
@@ -6129,34 +6126,34 @@
         <v>160</v>
       </c>
       <c r="B142" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C142" t="n">
-        <v>54</v>
+        <v>57.8</v>
       </c>
       <c r="D142" t="n">
-        <v>21.2</v>
+        <v>23</v>
       </c>
       <c r="E142" t="n">
-        <v>32.8</v>
+        <v>34.8</v>
       </c>
       <c r="F142" t="n">
-        <v>21.2</v>
+        <v>23</v>
       </c>
       <c r="G142" t="n">
-        <v>13</v>
+        <v>9.5</v>
       </c>
       <c r="H142" t="n">
-        <v>17.7</v>
+        <v>7.9</v>
       </c>
       <c r="I142" t="n">
-        <v>43.2</v>
+        <v>59.2</v>
       </c>
       <c r="J142" t="n">
-        <v>27.3</v>
+        <v>18.4</v>
       </c>
       <c r="K142" t="n">
-        <v>50</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="143">
@@ -6164,34 +6161,34 @@
         <v>161</v>
       </c>
       <c r="B143" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C143" t="n">
-        <v>57.8</v>
+        <v>72.6</v>
       </c>
       <c r="D143" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="E143" t="n">
-        <v>34.8</v>
+        <v>55.1</v>
       </c>
       <c r="F143" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="G143" t="n">
-        <v>9.5</v>
+        <v>27.3</v>
       </c>
       <c r="H143" t="n">
-        <v>7.9</v>
+        <v>13.5</v>
       </c>
       <c r="I143" t="n">
-        <v>59.2</v>
+        <v>30.5</v>
       </c>
       <c r="J143" t="n">
-        <v>18.4</v>
+        <v>33.9</v>
       </c>
       <c r="K143" t="n">
-        <v>29.2</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="144">
@@ -6199,34 +6196,34 @@
         <v>162</v>
       </c>
       <c r="B144" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C144" t="n">
-        <v>72.6</v>
+        <v>75</v>
       </c>
       <c r="D144" t="n">
-        <v>17.5</v>
+        <v>40</v>
       </c>
       <c r="E144" t="n">
-        <v>55.1</v>
+        <v>35</v>
       </c>
       <c r="F144" t="n">
-        <v>17.5</v>
+        <v>40</v>
       </c>
       <c r="G144" t="n">
-        <v>27.3</v>
+        <v>42.5</v>
       </c>
       <c r="H144" t="n">
-        <v>13.5</v>
+        <v>8.8</v>
       </c>
       <c r="I144" t="n">
-        <v>30.5</v>
+        <v>46.2</v>
       </c>
       <c r="J144" t="n">
-        <v>33.9</v>
+        <v>7.7</v>
       </c>
       <c r="K144" t="n">
-        <v>56.9</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="145">
@@ -6234,34 +6231,34 @@
         <v>163</v>
       </c>
       <c r="B145" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C145" t="n">
         <v>75</v>
       </c>
       <c r="D145" t="n">
-        <v>40</v>
+        <v>24.3</v>
       </c>
       <c r="E145" t="n">
-        <v>35</v>
+        <v>50.7</v>
       </c>
       <c r="F145" t="n">
-        <v>40</v>
+        <v>24.3</v>
       </c>
       <c r="G145" t="n">
-        <v>42.5</v>
+        <v>17.3</v>
       </c>
       <c r="H145" t="n">
-        <v>8.8</v>
+        <v>8</v>
       </c>
       <c r="I145" t="n">
-        <v>46.2</v>
+        <v>32.3</v>
       </c>
       <c r="J145" t="n">
-        <v>7.7</v>
+        <v>30.6</v>
       </c>
       <c r="K145" t="n">
-        <v>69.2</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="146">
@@ -6269,57 +6266,51 @@
         <v>164</v>
       </c>
       <c r="B146" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C146" t="n">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="D146" t="n">
-        <v>24.3</v>
+        <v>33.3</v>
       </c>
       <c r="E146" t="n">
-        <v>50.7</v>
+        <v>4.2</v>
       </c>
       <c r="F146" t="n">
-        <v>24.3</v>
+        <v>33.3</v>
       </c>
       <c r="G146" t="n">
-        <v>17.3</v>
+        <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>8</v>
-      </c>
-      <c r="I146" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="J146" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="K146" t="n">
-        <v>44.4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I146"/>
+      <c r="J146"/>
+      <c r="K146"/>
     </row>
     <row r="147">
       <c r="A147" t="s">
         <v>165</v>
       </c>
       <c r="B147" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C147" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="D147" t="n">
         <v>33.3</v>
       </c>
       <c r="E147" t="n">
-        <v>4.2</v>
+        <v>-33.3</v>
       </c>
       <c r="F147" t="n">
         <v>33.3</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -6329,65 +6320,36 @@
       <c r="K147"/>
     </row>
     <row r="148">
-      <c r="A148" t="s">
+      <c r="A148"/>
+      <c r="B148" t="s">
         <v>166</v>
       </c>
-      <c r="B148" t="s">
-        <v>153</v>
-      </c>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>68.1</v>
       </c>
       <c r="D148" t="n">
-        <v>33.3</v>
+        <v>27</v>
       </c>
       <c r="E148" t="n">
-        <v>-33.3</v>
+        <v>40.7</v>
       </c>
       <c r="F148" t="n">
-        <v>33.3</v>
+        <v>27</v>
       </c>
       <c r="G148" t="n">
-        <v>100</v>
+        <v>26.6</v>
       </c>
       <c r="H148" t="n">
-        <v>0</v>
-      </c>
-      <c r="I148"/>
-      <c r="J148"/>
-      <c r="K148"/>
-    </row>
-    <row r="149">
-      <c r="A149"/>
-      <c r="B149" t="s">
-        <v>167</v>
-      </c>
-      <c r="C149" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="D149" t="n">
-        <v>27</v>
-      </c>
-      <c r="E149" t="n">
-        <v>41</v>
-      </c>
-      <c r="F149" t="n">
-        <v>27</v>
-      </c>
-      <c r="G149" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="H149" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="I149" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I148" t="n">
         <v>48.5</v>
       </c>
-      <c r="J149" t="n">
+      <c r="J148" t="n">
         <v>24.1</v>
       </c>
-      <c r="K149" t="n">
-        <v>39.1</v>
+      <c r="K148" t="n">
+        <v>39.3</v>
       </c>
     </row>
   </sheetData>
@@ -6419,22 +6381,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -6443,18 +6405,18 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -6524,7 +6486,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -6594,7 +6556,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -6629,7 +6591,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -6664,7 +6626,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -6734,7 +6696,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
@@ -6769,7 +6731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -6804,7 +6766,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -6839,7 +6801,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -6907,7 +6869,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
@@ -6942,7 +6904,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s">
         <v>31</v>
@@ -6977,7 +6939,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s">
         <v>31</v>
@@ -7012,7 +6974,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
@@ -7047,7 +7009,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B19" t="s">
         <v>31</v>
@@ -7082,7 +7044,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B20" t="s">
         <v>31</v>
@@ -7117,7 +7079,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B21" t="s">
         <v>31</v>
@@ -7152,7 +7114,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B22" t="s">
         <v>31</v>
@@ -7187,7 +7149,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B23" t="s">
         <v>31</v>
@@ -7222,7 +7184,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
@@ -7257,7 +7219,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
@@ -7292,7 +7254,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B26" t="s">
         <v>31</v>
@@ -7327,7 +7289,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B27" t="s">
         <v>31</v>
@@ -7362,7 +7324,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B28" t="s">
         <v>31</v>
@@ -7397,7 +7359,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B29" t="s">
         <v>46</v>
@@ -7432,7 +7394,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B30" t="s">
         <v>46</v>
@@ -7502,7 +7464,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B32" t="s">
         <v>46</v>
@@ -7537,7 +7499,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B33" t="s">
         <v>46</v>
@@ -7572,7 +7534,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B34" t="s">
         <v>46</v>
@@ -7607,7 +7569,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B35" t="s">
         <v>46</v>
@@ -7640,7 +7602,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B36" t="s">
         <v>46</v>
@@ -7675,7 +7637,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B37" t="s">
         <v>46</v>
@@ -7710,7 +7672,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B38" t="s">
         <v>46</v>
@@ -7745,7 +7707,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B39" t="s">
         <v>46</v>
@@ -7780,7 +7742,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B40" t="s">
         <v>46</v>
@@ -7815,7 +7777,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
@@ -7848,7 +7810,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B42" t="s">
         <v>46</v>
@@ -7883,7 +7845,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B43" t="s">
         <v>62</v>
@@ -7918,7 +7880,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B44" t="s">
         <v>62</v>
@@ -7953,7 +7915,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B45" t="s">
         <v>62</v>
@@ -7988,7 +7950,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B46" t="s">
         <v>62</v>
@@ -8021,7 +7983,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B47" t="s">
         <v>62</v>
@@ -8056,7 +8018,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B48" t="s">
         <v>62</v>
@@ -8091,7 +8053,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B49" t="s">
         <v>62</v>
@@ -8124,7 +8086,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B50" t="s">
         <v>62</v>
@@ -8159,7 +8121,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B51" t="s">
         <v>62</v>
@@ -8194,7 +8156,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B52" t="s">
         <v>62</v>
@@ -8229,7 +8191,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B53" t="s">
         <v>62</v>
@@ -8264,7 +8226,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B54" t="s">
         <v>62</v>
@@ -8332,7 +8294,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B56" t="s">
         <v>62</v>
@@ -8402,7 +8364,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B58" t="s">
         <v>83</v>
@@ -8437,7 +8399,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B59" t="s">
         <v>83</v>
@@ -8472,7 +8434,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B60" t="s">
         <v>83</v>
@@ -8507,7 +8469,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B61" t="s">
         <v>83</v>
@@ -8542,7 +8504,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B62" t="s">
         <v>83</v>
@@ -8577,7 +8539,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B63" t="s">
         <v>83</v>
@@ -8612,7 +8574,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B64" t="s">
         <v>83</v>
@@ -8647,7 +8609,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B65" t="s">
         <v>83</v>
@@ -8682,7 +8644,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B66" t="s">
         <v>83</v>
@@ -8717,7 +8679,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B67" t="s">
         <v>83</v>
@@ -8752,7 +8714,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B68" t="s">
         <v>83</v>
@@ -8787,7 +8749,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B69" t="s">
         <v>83</v>
@@ -8822,7 +8784,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B70" t="s">
         <v>97</v>
@@ -8857,7 +8819,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B71" t="s">
         <v>97</v>
@@ -8892,7 +8854,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B72" t="s">
         <v>97</v>
@@ -8927,7 +8889,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B73" t="s">
         <v>97</v>
@@ -8960,7 +8922,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B74" t="s">
         <v>97</v>
@@ -9030,7 +8992,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B76" t="s">
         <v>97</v>
@@ -9065,7 +9027,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B77" t="s">
         <v>97</v>
@@ -9100,7 +9062,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B78" t="s">
         <v>97</v>
@@ -9135,7 +9097,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B79" t="s">
         <v>97</v>
@@ -9170,7 +9132,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B80" t="s">
         <v>97</v>
@@ -9205,7 +9167,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B81" t="s">
         <v>97</v>
@@ -9240,7 +9202,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B82" t="s">
         <v>114</v>
@@ -9275,7 +9237,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B83" t="s">
         <v>114</v>
@@ -9310,7 +9272,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B84" t="s">
         <v>114</v>
@@ -9345,7 +9307,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B85" t="s">
         <v>114</v>
@@ -9380,7 +9342,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B86" t="s">
         <v>114</v>
@@ -9415,7 +9377,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B87" t="s">
         <v>114</v>
@@ -9450,7 +9412,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B88" t="s">
         <v>114</v>
@@ -9485,7 +9447,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B89" t="s">
         <v>114</v>
@@ -9520,7 +9482,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B90" t="s">
         <v>114</v>
@@ -9555,7 +9517,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B91" t="s">
         <v>114</v>
@@ -9590,7 +9552,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B92" t="s">
         <v>131</v>
@@ -9660,7 +9622,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B94" t="s">
         <v>131</v>
@@ -9695,7 +9657,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B95" t="s">
         <v>131</v>
@@ -9728,7 +9690,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B96" t="s">
         <v>131</v>
@@ -9763,7 +9725,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B97" t="s">
         <v>131</v>
@@ -9833,7 +9795,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B99" t="s">
         <v>131</v>
@@ -9868,7 +9830,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B100" t="s">
         <v>131</v>
@@ -9903,7 +9865,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B101" t="s">
         <v>131</v>
@@ -9938,7 +9900,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B102" t="s">
         <v>131</v>
@@ -9973,7 +9935,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B103" t="s">
         <v>131</v>
@@ -10008,7 +9970,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B104" t="s">
         <v>131</v>
@@ -10043,7 +10005,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B105" t="s">
         <v>131</v>
@@ -10078,7 +10040,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B106" t="s">
         <v>131</v>
@@ -10113,10 +10075,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B107" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C107" t="n">
         <v>64.2</v>
@@ -10148,10 +10110,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B108" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C108" t="n">
         <v>55.4</v>
@@ -10183,10 +10145,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B109" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C109" t="n">
         <v>59</v>
@@ -10218,10 +10180,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B110" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C110" t="n">
         <v>62.5</v>
@@ -10253,10 +10215,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B111" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C111" t="n">
         <v>64.1</v>
@@ -10288,10 +10250,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B112" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C112" t="n">
         <v>84.6</v>
@@ -10321,10 +10283,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B113" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C113" t="n">
         <v>50</v>
@@ -10356,10 +10318,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B114" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C114" t="n">
         <v>61.3</v>
@@ -10391,10 +10353,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B115" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C115" t="n">
         <v>65.8</v>
@@ -10426,10 +10388,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B116" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C116" t="n">
         <v>50.6</v>
@@ -10461,10 +10423,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B117" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C117" t="n">
         <v>66.7</v>
@@ -10496,10 +10458,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B118" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C118" t="n">
         <v>68.5</v>
@@ -10531,10 +10493,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B119" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C119" t="n">
         <v>61.7</v>
@@ -10567,7 +10529,7 @@
     <row r="120">
       <c r="A120"/>
       <c r="B120" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C120" t="n">
         <v>57.7</v>

--- a/data/summary2026.xlsx
+++ b/data/summary2026.xlsx
@@ -3034,13 +3034,13 @@
         <v>73.9</v>
       </c>
       <c r="D52" t="n">
-        <v>34.8</v>
+        <v>32.3</v>
       </c>
       <c r="E52" t="n">
-        <v>39.1</v>
+        <v>41.6</v>
       </c>
       <c r="F52" t="n">
-        <v>34.8</v>
+        <v>32.3</v>
       </c>
       <c r="G52" t="n">
         <v>31</v>
@@ -3066,16 +3066,16 @@
         <v>65</v>
       </c>
       <c r="C53" t="n">
-        <v>76.5</v>
+        <v>77.6</v>
       </c>
       <c r="D53" t="n">
-        <v>46.8</v>
+        <v>43.6</v>
       </c>
       <c r="E53" t="n">
-        <v>29.7</v>
+        <v>34</v>
       </c>
       <c r="F53" t="n">
-        <v>46.8</v>
+        <v>43.6</v>
       </c>
       <c r="G53" t="n">
         <v>20.4</v>
@@ -3101,16 +3101,16 @@
         <v>65</v>
       </c>
       <c r="C54" t="n">
-        <v>56</v>
+        <v>54.2</v>
       </c>
       <c r="D54" t="n">
-        <v>17.5</v>
+        <v>16.7</v>
       </c>
       <c r="E54" t="n">
-        <v>38.5</v>
+        <v>37.5</v>
       </c>
       <c r="F54" t="n">
-        <v>17.5</v>
+        <v>16.7</v>
       </c>
       <c r="G54" t="n">
         <v>26.6</v>
@@ -3171,16 +3171,16 @@
         <v>65</v>
       </c>
       <c r="C56" t="n">
-        <v>54.8</v>
+        <v>55.2</v>
       </c>
       <c r="D56" t="n">
-        <v>51</v>
+        <v>48.5</v>
       </c>
       <c r="E56" t="n">
-        <v>3.8</v>
+        <v>6.7</v>
       </c>
       <c r="F56" t="n">
-        <v>51</v>
+        <v>48.5</v>
       </c>
       <c r="G56" t="n">
         <v>31</v>
@@ -3241,16 +3241,16 @@
         <v>65</v>
       </c>
       <c r="C58" t="n">
-        <v>79.5</v>
+        <v>79</v>
       </c>
       <c r="D58" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="E58" t="n">
-        <v>47.6</v>
+        <v>47.3</v>
       </c>
       <c r="F58" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="G58" t="n">
         <v>36.9</v>
@@ -3314,13 +3314,13 @@
         <v>84.9</v>
       </c>
       <c r="D60" t="n">
-        <v>24.8</v>
+        <v>22.3</v>
       </c>
       <c r="E60" t="n">
-        <v>60.1</v>
+        <v>62.6</v>
       </c>
       <c r="F60" t="n">
-        <v>24.8</v>
+        <v>22.3</v>
       </c>
       <c r="G60" t="n">
         <v>23.5</v>
@@ -3346,16 +3346,16 @@
         <v>65</v>
       </c>
       <c r="C61" t="n">
-        <v>76.2</v>
+        <v>76.9</v>
       </c>
       <c r="D61" t="n">
-        <v>28.8</v>
+        <v>17.8</v>
       </c>
       <c r="E61" t="n">
-        <v>47.4</v>
+        <v>59.1</v>
       </c>
       <c r="F61" t="n">
-        <v>28.8</v>
+        <v>17.8</v>
       </c>
       <c r="G61" t="n">
         <v>23.1</v>
@@ -3591,16 +3591,16 @@
         <v>65</v>
       </c>
       <c r="C68" t="n">
-        <v>71.8</v>
+        <v>72</v>
       </c>
       <c r="D68" t="n">
-        <v>25.6</v>
+        <v>26</v>
       </c>
       <c r="E68" t="n">
-        <v>46.2</v>
+        <v>46</v>
       </c>
       <c r="F68" t="n">
-        <v>25.6</v>
+        <v>26</v>
       </c>
       <c r="G68" t="n">
         <v>26.9</v>
@@ -3626,16 +3626,16 @@
         <v>65</v>
       </c>
       <c r="C69" t="n">
-        <v>75.4</v>
+        <v>76.2</v>
       </c>
       <c r="D69" t="n">
-        <v>49.5</v>
+        <v>47.6</v>
       </c>
       <c r="E69" t="n">
-        <v>25.9</v>
+        <v>28.6</v>
       </c>
       <c r="F69" t="n">
-        <v>49.5</v>
+        <v>47.6</v>
       </c>
       <c r="G69" t="n">
         <v>24.4</v>
@@ -3664,13 +3664,13 @@
         <v>57.1</v>
       </c>
       <c r="D70" t="n">
-        <v>15.9</v>
+        <v>15.4</v>
       </c>
       <c r="E70" t="n">
-        <v>41.2</v>
+        <v>41.7</v>
       </c>
       <c r="F70" t="n">
-        <v>15.9</v>
+        <v>15.4</v>
       </c>
       <c r="G70" t="n">
         <v>33.3</v>
@@ -3696,16 +3696,16 @@
         <v>65</v>
       </c>
       <c r="C71" t="n">
-        <v>71.7</v>
+        <v>72.9</v>
       </c>
       <c r="D71" t="n">
-        <v>34.2</v>
+        <v>31.3</v>
       </c>
       <c r="E71" t="n">
-        <v>37.5</v>
+        <v>41.6</v>
       </c>
       <c r="F71" t="n">
-        <v>34.2</v>
+        <v>31.3</v>
       </c>
       <c r="G71" t="n">
         <v>33</v>
@@ -4310,16 +4310,16 @@
         <v>100</v>
       </c>
       <c r="C89" t="n">
-        <v>55.6</v>
+        <v>58.3</v>
       </c>
       <c r="D89" t="n">
-        <v>53.1</v>
+        <v>51.9</v>
       </c>
       <c r="E89" t="n">
-        <v>2.5</v>
+        <v>6.4</v>
       </c>
       <c r="F89" t="n">
-        <v>53.1</v>
+        <v>51.9</v>
       </c>
       <c r="G89" t="n">
         <v>34.6</v>
@@ -4383,13 +4383,13 @@
         <v>75</v>
       </c>
       <c r="D91" t="n">
-        <v>37.6</v>
+        <v>36</v>
       </c>
       <c r="E91" t="n">
-        <v>37.4</v>
+        <v>39</v>
       </c>
       <c r="F91" t="n">
-        <v>37.6</v>
+        <v>36</v>
       </c>
       <c r="G91" t="n">
         <v>16.5</v>
@@ -4418,13 +4418,13 @@
         <v>67.9</v>
       </c>
       <c r="D92" t="n">
-        <v>18.1</v>
+        <v>16.9</v>
       </c>
       <c r="E92" t="n">
-        <v>49.8</v>
+        <v>51</v>
       </c>
       <c r="F92" t="n">
-        <v>18.1</v>
+        <v>16.9</v>
       </c>
       <c r="G92" t="n">
         <v>31.9</v>
@@ -4450,16 +4450,16 @@
         <v>100</v>
       </c>
       <c r="C93" t="n">
-        <v>65.7</v>
+        <v>66.2</v>
       </c>
       <c r="D93" t="n">
-        <v>38.8</v>
+        <v>36.1</v>
       </c>
       <c r="E93" t="n">
-        <v>26.9</v>
+        <v>30.1</v>
       </c>
       <c r="F93" t="n">
-        <v>38.8</v>
+        <v>36.1</v>
       </c>
       <c r="G93" t="n">
         <v>21.7</v>
@@ -4485,16 +4485,16 @@
         <v>100</v>
       </c>
       <c r="C94" t="n">
-        <v>84.6</v>
+        <v>84.3</v>
       </c>
       <c r="D94" t="n">
-        <v>34.4</v>
+        <v>32.5</v>
       </c>
       <c r="E94" t="n">
-        <v>50.2</v>
+        <v>51.8</v>
       </c>
       <c r="F94" t="n">
-        <v>34.4</v>
+        <v>32.5</v>
       </c>
       <c r="G94" t="n">
         <v>35.4</v>
@@ -4555,16 +4555,16 @@
         <v>100</v>
       </c>
       <c r="C96" t="n">
-        <v>51.2</v>
+        <v>48.6</v>
       </c>
       <c r="D96" t="n">
-        <v>39.2</v>
+        <v>28.1</v>
       </c>
       <c r="E96" t="n">
-        <v>12</v>
+        <v>20.5</v>
       </c>
       <c r="F96" t="n">
-        <v>39.2</v>
+        <v>28.1</v>
       </c>
       <c r="G96" t="n">
         <v>33.3</v>
@@ -4590,16 +4590,16 @@
         <v>100</v>
       </c>
       <c r="C97" t="n">
-        <v>76.1</v>
+        <v>75.8</v>
       </c>
       <c r="D97" t="n">
-        <v>38.9</v>
+        <v>35.2</v>
       </c>
       <c r="E97" t="n">
-        <v>37.2</v>
+        <v>40.6</v>
       </c>
       <c r="F97" t="n">
-        <v>38.9</v>
+        <v>35.2</v>
       </c>
       <c r="G97" t="n">
         <v>36.4</v>
@@ -4625,16 +4625,16 @@
         <v>100</v>
       </c>
       <c r="C98" t="n">
-        <v>63.4</v>
+        <v>63</v>
       </c>
       <c r="D98" t="n">
-        <v>27.1</v>
+        <v>24.6</v>
       </c>
       <c r="E98" t="n">
-        <v>36.3</v>
+        <v>38.4</v>
       </c>
       <c r="F98" t="n">
-        <v>27.1</v>
+        <v>24.6</v>
       </c>
       <c r="G98" t="n">
         <v>16.8</v>
@@ -4660,13 +4660,13 @@
         <v>100</v>
       </c>
       <c r="C99" t="n">
-        <v>54.7</v>
+        <v>55.8</v>
       </c>
       <c r="D99" t="n">
         <v>25.2</v>
       </c>
       <c r="E99" t="n">
-        <v>29.5</v>
+        <v>30.6</v>
       </c>
       <c r="F99" t="n">
         <v>25.2</v>
@@ -4695,16 +4695,16 @@
         <v>100</v>
       </c>
       <c r="C100" t="n">
-        <v>57.6</v>
+        <v>57.8</v>
       </c>
       <c r="D100" t="n">
-        <v>28.4</v>
+        <v>23.1</v>
       </c>
       <c r="E100" t="n">
-        <v>29.2</v>
+        <v>34.7</v>
       </c>
       <c r="F100" t="n">
-        <v>28.4</v>
+        <v>23.1</v>
       </c>
       <c r="G100" t="n">
         <v>21.9</v>
@@ -6498,13 +6498,13 @@
         <v>68.6</v>
       </c>
       <c r="D152" t="n">
-        <v>28.9</v>
+        <v>28.5</v>
       </c>
       <c r="E152" t="n">
-        <v>39.4</v>
+        <v>39.8</v>
       </c>
       <c r="F152" t="n">
-        <v>28.9</v>
+        <v>28.5</v>
       </c>
       <c r="G152" t="n">
         <v>26.5</v>
@@ -8167,7 +8167,7 @@
         <v>75.2</v>
       </c>
       <c r="E47" t="n">
-        <v>53.8</v>
+        <v>54.2</v>
       </c>
       <c r="F47" t="n">
         <v>75</v>
@@ -8480,7 +8480,7 @@
         <v>67.2</v>
       </c>
       <c r="E56" t="n">
-        <v>45.3</v>
+        <v>41</v>
       </c>
       <c r="F56" t="n">
         <v>36.2</v>
@@ -8514,9 +8514,7 @@
       <c r="D57" t="n">
         <v>64.6</v>
       </c>
-      <c r="E57" t="n">
-        <v>38.1</v>
-      </c>
+      <c r="E57"/>
       <c r="F57" t="n">
         <v>38.1</v>
       </c>
@@ -9248,7 +9246,7 @@
         <v>58.5</v>
       </c>
       <c r="E78" t="n">
-        <v>28.9</v>
+        <v>21.9</v>
       </c>
       <c r="F78" t="n">
         <v>23.3</v>
@@ -9283,7 +9281,7 @@
         <v>66.7</v>
       </c>
       <c r="E79" t="n">
-        <v>37.5</v>
+        <v>32.5</v>
       </c>
       <c r="F79" t="n">
         <v>39</v>
@@ -9353,7 +9351,7 @@
         <v>65.8</v>
       </c>
       <c r="E81" t="n">
-        <v>44.1</v>
+        <v>41.9</v>
       </c>
       <c r="F81" t="n">
         <v>37.7</v>
@@ -10887,7 +10885,7 @@
         <v>60.8</v>
       </c>
       <c r="E125" t="n">
-        <v>27.3</v>
+        <v>27.1</v>
       </c>
       <c r="F125" t="n">
         <v>38.5</v>

--- a/data/summary2026.xlsx
+++ b/data/summary2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="291">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -886,9 +886,6 @@
   </si>
   <si>
     <t xml:space="preserve">Yoilan Quinonez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yolian Quinonez</t>
   </si>
 </sst>
 </file>
@@ -963,8 +960,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K128" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K128"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K127" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K127"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -11055,99 +11052,64 @@
         <v>159</v>
       </c>
       <c r="C126" t="n">
-        <v>61.7</v>
+        <v>62.5</v>
       </c>
       <c r="D126" t="n">
-        <v>63.5</v>
+        <v>62.9</v>
       </c>
       <c r="E126" t="n">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="F126" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G126" t="n">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="H126" t="n">
-        <v>46.5</v>
+        <v>45.5</v>
       </c>
       <c r="I126" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J126" t="n">
-        <v>20.4</v>
+        <v>21.6</v>
       </c>
       <c r="K126" t="n">
-        <v>13.3</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="s">
-        <v>291</v>
-      </c>
+      <c r="A127"/>
       <c r="B127" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="C127" t="n">
-        <v>75</v>
+        <v>58.7</v>
       </c>
       <c r="D127" t="n">
-        <v>55.6</v>
+        <v>61</v>
       </c>
       <c r="E127" t="n">
-        <v>27.3</v>
+        <v>20.3</v>
       </c>
       <c r="F127" t="n">
-        <v>66.7</v>
+        <v>37.8</v>
       </c>
       <c r="G127" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>45.4</v>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="J127" t="n">
-        <v>37.5</v>
+        <v>25.2</v>
       </c>
       <c r="K127" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128"/>
-      <c r="B128" t="s">
-        <v>174</v>
-      </c>
-      <c r="C128" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="D128" t="n">
-        <v>61</v>
-      </c>
-      <c r="E128" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="F128" t="n">
-        <v>38</v>
-      </c>
-      <c r="G128" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H128" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="I128" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J128" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="K128" t="n">
-        <v>8.4</v>
+        <v>8.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/summary2026.xlsx
+++ b/data/summary2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="292">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -129,6 +129,9 @@
     <t xml:space="preserve">Cassidy Watt</t>
   </si>
   <si>
+    <t xml:space="preserve">Charlie Towers</t>
+  </si>
+  <si>
     <t xml:space="preserve">Christian Kuzemka</t>
   </si>
   <si>
@@ -159,6 +162,9 @@
     <t xml:space="preserve">Walker Hultgren</t>
   </si>
   <si>
+    <t xml:space="preserve">Walter Hultgren</t>
+  </si>
+  <si>
     <t xml:space="preserve">Andy Groening</t>
   </si>
   <si>
@@ -328,9 +334,6 @@
   </si>
   <si>
     <t xml:space="preserve">Cameron Bauer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charlie Towers</t>
   </si>
   <si>
     <t xml:space="preserve">Ernesto Punales</t>
@@ -940,8 +943,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K156" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K156"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K158" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K158"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -2040,28 +2043,28 @@
         <v>34</v>
       </c>
       <c r="C23" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D23" t="n">
-        <v>23.5</v>
+        <v>22.7</v>
       </c>
       <c r="E23" t="n">
-        <v>46.5</v>
+        <v>40.3</v>
       </c>
       <c r="F23" t="n">
-        <v>23.5</v>
+        <v>22.7</v>
       </c>
       <c r="G23" t="n">
-        <v>52.6</v>
+        <v>43.5</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="J23" t="n">
-        <v>16.7</v>
+        <v>30</v>
       </c>
       <c r="K23" t="n">
         <v>50</v>
@@ -2075,31 +2078,31 @@
         <v>34</v>
       </c>
       <c r="C24" t="n">
-        <v>75.4</v>
+        <v>75</v>
       </c>
       <c r="D24" t="n">
-        <v>26.6</v>
+        <v>26.8</v>
       </c>
       <c r="E24" t="n">
-        <v>48.8</v>
+        <v>48.2</v>
       </c>
       <c r="F24" t="n">
-        <v>26.6</v>
+        <v>26.8</v>
       </c>
       <c r="G24" t="n">
-        <v>22.7</v>
+        <v>20</v>
       </c>
       <c r="H24" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="I24" t="n">
-        <v>35.1</v>
+        <v>33.3</v>
       </c>
       <c r="J24" t="n">
-        <v>29.7</v>
+        <v>33.3</v>
       </c>
       <c r="K24" t="n">
-        <v>45.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25">
@@ -2110,31 +2113,31 @@
         <v>34</v>
       </c>
       <c r="C25" t="n">
-        <v>57.9</v>
+        <v>57.8</v>
       </c>
       <c r="D25" t="n">
-        <v>19.4</v>
+        <v>20.3</v>
       </c>
       <c r="E25" t="n">
-        <v>38.5</v>
+        <v>37.5</v>
       </c>
       <c r="F25" t="n">
-        <v>19.4</v>
+        <v>20.3</v>
       </c>
       <c r="G25" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I25" t="n">
         <v>35.3</v>
       </c>
-      <c r="H25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="I25" t="n">
-        <v>33.3</v>
-      </c>
       <c r="J25" t="n">
-        <v>39.4</v>
+        <v>38.2</v>
       </c>
       <c r="K25" t="n">
-        <v>35.3</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="26">
@@ -2145,31 +2148,31 @@
         <v>34</v>
       </c>
       <c r="C26" t="n">
-        <v>63</v>
+        <v>65.4</v>
       </c>
       <c r="D26" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="E26" t="n">
-        <v>39.2</v>
+        <v>41.8</v>
       </c>
       <c r="F26" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="G26" t="n">
-        <v>29.7</v>
+        <v>29.4</v>
       </c>
       <c r="H26" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="I26" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
       <c r="J26" t="n">
-        <v>10.3</v>
+        <v>11.6</v>
       </c>
       <c r="K26" t="n">
-        <v>34.2</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="27">
@@ -2180,31 +2183,31 @@
         <v>34</v>
       </c>
       <c r="C27" t="n">
-        <v>79.2</v>
+        <v>66.7</v>
       </c>
       <c r="D27" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>57.8</v>
+        <v>66.7</v>
       </c>
       <c r="F27" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>26.7</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>7.7</v>
+        <v>50</v>
       </c>
       <c r="K27" t="n">
-        <v>38.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -2215,31 +2218,31 @@
         <v>34</v>
       </c>
       <c r="C28" t="n">
-        <v>73.7</v>
+        <v>75.8</v>
       </c>
       <c r="D28" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="E28" t="n">
-        <v>47.7</v>
+        <v>49.7</v>
       </c>
       <c r="F28" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="G28" t="n">
-        <v>15.8</v>
+        <v>28.2</v>
       </c>
       <c r="H28" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>51.9</v>
+        <v>27.8</v>
       </c>
       <c r="J28" t="n">
-        <v>15.4</v>
+        <v>11.1</v>
       </c>
       <c r="K28" t="n">
-        <v>42.3</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="29">
@@ -2250,31 +2253,31 @@
         <v>34</v>
       </c>
       <c r="C29" t="n">
-        <v>47.5</v>
+        <v>75</v>
       </c>
       <c r="D29" t="n">
-        <v>6.1</v>
+        <v>25.9</v>
       </c>
       <c r="E29" t="n">
-        <v>41.4</v>
+        <v>49.1</v>
       </c>
       <c r="F29" t="n">
-        <v>6.1</v>
+        <v>25.9</v>
       </c>
       <c r="G29" t="n">
-        <v>17.9</v>
+        <v>17.5</v>
       </c>
       <c r="H29" t="n">
-        <v>16.7</v>
+        <v>4.3</v>
       </c>
       <c r="I29" t="n">
-        <v>90.9</v>
+        <v>50.9</v>
       </c>
       <c r="J29" t="n">
-        <v>9.1</v>
+        <v>16.4</v>
       </c>
       <c r="K29" t="n">
-        <v>18.2</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="30">
@@ -2285,31 +2288,31 @@
         <v>34</v>
       </c>
       <c r="C30" t="n">
-        <v>73.9</v>
+        <v>47.5</v>
       </c>
       <c r="D30" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="E30" t="n">
-        <v>68.3</v>
+        <v>41.4</v>
       </c>
       <c r="F30" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="G30" t="n">
-        <v>22.7</v>
+        <v>17.9</v>
       </c>
       <c r="H30" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>90.9</v>
       </c>
       <c r="J30" t="n">
-        <v>40</v>
+        <v>9.1</v>
       </c>
       <c r="K30" t="n">
-        <v>37.5</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="31">
@@ -2320,31 +2323,31 @@
         <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>67</v>
+        <v>73.9</v>
       </c>
       <c r="D31" t="n">
-        <v>16.9</v>
+        <v>5.6</v>
       </c>
       <c r="E31" t="n">
-        <v>50.1</v>
+        <v>68.3</v>
       </c>
       <c r="F31" t="n">
-        <v>16.9</v>
+        <v>5.6</v>
       </c>
       <c r="G31" t="n">
-        <v>21.9</v>
+        <v>22.7</v>
       </c>
       <c r="H31" t="n">
-        <v>16.4</v>
+        <v>20</v>
       </c>
       <c r="I31" t="n">
-        <v>47.5</v>
+        <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>12.5</v>
+        <v>40</v>
       </c>
       <c r="K31" t="n">
-        <v>46.2</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="32">
@@ -2355,31 +2358,31 @@
         <v>34</v>
       </c>
       <c r="C32" t="n">
-        <v>64.5</v>
+        <v>68.7</v>
       </c>
       <c r="D32" t="n">
-        <v>23.3</v>
+        <v>17.8</v>
       </c>
       <c r="E32" t="n">
-        <v>41.2</v>
+        <v>50.9</v>
       </c>
       <c r="F32" t="n">
-        <v>23.3</v>
+        <v>17.8</v>
       </c>
       <c r="G32" t="n">
-        <v>26.1</v>
+        <v>20.5</v>
       </c>
       <c r="H32" t="n">
-        <v>7.8</v>
+        <v>15.2</v>
       </c>
       <c r="I32" t="n">
         <v>45.7</v>
       </c>
       <c r="J32" t="n">
-        <v>25.7</v>
+        <v>17.4</v>
       </c>
       <c r="K32" t="n">
-        <v>33.3</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="33">
@@ -2390,31 +2393,31 @@
         <v>34</v>
       </c>
       <c r="C33" t="n">
-        <v>52.2</v>
+        <v>65.4</v>
       </c>
       <c r="D33" t="n">
-        <v>43.5</v>
+        <v>24.5</v>
       </c>
       <c r="E33" t="n">
-        <v>8.7</v>
+        <v>40.9</v>
       </c>
       <c r="F33" t="n">
-        <v>43.5</v>
+        <v>24.5</v>
       </c>
       <c r="G33" t="n">
-        <v>26.7</v>
+        <v>27.2</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="I33" t="n">
-        <v>50</v>
+        <v>47.2</v>
       </c>
       <c r="J33" t="n">
-        <v>27.8</v>
+        <v>25</v>
       </c>
       <c r="K33" t="n">
-        <v>41.2</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="34">
@@ -2425,31 +2428,31 @@
         <v>34</v>
       </c>
       <c r="C34" t="n">
-        <v>68</v>
+        <v>54.2</v>
       </c>
       <c r="D34" t="n">
-        <v>14.8</v>
+        <v>45.8</v>
       </c>
       <c r="E34" t="n">
-        <v>53.2</v>
+        <v>8.4</v>
       </c>
       <c r="F34" t="n">
-        <v>14.8</v>
+        <v>45.8</v>
       </c>
       <c r="G34" t="n">
-        <v>18.5</v>
+        <v>25.5</v>
       </c>
       <c r="H34" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>51.4</v>
+        <v>47.4</v>
       </c>
       <c r="J34" t="n">
-        <v>18.9</v>
+        <v>31.6</v>
       </c>
       <c r="K34" t="n">
-        <v>37.8</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="35">
@@ -2460,31 +2463,31 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>69.3</v>
+        <v>67.9</v>
       </c>
       <c r="D35" t="n">
-        <v>22.5</v>
+        <v>17.2</v>
       </c>
       <c r="E35" t="n">
-        <v>46.8</v>
+        <v>50.7</v>
       </c>
       <c r="F35" t="n">
-        <v>22.5</v>
+        <v>17.2</v>
       </c>
       <c r="G35" t="n">
-        <v>30.4</v>
+        <v>17</v>
       </c>
       <c r="H35" t="n">
-        <v>10</v>
+        <v>15.4</v>
       </c>
       <c r="I35" t="n">
-        <v>55</v>
+        <v>47.6</v>
       </c>
       <c r="J35" t="n">
-        <v>17.5</v>
+        <v>23.8</v>
       </c>
       <c r="K35" t="n">
-        <v>37.8</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="36">
@@ -2495,31 +2498,31 @@
         <v>34</v>
       </c>
       <c r="C36" t="n">
-        <v>78.6</v>
+        <v>69.3</v>
       </c>
       <c r="D36" t="n">
-        <v>26.3</v>
+        <v>22.5</v>
       </c>
       <c r="E36" t="n">
-        <v>52.3</v>
+        <v>46.8</v>
       </c>
       <c r="F36" t="n">
-        <v>26.3</v>
+        <v>22.5</v>
       </c>
       <c r="G36" t="n">
-        <v>37.1</v>
+        <v>30.4</v>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I36" t="n">
-        <v>28.6</v>
+        <v>55</v>
       </c>
       <c r="J36" t="n">
-        <v>42.9</v>
+        <v>17.5</v>
       </c>
       <c r="K36" t="n">
-        <v>21.7</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="37">
@@ -2527,98 +2530,104 @@
         <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C37" t="n">
-        <v>76.1</v>
+        <v>78.6</v>
       </c>
       <c r="D37" t="n">
-        <v>25</v>
+        <v>26.3</v>
       </c>
       <c r="E37" t="n">
-        <v>51.1</v>
+        <v>52.3</v>
       </c>
       <c r="F37" t="n">
-        <v>25</v>
+        <v>26.3</v>
       </c>
       <c r="G37" t="n">
-        <v>38.3</v>
+        <v>37.1</v>
       </c>
       <c r="H37" t="n">
-        <v>10.9</v>
+        <v>3</v>
       </c>
       <c r="I37" t="n">
-        <v>66.7</v>
+        <v>28.6</v>
       </c>
       <c r="J37" t="n">
-        <v>20</v>
+        <v>42.9</v>
       </c>
       <c r="K37" t="n">
-        <v>50</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C38" t="n">
-        <v>66.9</v>
+        <v>80</v>
       </c>
       <c r="D38" t="n">
-        <v>21.4</v>
+        <v>33.3</v>
       </c>
       <c r="E38" t="n">
-        <v>45.5</v>
+        <v>46.7</v>
       </c>
       <c r="F38" t="n">
-        <v>21.4</v>
+        <v>33.3</v>
       </c>
       <c r="G38" t="n">
-        <v>18.3</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>38.4</v>
+        <v>80</v>
       </c>
       <c r="J38" t="n">
-        <v>34.2</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>47.9</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" t="s">
         <v>51</v>
       </c>
-      <c r="B39" t="s">
-        <v>49</v>
-      </c>
       <c r="C39" t="n">
-        <v>100</v>
-      </c>
-      <c r="D39"/>
-      <c r="E39"/>
-      <c r="F39"/>
+        <v>76.1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>25</v>
+      </c>
+      <c r="E39" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>25</v>
+      </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>38.3</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="I39" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40">
@@ -2626,34 +2635,34 @@
         <v>52</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C40" t="n">
-        <v>69.9</v>
+        <v>66.9</v>
       </c>
       <c r="D40" t="n">
-        <v>15.5</v>
+        <v>21.4</v>
       </c>
       <c r="E40" t="n">
-        <v>54.4</v>
+        <v>45.5</v>
       </c>
       <c r="F40" t="n">
-        <v>15.5</v>
+        <v>21.4</v>
       </c>
       <c r="G40" t="n">
-        <v>12.4</v>
+        <v>18.3</v>
       </c>
       <c r="H40" t="n">
-        <v>8.8</v>
+        <v>4.5</v>
       </c>
       <c r="I40" t="n">
-        <v>50.7</v>
+        <v>38.4</v>
       </c>
       <c r="J40" t="n">
-        <v>23.2</v>
+        <v>34.2</v>
       </c>
       <c r="K40" t="n">
-        <v>26.1</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="41">
@@ -2661,34 +2670,28 @@
         <v>53</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C41" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="D41" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E41" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="F41" t="n">
-        <v>30.4</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D41"/>
+      <c r="E41"/>
+      <c r="F41"/>
       <c r="G41" t="n">
-        <v>25.3</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>48.5</v>
+        <v>100</v>
       </c>
       <c r="J41" t="n">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>42.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2696,34 +2699,34 @@
         <v>54</v>
       </c>
       <c r="B42" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C42" t="n">
-        <v>60.7</v>
+        <v>69.9</v>
       </c>
       <c r="D42" t="n">
-        <v>45.5</v>
+        <v>15.5</v>
       </c>
       <c r="E42" t="n">
-        <v>15.2</v>
+        <v>54.4</v>
       </c>
       <c r="F42" t="n">
-        <v>45.5</v>
+        <v>15.5</v>
       </c>
       <c r="G42" t="n">
-        <v>16.1</v>
+        <v>12.4</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>8.8</v>
       </c>
       <c r="I42" t="n">
-        <v>25</v>
+        <v>50.7</v>
       </c>
       <c r="J42" t="n">
-        <v>50</v>
+        <v>23.2</v>
       </c>
       <c r="K42" t="n">
-        <v>20</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="43">
@@ -2731,30 +2734,34 @@
         <v>55</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
-      </c>
-      <c r="C43"/>
+        <v>51</v>
+      </c>
+      <c r="C43" t="n">
+        <v>76.8</v>
+      </c>
       <c r="D43" t="n">
-        <v>100</v>
-      </c>
-      <c r="E43"/>
+        <v>30.4</v>
+      </c>
+      <c r="E43" t="n">
+        <v>46.4</v>
+      </c>
       <c r="F43" t="n">
-        <v>100</v>
+        <v>30.4</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>25.3</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="I43" t="n">
-        <v>100</v>
+        <v>48.5</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>30.3</v>
       </c>
       <c r="K43" t="n">
-        <v>100</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="44">
@@ -2762,34 +2769,34 @@
         <v>56</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C44" t="n">
-        <v>64.2</v>
+        <v>60.7</v>
       </c>
       <c r="D44" t="n">
-        <v>21.4</v>
+        <v>45.5</v>
       </c>
       <c r="E44" t="n">
-        <v>42.8</v>
+        <v>15.2</v>
       </c>
       <c r="F44" t="n">
-        <v>21.4</v>
+        <v>45.5</v>
       </c>
       <c r="G44" t="n">
-        <v>18.8</v>
+        <v>16.1</v>
       </c>
       <c r="H44" t="n">
-        <v>9.8</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>53.4</v>
+        <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>17.2</v>
+        <v>50</v>
       </c>
       <c r="K44" t="n">
-        <v>22.4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45">
@@ -2797,34 +2804,30 @@
         <v>57</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
-      </c>
-      <c r="C45" t="n">
-        <v>78.4</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="C45"/>
       <c r="D45" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="E45" t="n">
-        <v>57.2</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="E45"/>
       <c r="F45" t="n">
-        <v>21.2</v>
+        <v>100</v>
       </c>
       <c r="G45" t="n">
-        <v>39.3</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>52.2</v>
+        <v>100</v>
       </c>
       <c r="J45" t="n">
-        <v>21.7</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>26.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46">
@@ -2832,34 +2835,34 @@
         <v>58</v>
       </c>
       <c r="B46" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C46" t="n">
-        <v>79.3</v>
+        <v>64.2</v>
       </c>
       <c r="D46" t="n">
-        <v>38.2</v>
+        <v>21.4</v>
       </c>
       <c r="E46" t="n">
-        <v>41.1</v>
+        <v>42.8</v>
       </c>
       <c r="F46" t="n">
-        <v>38.2</v>
+        <v>21.4</v>
       </c>
       <c r="G46" t="n">
-        <v>38.3</v>
+        <v>18.8</v>
       </c>
       <c r="H46" t="n">
-        <v>8.1</v>
+        <v>9.8</v>
       </c>
       <c r="I46" t="n">
-        <v>52.4</v>
+        <v>53.4</v>
       </c>
       <c r="J46" t="n">
-        <v>28.6</v>
+        <v>17.2</v>
       </c>
       <c r="K46" t="n">
-        <v>52.4</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="47">
@@ -2867,34 +2870,34 @@
         <v>59</v>
       </c>
       <c r="B47" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C47" t="n">
-        <v>50.7</v>
+        <v>78.4</v>
       </c>
       <c r="D47" t="n">
-        <v>17.9</v>
+        <v>21.2</v>
       </c>
       <c r="E47" t="n">
-        <v>32.8</v>
+        <v>57.2</v>
       </c>
       <c r="F47" t="n">
-        <v>17.9</v>
+        <v>21.2</v>
       </c>
       <c r="G47" t="n">
-        <v>18.3</v>
+        <v>39.3</v>
       </c>
       <c r="H47" t="n">
-        <v>17.1</v>
+        <v>9.5</v>
       </c>
       <c r="I47" t="n">
-        <v>38.5</v>
+        <v>52.2</v>
       </c>
       <c r="J47" t="n">
-        <v>30.8</v>
+        <v>21.7</v>
       </c>
       <c r="K47" t="n">
-        <v>16.7</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="48">
@@ -2902,34 +2905,34 @@
         <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C48" t="n">
-        <v>69.4</v>
+        <v>79.3</v>
       </c>
       <c r="D48" t="n">
-        <v>16.4</v>
+        <v>38.2</v>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>41.1</v>
       </c>
       <c r="F48" t="n">
-        <v>16.4</v>
+        <v>38.2</v>
       </c>
       <c r="G48" t="n">
-        <v>31.4</v>
+        <v>38.3</v>
       </c>
       <c r="H48" t="n">
-        <v>12.8</v>
+        <v>8.1</v>
       </c>
       <c r="I48" t="n">
-        <v>35.4</v>
+        <v>52.4</v>
       </c>
       <c r="J48" t="n">
-        <v>43.8</v>
+        <v>28.6</v>
       </c>
       <c r="K48" t="n">
-        <v>27.1</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="49">
@@ -2937,34 +2940,34 @@
         <v>61</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C49" t="n">
-        <v>68</v>
+        <v>50.7</v>
       </c>
       <c r="D49" t="n">
-        <v>27.6</v>
+        <v>17.9</v>
       </c>
       <c r="E49" t="n">
-        <v>40.4</v>
+        <v>32.8</v>
       </c>
       <c r="F49" t="n">
-        <v>27.6</v>
+        <v>17.9</v>
       </c>
       <c r="G49" t="n">
-        <v>53.7</v>
+        <v>18.3</v>
       </c>
       <c r="H49" t="n">
-        <v>5.3</v>
+        <v>17.1</v>
       </c>
       <c r="I49" t="n">
-        <v>63.6</v>
+        <v>38.5</v>
       </c>
       <c r="J49" t="n">
-        <v>18.2</v>
+        <v>30.8</v>
       </c>
       <c r="K49" t="n">
-        <v>36.4</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="50">
@@ -2972,34 +2975,34 @@
         <v>62</v>
       </c>
       <c r="B50" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C50" t="n">
-        <v>70.7</v>
+        <v>69.4</v>
       </c>
       <c r="D50" t="n">
-        <v>14</v>
+        <v>16.4</v>
       </c>
       <c r="E50" t="n">
-        <v>56.7</v>
+        <v>53</v>
       </c>
       <c r="F50" t="n">
-        <v>14</v>
+        <v>16.4</v>
       </c>
       <c r="G50" t="n">
-        <v>21.5</v>
+        <v>31.4</v>
       </c>
       <c r="H50" t="n">
-        <v>7.5</v>
+        <v>12.8</v>
       </c>
       <c r="I50" t="n">
-        <v>67.7</v>
+        <v>35.4</v>
       </c>
       <c r="J50" t="n">
-        <v>12.9</v>
+        <v>43.8</v>
       </c>
       <c r="K50" t="n">
-        <v>25.8</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="51">
@@ -3007,34 +3010,34 @@
         <v>63</v>
       </c>
       <c r="B51" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C51" t="n">
-        <v>70.6</v>
+        <v>68</v>
       </c>
       <c r="D51" t="n">
-        <v>17.8</v>
+        <v>27.6</v>
       </c>
       <c r="E51" t="n">
-        <v>52.8</v>
+        <v>40.4</v>
       </c>
       <c r="F51" t="n">
-        <v>17.8</v>
+        <v>27.6</v>
       </c>
       <c r="G51" t="n">
-        <v>26.1</v>
+        <v>53.7</v>
       </c>
       <c r="H51" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I51" t="n">
-        <v>37</v>
+        <v>63.6</v>
       </c>
       <c r="J51" t="n">
-        <v>33.3</v>
+        <v>18.2</v>
       </c>
       <c r="K51" t="n">
-        <v>38.9</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="52">
@@ -3042,34 +3045,34 @@
         <v>64</v>
       </c>
       <c r="B52" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>74.3</v>
+        <v>70.7</v>
       </c>
       <c r="D52" t="n">
-        <v>13.4</v>
+        <v>14</v>
       </c>
       <c r="E52" t="n">
-        <v>60.9</v>
+        <v>56.7</v>
       </c>
       <c r="F52" t="n">
-        <v>13.4</v>
+        <v>14</v>
       </c>
       <c r="G52" t="n">
-        <v>36.1</v>
+        <v>21.5</v>
       </c>
       <c r="H52" t="n">
-        <v>13.1</v>
+        <v>7.5</v>
       </c>
       <c r="I52" t="n">
-        <v>20.8</v>
+        <v>67.7</v>
       </c>
       <c r="J52" t="n">
-        <v>41.7</v>
+        <v>12.9</v>
       </c>
       <c r="K52" t="n">
-        <v>52.1</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="53">
@@ -3077,125 +3080,139 @@
         <v>65</v>
       </c>
       <c r="B53" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C53" t="n">
-        <v>75.9</v>
+        <v>70.6</v>
       </c>
       <c r="D53" t="n">
-        <v>24.1</v>
+        <v>17.8</v>
       </c>
       <c r="E53" t="n">
-        <v>51.8</v>
+        <v>52.8</v>
       </c>
       <c r="F53" t="n">
-        <v>24.1</v>
+        <v>17.8</v>
       </c>
       <c r="G53" t="n">
-        <v>29.5</v>
+        <v>26.1</v>
       </c>
       <c r="H53" t="n">
-        <v>10.2</v>
+        <v>5.4</v>
       </c>
       <c r="I53" t="n">
-        <v>52.4</v>
+        <v>37</v>
       </c>
       <c r="J53" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="K53" t="n">
-        <v>47.6</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C54" t="n">
-        <v>78.6</v>
+        <v>74.3</v>
       </c>
       <c r="D54" t="n">
-        <v>30.2</v>
+        <v>13.4</v>
       </c>
       <c r="E54" t="n">
-        <v>48.4</v>
+        <v>60.9</v>
       </c>
       <c r="F54" t="n">
-        <v>30.2</v>
+        <v>13.4</v>
       </c>
       <c r="G54" t="n">
-        <v>19.4</v>
+        <v>36.1</v>
       </c>
       <c r="H54" t="n">
-        <v>4.8</v>
+        <v>13.1</v>
       </c>
       <c r="I54" t="n">
-        <v>38.5</v>
+        <v>20.8</v>
       </c>
       <c r="J54" t="n">
-        <v>25</v>
+        <v>41.7</v>
       </c>
       <c r="K54" t="n">
-        <v>32.7</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>67</v>
+      </c>
+      <c r="B55" t="s">
         <v>68</v>
       </c>
-      <c r="B55" t="s">
-        <v>66</v>
-      </c>
-      <c r="C55"/>
-      <c r="D55"/>
-      <c r="E55"/>
-      <c r="F55"/>
+      <c r="C55" t="n">
+        <v>75.9</v>
+      </c>
+      <c r="D55" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="F55" t="n">
+        <v>24.1</v>
+      </c>
       <c r="G55" t="n">
-        <v>33.3</v>
+        <v>29.5</v>
       </c>
       <c r="H55" t="n">
-        <v>50</v>
-      </c>
-      <c r="I55"/>
-      <c r="J55"/>
-      <c r="K55"/>
+        <v>10.2</v>
+      </c>
+      <c r="I55" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="J55" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="K55" t="n">
+        <v>47.6</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
         <v>69</v>
       </c>
       <c r="B56" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C56" t="n">
-        <v>57.8</v>
+        <v>78.6</v>
       </c>
       <c r="D56" t="n">
-        <v>7.6</v>
+        <v>30.2</v>
       </c>
       <c r="E56" t="n">
-        <v>50.2</v>
+        <v>48.4</v>
       </c>
       <c r="F56" t="n">
-        <v>7.6</v>
+        <v>30.2</v>
       </c>
       <c r="G56" t="n">
-        <v>26.6</v>
+        <v>19.4</v>
       </c>
       <c r="H56" t="n">
-        <v>12.9</v>
+        <v>4.8</v>
       </c>
       <c r="I56" t="n">
-        <v>60</v>
+        <v>38.5</v>
       </c>
       <c r="J56" t="n">
-        <v>14.3</v>
+        <v>25</v>
       </c>
       <c r="K56" t="n">
-        <v>32.4</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="57">
@@ -3203,69 +3220,55 @@
         <v>70</v>
       </c>
       <c r="B57" t="s">
-        <v>66</v>
-      </c>
-      <c r="C57" t="n">
-        <v>100</v>
-      </c>
-      <c r="D57" t="n">
-        <v>20</v>
-      </c>
-      <c r="E57" t="n">
-        <v>80</v>
-      </c>
-      <c r="F57" t="n">
-        <v>20</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="C57"/>
+      <c r="D57"/>
+      <c r="E57"/>
+      <c r="F57"/>
       <c r="G57" t="n">
-        <v>43.8</v>
+        <v>33.3</v>
       </c>
       <c r="H57" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="I57" t="n">
-        <v>40</v>
-      </c>
-      <c r="J57" t="n">
-        <v>60</v>
-      </c>
-      <c r="K57" t="n">
-        <v>20</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="I57"/>
+      <c r="J57"/>
+      <c r="K57"/>
     </row>
     <row r="58">
       <c r="A58" t="s">
         <v>71</v>
       </c>
       <c r="B58" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C58" t="n">
         <v>57.8</v>
       </c>
       <c r="D58" t="n">
-        <v>45.7</v>
+        <v>7.6</v>
       </c>
       <c r="E58" t="n">
-        <v>12.1</v>
+        <v>50.2</v>
       </c>
       <c r="F58" t="n">
-        <v>45.7</v>
+        <v>7.6</v>
       </c>
       <c r="G58" t="n">
-        <v>31</v>
+        <v>26.6</v>
       </c>
       <c r="H58" t="n">
-        <v>3.3</v>
+        <v>12.9</v>
       </c>
       <c r="I58" t="n">
-        <v>47.4</v>
+        <v>60</v>
       </c>
       <c r="J58" t="n">
-        <v>21.1</v>
+        <v>14.3</v>
       </c>
       <c r="K58" t="n">
-        <v>42.1</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="59">
@@ -3273,34 +3276,34 @@
         <v>72</v>
       </c>
       <c r="B59" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C59" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="E59" t="n">
-        <v>44.6</v>
+        <v>80</v>
       </c>
       <c r="F59" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="G59" t="n">
-        <v>14.3</v>
+        <v>43.8</v>
       </c>
       <c r="H59" t="n">
-        <v>16.7</v>
+        <v>22.2</v>
       </c>
       <c r="I59" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K59" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60">
@@ -3308,34 +3311,34 @@
         <v>73</v>
       </c>
       <c r="B60" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C60" t="n">
-        <v>78.3</v>
+        <v>57.8</v>
       </c>
       <c r="D60" t="n">
-        <v>21.9</v>
+        <v>45.7</v>
       </c>
       <c r="E60" t="n">
-        <v>56.4</v>
+        <v>12.1</v>
       </c>
       <c r="F60" t="n">
-        <v>21.9</v>
+        <v>45.7</v>
       </c>
       <c r="G60" t="n">
-        <v>36.6</v>
+        <v>31</v>
       </c>
       <c r="H60" t="n">
-        <v>9.7</v>
+        <v>3.3</v>
       </c>
       <c r="I60" t="n">
-        <v>45.6</v>
+        <v>47.4</v>
       </c>
       <c r="J60" t="n">
-        <v>24.6</v>
+        <v>21.1</v>
       </c>
       <c r="K60" t="n">
-        <v>47.4</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="61">
@@ -3343,34 +3346,34 @@
         <v>74</v>
       </c>
       <c r="B61" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C61" t="n">
-        <v>72.4</v>
+        <v>57.1</v>
       </c>
       <c r="D61" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="n">
-        <v>62.4</v>
+        <v>44.6</v>
       </c>
       <c r="F61" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="G61" t="n">
-        <v>41.2</v>
+        <v>14.3</v>
       </c>
       <c r="H61" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="I61" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J61" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62">
@@ -3378,34 +3381,34 @@
         <v>75</v>
       </c>
       <c r="B62" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C62" t="n">
-        <v>74.3</v>
+        <v>78.3</v>
       </c>
       <c r="D62" t="n">
-        <v>21.4</v>
+        <v>21.9</v>
       </c>
       <c r="E62" t="n">
-        <v>52.9</v>
+        <v>56.4</v>
       </c>
       <c r="F62" t="n">
-        <v>21.4</v>
+        <v>21.9</v>
       </c>
       <c r="G62" t="n">
-        <v>23.3</v>
+        <v>36.6</v>
       </c>
       <c r="H62" t="n">
-        <v>17.1</v>
+        <v>9.7</v>
       </c>
       <c r="I62" t="n">
-        <v>50</v>
+        <v>45.6</v>
       </c>
       <c r="J62" t="n">
-        <v>21.4</v>
+        <v>24.6</v>
       </c>
       <c r="K62" t="n">
-        <v>37</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="63">
@@ -3413,34 +3416,34 @@
         <v>76</v>
       </c>
       <c r="B63" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C63" t="n">
-        <v>80.4</v>
+        <v>72.4</v>
       </c>
       <c r="D63" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E63" t="n">
-        <v>64.4</v>
+        <v>62.4</v>
       </c>
       <c r="F63" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G63" t="n">
-        <v>23.1</v>
+        <v>41.2</v>
       </c>
       <c r="H63" t="n">
-        <v>10.3</v>
+        <v>14.3</v>
       </c>
       <c r="I63" t="n">
         <v>50</v>
       </c>
       <c r="J63" t="n">
-        <v>16.7</v>
+        <v>30</v>
       </c>
       <c r="K63" t="n">
-        <v>58.3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64">
@@ -3448,34 +3451,34 @@
         <v>77</v>
       </c>
       <c r="B64" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C64" t="n">
-        <v>100</v>
+        <v>74.3</v>
       </c>
       <c r="D64" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="E64" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="F64" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G64" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="H64" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="I64" t="n">
         <v>50</v>
       </c>
-      <c r="E64" t="n">
-        <v>50</v>
-      </c>
-      <c r="F64" t="n">
-        <v>50</v>
-      </c>
-      <c r="G64" t="n">
-        <v>25</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="n">
-        <v>100</v>
-      </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="K64" t="n">
-        <v>100</v>
+        <v>37</v>
       </c>
     </row>
     <row r="65">
@@ -3483,34 +3486,34 @@
         <v>78</v>
       </c>
       <c r="B65" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C65" t="n">
-        <v>33.3</v>
+        <v>80.4</v>
       </c>
       <c r="D65" t="n">
-        <v>33.3</v>
+        <v>16</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>64.4</v>
       </c>
       <c r="F65" t="n">
-        <v>33.3</v>
+        <v>16</v>
       </c>
       <c r="G65" t="n">
-        <v>25</v>
+        <v>23.1</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="I65" t="n">
         <v>50</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="K65" t="n">
-        <v>50</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="66">
@@ -3518,34 +3521,34 @@
         <v>79</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C66" t="n">
-        <v>74.1</v>
+        <v>100</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E66" t="n">
-        <v>74.1</v>
+        <v>50</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G66" t="n">
-        <v>31.4</v>
+        <v>25</v>
       </c>
       <c r="H66" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="J66" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>12.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="67">
@@ -3553,34 +3556,34 @@
         <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C67" t="n">
-        <v>69.6</v>
+        <v>33.3</v>
       </c>
       <c r="D67" t="n">
         <v>33.3</v>
       </c>
       <c r="E67" t="n">
-        <v>36.3</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
         <v>33.3</v>
       </c>
       <c r="G67" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H67" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="J67" t="n">
-        <v>30.8</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>53.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="68">
@@ -3588,34 +3591,34 @@
         <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C68" t="n">
-        <v>87.5</v>
+        <v>74.1</v>
       </c>
       <c r="D68" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>69.3</v>
+        <v>74.1</v>
       </c>
       <c r="F68" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>60</v>
+        <v>31.4</v>
       </c>
       <c r="H68" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="I68" t="n">
-        <v>66.7</v>
+        <v>62.5</v>
       </c>
       <c r="J68" t="n">
-        <v>33.3</v>
+        <v>12.5</v>
       </c>
       <c r="K68" t="n">
-        <v>100</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="69">
@@ -3623,34 +3626,34 @@
         <v>82</v>
       </c>
       <c r="B69" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C69" t="n">
-        <v>68.6</v>
+        <v>69.6</v>
       </c>
       <c r="D69" t="n">
-        <v>31.8</v>
+        <v>33.3</v>
       </c>
       <c r="E69" t="n">
-        <v>36.8</v>
+        <v>36.3</v>
       </c>
       <c r="F69" t="n">
-        <v>31.8</v>
+        <v>33.3</v>
       </c>
       <c r="G69" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="H69" t="n">
-        <v>3.4</v>
+        <v>11.8</v>
       </c>
       <c r="I69" t="n">
-        <v>47.6</v>
+        <v>46.2</v>
       </c>
       <c r="J69" t="n">
-        <v>28.6</v>
+        <v>30.8</v>
       </c>
       <c r="K69" t="n">
-        <v>38.1</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="70">
@@ -3658,34 +3661,34 @@
         <v>83</v>
       </c>
       <c r="B70" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C70" t="n">
-        <v>68.4</v>
+        <v>87.5</v>
       </c>
       <c r="D70" t="n">
-        <v>19.2</v>
+        <v>18.2</v>
       </c>
       <c r="E70" t="n">
-        <v>49.2</v>
+        <v>69.3</v>
       </c>
       <c r="F70" t="n">
-        <v>19.2</v>
+        <v>18.2</v>
       </c>
       <c r="G70" t="n">
-        <v>27.2</v>
+        <v>60</v>
       </c>
       <c r="H70" t="n">
-        <v>8.7</v>
+        <v>16.7</v>
       </c>
       <c r="I70" t="n">
-        <v>41.4</v>
+        <v>66.7</v>
       </c>
       <c r="J70" t="n">
-        <v>29.3</v>
+        <v>33.3</v>
       </c>
       <c r="K70" t="n">
-        <v>40.4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="71">
@@ -3693,34 +3696,34 @@
         <v>84</v>
       </c>
       <c r="B71" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C71" t="n">
-        <v>77.3</v>
+        <v>68.6</v>
       </c>
       <c r="D71" t="n">
-        <v>38.9</v>
+        <v>31.8</v>
       </c>
       <c r="E71" t="n">
-        <v>38.4</v>
+        <v>36.8</v>
       </c>
       <c r="F71" t="n">
-        <v>38.9</v>
+        <v>31.8</v>
       </c>
       <c r="G71" t="n">
-        <v>23.8</v>
+        <v>11.1</v>
       </c>
       <c r="H71" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I71" t="n">
-        <v>41.5</v>
+        <v>47.6</v>
       </c>
       <c r="J71" t="n">
-        <v>38.5</v>
+        <v>28.6</v>
       </c>
       <c r="K71" t="n">
-        <v>47.7</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="72">
@@ -3728,34 +3731,34 @@
         <v>85</v>
       </c>
       <c r="B72" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C72" t="n">
-        <v>56.8</v>
+        <v>68.4</v>
       </c>
       <c r="D72" t="n">
-        <v>8.5</v>
+        <v>19.2</v>
       </c>
       <c r="E72" t="n">
-        <v>48.3</v>
+        <v>49.2</v>
       </c>
       <c r="F72" t="n">
-        <v>8.5</v>
+        <v>19.2</v>
       </c>
       <c r="G72" t="n">
-        <v>32.5</v>
+        <v>27.2</v>
       </c>
       <c r="H72" t="n">
-        <v>14.8</v>
+        <v>8.7</v>
       </c>
       <c r="I72" t="n">
-        <v>48.8</v>
+        <v>41.4</v>
       </c>
       <c r="J72" t="n">
-        <v>27.9</v>
+        <v>29.3</v>
       </c>
       <c r="K72" t="n">
-        <v>22.5</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="73">
@@ -3763,26 +3766,34 @@
         <v>86</v>
       </c>
       <c r="B73" t="s">
-        <v>66</v>
-      </c>
-      <c r="C73"/>
-      <c r="D73"/>
-      <c r="E73"/>
-      <c r="F73"/>
+        <v>68</v>
+      </c>
+      <c r="C73" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="D73" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="E73" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="F73" t="n">
+        <v>38.9</v>
+      </c>
       <c r="G73" t="n">
-        <v>25</v>
+        <v>23.8</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="I73" t="n">
-        <v>33.3</v>
+        <v>41.5</v>
       </c>
       <c r="J73" t="n">
-        <v>33.3</v>
+        <v>38.5</v>
       </c>
       <c r="K73" t="n">
-        <v>66.7</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="74">
@@ -3790,34 +3801,34 @@
         <v>87</v>
       </c>
       <c r="B74" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C74" t="n">
-        <v>75.3</v>
+        <v>56.8</v>
       </c>
       <c r="D74" t="n">
-        <v>22.2</v>
+        <v>8.5</v>
       </c>
       <c r="E74" t="n">
-        <v>53.1</v>
+        <v>48.3</v>
       </c>
       <c r="F74" t="n">
-        <v>22.2</v>
+        <v>8.5</v>
       </c>
       <c r="G74" t="n">
-        <v>32.2</v>
+        <v>32.5</v>
       </c>
       <c r="H74" t="n">
-        <v>9.1</v>
+        <v>14.8</v>
       </c>
       <c r="I74" t="n">
-        <v>47.6</v>
+        <v>48.8</v>
       </c>
       <c r="J74" t="n">
-        <v>28.6</v>
+        <v>27.9</v>
       </c>
       <c r="K74" t="n">
-        <v>48.8</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="75">
@@ -3825,104 +3836,96 @@
         <v>88</v>
       </c>
       <c r="B75" t="s">
-        <v>89</v>
-      </c>
-      <c r="C75" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="D75" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="E75" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="F75" t="n">
-        <v>14.5</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="C75"/>
+      <c r="D75"/>
+      <c r="E75"/>
+      <c r="F75"/>
       <c r="G75" t="n">
-        <v>38.8</v>
+        <v>25</v>
       </c>
       <c r="H75" t="n">
-        <v>11.9</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
         <v>33.3</v>
       </c>
       <c r="J75" t="n">
-        <v>51.9</v>
+        <v>33.3</v>
       </c>
       <c r="K75" t="n">
-        <v>58.6</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B76" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="C76" t="n">
-        <v>71.4</v>
+        <v>75.3</v>
       </c>
       <c r="D76" t="n">
-        <v>26.1</v>
+        <v>22.2</v>
       </c>
       <c r="E76" t="n">
-        <v>45.3</v>
+        <v>53.1</v>
       </c>
       <c r="F76" t="n">
-        <v>26.1</v>
+        <v>22.2</v>
       </c>
       <c r="G76" t="n">
-        <v>22.8</v>
+        <v>32.2</v>
       </c>
       <c r="H76" t="n">
-        <v>5.1</v>
+        <v>9.1</v>
       </c>
       <c r="I76" t="n">
-        <v>60</v>
+        <v>47.6</v>
       </c>
       <c r="J76" t="n">
-        <v>20</v>
+        <v>28.6</v>
       </c>
       <c r="K76" t="n">
-        <v>44.7</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
+        <v>90</v>
+      </c>
+      <c r="B77" t="s">
         <v>91</v>
       </c>
-      <c r="B77" t="s">
-        <v>89</v>
-      </c>
       <c r="C77" t="n">
-        <v>75.8</v>
+        <v>82.7</v>
       </c>
       <c r="D77" t="n">
-        <v>28.2</v>
+        <v>14.5</v>
       </c>
       <c r="E77" t="n">
-        <v>47.6</v>
+        <v>68.2</v>
       </c>
       <c r="F77" t="n">
-        <v>28.2</v>
+        <v>14.5</v>
       </c>
       <c r="G77" t="n">
-        <v>32.7</v>
+        <v>38.8</v>
       </c>
       <c r="H77" t="n">
-        <v>9.5</v>
+        <v>11.9</v>
       </c>
       <c r="I77" t="n">
-        <v>44.4</v>
+        <v>33.3</v>
       </c>
       <c r="J77" t="n">
-        <v>26.7</v>
+        <v>51.9</v>
       </c>
       <c r="K77" t="n">
-        <v>66</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="78">
@@ -3930,34 +3933,34 @@
         <v>92</v>
       </c>
       <c r="B78" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C78" t="n">
-        <v>72.1</v>
+        <v>71.4</v>
       </c>
       <c r="D78" t="n">
-        <v>28</v>
+        <v>26.1</v>
       </c>
       <c r="E78" t="n">
-        <v>44.1</v>
+        <v>45.3</v>
       </c>
       <c r="F78" t="n">
-        <v>28</v>
+        <v>26.1</v>
       </c>
       <c r="G78" t="n">
-        <v>28.8</v>
+        <v>22.8</v>
       </c>
       <c r="H78" t="n">
-        <v>7.9</v>
+        <v>5.1</v>
       </c>
       <c r="I78" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="J78" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K78" t="n">
-        <v>47.9</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="79">
@@ -3965,34 +3968,34 @@
         <v>93</v>
       </c>
       <c r="B79" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C79" t="n">
-        <v>77.1</v>
+        <v>75.8</v>
       </c>
       <c r="D79" t="n">
-        <v>30.3</v>
+        <v>28.2</v>
       </c>
       <c r="E79" t="n">
-        <v>46.8</v>
+        <v>47.6</v>
       </c>
       <c r="F79" t="n">
-        <v>30.3</v>
+        <v>28.2</v>
       </c>
       <c r="G79" t="n">
-        <v>22.6</v>
+        <v>32.7</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="I79" t="n">
-        <v>36.4</v>
+        <v>44.4</v>
       </c>
       <c r="J79" t="n">
-        <v>27.3</v>
+        <v>26.7</v>
       </c>
       <c r="K79" t="n">
-        <v>66.1</v>
+        <v>66</v>
       </c>
     </row>
     <row r="80">
@@ -4000,34 +4003,34 @@
         <v>94</v>
       </c>
       <c r="B80" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C80" t="n">
-        <v>72.9</v>
+        <v>72.1</v>
       </c>
       <c r="D80" t="n">
-        <v>14.1</v>
+        <v>28</v>
       </c>
       <c r="E80" t="n">
-        <v>58.8</v>
+        <v>44.1</v>
       </c>
       <c r="F80" t="n">
-        <v>14.1</v>
+        <v>28</v>
       </c>
       <c r="G80" t="n">
-        <v>20.5</v>
+        <v>28.8</v>
       </c>
       <c r="H80" t="n">
-        <v>12.7</v>
+        <v>7.9</v>
       </c>
       <c r="I80" t="n">
-        <v>30.8</v>
+        <v>52</v>
       </c>
       <c r="J80" t="n">
-        <v>38.5</v>
+        <v>22</v>
       </c>
       <c r="K80" t="n">
-        <v>26</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="81">
@@ -4035,34 +4038,34 @@
         <v>95</v>
       </c>
       <c r="B81" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C81" t="n">
-        <v>72.1</v>
+        <v>77.1</v>
       </c>
       <c r="D81" t="n">
-        <v>22.9</v>
+        <v>30.3</v>
       </c>
       <c r="E81" t="n">
-        <v>49.2</v>
+        <v>46.8</v>
       </c>
       <c r="F81" t="n">
-        <v>22.9</v>
+        <v>30.3</v>
       </c>
       <c r="G81" t="n">
-        <v>32.5</v>
+        <v>22.6</v>
       </c>
       <c r="H81" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>46.9</v>
+        <v>36.4</v>
       </c>
       <c r="J81" t="n">
-        <v>25</v>
+        <v>27.3</v>
       </c>
       <c r="K81" t="n">
-        <v>30</v>
+        <v>66.1</v>
       </c>
     </row>
     <row r="82">
@@ -4070,34 +4073,34 @@
         <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C82" t="n">
-        <v>100</v>
+        <v>72.9</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="E82" t="n">
-        <v>100</v>
+        <v>58.8</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="G82" t="n">
-        <v>46.2</v>
+        <v>20.5</v>
       </c>
       <c r="H82" t="n">
-        <v>33.3</v>
+        <v>12.7</v>
       </c>
       <c r="I82" t="n">
-        <v>100</v>
+        <v>30.8</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>38.5</v>
       </c>
       <c r="K82" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="83">
@@ -4105,34 +4108,34 @@
         <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C83" t="n">
-        <v>66.7</v>
+        <v>72.1</v>
       </c>
       <c r="D83" t="n">
-        <v>29.3</v>
+        <v>22.9</v>
       </c>
       <c r="E83" t="n">
-        <v>37.4</v>
+        <v>49.2</v>
       </c>
       <c r="F83" t="n">
-        <v>29.3</v>
+        <v>22.9</v>
       </c>
       <c r="G83" t="n">
-        <v>20.2</v>
+        <v>32.5</v>
       </c>
       <c r="H83" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="I83" t="n">
-        <v>58.5</v>
+        <v>46.9</v>
       </c>
       <c r="J83" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="K83" t="n">
-        <v>43.4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="84">
@@ -4140,34 +4143,34 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C84" t="n">
-        <v>75.7</v>
+        <v>100</v>
       </c>
       <c r="D84" t="n">
-        <v>32.3</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>43.4</v>
+        <v>100</v>
       </c>
       <c r="F84" t="n">
-        <v>32.3</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>23.7</v>
+        <v>46.2</v>
       </c>
       <c r="H84" t="n">
-        <v>10.8</v>
+        <v>33.3</v>
       </c>
       <c r="I84" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="J84" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="85">
@@ -4175,34 +4178,34 @@
         <v>99</v>
       </c>
       <c r="B85" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C85" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>29.3</v>
       </c>
       <c r="E85" t="n">
-        <v>75</v>
+        <v>37.4</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>29.3</v>
       </c>
       <c r="G85" t="n">
-        <v>22.2</v>
+        <v>20.2</v>
       </c>
       <c r="H85" t="n">
-        <v>25</v>
+        <v>7.4</v>
       </c>
       <c r="I85" t="n">
-        <v>60</v>
+        <v>58.5</v>
       </c>
       <c r="J85" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K85" t="n">
-        <v>40</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="86">
@@ -4210,34 +4213,34 @@
         <v>100</v>
       </c>
       <c r="B86" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C86" t="n">
-        <v>63</v>
+        <v>75.7</v>
       </c>
       <c r="D86" t="n">
-        <v>14</v>
+        <v>32.3</v>
       </c>
       <c r="E86" t="n">
-        <v>49</v>
+        <v>43.4</v>
       </c>
       <c r="F86" t="n">
-        <v>14</v>
+        <v>32.3</v>
       </c>
       <c r="G86" t="n">
-        <v>19</v>
+        <v>23.7</v>
       </c>
       <c r="H86" t="n">
-        <v>11.5</v>
+        <v>10.8</v>
       </c>
       <c r="I86" t="n">
-        <v>60.8</v>
+        <v>48</v>
       </c>
       <c r="J86" t="n">
-        <v>17.6</v>
+        <v>32</v>
       </c>
       <c r="K86" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
     </row>
     <row r="87">
@@ -4245,34 +4248,34 @@
         <v>101</v>
       </c>
       <c r="B87" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C87" t="n">
-        <v>51.7</v>
+        <v>75</v>
       </c>
       <c r="D87" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>36.7</v>
+        <v>75</v>
       </c>
       <c r="F87" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>31.5</v>
+        <v>22.2</v>
       </c>
       <c r="H87" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="I87" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="J87" t="n">
         <v>20</v>
       </c>
       <c r="K87" t="n">
-        <v>29.2</v>
+        <v>40</v>
       </c>
     </row>
     <row r="88">
@@ -4280,401 +4283,401 @@
         <v>102</v>
       </c>
       <c r="B88" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C88" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D88" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="F88" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="G88" t="n">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88"/>
-      <c r="J88"/>
-      <c r="K88"/>
+        <v>11.5</v>
+      </c>
+      <c r="I88" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="J88" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="K88" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B89" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C89" t="n">
-        <v>100</v>
+        <v>51.7</v>
       </c>
       <c r="D89" t="n">
-        <v>33.3</v>
+        <v>15</v>
       </c>
       <c r="E89" t="n">
-        <v>66.7</v>
+        <v>36.7</v>
       </c>
       <c r="F89" t="n">
-        <v>33.3</v>
+        <v>15</v>
       </c>
       <c r="G89" t="n">
-        <v>50</v>
+        <v>31.5</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89"/>
-      <c r="J89"/>
-      <c r="K89"/>
+        <v>3</v>
+      </c>
+      <c r="I89" t="n">
+        <v>72</v>
+      </c>
+      <c r="J89" t="n">
+        <v>20</v>
+      </c>
+      <c r="K89" t="n">
+        <v>29.2</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
+        <v>104</v>
+      </c>
+      <c r="B90" t="s">
         <v>105</v>
       </c>
-      <c r="B90" t="s">
-        <v>103</v>
-      </c>
       <c r="C90" t="n">
-        <v>57.8</v>
+        <v>50</v>
       </c>
       <c r="D90" t="n">
-        <v>8.3</v>
+        <v>50</v>
       </c>
       <c r="E90" t="n">
-        <v>49.5</v>
+        <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>8.3</v>
+        <v>50</v>
       </c>
       <c r="G90" t="n">
-        <v>26.6</v>
+        <v>100</v>
       </c>
       <c r="H90" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I90" t="n">
-        <v>40</v>
-      </c>
-      <c r="J90" t="n">
-        <v>30</v>
-      </c>
-      <c r="K90" t="n">
-        <v>47.4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I90"/>
+      <c r="J90"/>
+      <c r="K90"/>
     </row>
     <row r="91">
       <c r="A91" t="s">
         <v>106</v>
       </c>
       <c r="B91" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C91" t="n">
-        <v>71.4</v>
+        <v>100</v>
       </c>
       <c r="D91" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="E91" t="n">
-        <v>51.4</v>
+        <v>66.7</v>
       </c>
       <c r="F91" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="G91" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="H91" t="n">
-        <v>50</v>
-      </c>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I91"/>
+      <c r="J91"/>
+      <c r="K91"/>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>107</v>
+        <v>38</v>
       </c>
       <c r="B92" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C92" t="n">
-        <v>61.1</v>
+        <v>57.8</v>
       </c>
       <c r="D92" t="n">
-        <v>43.5</v>
+        <v>8.3</v>
       </c>
       <c r="E92" t="n">
-        <v>17.6</v>
+        <v>49.5</v>
       </c>
       <c r="F92" t="n">
-        <v>43.5</v>
+        <v>8.3</v>
       </c>
       <c r="G92" t="n">
-        <v>34.6</v>
+        <v>26.6</v>
       </c>
       <c r="H92" t="n">
-        <v>3.4</v>
+        <v>13.5</v>
       </c>
       <c r="I92" t="n">
-        <v>43.8</v>
+        <v>40</v>
       </c>
       <c r="J92" t="n">
-        <v>12.5</v>
+        <v>30</v>
       </c>
       <c r="K92" t="n">
-        <v>13.3</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B93" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C93" t="n">
-        <v>77.3</v>
+        <v>71.4</v>
       </c>
       <c r="D93" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="E93" t="n">
-        <v>44</v>
+        <v>51.4</v>
       </c>
       <c r="F93" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="G93" t="n">
-        <v>43.5</v>
+        <v>16.7</v>
       </c>
       <c r="H93" t="n">
-        <v>12.2</v>
+        <v>50</v>
       </c>
       <c r="I93" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>41.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B94" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C94" t="n">
-        <v>73.2</v>
+        <v>61.1</v>
       </c>
       <c r="D94" t="n">
-        <v>22.9</v>
+        <v>43.5</v>
       </c>
       <c r="E94" t="n">
-        <v>50.3</v>
+        <v>17.6</v>
       </c>
       <c r="F94" t="n">
-        <v>22.9</v>
+        <v>43.5</v>
       </c>
       <c r="G94" t="n">
-        <v>16.5</v>
+        <v>34.6</v>
       </c>
       <c r="H94" t="n">
-        <v>6.3</v>
+        <v>3.4</v>
       </c>
       <c r="I94" t="n">
-        <v>48.3</v>
+        <v>43.8</v>
       </c>
       <c r="J94" t="n">
-        <v>20.7</v>
+        <v>12.5</v>
       </c>
       <c r="K94" t="n">
-        <v>31</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B95" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C95" t="n">
-        <v>65.2</v>
+        <v>77.3</v>
       </c>
       <c r="D95" t="n">
-        <v>8.4</v>
+        <v>33.3</v>
       </c>
       <c r="E95" t="n">
-        <v>56.8</v>
+        <v>44</v>
       </c>
       <c r="F95" t="n">
-        <v>8.4</v>
+        <v>33.3</v>
       </c>
       <c r="G95" t="n">
-        <v>31.9</v>
+        <v>43.5</v>
       </c>
       <c r="H95" t="n">
-        <v>23.1</v>
+        <v>12.2</v>
       </c>
       <c r="I95" t="n">
-        <v>26.9</v>
+        <v>52</v>
       </c>
       <c r="J95" t="n">
-        <v>34.6</v>
+        <v>16</v>
       </c>
       <c r="K95" t="n">
-        <v>42</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B96" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C96" t="n">
-        <v>68.3</v>
+        <v>73.2</v>
       </c>
       <c r="D96" t="n">
-        <v>26.3</v>
+        <v>22.9</v>
       </c>
       <c r="E96" t="n">
-        <v>42</v>
+        <v>50.3</v>
       </c>
       <c r="F96" t="n">
-        <v>26.3</v>
+        <v>22.9</v>
       </c>
       <c r="G96" t="n">
-        <v>21.7</v>
+        <v>16.5</v>
       </c>
       <c r="H96" t="n">
-        <v>10.5</v>
+        <v>6.3</v>
       </c>
       <c r="I96" t="n">
-        <v>41.9</v>
+        <v>48.3</v>
       </c>
       <c r="J96" t="n">
-        <v>29</v>
+        <v>20.7</v>
       </c>
       <c r="K96" t="n">
-        <v>46.8</v>
+        <v>31</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B97" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C97" t="n">
-        <v>82.2</v>
+        <v>65.2</v>
       </c>
       <c r="D97" t="n">
-        <v>21.7</v>
+        <v>8.4</v>
       </c>
       <c r="E97" t="n">
-        <v>60.5</v>
+        <v>56.8</v>
       </c>
       <c r="F97" t="n">
-        <v>21.7</v>
+        <v>8.4</v>
       </c>
       <c r="G97" t="n">
-        <v>35.4</v>
+        <v>31.9</v>
       </c>
       <c r="H97" t="n">
-        <v>7.5</v>
+        <v>23.1</v>
       </c>
       <c r="I97" t="n">
-        <v>33.3</v>
+        <v>26.9</v>
       </c>
       <c r="J97" t="n">
-        <v>35.7</v>
+        <v>34.6</v>
       </c>
       <c r="K97" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B98" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C98" t="n">
-        <v>71.4</v>
+        <v>68.3</v>
       </c>
       <c r="D98" t="n">
-        <v>35.7</v>
+        <v>26.3</v>
       </c>
       <c r="E98" t="n">
-        <v>35.7</v>
+        <v>42</v>
       </c>
       <c r="F98" t="n">
-        <v>35.7</v>
+        <v>26.3</v>
       </c>
       <c r="G98" t="n">
-        <v>6.1</v>
+        <v>21.7</v>
       </c>
       <c r="H98" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="I98" t="n">
-        <v>38.5</v>
+        <v>41.9</v>
       </c>
       <c r="J98" t="n">
-        <v>15.4</v>
+        <v>29</v>
       </c>
       <c r="K98" t="n">
-        <v>30.8</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B99" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C99" t="n">
-        <v>58.3</v>
+        <v>82.2</v>
       </c>
       <c r="D99" t="n">
-        <v>18.8</v>
+        <v>21.7</v>
       </c>
       <c r="E99" t="n">
-        <v>39.5</v>
+        <v>60.5</v>
       </c>
       <c r="F99" t="n">
-        <v>18.8</v>
+        <v>21.7</v>
       </c>
       <c r="G99" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="H99" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I99" t="n">
         <v>33.3</v>
-      </c>
-      <c r="H99" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" t="n">
-        <v>42.9</v>
       </c>
       <c r="J99" t="n">
         <v>35.7</v>
@@ -4685,798 +4688,798 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B100" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C100" t="n">
-        <v>77.8</v>
+        <v>71.4</v>
       </c>
       <c r="D100" t="n">
-        <v>24.5</v>
+        <v>35.7</v>
       </c>
       <c r="E100" t="n">
-        <v>53.3</v>
+        <v>35.7</v>
       </c>
       <c r="F100" t="n">
-        <v>24.5</v>
+        <v>35.7</v>
       </c>
       <c r="G100" t="n">
-        <v>36.4</v>
+        <v>6.1</v>
       </c>
       <c r="H100" t="n">
-        <v>7.7</v>
+        <v>5.9</v>
       </c>
       <c r="I100" t="n">
-        <v>37.8</v>
+        <v>38.5</v>
       </c>
       <c r="J100" t="n">
-        <v>28.9</v>
+        <v>15.4</v>
       </c>
       <c r="K100" t="n">
-        <v>42.2</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B101" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C101" t="n">
-        <v>65.5</v>
+        <v>58.3</v>
       </c>
       <c r="D101" t="n">
-        <v>15.2</v>
+        <v>18.8</v>
       </c>
       <c r="E101" t="n">
-        <v>50.3</v>
+        <v>39.5</v>
       </c>
       <c r="F101" t="n">
-        <v>15.2</v>
+        <v>18.8</v>
       </c>
       <c r="G101" t="n">
-        <v>16.8</v>
+        <v>33.3</v>
       </c>
       <c r="H101" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>38.9</v>
+        <v>42.9</v>
       </c>
       <c r="J101" t="n">
-        <v>20.8</v>
+        <v>35.7</v>
       </c>
       <c r="K101" t="n">
-        <v>43.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B102" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C102" t="n">
-        <v>54.8</v>
+        <v>77.8</v>
       </c>
       <c r="D102" t="n">
-        <v>18.9</v>
+        <v>24.5</v>
       </c>
       <c r="E102" t="n">
-        <v>35.9</v>
+        <v>53.3</v>
       </c>
       <c r="F102" t="n">
-        <v>18.9</v>
+        <v>24.5</v>
       </c>
       <c r="G102" t="n">
-        <v>17</v>
+        <v>36.4</v>
       </c>
       <c r="H102" t="n">
-        <v>10.8</v>
+        <v>7.7</v>
       </c>
       <c r="I102" t="n">
-        <v>45.2</v>
+        <v>37.8</v>
       </c>
       <c r="J102" t="n">
-        <v>24.2</v>
+        <v>28.9</v>
       </c>
       <c r="K102" t="n">
-        <v>43.5</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C103" t="n">
-        <v>63.2</v>
+        <v>65.5</v>
       </c>
       <c r="D103" t="n">
-        <v>14.8</v>
+        <v>15.2</v>
       </c>
       <c r="E103" t="n">
-        <v>48.4</v>
+        <v>50.3</v>
       </c>
       <c r="F103" t="n">
-        <v>14.8</v>
+        <v>15.2</v>
       </c>
       <c r="G103" t="n">
-        <v>21.9</v>
+        <v>16.8</v>
       </c>
       <c r="H103" t="n">
-        <v>9.5</v>
+        <v>10.2</v>
       </c>
       <c r="I103" t="n">
-        <v>56</v>
+        <v>38.9</v>
       </c>
       <c r="J103" t="n">
-        <v>26</v>
+        <v>20.8</v>
       </c>
       <c r="K103" t="n">
-        <v>52.9</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B104" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C104" t="n">
-        <v>70.2</v>
+        <v>54.8</v>
       </c>
       <c r="D104" t="n">
-        <v>45.7</v>
+        <v>18.9</v>
       </c>
       <c r="E104" t="n">
-        <v>24.5</v>
+        <v>35.9</v>
       </c>
       <c r="F104" t="n">
-        <v>45.7</v>
+        <v>18.9</v>
       </c>
       <c r="G104" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="I104" t="n">
-        <v>42.9</v>
+        <v>45.2</v>
       </c>
       <c r="J104" t="n">
-        <v>33.3</v>
+        <v>24.2</v>
       </c>
       <c r="K104" t="n">
-        <v>52.4</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B105" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C105" t="n">
-        <v>81.8</v>
+        <v>63.2</v>
       </c>
       <c r="D105" t="n">
-        <v>21.4</v>
+        <v>14.8</v>
       </c>
       <c r="E105" t="n">
-        <v>60.4</v>
+        <v>48.4</v>
       </c>
       <c r="F105" t="n">
-        <v>21.4</v>
+        <v>14.8</v>
       </c>
       <c r="G105" t="n">
-        <v>13.3</v>
+        <v>21.9</v>
       </c>
       <c r="H105" t="n">
-        <v>8.3</v>
+        <v>9.5</v>
       </c>
       <c r="I105" t="n">
-        <v>33.3</v>
+        <v>56</v>
       </c>
       <c r="J105" t="n">
-        <v>44.4</v>
+        <v>26</v>
       </c>
       <c r="K105" t="n">
-        <v>55.6</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B106" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C106" t="n">
-        <v>80</v>
+        <v>70.2</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>45.7</v>
       </c>
       <c r="E106" t="n">
-        <v>80</v>
+        <v>24.5</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>45.7</v>
       </c>
       <c r="G106" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="J106" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="K106" t="n">
-        <v>0</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B107" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C107" t="n">
-        <v>70.4</v>
+        <v>81.8</v>
       </c>
       <c r="D107" t="n">
-        <v>18.5</v>
+        <v>21.4</v>
       </c>
       <c r="E107" t="n">
-        <v>51.9</v>
+        <v>60.4</v>
       </c>
       <c r="F107" t="n">
-        <v>18.5</v>
+        <v>21.4</v>
       </c>
       <c r="G107" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="H107" t="n">
-        <v>15.4</v>
+        <v>8.3</v>
       </c>
       <c r="I107" t="n">
-        <v>35.7</v>
+        <v>33.3</v>
       </c>
       <c r="J107" t="n">
-        <v>28.6</v>
+        <v>44.4</v>
       </c>
       <c r="K107" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B108" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C108" t="n">
-        <v>67.6</v>
+        <v>80</v>
       </c>
       <c r="D108" t="n">
-        <v>25.8</v>
+        <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>41.8</v>
+        <v>80</v>
       </c>
       <c r="F108" t="n">
-        <v>25.8</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>32.3</v>
+        <v>25</v>
       </c>
       <c r="H108" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>37.1</v>
+        <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>22.9</v>
+        <v>100</v>
       </c>
       <c r="K108" t="n">
-        <v>37.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B109" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C109" t="n">
-        <v>81.2</v>
+        <v>70.4</v>
       </c>
       <c r="D109" t="n">
-        <v>29.9</v>
+        <v>18.5</v>
       </c>
       <c r="E109" t="n">
-        <v>51.3</v>
+        <v>51.9</v>
       </c>
       <c r="F109" t="n">
-        <v>29.9</v>
+        <v>18.5</v>
       </c>
       <c r="G109" t="n">
-        <v>23.7</v>
+        <v>10</v>
       </c>
       <c r="H109" t="n">
-        <v>6.5</v>
+        <v>15.4</v>
       </c>
       <c r="I109" t="n">
-        <v>40</v>
+        <v>35.7</v>
       </c>
       <c r="J109" t="n">
-        <v>29.2</v>
+        <v>28.6</v>
       </c>
       <c r="K109" t="n">
-        <v>28.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B110" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C110" t="n">
-        <v>53.5</v>
+        <v>67.6</v>
       </c>
       <c r="D110" t="n">
-        <v>30</v>
+        <v>25.8</v>
       </c>
       <c r="E110" t="n">
-        <v>23.5</v>
+        <v>41.8</v>
       </c>
       <c r="F110" t="n">
-        <v>30</v>
+        <v>25.8</v>
       </c>
       <c r="G110" t="n">
-        <v>18.1</v>
+        <v>32.3</v>
       </c>
       <c r="H110" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="I110" t="n">
-        <v>61.9</v>
+        <v>37.1</v>
       </c>
       <c r="J110" t="n">
-        <v>11.9</v>
+        <v>22.9</v>
       </c>
       <c r="K110" t="n">
-        <v>52.4</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B111" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C111" t="n">
-        <v>54.9</v>
+        <v>81.2</v>
       </c>
       <c r="D111" t="n">
-        <v>18.6</v>
+        <v>29.9</v>
       </c>
       <c r="E111" t="n">
-        <v>36.3</v>
+        <v>51.3</v>
       </c>
       <c r="F111" t="n">
-        <v>18.6</v>
+        <v>29.9</v>
       </c>
       <c r="G111" t="n">
-        <v>9.5</v>
+        <v>23.7</v>
       </c>
       <c r="H111" t="n">
-        <v>10.9</v>
+        <v>6.5</v>
       </c>
       <c r="I111" t="n">
-        <v>63.8</v>
+        <v>40</v>
       </c>
       <c r="J111" t="n">
-        <v>13</v>
+        <v>29.2</v>
       </c>
       <c r="K111" t="n">
-        <v>22.1</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B112" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C112" t="n">
-        <v>80</v>
+        <v>53.5</v>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>30</v>
       </c>
       <c r="E112" t="n">
-        <v>68.9</v>
+        <v>23.5</v>
       </c>
       <c r="F112" t="n">
-        <v>11.1</v>
+        <v>30</v>
       </c>
       <c r="G112" t="n">
-        <v>39.5</v>
+        <v>18.1</v>
       </c>
       <c r="H112" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="I112" t="n">
-        <v>63.6</v>
+        <v>61.9</v>
       </c>
       <c r="J112" t="n">
-        <v>9.1</v>
+        <v>11.9</v>
       </c>
       <c r="K112" t="n">
-        <v>45.5</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B113" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C113" t="n">
-        <v>71.9</v>
+        <v>54.9</v>
       </c>
       <c r="D113" t="n">
-        <v>25.7</v>
+        <v>18.6</v>
       </c>
       <c r="E113" t="n">
-        <v>46.2</v>
+        <v>36.3</v>
       </c>
       <c r="F113" t="n">
-        <v>25.7</v>
+        <v>18.6</v>
       </c>
       <c r="G113" t="n">
-        <v>20.9</v>
+        <v>9.5</v>
       </c>
       <c r="H113" t="n">
-        <v>5.7</v>
+        <v>10.9</v>
       </c>
       <c r="I113" t="n">
-        <v>41</v>
+        <v>63.8</v>
       </c>
       <c r="J113" t="n">
-        <v>30.1</v>
+        <v>13</v>
       </c>
       <c r="K113" t="n">
-        <v>43.4</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B114" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C114" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D114" t="n">
-        <v>26.7</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="n">
-        <v>43.3</v>
+        <v>68.9</v>
       </c>
       <c r="F114" t="n">
-        <v>26.7</v>
+        <v>11.1</v>
       </c>
       <c r="G114" t="n">
-        <v>14.8</v>
+        <v>39.5</v>
       </c>
       <c r="H114" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="I114" t="n">
-        <v>60</v>
+        <v>63.6</v>
       </c>
       <c r="J114" t="n">
-        <v>30</v>
+        <v>9.1</v>
       </c>
       <c r="K114" t="n">
-        <v>10</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B115" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C115" t="n">
-        <v>58.5</v>
+        <v>71.9</v>
       </c>
       <c r="D115" t="n">
-        <v>20</v>
+        <v>25.7</v>
       </c>
       <c r="E115" t="n">
-        <v>38.5</v>
+        <v>46.2</v>
       </c>
       <c r="F115" t="n">
-        <v>20</v>
+        <v>25.7</v>
       </c>
       <c r="G115" t="n">
-        <v>20</v>
+        <v>20.9</v>
       </c>
       <c r="H115" t="n">
-        <v>11.8</v>
+        <v>5.7</v>
       </c>
       <c r="I115" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="J115" t="n">
-        <v>25</v>
+        <v>30.1</v>
       </c>
       <c r="K115" t="n">
-        <v>52.6</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B116" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C116" t="n">
-        <v>71.8</v>
+        <v>70</v>
       </c>
       <c r="D116" t="n">
-        <v>22.1</v>
+        <v>26.7</v>
       </c>
       <c r="E116" t="n">
-        <v>49.7</v>
+        <v>43.3</v>
       </c>
       <c r="F116" t="n">
-        <v>22.1</v>
+        <v>26.7</v>
       </c>
       <c r="G116" t="n">
-        <v>32.9</v>
+        <v>14.8</v>
       </c>
       <c r="H116" t="n">
-        <v>9.9</v>
+        <v>12.5</v>
       </c>
       <c r="I116" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J116" t="n">
-        <v>16.1</v>
+        <v>30</v>
       </c>
       <c r="K116" t="n">
-        <v>42.1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B117" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C117" t="n">
-        <v>76.9</v>
+        <v>58.5</v>
       </c>
       <c r="D117" t="n">
         <v>20</v>
       </c>
       <c r="E117" t="n">
-        <v>56.9</v>
+        <v>38.5</v>
       </c>
       <c r="F117" t="n">
         <v>20</v>
       </c>
       <c r="G117" t="n">
-        <v>28.2</v>
+        <v>20</v>
       </c>
       <c r="H117" t="n">
-        <v>10.1</v>
+        <v>11.8</v>
       </c>
       <c r="I117" t="n">
-        <v>39.1</v>
+        <v>50</v>
       </c>
       <c r="J117" t="n">
-        <v>26.6</v>
+        <v>25</v>
       </c>
       <c r="K117" t="n">
-        <v>44.4</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B118" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C118" t="n">
-        <v>72.1</v>
+        <v>71.8</v>
       </c>
       <c r="D118" t="n">
-        <v>24.1</v>
+        <v>22.1</v>
       </c>
       <c r="E118" t="n">
-        <v>48</v>
+        <v>49.7</v>
       </c>
       <c r="F118" t="n">
-        <v>24.1</v>
+        <v>22.1</v>
       </c>
       <c r="G118" t="n">
-        <v>25.5</v>
+        <v>32.9</v>
       </c>
       <c r="H118" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="I118" t="n">
-        <v>40.3</v>
+        <v>50</v>
       </c>
       <c r="J118" t="n">
-        <v>35.8</v>
+        <v>16.1</v>
       </c>
       <c r="K118" t="n">
-        <v>52.2</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B119" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C119" t="n">
-        <v>65.9</v>
+        <v>76.9</v>
       </c>
       <c r="D119" t="n">
-        <v>22.2</v>
+        <v>20</v>
       </c>
       <c r="E119" t="n">
-        <v>43.7</v>
+        <v>56.9</v>
       </c>
       <c r="F119" t="n">
-        <v>22.2</v>
+        <v>20</v>
       </c>
       <c r="G119" t="n">
-        <v>15.6</v>
+        <v>28.2</v>
       </c>
       <c r="H119" t="n">
-        <v>13.8</v>
+        <v>10.1</v>
       </c>
       <c r="I119" t="n">
-        <v>50</v>
+        <v>39.1</v>
       </c>
       <c r="J119" t="n">
-        <v>10</v>
+        <v>26.6</v>
       </c>
       <c r="K119" t="n">
-        <v>35</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B120" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="C120" t="n">
-        <v>100</v>
-      </c>
-      <c r="D120"/>
-      <c r="E120"/>
-      <c r="F120"/>
+        <v>72.1</v>
+      </c>
+      <c r="D120" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E120" t="n">
+        <v>48</v>
+      </c>
+      <c r="F120" t="n">
+        <v>24.1</v>
+      </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>25.5</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>40.3</v>
       </c>
       <c r="J120" t="n">
-        <v>100</v>
+        <v>35.8</v>
       </c>
       <c r="K120" t="n">
-        <v>0</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B121" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="C121" t="n">
-        <v>77.8</v>
+        <v>65.9</v>
       </c>
       <c r="D121" t="n">
-        <v>27.3</v>
+        <v>22.2</v>
       </c>
       <c r="E121" t="n">
-        <v>50.5</v>
+        <v>43.7</v>
       </c>
       <c r="F121" t="n">
-        <v>27.3</v>
+        <v>22.2</v>
       </c>
       <c r="G121" t="n">
-        <v>17.6</v>
+        <v>15.6</v>
       </c>
       <c r="H121" t="n">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="I121" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K121" t="n">
-        <v>28.6</v>
+        <v>35</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B122" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C122" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="D122" t="n">
-        <v>60</v>
-      </c>
-      <c r="E122" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="F122" t="n">
-        <v>60</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D122"/>
+      <c r="E122"/>
+      <c r="F122"/>
       <c r="G122" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -5484,69 +5487,69 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B123" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C123" t="n">
-        <v>62.5</v>
+        <v>77.8</v>
       </c>
       <c r="D123" t="n">
-        <v>21.8</v>
+        <v>27.3</v>
       </c>
       <c r="E123" t="n">
-        <v>40.7</v>
+        <v>50.5</v>
       </c>
       <c r="F123" t="n">
-        <v>21.8</v>
+        <v>27.3</v>
       </c>
       <c r="G123" t="n">
-        <v>15</v>
+        <v>17.6</v>
       </c>
       <c r="H123" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="J123" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>39.4</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B124" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C124" t="n">
-        <v>35</v>
+        <v>66.7</v>
       </c>
       <c r="D124" t="n">
-        <v>13.3</v>
+        <v>60</v>
       </c>
       <c r="E124" t="n">
-        <v>21.7</v>
+        <v>6.7</v>
       </c>
       <c r="F124" t="n">
-        <v>13.3</v>
+        <v>60</v>
       </c>
       <c r="G124" t="n">
         <v>33.3</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I124" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -5554,174 +5557,174 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B125" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C125" t="n">
-        <v>71.4</v>
+        <v>62.5</v>
       </c>
       <c r="D125" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E125" t="n">
-        <v>49.8</v>
+        <v>40.7</v>
       </c>
       <c r="F125" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="G125" t="n">
-        <v>41.2</v>
+        <v>15</v>
       </c>
       <c r="H125" t="n">
-        <v>10</v>
+        <v>8.3</v>
       </c>
       <c r="I125" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="J125" t="n">
-        <v>22.2</v>
+        <v>17.6</v>
       </c>
       <c r="K125" t="n">
-        <v>55.6</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B126" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C126" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="D126" t="n">
-        <v>27</v>
+        <v>13.3</v>
       </c>
       <c r="E126" t="n">
-        <v>43</v>
+        <v>21.7</v>
       </c>
       <c r="F126" t="n">
-        <v>27</v>
+        <v>13.3</v>
       </c>
       <c r="G126" t="n">
-        <v>35.2</v>
+        <v>33.3</v>
       </c>
       <c r="H126" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>32.4</v>
+        <v>50</v>
       </c>
       <c r="J126" t="n">
-        <v>38.2</v>
+        <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>39.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B127" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C127" t="n">
-        <v>60</v>
+        <v>71.4</v>
       </c>
       <c r="D127" t="n">
-        <v>37.5</v>
+        <v>21.6</v>
       </c>
       <c r="E127" t="n">
-        <v>22.5</v>
+        <v>49.8</v>
       </c>
       <c r="F127" t="n">
-        <v>37.5</v>
+        <v>21.6</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>41.2</v>
       </c>
       <c r="H127" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I127" t="n">
-        <v>25</v>
+        <v>55.6</v>
       </c>
       <c r="J127" t="n">
-        <v>50</v>
+        <v>22.2</v>
       </c>
       <c r="K127" t="n">
-        <v>0</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B128" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C128" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D128" t="n">
-        <v>21.2</v>
+        <v>27</v>
       </c>
       <c r="E128" t="n">
-        <v>39.8</v>
+        <v>43</v>
       </c>
       <c r="F128" t="n">
-        <v>21.2</v>
+        <v>27</v>
       </c>
       <c r="G128" t="n">
-        <v>19.4</v>
+        <v>35.2</v>
       </c>
       <c r="H128" t="n">
-        <v>7.5</v>
+        <v>8.9</v>
       </c>
       <c r="I128" t="n">
-        <v>61.4</v>
+        <v>32.4</v>
       </c>
       <c r="J128" t="n">
-        <v>13.6</v>
+        <v>38.2</v>
       </c>
       <c r="K128" t="n">
-        <v>40.9</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B129" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C129" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E129" t="n">
-        <v>66.7</v>
+        <v>22.5</v>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="G129" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I129" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="J129" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -5729,933 +5732,1003 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B130" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C130" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D130" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="E130" t="n">
-        <v>38.9</v>
+        <v>39.8</v>
       </c>
       <c r="F130" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="G130" t="n">
-        <v>36.4</v>
+        <v>19.4</v>
       </c>
       <c r="H130" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="I130" t="n">
-        <v>84.6</v>
+        <v>61.4</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="K130" t="n">
-        <v>46.2</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B131" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C131" t="n">
-        <v>51.9</v>
+        <v>66.7</v>
       </c>
       <c r="D131" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E131" t="n">
-        <v>36.9</v>
+        <v>66.7</v>
       </c>
       <c r="F131" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>30</v>
+        <v>18.2</v>
       </c>
       <c r="H131" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>71.4</v>
+        <v>75</v>
       </c>
       <c r="J131" t="n">
-        <v>28.6</v>
+        <v>25</v>
       </c>
       <c r="K131" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B132" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C132" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D132" t="n">
-        <v>24.8</v>
+        <v>21.1</v>
       </c>
       <c r="E132" t="n">
-        <v>40.2</v>
+        <v>38.9</v>
       </c>
       <c r="F132" t="n">
-        <v>24.8</v>
+        <v>21.1</v>
       </c>
       <c r="G132" t="n">
-        <v>29.7</v>
+        <v>36.4</v>
       </c>
       <c r="H132" t="n">
-        <v>8.1</v>
+        <v>9.5</v>
       </c>
       <c r="I132" t="n">
-        <v>34.9</v>
+        <v>84.6</v>
       </c>
       <c r="J132" t="n">
-        <v>27.9</v>
+        <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>51.2</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B133" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C133" t="n">
-        <v>81.8</v>
+        <v>51.9</v>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E133" t="n">
-        <v>81.8</v>
+        <v>36.9</v>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G133" t="n">
-        <v>11.1</v>
+        <v>30</v>
       </c>
       <c r="H133" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="I133" t="n">
-        <v>20</v>
+        <v>71.4</v>
       </c>
       <c r="J133" t="n">
-        <v>40</v>
+        <v>28.6</v>
       </c>
       <c r="K133" t="n">
-        <v>20</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B134" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C134" t="n">
-        <v>63.9</v>
+        <v>65</v>
       </c>
       <c r="D134" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="E134" t="n">
-        <v>39.2</v>
+        <v>40.2</v>
       </c>
       <c r="F134" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="G134" t="n">
-        <v>21.1</v>
+        <v>29.7</v>
       </c>
       <c r="H134" t="n">
-        <v>1.5</v>
+        <v>8.1</v>
       </c>
       <c r="I134" t="n">
-        <v>64.6</v>
+        <v>34.9</v>
       </c>
       <c r="J134" t="n">
-        <v>18.8</v>
+        <v>27.9</v>
       </c>
       <c r="K134" t="n">
-        <v>31.9</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B135" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C135" t="n">
-        <v>56.1</v>
+        <v>81.8</v>
       </c>
       <c r="D135" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="E135" t="n">
-        <v>36.9</v>
+        <v>81.8</v>
       </c>
       <c r="F135" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>22.5</v>
+        <v>11.1</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>40.5</v>
+        <v>20</v>
       </c>
       <c r="J135" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="K135" t="n">
-        <v>40.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B136" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C136" t="n">
-        <v>77.3</v>
+        <v>63.9</v>
       </c>
       <c r="D136" t="n">
-        <v>21.7</v>
+        <v>24.7</v>
       </c>
       <c r="E136" t="n">
-        <v>55.6</v>
+        <v>39.2</v>
       </c>
       <c r="F136" t="n">
-        <v>21.7</v>
+        <v>24.7</v>
       </c>
       <c r="G136" t="n">
-        <v>33.3</v>
+        <v>21.1</v>
       </c>
       <c r="H136" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I136" t="n">
-        <v>40</v>
+        <v>64.6</v>
       </c>
       <c r="J136" t="n">
-        <v>20</v>
+        <v>18.8</v>
       </c>
       <c r="K136" t="n">
-        <v>10</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C137" t="n">
-        <v>60</v>
+        <v>56.1</v>
       </c>
       <c r="D137" t="n">
-        <v>7.9</v>
+        <v>19.2</v>
       </c>
       <c r="E137" t="n">
-        <v>52.1</v>
+        <v>36.9</v>
       </c>
       <c r="F137" t="n">
-        <v>7.9</v>
+        <v>19.2</v>
       </c>
       <c r="G137" t="n">
-        <v>9.4</v>
+        <v>22.5</v>
       </c>
       <c r="H137" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>51.1</v>
+        <v>40.5</v>
       </c>
       <c r="J137" t="n">
-        <v>10.6</v>
+        <v>27</v>
       </c>
       <c r="K137" t="n">
-        <v>37.8</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B138" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C138" t="n">
-        <v>63.2</v>
+        <v>77.3</v>
       </c>
       <c r="D138" t="n">
-        <v>45</v>
+        <v>21.7</v>
       </c>
       <c r="E138" t="n">
-        <v>18.2</v>
+        <v>55.6</v>
       </c>
       <c r="F138" t="n">
-        <v>45</v>
+        <v>21.7</v>
       </c>
       <c r="G138" t="n">
-        <v>26.9</v>
+        <v>33.3</v>
       </c>
       <c r="H138" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="I138" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J138" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K138" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B139" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C139" t="n">
-        <v>75.5</v>
+        <v>60</v>
       </c>
       <c r="D139" t="n">
-        <v>11.4</v>
+        <v>7.9</v>
       </c>
       <c r="E139" t="n">
-        <v>64.1</v>
+        <v>52.1</v>
       </c>
       <c r="F139" t="n">
-        <v>11.4</v>
+        <v>7.9</v>
       </c>
       <c r="G139" t="n">
-        <v>23.5</v>
+        <v>9.4</v>
       </c>
       <c r="H139" t="n">
-        <v>16.2</v>
+        <v>6.7</v>
       </c>
       <c r="I139" t="n">
-        <v>27.7</v>
+        <v>51.1</v>
       </c>
       <c r="J139" t="n">
-        <v>38.3</v>
+        <v>10.6</v>
       </c>
       <c r="K139" t="n">
-        <v>36.2</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B140" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C140" t="n">
-        <v>74.1</v>
+        <v>63.2</v>
       </c>
       <c r="D140" t="n">
-        <v>22.4</v>
+        <v>45</v>
       </c>
       <c r="E140" t="n">
-        <v>51.7</v>
+        <v>18.2</v>
       </c>
       <c r="F140" t="n">
-        <v>22.4</v>
+        <v>45</v>
       </c>
       <c r="G140" t="n">
-        <v>9.4</v>
+        <v>26.9</v>
       </c>
       <c r="H140" t="n">
-        <v>2.6</v>
+        <v>7.7</v>
       </c>
       <c r="I140" t="n">
-        <v>45.3</v>
+        <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>23.4</v>
+        <v>25</v>
       </c>
       <c r="K140" t="n">
-        <v>32.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B141" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="C141" t="n">
-        <v>71.9</v>
+        <v>75.5</v>
       </c>
       <c r="D141" t="n">
-        <v>17</v>
+        <v>11.4</v>
       </c>
       <c r="E141" t="n">
-        <v>54.9</v>
+        <v>64.1</v>
       </c>
       <c r="F141" t="n">
-        <v>17</v>
+        <v>11.4</v>
       </c>
       <c r="G141" t="n">
-        <v>34.1</v>
+        <v>23.5</v>
       </c>
       <c r="H141" t="n">
-        <v>11.3</v>
+        <v>16.2</v>
       </c>
       <c r="I141" t="n">
-        <v>51.2</v>
+        <v>27.7</v>
       </c>
       <c r="J141" t="n">
-        <v>23.3</v>
+        <v>38.3</v>
       </c>
       <c r="K141" t="n">
-        <v>35.1</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B142" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="C142" t="n">
-        <v>69</v>
+        <v>74.1</v>
       </c>
       <c r="D142" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E142" t="n">
-        <v>46.8</v>
+        <v>51.7</v>
       </c>
       <c r="F142" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="G142" t="n">
-        <v>16.2</v>
+        <v>9.4</v>
       </c>
       <c r="H142" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="I142" t="n">
-        <v>57.1</v>
+        <v>45.3</v>
       </c>
       <c r="J142" t="n">
-        <v>17.9</v>
+        <v>23.4</v>
       </c>
       <c r="K142" t="n">
-        <v>40.4</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B143" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C143" t="n">
-        <v>64.6</v>
+        <v>70.6</v>
       </c>
       <c r="D143" t="n">
-        <v>16.7</v>
+        <v>19.2</v>
       </c>
       <c r="E143" t="n">
-        <v>47.9</v>
+        <v>51.4</v>
       </c>
       <c r="F143" t="n">
-        <v>16.7</v>
+        <v>19.2</v>
       </c>
       <c r="G143" t="n">
-        <v>37.7</v>
+        <v>32.8</v>
       </c>
       <c r="H143" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="I143" t="n">
-        <v>29.6</v>
+        <v>53.2</v>
       </c>
       <c r="J143" t="n">
-        <v>48.1</v>
+        <v>23.4</v>
       </c>
       <c r="K143" t="n">
-        <v>38.5</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B144" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C144" t="n">
-        <v>55.6</v>
+        <v>66.4</v>
       </c>
       <c r="D144" t="n">
-        <v>15.5</v>
+        <v>22.7</v>
       </c>
       <c r="E144" t="n">
-        <v>40.1</v>
+        <v>43.7</v>
       </c>
       <c r="F144" t="n">
-        <v>15.5</v>
+        <v>22.7</v>
       </c>
       <c r="G144" t="n">
-        <v>40</v>
+        <v>14.9</v>
       </c>
       <c r="H144" t="n">
-        <v>14.3</v>
+        <v>6.7</v>
       </c>
       <c r="I144" t="n">
-        <v>29.4</v>
+        <v>57.4</v>
       </c>
       <c r="J144" t="n">
-        <v>41.2</v>
+        <v>16.4</v>
       </c>
       <c r="K144" t="n">
-        <v>26.7</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B145" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C145" t="n">
-        <v>66.1</v>
+        <v>64.6</v>
       </c>
       <c r="D145" t="n">
-        <v>13.4</v>
+        <v>16.7</v>
       </c>
       <c r="E145" t="n">
-        <v>52.7</v>
+        <v>47.9</v>
       </c>
       <c r="F145" t="n">
-        <v>13.4</v>
+        <v>16.7</v>
       </c>
       <c r="G145" t="n">
-        <v>10.7</v>
+        <v>37.7</v>
       </c>
       <c r="H145" t="n">
-        <v>17.1</v>
+        <v>12.5</v>
       </c>
       <c r="I145" t="n">
-        <v>64.9</v>
+        <v>29.6</v>
       </c>
       <c r="J145" t="n">
-        <v>16.2</v>
+        <v>48.1</v>
       </c>
       <c r="K145" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B146" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C146" t="n">
-        <v>78</v>
+        <v>57.6</v>
       </c>
       <c r="D146" t="n">
-        <v>15.7</v>
+        <v>21.4</v>
       </c>
       <c r="E146" t="n">
-        <v>62.3</v>
+        <v>36.2</v>
       </c>
       <c r="F146" t="n">
-        <v>15.7</v>
+        <v>21.4</v>
       </c>
       <c r="G146" t="n">
-        <v>21.7</v>
+        <v>33.9</v>
       </c>
       <c r="H146" t="n">
-        <v>9.6</v>
+        <v>13.2</v>
       </c>
       <c r="I146" t="n">
-        <v>34.3</v>
+        <v>27.8</v>
       </c>
       <c r="J146" t="n">
-        <v>34.3</v>
+        <v>38.9</v>
       </c>
       <c r="K146" t="n">
-        <v>40</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B147" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C147" t="n">
-        <v>53.8</v>
+        <v>65.5</v>
       </c>
       <c r="D147" t="n">
-        <v>18.3</v>
+        <v>15.4</v>
       </c>
       <c r="E147" t="n">
-        <v>35.5</v>
+        <v>50.1</v>
       </c>
       <c r="F147" t="n">
-        <v>18.3</v>
+        <v>15.4</v>
       </c>
       <c r="G147" t="n">
-        <v>23.5</v>
+        <v>10.2</v>
       </c>
       <c r="H147" t="n">
-        <v>13.9</v>
+        <v>16.2</v>
       </c>
       <c r="I147" t="n">
-        <v>51.3</v>
+        <v>63.7</v>
       </c>
       <c r="J147" t="n">
-        <v>23.1</v>
+        <v>17.5</v>
       </c>
       <c r="K147" t="n">
-        <v>28.6</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B148" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C148" t="n">
-        <v>75</v>
+        <v>78.4</v>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
+        <v>15.9</v>
       </c>
       <c r="E148" t="n">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="F148" t="n">
-        <v>0</v>
+        <v>15.9</v>
       </c>
       <c r="G148" t="n">
-        <v>66.7</v>
+        <v>21.1</v>
       </c>
       <c r="H148" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>37.3</v>
       </c>
       <c r="J148" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K148" t="n">
-        <v>0</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B149" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C149" t="n">
-        <v>55.5</v>
+        <v>53.8</v>
       </c>
       <c r="D149" t="n">
-        <v>15.7</v>
+        <v>18.3</v>
       </c>
       <c r="E149" t="n">
-        <v>39.8</v>
+        <v>35.5</v>
       </c>
       <c r="F149" t="n">
-        <v>15.7</v>
+        <v>18.3</v>
       </c>
       <c r="G149" t="n">
-        <v>12.3</v>
+        <v>23.5</v>
       </c>
       <c r="H149" t="n">
-        <v>16.9</v>
+        <v>13.9</v>
       </c>
       <c r="I149" t="n">
-        <v>38</v>
+        <v>51.3</v>
       </c>
       <c r="J149" t="n">
-        <v>26</v>
+        <v>23.1</v>
       </c>
       <c r="K149" t="n">
-        <v>46.7</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B150" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C150" t="n">
-        <v>60.5</v>
+        <v>75</v>
       </c>
       <c r="D150" t="n">
-        <v>20.3</v>
+        <v>0</v>
       </c>
       <c r="E150" t="n">
-        <v>40.2</v>
+        <v>75</v>
       </c>
       <c r="F150" t="n">
-        <v>20.3</v>
+        <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>9.5</v>
+        <v>66.7</v>
       </c>
       <c r="H150" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>57.5</v>
+        <v>0</v>
       </c>
       <c r="J150" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>28.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B151" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C151" t="n">
-        <v>72.5</v>
+        <v>55.8</v>
       </c>
       <c r="D151" t="n">
-        <v>13.1</v>
+        <v>17.6</v>
       </c>
       <c r="E151" t="n">
-        <v>59.4</v>
+        <v>38.2</v>
       </c>
       <c r="F151" t="n">
-        <v>13.1</v>
+        <v>17.6</v>
       </c>
       <c r="G151" t="n">
-        <v>25.6</v>
+        <v>12</v>
       </c>
       <c r="H151" t="n">
-        <v>13.2</v>
+        <v>15.6</v>
       </c>
       <c r="I151" t="n">
-        <v>33.3</v>
+        <v>35.7</v>
       </c>
       <c r="J151" t="n">
-        <v>34.8</v>
+        <v>30.4</v>
       </c>
       <c r="K151" t="n">
-        <v>56.9</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B152" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C152" t="n">
-        <v>82.1</v>
+        <v>59.7</v>
       </c>
       <c r="D152" t="n">
-        <v>27.6</v>
+        <v>20.8</v>
       </c>
       <c r="E152" t="n">
-        <v>54.5</v>
+        <v>38.9</v>
       </c>
       <c r="F152" t="n">
-        <v>27.6</v>
+        <v>20.8</v>
       </c>
       <c r="G152" t="n">
-        <v>40.9</v>
+        <v>9.8</v>
       </c>
       <c r="H152" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="I152" t="n">
-        <v>35.3</v>
+        <v>58.9</v>
       </c>
       <c r="J152" t="n">
-        <v>23.5</v>
+        <v>18.9</v>
       </c>
       <c r="K152" t="n">
-        <v>70.6</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B153" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C153" t="n">
-        <v>74.1</v>
+        <v>71.3</v>
       </c>
       <c r="D153" t="n">
-        <v>19.6</v>
+        <v>15.2</v>
       </c>
       <c r="E153" t="n">
-        <v>54.5</v>
+        <v>56.1</v>
       </c>
       <c r="F153" t="n">
-        <v>19.6</v>
+        <v>15.2</v>
       </c>
       <c r="G153" t="n">
-        <v>17</v>
+        <v>23.8</v>
       </c>
       <c r="H153" t="n">
-        <v>8.4</v>
+        <v>13.4</v>
       </c>
       <c r="I153" t="n">
-        <v>30.9</v>
+        <v>35.7</v>
       </c>
       <c r="J153" t="n">
-        <v>29.4</v>
+        <v>34.3</v>
       </c>
       <c r="K153" t="n">
-        <v>43.3</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B154" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C154" t="n">
-        <v>37.5</v>
+        <v>79.5</v>
       </c>
       <c r="D154" t="n">
-        <v>33.3</v>
+        <v>31.9</v>
       </c>
       <c r="E154" t="n">
-        <v>4.2</v>
+        <v>47.6</v>
       </c>
       <c r="F154" t="n">
-        <v>33.3</v>
+        <v>31.9</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>39.2</v>
       </c>
       <c r="H154" t="n">
-        <v>0</v>
-      </c>
-      <c r="I154"/>
-      <c r="J154"/>
-      <c r="K154"/>
+        <v>8.9</v>
+      </c>
+      <c r="I154" t="n">
+        <v>35</v>
+      </c>
+      <c r="J154" t="n">
+        <v>25</v>
+      </c>
+      <c r="K154" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
+        <v>172</v>
+      </c>
+      <c r="B155" t="s">
+        <v>160</v>
+      </c>
+      <c r="C155" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="D155" t="n">
+        <v>21</v>
+      </c>
+      <c r="E155" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="F155" t="n">
+        <v>21</v>
+      </c>
+      <c r="G155" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H155" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="I155" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="J155" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="K155" t="n">
+        <v>46.2</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
         <v>173</v>
       </c>
-      <c r="B155" t="s">
-        <v>159</v>
-      </c>
-      <c r="C155" t="n">
-        <v>0</v>
-      </c>
-      <c r="D155" t="n">
+      <c r="B156" t="s">
+        <v>160</v>
+      </c>
+      <c r="C156" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="D156" t="n">
         <v>33.3</v>
       </c>
-      <c r="E155" t="n">
+      <c r="E156" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F156" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156"/>
+      <c r="J156"/>
+      <c r="K156"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>174</v>
+      </c>
+      <c r="B157" t="s">
+        <v>160</v>
+      </c>
+      <c r="C157" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E157" t="n">
         <v>-33.3</v>
       </c>
-      <c r="F155" t="n">
+      <c r="F157" t="n">
         <v>33.3</v>
       </c>
-      <c r="G155" t="n">
+      <c r="G157" t="n">
         <v>100</v>
       </c>
-      <c r="H155" t="n">
-        <v>0</v>
-      </c>
-      <c r="I155"/>
-      <c r="J155"/>
-      <c r="K155"/>
-    </row>
-    <row r="156">
-      <c r="A156"/>
-      <c r="B156" t="s">
-        <v>174</v>
-      </c>
-      <c r="C156" t="n">
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157"/>
+      <c r="J157"/>
+      <c r="K157"/>
+    </row>
+    <row r="158">
+      <c r="A158"/>
+      <c r="B158" t="s">
+        <v>175</v>
+      </c>
+      <c r="C158" t="n">
         <v>69.1</v>
       </c>
-      <c r="D156" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E156" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="F156" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G156" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="H156" t="n">
-        <v>9.3</v>
-      </c>
-      <c r="I156" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="J156" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="K156" t="n">
-        <v>38.7</v>
+      <c r="D158" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E158" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="F158" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G158" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="H158" t="n">
+        <v>9.2</v>
+      </c>
+      <c r="I158" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="J158" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="K158" t="n">
+        <v>39.8</v>
       </c>
     </row>
   </sheetData>
@@ -6687,22 +6760,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -6711,18 +6784,18 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -6757,7 +6830,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -6827,7 +6900,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -6862,7 +6935,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -6897,7 +6970,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -6932,7 +7005,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -6967,7 +7040,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -7037,7 +7110,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -7072,7 +7145,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -7107,7 +7180,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -7142,7 +7215,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -7210,7 +7283,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
@@ -7245,77 +7318,77 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
       </c>
       <c r="C17" t="n">
-        <v>50</v>
+        <v>53.8</v>
       </c>
       <c r="D17" t="n">
-        <v>53.5</v>
+        <v>54.7</v>
       </c>
       <c r="E17" t="n">
-        <v>18.5</v>
+        <v>18.8</v>
       </c>
       <c r="F17" t="n">
-        <v>38.5</v>
+        <v>35.7</v>
       </c>
       <c r="G17" t="n">
-        <v>29.8</v>
+        <v>27.5</v>
       </c>
       <c r="H17" t="n">
-        <v>65</v>
+        <v>62.5</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>27.1</v>
+        <v>25</v>
       </c>
       <c r="K17" t="n">
-        <v>-8.5</v>
+        <v>-7.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>44.4</v>
+        <v>52.9</v>
       </c>
       <c r="D18" t="n">
-        <v>40.6</v>
+        <v>39.1</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>22.2</v>
+        <v>35.3</v>
       </c>
       <c r="H18" t="n">
-        <v>40</v>
+        <v>55.6</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>14.3</v>
+        <v>8.3</v>
       </c>
       <c r="K18" t="n">
-        <v>-22.2</v>
+        <v>-35.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
@@ -7350,7 +7423,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
@@ -7385,42 +7458,42 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
       </c>
       <c r="C21" t="n">
-        <v>70.9</v>
+        <v>69.3</v>
       </c>
       <c r="D21" t="n">
-        <v>63.6</v>
+        <v>63.1</v>
       </c>
       <c r="E21" t="n">
-        <v>29.9</v>
+        <v>30.5</v>
       </c>
       <c r="F21" t="n">
-        <v>45.5</v>
+        <v>41.3</v>
       </c>
       <c r="G21" t="n">
-        <v>8.2</v>
+        <v>7.8</v>
       </c>
       <c r="H21" t="n">
-        <v>48.5</v>
+        <v>51.2</v>
       </c>
       <c r="I21" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="J21" t="n">
-        <v>28.9</v>
+        <v>26.6</v>
       </c>
       <c r="K21" t="n">
-        <v>15.4</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B22" t="s">
         <v>34</v>
@@ -7455,7 +7528,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B23" t="s">
         <v>34</v>
@@ -7464,33 +7537,33 @@
         <v>55.6</v>
       </c>
       <c r="D23" t="n">
-        <v>59.1</v>
+        <v>61.5</v>
       </c>
       <c r="E23" t="n">
-        <v>27</v>
+        <v>33.8</v>
       </c>
       <c r="F23" t="n">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
       <c r="G23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="K23" t="n">
         <v>11.1</v>
-      </c>
-      <c r="H23" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>24</v>
-      </c>
-      <c r="K23" t="n">
-        <v>5.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B24" t="s">
         <v>34</v>
@@ -7525,7 +7598,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B25" t="s">
         <v>34</v>
@@ -7560,7 +7633,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
@@ -7569,33 +7642,33 @@
         <v>67.6</v>
       </c>
       <c r="D26" t="n">
-        <v>67.9</v>
+        <v>68</v>
       </c>
       <c r="E26" t="n">
         <v>39.7</v>
       </c>
       <c r="F26" t="n">
-        <v>58.3</v>
+        <v>59.3</v>
       </c>
       <c r="G26" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="H26" t="n">
-        <v>50</v>
+        <v>47.1</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>44.1</v>
+        <v>40</v>
       </c>
       <c r="K26" t="n">
-        <v>35.3</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B27" t="s">
         <v>34</v>
@@ -7630,7 +7703,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B28" t="s">
         <v>34</v>
@@ -7665,42 +7738,42 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B29" t="s">
         <v>34</v>
       </c>
       <c r="C29" t="n">
-        <v>57</v>
+        <v>59.6</v>
       </c>
       <c r="D29" t="n">
-        <v>58.2</v>
+        <v>58.8</v>
       </c>
       <c r="E29" t="n">
-        <v>15.6</v>
+        <v>19.6</v>
       </c>
       <c r="F29" t="n">
-        <v>18.8</v>
+        <v>17.6</v>
       </c>
       <c r="G29" t="n">
-        <v>13.7</v>
+        <v>13.3</v>
       </c>
       <c r="H29" t="n">
-        <v>42.6</v>
+        <v>42.9</v>
       </c>
       <c r="I29" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="J29" t="n">
-        <v>25.9</v>
+        <v>23.1</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.1</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B30" t="s">
         <v>34</v>
@@ -7735,45 +7808,45 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B31" t="s">
         <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D31" t="n">
-        <v>59.6</v>
+        <v>57.9</v>
       </c>
       <c r="E31" t="n">
-        <v>16.7</v>
+        <v>20.3</v>
       </c>
       <c r="F31" t="n">
-        <v>47.4</v>
+        <v>45.5</v>
       </c>
       <c r="G31" t="n">
-        <v>11.8</v>
+        <v>10</v>
       </c>
       <c r="H31" t="n">
-        <v>35</v>
+        <v>37.5</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>29.3</v>
+        <v>27.5</v>
       </c>
       <c r="K31" t="n">
-        <v>14.7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C32" t="n">
         <v>52.1</v>
@@ -7805,10 +7878,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C33" t="n">
         <v>55.6</v>
@@ -7840,10 +7913,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C34" t="n">
         <v>52.3</v>
@@ -7875,10 +7948,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" t="s">
         <v>51</v>
-      </c>
-      <c r="B35" t="s">
-        <v>49</v>
       </c>
       <c r="C35" t="n">
         <v>47.8</v>
@@ -7910,10 +7983,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C36" t="n">
         <v>50.5</v>
@@ -7945,10 +8018,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C37" t="n">
         <v>63.5</v>
@@ -7980,10 +8053,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C38" t="n">
         <v>54.8</v>
@@ -8015,10 +8088,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C39" t="n">
         <v>100</v>
@@ -8048,10 +8121,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C40" t="n">
         <v>67.6</v>
@@ -8083,10 +8156,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C41" t="n">
         <v>50</v>
@@ -8118,10 +8191,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B42" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C42" t="n">
         <v>58.8</v>
@@ -8153,10 +8226,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C43" t="n">
         <v>68.4</v>
@@ -8188,10 +8261,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C44" t="n">
         <v>56.5</v>
@@ -8223,10 +8296,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C45" t="n">
         <v>58</v>
@@ -8258,10 +8331,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B46" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C46" t="n">
         <v>44.4</v>
@@ -8291,10 +8364,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B47" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C47" t="n">
         <v>51.6</v>
@@ -8326,10 +8399,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B48" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C48" t="n">
         <v>60</v>
@@ -8361,10 +8434,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B49" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C49" t="n">
         <v>72.5</v>
@@ -8396,10 +8469,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B50" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C50" t="n">
         <v>59.5</v>
@@ -8431,10 +8504,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B51" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C51" t="n">
         <v>66.7</v>
@@ -8464,10 +8537,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B52" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C52" t="n">
         <v>65.9</v>
@@ -8499,10 +8572,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B53" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C53" t="n">
         <v>53.4</v>
@@ -8534,10 +8607,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B54" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C54" t="n">
         <v>100</v>
@@ -8567,10 +8640,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B55" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C55" t="n">
         <v>62.5</v>
@@ -8602,10 +8675,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B56" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C56" t="n">
         <v>61.7</v>
@@ -8637,10 +8710,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B57" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C57" t="n">
         <v>60.3</v>
@@ -8672,10 +8745,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B58" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C58" t="n">
         <v>59.5</v>
@@ -8707,10 +8780,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B59" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C59" t="n">
         <v>67</v>
@@ -8742,10 +8815,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B60" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C60" t="n">
         <v>63.8</v>
@@ -8777,10 +8850,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B61" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C61" t="n">
         <v>30</v>
@@ -8812,10 +8885,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B62" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C62" t="n">
         <v>37</v>
@@ -8847,10 +8920,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B63" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C63" t="n">
         <v>40</v>
@@ -8882,10 +8955,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B64" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C64" t="n">
         <v>69.5</v>
@@ -8917,10 +8990,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B65" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C65" t="n">
         <v>68.2</v>
@@ -8952,10 +9025,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B66" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C66" t="n">
         <v>50</v>
@@ -8987,10 +9060,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B67" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C67" t="n">
         <v>53.1</v>
@@ -9022,10 +9095,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B68" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C68" t="n">
         <v>64.7</v>
@@ -9057,10 +9130,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B69" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C69" t="n">
         <v>61.1</v>
@@ -9092,10 +9165,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B70" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C70" t="n">
         <v>69.4</v>
@@ -9127,10 +9200,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B71" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C71" t="n">
         <v>58.3</v>
@@ -9162,10 +9235,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B72" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C72" t="n">
         <v>72.7</v>
@@ -9197,10 +9270,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B73" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C73" t="n">
         <v>65</v>
@@ -9232,10 +9305,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B74" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C74" t="n">
         <v>60.1</v>
@@ -9267,10 +9340,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B75" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C75" t="n">
         <v>64.5</v>
@@ -9302,10 +9375,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B76" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C76" t="n">
         <v>42</v>
@@ -9337,10 +9410,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B77" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C77" t="n">
         <v>71.2</v>
@@ -9372,10 +9445,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B78" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C78" t="n">
         <v>50</v>
@@ -9407,10 +9480,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B79" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C79" t="n">
         <v>28.6</v>
@@ -9440,10 +9513,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B80" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C80" t="n">
         <v>48.6</v>
@@ -9475,10 +9548,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B81" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C81" t="n">
         <v>57.9</v>
@@ -9510,10 +9583,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B82" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C82" t="n">
         <v>62.9</v>
@@ -9545,10 +9618,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B83" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C83" t="n">
         <v>54.5</v>
@@ -9580,10 +9653,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B84" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C84" t="n">
         <v>67.3</v>
@@ -9615,10 +9688,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B85" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C85" t="n">
         <v>63.6</v>
@@ -9650,10 +9723,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B86" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C86" t="n">
         <v>50.4</v>
@@ -9685,10 +9758,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B87" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C87" t="n">
         <v>75</v>
@@ -9720,10 +9793,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B88" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C88" t="n">
         <v>55.2</v>
@@ -9755,10 +9828,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B89" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C89" t="n">
         <v>74.2</v>
@@ -9790,10 +9863,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B90" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C90" t="n">
         <v>55.6</v>
@@ -9825,10 +9898,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B91" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C91" t="n">
         <v>59.8</v>
@@ -9860,10 +9933,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B92" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C92" t="n">
         <v>61.2</v>
@@ -9895,10 +9968,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B93" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C93" t="n">
         <v>71.1</v>
@@ -9930,10 +10003,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B94" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C94" t="n">
         <v>58.5</v>
@@ -9965,10 +10038,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B95" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C95" t="n">
         <v>71.4</v>
@@ -10000,10 +10073,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B96" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C96" t="n">
         <v>67.8</v>
@@ -10035,10 +10108,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B97" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C97" t="n">
         <v>70.6</v>
@@ -10070,10 +10143,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B98" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C98" t="n">
         <v>64.1</v>
@@ -10105,10 +10178,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B99" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C99" t="n">
         <v>50</v>
@@ -10140,10 +10213,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
+        <v>139</v>
+      </c>
+      <c r="B100" t="s">
         <v>138</v>
-      </c>
-      <c r="B100" t="s">
-        <v>137</v>
       </c>
       <c r="C100" t="n">
         <v>51.6</v>
@@ -10175,10 +10248,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B101" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C101" t="n">
         <v>62</v>
@@ -10210,10 +10283,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B102" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C102" t="n">
         <v>50</v>
@@ -10243,10 +10316,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B103" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C103" t="n">
         <v>69.7</v>
@@ -10278,10 +10351,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B104" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C104" t="n">
         <v>54.1</v>
@@ -10313,10 +10386,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B105" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C105" t="n">
         <v>50.9</v>
@@ -10348,10 +10421,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B106" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C106" t="n">
         <v>68</v>
@@ -10383,10 +10456,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B107" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C107" t="n">
         <v>52.6</v>
@@ -10418,10 +10491,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B108" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C108" t="n">
         <v>58.1</v>
@@ -10453,10 +10526,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B109" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C109" t="n">
         <v>60.8</v>
@@ -10488,10 +10561,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B110" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C110" t="n">
         <v>44</v>
@@ -10523,10 +10596,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B111" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C111" t="n">
         <v>38.9</v>
@@ -10558,10 +10631,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B112" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C112" t="n">
         <v>59.2</v>
@@ -10593,10 +10666,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B113" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C113" t="n">
         <v>57.8</v>
@@ -10628,10 +10701,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B114" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C114" t="n">
         <v>62.4</v>
@@ -10663,45 +10736,45 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B115" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C115" t="n">
-        <v>56</v>
+        <v>57.8</v>
       </c>
       <c r="D115" t="n">
-        <v>63.7</v>
+        <v>64.1</v>
       </c>
       <c r="E115" t="n">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="F115" t="n">
-        <v>34.5</v>
+        <v>32.3</v>
       </c>
       <c r="G115" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="H115" t="n">
-        <v>32.2</v>
+        <v>28.8</v>
       </c>
       <c r="I115" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="J115" t="n">
-        <v>20.2</v>
+        <v>18.3</v>
       </c>
       <c r="K115" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B116" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C116" t="n">
         <v>60.5</v>
@@ -10733,10 +10806,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B117" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C117" t="n">
         <v>62.5</v>
@@ -10768,10 +10841,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B118" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C118" t="n">
         <v>64.1</v>
@@ -10803,10 +10876,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B119" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C119" t="n">
         <v>84.6</v>
@@ -10836,10 +10909,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B120" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C120" t="n">
         <v>50</v>
@@ -10871,10 +10944,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B121" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C121" t="n">
         <v>61.3</v>
@@ -10906,10 +10979,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B122" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C122" t="n">
         <v>65.8</v>
@@ -10941,45 +11014,45 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B123" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C123" t="n">
-        <v>52.2</v>
+        <v>53.5</v>
       </c>
       <c r="D123" t="n">
-        <v>60.3</v>
+        <v>61.1</v>
       </c>
       <c r="E123" t="n">
-        <v>23.3</v>
+        <v>26.4</v>
       </c>
       <c r="F123" t="n">
-        <v>43.8</v>
+        <v>41.2</v>
       </c>
       <c r="G123" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H123" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="I123" t="n">
+        <v>2</v>
+      </c>
+      <c r="J123" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="K123" t="n">
         <v>10.9</v>
-      </c>
-      <c r="H123" t="n">
-        <v>60</v>
-      </c>
-      <c r="I123" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J123" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="K123" t="n">
-        <v>11.9</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B124" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C124" t="n">
         <v>66.7</v>
@@ -11011,10 +11084,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B125" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C125" t="n">
         <v>69.5</v>
@@ -11046,70 +11119,70 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B126" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C126" t="n">
-        <v>62.5</v>
+        <v>63</v>
       </c>
       <c r="D126" t="n">
-        <v>62.9</v>
+        <v>64.4</v>
       </c>
       <c r="E126" t="n">
-        <v>24.8</v>
+        <v>27</v>
       </c>
       <c r="F126" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="G126" t="n">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="H126" t="n">
-        <v>45.5</v>
+        <v>45.7</v>
       </c>
       <c r="I126" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="J126" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="K126" t="n">
-        <v>14.1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="127">
       <c r="A127"/>
       <c r="B127" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C127" t="n">
-        <v>58.7</v>
+        <v>58.8</v>
       </c>
       <c r="D127" t="n">
-        <v>61</v>
+        <v>61.1</v>
       </c>
       <c r="E127" t="n">
-        <v>20.3</v>
+        <v>20.6</v>
       </c>
       <c r="F127" t="n">
-        <v>37.8</v>
+        <v>37.6</v>
       </c>
       <c r="G127" t="n">
         <v>11</v>
       </c>
       <c r="H127" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="I127" t="n">
         <v>3.2</v>
       </c>
       <c r="J127" t="n">
-        <v>25.2</v>
+        <v>25</v>
       </c>
       <c r="K127" t="n">
-        <v>8.3</v>
+        <v>8.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/summary2026.xlsx
+++ b/data/summary2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="296">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -396,6 +396,9 @@
     <t xml:space="preserve">Eduardo De Oleo</t>
   </si>
   <si>
+    <t xml:space="preserve">Eduardo DeOleo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jaden Babiuk</t>
   </si>
   <si>
@@ -405,6 +408,9 @@
     <t xml:space="preserve">Luis Jean</t>
   </si>
   <si>
+    <t xml:space="preserve">Maikol Escitto</t>
+  </si>
+  <si>
     <t xml:space="preserve">Maikol Escotto</t>
   </si>
   <si>
@@ -639,6 +645,9 @@
     <t xml:space="preserve">Ayden VanEnkevort</t>
   </si>
   <si>
+    <t xml:space="preserve">Ayden Vanenkevort</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bo Buckley</t>
   </si>
   <si>
@@ -814,6 +823,9 @@
   </si>
   <si>
     <t xml:space="preserve">Zachary Laird</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Gerard</t>
   </si>
   <si>
     <t xml:space="preserve">Alex Lanigan</t>
@@ -943,8 +955,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K158" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K158"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K160" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K160"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -963,8 +975,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K127" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K127"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K129" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K129"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -2638,31 +2650,31 @@
         <v>51</v>
       </c>
       <c r="C40" t="n">
-        <v>66.9</v>
+        <v>66.2</v>
       </c>
       <c r="D40" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="E40" t="n">
-        <v>45.5</v>
+        <v>46.5</v>
       </c>
       <c r="F40" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="G40" t="n">
-        <v>18.3</v>
+        <v>18.8</v>
       </c>
       <c r="H40" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="I40" t="n">
-        <v>38.4</v>
+        <v>40</v>
       </c>
       <c r="J40" t="n">
-        <v>34.2</v>
+        <v>33.3</v>
       </c>
       <c r="K40" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="41">
@@ -2702,31 +2714,31 @@
         <v>51</v>
       </c>
       <c r="C42" t="n">
-        <v>69.9</v>
+        <v>70.8</v>
       </c>
       <c r="D42" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="E42" t="n">
-        <v>54.4</v>
+        <v>54.8</v>
       </c>
       <c r="F42" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="G42" t="n">
-        <v>12.4</v>
+        <v>13.2</v>
       </c>
       <c r="H42" t="n">
-        <v>8.8</v>
+        <v>8.3</v>
       </c>
       <c r="I42" t="n">
-        <v>50.7</v>
+        <v>53.4</v>
       </c>
       <c r="J42" t="n">
-        <v>23.2</v>
+        <v>21.9</v>
       </c>
       <c r="K42" t="n">
-        <v>26.1</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="43">
@@ -2737,31 +2749,31 @@
         <v>51</v>
       </c>
       <c r="C43" t="n">
-        <v>76.8</v>
+        <v>77.6</v>
       </c>
       <c r="D43" t="n">
-        <v>30.4</v>
+        <v>29.8</v>
       </c>
       <c r="E43" t="n">
-        <v>46.4</v>
+        <v>47.8</v>
       </c>
       <c r="F43" t="n">
-        <v>30.4</v>
+        <v>29.8</v>
       </c>
       <c r="G43" t="n">
-        <v>25.3</v>
+        <v>24.6</v>
       </c>
       <c r="H43" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I43" t="n">
-        <v>48.5</v>
+        <v>47.8</v>
       </c>
       <c r="J43" t="n">
-        <v>30.3</v>
+        <v>31.9</v>
       </c>
       <c r="K43" t="n">
-        <v>42.2</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="44">
@@ -2838,31 +2850,31 @@
         <v>51</v>
       </c>
       <c r="C46" t="n">
-        <v>64.2</v>
+        <v>65.6</v>
       </c>
       <c r="D46" t="n">
-        <v>21.4</v>
+        <v>22.1</v>
       </c>
       <c r="E46" t="n">
-        <v>42.8</v>
+        <v>43.5</v>
       </c>
       <c r="F46" t="n">
-        <v>21.4</v>
+        <v>22.1</v>
       </c>
       <c r="G46" t="n">
-        <v>18.8</v>
+        <v>19.3</v>
       </c>
       <c r="H46" t="n">
-        <v>9.8</v>
+        <v>9.3</v>
       </c>
       <c r="I46" t="n">
-        <v>53.4</v>
+        <v>54.1</v>
       </c>
       <c r="J46" t="n">
-        <v>17.2</v>
+        <v>16.4</v>
       </c>
       <c r="K46" t="n">
-        <v>22.4</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="47">
@@ -2873,22 +2885,22 @@
         <v>51</v>
       </c>
       <c r="C47" t="n">
-        <v>78.4</v>
+        <v>77.6</v>
       </c>
       <c r="D47" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E47" t="n">
-        <v>57.2</v>
+        <v>55.9</v>
       </c>
       <c r="F47" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="G47" t="n">
-        <v>39.3</v>
+        <v>40.7</v>
       </c>
       <c r="H47" t="n">
-        <v>9.5</v>
+        <v>9.3</v>
       </c>
       <c r="I47" t="n">
         <v>52.2</v>
@@ -2908,31 +2920,31 @@
         <v>51</v>
       </c>
       <c r="C48" t="n">
-        <v>79.3</v>
+        <v>80</v>
       </c>
       <c r="D48" t="n">
-        <v>38.2</v>
+        <v>38.4</v>
       </c>
       <c r="E48" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="F48" t="n">
-        <v>38.2</v>
+        <v>38.4</v>
       </c>
       <c r="G48" t="n">
-        <v>38.3</v>
+        <v>36.9</v>
       </c>
       <c r="H48" t="n">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="I48" t="n">
-        <v>52.4</v>
+        <v>48</v>
       </c>
       <c r="J48" t="n">
-        <v>28.6</v>
+        <v>32</v>
       </c>
       <c r="K48" t="n">
-        <v>52.4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49">
@@ -2978,22 +2990,22 @@
         <v>51</v>
       </c>
       <c r="C50" t="n">
-        <v>69.4</v>
+        <v>67.4</v>
       </c>
       <c r="D50" t="n">
-        <v>16.4</v>
+        <v>15.3</v>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>52.1</v>
       </c>
       <c r="F50" t="n">
-        <v>16.4</v>
+        <v>15.3</v>
       </c>
       <c r="G50" t="n">
-        <v>31.4</v>
+        <v>32.6</v>
       </c>
       <c r="H50" t="n">
-        <v>12.8</v>
+        <v>13.4</v>
       </c>
       <c r="I50" t="n">
         <v>35.4</v>
@@ -3013,31 +3025,31 @@
         <v>51</v>
       </c>
       <c r="C51" t="n">
-        <v>68</v>
+        <v>66.7</v>
       </c>
       <c r="D51" t="n">
-        <v>27.6</v>
+        <v>25</v>
       </c>
       <c r="E51" t="n">
-        <v>40.4</v>
+        <v>41.7</v>
       </c>
       <c r="F51" t="n">
-        <v>27.6</v>
+        <v>25</v>
       </c>
       <c r="G51" t="n">
-        <v>53.7</v>
+        <v>54.5</v>
       </c>
       <c r="H51" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="I51" t="n">
-        <v>63.6</v>
+        <v>58.3</v>
       </c>
       <c r="J51" t="n">
-        <v>18.2</v>
+        <v>25</v>
       </c>
       <c r="K51" t="n">
-        <v>36.4</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="52">
@@ -3048,22 +3060,22 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>70.7</v>
+        <v>70.6</v>
       </c>
       <c r="D52" t="n">
-        <v>14</v>
+        <v>13.3</v>
       </c>
       <c r="E52" t="n">
-        <v>56.7</v>
+        <v>57.3</v>
       </c>
       <c r="F52" t="n">
-        <v>14</v>
+        <v>13.3</v>
       </c>
       <c r="G52" t="n">
-        <v>21.5</v>
+        <v>21</v>
       </c>
       <c r="H52" t="n">
-        <v>7.5</v>
+        <v>9.3</v>
       </c>
       <c r="I52" t="n">
         <v>67.7</v>
@@ -3083,31 +3095,31 @@
         <v>51</v>
       </c>
       <c r="C53" t="n">
-        <v>70.6</v>
+        <v>70.5</v>
       </c>
       <c r="D53" t="n">
-        <v>17.8</v>
+        <v>16.5</v>
       </c>
       <c r="E53" t="n">
-        <v>52.8</v>
+        <v>54</v>
       </c>
       <c r="F53" t="n">
-        <v>17.8</v>
+        <v>16.5</v>
       </c>
       <c r="G53" t="n">
-        <v>26.1</v>
+        <v>24.8</v>
       </c>
       <c r="H53" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I53" t="n">
-        <v>37</v>
+        <v>37.9</v>
       </c>
       <c r="J53" t="n">
-        <v>33.3</v>
+        <v>32.8</v>
       </c>
       <c r="K53" t="n">
-        <v>38.9</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="54">
@@ -3118,31 +3130,31 @@
         <v>51</v>
       </c>
       <c r="C54" t="n">
-        <v>74.3</v>
+        <v>75.3</v>
       </c>
       <c r="D54" t="n">
-        <v>13.4</v>
+        <v>13.1</v>
       </c>
       <c r="E54" t="n">
-        <v>60.9</v>
+        <v>62.2</v>
       </c>
       <c r="F54" t="n">
-        <v>13.4</v>
+        <v>13.1</v>
       </c>
       <c r="G54" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="H54" t="n">
-        <v>13.1</v>
+        <v>12.5</v>
       </c>
       <c r="I54" t="n">
-        <v>20.8</v>
+        <v>21.6</v>
       </c>
       <c r="J54" t="n">
-        <v>41.7</v>
+        <v>41.2</v>
       </c>
       <c r="K54" t="n">
-        <v>52.1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="55">
@@ -3188,31 +3200,31 @@
         <v>68</v>
       </c>
       <c r="C56" t="n">
-        <v>78.6</v>
+        <v>78</v>
       </c>
       <c r="D56" t="n">
-        <v>30.2</v>
+        <v>29.4</v>
       </c>
       <c r="E56" t="n">
-        <v>48.4</v>
+        <v>48.6</v>
       </c>
       <c r="F56" t="n">
-        <v>30.2</v>
+        <v>29.4</v>
       </c>
       <c r="G56" t="n">
-        <v>19.4</v>
+        <v>20.2</v>
       </c>
       <c r="H56" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I56" t="n">
-        <v>38.5</v>
+        <v>41.1</v>
       </c>
       <c r="J56" t="n">
         <v>25</v>
       </c>
       <c r="K56" t="n">
-        <v>32.7</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="57">
@@ -3244,28 +3256,28 @@
         <v>68</v>
       </c>
       <c r="C58" t="n">
-        <v>57.8</v>
+        <v>58.1</v>
       </c>
       <c r="D58" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="E58" t="n">
-        <v>50.2</v>
+        <v>49.6</v>
       </c>
       <c r="F58" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="G58" t="n">
-        <v>26.6</v>
+        <v>25.6</v>
       </c>
       <c r="H58" t="n">
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
       <c r="I58" t="n">
-        <v>60</v>
+        <v>57.9</v>
       </c>
       <c r="J58" t="n">
-        <v>14.3</v>
+        <v>13.2</v>
       </c>
       <c r="K58" t="n">
         <v>32.4</v>
@@ -3384,31 +3396,31 @@
         <v>68</v>
       </c>
       <c r="C62" t="n">
-        <v>78.3</v>
+        <v>78</v>
       </c>
       <c r="D62" t="n">
-        <v>21.9</v>
+        <v>22.3</v>
       </c>
       <c r="E62" t="n">
-        <v>56.4</v>
+        <v>55.7</v>
       </c>
       <c r="F62" t="n">
-        <v>21.9</v>
+        <v>22.3</v>
       </c>
       <c r="G62" t="n">
-        <v>36.6</v>
+        <v>37.6</v>
       </c>
       <c r="H62" t="n">
-        <v>9.7</v>
+        <v>9.3</v>
       </c>
       <c r="I62" t="n">
-        <v>45.6</v>
+        <v>43.3</v>
       </c>
       <c r="J62" t="n">
-        <v>24.6</v>
+        <v>25</v>
       </c>
       <c r="K62" t="n">
-        <v>47.4</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="63">
@@ -3454,31 +3466,31 @@
         <v>68</v>
       </c>
       <c r="C64" t="n">
-        <v>74.3</v>
+        <v>75.3</v>
       </c>
       <c r="D64" t="n">
-        <v>21.4</v>
+        <v>20.4</v>
       </c>
       <c r="E64" t="n">
-        <v>52.9</v>
+        <v>54.9</v>
       </c>
       <c r="F64" t="n">
-        <v>21.4</v>
+        <v>20.4</v>
       </c>
       <c r="G64" t="n">
-        <v>23.3</v>
+        <v>23.8</v>
       </c>
       <c r="H64" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="I64" t="n">
-        <v>50</v>
+        <v>48.3</v>
       </c>
       <c r="J64" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="K64" t="n">
-        <v>37</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="65">
@@ -3734,31 +3746,31 @@
         <v>68</v>
       </c>
       <c r="C72" t="n">
-        <v>68.4</v>
+        <v>68</v>
       </c>
       <c r="D72" t="n">
-        <v>19.2</v>
+        <v>18.1</v>
       </c>
       <c r="E72" t="n">
-        <v>49.2</v>
+        <v>49.9</v>
       </c>
       <c r="F72" t="n">
-        <v>19.2</v>
+        <v>18.1</v>
       </c>
       <c r="G72" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="H72" t="n">
-        <v>8.7</v>
+        <v>9.4</v>
       </c>
       <c r="I72" t="n">
-        <v>41.4</v>
+        <v>41.7</v>
       </c>
       <c r="J72" t="n">
-        <v>29.3</v>
+        <v>28.3</v>
       </c>
       <c r="K72" t="n">
-        <v>40.4</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="73">
@@ -3769,31 +3781,31 @@
         <v>68</v>
       </c>
       <c r="C73" t="n">
-        <v>77.3</v>
+        <v>78.4</v>
       </c>
       <c r="D73" t="n">
-        <v>38.9</v>
+        <v>38.2</v>
       </c>
       <c r="E73" t="n">
-        <v>38.4</v>
+        <v>40.2</v>
       </c>
       <c r="F73" t="n">
-        <v>38.9</v>
+        <v>38.2</v>
       </c>
       <c r="G73" t="n">
         <v>23.8</v>
       </c>
       <c r="H73" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="I73" t="n">
-        <v>41.5</v>
+        <v>39.1</v>
       </c>
       <c r="J73" t="n">
-        <v>38.5</v>
+        <v>37.7</v>
       </c>
       <c r="K73" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="74">
@@ -3804,31 +3816,31 @@
         <v>68</v>
       </c>
       <c r="C74" t="n">
-        <v>56.8</v>
+        <v>56.7</v>
       </c>
       <c r="D74" t="n">
-        <v>8.5</v>
+        <v>8.7</v>
       </c>
       <c r="E74" t="n">
-        <v>48.3</v>
+        <v>48</v>
       </c>
       <c r="F74" t="n">
-        <v>8.5</v>
+        <v>8.7</v>
       </c>
       <c r="G74" t="n">
-        <v>32.5</v>
+        <v>33.3</v>
       </c>
       <c r="H74" t="n">
-        <v>14.8</v>
+        <v>15.2</v>
       </c>
       <c r="I74" t="n">
-        <v>48.8</v>
+        <v>50</v>
       </c>
       <c r="J74" t="n">
-        <v>27.9</v>
+        <v>27.3</v>
       </c>
       <c r="K74" t="n">
-        <v>22.5</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="75">
@@ -3838,24 +3850,32 @@
       <c r="B75" t="s">
         <v>68</v>
       </c>
-      <c r="C75"/>
-      <c r="D75"/>
-      <c r="E75"/>
-      <c r="F75"/>
+      <c r="C75" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
       <c r="G75" t="n">
-        <v>25</v>
+        <v>31.6</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I75" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="K75" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="76">
@@ -3866,31 +3886,31 @@
         <v>68</v>
       </c>
       <c r="C76" t="n">
-        <v>75.3</v>
+        <v>73.8</v>
       </c>
       <c r="D76" t="n">
-        <v>22.2</v>
+        <v>19.2</v>
       </c>
       <c r="E76" t="n">
-        <v>53.1</v>
+        <v>54.6</v>
       </c>
       <c r="F76" t="n">
-        <v>22.2</v>
+        <v>19.2</v>
       </c>
       <c r="G76" t="n">
-        <v>32.2</v>
+        <v>34.4</v>
       </c>
       <c r="H76" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="I76" t="n">
-        <v>47.6</v>
+        <v>48.8</v>
       </c>
       <c r="J76" t="n">
-        <v>28.6</v>
+        <v>27.9</v>
       </c>
       <c r="K76" t="n">
-        <v>48.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="77">
@@ -3936,31 +3956,31 @@
         <v>91</v>
       </c>
       <c r="C78" t="n">
-        <v>71.4</v>
+        <v>72.7</v>
       </c>
       <c r="D78" t="n">
-        <v>26.1</v>
+        <v>31.8</v>
       </c>
       <c r="E78" t="n">
-        <v>45.3</v>
+        <v>40.9</v>
       </c>
       <c r="F78" t="n">
-        <v>26.1</v>
+        <v>31.8</v>
       </c>
       <c r="G78" t="n">
-        <v>22.8</v>
+        <v>21.4</v>
       </c>
       <c r="H78" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="I78" t="n">
         <v>60</v>
       </c>
       <c r="J78" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="K78" t="n">
-        <v>44.7</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="79">
@@ -3971,31 +3991,31 @@
         <v>91</v>
       </c>
       <c r="C79" t="n">
-        <v>75.8</v>
+        <v>74.7</v>
       </c>
       <c r="D79" t="n">
-        <v>28.2</v>
+        <v>28.6</v>
       </c>
       <c r="E79" t="n">
-        <v>47.6</v>
+        <v>46.1</v>
       </c>
       <c r="F79" t="n">
-        <v>28.2</v>
+        <v>28.6</v>
       </c>
       <c r="G79" t="n">
-        <v>32.7</v>
+        <v>33.9</v>
       </c>
       <c r="H79" t="n">
-        <v>9.5</v>
+        <v>10.8</v>
       </c>
       <c r="I79" t="n">
-        <v>44.4</v>
+        <v>43.1</v>
       </c>
       <c r="J79" t="n">
-        <v>26.7</v>
+        <v>25.5</v>
       </c>
       <c r="K79" t="n">
-        <v>66</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="80">
@@ -4006,31 +4026,31 @@
         <v>91</v>
       </c>
       <c r="C80" t="n">
-        <v>72.1</v>
+        <v>73.6</v>
       </c>
       <c r="D80" t="n">
-        <v>28</v>
+        <v>28.7</v>
       </c>
       <c r="E80" t="n">
-        <v>44.1</v>
+        <v>44.9</v>
       </c>
       <c r="F80" t="n">
-        <v>28</v>
+        <v>28.7</v>
       </c>
       <c r="G80" t="n">
-        <v>28.8</v>
+        <v>27</v>
       </c>
       <c r="H80" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="I80" t="n">
-        <v>52</v>
+        <v>53.6</v>
       </c>
       <c r="J80" t="n">
-        <v>22</v>
+        <v>21.4</v>
       </c>
       <c r="K80" t="n">
-        <v>47.9</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="81">
@@ -4041,31 +4061,31 @@
         <v>91</v>
       </c>
       <c r="C81" t="n">
-        <v>77.1</v>
+        <v>78.6</v>
       </c>
       <c r="D81" t="n">
-        <v>30.3</v>
+        <v>30.1</v>
       </c>
       <c r="E81" t="n">
-        <v>46.8</v>
+        <v>48.5</v>
       </c>
       <c r="F81" t="n">
-        <v>30.3</v>
+        <v>30.1</v>
       </c>
       <c r="G81" t="n">
-        <v>22.6</v>
+        <v>24.4</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>36.4</v>
+        <v>38.9</v>
       </c>
       <c r="J81" t="n">
-        <v>27.3</v>
+        <v>27.8</v>
       </c>
       <c r="K81" t="n">
-        <v>66.1</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="82">
@@ -4076,31 +4096,31 @@
         <v>91</v>
       </c>
       <c r="C82" t="n">
-        <v>72.9</v>
+        <v>74</v>
       </c>
       <c r="D82" t="n">
-        <v>14.1</v>
+        <v>19.1</v>
       </c>
       <c r="E82" t="n">
-        <v>58.8</v>
+        <v>54.9</v>
       </c>
       <c r="F82" t="n">
-        <v>14.1</v>
+        <v>19.1</v>
       </c>
       <c r="G82" t="n">
-        <v>20.5</v>
+        <v>24.1</v>
       </c>
       <c r="H82" t="n">
-        <v>12.7</v>
+        <v>11.4</v>
       </c>
       <c r="I82" t="n">
-        <v>30.8</v>
+        <v>31</v>
       </c>
       <c r="J82" t="n">
-        <v>38.5</v>
+        <v>37.9</v>
       </c>
       <c r="K82" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83">
@@ -4111,31 +4131,31 @@
         <v>91</v>
       </c>
       <c r="C83" t="n">
-        <v>72.1</v>
+        <v>72.4</v>
       </c>
       <c r="D83" t="n">
-        <v>22.9</v>
+        <v>22.6</v>
       </c>
       <c r="E83" t="n">
-        <v>49.2</v>
+        <v>49.8</v>
       </c>
       <c r="F83" t="n">
-        <v>22.9</v>
+        <v>22.6</v>
       </c>
       <c r="G83" t="n">
-        <v>32.5</v>
+        <v>30.5</v>
       </c>
       <c r="H83" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="I83" t="n">
-        <v>46.9</v>
+        <v>48.5</v>
       </c>
       <c r="J83" t="n">
-        <v>25</v>
+        <v>24.2</v>
       </c>
       <c r="K83" t="n">
-        <v>30</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="84">
@@ -4146,31 +4166,31 @@
         <v>91</v>
       </c>
       <c r="C84" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E84" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G84" t="n">
-        <v>46.2</v>
+        <v>43.8</v>
       </c>
       <c r="H84" t="n">
-        <v>33.3</v>
+        <v>26.7</v>
       </c>
       <c r="I84" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
     </row>
     <row r="85">
@@ -4181,31 +4201,31 @@
         <v>91</v>
       </c>
       <c r="C85" t="n">
-        <v>66.7</v>
+        <v>70.7</v>
       </c>
       <c r="D85" t="n">
-        <v>29.3</v>
+        <v>26.9</v>
       </c>
       <c r="E85" t="n">
-        <v>37.4</v>
+        <v>43.8</v>
       </c>
       <c r="F85" t="n">
-        <v>29.3</v>
+        <v>26.9</v>
       </c>
       <c r="G85" t="n">
-        <v>20.2</v>
+        <v>19.2</v>
       </c>
       <c r="H85" t="n">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="I85" t="n">
-        <v>58.5</v>
+        <v>57.6</v>
       </c>
       <c r="J85" t="n">
-        <v>17</v>
+        <v>18.6</v>
       </c>
       <c r="K85" t="n">
-        <v>43.4</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="86">
@@ -4251,31 +4271,31 @@
         <v>91</v>
       </c>
       <c r="C87" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E87" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G87" t="n">
-        <v>22.2</v>
+        <v>30.8</v>
       </c>
       <c r="H87" t="n">
-        <v>25</v>
+        <v>18.2</v>
       </c>
       <c r="I87" t="n">
-        <v>60</v>
+        <v>57.1</v>
       </c>
       <c r="J87" t="n">
-        <v>20</v>
+        <v>14.3</v>
       </c>
       <c r="K87" t="n">
-        <v>40</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="88">
@@ -4286,31 +4306,31 @@
         <v>91</v>
       </c>
       <c r="C88" t="n">
+        <v>64</v>
+      </c>
+      <c r="D88" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="E88" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="G88" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H88" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I88" t="n">
         <v>63</v>
       </c>
-      <c r="D88" t="n">
-        <v>14</v>
-      </c>
-      <c r="E88" t="n">
-        <v>49</v>
-      </c>
-      <c r="F88" t="n">
-        <v>14</v>
-      </c>
-      <c r="G88" t="n">
-        <v>19</v>
-      </c>
-      <c r="H88" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="I88" t="n">
-        <v>60.8</v>
-      </c>
       <c r="J88" t="n">
-        <v>17.6</v>
+        <v>16.7</v>
       </c>
       <c r="K88" t="n">
-        <v>42</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="89">
@@ -4321,31 +4341,31 @@
         <v>91</v>
       </c>
       <c r="C89" t="n">
-        <v>51.7</v>
+        <v>53.6</v>
       </c>
       <c r="D89" t="n">
-        <v>15</v>
+        <v>15.6</v>
       </c>
       <c r="E89" t="n">
-        <v>36.7</v>
+        <v>38</v>
       </c>
       <c r="F89" t="n">
-        <v>15</v>
+        <v>15.6</v>
       </c>
       <c r="G89" t="n">
-        <v>31.5</v>
+        <v>30.8</v>
       </c>
       <c r="H89" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="I89" t="n">
-        <v>72</v>
+        <v>66.7</v>
       </c>
       <c r="J89" t="n">
-        <v>20</v>
+        <v>26.7</v>
       </c>
       <c r="K89" t="n">
-        <v>29.2</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="90">
@@ -4417,28 +4437,28 @@
         <v>57.8</v>
       </c>
       <c r="D92" t="n">
-        <v>8.3</v>
+        <v>10.8</v>
       </c>
       <c r="E92" t="n">
-        <v>49.5</v>
+        <v>47</v>
       </c>
       <c r="F92" t="n">
-        <v>8.3</v>
+        <v>10.8</v>
       </c>
       <c r="G92" t="n">
-        <v>26.6</v>
+        <v>26.2</v>
       </c>
       <c r="H92" t="n">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="I92" t="n">
-        <v>40</v>
+        <v>42.9</v>
       </c>
       <c r="J92" t="n">
-        <v>30</v>
+        <v>28.6</v>
       </c>
       <c r="K92" t="n">
-        <v>47.4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="93">
@@ -4522,28 +4542,28 @@
         <v>77.3</v>
       </c>
       <c r="D95" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="E95" t="n">
-        <v>44</v>
+        <v>37.3</v>
       </c>
       <c r="F95" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="G95" t="n">
-        <v>43.5</v>
+        <v>43.6</v>
       </c>
       <c r="H95" t="n">
-        <v>12.2</v>
+        <v>11.3</v>
       </c>
       <c r="I95" t="n">
-        <v>52</v>
+        <v>53.6</v>
       </c>
       <c r="J95" t="n">
-        <v>16</v>
+        <v>17.9</v>
       </c>
       <c r="K95" t="n">
-        <v>41.7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="96">
@@ -4554,31 +4574,31 @@
         <v>105</v>
       </c>
       <c r="C96" t="n">
-        <v>73.2</v>
+        <v>74.7</v>
       </c>
       <c r="D96" t="n">
-        <v>22.9</v>
+        <v>22.2</v>
       </c>
       <c r="E96" t="n">
-        <v>50.3</v>
+        <v>52.5</v>
       </c>
       <c r="F96" t="n">
-        <v>22.9</v>
+        <v>22.2</v>
       </c>
       <c r="G96" t="n">
-        <v>16.5</v>
+        <v>15.7</v>
       </c>
       <c r="H96" t="n">
-        <v>6.3</v>
+        <v>7.2</v>
       </c>
       <c r="I96" t="n">
-        <v>48.3</v>
+        <v>49.2</v>
       </c>
       <c r="J96" t="n">
-        <v>20.7</v>
+        <v>19.7</v>
       </c>
       <c r="K96" t="n">
-        <v>31</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="97">
@@ -4589,31 +4609,31 @@
         <v>105</v>
       </c>
       <c r="C97" t="n">
-        <v>65.2</v>
+        <v>65.5</v>
       </c>
       <c r="D97" t="n">
-        <v>8.4</v>
+        <v>9.7</v>
       </c>
       <c r="E97" t="n">
-        <v>56.8</v>
+        <v>55.8</v>
       </c>
       <c r="F97" t="n">
-        <v>8.4</v>
+        <v>9.7</v>
       </c>
       <c r="G97" t="n">
-        <v>31.9</v>
+        <v>32.3</v>
       </c>
       <c r="H97" t="n">
         <v>23.1</v>
       </c>
       <c r="I97" t="n">
-        <v>26.9</v>
+        <v>28.3</v>
       </c>
       <c r="J97" t="n">
-        <v>34.6</v>
+        <v>34</v>
       </c>
       <c r="K97" t="n">
-        <v>42</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="98">
@@ -4624,31 +4644,31 @@
         <v>105</v>
       </c>
       <c r="C98" t="n">
-        <v>68.3</v>
+        <v>69.2</v>
       </c>
       <c r="D98" t="n">
-        <v>26.3</v>
+        <v>28.2</v>
       </c>
       <c r="E98" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F98" t="n">
-        <v>26.3</v>
+        <v>28.2</v>
       </c>
       <c r="G98" t="n">
-        <v>21.7</v>
+        <v>22.9</v>
       </c>
       <c r="H98" t="n">
-        <v>10.5</v>
+        <v>9.9</v>
       </c>
       <c r="I98" t="n">
-        <v>41.9</v>
+        <v>42.4</v>
       </c>
       <c r="J98" t="n">
-        <v>29</v>
+        <v>27.3</v>
       </c>
       <c r="K98" t="n">
-        <v>46.8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="99">
@@ -4659,31 +4679,31 @@
         <v>105</v>
       </c>
       <c r="C99" t="n">
-        <v>82.2</v>
+        <v>82.4</v>
       </c>
       <c r="D99" t="n">
-        <v>21.7</v>
+        <v>25.6</v>
       </c>
       <c r="E99" t="n">
-        <v>60.5</v>
+        <v>56.8</v>
       </c>
       <c r="F99" t="n">
-        <v>21.7</v>
+        <v>25.6</v>
       </c>
       <c r="G99" t="n">
-        <v>35.4</v>
+        <v>34.7</v>
       </c>
       <c r="H99" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="I99" t="n">
-        <v>33.3</v>
+        <v>37</v>
       </c>
       <c r="J99" t="n">
-        <v>35.7</v>
+        <v>34.8</v>
       </c>
       <c r="K99" t="n">
-        <v>50</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="100">
@@ -4764,31 +4784,31 @@
         <v>105</v>
       </c>
       <c r="C102" t="n">
-        <v>77.8</v>
+        <v>78</v>
       </c>
       <c r="D102" t="n">
-        <v>24.5</v>
+        <v>27.1</v>
       </c>
       <c r="E102" t="n">
-        <v>53.3</v>
+        <v>50.9</v>
       </c>
       <c r="F102" t="n">
-        <v>24.5</v>
+        <v>27.1</v>
       </c>
       <c r="G102" t="n">
-        <v>36.4</v>
+        <v>36.1</v>
       </c>
       <c r="H102" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="I102" t="n">
-        <v>37.8</v>
+        <v>38.3</v>
       </c>
       <c r="J102" t="n">
-        <v>28.9</v>
+        <v>27.7</v>
       </c>
       <c r="K102" t="n">
-        <v>42.2</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="103">
@@ -4799,31 +4819,31 @@
         <v>105</v>
       </c>
       <c r="C103" t="n">
-        <v>65.5</v>
+        <v>66.1</v>
       </c>
       <c r="D103" t="n">
-        <v>15.2</v>
+        <v>18.9</v>
       </c>
       <c r="E103" t="n">
-        <v>50.3</v>
+        <v>47.2</v>
       </c>
       <c r="F103" t="n">
-        <v>15.2</v>
+        <v>18.9</v>
       </c>
       <c r="G103" t="n">
-        <v>16.8</v>
+        <v>17.1</v>
       </c>
       <c r="H103" t="n">
-        <v>10.2</v>
+        <v>9.8</v>
       </c>
       <c r="I103" t="n">
-        <v>38.9</v>
+        <v>40</v>
       </c>
       <c r="J103" t="n">
-        <v>20.8</v>
+        <v>20</v>
       </c>
       <c r="K103" t="n">
-        <v>43.1</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="104">
@@ -4834,31 +4854,31 @@
         <v>105</v>
       </c>
       <c r="C104" t="n">
-        <v>54.8</v>
+        <v>54.1</v>
       </c>
       <c r="D104" t="n">
-        <v>18.9</v>
+        <v>22.6</v>
       </c>
       <c r="E104" t="n">
-        <v>35.9</v>
+        <v>31.5</v>
       </c>
       <c r="F104" t="n">
-        <v>18.9</v>
+        <v>22.6</v>
       </c>
       <c r="G104" t="n">
         <v>17</v>
       </c>
       <c r="H104" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="I104" t="n">
-        <v>45.2</v>
+        <v>43.8</v>
       </c>
       <c r="J104" t="n">
-        <v>24.2</v>
+        <v>23.4</v>
       </c>
       <c r="K104" t="n">
-        <v>43.5</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="105">
@@ -4869,31 +4889,31 @@
         <v>105</v>
       </c>
       <c r="C105" t="n">
-        <v>63.2</v>
+        <v>63.6</v>
       </c>
       <c r="D105" t="n">
-        <v>14.8</v>
+        <v>18.1</v>
       </c>
       <c r="E105" t="n">
-        <v>48.4</v>
+        <v>45.5</v>
       </c>
       <c r="F105" t="n">
-        <v>14.8</v>
+        <v>18.1</v>
       </c>
       <c r="G105" t="n">
-        <v>21.9</v>
+        <v>23.9</v>
       </c>
       <c r="H105" t="n">
-        <v>9.5</v>
+        <v>9.2</v>
       </c>
       <c r="I105" t="n">
-        <v>56</v>
+        <v>56.9</v>
       </c>
       <c r="J105" t="n">
-        <v>26</v>
+        <v>25.5</v>
       </c>
       <c r="K105" t="n">
-        <v>52.9</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="106">
@@ -4904,31 +4924,31 @@
         <v>121</v>
       </c>
       <c r="C106" t="n">
-        <v>70.2</v>
+        <v>67.8</v>
       </c>
       <c r="D106" t="n">
-        <v>45.7</v>
+        <v>34.5</v>
       </c>
       <c r="E106" t="n">
-        <v>24.5</v>
+        <v>33.3</v>
       </c>
       <c r="F106" t="n">
-        <v>45.7</v>
+        <v>34.5</v>
       </c>
       <c r="G106" t="n">
-        <v>26</v>
+        <v>26.7</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="I106" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="J106" t="n">
-        <v>33.3</v>
+        <v>32</v>
       </c>
       <c r="K106" t="n">
-        <v>52.4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="107">
@@ -5009,31 +5029,31 @@
         <v>121</v>
       </c>
       <c r="C109" t="n">
-        <v>70.4</v>
+        <v>69.6</v>
       </c>
       <c r="D109" t="n">
-        <v>18.5</v>
+        <v>23.4</v>
       </c>
       <c r="E109" t="n">
-        <v>51.9</v>
+        <v>46.2</v>
       </c>
       <c r="F109" t="n">
-        <v>18.5</v>
+        <v>23.4</v>
       </c>
       <c r="G109" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="H109" t="n">
-        <v>15.4</v>
+        <v>12.5</v>
       </c>
       <c r="I109" t="n">
-        <v>35.7</v>
+        <v>36.1</v>
       </c>
       <c r="J109" t="n">
-        <v>28.6</v>
+        <v>30.6</v>
       </c>
       <c r="K109" t="n">
-        <v>50</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="110">
@@ -5044,31 +5064,31 @@
         <v>121</v>
       </c>
       <c r="C110" t="n">
-        <v>67.6</v>
+        <v>65.4</v>
       </c>
       <c r="D110" t="n">
-        <v>25.8</v>
+        <v>28.2</v>
       </c>
       <c r="E110" t="n">
-        <v>41.8</v>
+        <v>37.2</v>
       </c>
       <c r="F110" t="n">
-        <v>25.8</v>
+        <v>28.2</v>
       </c>
       <c r="G110" t="n">
-        <v>32.3</v>
+        <v>31.9</v>
       </c>
       <c r="H110" t="n">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="I110" t="n">
-        <v>37.1</v>
+        <v>40.5</v>
       </c>
       <c r="J110" t="n">
-        <v>22.9</v>
+        <v>26.2</v>
       </c>
       <c r="K110" t="n">
-        <v>37.1</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="111">
@@ -5079,31 +5099,31 @@
         <v>121</v>
       </c>
       <c r="C111" t="n">
-        <v>81.2</v>
+        <v>81</v>
       </c>
       <c r="D111" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E111" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="F111" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="G111" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="H111" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I111" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="J111" t="n">
         <v>29.9</v>
       </c>
-      <c r="E111" t="n">
-        <v>51.3</v>
-      </c>
-      <c r="F111" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="G111" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="H111" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I111" t="n">
-        <v>40</v>
-      </c>
-      <c r="J111" t="n">
-        <v>29.2</v>
-      </c>
       <c r="K111" t="n">
-        <v>28.1</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="112">
@@ -5114,31 +5134,31 @@
         <v>121</v>
       </c>
       <c r="C112" t="n">
-        <v>53.5</v>
+        <v>77.8</v>
       </c>
       <c r="D112" t="n">
-        <v>30</v>
+        <v>33.3</v>
       </c>
       <c r="E112" t="n">
-        <v>23.5</v>
+        <v>44.5</v>
       </c>
       <c r="F112" t="n">
-        <v>30</v>
+        <v>33.3</v>
       </c>
       <c r="G112" t="n">
-        <v>18.1</v>
+        <v>45.5</v>
       </c>
       <c r="H112" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>61.9</v>
+        <v>50</v>
       </c>
       <c r="J112" t="n">
-        <v>11.9</v>
+        <v>25</v>
       </c>
       <c r="K112" t="n">
-        <v>52.4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="113">
@@ -5149,31 +5169,31 @@
         <v>121</v>
       </c>
       <c r="C113" t="n">
-        <v>54.9</v>
+        <v>53.4</v>
       </c>
       <c r="D113" t="n">
-        <v>18.6</v>
+        <v>28.1</v>
       </c>
       <c r="E113" t="n">
-        <v>36.3</v>
+        <v>25.3</v>
       </c>
       <c r="F113" t="n">
-        <v>18.6</v>
+        <v>28.1</v>
       </c>
       <c r="G113" t="n">
-        <v>9.5</v>
+        <v>19</v>
       </c>
       <c r="H113" t="n">
-        <v>10.9</v>
+        <v>7.9</v>
       </c>
       <c r="I113" t="n">
-        <v>63.8</v>
+        <v>61.9</v>
       </c>
       <c r="J113" t="n">
-        <v>13</v>
+        <v>11.9</v>
       </c>
       <c r="K113" t="n">
-        <v>22.1</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="114">
@@ -5184,31 +5204,31 @@
         <v>121</v>
       </c>
       <c r="C114" t="n">
-        <v>80</v>
+        <v>54.6</v>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>23.1</v>
       </c>
       <c r="E114" t="n">
-        <v>68.9</v>
+        <v>31.5</v>
       </c>
       <c r="F114" t="n">
-        <v>11.1</v>
+        <v>23.1</v>
       </c>
       <c r="G114" t="n">
-        <v>39.5</v>
+        <v>9.4</v>
       </c>
       <c r="H114" t="n">
-        <v>10</v>
+        <v>11.2</v>
       </c>
       <c r="I114" t="n">
-        <v>63.6</v>
+        <v>60.8</v>
       </c>
       <c r="J114" t="n">
-        <v>9.1</v>
+        <v>13.5</v>
       </c>
       <c r="K114" t="n">
-        <v>45.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="115">
@@ -5219,31 +5239,31 @@
         <v>121</v>
       </c>
       <c r="C115" t="n">
-        <v>71.9</v>
+        <v>80</v>
       </c>
       <c r="D115" t="n">
-        <v>25.7</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="n">
-        <v>46.2</v>
+        <v>68.9</v>
       </c>
       <c r="F115" t="n">
-        <v>25.7</v>
+        <v>11.1</v>
       </c>
       <c r="G115" t="n">
-        <v>20.9</v>
+        <v>39.5</v>
       </c>
       <c r="H115" t="n">
-        <v>5.7</v>
+        <v>10</v>
       </c>
       <c r="I115" t="n">
-        <v>41</v>
+        <v>63.6</v>
       </c>
       <c r="J115" t="n">
-        <v>30.1</v>
+        <v>9.1</v>
       </c>
       <c r="K115" t="n">
-        <v>43.4</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="116">
@@ -5254,31 +5274,31 @@
         <v>121</v>
       </c>
       <c r="C116" t="n">
-        <v>70</v>
+        <v>72.7</v>
       </c>
       <c r="D116" t="n">
-        <v>26.7</v>
+        <v>14.3</v>
       </c>
       <c r="E116" t="n">
-        <v>43.3</v>
+        <v>58.4</v>
       </c>
       <c r="F116" t="n">
-        <v>26.7</v>
+        <v>14.3</v>
       </c>
       <c r="G116" t="n">
-        <v>14.8</v>
+        <v>33.3</v>
       </c>
       <c r="H116" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="J116" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="K116" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="117">
@@ -5289,31 +5309,31 @@
         <v>121</v>
       </c>
       <c r="C117" t="n">
-        <v>58.5</v>
+        <v>71.7</v>
       </c>
       <c r="D117" t="n">
-        <v>20</v>
+        <v>27.8</v>
       </c>
       <c r="E117" t="n">
-        <v>38.5</v>
+        <v>43.9</v>
       </c>
       <c r="F117" t="n">
-        <v>20</v>
+        <v>27.8</v>
       </c>
       <c r="G117" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="H117" t="n">
-        <v>11.8</v>
+        <v>5.5</v>
       </c>
       <c r="I117" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="J117" t="n">
-        <v>25</v>
+        <v>30.7</v>
       </c>
       <c r="K117" t="n">
-        <v>52.6</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="118">
@@ -5324,31 +5344,31 @@
         <v>121</v>
       </c>
       <c r="C118" t="n">
-        <v>71.8</v>
+        <v>70</v>
       </c>
       <c r="D118" t="n">
-        <v>22.1</v>
+        <v>26.7</v>
       </c>
       <c r="E118" t="n">
-        <v>49.7</v>
+        <v>43.3</v>
       </c>
       <c r="F118" t="n">
-        <v>22.1</v>
+        <v>26.7</v>
       </c>
       <c r="G118" t="n">
-        <v>32.9</v>
+        <v>14.8</v>
       </c>
       <c r="H118" t="n">
-        <v>9.9</v>
+        <v>12.5</v>
       </c>
       <c r="I118" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J118" t="n">
-        <v>16.1</v>
+        <v>30</v>
       </c>
       <c r="K118" t="n">
-        <v>42.1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="119">
@@ -5359,31 +5379,31 @@
         <v>121</v>
       </c>
       <c r="C119" t="n">
-        <v>76.9</v>
+        <v>56.8</v>
       </c>
       <c r="D119" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="E119" t="n">
-        <v>56.9</v>
+        <v>37.2</v>
       </c>
       <c r="F119" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="G119" t="n">
-        <v>28.2</v>
+        <v>19.6</v>
       </c>
       <c r="H119" t="n">
-        <v>10.1</v>
+        <v>11.4</v>
       </c>
       <c r="I119" t="n">
-        <v>39.1</v>
+        <v>50</v>
       </c>
       <c r="J119" t="n">
-        <v>26.6</v>
+        <v>25</v>
       </c>
       <c r="K119" t="n">
-        <v>44.4</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="120">
@@ -5397,28 +5417,28 @@
         <v>72.1</v>
       </c>
       <c r="D120" t="n">
-        <v>24.1</v>
+        <v>22.6</v>
       </c>
       <c r="E120" t="n">
-        <v>48</v>
+        <v>49.5</v>
       </c>
       <c r="F120" t="n">
-        <v>24.1</v>
+        <v>22.6</v>
       </c>
       <c r="G120" t="n">
-        <v>25.5</v>
+        <v>32.6</v>
       </c>
       <c r="H120" t="n">
         <v>9</v>
       </c>
       <c r="I120" t="n">
-        <v>40.3</v>
+        <v>50</v>
       </c>
       <c r="J120" t="n">
-        <v>35.8</v>
+        <v>19.4</v>
       </c>
       <c r="K120" t="n">
-        <v>52.2</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="121">
@@ -5429,31 +5449,31 @@
         <v>121</v>
       </c>
       <c r="C121" t="n">
-        <v>65.9</v>
+        <v>76.3</v>
       </c>
       <c r="D121" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E121" t="n">
-        <v>43.7</v>
+        <v>53.9</v>
       </c>
       <c r="F121" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="G121" t="n">
-        <v>15.6</v>
+        <v>30.3</v>
       </c>
       <c r="H121" t="n">
-        <v>13.8</v>
+        <v>10</v>
       </c>
       <c r="I121" t="n">
-        <v>50</v>
+        <v>37.9</v>
       </c>
       <c r="J121" t="n">
-        <v>10</v>
+        <v>27.3</v>
       </c>
       <c r="K121" t="n">
-        <v>35</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="122">
@@ -5461,95 +5481,95 @@
         <v>137</v>
       </c>
       <c r="B122" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="C122" t="n">
-        <v>100</v>
-      </c>
-      <c r="D122"/>
-      <c r="E122"/>
-      <c r="F122"/>
+        <v>73.7</v>
+      </c>
+      <c r="D122" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E122" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="F122" t="n">
+        <v>23.1</v>
+      </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>26.9</v>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>41.1</v>
       </c>
       <c r="J122" t="n">
-        <v>100</v>
+        <v>34.2</v>
       </c>
       <c r="K122" t="n">
-        <v>0</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B123" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="C123" t="n">
-        <v>77.8</v>
+        <v>67.4</v>
       </c>
       <c r="D123" t="n">
-        <v>27.3</v>
+        <v>21.6</v>
       </c>
       <c r="E123" t="n">
-        <v>50.5</v>
+        <v>45.8</v>
       </c>
       <c r="F123" t="n">
-        <v>27.3</v>
+        <v>21.6</v>
       </c>
       <c r="G123" t="n">
-        <v>17.6</v>
+        <v>14.9</v>
       </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="I123" t="n">
-        <v>42.9</v>
+        <v>54.5</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="K123" t="n">
-        <v>28.6</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
+        <v>139</v>
+      </c>
+      <c r="B124" t="s">
         <v>140</v>
       </c>
-      <c r="B124" t="s">
-        <v>138</v>
-      </c>
       <c r="C124" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="D124" t="n">
-        <v>60</v>
-      </c>
-      <c r="E124" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="F124" t="n">
-        <v>60</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D124"/>
+      <c r="E124"/>
+      <c r="F124"/>
       <c r="G124" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -5560,34 +5580,34 @@
         <v>141</v>
       </c>
       <c r="B125" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C125" t="n">
-        <v>62.5</v>
+        <v>77.8</v>
       </c>
       <c r="D125" t="n">
-        <v>21.8</v>
+        <v>27.3</v>
       </c>
       <c r="E125" t="n">
-        <v>40.7</v>
+        <v>50.5</v>
       </c>
       <c r="F125" t="n">
-        <v>21.8</v>
+        <v>27.3</v>
       </c>
       <c r="G125" t="n">
-        <v>15</v>
+        <v>17.6</v>
       </c>
       <c r="H125" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="J125" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>39.4</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="126">
@@ -5595,31 +5615,31 @@
         <v>142</v>
       </c>
       <c r="B126" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C126" t="n">
-        <v>35</v>
+        <v>66.7</v>
       </c>
       <c r="D126" t="n">
-        <v>13.3</v>
+        <v>60</v>
       </c>
       <c r="E126" t="n">
-        <v>21.7</v>
+        <v>6.7</v>
       </c>
       <c r="F126" t="n">
-        <v>13.3</v>
+        <v>60</v>
       </c>
       <c r="G126" t="n">
         <v>33.3</v>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I126" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
@@ -5630,34 +5650,34 @@
         <v>143</v>
       </c>
       <c r="B127" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C127" t="n">
-        <v>71.4</v>
+        <v>64.6</v>
       </c>
       <c r="D127" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E127" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F127" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="G127" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="H127" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I127" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="J127" t="n">
         <v>21.6</v>
       </c>
-      <c r="E127" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="F127" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G127" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="H127" t="n">
-        <v>10</v>
-      </c>
-      <c r="I127" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="J127" t="n">
-        <v>22.2</v>
-      </c>
       <c r="K127" t="n">
-        <v>55.6</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="128">
@@ -5665,34 +5685,34 @@
         <v>144</v>
       </c>
       <c r="B128" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C128" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="D128" t="n">
-        <v>27</v>
+        <v>13.3</v>
       </c>
       <c r="E128" t="n">
-        <v>43</v>
+        <v>21.7</v>
       </c>
       <c r="F128" t="n">
-        <v>27</v>
+        <v>13.3</v>
       </c>
       <c r="G128" t="n">
-        <v>35.2</v>
+        <v>33.3</v>
       </c>
       <c r="H128" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>32.4</v>
+        <v>50</v>
       </c>
       <c r="J128" t="n">
-        <v>38.2</v>
+        <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>39.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -5700,34 +5720,34 @@
         <v>145</v>
       </c>
       <c r="B129" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C129" t="n">
-        <v>60</v>
+        <v>73.1</v>
       </c>
       <c r="D129" t="n">
-        <v>37.5</v>
+        <v>33.9</v>
       </c>
       <c r="E129" t="n">
-        <v>22.5</v>
+        <v>39.2</v>
       </c>
       <c r="F129" t="n">
-        <v>37.5</v>
+        <v>33.9</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>35.7</v>
       </c>
       <c r="H129" t="n">
-        <v>20</v>
+        <v>7.9</v>
       </c>
       <c r="I129" t="n">
-        <v>25</v>
+        <v>53.8</v>
       </c>
       <c r="J129" t="n">
-        <v>50</v>
+        <v>23.1</v>
       </c>
       <c r="K129" t="n">
-        <v>0</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="130">
@@ -5735,34 +5755,34 @@
         <v>146</v>
       </c>
       <c r="B130" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C130" t="n">
-        <v>61</v>
+        <v>71.7</v>
       </c>
       <c r="D130" t="n">
-        <v>21.2</v>
+        <v>27.7</v>
       </c>
       <c r="E130" t="n">
-        <v>39.8</v>
+        <v>44</v>
       </c>
       <c r="F130" t="n">
-        <v>21.2</v>
+        <v>27.7</v>
       </c>
       <c r="G130" t="n">
-        <v>19.4</v>
+        <v>32.8</v>
       </c>
       <c r="H130" t="n">
-        <v>7.5</v>
+        <v>10.8</v>
       </c>
       <c r="I130" t="n">
-        <v>61.4</v>
+        <v>35.9</v>
       </c>
       <c r="J130" t="n">
-        <v>13.6</v>
+        <v>35.9</v>
       </c>
       <c r="K130" t="n">
-        <v>40.9</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="131">
@@ -5770,31 +5790,31 @@
         <v>147</v>
       </c>
       <c r="B131" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C131" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>36.4</v>
       </c>
       <c r="E131" t="n">
-        <v>66.7</v>
+        <v>23.6</v>
       </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>36.4</v>
       </c>
       <c r="G131" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I131" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="J131" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -5805,34 +5825,34 @@
         <v>148</v>
       </c>
       <c r="B132" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C132" t="n">
-        <v>60</v>
+        <v>62.6</v>
       </c>
       <c r="D132" t="n">
-        <v>21.1</v>
+        <v>23.9</v>
       </c>
       <c r="E132" t="n">
-        <v>38.9</v>
+        <v>38.7</v>
       </c>
       <c r="F132" t="n">
-        <v>21.1</v>
+        <v>23.9</v>
       </c>
       <c r="G132" t="n">
-        <v>36.4</v>
+        <v>18.6</v>
       </c>
       <c r="H132" t="n">
-        <v>9.5</v>
+        <v>6.6</v>
       </c>
       <c r="I132" t="n">
-        <v>84.6</v>
+        <v>58.8</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
+        <v>15.7</v>
       </c>
       <c r="K132" t="n">
-        <v>46.2</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="133">
@@ -5840,34 +5860,34 @@
         <v>149</v>
       </c>
       <c r="B133" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C133" t="n">
-        <v>51.9</v>
+        <v>66.7</v>
       </c>
       <c r="D133" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>36.9</v>
+        <v>66.7</v>
       </c>
       <c r="F133" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>30</v>
+        <v>18.2</v>
       </c>
       <c r="H133" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>71.4</v>
+        <v>75</v>
       </c>
       <c r="J133" t="n">
-        <v>28.6</v>
+        <v>25</v>
       </c>
       <c r="K133" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -5875,34 +5895,34 @@
         <v>150</v>
       </c>
       <c r="B134" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C134" t="n">
-        <v>65</v>
+        <v>65.6</v>
       </c>
       <c r="D134" t="n">
-        <v>24.8</v>
+        <v>21.7</v>
       </c>
       <c r="E134" t="n">
-        <v>40.2</v>
+        <v>43.9</v>
       </c>
       <c r="F134" t="n">
-        <v>24.8</v>
+        <v>21.7</v>
       </c>
       <c r="G134" t="n">
-        <v>29.7</v>
+        <v>35</v>
       </c>
       <c r="H134" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I134" t="n">
-        <v>34.9</v>
+        <v>81.2</v>
       </c>
       <c r="J134" t="n">
-        <v>27.9</v>
+        <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>51.2</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="135">
@@ -5910,34 +5930,34 @@
         <v>151</v>
       </c>
       <c r="B135" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C135" t="n">
-        <v>81.8</v>
+        <v>51.9</v>
       </c>
       <c r="D135" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E135" t="n">
-        <v>81.8</v>
+        <v>36.9</v>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G135" t="n">
-        <v>11.1</v>
+        <v>30</v>
       </c>
       <c r="H135" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="I135" t="n">
-        <v>20</v>
+        <v>71.4</v>
       </c>
       <c r="J135" t="n">
-        <v>40</v>
+        <v>28.6</v>
       </c>
       <c r="K135" t="n">
-        <v>20</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="136">
@@ -5945,34 +5965,34 @@
         <v>152</v>
       </c>
       <c r="B136" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C136" t="n">
-        <v>63.9</v>
+        <v>67.2</v>
       </c>
       <c r="D136" t="n">
-        <v>24.7</v>
+        <v>29.6</v>
       </c>
       <c r="E136" t="n">
-        <v>39.2</v>
+        <v>37.6</v>
       </c>
       <c r="F136" t="n">
-        <v>24.7</v>
+        <v>29.6</v>
       </c>
       <c r="G136" t="n">
-        <v>21.1</v>
+        <v>31.5</v>
       </c>
       <c r="H136" t="n">
-        <v>1.5</v>
+        <v>7.2</v>
       </c>
       <c r="I136" t="n">
-        <v>64.6</v>
+        <v>36</v>
       </c>
       <c r="J136" t="n">
-        <v>18.8</v>
+        <v>28</v>
       </c>
       <c r="K136" t="n">
-        <v>31.9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="137">
@@ -5980,34 +6000,34 @@
         <v>153</v>
       </c>
       <c r="B137" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C137" t="n">
-        <v>56.1</v>
+        <v>81.8</v>
       </c>
       <c r="D137" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>36.9</v>
+        <v>81.8</v>
       </c>
       <c r="F137" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>22.5</v>
+        <v>11.1</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>40.5</v>
+        <v>20</v>
       </c>
       <c r="J137" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="K137" t="n">
-        <v>40.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="138">
@@ -6015,34 +6035,34 @@
         <v>154</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C138" t="n">
-        <v>77.3</v>
+        <v>64.7</v>
       </c>
       <c r="D138" t="n">
-        <v>21.7</v>
+        <v>25</v>
       </c>
       <c r="E138" t="n">
-        <v>55.6</v>
+        <v>39.7</v>
       </c>
       <c r="F138" t="n">
-        <v>21.7</v>
+        <v>25</v>
       </c>
       <c r="G138" t="n">
-        <v>33.3</v>
+        <v>21.2</v>
       </c>
       <c r="H138" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="I138" t="n">
-        <v>40</v>
+        <v>61.1</v>
       </c>
       <c r="J138" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="K138" t="n">
-        <v>10</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="139">
@@ -6050,34 +6070,34 @@
         <v>155</v>
       </c>
       <c r="B139" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C139" t="n">
-        <v>60</v>
+        <v>56.1</v>
       </c>
       <c r="D139" t="n">
-        <v>7.9</v>
+        <v>19.2</v>
       </c>
       <c r="E139" t="n">
-        <v>52.1</v>
+        <v>36.9</v>
       </c>
       <c r="F139" t="n">
-        <v>7.9</v>
+        <v>19.2</v>
       </c>
       <c r="G139" t="n">
-        <v>9.4</v>
+        <v>22.5</v>
       </c>
       <c r="H139" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>51.1</v>
+        <v>40.5</v>
       </c>
       <c r="J139" t="n">
-        <v>10.6</v>
+        <v>27</v>
       </c>
       <c r="K139" t="n">
-        <v>37.8</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="140">
@@ -6085,34 +6105,34 @@
         <v>156</v>
       </c>
       <c r="B140" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C140" t="n">
-        <v>63.2</v>
+        <v>78.6</v>
       </c>
       <c r="D140" t="n">
-        <v>45</v>
+        <v>39.1</v>
       </c>
       <c r="E140" t="n">
-        <v>18.2</v>
+        <v>39.5</v>
       </c>
       <c r="F140" t="n">
-        <v>45</v>
+        <v>39.1</v>
       </c>
       <c r="G140" t="n">
-        <v>26.9</v>
+        <v>28.9</v>
       </c>
       <c r="H140" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>0</v>
+        <v>57.1</v>
       </c>
       <c r="J140" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
       <c r="K140" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="141">
@@ -6120,34 +6140,34 @@
         <v>157</v>
       </c>
       <c r="B141" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C141" t="n">
-        <v>75.5</v>
+        <v>61.5</v>
       </c>
       <c r="D141" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="E141" t="n">
-        <v>64.1</v>
+        <v>50.3</v>
       </c>
       <c r="F141" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="G141" t="n">
-        <v>23.5</v>
+        <v>9.3</v>
       </c>
       <c r="H141" t="n">
-        <v>16.2</v>
+        <v>8.6</v>
       </c>
       <c r="I141" t="n">
-        <v>27.7</v>
+        <v>49.1</v>
       </c>
       <c r="J141" t="n">
-        <v>38.3</v>
+        <v>10.9</v>
       </c>
       <c r="K141" t="n">
-        <v>36.2</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="142">
@@ -6155,34 +6175,34 @@
         <v>158</v>
       </c>
       <c r="B142" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C142" t="n">
-        <v>74.1</v>
+        <v>63.2</v>
       </c>
       <c r="D142" t="n">
-        <v>22.4</v>
+        <v>45</v>
       </c>
       <c r="E142" t="n">
-        <v>51.7</v>
+        <v>18.2</v>
       </c>
       <c r="F142" t="n">
-        <v>22.4</v>
+        <v>45</v>
       </c>
       <c r="G142" t="n">
-        <v>9.4</v>
+        <v>26.9</v>
       </c>
       <c r="H142" t="n">
-        <v>2.6</v>
+        <v>7.7</v>
       </c>
       <c r="I142" t="n">
-        <v>45.3</v>
+        <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>23.4</v>
+        <v>25</v>
       </c>
       <c r="K142" t="n">
-        <v>32.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="143">
@@ -6190,104 +6210,104 @@
         <v>159</v>
       </c>
       <c r="B143" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="C143" t="n">
-        <v>70.6</v>
+        <v>75</v>
       </c>
       <c r="D143" t="n">
-        <v>19.2</v>
+        <v>12.7</v>
       </c>
       <c r="E143" t="n">
-        <v>51.4</v>
+        <v>62.3</v>
       </c>
       <c r="F143" t="n">
-        <v>19.2</v>
+        <v>12.7</v>
       </c>
       <c r="G143" t="n">
-        <v>32.8</v>
+        <v>23.8</v>
       </c>
       <c r="H143" t="n">
-        <v>10.4</v>
+        <v>15.7</v>
       </c>
       <c r="I143" t="n">
-        <v>53.2</v>
+        <v>29.6</v>
       </c>
       <c r="J143" t="n">
-        <v>23.4</v>
+        <v>37</v>
       </c>
       <c r="K143" t="n">
-        <v>41.5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B144" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="C144" t="n">
-        <v>66.4</v>
+        <v>74.6</v>
       </c>
       <c r="D144" t="n">
-        <v>22.7</v>
+        <v>25.3</v>
       </c>
       <c r="E144" t="n">
-        <v>43.7</v>
+        <v>49.3</v>
       </c>
       <c r="F144" t="n">
-        <v>22.7</v>
+        <v>25.3</v>
       </c>
       <c r="G144" t="n">
-        <v>14.9</v>
+        <v>8.6</v>
       </c>
       <c r="H144" t="n">
-        <v>6.7</v>
+        <v>2.4</v>
       </c>
       <c r="I144" t="n">
-        <v>57.4</v>
+        <v>46.4</v>
       </c>
       <c r="J144" t="n">
-        <v>16.4</v>
+        <v>23.2</v>
       </c>
       <c r="K144" t="n">
-        <v>40.4</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
+        <v>161</v>
+      </c>
+      <c r="B145" t="s">
         <v>162</v>
       </c>
-      <c r="B145" t="s">
-        <v>160</v>
-      </c>
       <c r="C145" t="n">
-        <v>64.6</v>
+        <v>70.6</v>
       </c>
       <c r="D145" t="n">
-        <v>16.7</v>
+        <v>20.2</v>
       </c>
       <c r="E145" t="n">
-        <v>47.9</v>
+        <v>50.4</v>
       </c>
       <c r="F145" t="n">
-        <v>16.7</v>
+        <v>20.2</v>
       </c>
       <c r="G145" t="n">
-        <v>37.7</v>
+        <v>36.2</v>
       </c>
       <c r="H145" t="n">
-        <v>12.5</v>
+        <v>9.9</v>
       </c>
       <c r="I145" t="n">
-        <v>29.6</v>
+        <v>52.1</v>
       </c>
       <c r="J145" t="n">
-        <v>48.1</v>
+        <v>22.9</v>
       </c>
       <c r="K145" t="n">
-        <v>38.5</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="146">
@@ -6295,34 +6315,34 @@
         <v>163</v>
       </c>
       <c r="B146" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C146" t="n">
-        <v>57.6</v>
+        <v>66.4</v>
       </c>
       <c r="D146" t="n">
-        <v>21.4</v>
+        <v>20.8</v>
       </c>
       <c r="E146" t="n">
-        <v>36.2</v>
+        <v>45.6</v>
       </c>
       <c r="F146" t="n">
-        <v>21.4</v>
+        <v>20.8</v>
       </c>
       <c r="G146" t="n">
-        <v>33.9</v>
+        <v>16.1</v>
       </c>
       <c r="H146" t="n">
-        <v>13.2</v>
+        <v>7.4</v>
       </c>
       <c r="I146" t="n">
-        <v>27.8</v>
+        <v>54.7</v>
       </c>
       <c r="J146" t="n">
-        <v>38.9</v>
+        <v>20.3</v>
       </c>
       <c r="K146" t="n">
-        <v>31.2</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="147">
@@ -6330,34 +6350,34 @@
         <v>164</v>
       </c>
       <c r="B147" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C147" t="n">
-        <v>65.5</v>
+        <v>64.6</v>
       </c>
       <c r="D147" t="n">
-        <v>15.4</v>
+        <v>16.7</v>
       </c>
       <c r="E147" t="n">
-        <v>50.1</v>
+        <v>47.9</v>
       </c>
       <c r="F147" t="n">
-        <v>15.4</v>
+        <v>16.7</v>
       </c>
       <c r="G147" t="n">
-        <v>10.2</v>
+        <v>37.7</v>
       </c>
       <c r="H147" t="n">
-        <v>16.2</v>
+        <v>12.5</v>
       </c>
       <c r="I147" t="n">
-        <v>63.7</v>
+        <v>29.6</v>
       </c>
       <c r="J147" t="n">
-        <v>17.5</v>
+        <v>48.1</v>
       </c>
       <c r="K147" t="n">
-        <v>38.2</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="148">
@@ -6365,34 +6385,34 @@
         <v>165</v>
       </c>
       <c r="B148" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C148" t="n">
-        <v>78.4</v>
+        <v>57.6</v>
       </c>
       <c r="D148" t="n">
-        <v>15.9</v>
+        <v>21.4</v>
       </c>
       <c r="E148" t="n">
-        <v>62.5</v>
+        <v>36.2</v>
       </c>
       <c r="F148" t="n">
-        <v>15.9</v>
+        <v>21.4</v>
       </c>
       <c r="G148" t="n">
-        <v>21.1</v>
+        <v>33.9</v>
       </c>
       <c r="H148" t="n">
-        <v>10</v>
+        <v>13.2</v>
       </c>
       <c r="I148" t="n">
-        <v>37.3</v>
+        <v>27.8</v>
       </c>
       <c r="J148" t="n">
-        <v>33.3</v>
+        <v>38.9</v>
       </c>
       <c r="K148" t="n">
-        <v>44.3</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="149">
@@ -6400,34 +6420,34 @@
         <v>166</v>
       </c>
       <c r="B149" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C149" t="n">
-        <v>53.8</v>
+        <v>65.5</v>
       </c>
       <c r="D149" t="n">
-        <v>18.3</v>
+        <v>15.4</v>
       </c>
       <c r="E149" t="n">
-        <v>35.5</v>
+        <v>50.1</v>
       </c>
       <c r="F149" t="n">
-        <v>18.3</v>
+        <v>15.4</v>
       </c>
       <c r="G149" t="n">
-        <v>23.5</v>
+        <v>10.2</v>
       </c>
       <c r="H149" t="n">
-        <v>13.9</v>
+        <v>16.2</v>
       </c>
       <c r="I149" t="n">
-        <v>51.3</v>
+        <v>63.7</v>
       </c>
       <c r="J149" t="n">
-        <v>23.1</v>
+        <v>17.5</v>
       </c>
       <c r="K149" t="n">
-        <v>28.6</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="150">
@@ -6435,34 +6455,34 @@
         <v>167</v>
       </c>
       <c r="B150" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C150" t="n">
-        <v>75</v>
+        <v>79.9</v>
       </c>
       <c r="D150" t="n">
-        <v>0</v>
+        <v>14.9</v>
       </c>
       <c r="E150" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F150" t="n">
-        <v>0</v>
+        <v>14.9</v>
       </c>
       <c r="G150" t="n">
-        <v>66.7</v>
+        <v>22.1</v>
       </c>
       <c r="H150" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="I150" t="n">
-        <v>0</v>
+        <v>37.2</v>
       </c>
       <c r="J150" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K150" t="n">
-        <v>0</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="151">
@@ -6470,34 +6490,34 @@
         <v>168</v>
       </c>
       <c r="B151" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C151" t="n">
-        <v>55.8</v>
+        <v>54.6</v>
       </c>
       <c r="D151" t="n">
-        <v>17.6</v>
+        <v>16.9</v>
       </c>
       <c r="E151" t="n">
-        <v>38.2</v>
+        <v>37.7</v>
       </c>
       <c r="F151" t="n">
-        <v>17.6</v>
+        <v>16.9</v>
       </c>
       <c r="G151" t="n">
-        <v>12</v>
+        <v>27.4</v>
       </c>
       <c r="H151" t="n">
-        <v>15.6</v>
+        <v>13</v>
       </c>
       <c r="I151" t="n">
-        <v>35.7</v>
+        <v>51.2</v>
       </c>
       <c r="J151" t="n">
-        <v>30.4</v>
+        <v>24.4</v>
       </c>
       <c r="K151" t="n">
-        <v>43.1</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="152">
@@ -6505,34 +6525,34 @@
         <v>169</v>
       </c>
       <c r="B152" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C152" t="n">
-        <v>59.7</v>
+        <v>75</v>
       </c>
       <c r="D152" t="n">
-        <v>20.8</v>
+        <v>0</v>
       </c>
       <c r="E152" t="n">
-        <v>38.9</v>
+        <v>75</v>
       </c>
       <c r="F152" t="n">
-        <v>20.8</v>
+        <v>0</v>
       </c>
       <c r="G152" t="n">
-        <v>9.8</v>
+        <v>66.7</v>
       </c>
       <c r="H152" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>58.9</v>
+        <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>18.9</v>
+        <v>0</v>
       </c>
       <c r="K152" t="n">
-        <v>29.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -6540,34 +6560,34 @@
         <v>170</v>
       </c>
       <c r="B153" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C153" t="n">
-        <v>71.3</v>
+        <v>54.7</v>
       </c>
       <c r="D153" t="n">
-        <v>15.2</v>
+        <v>17</v>
       </c>
       <c r="E153" t="n">
-        <v>56.1</v>
+        <v>37.7</v>
       </c>
       <c r="F153" t="n">
-        <v>15.2</v>
+        <v>17</v>
       </c>
       <c r="G153" t="n">
-        <v>23.8</v>
+        <v>13.2</v>
       </c>
       <c r="H153" t="n">
-        <v>13.4</v>
+        <v>17.1</v>
       </c>
       <c r="I153" t="n">
-        <v>35.7</v>
+        <v>36.2</v>
       </c>
       <c r="J153" t="n">
-        <v>34.3</v>
+        <v>31</v>
       </c>
       <c r="K153" t="n">
-        <v>58.1</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="154">
@@ -6575,34 +6595,34 @@
         <v>171</v>
       </c>
       <c r="B154" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C154" t="n">
-        <v>79.5</v>
+        <v>60.7</v>
       </c>
       <c r="D154" t="n">
-        <v>31.9</v>
+        <v>20.3</v>
       </c>
       <c r="E154" t="n">
-        <v>47.6</v>
+        <v>40.4</v>
       </c>
       <c r="F154" t="n">
-        <v>31.9</v>
+        <v>20.3</v>
       </c>
       <c r="G154" t="n">
-        <v>39.2</v>
+        <v>10.3</v>
       </c>
       <c r="H154" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="I154" t="n">
-        <v>35</v>
+        <v>58.5</v>
       </c>
       <c r="J154" t="n">
-        <v>25</v>
+        <v>18.1</v>
       </c>
       <c r="K154" t="n">
-        <v>70</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="155">
@@ -6610,34 +6630,34 @@
         <v>172</v>
       </c>
       <c r="B155" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C155" t="n">
-        <v>73.8</v>
+        <v>70.9</v>
       </c>
       <c r="D155" t="n">
-        <v>21</v>
+        <v>15.8</v>
       </c>
       <c r="E155" t="n">
-        <v>52.8</v>
+        <v>55.1</v>
       </c>
       <c r="F155" t="n">
-        <v>21</v>
+        <v>15.8</v>
       </c>
       <c r="G155" t="n">
-        <v>16.7</v>
+        <v>24</v>
       </c>
       <c r="H155" t="n">
-        <v>8.9</v>
+        <v>12.9</v>
       </c>
       <c r="I155" t="n">
-        <v>31.5</v>
+        <v>37.8</v>
       </c>
       <c r="J155" t="n">
-        <v>30.1</v>
+        <v>32.4</v>
       </c>
       <c r="K155" t="n">
-        <v>46.2</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="156">
@@ -6645,90 +6665,160 @@
         <v>173</v>
       </c>
       <c r="B156" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C156" t="n">
-        <v>37.5</v>
+        <v>78</v>
       </c>
       <c r="D156" t="n">
-        <v>33.3</v>
+        <v>30.7</v>
       </c>
       <c r="E156" t="n">
-        <v>4.2</v>
+        <v>47.3</v>
       </c>
       <c r="F156" t="n">
-        <v>33.3</v>
+        <v>30.7</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>39.4</v>
       </c>
       <c r="H156" t="n">
-        <v>0</v>
-      </c>
-      <c r="I156"/>
-      <c r="J156"/>
-      <c r="K156"/>
+        <v>8</v>
+      </c>
+      <c r="I156" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="J156" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="K156" t="n">
+        <v>68.2</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
         <v>174</v>
       </c>
       <c r="B157" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C157" t="n">
-        <v>0</v>
+        <v>72.8</v>
       </c>
       <c r="D157" t="n">
+        <v>20</v>
+      </c>
+      <c r="E157" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="F157" t="n">
+        <v>20</v>
+      </c>
+      <c r="G157" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="H157" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I157" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="J157" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="K157" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>175</v>
+      </c>
+      <c r="B158" t="s">
+        <v>162</v>
+      </c>
+      <c r="C158" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="D158" t="n">
         <v>33.3</v>
       </c>
-      <c r="E157" t="n">
+      <c r="E158" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F158" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158"/>
+      <c r="J158"/>
+      <c r="K158"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>176</v>
+      </c>
+      <c r="B159" t="s">
+        <v>162</v>
+      </c>
+      <c r="C159" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E159" t="n">
         <v>-33.3</v>
       </c>
-      <c r="F157" t="n">
+      <c r="F159" t="n">
         <v>33.3</v>
       </c>
-      <c r="G157" t="n">
+      <c r="G159" t="n">
         <v>100</v>
       </c>
-      <c r="H157" t="n">
-        <v>0</v>
-      </c>
-      <c r="I157"/>
-      <c r="J157"/>
-      <c r="K157"/>
-    </row>
-    <row r="158">
-      <c r="A158"/>
-      <c r="B158" t="s">
-        <v>175</v>
-      </c>
-      <c r="C158" t="n">
-        <v>69.1</v>
-      </c>
-      <c r="D158" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="E158" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="F158" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="G158" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="H158" t="n">
-        <v>9.2</v>
-      </c>
-      <c r="I158" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="J158" t="n">
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159"/>
+      <c r="J159"/>
+      <c r="K159"/>
+    </row>
+    <row r="160">
+      <c r="A160"/>
+      <c r="B160" t="s">
+        <v>177</v>
+      </c>
+      <c r="C160" t="n">
+        <v>68.9</v>
+      </c>
+      <c r="D160" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E160" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="F160" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G160" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="H160" t="n">
+        <v>9</v>
+      </c>
+      <c r="I160" t="n">
+        <v>47</v>
+      </c>
+      <c r="J160" t="n">
         <v>25.6</v>
       </c>
-      <c r="K158" t="n">
-        <v>39.8</v>
+      <c r="K160" t="n">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -6760,22 +6850,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -6784,18 +6874,18 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -6830,7 +6920,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -6900,7 +6990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -6970,7 +7060,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -7005,7 +7095,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -7040,7 +7130,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -7110,7 +7200,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -7145,7 +7235,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -7180,7 +7270,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -7215,7 +7305,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -7283,7 +7373,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
@@ -7318,7 +7408,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
@@ -7353,7 +7443,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
@@ -7423,7 +7513,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
@@ -7458,7 +7548,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
@@ -7493,7 +7583,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B22" t="s">
         <v>34</v>
@@ -7528,7 +7618,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B23" t="s">
         <v>34</v>
@@ -7563,7 +7653,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B24" t="s">
         <v>34</v>
@@ -7598,7 +7688,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B25" t="s">
         <v>34</v>
@@ -7633,7 +7723,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
@@ -7668,7 +7758,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B27" t="s">
         <v>34</v>
@@ -7703,7 +7793,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B28" t="s">
         <v>34</v>
@@ -7738,7 +7828,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B29" t="s">
         <v>34</v>
@@ -7773,7 +7863,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B30" t="s">
         <v>34</v>
@@ -7808,7 +7898,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B31" t="s">
         <v>34</v>
@@ -7843,7 +7933,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B32" t="s">
         <v>51</v>
@@ -7878,7 +7968,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B33" t="s">
         <v>51</v>
@@ -7913,3275 +8003,3343 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B34" t="s">
         <v>51</v>
       </c>
       <c r="C34" t="n">
-        <v>52.3</v>
+        <v>25</v>
       </c>
       <c r="D34" t="n">
-        <v>56.9</v>
+        <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="F34" t="n">
-        <v>34.4</v>
+        <v>75</v>
       </c>
       <c r="G34" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="H34" t="n">
-        <v>45.7</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="H34"/>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>22.7</v>
+        <v>66.7</v>
       </c>
       <c r="K34" t="n">
-        <v>4.6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>53</v>
+        <v>211</v>
       </c>
       <c r="B35" t="s">
         <v>51</v>
       </c>
       <c r="C35" t="n">
-        <v>47.8</v>
+        <v>52.3</v>
       </c>
       <c r="D35" t="n">
-        <v>53.7</v>
+        <v>56.9</v>
       </c>
       <c r="E35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="G35" t="n">
         <v>12.1</v>
       </c>
-      <c r="F35" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="G35" t="n">
-        <v>15.2</v>
-      </c>
       <c r="H35" t="n">
-        <v>53.3</v>
+        <v>45.7</v>
       </c>
       <c r="I35" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>19.4</v>
+        <v>22.7</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.2</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>209</v>
+        <v>53</v>
       </c>
       <c r="B36" t="s">
         <v>51</v>
       </c>
       <c r="C36" t="n">
-        <v>50.5</v>
+        <v>47.8</v>
       </c>
       <c r="D36" t="n">
-        <v>56.9</v>
+        <v>53.7</v>
       </c>
       <c r="E36" t="n">
-        <v>15.9</v>
+        <v>12.1</v>
       </c>
       <c r="F36" t="n">
-        <v>37.5</v>
+        <v>28.6</v>
       </c>
       <c r="G36" t="n">
-        <v>11</v>
+        <v>15.2</v>
       </c>
       <c r="H36" t="n">
-        <v>56.1</v>
+        <v>53.3</v>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J36" t="n">
-        <v>24.5</v>
+        <v>19.4</v>
       </c>
       <c r="K36" t="n">
-        <v>5.5</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B37" t="s">
         <v>51</v>
       </c>
       <c r="C37" t="n">
-        <v>63.5</v>
+        <v>50.5</v>
       </c>
       <c r="D37" t="n">
-        <v>64.4</v>
+        <v>56.9</v>
       </c>
       <c r="E37" t="n">
-        <v>19.3</v>
+        <v>15.9</v>
       </c>
       <c r="F37" t="n">
-        <v>28.6</v>
+        <v>37.5</v>
       </c>
       <c r="G37" t="n">
-        <v>7.7</v>
+        <v>11</v>
       </c>
       <c r="H37" t="n">
-        <v>37.8</v>
+        <v>56.1</v>
       </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
-        <v>22</v>
+        <v>24.5</v>
       </c>
       <c r="K37" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B38" t="s">
         <v>51</v>
       </c>
       <c r="C38" t="n">
-        <v>54.8</v>
+        <v>63.5</v>
       </c>
       <c r="D38" t="n">
-        <v>64.3</v>
+        <v>64.4</v>
       </c>
       <c r="E38" t="n">
-        <v>23.7</v>
+        <v>19.3</v>
       </c>
       <c r="F38" t="n">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="G38" t="n">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="H38" t="n">
-        <v>38.1</v>
+        <v>37.8</v>
       </c>
       <c r="I38" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="J38" t="n">
-        <v>20.8</v>
+        <v>22</v>
       </c>
       <c r="K38" t="n">
-        <v>16.1</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B39" t="s">
         <v>51</v>
       </c>
       <c r="C39" t="n">
-        <v>100</v>
+        <v>54.8</v>
       </c>
       <c r="D39" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="E39" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="F39" t="n">
         <v>50</v>
       </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>100</v>
-      </c>
       <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39"/>
+        <v>6.5</v>
+      </c>
+      <c r="H39" t="n">
+        <v>38.1</v>
+      </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="J39" t="n">
-        <v>50</v>
+        <v>20.8</v>
       </c>
       <c r="K39" t="n">
-        <v>100</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B40" t="s">
         <v>51</v>
       </c>
       <c r="C40" t="n">
-        <v>67.6</v>
+        <v>100</v>
       </c>
       <c r="D40" t="n">
-        <v>64.1</v>
+        <v>50</v>
       </c>
       <c r="E40" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>51.7</v>
+        <v>100</v>
       </c>
       <c r="G40" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H40" t="n">
-        <v>62</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H40"/>
       <c r="I40" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>18.7</v>
+        <v>50</v>
       </c>
       <c r="K40" t="n">
-        <v>18.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B41" t="s">
         <v>51</v>
       </c>
       <c r="C41" t="n">
-        <v>50</v>
+        <v>67.1</v>
       </c>
       <c r="D41" t="n">
-        <v>62.5</v>
+        <v>64.6</v>
       </c>
       <c r="E41" t="n">
-        <v>35.3</v>
+        <v>15.2</v>
       </c>
       <c r="F41" t="n">
-        <v>40</v>
+        <v>51.6</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="H41" t="n">
-        <v>40</v>
+        <v>61.7</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J41" t="n">
-        <v>28.6</v>
+        <v>18.5</v>
       </c>
       <c r="K41" t="n">
-        <v>25</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B42" t="s">
         <v>51</v>
       </c>
       <c r="C42" t="n">
-        <v>58.8</v>
+        <v>50</v>
       </c>
       <c r="D42" t="n">
-        <v>63</v>
+        <v>62.5</v>
       </c>
       <c r="E42" t="n">
-        <v>15.9</v>
+        <v>35.3</v>
       </c>
       <c r="F42" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G42" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>48.8</v>
+        <v>40</v>
       </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>29.8</v>
+        <v>28.6</v>
       </c>
       <c r="K42" t="n">
-        <v>8.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B43" t="s">
         <v>51</v>
       </c>
       <c r="C43" t="n">
-        <v>68.4</v>
+        <v>58.8</v>
       </c>
       <c r="D43" t="n">
-        <v>70.6</v>
+        <v>63</v>
       </c>
       <c r="E43" t="n">
-        <v>24.8</v>
+        <v>15.9</v>
       </c>
       <c r="F43" t="n">
-        <v>47.8</v>
+        <v>50</v>
       </c>
       <c r="G43" t="n">
-        <v>4.3</v>
+        <v>11.8</v>
       </c>
       <c r="H43" t="n">
-        <v>31.9</v>
+        <v>48.8</v>
       </c>
       <c r="I43" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
-        <v>27.9</v>
+        <v>29.8</v>
       </c>
       <c r="K43" t="n">
-        <v>24.4</v>
+        <v>8.8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B44" t="s">
         <v>51</v>
       </c>
       <c r="C44" t="n">
-        <v>56.5</v>
+        <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>60.1</v>
+        <v>68.4</v>
       </c>
       <c r="E44" t="n">
-        <v>18.6</v>
+        <v>23.3</v>
       </c>
       <c r="F44" t="n">
-        <v>43.5</v>
+        <v>46.3</v>
       </c>
       <c r="G44" t="n">
-        <v>8.9</v>
+        <v>5</v>
       </c>
       <c r="H44" t="n">
-        <v>55.2</v>
+        <v>33.3</v>
       </c>
       <c r="I44" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="J44" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="K44" t="n">
-        <v>13.3</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B45" t="s">
         <v>51</v>
       </c>
       <c r="C45" t="n">
-        <v>58</v>
+        <v>55.8</v>
       </c>
       <c r="D45" t="n">
-        <v>64</v>
+        <v>60.8</v>
       </c>
       <c r="E45" t="n">
-        <v>16.3</v>
+        <v>19.1</v>
       </c>
       <c r="F45" t="n">
-        <v>43.8</v>
+        <v>42.3</v>
       </c>
       <c r="G45" t="n">
-        <v>6.1</v>
+        <v>7.8</v>
       </c>
       <c r="H45" t="n">
-        <v>52.8</v>
+        <v>50</v>
       </c>
       <c r="I45" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="J45" t="n">
-        <v>26.6</v>
+        <v>27.6</v>
       </c>
       <c r="K45" t="n">
-        <v>20.7</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B46" t="s">
         <v>51</v>
       </c>
       <c r="C46" t="n">
-        <v>44.4</v>
+        <v>58</v>
       </c>
       <c r="D46" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="E46"/>
+        <v>64</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.3</v>
+      </c>
       <c r="F46" t="n">
-        <v>25</v>
+        <v>43.8</v>
       </c>
       <c r="G46" t="n">
-        <v>33.3</v>
+        <v>6.1</v>
       </c>
       <c r="H46" t="n">
-        <v>20</v>
+        <v>52.8</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J46" t="n">
-        <v>27.3</v>
+        <v>26.6</v>
       </c>
       <c r="K46" t="n">
-        <v>-22.2</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B47" t="s">
         <v>51</v>
       </c>
       <c r="C47" t="n">
-        <v>51.6</v>
+        <v>44.4</v>
       </c>
       <c r="D47" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="E47" t="n">
-        <v>16</v>
-      </c>
+        <v>45.5</v>
+      </c>
+      <c r="E47"/>
       <c r="F47" t="n">
-        <v>22.2</v>
+        <v>25</v>
       </c>
       <c r="G47" t="n">
-        <v>9.8</v>
+        <v>33.3</v>
       </c>
       <c r="H47" t="n">
-        <v>36.5</v>
+        <v>20</v>
       </c>
       <c r="I47" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>11.9</v>
+        <v>27.3</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.7</v>
+        <v>-22.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B48" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="C48" t="n">
-        <v>60</v>
+        <v>51.6</v>
       </c>
       <c r="D48" t="n">
-        <v>57.4</v>
+        <v>57.1</v>
       </c>
       <c r="E48" t="n">
-        <v>16.9</v>
+        <v>16</v>
       </c>
       <c r="F48" t="n">
-        <v>35.6</v>
+        <v>22.2</v>
       </c>
       <c r="G48" t="n">
-        <v>13.6</v>
+        <v>9.8</v>
       </c>
       <c r="H48" t="n">
-        <v>31.2</v>
+        <v>36.5</v>
       </c>
       <c r="I48" t="n">
-        <v>2.3</v>
+        <v>6.5</v>
       </c>
       <c r="J48" t="n">
-        <v>28.4</v>
+        <v>11.9</v>
       </c>
       <c r="K48" t="n">
-        <v>4.6</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B49" t="s">
         <v>68</v>
       </c>
       <c r="C49" t="n">
-        <v>72.5</v>
+        <v>60</v>
       </c>
       <c r="D49" t="n">
-        <v>75.2</v>
+        <v>57.4</v>
       </c>
       <c r="E49" t="n">
-        <v>46.7</v>
+        <v>16.9</v>
       </c>
       <c r="F49" t="n">
-        <v>75</v>
+        <v>35.6</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="H49" t="n">
-        <v>36.8</v>
+        <v>31.2</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="J49" t="n">
-        <v>46.7</v>
+        <v>28.4</v>
       </c>
       <c r="K49" t="n">
-        <v>38.5</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B50" t="s">
         <v>68</v>
       </c>
       <c r="C50" t="n">
-        <v>59.5</v>
+        <v>72.5</v>
       </c>
       <c r="D50" t="n">
-        <v>60.1</v>
+        <v>75.2</v>
       </c>
       <c r="E50" t="n">
-        <v>15.4</v>
+        <v>46.7</v>
       </c>
       <c r="F50" t="n">
-        <v>48.1</v>
+        <v>75</v>
       </c>
       <c r="G50" t="n">
-        <v>14.6</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>50</v>
+        <v>36.8</v>
       </c>
       <c r="I50" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>34.5</v>
+        <v>46.7</v>
       </c>
       <c r="K50" t="n">
-        <v>17.1</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B51" t="s">
         <v>68</v>
       </c>
       <c r="C51" t="n">
-        <v>66.7</v>
+        <v>59.5</v>
       </c>
       <c r="D51" t="n">
-        <v>71.4</v>
-      </c>
-      <c r="E51"/>
+        <v>60.1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>15.4</v>
+      </c>
       <c r="F51" t="n">
-        <v>33.3</v>
+        <v>48.1</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>14.6</v>
       </c>
       <c r="H51" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="J51" t="n">
-        <v>25</v>
+        <v>34.5</v>
       </c>
       <c r="K51" t="n">
-        <v>33.3</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B52" t="s">
         <v>68</v>
       </c>
       <c r="C52" t="n">
-        <v>65.9</v>
+        <v>66.7</v>
       </c>
       <c r="D52" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="E52" t="n">
-        <v>22</v>
-      </c>
+        <v>71.4</v>
+      </c>
+      <c r="E52"/>
       <c r="F52" t="n">
-        <v>38.3</v>
+        <v>33.3</v>
       </c>
       <c r="G52" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>42.1</v>
+        <v>100</v>
       </c>
       <c r="I52" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>22.3</v>
+        <v>25</v>
       </c>
       <c r="K52" t="n">
-        <v>14.2</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B53" t="s">
         <v>68</v>
       </c>
       <c r="C53" t="n">
-        <v>53.4</v>
+        <v>65.9</v>
       </c>
       <c r="D53" t="n">
-        <v>59.7</v>
+        <v>68.2</v>
       </c>
       <c r="E53" t="n">
-        <v>23.8</v>
+        <v>22</v>
       </c>
       <c r="F53" t="n">
-        <v>42.9</v>
+        <v>38.3</v>
       </c>
       <c r="G53" t="n">
-        <v>14.6</v>
+        <v>3.7</v>
       </c>
       <c r="H53" t="n">
-        <v>37.7</v>
+        <v>42.1</v>
       </c>
       <c r="I53" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J53" t="n">
-        <v>34.2</v>
+        <v>22.3</v>
       </c>
       <c r="K53" t="n">
-        <v>6.8</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B54" t="s">
         <v>68</v>
       </c>
       <c r="C54" t="n">
-        <v>100</v>
+        <v>54.7</v>
       </c>
       <c r="D54" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="E54"/>
+        <v>59.8</v>
+      </c>
+      <c r="E54" t="n">
+        <v>22</v>
+      </c>
       <c r="F54" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="J54" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="K54" t="n">
-        <v>33.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B55" t="s">
         <v>68</v>
       </c>
       <c r="C55" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="D55" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
+        <v>66.7</v>
+      </c>
+      <c r="E55"/>
       <c r="F55" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="G55" t="n">
-        <v>26.7</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>44.8</v>
+        <v>20</v>
       </c>
       <c r="K55" t="n">
-        <v>6.6</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B56" t="s">
         <v>68</v>
       </c>
       <c r="C56" t="n">
-        <v>61.7</v>
+        <v>63.2</v>
       </c>
       <c r="D56" t="n">
-        <v>63.1</v>
+        <v>54.9</v>
       </c>
       <c r="E56" t="n">
-        <v>23.4</v>
+        <v>4.5</v>
       </c>
       <c r="F56" t="n">
-        <v>34</v>
+        <v>72.7</v>
       </c>
       <c r="G56" t="n">
-        <v>8.1</v>
+        <v>22.2</v>
       </c>
       <c r="H56" t="n">
-        <v>34.6</v>
+        <v>50</v>
       </c>
       <c r="I56" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>15.7</v>
+        <v>51.4</v>
       </c>
       <c r="K56" t="n">
-        <v>4.1</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B57" t="s">
         <v>68</v>
       </c>
       <c r="C57" t="n">
-        <v>60.3</v>
+        <v>61.7</v>
       </c>
       <c r="D57" t="n">
-        <v>65.7</v>
+        <v>63.1</v>
       </c>
       <c r="E57" t="n">
-        <v>23</v>
+        <v>23.4</v>
       </c>
       <c r="F57" t="n">
-        <v>43.8</v>
+        <v>34</v>
       </c>
       <c r="G57" t="n">
-        <v>6.3</v>
+        <v>8.1</v>
       </c>
       <c r="H57" t="n">
-        <v>65.9</v>
+        <v>34.6</v>
       </c>
       <c r="I57" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="J57" t="n">
-        <v>32.4</v>
+        <v>15.7</v>
       </c>
       <c r="K57" t="n">
-        <v>15.9</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B58" t="s">
         <v>68</v>
       </c>
       <c r="C58" t="n">
-        <v>59.5</v>
+        <v>60.9</v>
       </c>
       <c r="D58" t="n">
-        <v>61.4</v>
+        <v>64.1</v>
       </c>
       <c r="E58" t="n">
-        <v>8.3</v>
+        <v>20.5</v>
       </c>
       <c r="F58" t="n">
-        <v>44.4</v>
+        <v>44.1</v>
       </c>
       <c r="G58" t="n">
-        <v>9.5</v>
+        <v>7.1</v>
       </c>
       <c r="H58" t="n">
-        <v>55.2</v>
+        <v>64.4</v>
       </c>
       <c r="I58" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="J58" t="n">
-        <v>24.3</v>
+        <v>34.4</v>
       </c>
       <c r="K58" t="n">
-        <v>9.5</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B59" t="s">
         <v>68</v>
       </c>
       <c r="C59" t="n">
-        <v>67</v>
+        <v>56.5</v>
       </c>
       <c r="D59" t="n">
-        <v>67.2</v>
+        <v>61.6</v>
       </c>
       <c r="E59" t="n">
-        <v>27.2</v>
+        <v>6.5</v>
       </c>
       <c r="F59" t="n">
-        <v>36.2</v>
+        <v>42.9</v>
       </c>
       <c r="G59" t="n">
-        <v>3.6</v>
+        <v>8.7</v>
       </c>
       <c r="H59" t="n">
-        <v>59</v>
+        <v>56.2</v>
       </c>
       <c r="I59" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
-        <v>20.1</v>
+        <v>23.8</v>
       </c>
       <c r="K59" t="n">
-        <v>11.9</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B60" t="s">
         <v>68</v>
       </c>
       <c r="C60" t="n">
-        <v>63.8</v>
+        <v>66.1</v>
       </c>
       <c r="D60" t="n">
-        <v>64.6</v>
+        <v>66.2</v>
       </c>
       <c r="E60" t="n">
-        <v>33.3</v>
+        <v>25.5</v>
       </c>
       <c r="F60" t="n">
-        <v>38.1</v>
+        <v>36</v>
       </c>
       <c r="G60" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="H60" t="n">
-        <v>19.4</v>
+        <v>58.1</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="J60" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="K60" t="n">
-        <v>13.1</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>85</v>
+        <v>236</v>
       </c>
       <c r="B61" t="s">
         <v>68</v>
       </c>
       <c r="C61" t="n">
-        <v>30</v>
+        <v>63.8</v>
       </c>
       <c r="D61" t="n">
-        <v>60.6</v>
+        <v>64.6</v>
       </c>
       <c r="E61" t="n">
-        <v>46.7</v>
+        <v>33.3</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>38.1</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="H61" t="n">
-        <v>25</v>
+        <v>19.4</v>
       </c>
       <c r="I61" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>234</v>
+        <v>85</v>
       </c>
       <c r="B62" t="s">
         <v>68</v>
       </c>
       <c r="C62" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D62" t="n">
-        <v>51.9</v>
+        <v>60.6</v>
       </c>
       <c r="E62" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
         <v>25</v>
       </c>
-      <c r="F62" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="G62" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="H62" t="n">
-        <v>46.7</v>
-      </c>
       <c r="I62" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="J62" t="n">
-        <v>32.5</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>-7.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>87</v>
+        <v>237</v>
       </c>
       <c r="B63" t="s">
         <v>68</v>
       </c>
       <c r="C63" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D63" t="n">
-        <v>57.1</v>
+        <v>51.9</v>
       </c>
       <c r="E63" t="n">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>30.8</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="H63" t="n">
-        <v>20</v>
+        <v>46.7</v>
       </c>
       <c r="I63" t="n">
-        <v>40</v>
+        <v>11.1</v>
       </c>
       <c r="J63" t="n">
-        <v>14.3</v>
+        <v>32.5</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>-7.4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>235</v>
+        <v>87</v>
       </c>
       <c r="B64" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="C64" t="n">
-        <v>69.5</v>
+        <v>40</v>
       </c>
       <c r="D64" t="n">
-        <v>68.7</v>
+        <v>57.1</v>
       </c>
       <c r="E64" t="n">
-        <v>18</v>
+        <v>37.5</v>
       </c>
       <c r="F64" t="n">
-        <v>48.3</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>54.3</v>
+        <v>20</v>
       </c>
       <c r="I64" t="n">
-        <v>1.7</v>
+        <v>40</v>
       </c>
       <c r="J64" t="n">
-        <v>24.4</v>
+        <v>14.3</v>
       </c>
       <c r="K64" t="n">
-        <v>20.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B65" t="s">
         <v>91</v>
       </c>
       <c r="C65" t="n">
-        <v>68.2</v>
+        <v>69.5</v>
       </c>
       <c r="D65" t="n">
-        <v>67.2</v>
+        <v>68.7</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F65" t="n">
-        <v>50</v>
+        <v>48.3</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="H65" t="n">
-        <v>37.5</v>
+        <v>54.3</v>
       </c>
       <c r="I65" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J65" t="n">
-        <v>6.7</v>
+        <v>24.4</v>
       </c>
       <c r="K65" t="n">
-        <v>9.1</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B66" t="s">
         <v>91</v>
       </c>
       <c r="C66" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D66" t="n">
-        <v>64.3</v>
+        <v>67.1</v>
       </c>
       <c r="E66" t="n">
-        <v>22.2</v>
+        <v>17.9</v>
       </c>
       <c r="F66" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="G66" t="n">
-        <v>12.5</v>
+        <v>3.4</v>
       </c>
       <c r="H66" t="n">
-        <v>40</v>
+        <v>36.4</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="J66" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="K66" t="n">
-        <v>12.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B67" t="s">
         <v>91</v>
       </c>
       <c r="C67" t="n">
-        <v>53.1</v>
+        <v>46.2</v>
       </c>
       <c r="D67" t="n">
-        <v>61.1</v>
+        <v>65.2</v>
       </c>
       <c r="E67" t="n">
-        <v>22.2</v>
+        <v>31.8</v>
       </c>
       <c r="F67" t="n">
-        <v>35.7</v>
+        <v>28.6</v>
       </c>
       <c r="G67" t="n">
-        <v>12.5</v>
+        <v>15.4</v>
       </c>
       <c r="H67" t="n">
-        <v>55</v>
+        <v>44.4</v>
       </c>
       <c r="I67" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>18.8</v>
+        <v>13</v>
       </c>
       <c r="K67" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B68" t="s">
         <v>91</v>
       </c>
       <c r="C68" t="n">
-        <v>64.7</v>
+        <v>56.4</v>
       </c>
       <c r="D68" t="n">
-        <v>65.1</v>
+        <v>61.5</v>
       </c>
       <c r="E68" t="n">
-        <v>37.5</v>
+        <v>20.5</v>
       </c>
       <c r="F68" t="n">
-        <v>53.3</v>
+        <v>40</v>
       </c>
       <c r="G68" t="n">
-        <v>14.7</v>
+        <v>12.8</v>
       </c>
       <c r="H68" t="n">
-        <v>52.9</v>
+        <v>48</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="J68" t="n">
-        <v>28.9</v>
+        <v>19.3</v>
       </c>
       <c r="K68" t="n">
-        <v>8.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B69" t="s">
         <v>91</v>
       </c>
       <c r="C69" t="n">
-        <v>61.1</v>
+        <v>64.7</v>
       </c>
       <c r="D69" t="n">
-        <v>63</v>
+        <v>65.1</v>
       </c>
       <c r="E69" t="n">
-        <v>17.6</v>
+        <v>37.5</v>
       </c>
       <c r="F69" t="n">
-        <v>55</v>
+        <v>53.3</v>
       </c>
       <c r="G69" t="n">
-        <v>7.1</v>
+        <v>14.7</v>
       </c>
       <c r="H69" t="n">
-        <v>56.5</v>
+        <v>52.9</v>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>36.2</v>
+        <v>28.9</v>
       </c>
       <c r="K69" t="n">
-        <v>22.1</v>
+        <v>8.8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B70" t="s">
         <v>91</v>
       </c>
       <c r="C70" t="n">
-        <v>69.4</v>
+        <v>61.1</v>
       </c>
       <c r="D70" t="n">
-        <v>59.8</v>
+        <v>63</v>
       </c>
       <c r="E70" t="n">
-        <v>17.9</v>
+        <v>17.6</v>
       </c>
       <c r="F70" t="n">
-        <v>61.7</v>
+        <v>55</v>
       </c>
       <c r="G70" t="n">
-        <v>11</v>
+        <v>7.1</v>
       </c>
       <c r="H70" t="n">
-        <v>57.7</v>
+        <v>56.5</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
-        <v>43.9</v>
+        <v>36.2</v>
       </c>
       <c r="K70" t="n">
-        <v>28.7</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B71" t="s">
         <v>91</v>
       </c>
       <c r="C71" t="n">
-        <v>58.3</v>
+        <v>67</v>
       </c>
       <c r="D71" t="n">
-        <v>65.6</v>
+        <v>60.6</v>
       </c>
       <c r="E71" t="n">
-        <v>27.8</v>
+        <v>29</v>
       </c>
       <c r="F71" t="n">
-        <v>7.7</v>
+        <v>60</v>
       </c>
       <c r="G71" t="n">
-        <v>8.3</v>
+        <v>9</v>
       </c>
       <c r="H71" t="n">
-        <v>42.9</v>
+        <v>58.1</v>
       </c>
       <c r="I71" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>21.1</v>
+        <v>41.7</v>
       </c>
       <c r="K71" t="n">
-        <v>-4.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B72" t="s">
         <v>91</v>
       </c>
       <c r="C72" t="n">
-        <v>72.7</v>
+        <v>57.1</v>
       </c>
       <c r="D72" t="n">
-        <v>66.2</v>
+        <v>66.7</v>
       </c>
       <c r="E72" t="n">
-        <v>21.7</v>
+        <v>34.5</v>
       </c>
       <c r="F72" t="n">
-        <v>38.5</v>
+        <v>20</v>
       </c>
       <c r="G72" t="n">
-        <v>13.6</v>
+        <v>7.1</v>
       </c>
       <c r="H72" t="n">
-        <v>46.2</v>
+        <v>47.8</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="J72" t="n">
-        <v>30.6</v>
+        <v>22.7</v>
       </c>
       <c r="K72" t="n">
-        <v>9.1</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B73" t="s">
         <v>91</v>
       </c>
       <c r="C73" t="n">
-        <v>65</v>
+        <v>72.7</v>
       </c>
       <c r="D73" t="n">
-        <v>66.5</v>
+        <v>66.2</v>
       </c>
       <c r="E73" t="n">
-        <v>34</v>
+        <v>21.7</v>
       </c>
       <c r="F73" t="n">
-        <v>40</v>
+        <v>38.5</v>
       </c>
       <c r="G73" t="n">
-        <v>10</v>
+        <v>13.6</v>
       </c>
       <c r="H73" t="n">
-        <v>61</v>
+        <v>46.2</v>
       </c>
       <c r="I73" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>28.4</v>
+        <v>30.6</v>
       </c>
       <c r="K73" t="n">
-        <v>10</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B74" t="s">
         <v>91</v>
       </c>
       <c r="C74" t="n">
-        <v>60.1</v>
+        <v>68.3</v>
       </c>
       <c r="D74" t="n">
-        <v>62.7</v>
+        <v>69</v>
       </c>
       <c r="E74" t="n">
-        <v>25.7</v>
+        <v>26.9</v>
       </c>
       <c r="F74" t="n">
-        <v>55.2</v>
+        <v>38.5</v>
       </c>
       <c r="G74" t="n">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="H74" t="n">
-        <v>37.6</v>
+        <v>56.7</v>
       </c>
       <c r="I74" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
       <c r="J74" t="n">
-        <v>30.1</v>
+        <v>25</v>
       </c>
       <c r="K74" t="n">
-        <v>18.7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B75" t="s">
         <v>91</v>
       </c>
       <c r="C75" t="n">
-        <v>64.5</v>
+        <v>60.1</v>
       </c>
       <c r="D75" t="n">
-        <v>64.8</v>
+        <v>62.7</v>
       </c>
       <c r="E75" t="n">
-        <v>25</v>
+        <v>25.7</v>
       </c>
       <c r="F75" t="n">
-        <v>30.8</v>
+        <v>55.2</v>
       </c>
       <c r="G75" t="n">
-        <v>9.4</v>
+        <v>7.9</v>
       </c>
       <c r="H75" t="n">
-        <v>40</v>
+        <v>37.6</v>
       </c>
       <c r="I75" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J75" t="n">
-        <v>20</v>
+        <v>30.1</v>
       </c>
       <c r="K75" t="n">
-        <v>3.1</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B76" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="C76" t="n">
-        <v>42</v>
+        <v>64.5</v>
       </c>
       <c r="D76" t="n">
-        <v>44.7</v>
+        <v>64.8</v>
       </c>
       <c r="E76" t="n">
-        <v>6.3</v>
+        <v>25</v>
       </c>
       <c r="F76" t="n">
-        <v>46.4</v>
+        <v>30.8</v>
       </c>
       <c r="G76" t="n">
-        <v>31.9</v>
+        <v>9.4</v>
       </c>
       <c r="H76" t="n">
-        <v>41.4</v>
+        <v>40</v>
       </c>
       <c r="I76" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J76" t="n">
-        <v>30.4</v>
+        <v>20</v>
       </c>
       <c r="K76" t="n">
-        <v>-13.1</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B77" t="s">
         <v>105</v>
       </c>
       <c r="C77" t="n">
-        <v>71.2</v>
+        <v>42</v>
       </c>
       <c r="D77" t="n">
-        <v>63.9</v>
+        <v>44.7</v>
       </c>
       <c r="E77" t="n">
-        <v>16.7</v>
+        <v>6.3</v>
       </c>
       <c r="F77" t="n">
-        <v>48.7</v>
+        <v>46.4</v>
       </c>
       <c r="G77" t="n">
-        <v>12</v>
+        <v>31.9</v>
       </c>
       <c r="H77" t="n">
-        <v>52.3</v>
+        <v>41.4</v>
       </c>
       <c r="I77" t="n">
-        <v>6.7</v>
+        <v>2.9</v>
       </c>
       <c r="J77" t="n">
-        <v>30.6</v>
+        <v>30.4</v>
       </c>
       <c r="K77" t="n">
-        <v>13.3</v>
+        <v>-13.1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>185</v>
+        <v>251</v>
       </c>
       <c r="B78" t="s">
         <v>105</v>
       </c>
       <c r="C78" t="n">
-        <v>50</v>
+        <v>67.9</v>
       </c>
       <c r="D78" t="n">
-        <v>53.5</v>
+        <v>63.4</v>
       </c>
       <c r="E78" t="n">
-        <v>10.1</v>
+        <v>26</v>
       </c>
       <c r="F78" t="n">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
       <c r="G78" t="n">
-        <v>13.6</v>
+        <v>10.5</v>
       </c>
       <c r="H78" t="n">
-        <v>38.5</v>
+        <v>53.7</v>
       </c>
       <c r="I78" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="J78" t="n">
-        <v>22.1</v>
+        <v>29.9</v>
       </c>
       <c r="K78" t="n">
-        <v>6.1</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>249</v>
+        <v>187</v>
       </c>
       <c r="B79" t="s">
         <v>105</v>
       </c>
       <c r="C79" t="n">
-        <v>28.6</v>
+        <v>50</v>
       </c>
       <c r="D79" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="E79"/>
+        <v>53.5</v>
+      </c>
+      <c r="E79" t="n">
+        <v>10.1</v>
+      </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>46.4</v>
       </c>
       <c r="G79" t="n">
-        <v>42.9</v>
+        <v>13.6</v>
       </c>
       <c r="H79" t="n">
-        <v>25</v>
+        <v>38.5</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="J79" t="n">
-        <v>14.3</v>
+        <v>22.1</v>
       </c>
       <c r="K79" t="n">
-        <v>-42.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B80" t="s">
         <v>105</v>
       </c>
       <c r="C80" t="n">
-        <v>48.6</v>
+        <v>28.6</v>
       </c>
       <c r="D80" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="E80" t="n">
-        <v>22.6</v>
-      </c>
+        <v>41.9</v>
+      </c>
+      <c r="E80"/>
       <c r="F80" t="n">
-        <v>41.5</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>14.9</v>
+        <v>42.9</v>
       </c>
       <c r="H80" t="n">
-        <v>32.6</v>
+        <v>25</v>
       </c>
       <c r="I80" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>33.6</v>
+        <v>14.3</v>
       </c>
       <c r="K80" t="n">
-        <v>8.1</v>
+        <v>-42.9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>107</v>
+        <v>253</v>
       </c>
       <c r="B81" t="s">
         <v>105</v>
       </c>
       <c r="C81" t="n">
-        <v>57.9</v>
+        <v>48.6</v>
       </c>
       <c r="D81" t="n">
-        <v>58.5</v>
+        <v>56.4</v>
       </c>
       <c r="E81" t="n">
-        <v>19.1</v>
+        <v>22.6</v>
       </c>
       <c r="F81" t="n">
-        <v>23.3</v>
+        <v>41.5</v>
       </c>
       <c r="G81" t="n">
-        <v>6.9</v>
+        <v>14.9</v>
       </c>
       <c r="H81" t="n">
-        <v>39.5</v>
+        <v>32.6</v>
       </c>
       <c r="I81" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="J81" t="n">
-        <v>22</v>
+        <v>33.6</v>
       </c>
       <c r="K81" t="n">
-        <v>5.2</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>212</v>
+        <v>107</v>
       </c>
       <c r="B82" t="s">
         <v>105</v>
       </c>
       <c r="C82" t="n">
-        <v>62.9</v>
+        <v>57.9</v>
       </c>
       <c r="D82" t="n">
-        <v>66.7</v>
+        <v>58.5</v>
       </c>
       <c r="E82" t="n">
-        <v>27.9</v>
+        <v>19.1</v>
       </c>
       <c r="F82" t="n">
-        <v>39</v>
+        <v>23.3</v>
       </c>
       <c r="G82" t="n">
-        <v>5.1</v>
+        <v>6.9</v>
       </c>
       <c r="H82" t="n">
-        <v>41.8</v>
+        <v>39.5</v>
       </c>
       <c r="I82" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="J82" t="n">
-        <v>22.3</v>
+        <v>22</v>
       </c>
       <c r="K82" t="n">
-        <v>11.8</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>251</v>
+        <v>215</v>
       </c>
       <c r="B83" t="s">
         <v>105</v>
       </c>
       <c r="C83" t="n">
-        <v>54.5</v>
+        <v>62.9</v>
       </c>
       <c r="D83" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="E83" t="n">
-        <v>10.4</v>
+        <v>27.9</v>
       </c>
       <c r="F83" t="n">
-        <v>29.4</v>
+        <v>39</v>
       </c>
       <c r="G83" t="n">
-        <v>15.2</v>
+        <v>5.1</v>
       </c>
       <c r="H83" t="n">
-        <v>45</v>
+        <v>41.8</v>
       </c>
       <c r="I83" t="n">
-        <v>6.1</v>
+        <v>4.5</v>
       </c>
       <c r="J83" t="n">
-        <v>26.6</v>
+        <v>22.3</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B84" t="s">
         <v>105</v>
       </c>
       <c r="C84" t="n">
-        <v>67.3</v>
+        <v>54.5</v>
       </c>
       <c r="D84" t="n">
-        <v>65.8</v>
+        <v>55.6</v>
       </c>
       <c r="E84" t="n">
-        <v>30.1</v>
+        <v>10.4</v>
       </c>
       <c r="F84" t="n">
-        <v>37.7</v>
+        <v>29.4</v>
       </c>
       <c r="G84" t="n">
-        <v>8.6</v>
+        <v>15.2</v>
       </c>
       <c r="H84" t="n">
-        <v>48.6</v>
+        <v>45</v>
       </c>
       <c r="I84" t="n">
-        <v>3.8</v>
+        <v>6.1</v>
       </c>
       <c r="J84" t="n">
-        <v>28.9</v>
+        <v>26.6</v>
       </c>
       <c r="K84" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B85" t="s">
         <v>105</v>
       </c>
       <c r="C85" t="n">
-        <v>63.6</v>
+        <v>67.3</v>
       </c>
       <c r="D85" t="n">
-        <v>63.1</v>
+        <v>65.8</v>
       </c>
       <c r="E85" t="n">
-        <v>14.6</v>
+        <v>30.1</v>
       </c>
       <c r="F85" t="n">
-        <v>38.5</v>
+        <v>37.7</v>
       </c>
       <c r="G85" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="H85" t="n">
-        <v>54.5</v>
+        <v>48.6</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="J85" t="n">
-        <v>23.5</v>
+        <v>28.9</v>
       </c>
       <c r="K85" t="n">
-        <v>13.6</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B86" t="s">
         <v>105</v>
       </c>
       <c r="C86" t="n">
-        <v>50.4</v>
+        <v>63.6</v>
       </c>
       <c r="D86" t="n">
-        <v>55.1</v>
+        <v>63.1</v>
       </c>
       <c r="E86" t="n">
-        <v>21.1</v>
+        <v>14.6</v>
       </c>
       <c r="F86" t="n">
-        <v>37.9</v>
+        <v>38.5</v>
       </c>
       <c r="G86" t="n">
-        <v>12.3</v>
+        <v>9.1</v>
       </c>
       <c r="H86" t="n">
-        <v>25.3</v>
+        <v>54.5</v>
       </c>
       <c r="I86" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>25.2</v>
+        <v>23.5</v>
       </c>
       <c r="K86" t="n">
-        <v>4.6</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B87" t="s">
         <v>105</v>
       </c>
       <c r="C87" t="n">
-        <v>75</v>
+        <v>52.6</v>
       </c>
       <c r="D87" t="n">
-        <v>65</v>
+        <v>55.8</v>
       </c>
       <c r="E87" t="n">
-        <v>12.1</v>
+        <v>25.6</v>
       </c>
       <c r="F87" t="n">
-        <v>37.5</v>
+        <v>37.9</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>12.4</v>
       </c>
       <c r="H87" t="n">
-        <v>53.8</v>
+        <v>30</v>
       </c>
       <c r="I87" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="J87" t="n">
-        <v>26.9</v>
+        <v>24.9</v>
       </c>
       <c r="K87" t="n">
-        <v>18.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B88" t="s">
         <v>105</v>
       </c>
       <c r="C88" t="n">
-        <v>55.2</v>
+        <v>75</v>
       </c>
       <c r="D88" t="n">
-        <v>61.1</v>
+        <v>65</v>
       </c>
       <c r="E88" t="n">
-        <v>23.4</v>
+        <v>12.1</v>
       </c>
       <c r="F88" t="n">
-        <v>38.3</v>
+        <v>37.5</v>
       </c>
       <c r="G88" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>50.7</v>
+        <v>53.8</v>
       </c>
       <c r="I88" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J88" t="n">
-        <v>24.5</v>
+        <v>26.9</v>
       </c>
       <c r="K88" t="n">
-        <v>13.3</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B89" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="C89" t="n">
-        <v>74.2</v>
+        <v>55.2</v>
       </c>
       <c r="D89" t="n">
-        <v>69.7</v>
+        <v>61.1</v>
       </c>
       <c r="E89" t="n">
-        <v>39.1</v>
+        <v>23.4</v>
       </c>
       <c r="F89" t="n">
-        <v>33.3</v>
+        <v>38.3</v>
       </c>
       <c r="G89" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="H89" t="n">
-        <v>52.2</v>
+        <v>50.7</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="J89" t="n">
-        <v>22.9</v>
+        <v>24.5</v>
       </c>
       <c r="K89" t="n">
-        <v>6.2</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B90" t="s">
         <v>121</v>
       </c>
       <c r="C90" t="n">
-        <v>55.6</v>
+        <v>74.2</v>
       </c>
       <c r="D90" t="n">
-        <v>57.4</v>
+        <v>69.7</v>
       </c>
       <c r="E90" t="n">
-        <v>18.5</v>
+        <v>39.1</v>
       </c>
       <c r="F90" t="n">
-        <v>35.3</v>
+        <v>33.3</v>
       </c>
       <c r="G90" t="n">
-        <v>13.9</v>
+        <v>9.4</v>
       </c>
       <c r="H90" t="n">
-        <v>32</v>
+        <v>52.2</v>
       </c>
       <c r="I90" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>31.1</v>
+        <v>22.9</v>
       </c>
       <c r="K90" t="n">
-        <v>2.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B91" t="s">
         <v>121</v>
       </c>
       <c r="C91" t="n">
-        <v>59.8</v>
+        <v>60</v>
       </c>
       <c r="D91" t="n">
-        <v>65.7</v>
+        <v>57.7</v>
       </c>
       <c r="E91" t="n">
-        <v>24.5</v>
+        <v>17.6</v>
       </c>
       <c r="F91" t="n">
-        <v>43.2</v>
+        <v>42.1</v>
       </c>
       <c r="G91" t="n">
-        <v>5.3</v>
+        <v>12.5</v>
       </c>
       <c r="H91" t="n">
-        <v>48.8</v>
+        <v>37</v>
       </c>
       <c r="I91" t="n">
-        <v>2.7</v>
+        <v>7.5</v>
       </c>
       <c r="J91" t="n">
-        <v>19.8</v>
+        <v>33.8</v>
       </c>
       <c r="K91" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B92" t="s">
         <v>121</v>
       </c>
       <c r="C92" t="n">
-        <v>61.2</v>
+        <v>57.5</v>
       </c>
       <c r="D92" t="n">
         <v>64.6</v>
       </c>
       <c r="E92" t="n">
-        <v>22.1</v>
+        <v>30</v>
       </c>
       <c r="F92" t="n">
-        <v>66.7</v>
+        <v>40.8</v>
       </c>
       <c r="G92" t="n">
-        <v>10.2</v>
+        <v>6.7</v>
       </c>
       <c r="H92" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J92" t="n">
-        <v>36.8</v>
+        <v>21.8</v>
       </c>
       <c r="K92" t="n">
-        <v>26.5</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B93" t="s">
         <v>121</v>
       </c>
       <c r="C93" t="n">
-        <v>71.1</v>
+        <v>62.7</v>
       </c>
       <c r="D93" t="n">
-        <v>68.4</v>
+        <v>66.7</v>
       </c>
       <c r="E93" t="n">
-        <v>35.7</v>
+        <v>34.9</v>
       </c>
       <c r="F93" t="n">
-        <v>68.2</v>
+        <v>54.5</v>
       </c>
       <c r="G93" t="n">
-        <v>6.7</v>
+        <v>8.5</v>
       </c>
       <c r="H93" t="n">
-        <v>50</v>
+        <v>58.8</v>
       </c>
       <c r="I93" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J93" t="n">
-        <v>32.4</v>
+        <v>31.6</v>
       </c>
       <c r="K93" t="n">
-        <v>26.6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B94" t="s">
         <v>121</v>
       </c>
       <c r="C94" t="n">
-        <v>58.5</v>
+        <v>65.3</v>
       </c>
       <c r="D94" t="n">
-        <v>63.9</v>
+        <v>67.2</v>
       </c>
       <c r="E94" t="n">
-        <v>14.3</v>
+        <v>33.8</v>
       </c>
       <c r="F94" t="n">
-        <v>26.7</v>
+        <v>64</v>
       </c>
       <c r="G94" t="n">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
       <c r="H94" t="n">
-        <v>66.7</v>
+        <v>55.2</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J94" t="n">
-        <v>19</v>
+        <v>31.8</v>
       </c>
       <c r="K94" t="n">
-        <v>7.2</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B95" t="s">
         <v>121</v>
       </c>
       <c r="C95" t="n">
-        <v>71.4</v>
+        <v>60.6</v>
       </c>
       <c r="D95" t="n">
+        <v>64.6</v>
+      </c>
+      <c r="E95" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="F95" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G95" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H95" t="n">
         <v>67.9</v>
       </c>
-      <c r="E95" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="F95" t="n">
-        <v>50</v>
-      </c>
-      <c r="G95" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="H95" t="n">
-        <v>52.4</v>
-      </c>
       <c r="I95" t="n">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="J95" t="n">
-        <v>39.7</v>
+        <v>19.3</v>
       </c>
       <c r="K95" t="n">
-        <v>17.2</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B96" t="s">
         <v>121</v>
       </c>
       <c r="C96" t="n">
-        <v>67.8</v>
+        <v>72.2</v>
       </c>
       <c r="D96" t="n">
-        <v>65.4</v>
+        <v>67.9</v>
       </c>
       <c r="E96" t="n">
-        <v>21.8</v>
+        <v>34.3</v>
       </c>
       <c r="F96" t="n">
-        <v>36.5</v>
+        <v>50</v>
       </c>
       <c r="G96" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="H96" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="I96" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="J96" t="n">
-        <v>22.5</v>
+        <v>38.7</v>
       </c>
       <c r="K96" t="n">
-        <v>5.9</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B97" t="s">
         <v>121</v>
       </c>
       <c r="C97" t="n">
-        <v>70.6</v>
+        <v>67.8</v>
       </c>
       <c r="D97" t="n">
-        <v>71</v>
+        <v>65.4</v>
       </c>
       <c r="E97" t="n">
-        <v>25.8</v>
+        <v>21.8</v>
       </c>
       <c r="F97" t="n">
-        <v>50.5</v>
+        <v>36.5</v>
       </c>
       <c r="G97" t="n">
-        <v>0.5</v>
+        <v>9.9</v>
       </c>
       <c r="H97" t="n">
-        <v>43.7</v>
+        <v>42.9</v>
       </c>
       <c r="I97" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J97" t="n">
-        <v>21.8</v>
+        <v>22.5</v>
       </c>
       <c r="K97" t="n">
-        <v>23.2</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B98" t="s">
         <v>121</v>
       </c>
       <c r="C98" t="n">
-        <v>64.1</v>
+        <v>67.6</v>
       </c>
       <c r="D98" t="n">
-        <v>62.8</v>
+        <v>70.2</v>
       </c>
       <c r="E98" t="n">
-        <v>14</v>
+        <v>22.7</v>
       </c>
       <c r="F98" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G98" t="n">
-        <v>14.1</v>
+        <v>0.5</v>
       </c>
       <c r="H98" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I98" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J98" t="n">
-        <v>35</v>
+        <v>21.6</v>
       </c>
       <c r="K98" t="n">
-        <v>28.1</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B99" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="C99" t="n">
-        <v>50</v>
+        <v>65.7</v>
       </c>
       <c r="D99" t="n">
-        <v>54.4</v>
+        <v>61.8</v>
       </c>
       <c r="E99" t="n">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="F99" t="n">
-        <v>20</v>
+        <v>57.1</v>
       </c>
       <c r="G99" t="n">
-        <v>15.6</v>
+        <v>17.1</v>
       </c>
       <c r="H99" t="n">
-        <v>40.9</v>
+        <v>34.5</v>
       </c>
       <c r="I99" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J99" t="n">
-        <v>16.3</v>
+        <v>35.4</v>
       </c>
       <c r="K99" t="n">
-        <v>-9.4</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>139</v>
+        <v>270</v>
       </c>
       <c r="B100" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C100" t="n">
-        <v>51.6</v>
+        <v>33.3</v>
       </c>
       <c r="D100" t="n">
-        <v>58.9</v>
+        <v>56.2</v>
       </c>
       <c r="E100" t="n">
-        <v>16</v>
+        <v>36.4</v>
       </c>
       <c r="F100" t="n">
-        <v>40.9</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>12.9</v>
+        <v>33.3</v>
       </c>
       <c r="H100" t="n">
-        <v>44.4</v>
+        <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>8.1</v>
+        <v>33.3</v>
       </c>
       <c r="J100" t="n">
-        <v>24.4</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>1.6</v>
+        <v>-33.3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B101" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C101" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D101" t="n">
-        <v>65.2</v>
+        <v>54.4</v>
       </c>
       <c r="E101" t="n">
-        <v>19.6</v>
+        <v>13.5</v>
       </c>
       <c r="F101" t="n">
-        <v>35.7</v>
+        <v>20</v>
       </c>
       <c r="G101" t="n">
-        <v>8.3</v>
+        <v>15.6</v>
       </c>
       <c r="H101" t="n">
-        <v>37.7</v>
+        <v>40.9</v>
       </c>
       <c r="I101" t="n">
-        <v>5.6</v>
+        <v>3.1</v>
       </c>
       <c r="J101" t="n">
-        <v>18.1</v>
+        <v>16.3</v>
       </c>
       <c r="K101" t="n">
-        <v>5.6</v>
+        <v>-9.4</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>269</v>
+        <v>141</v>
       </c>
       <c r="B102" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C102" t="n">
-        <v>50</v>
+        <v>51.6</v>
       </c>
       <c r="D102" t="n">
-        <v>45.5</v>
+        <v>58.9</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102"/>
+        <v>16</v>
+      </c>
+      <c r="F102" t="n">
+        <v>40.9</v>
+      </c>
       <c r="G102" t="n">
-        <v>25</v>
+        <v>12.9</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>44.4</v>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J102" t="n">
-        <v>0</v>
+        <v>24.4</v>
       </c>
       <c r="K102" t="n">
-        <v>-25</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B103" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C103" t="n">
-        <v>69.7</v>
+        <v>62</v>
       </c>
       <c r="D103" t="n">
-        <v>62.4</v>
+        <v>65.2</v>
       </c>
       <c r="E103" t="n">
-        <v>25</v>
+        <v>19.6</v>
       </c>
       <c r="F103" t="n">
-        <v>20</v>
+        <v>35.7</v>
       </c>
       <c r="G103" t="n">
-        <v>14.6</v>
+        <v>8.3</v>
       </c>
       <c r="H103" t="n">
-        <v>53.7</v>
+        <v>37.7</v>
       </c>
       <c r="I103" t="n">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="J103" t="n">
-        <v>21.9</v>
+        <v>18.1</v>
       </c>
       <c r="K103" t="n">
-        <v>-5.6</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B104" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C104" t="n">
-        <v>54.1</v>
+        <v>50</v>
       </c>
       <c r="D104" t="n">
-        <v>61.9</v>
+        <v>45.5</v>
       </c>
       <c r="E104" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F104" t="n">
-        <v>20</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F104"/>
       <c r="G104" t="n">
-        <v>5.4</v>
+        <v>25</v>
       </c>
       <c r="H104" t="n">
-        <v>44.8</v>
+        <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>15.6</v>
+        <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>2.7</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>149</v>
+        <v>274</v>
       </c>
       <c r="B105" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C105" t="n">
-        <v>50.9</v>
+        <v>69.7</v>
       </c>
       <c r="D105" t="n">
-        <v>57.5</v>
+        <v>62.4</v>
       </c>
       <c r="E105" t="n">
-        <v>22.4</v>
+        <v>25</v>
       </c>
       <c r="F105" t="n">
-        <v>35.7</v>
+        <v>20</v>
       </c>
       <c r="G105" t="n">
-        <v>16.1</v>
+        <v>14.6</v>
       </c>
       <c r="H105" t="n">
-        <v>44.8</v>
+        <v>53.7</v>
       </c>
       <c r="I105" t="n">
-        <v>8.9</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
-        <v>26.2</v>
+        <v>21.9</v>
       </c>
       <c r="K105" t="n">
-        <v>3.5</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B106" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C106" t="n">
-        <v>68</v>
+        <v>54.1</v>
       </c>
       <c r="D106" t="n">
-        <v>63</v>
+        <v>61.9</v>
       </c>
       <c r="E106" t="n">
-        <v>22.2</v>
+        <v>17.2</v>
       </c>
       <c r="F106" t="n">
-        <v>8.3</v>
+        <v>20</v>
       </c>
       <c r="G106" t="n">
-        <v>12</v>
+        <v>5.4</v>
       </c>
       <c r="H106" t="n">
-        <v>47.6</v>
+        <v>44.8</v>
       </c>
       <c r="I106" t="n">
-        <v>4</v>
+        <v>8.1</v>
       </c>
       <c r="J106" t="n">
-        <v>14.3</v>
+        <v>15.6</v>
       </c>
       <c r="K106" t="n">
-        <v>-8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>273</v>
+        <v>151</v>
       </c>
       <c r="B107" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C107" t="n">
-        <v>52.6</v>
+        <v>51.6</v>
       </c>
       <c r="D107" t="n">
-        <v>56.2</v>
+        <v>59.1</v>
       </c>
       <c r="E107" t="n">
-        <v>30</v>
+        <v>31.1</v>
       </c>
       <c r="F107" t="n">
-        <v>10</v>
+        <v>39.4</v>
       </c>
       <c r="G107" t="n">
-        <v>15.8</v>
+        <v>14.3</v>
       </c>
       <c r="H107" t="n">
-        <v>50</v>
+        <v>48.5</v>
       </c>
       <c r="I107" t="n">
-        <v>5.3</v>
+        <v>7.9</v>
       </c>
       <c r="J107" t="n">
-        <v>15.2</v>
+        <v>28</v>
       </c>
       <c r="K107" t="n">
-        <v>-10.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B108" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C108" t="n">
-        <v>58.1</v>
+        <v>60</v>
       </c>
       <c r="D108" t="n">
-        <v>62.5</v>
+        <v>60.4</v>
       </c>
       <c r="E108" t="n">
-        <v>28.4</v>
+        <v>21</v>
       </c>
       <c r="F108" t="n">
-        <v>54.5</v>
+        <v>26.3</v>
       </c>
       <c r="G108" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="H108" t="n">
-        <v>34.7</v>
+        <v>50</v>
       </c>
       <c r="I108" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="J108" t="n">
-        <v>29.9</v>
+        <v>20.9</v>
       </c>
       <c r="K108" t="n">
-        <v>17.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B109" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C109" t="n">
-        <v>60.8</v>
+        <v>52.6</v>
       </c>
       <c r="D109" t="n">
-        <v>62.1</v>
+        <v>56.2</v>
       </c>
       <c r="E109" t="n">
-        <v>21.4</v>
+        <v>30</v>
       </c>
       <c r="F109" t="n">
-        <v>46.4</v>
+        <v>10</v>
       </c>
       <c r="G109" t="n">
-        <v>9.8</v>
+        <v>15.8</v>
       </c>
       <c r="H109" t="n">
-        <v>44.8</v>
+        <v>50</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="J109" t="n">
-        <v>35.7</v>
+        <v>15.2</v>
       </c>
       <c r="K109" t="n">
-        <v>15.7</v>
+        <v>-10.5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B110" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C110" t="n">
-        <v>44</v>
+        <v>61.3</v>
       </c>
       <c r="D110" t="n">
-        <v>56.3</v>
+        <v>63.9</v>
       </c>
       <c r="E110" t="n">
-        <v>23.1</v>
+        <v>28.5</v>
       </c>
       <c r="F110" t="n">
-        <v>38.5</v>
+        <v>54.4</v>
       </c>
       <c r="G110" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H110" t="n">
-        <v>50</v>
+        <v>39.1</v>
       </c>
       <c r="I110" t="n">
-        <v>8</v>
+        <v>2.7</v>
       </c>
       <c r="J110" t="n">
-        <v>26.5</v>
+        <v>29.2</v>
       </c>
       <c r="K110" t="n">
-        <v>12</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B111" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C111" t="n">
-        <v>38.9</v>
+        <v>59.7</v>
       </c>
       <c r="D111" t="n">
-        <v>52</v>
+        <v>61.8</v>
       </c>
       <c r="E111" t="n">
-        <v>16.3</v>
+        <v>20</v>
       </c>
       <c r="F111" t="n">
-        <v>33.3</v>
+        <v>51.5</v>
       </c>
       <c r="G111" t="n">
-        <v>27.8</v>
+        <v>11.3</v>
       </c>
       <c r="H111" t="n">
-        <v>22.2</v>
+        <v>39.4</v>
       </c>
       <c r="I111" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>31</v>
+        <v>34.7</v>
       </c>
       <c r="K111" t="n">
-        <v>-11.1</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B112" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C112" t="n">
-        <v>59.2</v>
+        <v>44</v>
       </c>
       <c r="D112" t="n">
-        <v>62.2</v>
+        <v>56.3</v>
       </c>
       <c r="E112" t="n">
-        <v>21.3</v>
+        <v>23.1</v>
       </c>
       <c r="F112" t="n">
-        <v>26.9</v>
+        <v>38.5</v>
       </c>
       <c r="G112" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="H112" t="n">
-        <v>59.4</v>
+        <v>50</v>
       </c>
       <c r="I112" t="n">
-        <v>3.4</v>
+        <v>8</v>
       </c>
       <c r="J112" t="n">
-        <v>20.5</v>
+        <v>26.5</v>
       </c>
       <c r="K112" t="n">
-        <v>5.4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B113" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C113" t="n">
-        <v>57.8</v>
+        <v>38.9</v>
       </c>
       <c r="D113" t="n">
-        <v>60.8</v>
+        <v>52</v>
       </c>
       <c r="E113" t="n">
-        <v>19.8</v>
+        <v>16.3</v>
       </c>
       <c r="F113" t="n">
-        <v>39.5</v>
+        <v>33.3</v>
       </c>
       <c r="G113" t="n">
-        <v>5.5</v>
+        <v>27.8</v>
       </c>
       <c r="H113" t="n">
-        <v>41.7</v>
+        <v>22.2</v>
       </c>
       <c r="I113" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="J113" t="n">
-        <v>15.6</v>
+        <v>31</v>
       </c>
       <c r="K113" t="n">
-        <v>7.8</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B114" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="C114" t="n">
-        <v>62.4</v>
+        <v>59.2</v>
       </c>
       <c r="D114" t="n">
-        <v>67.5</v>
+        <v>62.2</v>
       </c>
       <c r="E114" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="F114" t="n">
-        <v>44.3</v>
+        <v>26.9</v>
       </c>
       <c r="G114" t="n">
-        <v>2.4</v>
+        <v>6.8</v>
       </c>
       <c r="H114" t="n">
-        <v>48.4</v>
+        <v>59.4</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="J114" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="K114" t="n">
-        <v>14</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B115" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="C115" t="n">
-        <v>57.8</v>
+        <v>57.9</v>
       </c>
       <c r="D115" t="n">
-        <v>64.1</v>
+        <v>59.8</v>
       </c>
       <c r="E115" t="n">
-        <v>11.9</v>
+        <v>24.6</v>
       </c>
       <c r="F115" t="n">
-        <v>32.3</v>
+        <v>38.9</v>
       </c>
       <c r="G115" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="H115" t="n">
-        <v>28.8</v>
+        <v>42</v>
       </c>
       <c r="I115" t="n">
-        <v>3.6</v>
+        <v>8.6</v>
       </c>
       <c r="J115" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="K115" t="n">
-        <v>4.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B116" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C116" t="n">
-        <v>60.5</v>
+        <v>62.4</v>
       </c>
       <c r="D116" t="n">
-        <v>66.7</v>
+        <v>67.5</v>
       </c>
       <c r="E116" t="n">
-        <v>38.7</v>
+        <v>22.6</v>
       </c>
       <c r="F116" t="n">
-        <v>71.4</v>
+        <v>44.3</v>
       </c>
       <c r="G116" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H116" t="n">
-        <v>53.3</v>
+        <v>48.4</v>
       </c>
       <c r="I116" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>42.9</v>
+        <v>20.7</v>
       </c>
       <c r="K116" t="n">
-        <v>45.2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>211</v>
+        <v>285</v>
       </c>
       <c r="B117" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C117" t="n">
-        <v>62.5</v>
+        <v>60.7</v>
       </c>
       <c r="D117" t="n">
-        <v>61.2</v>
+        <v>64.8</v>
       </c>
       <c r="E117" t="n">
-        <v>13.4</v>
+        <v>11.2</v>
       </c>
       <c r="F117" t="n">
-        <v>36.4</v>
+        <v>32.4</v>
       </c>
       <c r="G117" t="n">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="H117" t="n">
-        <v>42.5</v>
+        <v>29.6</v>
       </c>
       <c r="I117" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J117" t="n">
-        <v>26.8</v>
+        <v>19.6</v>
       </c>
       <c r="K117" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B118" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C118" t="n">
-        <v>64.1</v>
+        <v>60.4</v>
       </c>
       <c r="D118" t="n">
-        <v>62.1</v>
+        <v>64.6</v>
       </c>
       <c r="E118" t="n">
-        <v>29</v>
+        <v>33.8</v>
       </c>
       <c r="F118" t="n">
-        <v>45.8</v>
+        <v>71.9</v>
       </c>
       <c r="G118" t="n">
-        <v>7.7</v>
+        <v>6.4</v>
       </c>
       <c r="H118" t="n">
         <v>50</v>
       </c>
       <c r="I118" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J118" t="n">
-        <v>42.9</v>
+        <v>43.6</v>
       </c>
       <c r="K118" t="n">
-        <v>20.5</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>284</v>
+        <v>214</v>
       </c>
       <c r="B119" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C119" t="n">
-        <v>84.6</v>
+        <v>59.4</v>
       </c>
       <c r="D119" t="n">
-        <v>74.4</v>
-      </c>
-      <c r="E119"/>
+        <v>60.3</v>
+      </c>
+      <c r="E119" t="n">
+        <v>10.3</v>
+      </c>
       <c r="F119" t="n">
-        <v>47.1</v>
+        <v>29</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>8.8</v>
       </c>
       <c r="H119" t="n">
-        <v>45.2</v>
+        <v>40</v>
       </c>
       <c r="I119" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J119" t="n">
-        <v>28.4</v>
+        <v>22.6</v>
       </c>
       <c r="K119" t="n">
-        <v>19.5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B120" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C120" t="n">
-        <v>50</v>
+        <v>67.3</v>
       </c>
       <c r="D120" t="n">
-        <v>45.1</v>
+        <v>63.7</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>28.4</v>
       </c>
       <c r="F120" t="n">
-        <v>25</v>
+        <v>45.9</v>
       </c>
       <c r="G120" t="n">
-        <v>30.8</v>
+        <v>7.3</v>
       </c>
       <c r="H120" t="n">
-        <v>37.5</v>
+        <v>46.7</v>
       </c>
       <c r="I120" t="n">
-        <v>7.7</v>
+        <v>1.8</v>
       </c>
       <c r="J120" t="n">
-        <v>31.2</v>
+        <v>46.8</v>
       </c>
       <c r="K120" t="n">
-        <v>-23.1</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B121" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C121" t="n">
-        <v>61.3</v>
+        <v>84.6</v>
       </c>
       <c r="D121" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="E121" t="n">
-        <v>23.6</v>
-      </c>
+        <v>74.4</v>
+      </c>
+      <c r="E121"/>
       <c r="F121" t="n">
-        <v>31.8</v>
+        <v>47.1</v>
       </c>
       <c r="G121" t="n">
-        <v>16.1</v>
+        <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>50</v>
+        <v>45.2</v>
       </c>
       <c r="I121" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J121" t="n">
-        <v>29.4</v>
+        <v>28.4</v>
       </c>
       <c r="K121" t="n">
-        <v>6.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B122" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C122" t="n">
-        <v>65.8</v>
+        <v>50</v>
       </c>
       <c r="D122" t="n">
-        <v>67.5</v>
+        <v>45.1</v>
       </c>
       <c r="E122" t="n">
-        <v>36.4</v>
+        <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>38.1</v>
+        <v>25</v>
       </c>
       <c r="G122" t="n">
-        <v>7.9</v>
+        <v>30.8</v>
       </c>
       <c r="H122" t="n">
-        <v>53.8</v>
+        <v>37.5</v>
       </c>
       <c r="I122" t="n">
-        <v>2.6</v>
+        <v>7.7</v>
       </c>
       <c r="J122" t="n">
-        <v>26.8</v>
+        <v>31.2</v>
       </c>
       <c r="K122" t="n">
-        <v>13.2</v>
+        <v>-23.1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B123" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C123" t="n">
-        <v>53.5</v>
+        <v>61.3</v>
       </c>
       <c r="D123" t="n">
-        <v>61.1</v>
+        <v>64.8</v>
       </c>
       <c r="E123" t="n">
-        <v>26.4</v>
+        <v>23.6</v>
       </c>
       <c r="F123" t="n">
-        <v>41.2</v>
+        <v>31.8</v>
       </c>
       <c r="G123" t="n">
-        <v>9.9</v>
+        <v>16.1</v>
       </c>
       <c r="H123" t="n">
-        <v>56.5</v>
+        <v>50</v>
       </c>
       <c r="I123" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J123" t="n">
-        <v>22.4</v>
+        <v>29.4</v>
       </c>
       <c r="K123" t="n">
-        <v>10.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B124" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C124" t="n">
-        <v>66.7</v>
+        <v>65.8</v>
       </c>
       <c r="D124" t="n">
-        <v>56.7</v>
+        <v>67.5</v>
       </c>
       <c r="E124" t="n">
-        <v>14.3</v>
+        <v>36.4</v>
       </c>
       <c r="F124" t="n">
-        <v>50</v>
+        <v>38.1</v>
       </c>
       <c r="G124" t="n">
-        <v>22.2</v>
+        <v>7.9</v>
       </c>
       <c r="H124" t="n">
-        <v>20</v>
+        <v>53.8</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="J124" t="n">
-        <v>25</v>
+        <v>26.8</v>
       </c>
       <c r="K124" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B125" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C125" t="n">
-        <v>69.5</v>
+        <v>53.5</v>
       </c>
       <c r="D125" t="n">
-        <v>70.3</v>
+        <v>61.1</v>
       </c>
       <c r="E125" t="n">
-        <v>25</v>
+        <v>26.4</v>
       </c>
       <c r="F125" t="n">
-        <v>50</v>
+        <v>41.2</v>
       </c>
       <c r="G125" t="n">
-        <v>4</v>
+        <v>9.9</v>
       </c>
       <c r="H125" t="n">
-        <v>41.9</v>
+        <v>56.5</v>
       </c>
       <c r="I125" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J125" t="n">
-        <v>26.3</v>
+        <v>22.4</v>
       </c>
       <c r="K125" t="n">
-        <v>18.2</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B126" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C126" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D126" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="E126" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F126" t="n">
+        <v>50</v>
+      </c>
+      <c r="G126" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="H126" t="n">
+        <v>20</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>25</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>294</v>
+      </c>
+      <c r="B127" t="s">
+        <v>162</v>
+      </c>
+      <c r="C127" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="D127" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="E127" t="n">
+        <v>25</v>
+      </c>
+      <c r="F127" t="n">
+        <v>50</v>
+      </c>
+      <c r="G127" t="n">
+        <v>4</v>
+      </c>
+      <c r="H127" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="I127" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J127" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="K127" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>295</v>
+      </c>
+      <c r="B128" t="s">
+        <v>162</v>
+      </c>
+      <c r="C128" t="n">
         <v>63</v>
       </c>
-      <c r="D126" t="n">
+      <c r="D128" t="n">
         <v>64.4</v>
       </c>
-      <c r="E126" t="n">
+      <c r="E128" t="n">
         <v>27</v>
       </c>
-      <c r="F126" t="n">
+      <c r="F128" t="n">
         <v>44.4</v>
       </c>
-      <c r="G126" t="n">
+      <c r="G128" t="n">
         <v>5.4</v>
       </c>
-      <c r="H126" t="n">
+      <c r="H128" t="n">
         <v>45.7</v>
       </c>
-      <c r="I126" t="n">
+      <c r="I128" t="n">
         <v>3.3</v>
       </c>
-      <c r="J126" t="n">
+      <c r="J128" t="n">
         <v>21.8</v>
       </c>
-      <c r="K126" t="n">
+      <c r="K128" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127"/>
-      <c r="B127" t="s">
-        <v>175</v>
-      </c>
-      <c r="C127" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="D127" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="E127" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="F127" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="G127" t="n">
-        <v>11</v>
-      </c>
-      <c r="H127" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="I127" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J127" t="n">
-        <v>25</v>
-      </c>
-      <c r="K127" t="n">
+    <row r="129">
+      <c r="A129"/>
+      <c r="B129" t="s">
+        <v>177</v>
+      </c>
+      <c r="C129" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="D129" t="n">
+        <v>61</v>
+      </c>
+      <c r="E129" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="F129" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="G129" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H129" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="I129" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J129" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="K129" t="n">
         <v>8.2</v>
       </c>
     </row>

--- a/data/summary2026.xlsx
+++ b/data/summary2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="293">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -381,9 +381,6 @@
     <t xml:space="preserve">London Majors</t>
   </si>
   <si>
-    <t xml:space="preserve">Christian Inoa</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cleveland Brownlee</t>
   </si>
   <si>
@@ -396,9 +393,6 @@
     <t xml:space="preserve">Eduardo De Oleo</t>
   </si>
   <si>
-    <t xml:space="preserve">Eduardo DeOleo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jaden Babiuk</t>
   </si>
   <si>
@@ -406,9 +400,6 @@
   </si>
   <si>
     <t xml:space="preserve">Luis Jean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maikol Escitto</t>
   </si>
   <si>
     <t xml:space="preserve">Maikol Escotto</t>
@@ -955,8 +946,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K160" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K160"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K157" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K157"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -4959,31 +4950,31 @@
         <v>121</v>
       </c>
       <c r="C107" t="n">
-        <v>81.8</v>
+        <v>80</v>
       </c>
       <c r="D107" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>60.4</v>
+        <v>80</v>
       </c>
       <c r="F107" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>13.3</v>
+        <v>25</v>
       </c>
       <c r="H107" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>44.4</v>
+        <v>100</v>
       </c>
       <c r="K107" t="n">
-        <v>55.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -4994,31 +4985,31 @@
         <v>121</v>
       </c>
       <c r="C108" t="n">
-        <v>80</v>
+        <v>71.2</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="E108" t="n">
-        <v>80</v>
+        <v>48.1</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="G108" t="n">
-        <v>25</v>
+        <v>10.8</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>35.6</v>
       </c>
       <c r="J108" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="K108" t="n">
-        <v>0</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="109">
@@ -5029,31 +5020,31 @@
         <v>121</v>
       </c>
       <c r="C109" t="n">
-        <v>69.6</v>
+        <v>65.4</v>
       </c>
       <c r="D109" t="n">
-        <v>23.4</v>
+        <v>28.2</v>
       </c>
       <c r="E109" t="n">
-        <v>46.2</v>
+        <v>37.2</v>
       </c>
       <c r="F109" t="n">
-        <v>23.4</v>
+        <v>28.2</v>
       </c>
       <c r="G109" t="n">
-        <v>10.3</v>
+        <v>31.9</v>
       </c>
       <c r="H109" t="n">
-        <v>12.5</v>
+        <v>5.5</v>
       </c>
       <c r="I109" t="n">
-        <v>36.1</v>
+        <v>40.5</v>
       </c>
       <c r="J109" t="n">
-        <v>30.6</v>
+        <v>26.2</v>
       </c>
       <c r="K109" t="n">
-        <v>47.1</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="110">
@@ -5064,31 +5055,31 @@
         <v>121</v>
       </c>
       <c r="C110" t="n">
-        <v>65.4</v>
+        <v>80.8</v>
       </c>
       <c r="D110" t="n">
-        <v>28.2</v>
+        <v>31.4</v>
       </c>
       <c r="E110" t="n">
-        <v>37.2</v>
+        <v>49.4</v>
       </c>
       <c r="F110" t="n">
-        <v>28.2</v>
+        <v>31.4</v>
       </c>
       <c r="G110" t="n">
-        <v>31.9</v>
+        <v>25.4</v>
       </c>
       <c r="H110" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="I110" t="n">
-        <v>40.5</v>
+        <v>40.8</v>
       </c>
       <c r="J110" t="n">
-        <v>26.2</v>
+        <v>29.6</v>
       </c>
       <c r="K110" t="n">
-        <v>42.9</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="111">
@@ -5099,31 +5090,31 @@
         <v>121</v>
       </c>
       <c r="C111" t="n">
-        <v>81</v>
+        <v>53.4</v>
       </c>
       <c r="D111" t="n">
-        <v>31.2</v>
+        <v>28.1</v>
       </c>
       <c r="E111" t="n">
-        <v>49.8</v>
+        <v>25.3</v>
       </c>
       <c r="F111" t="n">
-        <v>31.2</v>
+        <v>28.1</v>
       </c>
       <c r="G111" t="n">
-        <v>24.2</v>
+        <v>19</v>
       </c>
       <c r="H111" t="n">
-        <v>6.2</v>
+        <v>7.9</v>
       </c>
       <c r="I111" t="n">
-        <v>40.3</v>
+        <v>61.9</v>
       </c>
       <c r="J111" t="n">
-        <v>29.9</v>
+        <v>11.9</v>
       </c>
       <c r="K111" t="n">
-        <v>27.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="112">
@@ -5134,31 +5125,31 @@
         <v>121</v>
       </c>
       <c r="C112" t="n">
-        <v>77.8</v>
+        <v>54.6</v>
       </c>
       <c r="D112" t="n">
-        <v>33.3</v>
+        <v>23.1</v>
       </c>
       <c r="E112" t="n">
-        <v>44.5</v>
+        <v>31.5</v>
       </c>
       <c r="F112" t="n">
-        <v>33.3</v>
+        <v>23.1</v>
       </c>
       <c r="G112" t="n">
-        <v>45.5</v>
+        <v>9.4</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="I112" t="n">
-        <v>50</v>
+        <v>60.8</v>
       </c>
       <c r="J112" t="n">
-        <v>25</v>
+        <v>13.5</v>
       </c>
       <c r="K112" t="n">
-        <v>50</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="113">
@@ -5169,31 +5160,31 @@
         <v>121</v>
       </c>
       <c r="C113" t="n">
-        <v>53.4</v>
+        <v>80</v>
       </c>
       <c r="D113" t="n">
-        <v>28.1</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="n">
-        <v>25.3</v>
+        <v>68.9</v>
       </c>
       <c r="F113" t="n">
-        <v>28.1</v>
+        <v>11.1</v>
       </c>
       <c r="G113" t="n">
-        <v>19</v>
+        <v>39.5</v>
       </c>
       <c r="H113" t="n">
-        <v>7.9</v>
+        <v>10</v>
       </c>
       <c r="I113" t="n">
-        <v>61.9</v>
+        <v>63.6</v>
       </c>
       <c r="J113" t="n">
-        <v>11.9</v>
+        <v>9.1</v>
       </c>
       <c r="K113" t="n">
-        <v>52.4</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="114">
@@ -5204,31 +5195,31 @@
         <v>121</v>
       </c>
       <c r="C114" t="n">
-        <v>54.6</v>
+        <v>71.8</v>
       </c>
       <c r="D114" t="n">
-        <v>23.1</v>
+        <v>27.1</v>
       </c>
       <c r="E114" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="F114" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="G114" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H114" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I114" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="J114" t="n">
         <v>31.5</v>
       </c>
-      <c r="F114" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="G114" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="H114" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="I114" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="J114" t="n">
-        <v>13.5</v>
-      </c>
       <c r="K114" t="n">
-        <v>20.5</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="115">
@@ -5239,31 +5230,31 @@
         <v>121</v>
       </c>
       <c r="C115" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>26.7</v>
       </c>
       <c r="E115" t="n">
-        <v>68.9</v>
+        <v>43.3</v>
       </c>
       <c r="F115" t="n">
-        <v>11.1</v>
+        <v>26.7</v>
       </c>
       <c r="G115" t="n">
-        <v>39.5</v>
+        <v>14.8</v>
       </c>
       <c r="H115" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I115" t="n">
+        <v>60</v>
+      </c>
+      <c r="J115" t="n">
+        <v>30</v>
+      </c>
+      <c r="K115" t="n">
         <v>10</v>
-      </c>
-      <c r="I115" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="J115" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="K115" t="n">
-        <v>45.5</v>
       </c>
     </row>
     <row r="116">
@@ -5274,31 +5265,31 @@
         <v>121</v>
       </c>
       <c r="C116" t="n">
-        <v>72.7</v>
+        <v>56.8</v>
       </c>
       <c r="D116" t="n">
-        <v>14.3</v>
+        <v>19.6</v>
       </c>
       <c r="E116" t="n">
-        <v>58.4</v>
+        <v>37.2</v>
       </c>
       <c r="F116" t="n">
-        <v>14.3</v>
+        <v>19.6</v>
       </c>
       <c r="G116" t="n">
-        <v>33.3</v>
+        <v>19.6</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="I116" t="n">
+        <v>50</v>
+      </c>
+      <c r="J116" t="n">
         <v>25</v>
       </c>
-      <c r="J116" t="n">
-        <v>50</v>
-      </c>
       <c r="K116" t="n">
-        <v>25</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="117">
@@ -5309,31 +5300,31 @@
         <v>121</v>
       </c>
       <c r="C117" t="n">
-        <v>71.7</v>
+        <v>72.1</v>
       </c>
       <c r="D117" t="n">
-        <v>27.8</v>
+        <v>22.6</v>
       </c>
       <c r="E117" t="n">
-        <v>43.9</v>
+        <v>49.5</v>
       </c>
       <c r="F117" t="n">
-        <v>27.8</v>
+        <v>22.6</v>
       </c>
       <c r="G117" t="n">
-        <v>20.1</v>
+        <v>32.6</v>
       </c>
       <c r="H117" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="I117" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="J117" t="n">
-        <v>30.7</v>
+        <v>19.4</v>
       </c>
       <c r="K117" t="n">
-        <v>44.3</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="118">
@@ -5344,31 +5335,31 @@
         <v>121</v>
       </c>
       <c r="C118" t="n">
-        <v>70</v>
+        <v>76.3</v>
       </c>
       <c r="D118" t="n">
-        <v>26.7</v>
+        <v>22.4</v>
       </c>
       <c r="E118" t="n">
-        <v>43.3</v>
+        <v>53.9</v>
       </c>
       <c r="F118" t="n">
-        <v>26.7</v>
+        <v>22.4</v>
       </c>
       <c r="G118" t="n">
-        <v>14.8</v>
+        <v>30.3</v>
       </c>
       <c r="H118" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="I118" t="n">
-        <v>60</v>
+        <v>37.9</v>
       </c>
       <c r="J118" t="n">
-        <v>30</v>
+        <v>27.3</v>
       </c>
       <c r="K118" t="n">
-        <v>10</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="119">
@@ -5379,31 +5370,31 @@
         <v>121</v>
       </c>
       <c r="C119" t="n">
-        <v>56.8</v>
+        <v>73.7</v>
       </c>
       <c r="D119" t="n">
-        <v>19.6</v>
+        <v>23.1</v>
       </c>
       <c r="E119" t="n">
-        <v>37.2</v>
+        <v>50.6</v>
       </c>
       <c r="F119" t="n">
-        <v>19.6</v>
+        <v>23.1</v>
       </c>
       <c r="G119" t="n">
-        <v>19.6</v>
+        <v>26.9</v>
       </c>
       <c r="H119" t="n">
-        <v>11.4</v>
+        <v>9.1</v>
       </c>
       <c r="I119" t="n">
-        <v>50</v>
+        <v>41.1</v>
       </c>
       <c r="J119" t="n">
-        <v>25</v>
+        <v>34.2</v>
       </c>
       <c r="K119" t="n">
-        <v>52.6</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="120">
@@ -5414,31 +5405,31 @@
         <v>121</v>
       </c>
       <c r="C120" t="n">
-        <v>72.1</v>
+        <v>67.4</v>
       </c>
       <c r="D120" t="n">
-        <v>22.6</v>
+        <v>21.6</v>
       </c>
       <c r="E120" t="n">
-        <v>49.5</v>
+        <v>45.8</v>
       </c>
       <c r="F120" t="n">
-        <v>22.6</v>
+        <v>21.6</v>
       </c>
       <c r="G120" t="n">
-        <v>32.6</v>
+        <v>14.9</v>
       </c>
       <c r="H120" t="n">
-        <v>9</v>
+        <v>12.9</v>
       </c>
       <c r="I120" t="n">
-        <v>50</v>
+        <v>54.5</v>
       </c>
       <c r="J120" t="n">
-        <v>19.4</v>
+        <v>9.1</v>
       </c>
       <c r="K120" t="n">
-        <v>41.3</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="121">
@@ -5446,133 +5437,133 @@
         <v>136</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="C121" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="D121" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="E121" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="F121" t="n">
-        <v>22.4</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D121"/>
+      <c r="E121"/>
+      <c r="F121"/>
       <c r="G121" t="n">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>37.9</v>
+        <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>27.3</v>
+        <v>100</v>
       </c>
       <c r="K121" t="n">
-        <v>43.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
+        <v>138</v>
+      </c>
+      <c r="B122" t="s">
         <v>137</v>
       </c>
-      <c r="B122" t="s">
-        <v>121</v>
-      </c>
       <c r="C122" t="n">
-        <v>73.7</v>
+        <v>77.8</v>
       </c>
       <c r="D122" t="n">
-        <v>23.1</v>
+        <v>27.3</v>
       </c>
       <c r="E122" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="F122" t="n">
-        <v>23.1</v>
+        <v>27.3</v>
       </c>
       <c r="G122" t="n">
-        <v>26.9</v>
+        <v>17.6</v>
       </c>
       <c r="H122" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>41.1</v>
+        <v>42.9</v>
       </c>
       <c r="J122" t="n">
-        <v>34.2</v>
+        <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>50.7</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B123" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="C123" t="n">
-        <v>67.4</v>
+        <v>66.7</v>
       </c>
       <c r="D123" t="n">
-        <v>21.6</v>
+        <v>60</v>
       </c>
       <c r="E123" t="n">
-        <v>45.8</v>
+        <v>6.7</v>
       </c>
       <c r="F123" t="n">
-        <v>21.6</v>
+        <v>60</v>
       </c>
       <c r="G123" t="n">
-        <v>14.9</v>
+        <v>33.3</v>
       </c>
       <c r="H123" t="n">
-        <v>12.9</v>
+        <v>11.1</v>
       </c>
       <c r="I123" t="n">
-        <v>54.5</v>
+        <v>25</v>
       </c>
       <c r="J123" t="n">
-        <v>9.1</v>
+        <v>25</v>
       </c>
       <c r="K123" t="n">
-        <v>31.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B124" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C124" t="n">
-        <v>100</v>
-      </c>
-      <c r="D124"/>
-      <c r="E124"/>
-      <c r="F124"/>
+        <v>64.6</v>
+      </c>
+      <c r="D124" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E124" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F124" t="n">
+        <v>21.7</v>
+      </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>15.7</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>48.6</v>
       </c>
       <c r="J124" t="n">
-        <v>100</v>
+        <v>21.6</v>
       </c>
       <c r="K124" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="125">
@@ -5580,34 +5571,34 @@
         <v>141</v>
       </c>
       <c r="B125" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C125" t="n">
-        <v>77.8</v>
+        <v>35</v>
       </c>
       <c r="D125" t="n">
-        <v>27.3</v>
+        <v>13.3</v>
       </c>
       <c r="E125" t="n">
-        <v>50.5</v>
+        <v>21.7</v>
       </c>
       <c r="F125" t="n">
-        <v>27.3</v>
+        <v>13.3</v>
       </c>
       <c r="G125" t="n">
-        <v>17.6</v>
+        <v>33.3</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -5615,34 +5606,34 @@
         <v>142</v>
       </c>
       <c r="B126" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C126" t="n">
-        <v>66.7</v>
+        <v>73.1</v>
       </c>
       <c r="D126" t="n">
-        <v>60</v>
+        <v>33.9</v>
       </c>
       <c r="E126" t="n">
-        <v>6.7</v>
+        <v>39.2</v>
       </c>
       <c r="F126" t="n">
-        <v>60</v>
+        <v>33.9</v>
       </c>
       <c r="G126" t="n">
-        <v>33.3</v>
+        <v>35.7</v>
       </c>
       <c r="H126" t="n">
-        <v>11.1</v>
+        <v>7.9</v>
       </c>
       <c r="I126" t="n">
-        <v>25</v>
+        <v>53.8</v>
       </c>
       <c r="J126" t="n">
-        <v>25</v>
+        <v>23.1</v>
       </c>
       <c r="K126" t="n">
-        <v>0</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="127">
@@ -5650,34 +5641,34 @@
         <v>143</v>
       </c>
       <c r="B127" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C127" t="n">
-        <v>64.6</v>
+        <v>71.7</v>
       </c>
       <c r="D127" t="n">
-        <v>21.7</v>
+        <v>27.7</v>
       </c>
       <c r="E127" t="n">
-        <v>42.9</v>
+        <v>44</v>
       </c>
       <c r="F127" t="n">
-        <v>21.7</v>
+        <v>27.7</v>
       </c>
       <c r="G127" t="n">
-        <v>15.7</v>
+        <v>32.8</v>
       </c>
       <c r="H127" t="n">
-        <v>7.7</v>
+        <v>10.8</v>
       </c>
       <c r="I127" t="n">
-        <v>48.6</v>
+        <v>35.9</v>
       </c>
       <c r="J127" t="n">
-        <v>21.6</v>
+        <v>35.9</v>
       </c>
       <c r="K127" t="n">
-        <v>41.7</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="128">
@@ -5685,31 +5676,31 @@
         <v>144</v>
       </c>
       <c r="B128" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C128" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="D128" t="n">
-        <v>13.3</v>
+        <v>36.4</v>
       </c>
       <c r="E128" t="n">
-        <v>21.7</v>
+        <v>23.6</v>
       </c>
       <c r="F128" t="n">
-        <v>13.3</v>
+        <v>36.4</v>
       </c>
       <c r="G128" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I128" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
@@ -5720,34 +5711,34 @@
         <v>145</v>
       </c>
       <c r="B129" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C129" t="n">
-        <v>73.1</v>
+        <v>62.6</v>
       </c>
       <c r="D129" t="n">
-        <v>33.9</v>
+        <v>23.9</v>
       </c>
       <c r="E129" t="n">
-        <v>39.2</v>
+        <v>38.7</v>
       </c>
       <c r="F129" t="n">
-        <v>33.9</v>
+        <v>23.9</v>
       </c>
       <c r="G129" t="n">
-        <v>35.7</v>
+        <v>18.6</v>
       </c>
       <c r="H129" t="n">
-        <v>7.9</v>
+        <v>6.6</v>
       </c>
       <c r="I129" t="n">
-        <v>53.8</v>
+        <v>58.8</v>
       </c>
       <c r="J129" t="n">
-        <v>23.1</v>
+        <v>15.7</v>
       </c>
       <c r="K129" t="n">
-        <v>38.5</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="130">
@@ -5755,34 +5746,34 @@
         <v>146</v>
       </c>
       <c r="B130" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C130" t="n">
-        <v>71.7</v>
+        <v>66.7</v>
       </c>
       <c r="D130" t="n">
-        <v>27.7</v>
+        <v>0</v>
       </c>
       <c r="E130" t="n">
-        <v>44</v>
+        <v>66.7</v>
       </c>
       <c r="F130" t="n">
-        <v>27.7</v>
+        <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>32.8</v>
+        <v>18.2</v>
       </c>
       <c r="H130" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>35.9</v>
+        <v>75</v>
       </c>
       <c r="J130" t="n">
-        <v>35.9</v>
+        <v>25</v>
       </c>
       <c r="K130" t="n">
-        <v>42.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -5790,34 +5781,34 @@
         <v>147</v>
       </c>
       <c r="B131" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C131" t="n">
-        <v>60</v>
+        <v>65.6</v>
       </c>
       <c r="D131" t="n">
-        <v>36.4</v>
+        <v>21.7</v>
       </c>
       <c r="E131" t="n">
-        <v>23.6</v>
+        <v>43.9</v>
       </c>
       <c r="F131" t="n">
-        <v>36.4</v>
+        <v>21.7</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H131" t="n">
-        <v>16.7</v>
+        <v>8</v>
       </c>
       <c r="I131" t="n">
-        <v>40</v>
+        <v>81.2</v>
       </c>
       <c r="J131" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>0</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="132">
@@ -5825,34 +5816,34 @@
         <v>148</v>
       </c>
       <c r="B132" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C132" t="n">
-        <v>62.6</v>
+        <v>51.9</v>
       </c>
       <c r="D132" t="n">
-        <v>23.9</v>
+        <v>15</v>
       </c>
       <c r="E132" t="n">
-        <v>38.7</v>
+        <v>36.9</v>
       </c>
       <c r="F132" t="n">
-        <v>23.9</v>
+        <v>15</v>
       </c>
       <c r="G132" t="n">
-        <v>18.6</v>
+        <v>30</v>
       </c>
       <c r="H132" t="n">
-        <v>6.6</v>
+        <v>13.3</v>
       </c>
       <c r="I132" t="n">
-        <v>58.8</v>
+        <v>71.4</v>
       </c>
       <c r="J132" t="n">
-        <v>15.7</v>
+        <v>28.6</v>
       </c>
       <c r="K132" t="n">
-        <v>35.3</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="133">
@@ -5860,34 +5851,34 @@
         <v>149</v>
       </c>
       <c r="B133" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C133" t="n">
-        <v>66.7</v>
+        <v>67.2</v>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>29.6</v>
       </c>
       <c r="E133" t="n">
-        <v>66.7</v>
+        <v>37.6</v>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>29.6</v>
       </c>
       <c r="G133" t="n">
-        <v>18.2</v>
+        <v>31.5</v>
       </c>
       <c r="H133" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="I133" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="J133" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K133" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="134">
@@ -5895,34 +5886,34 @@
         <v>150</v>
       </c>
       <c r="B134" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C134" t="n">
-        <v>65.6</v>
+        <v>81.8</v>
       </c>
       <c r="D134" t="n">
-        <v>21.7</v>
+        <v>0</v>
       </c>
       <c r="E134" t="n">
-        <v>43.9</v>
+        <v>81.8</v>
       </c>
       <c r="F134" t="n">
-        <v>21.7</v>
+        <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>35</v>
+        <v>11.1</v>
       </c>
       <c r="H134" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>81.2</v>
+        <v>20</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K134" t="n">
-        <v>43.8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="135">
@@ -5930,34 +5921,34 @@
         <v>151</v>
       </c>
       <c r="B135" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C135" t="n">
-        <v>51.9</v>
+        <v>64.7</v>
       </c>
       <c r="D135" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E135" t="n">
-        <v>36.9</v>
+        <v>39.7</v>
       </c>
       <c r="F135" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G135" t="n">
-        <v>30</v>
+        <v>21.2</v>
       </c>
       <c r="H135" t="n">
-        <v>13.3</v>
+        <v>1.4</v>
       </c>
       <c r="I135" t="n">
-        <v>71.4</v>
+        <v>61.1</v>
       </c>
       <c r="J135" t="n">
-        <v>28.6</v>
+        <v>22.2</v>
       </c>
       <c r="K135" t="n">
-        <v>57.1</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="136">
@@ -5965,34 +5956,34 @@
         <v>152</v>
       </c>
       <c r="B136" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C136" t="n">
-        <v>67.2</v>
+        <v>56.1</v>
       </c>
       <c r="D136" t="n">
-        <v>29.6</v>
+        <v>19.2</v>
       </c>
       <c r="E136" t="n">
-        <v>37.6</v>
+        <v>36.9</v>
       </c>
       <c r="F136" t="n">
-        <v>29.6</v>
+        <v>19.2</v>
       </c>
       <c r="G136" t="n">
-        <v>31.5</v>
+        <v>22.5</v>
       </c>
       <c r="H136" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>36</v>
+        <v>40.5</v>
       </c>
       <c r="J136" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K136" t="n">
-        <v>48</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="137">
@@ -6000,34 +5991,34 @@
         <v>153</v>
       </c>
       <c r="B137" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C137" t="n">
-        <v>81.8</v>
+        <v>78.6</v>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
+        <v>39.1</v>
       </c>
       <c r="E137" t="n">
-        <v>81.8</v>
+        <v>39.5</v>
       </c>
       <c r="F137" t="n">
-        <v>0</v>
+        <v>39.1</v>
       </c>
       <c r="G137" t="n">
-        <v>11.1</v>
+        <v>28.9</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>20</v>
+        <v>57.1</v>
       </c>
       <c r="J137" t="n">
-        <v>40</v>
+        <v>14.3</v>
       </c>
       <c r="K137" t="n">
-        <v>20</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="138">
@@ -6035,34 +6026,34 @@
         <v>154</v>
       </c>
       <c r="B138" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C138" t="n">
-        <v>64.7</v>
+        <v>61.5</v>
       </c>
       <c r="D138" t="n">
-        <v>25</v>
+        <v>11.2</v>
       </c>
       <c r="E138" t="n">
-        <v>39.7</v>
+        <v>50.3</v>
       </c>
       <c r="F138" t="n">
-        <v>25</v>
+        <v>11.2</v>
       </c>
       <c r="G138" t="n">
-        <v>21.2</v>
+        <v>9.3</v>
       </c>
       <c r="H138" t="n">
-        <v>1.4</v>
+        <v>8.6</v>
       </c>
       <c r="I138" t="n">
-        <v>61.1</v>
+        <v>49.1</v>
       </c>
       <c r="J138" t="n">
-        <v>22.2</v>
+        <v>10.9</v>
       </c>
       <c r="K138" t="n">
-        <v>30.2</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="139">
@@ -6070,34 +6061,34 @@
         <v>155</v>
       </c>
       <c r="B139" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C139" t="n">
-        <v>56.1</v>
+        <v>63.2</v>
       </c>
       <c r="D139" t="n">
-        <v>19.2</v>
+        <v>45</v>
       </c>
       <c r="E139" t="n">
-        <v>36.9</v>
+        <v>18.2</v>
       </c>
       <c r="F139" t="n">
-        <v>19.2</v>
+        <v>45</v>
       </c>
       <c r="G139" t="n">
-        <v>22.5</v>
+        <v>26.9</v>
       </c>
       <c r="H139" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="I139" t="n">
-        <v>40.5</v>
+        <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K139" t="n">
-        <v>40.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="140">
@@ -6105,34 +6096,34 @@
         <v>156</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C140" t="n">
-        <v>78.6</v>
+        <v>75</v>
       </c>
       <c r="D140" t="n">
-        <v>39.1</v>
+        <v>12.7</v>
       </c>
       <c r="E140" t="n">
-        <v>39.5</v>
+        <v>62.3</v>
       </c>
       <c r="F140" t="n">
-        <v>39.1</v>
+        <v>12.7</v>
       </c>
       <c r="G140" t="n">
-        <v>28.9</v>
+        <v>23.8</v>
       </c>
       <c r="H140" t="n">
-        <v>0</v>
+        <v>15.7</v>
       </c>
       <c r="I140" t="n">
-        <v>57.1</v>
+        <v>29.6</v>
       </c>
       <c r="J140" t="n">
-        <v>14.3</v>
+        <v>37</v>
       </c>
       <c r="K140" t="n">
-        <v>14.3</v>
+        <v>37</v>
       </c>
     </row>
     <row r="141">
@@ -6140,34 +6131,34 @@
         <v>157</v>
       </c>
       <c r="B141" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C141" t="n">
-        <v>61.5</v>
+        <v>74.6</v>
       </c>
       <c r="D141" t="n">
-        <v>11.2</v>
+        <v>25.3</v>
       </c>
       <c r="E141" t="n">
-        <v>50.3</v>
+        <v>49.3</v>
       </c>
       <c r="F141" t="n">
-        <v>11.2</v>
+        <v>25.3</v>
       </c>
       <c r="G141" t="n">
-        <v>9.3</v>
+        <v>8.6</v>
       </c>
       <c r="H141" t="n">
-        <v>8.6</v>
+        <v>2.4</v>
       </c>
       <c r="I141" t="n">
-        <v>49.1</v>
+        <v>46.4</v>
       </c>
       <c r="J141" t="n">
-        <v>10.9</v>
+        <v>23.2</v>
       </c>
       <c r="K141" t="n">
-        <v>35.8</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="142">
@@ -6175,139 +6166,139 @@
         <v>158</v>
       </c>
       <c r="B142" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="C142" t="n">
-        <v>63.2</v>
+        <v>70.6</v>
       </c>
       <c r="D142" t="n">
-        <v>45</v>
+        <v>20.2</v>
       </c>
       <c r="E142" t="n">
-        <v>18.2</v>
+        <v>50.4</v>
       </c>
       <c r="F142" t="n">
-        <v>45</v>
+        <v>20.2</v>
       </c>
       <c r="G142" t="n">
-        <v>26.9</v>
+        <v>36.2</v>
       </c>
       <c r="H142" t="n">
-        <v>7.7</v>
+        <v>9.9</v>
       </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>52.1</v>
       </c>
       <c r="J142" t="n">
-        <v>25</v>
+        <v>22.9</v>
       </c>
       <c r="K142" t="n">
-        <v>25</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
+        <v>160</v>
+      </c>
+      <c r="B143" t="s">
         <v>159</v>
       </c>
-      <c r="B143" t="s">
-        <v>140</v>
-      </c>
       <c r="C143" t="n">
-        <v>75</v>
+        <v>66.4</v>
       </c>
       <c r="D143" t="n">
-        <v>12.7</v>
+        <v>20.8</v>
       </c>
       <c r="E143" t="n">
-        <v>62.3</v>
+        <v>45.6</v>
       </c>
       <c r="F143" t="n">
-        <v>12.7</v>
+        <v>20.8</v>
       </c>
       <c r="G143" t="n">
-        <v>23.8</v>
+        <v>16.1</v>
       </c>
       <c r="H143" t="n">
-        <v>15.7</v>
+        <v>7.4</v>
       </c>
       <c r="I143" t="n">
-        <v>29.6</v>
+        <v>54.7</v>
       </c>
       <c r="J143" t="n">
-        <v>37</v>
+        <v>20.3</v>
       </c>
       <c r="K143" t="n">
-        <v>37</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B144" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="C144" t="n">
-        <v>74.6</v>
+        <v>64.6</v>
       </c>
       <c r="D144" t="n">
-        <v>25.3</v>
+        <v>16.7</v>
       </c>
       <c r="E144" t="n">
-        <v>49.3</v>
+        <v>47.9</v>
       </c>
       <c r="F144" t="n">
-        <v>25.3</v>
+        <v>16.7</v>
       </c>
       <c r="G144" t="n">
-        <v>8.6</v>
+        <v>37.7</v>
       </c>
       <c r="H144" t="n">
-        <v>2.4</v>
+        <v>12.5</v>
       </c>
       <c r="I144" t="n">
-        <v>46.4</v>
+        <v>29.6</v>
       </c>
       <c r="J144" t="n">
-        <v>23.2</v>
+        <v>48.1</v>
       </c>
       <c r="K144" t="n">
-        <v>33.3</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B145" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C145" t="n">
-        <v>70.6</v>
+        <v>57.6</v>
       </c>
       <c r="D145" t="n">
-        <v>20.2</v>
+        <v>21.4</v>
       </c>
       <c r="E145" t="n">
-        <v>50.4</v>
+        <v>36.2</v>
       </c>
       <c r="F145" t="n">
-        <v>20.2</v>
+        <v>21.4</v>
       </c>
       <c r="G145" t="n">
-        <v>36.2</v>
+        <v>33.9</v>
       </c>
       <c r="H145" t="n">
-        <v>9.9</v>
+        <v>13.2</v>
       </c>
       <c r="I145" t="n">
-        <v>52.1</v>
+        <v>27.8</v>
       </c>
       <c r="J145" t="n">
-        <v>22.9</v>
+        <v>38.9</v>
       </c>
       <c r="K145" t="n">
-        <v>40.5</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="146">
@@ -6315,34 +6306,34 @@
         <v>163</v>
       </c>
       <c r="B146" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C146" t="n">
-        <v>66.4</v>
+        <v>65.5</v>
       </c>
       <c r="D146" t="n">
-        <v>20.8</v>
+        <v>15.4</v>
       </c>
       <c r="E146" t="n">
-        <v>45.6</v>
+        <v>50.1</v>
       </c>
       <c r="F146" t="n">
-        <v>20.8</v>
+        <v>15.4</v>
       </c>
       <c r="G146" t="n">
-        <v>16.1</v>
+        <v>10.2</v>
       </c>
       <c r="H146" t="n">
-        <v>7.4</v>
+        <v>16.2</v>
       </c>
       <c r="I146" t="n">
-        <v>54.7</v>
+        <v>63.7</v>
       </c>
       <c r="J146" t="n">
-        <v>20.3</v>
+        <v>17.5</v>
       </c>
       <c r="K146" t="n">
-        <v>41.7</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="147">
@@ -6350,34 +6341,34 @@
         <v>164</v>
       </c>
       <c r="B147" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C147" t="n">
-        <v>64.6</v>
+        <v>79.9</v>
       </c>
       <c r="D147" t="n">
-        <v>16.7</v>
+        <v>14.9</v>
       </c>
       <c r="E147" t="n">
-        <v>47.9</v>
+        <v>65</v>
       </c>
       <c r="F147" t="n">
-        <v>16.7</v>
+        <v>14.9</v>
       </c>
       <c r="G147" t="n">
-        <v>37.7</v>
+        <v>22.1</v>
       </c>
       <c r="H147" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="I147" t="n">
-        <v>29.6</v>
+        <v>37.2</v>
       </c>
       <c r="J147" t="n">
-        <v>48.1</v>
+        <v>33.3</v>
       </c>
       <c r="K147" t="n">
-        <v>38.5</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="148">
@@ -6385,34 +6376,34 @@
         <v>165</v>
       </c>
       <c r="B148" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C148" t="n">
-        <v>57.6</v>
+        <v>54.6</v>
       </c>
       <c r="D148" t="n">
-        <v>21.4</v>
+        <v>16.9</v>
       </c>
       <c r="E148" t="n">
-        <v>36.2</v>
+        <v>37.7</v>
       </c>
       <c r="F148" t="n">
-        <v>21.4</v>
+        <v>16.9</v>
       </c>
       <c r="G148" t="n">
-        <v>33.9</v>
+        <v>27.4</v>
       </c>
       <c r="H148" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="I148" t="n">
-        <v>27.8</v>
+        <v>51.2</v>
       </c>
       <c r="J148" t="n">
-        <v>38.9</v>
+        <v>24.4</v>
       </c>
       <c r="K148" t="n">
-        <v>31.2</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="149">
@@ -6420,34 +6411,34 @@
         <v>166</v>
       </c>
       <c r="B149" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C149" t="n">
-        <v>65.5</v>
+        <v>75</v>
       </c>
       <c r="D149" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="E149" t="n">
-        <v>50.1</v>
+        <v>75</v>
       </c>
       <c r="F149" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>10.2</v>
+        <v>66.7</v>
       </c>
       <c r="H149" t="n">
-        <v>16.2</v>
+        <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>63.7</v>
+        <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>38.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -6455,34 +6446,34 @@
         <v>167</v>
       </c>
       <c r="B150" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C150" t="n">
-        <v>79.9</v>
+        <v>54.7</v>
       </c>
       <c r="D150" t="n">
-        <v>14.9</v>
+        <v>17</v>
       </c>
       <c r="E150" t="n">
-        <v>65</v>
+        <v>37.7</v>
       </c>
       <c r="F150" t="n">
-        <v>14.9</v>
+        <v>17</v>
       </c>
       <c r="G150" t="n">
-        <v>22.1</v>
+        <v>13.2</v>
       </c>
       <c r="H150" t="n">
-        <v>10.5</v>
+        <v>17.1</v>
       </c>
       <c r="I150" t="n">
-        <v>37.2</v>
+        <v>36.2</v>
       </c>
       <c r="J150" t="n">
-        <v>33.3</v>
+        <v>31</v>
       </c>
       <c r="K150" t="n">
-        <v>46.6</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="151">
@@ -6490,34 +6481,34 @@
         <v>168</v>
       </c>
       <c r="B151" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C151" t="n">
-        <v>54.6</v>
+        <v>60.7</v>
       </c>
       <c r="D151" t="n">
-        <v>16.9</v>
+        <v>20.3</v>
       </c>
       <c r="E151" t="n">
-        <v>37.7</v>
+        <v>40.4</v>
       </c>
       <c r="F151" t="n">
-        <v>16.9</v>
+        <v>20.3</v>
       </c>
       <c r="G151" t="n">
-        <v>27.4</v>
+        <v>10.3</v>
       </c>
       <c r="H151" t="n">
-        <v>13</v>
+        <v>8.1</v>
       </c>
       <c r="I151" t="n">
-        <v>51.2</v>
+        <v>58.5</v>
       </c>
       <c r="J151" t="n">
-        <v>24.4</v>
+        <v>18.1</v>
       </c>
       <c r="K151" t="n">
-        <v>32.4</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="152">
@@ -6525,34 +6516,34 @@
         <v>169</v>
       </c>
       <c r="B152" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C152" t="n">
-        <v>75</v>
+        <v>70.9</v>
       </c>
       <c r="D152" t="n">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="E152" t="n">
-        <v>75</v>
+        <v>55.1</v>
       </c>
       <c r="F152" t="n">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="G152" t="n">
-        <v>66.7</v>
+        <v>24</v>
       </c>
       <c r="H152" t="n">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="I152" t="n">
-        <v>0</v>
+        <v>37.8</v>
       </c>
       <c r="J152" t="n">
-        <v>0</v>
+        <v>32.4</v>
       </c>
       <c r="K152" t="n">
-        <v>0</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="153">
@@ -6560,34 +6551,34 @@
         <v>170</v>
       </c>
       <c r="B153" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C153" t="n">
-        <v>54.7</v>
+        <v>78</v>
       </c>
       <c r="D153" t="n">
-        <v>17</v>
+        <v>30.7</v>
       </c>
       <c r="E153" t="n">
-        <v>37.7</v>
+        <v>47.3</v>
       </c>
       <c r="F153" t="n">
-        <v>17</v>
+        <v>30.7</v>
       </c>
       <c r="G153" t="n">
-        <v>13.2</v>
+        <v>39.4</v>
       </c>
       <c r="H153" t="n">
-        <v>17.1</v>
+        <v>8</v>
       </c>
       <c r="I153" t="n">
-        <v>36.2</v>
+        <v>36.4</v>
       </c>
       <c r="J153" t="n">
-        <v>31</v>
+        <v>22.7</v>
       </c>
       <c r="K153" t="n">
-        <v>43.4</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="154">
@@ -6595,34 +6586,34 @@
         <v>171</v>
       </c>
       <c r="B154" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C154" t="n">
-        <v>60.7</v>
+        <v>72.8</v>
       </c>
       <c r="D154" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
       <c r="E154" t="n">
-        <v>40.4</v>
+        <v>52.8</v>
       </c>
       <c r="F154" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
       <c r="G154" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="H154" t="n">
         <v>10.3</v>
       </c>
-      <c r="H154" t="n">
-        <v>8.1</v>
-      </c>
       <c r="I154" t="n">
-        <v>58.5</v>
+        <v>31.1</v>
       </c>
       <c r="J154" t="n">
-        <v>18.1</v>
+        <v>31.1</v>
       </c>
       <c r="K154" t="n">
-        <v>28.9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="155">
@@ -6630,194 +6621,89 @@
         <v>172</v>
       </c>
       <c r="B155" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C155" t="n">
-        <v>70.9</v>
+        <v>37.5</v>
       </c>
       <c r="D155" t="n">
-        <v>15.8</v>
+        <v>33.3</v>
       </c>
       <c r="E155" t="n">
-        <v>55.1</v>
+        <v>4.2</v>
       </c>
       <c r="F155" t="n">
-        <v>15.8</v>
+        <v>33.3</v>
       </c>
       <c r="G155" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="I155" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="J155" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="K155" t="n">
-        <v>59.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I155"/>
+      <c r="J155"/>
+      <c r="K155"/>
     </row>
     <row r="156">
       <c r="A156" t="s">
         <v>173</v>
       </c>
       <c r="B156" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C156" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>30.7</v>
+        <v>33.3</v>
       </c>
       <c r="E156" t="n">
-        <v>47.3</v>
+        <v>-33.3</v>
       </c>
       <c r="F156" t="n">
-        <v>30.7</v>
+        <v>33.3</v>
       </c>
       <c r="G156" t="n">
-        <v>39.4</v>
+        <v>100</v>
       </c>
       <c r="H156" t="n">
-        <v>8</v>
-      </c>
-      <c r="I156" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="J156" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="K156" t="n">
-        <v>68.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I156"/>
+      <c r="J156"/>
+      <c r="K156"/>
     </row>
     <row r="157">
-      <c r="A157" t="s">
+      <c r="A157"/>
+      <c r="B157" t="s">
         <v>174</v>
       </c>
-      <c r="B157" t="s">
-        <v>162</v>
-      </c>
       <c r="C157" t="n">
-        <v>72.8</v>
+        <v>68.8</v>
       </c>
       <c r="D157" t="n">
-        <v>20</v>
+        <v>23.1</v>
       </c>
       <c r="E157" t="n">
-        <v>52.8</v>
+        <v>45.8</v>
       </c>
       <c r="F157" t="n">
-        <v>20</v>
+        <v>23.1</v>
       </c>
       <c r="G157" t="n">
-        <v>17.7</v>
+        <v>26.5</v>
       </c>
       <c r="H157" t="n">
-        <v>10.3</v>
+        <v>9.1</v>
       </c>
       <c r="I157" t="n">
-        <v>31.1</v>
+        <v>47.2</v>
       </c>
       <c r="J157" t="n">
-        <v>31.1</v>
+        <v>25.4</v>
       </c>
       <c r="K157" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>175</v>
-      </c>
-      <c r="B158" t="s">
-        <v>162</v>
-      </c>
-      <c r="C158" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="D158" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="E158" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F158" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G158" t="n">
-        <v>0</v>
-      </c>
-      <c r="H158" t="n">
-        <v>0</v>
-      </c>
-      <c r="I158"/>
-      <c r="J158"/>
-      <c r="K158"/>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>176</v>
-      </c>
-      <c r="B159" t="s">
-        <v>162</v>
-      </c>
-      <c r="C159" t="n">
-        <v>0</v>
-      </c>
-      <c r="D159" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="E159" t="n">
-        <v>-33.3</v>
-      </c>
-      <c r="F159" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G159" t="n">
-        <v>100</v>
-      </c>
-      <c r="H159" t="n">
-        <v>0</v>
-      </c>
-      <c r="I159"/>
-      <c r="J159"/>
-      <c r="K159"/>
-    </row>
-    <row r="160">
-      <c r="A160"/>
-      <c r="B160" t="s">
-        <v>177</v>
-      </c>
-      <c r="C160" t="n">
-        <v>68.9</v>
-      </c>
-      <c r="D160" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="E160" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="F160" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="G160" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="H160" t="n">
-        <v>9</v>
-      </c>
-      <c r="I160" t="n">
-        <v>47</v>
-      </c>
-      <c r="J160" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="K160" t="n">
         <v>39</v>
       </c>
     </row>
@@ -6850,22 +6736,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -6874,18 +6760,18 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -6920,7 +6806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -6990,7 +6876,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -7060,7 +6946,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -7095,7 +6981,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -7130,7 +7016,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -7200,7 +7086,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -7235,7 +7121,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -7270,7 +7156,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -7305,7 +7191,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -7373,7 +7259,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
@@ -7408,7 +7294,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
@@ -7443,7 +7329,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
@@ -7513,7 +7399,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
@@ -7548,7 +7434,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
@@ -7583,7 +7469,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B22" t="s">
         <v>34</v>
@@ -7618,7 +7504,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B23" t="s">
         <v>34</v>
@@ -7653,7 +7539,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B24" t="s">
         <v>34</v>
@@ -7688,7 +7574,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B25" t="s">
         <v>34</v>
@@ -7723,7 +7609,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
@@ -7758,7 +7644,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B27" t="s">
         <v>34</v>
@@ -7793,7 +7679,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B28" t="s">
         <v>34</v>
@@ -7828,7 +7714,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B29" t="s">
         <v>34</v>
@@ -7863,7 +7749,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B30" t="s">
         <v>34</v>
@@ -7898,7 +7784,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B31" t="s">
         <v>34</v>
@@ -7933,7 +7819,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B32" t="s">
         <v>51</v>
@@ -7968,7 +7854,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B33" t="s">
         <v>51</v>
@@ -8003,7 +7889,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B34" t="s">
         <v>51</v>
@@ -8036,7 +7922,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B35" t="s">
         <v>51</v>
@@ -8106,7 +7992,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B37" t="s">
         <v>51</v>
@@ -8141,7 +8027,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B38" t="s">
         <v>51</v>
@@ -8176,7 +8062,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B39" t="s">
         <v>51</v>
@@ -8211,7 +8097,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B40" t="s">
         <v>51</v>
@@ -8244,7 +8130,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B41" t="s">
         <v>51</v>
@@ -8279,7 +8165,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B42" t="s">
         <v>51</v>
@@ -8314,7 +8200,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B43" t="s">
         <v>51</v>
@@ -8349,7 +8235,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B44" t="s">
         <v>51</v>
@@ -8384,7 +8270,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B45" t="s">
         <v>51</v>
@@ -8419,7 +8305,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B46" t="s">
         <v>51</v>
@@ -8454,7 +8340,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B47" t="s">
         <v>51</v>
@@ -8487,7 +8373,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B48" t="s">
         <v>51</v>
@@ -8522,7 +8408,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B49" t="s">
         <v>68</v>
@@ -8557,7 +8443,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B50" t="s">
         <v>68</v>
@@ -8592,7 +8478,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B51" t="s">
         <v>68</v>
@@ -8627,7 +8513,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B52" t="s">
         <v>68</v>
@@ -8660,7 +8546,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B53" t="s">
         <v>68</v>
@@ -8695,7 +8581,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B54" t="s">
         <v>68</v>
@@ -8730,7 +8616,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B55" t="s">
         <v>68</v>
@@ -8763,7 +8649,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B56" t="s">
         <v>68</v>
@@ -8798,7 +8684,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B57" t="s">
         <v>68</v>
@@ -8833,7 +8719,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B58" t="s">
         <v>68</v>
@@ -8868,7 +8754,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B59" t="s">
         <v>68</v>
@@ -8903,7 +8789,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B60" t="s">
         <v>68</v>
@@ -8938,7 +8824,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B61" t="s">
         <v>68</v>
@@ -9008,7 +8894,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B63" t="s">
         <v>68</v>
@@ -9078,7 +8964,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B65" t="s">
         <v>91</v>
@@ -9113,7 +8999,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B66" t="s">
         <v>91</v>
@@ -9148,7 +9034,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B67" t="s">
         <v>91</v>
@@ -9183,7 +9069,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B68" t="s">
         <v>91</v>
@@ -9218,7 +9104,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B69" t="s">
         <v>91</v>
@@ -9253,7 +9139,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B70" t="s">
         <v>91</v>
@@ -9288,7 +9174,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B71" t="s">
         <v>91</v>
@@ -9323,7 +9209,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B72" t="s">
         <v>91</v>
@@ -9358,7 +9244,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B73" t="s">
         <v>91</v>
@@ -9393,7 +9279,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B74" t="s">
         <v>91</v>
@@ -9428,7 +9314,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B75" t="s">
         <v>91</v>
@@ -9463,7 +9349,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B76" t="s">
         <v>91</v>
@@ -9498,7 +9384,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B77" t="s">
         <v>105</v>
@@ -9533,7 +9419,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B78" t="s">
         <v>105</v>
@@ -9568,7 +9454,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B79" t="s">
         <v>105</v>
@@ -9603,7 +9489,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B80" t="s">
         <v>105</v>
@@ -9636,7 +9522,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B81" t="s">
         <v>105</v>
@@ -9706,7 +9592,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B83" t="s">
         <v>105</v>
@@ -9741,7 +9627,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B84" t="s">
         <v>105</v>
@@ -9776,7 +9662,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B85" t="s">
         <v>105</v>
@@ -9811,7 +9697,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B86" t="s">
         <v>105</v>
@@ -9846,7 +9732,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B87" t="s">
         <v>105</v>
@@ -9881,7 +9767,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B88" t="s">
         <v>105</v>
@@ -9916,7 +9802,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B89" t="s">
         <v>105</v>
@@ -9951,7 +9837,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B90" t="s">
         <v>121</v>
@@ -9986,7 +9872,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B91" t="s">
         <v>121</v>
@@ -10021,7 +9907,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B92" t="s">
         <v>121</v>
@@ -10056,7 +9942,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B93" t="s">
         <v>121</v>
@@ -10091,7 +9977,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B94" t="s">
         <v>121</v>
@@ -10126,7 +10012,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B95" t="s">
         <v>121</v>
@@ -10161,7 +10047,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B96" t="s">
         <v>121</v>
@@ -10196,7 +10082,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B97" t="s">
         <v>121</v>
@@ -10231,7 +10117,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B98" t="s">
         <v>121</v>
@@ -10266,7 +10152,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B99" t="s">
         <v>121</v>
@@ -10301,10 +10187,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B100" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C100" t="n">
         <v>33.3</v>
@@ -10336,10 +10222,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B101" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C101" t="n">
         <v>50</v>
@@ -10371,10 +10257,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B102" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C102" t="n">
         <v>51.6</v>
@@ -10406,10 +10292,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B103" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C103" t="n">
         <v>62</v>
@@ -10441,10 +10327,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B104" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C104" t="n">
         <v>50</v>
@@ -10474,10 +10360,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B105" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C105" t="n">
         <v>69.7</v>
@@ -10509,10 +10395,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B106" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C106" t="n">
         <v>54.1</v>
@@ -10544,10 +10430,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B107" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C107" t="n">
         <v>51.6</v>
@@ -10579,10 +10465,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B108" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C108" t="n">
         <v>60</v>
@@ -10614,10 +10500,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B109" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C109" t="n">
         <v>52.6</v>
@@ -10649,10 +10535,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B110" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C110" t="n">
         <v>61.3</v>
@@ -10684,10 +10570,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B111" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C111" t="n">
         <v>59.7</v>
@@ -10719,10 +10605,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B112" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C112" t="n">
         <v>44</v>
@@ -10754,10 +10640,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B113" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C113" t="n">
         <v>38.9</v>
@@ -10789,10 +10675,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B114" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C114" t="n">
         <v>59.2</v>
@@ -10824,10 +10710,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B115" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C115" t="n">
         <v>57.9</v>
@@ -10859,10 +10745,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B116" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C116" t="n">
         <v>62.4</v>
@@ -10894,10 +10780,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B117" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C117" t="n">
         <v>60.7</v>
@@ -10929,10 +10815,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B118" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C118" t="n">
         <v>60.4</v>
@@ -10964,10 +10850,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B119" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C119" t="n">
         <v>59.4</v>
@@ -10999,10 +10885,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B120" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C120" t="n">
         <v>67.3</v>
@@ -11034,10 +10920,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B121" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C121" t="n">
         <v>84.6</v>
@@ -11067,10 +10953,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B122" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C122" t="n">
         <v>50</v>
@@ -11102,10 +10988,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B123" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C123" t="n">
         <v>61.3</v>
@@ -11137,10 +11023,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B124" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C124" t="n">
         <v>65.8</v>
@@ -11172,10 +11058,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B125" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C125" t="n">
         <v>53.5</v>
@@ -11207,10 +11093,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B126" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C126" t="n">
         <v>66.7</v>
@@ -11242,10 +11128,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B127" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C127" t="n">
         <v>69.5</v>
@@ -11277,10 +11163,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B128" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C128" t="n">
         <v>63</v>
@@ -11313,7 +11199,7 @@
     <row r="129">
       <c r="A129"/>
       <c r="B129" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C129" t="n">
         <v>58.3</v>
